--- a/data/REY.MI.xlsx
+++ b/data/REY.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">29.255973815918</t>
+    <t xml:space="preserve">29.2559719085693</t>
   </si>
   <si>
     <t xml:space="preserve">REY.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">28.8380298614502</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3272075653076</t>
+    <t xml:space="preserve">28.3272113800049</t>
   </si>
   <si>
     <t xml:space="preserve">27.6306400299072</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8396091461182</t>
+    <t xml:space="preserve">27.8396129608154</t>
   </si>
   <si>
     <t xml:space="preserve">28.2111186981201</t>
@@ -62,25 +62,25 @@
     <t xml:space="preserve">29.0005626678467</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5594005584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1414566040039</t>
+    <t xml:space="preserve">28.5594043731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1414585113525</t>
   </si>
   <si>
     <t xml:space="preserve">27.1198215484619</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9789257049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8644142150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4448871612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.932487487793</t>
+    <t xml:space="preserve">27.9789276123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8644104003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4448890686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9324855804443</t>
   </si>
   <si>
     <t xml:space="preserve">27.8163909912109</t>
@@ -92,34 +92,34 @@
     <t xml:space="preserve">27.6770763397217</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0950222015381</t>
+    <t xml:space="preserve">28.0950202941895</t>
   </si>
   <si>
     <t xml:space="preserve">27.8628311157227</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2591342926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7018775939941</t>
+    <t xml:space="preserve">27.2591361999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7018795013428</t>
   </si>
   <si>
     <t xml:space="preserve">26.1678409576416</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2855186462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.379976272583</t>
+    <t xml:space="preserve">25.2855167388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3799743652344</t>
   </si>
   <si>
     <t xml:space="preserve">24.6121673583984</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0053081512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5177097320557</t>
+    <t xml:space="preserve">26.0053100585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5177116394043</t>
   </si>
   <si>
     <t xml:space="preserve">25.6570224761963</t>
@@ -128,163 +128,163 @@
     <t xml:space="preserve">27.6074199676514</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3071537017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0733833312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2142791748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4696865081787</t>
+    <t xml:space="preserve">26.3071556091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0733814239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2142810821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.469690322876</t>
   </si>
   <si>
     <t xml:space="preserve">26.0517463684082</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7034587860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7266826629639</t>
+    <t xml:space="preserve">25.7034606933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7266807556152</t>
   </si>
   <si>
     <t xml:space="preserve">26.7483177185059</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4929103851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.352014541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1894798278809</t>
+    <t xml:space="preserve">26.4929065704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3520107269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1894779205322</t>
   </si>
   <si>
     <t xml:space="preserve">27.2359161376953</t>
   </si>
   <si>
-    <t xml:space="preserve">27.166259765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9092693328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0237846374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5546550750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3008308410645</t>
+    <t xml:space="preserve">27.1662616729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9092655181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0237808227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5546493530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3008270263672</t>
   </si>
   <si>
     <t xml:space="preserve">30.4169235229492</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9989814758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9757633209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7900085449219</t>
+    <t xml:space="preserve">29.9989776611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9757614135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7900123596191</t>
   </si>
   <si>
     <t xml:space="preserve">29.952543258667</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2311706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7203502655029</t>
+    <t xml:space="preserve">30.2311687469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7203521728516</t>
   </si>
   <si>
     <t xml:space="preserve">30.0686359405518</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8596649169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5578193664551</t>
+    <t xml:space="preserve">29.8596668243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5578212738037</t>
   </si>
   <si>
     <t xml:space="preserve">29.3256301879883</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4881629943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.511381149292</t>
+    <t xml:space="preserve">29.4881610870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5113792419434</t>
   </si>
   <si>
     <t xml:space="preserve">29.2095355987549</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1615104675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3720645904541</t>
+    <t xml:space="preserve">30.1615123748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3720684051514</t>
   </si>
   <si>
     <t xml:space="preserve">29.5345993041992</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4433078765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6754932403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8612461090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8148078918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9076824188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.629056930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4200859069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6776008605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.560546875</t>
+    <t xml:space="preserve">28.4433059692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6754989624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8612480163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.814811706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9076862335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6290588378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4200878143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6776027679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5605487823486</t>
   </si>
   <si>
     <t xml:space="preserve">29.0287532806396</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3264465332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5137310028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7946510314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0053443908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2628593444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1992683410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5036029815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5504245758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.901575088501</t>
+    <t xml:space="preserve">28.3264484405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.513729095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7946548461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0053424835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2628574371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1992702484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5036010742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.550422668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9015769958496</t>
   </si>
   <si>
     <t xml:space="preserve">30.6674747467041</t>
@@ -293,43 +293,43 @@
     <t xml:space="preserve">30.7142944335938</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4567813873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4333724975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2694969177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8949317932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1859874725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3096790313721</t>
+    <t xml:space="preserve">30.4567852020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.43337059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2694988250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8949337005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1859817504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3096771240234</t>
   </si>
   <si>
     <t xml:space="preserve">29.4969635009766</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6943683624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7747230529785</t>
+    <t xml:space="preserve">27.6943702697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7747249603271</t>
   </si>
   <si>
     <t xml:space="preserve">26.8047771453857</t>
   </si>
   <si>
-    <t xml:space="preserve">27.319803237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9218273162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5070838928223</t>
+    <t xml:space="preserve">27.3198013305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9218292236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5070858001709</t>
   </si>
   <si>
     <t xml:space="preserve">26.945240020752</t>
@@ -344,16 +344,16 @@
     <t xml:space="preserve">27.10910987854</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6241397857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3666229248047</t>
+    <t xml:space="preserve">27.6241359710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3666248321533</t>
   </si>
   <si>
     <t xml:space="preserve">28.303035736084</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8882923126221</t>
+    <t xml:space="preserve">28.8882904052734</t>
   </si>
   <si>
     <t xml:space="preserve">28.7478313446045</t>
@@ -362,13 +362,13 @@
     <t xml:space="preserve">28.4435005187988</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9819355010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9117012023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3799076080322</t>
+    <t xml:space="preserve">28.98193359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9117069244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3799095153809</t>
   </si>
   <si>
     <t xml:space="preserve">29.4501419067383</t>
@@ -380,16 +380,16 @@
     <t xml:space="preserve">30.1524467468262</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9651641845703</t>
+    <t xml:space="preserve">29.9651660919189</t>
   </si>
   <si>
     <t xml:space="preserve">28.7244186401367</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1458034515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0989837646484</t>
+    <t xml:space="preserve">29.1458053588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0989856719971</t>
   </si>
   <si>
     <t xml:space="preserve">28.9351139068604</t>
@@ -398,79 +398,79 @@
     <t xml:space="preserve">28.4903182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9752902984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3732643127441</t>
+    <t xml:space="preserve">27.9752941131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3732662200928</t>
   </si>
   <si>
     <t xml:space="preserve">28.0923442840576</t>
   </si>
   <si>
-    <t xml:space="preserve">27.272985458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0622882843018</t>
+    <t xml:space="preserve">27.2729835510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0622901916504</t>
   </si>
   <si>
     <t xml:space="preserve">27.0388793945312</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8984184265137</t>
+    <t xml:space="preserve">26.898416519165</t>
   </si>
   <si>
     <t xml:space="preserve">26.1492881774902</t>
   </si>
   <si>
-    <t xml:space="preserve">25.798131942749</t>
+    <t xml:space="preserve">25.7981376647949</t>
   </si>
   <si>
     <t xml:space="preserve">25.8917770385742</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7579574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9518852233887</t>
+    <t xml:space="preserve">26.7579536437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9518814086914</t>
   </si>
   <si>
     <t xml:space="preserve">27.8816471099854</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8114204406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9050579071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2963943481445</t>
+    <t xml:space="preserve">27.8114223480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9050598144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2963924407959</t>
   </si>
   <si>
     <t xml:space="preserve">27.8582401275635</t>
   </si>
   <si>
-    <t xml:space="preserve">27.577320098877</t>
+    <t xml:space="preserve">27.5773181915283</t>
   </si>
   <si>
     <t xml:space="preserve">27.7177772521973</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7411861419678</t>
+    <t xml:space="preserve">27.7411880493164</t>
   </si>
   <si>
     <t xml:space="preserve">28.0455207824707</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7880077362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3900337219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1223945617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6541881561279</t>
+    <t xml:space="preserve">27.7880096435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3900356292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1223926544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6541900634766</t>
   </si>
   <si>
     <t xml:space="preserve">28.2093963623047</t>
@@ -479,22 +479,22 @@
     <t xml:space="preserve">27.413444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0857009887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8515949249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4368572235107</t>
+    <t xml:space="preserve">27.0856990814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.851598739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4368553161621</t>
   </si>
   <si>
     <t xml:space="preserve">26.6877250671387</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2261638641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8281841278076</t>
+    <t xml:space="preserve">27.2261619567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8281879425049</t>
   </si>
   <si>
     <t xml:space="preserve">26.640905380249</t>
@@ -503,10 +503,10 @@
     <t xml:space="preserve">26.4536228179932</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5706748962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.523853302002</t>
+    <t xml:space="preserve">26.5706729888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5238552093506</t>
   </si>
   <si>
     <t xml:space="preserve">26.3365707397461</t>
@@ -515,34 +515,34 @@
     <t xml:space="preserve">25.7513122558594</t>
   </si>
   <si>
-    <t xml:space="preserve">25.329927444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7446708679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7680816650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8851337432861</t>
+    <t xml:space="preserve">25.3299293518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7446689605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7680797576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8851318359375</t>
   </si>
   <si>
     <t xml:space="preserve">24.2530555725098</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0490055084229</t>
+    <t xml:space="preserve">25.0490036010742</t>
   </si>
   <si>
     <t xml:space="preserve">25.4703903198242</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5172100067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2831077575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1660594940186</t>
+    <t xml:space="preserve">25.5172080993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2831039428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1660556793213</t>
   </si>
   <si>
     <t xml:space="preserve">25.4469814300537</t>
@@ -551,19 +551,19 @@
     <t xml:space="preserve">25.0958251953125</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9319534301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0724182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6342620849609</t>
+    <t xml:space="preserve">24.9319553375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.072416305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6342601776123</t>
   </si>
   <si>
     <t xml:space="preserve">26.1961116790771</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1726989746094</t>
+    <t xml:space="preserve">26.172700881958</t>
   </si>
   <si>
     <t xml:space="preserve">27.8348293304443</t>
@@ -575,73 +575,73 @@
     <t xml:space="preserve">27.4602661132812</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9987010955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6307792663574</t>
+    <t xml:space="preserve">27.9986991882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6307811737061</t>
   </si>
   <si>
     <t xml:space="preserve">29.2160396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3330879211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8648815155029</t>
+    <t xml:space="preserve">29.3330917358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8648834228516</t>
   </si>
   <si>
     <t xml:space="preserve">28.3498554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6073703765869</t>
+    <t xml:space="preserve">28.6073665618896</t>
   </si>
   <si>
     <t xml:space="preserve">29.4735507965088</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2394485473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7076530456543</t>
+    <t xml:space="preserve">29.2394466400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7076511383057</t>
   </si>
   <si>
     <t xml:space="preserve">29.4267292022705</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8313426971436</t>
+    <t xml:space="preserve">30.8313484191895</t>
   </si>
   <si>
     <t xml:space="preserve">30.9952182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4868335723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2527332305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3697814941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.135684967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1891479492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3061943054199</t>
+    <t xml:space="preserve">31.486837387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2527294158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3697853088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1356773376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1891441345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3061904907227</t>
   </si>
   <si>
     <t xml:space="preserve">33.2660179138184</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0619697570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6472206115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4599456787109</t>
+    <t xml:space="preserve">34.0619621276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6472244262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4599342346191</t>
   </si>
   <si>
     <t xml:space="preserve">34.7408599853516</t>
@@ -650,31 +650,31 @@
     <t xml:space="preserve">34.6706352233887</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9983787536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8579063415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.179012298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7642707824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8813323974609</t>
+    <t xml:space="preserve">34.9983749389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8579139709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1790161132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7642669677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8813247680664</t>
   </si>
   <si>
     <t xml:space="preserve">34.389705657959</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4131278991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6070442199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4665794372559</t>
+    <t xml:space="preserve">34.4131202697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.607048034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4665832519531</t>
   </si>
   <si>
     <t xml:space="preserve">35.7943267822266</t>
@@ -683,55 +683,55 @@
     <t xml:space="preserve">36.8243789672852</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6671447753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8778495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9882545471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5735054016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6203308105469</t>
+    <t xml:space="preserve">37.6671524047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8778419494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9882469177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5735092163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6203269958496</t>
   </si>
   <si>
     <t xml:space="preserve">37.6085395812988</t>
   </si>
   <si>
-    <t xml:space="preserve">37.726432800293</t>
+    <t xml:space="preserve">37.7264404296875</t>
   </si>
   <si>
     <t xml:space="preserve">37.9150695800781</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1980094909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9386405944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1508636474609</t>
+    <t xml:space="preserve">38.1980171203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9386444091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1508560180664</t>
   </si>
   <si>
     <t xml:space="preserve">37.4906463623047</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0232849121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.084342956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0607604980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8013916015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2397003173828</t>
+    <t xml:space="preserve">39.0232772827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0843353271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0607566833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8013877868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2397079467773</t>
   </si>
   <si>
     <t xml:space="preserve">41.0275001525879</t>
@@ -743,22 +743,22 @@
     <t xml:space="preserve">41.7112922668457</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4990768432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8056106567383</t>
+    <t xml:space="preserve">41.499080657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.805606842041</t>
   </si>
   <si>
     <t xml:space="preserve">42.3243446350098</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1828727722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0885543823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2771835327148</t>
+    <t xml:space="preserve">42.1828689575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.088550567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2771873474121</t>
   </si>
   <si>
     <t xml:space="preserve">41.8291816711426</t>
@@ -767,25 +767,25 @@
     <t xml:space="preserve">39.9664421081543</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5891761779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4338035583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9997062683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6363334655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9428596496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4380264282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5517044067383</t>
+    <t xml:space="preserve">39.5891723632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4338073730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.999698638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6363372802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9428634643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4380187988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.551700592041</t>
   </si>
   <si>
     <t xml:space="preserve">38.0565376281738</t>
@@ -794,43 +794,43 @@
     <t xml:space="preserve">39.1411781311035</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3298110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0704383850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1647529602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6695899963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8346519470215</t>
+    <t xml:space="preserve">39.3298072814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0704345703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1647567749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6695976257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8346481323242</t>
   </si>
   <si>
     <t xml:space="preserve">38.905387878418</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0940208435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8110694885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2687492370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7403373718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6931838989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2354927062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2590637207031</t>
+    <t xml:space="preserve">39.0940170288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8110733032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2687530517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7403297424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.693172454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2354888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2590713500977</t>
   </si>
   <si>
     <t xml:space="preserve">42.1357116699219</t>
@@ -839,16 +839,16 @@
     <t xml:space="preserve">42.5129776000977</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7765579223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8001365661621</t>
+    <t xml:space="preserve">44.7765617370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8001403808594</t>
   </si>
   <si>
     <t xml:space="preserve">45.507511138916</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3188743591309</t>
+    <t xml:space="preserve">45.3188781738281</t>
   </si>
   <si>
     <t xml:space="preserve">45.814037322998</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">43.7862396240234</t>
   </si>
   <si>
-    <t xml:space="preserve">44.752986907959</t>
+    <t xml:space="preserve">44.7529754638672</t>
   </si>
   <si>
     <t xml:space="preserve">45.1302452087402</t>
@@ -869,13 +869,13 @@
     <t xml:space="preserve">44.4464569091797</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5879325866699</t>
+    <t xml:space="preserve">44.5879287719727</t>
   </si>
   <si>
     <t xml:space="preserve">44.3285598754883</t>
   </si>
   <si>
-    <t xml:space="preserve">44.3049812316895</t>
+    <t xml:space="preserve">44.3049774169922</t>
   </si>
   <si>
     <t xml:space="preserve">43.6211853027344</t>
@@ -890,19 +890,19 @@
     <t xml:space="preserve">42.5837135314941</t>
   </si>
   <si>
-    <t xml:space="preserve">43.267505645752</t>
+    <t xml:space="preserve">43.2675018310547</t>
   </si>
   <si>
     <t xml:space="preserve">45.3660316467285</t>
   </si>
   <si>
-    <t xml:space="preserve">44.98876953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4936103820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.5171966552734</t>
+    <t xml:space="preserve">44.9887657165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4936180114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.5171890258789</t>
   </si>
   <si>
     <t xml:space="preserve">45.6254043579102</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">45.8611946105957</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4035186767578</t>
+    <t xml:space="preserve">46.4035148620605</t>
   </si>
   <si>
     <t xml:space="preserve">47.5824661254883</t>
@@ -923,34 +923,34 @@
     <t xml:space="preserve">47.134464263916</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1580429077148</t>
+    <t xml:space="preserve">47.1580467224121</t>
   </si>
   <si>
     <t xml:space="preserve">47.9125747680664</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3508911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7378349304199</t>
+    <t xml:space="preserve">49.350887298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7378387451172</t>
   </si>
   <si>
     <t xml:space="preserve">48.1012001037598</t>
   </si>
   <si>
-    <t xml:space="preserve">48.8321533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6296234130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0540542602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8654174804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9597320556641</t>
+    <t xml:space="preserve">48.8321571350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6296195983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0540504455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8654098510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9597282409668</t>
   </si>
   <si>
     <t xml:space="preserve">49.1858406066895</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">45.2717170715332</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0359306335449</t>
+    <t xml:space="preserve">45.0359268188477</t>
   </si>
   <si>
     <t xml:space="preserve">44.5643501281738</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">43.9748802185059</t>
   </si>
   <si>
-    <t xml:space="preserve">42.560131072998</t>
+    <t xml:space="preserve">42.5601348876953</t>
   </si>
   <si>
     <t xml:space="preserve">42.9138221740723</t>
@@ -977,13 +977,13 @@
     <t xml:space="preserve">42.7251892089844</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2064476013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4328079223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1781578063965</t>
+    <t xml:space="preserve">42.2064514160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4328117370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.178150177002</t>
   </si>
   <si>
     <t xml:space="preserve">43.3476715087891</t>
@@ -992,19 +992,19 @@
     <t xml:space="preserve">41.9800872802734</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3010139465332</t>
+    <t xml:space="preserve">41.3010101318359</t>
   </si>
   <si>
     <t xml:space="preserve">42.0838394165039</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7534828186035</t>
+    <t xml:space="preserve">42.7534790039062</t>
   </si>
   <si>
     <t xml:space="preserve">42.5931434631348</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4799652099609</t>
+    <t xml:space="preserve">42.4799690246582</t>
   </si>
   <si>
     <t xml:space="preserve">43.0081367492676</t>
@@ -1025,88 +1025,88 @@
     <t xml:space="preserve">44.2342491149902</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1210594177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2439193725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1027030944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1689720153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2729759216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4045104980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7626724243164</t>
+    <t xml:space="preserve">44.1210632324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2439231872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1026992797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1689796447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2729644775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4045143127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7626686096191</t>
   </si>
   <si>
     <t xml:space="preserve">44.2531051635742</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0547943115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.951042175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2809028625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1488609313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3094482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9981994628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5358085632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1679763793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.592399597168</t>
+    <t xml:space="preserve">45.0547981262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9510459899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2809066772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1488571166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3094444274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9982109069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5358047485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1679725646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5923957824707</t>
   </si>
   <si>
     <t xml:space="preserve">44.6586647033691</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2533569335938</t>
+    <t xml:space="preserve">43.253360748291</t>
   </si>
   <si>
     <t xml:space="preserve">43.6683502197266</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2248153686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0830841064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2056922912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3280563354492</t>
+    <t xml:space="preserve">44.2248077392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0830917358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.205696105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3280639648438</t>
   </si>
   <si>
     <t xml:space="preserve">46.0356826782227</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6584167480469</t>
+    <t xml:space="preserve">45.6584205627441</t>
   </si>
   <si>
     <t xml:space="preserve">45.5169410705566</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1682243347168</t>
+    <t xml:space="preserve">44.1682281494141</t>
   </si>
   <si>
     <t xml:space="preserve">43.8664093017578</t>
@@ -1115,55 +1115,55 @@
     <t xml:space="preserve">43.5457344055176</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8852767944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4606018066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.611255645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.630126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7244415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.290340423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.026252746582</t>
+    <t xml:space="preserve">43.8852806091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4605979919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6112670898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6301231384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.724437713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2903366088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0262489318848</t>
   </si>
   <si>
     <t xml:space="preserve">46.2148857116699</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6487312316895</t>
+    <t xml:space="preserve">46.6487350463867</t>
   </si>
   <si>
     <t xml:space="preserve">46.705322265625</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5921478271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8939590454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7711029052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8182563781738</t>
+    <t xml:space="preserve">46.5921516418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8939628601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7710990905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8182601928711</t>
   </si>
   <si>
     <t xml:space="preserve">48.1955146789551</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9972114562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5727806091309</t>
+    <t xml:space="preserve">48.9972076416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5727844238281</t>
   </si>
   <si>
     <t xml:space="preserve">49.3273124694824</t>
@@ -1172,7 +1172,7 @@
     <t xml:space="preserve">50.3176307678223</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4119529724121</t>
+    <t xml:space="preserve">50.4119491577148</t>
   </si>
   <si>
     <t xml:space="preserve">49.8460464477539</t>
@@ -1181,22 +1181,22 @@
     <t xml:space="preserve">49.3744735717773</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2233123779297</t>
+    <t xml:space="preserve">50.223316192627</t>
   </si>
   <si>
     <t xml:space="preserve">50.0818405151367</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5353126525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1960220336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2052001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0068893432617</t>
+    <t xml:space="preserve">47.5353088378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1960182189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2052040100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.006893157959</t>
   </si>
   <si>
     <t xml:space="preserve">47.2523574829102</t>
@@ -1205,16 +1205,16 @@
     <t xml:space="preserve">46.4223785400391</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8376197814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6489906311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8753433227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5732917785645</t>
+    <t xml:space="preserve">45.8376083374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6489868164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8753471374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5732879638672</t>
   </si>
   <si>
     <t xml:space="preserve">49.4687881469727</t>
@@ -1223,25 +1223,25 @@
     <t xml:space="preserve">48.8085746765137</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4789695739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3938369750977</t>
+    <t xml:space="preserve">46.4789657592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3938331604004</t>
   </si>
   <si>
     <t xml:space="preserve">46.5166931152344</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1774024963379</t>
+    <t xml:space="preserve">45.1774101257324</t>
   </si>
   <si>
     <t xml:space="preserve">44.7812728881836</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8378677368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4983253479004</t>
+    <t xml:space="preserve">44.8378639221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4983291625977</t>
   </si>
   <si>
     <t xml:space="preserve">44.1776580810547</t>
@@ -1253,10 +1253,10 @@
     <t xml:space="preserve">42.2913360595703</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4988250732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0652236938477</t>
+    <t xml:space="preserve">42.4988288879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0652198791504</t>
   </si>
   <si>
     <t xml:space="preserve">41.9517936706543</t>
@@ -1265,7 +1265,7 @@
     <t xml:space="preserve">45.3283157348633</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4414939880371</t>
+    <t xml:space="preserve">45.4414901733398</t>
   </si>
   <si>
     <t xml:space="preserve">45.4603500366211</t>
@@ -1274,79 +1274,79 @@
     <t xml:space="preserve">45.4037628173828</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1017036437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9885177612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3846549987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.0443687438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.902889251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.2898368835449</t>
+    <t xml:space="preserve">46.1016998291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9885215759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3846473693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.044361114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9028816223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.2898445129395</t>
   </si>
   <si>
     <t xml:space="preserve">51.1193199157715</t>
   </si>
   <si>
-    <t xml:space="preserve">50.6949005126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6005821228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9328575134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4107131958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0277976989746</t>
+    <t xml:space="preserve">50.694896697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6005783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9328536987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4107093811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0277900695801</t>
   </si>
   <si>
     <t xml:space="preserve">52.2144813537598</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1195526123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7398109436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8410987854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5024681091309</t>
+    <t xml:space="preserve">52.1195487976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7397994995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8410949707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5024604797363</t>
   </si>
   <si>
     <t xml:space="preserve">49.2714881896973</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3664207458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.081615447998</t>
+    <t xml:space="preserve">49.3664169311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.0816192626953</t>
   </si>
   <si>
     <t xml:space="preserve">49.7936325073242</t>
   </si>
   <si>
-    <t xml:space="preserve">48.2746658325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8221549987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0847969055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6544075012207</t>
+    <t xml:space="preserve">48.2746620178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.822151184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0847930908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6544036865234</t>
   </si>
   <si>
     <t xml:space="preserve">49.3189544677734</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">50.3632431030273</t>
   </si>
   <si>
-    <t xml:space="preserve">51.217658996582</t>
+    <t xml:space="preserve">51.2176628112793</t>
   </si>
   <si>
     <t xml:space="preserve">50.1733665466309</t>
@@ -1370,16 +1370,16 @@
     <t xml:space="preserve">51.4550018310547</t>
   </si>
   <si>
-    <t xml:space="preserve">52.0246124267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0689010620117</t>
+    <t xml:space="preserve">52.0246162414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.068904876709</t>
   </si>
   <si>
     <t xml:space="preserve">52.7840995788574</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4422912597656</t>
+    <t xml:space="preserve">55.4422874450684</t>
   </si>
   <si>
     <t xml:space="preserve">54.682804107666</t>
@@ -1388,16 +1388,16 @@
     <t xml:space="preserve">55.1100120544434</t>
   </si>
   <si>
-    <t xml:space="preserve">55.5846939086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3916435241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.7302742004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.0625495910645</t>
+    <t xml:space="preserve">55.5846900939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3916473388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.7302703857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.0625534057617</t>
   </si>
   <si>
     <t xml:space="preserve">55.4897575378418</t>
@@ -1409,19 +1409,19 @@
     <t xml:space="preserve">53.1638412475586</t>
   </si>
   <si>
-    <t xml:space="preserve">53.6385116577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.018253326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3030662536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1131896972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8283920288086</t>
+    <t xml:space="preserve">53.6385154724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0182571411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3030624389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1131935119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8283882141113</t>
   </si>
   <si>
     <t xml:space="preserve">54.7777404785156</t>
@@ -1433,154 +1433,154 @@
     <t xml:space="preserve">56.9137878417969</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2967071533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.011905670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2017669677734</t>
+    <t xml:space="preserve">56.2966995239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0118980407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2017707824707</t>
   </si>
   <si>
     <t xml:space="preserve">56.5340385437012</t>
   </si>
   <si>
-    <t xml:space="preserve">56.6764526367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9676170349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5942306518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0214309692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1574783325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.350528717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9264984130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.8790321350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0657196044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5878677368164</t>
+    <t xml:space="preserve">56.6764488220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9676094055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5942268371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0214347839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1574821472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3505325317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9265022277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.879035949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0657272338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5878715515137</t>
   </si>
   <si>
     <t xml:space="preserve">53.4486427307129</t>
   </si>
   <si>
-    <t xml:space="preserve">53.6859817504883</t>
+    <t xml:space="preserve">53.685977935791</t>
   </si>
   <si>
     <t xml:space="preserve">53.3062438964844</t>
   </si>
   <si>
-    <t xml:space="preserve">52.404354095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0752601623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4581832885742</t>
+    <t xml:space="preserve">52.4043579101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0752563476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4581756591797</t>
   </si>
   <si>
     <t xml:space="preserve">52.2619514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">51.8822059631348</t>
+    <t xml:space="preserve">51.8822135925293</t>
   </si>
   <si>
     <t xml:space="preserve">54.1606597900391</t>
   </si>
   <si>
-    <t xml:space="preserve">54.2081260681152</t>
+    <t xml:space="preserve">54.2081298828125</t>
   </si>
   <si>
     <t xml:space="preserve">53.5435791015625</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5404014587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2049522399902</t>
+    <t xml:space="preserve">54.540397644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.204948425293</t>
   </si>
   <si>
     <t xml:space="preserve">56.2492370605469</t>
   </si>
   <si>
-    <t xml:space="preserve">57.1036605834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.2460632324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9106063842773</t>
+    <t xml:space="preserve">57.1036567687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.2460594177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9106101989746</t>
   </si>
   <si>
     <t xml:space="preserve">56.9612579345703</t>
   </si>
   <si>
-    <t xml:space="preserve">50.790454864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.4138870239258</t>
+    <t xml:space="preserve">50.7904510498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.413890838623</t>
   </si>
   <si>
     <t xml:space="preserve">47.012020111084</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0499954223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.2271957397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4677085876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0309677124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3157806396484</t>
+    <t xml:space="preserve">47.0499992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.2271995544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.467716217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0309753417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3157768249512</t>
   </si>
   <si>
     <t xml:space="preserve">46.3474769592285</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7525596618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6766204833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6956024169922</t>
+    <t xml:space="preserve">44.752555847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6766090393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6955986022949</t>
   </si>
   <si>
     <t xml:space="preserve">46.1955757141113</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5563354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4803886413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9487495422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4107513427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5373458862305</t>
+    <t xml:space="preserve">46.5563278198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4803848266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9487457275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4107437133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5373420715332</t>
   </si>
   <si>
     <t xml:space="preserve">46.5183601379395</t>
@@ -1589,16 +1589,16 @@
     <t xml:space="preserve">46.746208190918</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4424057006836</t>
+    <t xml:space="preserve">46.4424133300781</t>
   </si>
   <si>
     <t xml:space="preserve">45.4930534362793</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1323013305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5690078735352</t>
+    <t xml:space="preserve">45.1322975158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5690002441406</t>
   </si>
   <si>
     <t xml:space="preserve">45.7019119262695</t>
@@ -1607,22 +1607,22 @@
     <t xml:space="preserve">42.3601875305176</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4677963256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9234848022461</t>
+    <t xml:space="preserve">41.4677925109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9234809875488</t>
   </si>
   <si>
     <t xml:space="preserve">42.8728370666504</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7462425231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8601684570312</t>
+    <t xml:space="preserve">43.7462463378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2968673706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.860164642334</t>
   </si>
   <si>
     <t xml:space="preserve">45.7209014892578</t>
@@ -1637,7 +1637,7 @@
     <t xml:space="preserve">47.2398643493652</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2905082702637</t>
+    <t xml:space="preserve">46.2905120849609</t>
   </si>
   <si>
     <t xml:space="preserve">45.1892623901367</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">45.2082481384277</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2841949462891</t>
+    <t xml:space="preserve">45.2841911315918</t>
   </si>
   <si>
     <t xml:space="preserve">47.3158149719238</t>
@@ -1664,13 +1664,13 @@
     <t xml:space="preserve">43.5373878479004</t>
   </si>
   <si>
-    <t xml:space="preserve">43.5183982849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0753784179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5627250671387</t>
+    <t xml:space="preserve">43.5184020996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.075382232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5627326965332</t>
   </si>
   <si>
     <t xml:space="preserve">40.2146492004395</t>
@@ -1688,7 +1688,7 @@
     <t xml:space="preserve">41.8095588684082</t>
   </si>
   <si>
-    <t xml:space="preserve">43.195613861084</t>
+    <t xml:space="preserve">43.1956214904785</t>
   </si>
   <si>
     <t xml:space="preserve">44.0310516357422</t>
@@ -1700,16 +1700,16 @@
     <t xml:space="preserve">44.3348426818848</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8791580200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7398910522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8348236083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.803165435791</t>
+    <t xml:space="preserve">43.8791542053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7398872375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8348197937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8031692504883</t>
   </si>
   <si>
     <t xml:space="preserve">46.3854522705078</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">46.4234237670898</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1829071044922</t>
+    <t xml:space="preserve">47.1829109191895</t>
   </si>
   <si>
     <t xml:space="preserve">49.1765518188477</t>
@@ -1733,25 +1733,25 @@
     <t xml:space="preserve">45.0753364562988</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6449508666992</t>
+    <t xml:space="preserve">45.6449584960938</t>
   </si>
   <si>
     <t xml:space="preserve">47.2588500976562</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4645347595215</t>
+    <t xml:space="preserve">48.4645309448242</t>
   </si>
   <si>
     <t xml:space="preserve">49.8885650634766</t>
   </si>
   <si>
-    <t xml:space="preserve">50.1259002685547</t>
+    <t xml:space="preserve">50.125904083252</t>
   </si>
   <si>
     <t xml:space="preserve">50.6955146789551</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2208404541016</t>
+    <t xml:space="preserve">50.2208366394043</t>
   </si>
   <si>
     <t xml:space="preserve">49.9360313415527</t>
@@ -1760,7 +1760,7 @@
     <t xml:space="preserve">50.0784339904785</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1670150756836</t>
+    <t xml:space="preserve">52.1670188903809</t>
   </si>
   <si>
     <t xml:space="preserve">52.6891632080078</t>
@@ -1769,55 +1769,55 @@
     <t xml:space="preserve">52.9739646911621</t>
   </si>
   <si>
-    <t xml:space="preserve">54.2555999755859</t>
+    <t xml:space="preserve">54.2555885314941</t>
   </si>
   <si>
     <t xml:space="preserve">53.2587738037109</t>
   </si>
   <si>
-    <t xml:space="preserve">53.9707832336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.7334480285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2998847961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3979949951172</t>
+    <t xml:space="preserve">53.9707870483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.7334518432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.2998886108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3979988098145</t>
   </si>
   <si>
     <t xml:space="preserve">53.4011764526367</t>
   </si>
   <si>
-    <t xml:space="preserve">53.9233245849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4929351806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4454650878906</t>
+    <t xml:space="preserve">53.9233207702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4929313659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4454689025879</t>
   </si>
   <si>
     <t xml:space="preserve">53.4961128234863</t>
   </si>
   <si>
-    <t xml:space="preserve">54.6353340148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.9644355773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.7270927429199</t>
+    <t xml:space="preserve">54.6353378295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.9644317626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.7270965576172</t>
   </si>
   <si>
     <t xml:space="preserve">56.1068382263184</t>
   </si>
   <si>
-    <t xml:space="preserve">55.5328483581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5239105224609</t>
+    <t xml:space="preserve">55.5328521728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5239181518555</t>
   </si>
   <si>
     <t xml:space="preserve">53.5717468261719</t>
@@ -1826,31 +1826,31 @@
     <t xml:space="preserve">52.615104675293</t>
   </si>
   <si>
-    <t xml:space="preserve">52.5194396972656</t>
+    <t xml:space="preserve">52.5194435119629</t>
   </si>
   <si>
     <t xml:space="preserve">51.4671401977539</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5283851623535</t>
+    <t xml:space="preserve">54.5283813476562</t>
   </si>
   <si>
     <t xml:space="preserve">55.9633407592773</t>
   </si>
   <si>
-    <t xml:space="preserve">56.0589981079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1980323791504</t>
+    <t xml:space="preserve">56.0590057373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1980285644531</t>
   </si>
   <si>
     <t xml:space="preserve">56.776481628418</t>
   </si>
   <si>
-    <t xml:space="preserve">56.0111656188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.6285209655762</t>
+    <t xml:space="preserve">56.0111694335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.6285133361816</t>
   </si>
   <si>
     <t xml:space="preserve">56.2024993896484</t>
@@ -1862,52 +1862,52 @@
     <t xml:space="preserve">56.4416618347168</t>
   </si>
   <si>
-    <t xml:space="preserve">55.580680847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3460006713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1501998901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5762138366699</t>
+    <t xml:space="preserve">55.5806846618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3459968566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1501960754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5762100219727</t>
   </si>
   <si>
     <t xml:space="preserve">54.4327163696289</t>
   </si>
   <si>
-    <t xml:space="preserve">54.8632011413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9199752807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8243141174316</t>
+    <t xml:space="preserve">54.8632049560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.919979095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8243179321289</t>
   </si>
   <si>
     <t xml:space="preserve">57.2547988891602</t>
   </si>
   <si>
-    <t xml:space="preserve">56.6808166503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.7286491394043</t>
+    <t xml:space="preserve">56.6808204650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.728645324707</t>
   </si>
   <si>
     <t xml:space="preserve">58.2114372253418</t>
   </si>
   <si>
-    <t xml:space="preserve">57.6374588012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5462646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9244499206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.3549270629883</t>
+    <t xml:space="preserve">57.6374549865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5462608337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.924446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.3549385070801</t>
   </si>
   <si>
     <t xml:space="preserve">57.7331199645996</t>
@@ -1916,13 +1916,13 @@
     <t xml:space="preserve">57.3504676818848</t>
   </si>
   <si>
-    <t xml:space="preserve">58.3071022033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.2682075500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1725463867188</t>
+    <t xml:space="preserve">58.3071060180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.2682151794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1725540161133</t>
   </si>
   <si>
     <t xml:space="preserve">59.7420616149902</t>
@@ -1937,10 +1937,10 @@
     <t xml:space="preserve">57.3026351928711</t>
   </si>
   <si>
-    <t xml:space="preserve">57.8287887573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.1157760620117</t>
+    <t xml:space="preserve">57.828784942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.115779876709</t>
   </si>
   <si>
     <t xml:space="preserve">57.7809524536133</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">59.0245819091797</t>
   </si>
   <si>
-    <t xml:space="preserve">59.4550666809082</t>
+    <t xml:space="preserve">59.4550704956055</t>
   </si>
   <si>
     <t xml:space="preserve">60.3160438537598</t>
@@ -1958,13 +1958,13 @@
     <t xml:space="preserve">60.029052734375</t>
   </si>
   <si>
-    <t xml:space="preserve">59.0724143981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.2592697143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0201148986816</t>
+    <t xml:space="preserve">59.0724182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.2592735290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0201110839844</t>
   </si>
   <si>
     <t xml:space="preserve">50.9888191223145</t>
@@ -1973,16 +1973,16 @@
     <t xml:space="preserve">50.4148406982422</t>
   </si>
   <si>
-    <t xml:space="preserve">51.2279815673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3236465454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8931617736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.793025970459</t>
+    <t xml:space="preserve">51.2279777526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3236427307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8931541442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7930221557617</t>
   </si>
   <si>
     <t xml:space="preserve">49.8408508300781</t>
@@ -1994,61 +1994,61 @@
     <t xml:space="preserve">49.2668724060059</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9843521118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9365196228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0800132751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6540031433105</t>
+    <t xml:space="preserve">49.9843482971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9365234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0800094604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6539993286133</t>
   </si>
   <si>
     <t xml:space="preserve">50.2235069274902</t>
   </si>
   <si>
-    <t xml:space="preserve">50.845329284668</t>
+    <t xml:space="preserve">50.8453216552734</t>
   </si>
   <si>
     <t xml:space="preserve">51.419303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">50.940990447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5149688720703</t>
+    <t xml:space="preserve">50.9409866333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5149726867676</t>
   </si>
   <si>
     <t xml:space="preserve">50.797492980957</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1323204040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6973609924316</t>
+    <t xml:space="preserve">51.1323165893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6973648071289</t>
   </si>
   <si>
     <t xml:space="preserve">49.3147048950195</t>
   </si>
   <si>
-    <t xml:space="preserve">49.458194732666</t>
+    <t xml:space="preserve">49.4582061767578</t>
   </si>
   <si>
     <t xml:space="preserve">49.745189666748</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0321807861328</t>
+    <t xml:space="preserve">50.0321846008301</t>
   </si>
   <si>
     <t xml:space="preserve">48.8363838195801</t>
   </si>
   <si>
-    <t xml:space="preserve">48.5972213745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3625297546387</t>
+    <t xml:space="preserve">48.5972290039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3625335693359</t>
   </si>
   <si>
     <t xml:space="preserve">54.0022315979004</t>
@@ -2057,34 +2057,34 @@
     <t xml:space="preserve">53.4282493591309</t>
   </si>
   <si>
-    <t xml:space="preserve">54.2892265319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1935577392578</t>
+    <t xml:space="preserve">54.2892227172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1935539245605</t>
   </si>
   <si>
     <t xml:space="preserve">53.0934257507324</t>
   </si>
   <si>
-    <t xml:space="preserve">52.471607208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2847518920898</t>
+    <t xml:space="preserve">52.4716148376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2847557067871</t>
   </si>
   <si>
     <t xml:space="preserve">54.0978927612305</t>
   </si>
   <si>
-    <t xml:space="preserve">54.9110374450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3370552062988</t>
+    <t xml:space="preserve">54.9110336303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3370513916016</t>
   </si>
   <si>
     <t xml:space="preserve">53.8587341308594</t>
   </si>
   <si>
-    <t xml:space="preserve">54.4805488586426</t>
+    <t xml:space="preserve">54.4805526733398</t>
   </si>
   <si>
     <t xml:space="preserve">55.0545310974121</t>
@@ -2093,31 +2093,31 @@
     <t xml:space="preserve">55.3415260314941</t>
   </si>
   <si>
-    <t xml:space="preserve">55.8676795959473</t>
+    <t xml:space="preserve">55.86767578125</t>
   </si>
   <si>
     <t xml:space="preserve">56.5373229980469</t>
   </si>
   <si>
-    <t xml:space="preserve">56.632984161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.4027709960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.067943572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6942291259766</t>
+    <t xml:space="preserve">56.6329879760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.4027633666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0679473876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6942329406738</t>
   </si>
   <si>
     <t xml:space="preserve">59.3115730285645</t>
   </si>
   <si>
-    <t xml:space="preserve">62.8511238098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6164512634277</t>
+    <t xml:space="preserve">62.8511390686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6164436340332</t>
   </si>
   <si>
     <t xml:space="preserve">65.3383941650391</t>
@@ -2132,28 +2132,28 @@
     <t xml:space="preserve">67.9213180541992</t>
   </si>
   <si>
-    <t xml:space="preserve">69.260612487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.0692901611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.3951644897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.0169830322266</t>
+    <t xml:space="preserve">69.2606201171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.0692749023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.3951568603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.016975402832</t>
   </si>
   <si>
     <t xml:space="preserve">66.8690185546875</t>
   </si>
   <si>
-    <t xml:space="preserve">67.2994995117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.5386657714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.92578125</t>
+    <t xml:space="preserve">67.2995071411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.5386581420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.9257888793945</t>
   </si>
   <si>
     <t xml:space="preserve">69.2127838134766</t>
@@ -2162,22 +2162,22 @@
     <t xml:space="preserve">68.4474716186523</t>
   </si>
   <si>
-    <t xml:space="preserve">67.8734817504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.7778167724609</t>
+    <t xml:space="preserve">67.8734741210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.7778244018555</t>
   </si>
   <si>
     <t xml:space="preserve">67.0603408813477</t>
   </si>
   <si>
-    <t xml:space="preserve">66.0080490112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.4385299682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5775527954102</t>
+    <t xml:space="preserve">66.0080337524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.4385223388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5775604248047</t>
   </si>
   <si>
     <t xml:space="preserve">65.9123840332031</t>
@@ -2186,7 +2186,7 @@
     <t xml:space="preserve">67.2516708374023</t>
   </si>
   <si>
-    <t xml:space="preserve">67.8256454467773</t>
+    <t xml:space="preserve">67.8256607055664</t>
   </si>
   <si>
     <t xml:space="preserve">67.6343231201172</t>
@@ -2207,10 +2207,10 @@
     <t xml:space="preserve">70.3129196166992</t>
   </si>
   <si>
-    <t xml:space="preserve">73.3263244628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.2306594848633</t>
+    <t xml:space="preserve">73.3263320922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.2306671142578</t>
   </si>
   <si>
     <t xml:space="preserve">74.0916290283203</t>
@@ -2219,37 +2219,37 @@
     <t xml:space="preserve">73.6611480712891</t>
   </si>
   <si>
-    <t xml:space="preserve">73.3741455078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6955642700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.7912445068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.4653549194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.2650756835938</t>
+    <t xml:space="preserve">73.3741607666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6955718994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.7912292480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.4653472900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.2650833129883</t>
   </si>
   <si>
     <t xml:space="preserve">68.638801574707</t>
   </si>
   <si>
-    <t xml:space="preserve">71.3173980712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9391937255859</t>
+    <t xml:space="preserve">71.3173828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9392013549805</t>
   </si>
   <si>
     <t xml:space="preserve">72.7045059204102</t>
   </si>
   <si>
-    <t xml:space="preserve">72.7523345947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.6088562011719</t>
+    <t xml:space="preserve">72.7523498535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.6088485717773</t>
   </si>
   <si>
     <t xml:space="preserve">74.4264602661133</t>
@@ -2258,16 +2258,16 @@
     <t xml:space="preserve">74.1394653320312</t>
   </si>
   <si>
-    <t xml:space="preserve">71.7478713989258</t>
+    <t xml:space="preserve">71.7478790283203</t>
   </si>
   <si>
     <t xml:space="preserve">71.9870300292969</t>
   </si>
   <si>
-    <t xml:space="preserve">73.2784881591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.4130554199219</t>
+    <t xml:space="preserve">73.2784957885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.4130477905273</t>
   </si>
   <si>
     <t xml:space="preserve">66.8211898803711</t>
@@ -2276,73 +2276,73 @@
     <t xml:space="preserve">65.7210464477539</t>
   </si>
   <si>
-    <t xml:space="preserve">62.1336479187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.8077735900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8944969177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9378623962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.8766136169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5672721862793</t>
+    <t xml:space="preserve">62.1336555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.8077697753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8944854736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.937858581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.8766174316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5672798156738</t>
   </si>
   <si>
     <t xml:space="preserve">52.0889549255371</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3778266906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.74072265625</t>
+    <t xml:space="preserve">46.3778190612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7407264709473</t>
   </si>
   <si>
     <t xml:space="preserve">45.4594535827637</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7094230651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8714332580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2107276916504</t>
+    <t xml:space="preserve">41.7094306945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8714294433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2107238769531</t>
   </si>
   <si>
     <t xml:space="preserve">45.3446578979492</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1048698425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0844879150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2190399169922</t>
+    <t xml:space="preserve">47.1048736572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0844802856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2190437316895</t>
   </si>
   <si>
     <t xml:space="preserve">59.1680793762207</t>
   </si>
   <si>
-    <t xml:space="preserve">57.6852874755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.263744354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.081356048584</t>
+    <t xml:space="preserve">57.6852798461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.2637405395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0813522338867</t>
   </si>
   <si>
     <t xml:space="preserve">60.3638763427734</t>
   </si>
   <si>
-    <t xml:space="preserve">61.1291847229004</t>
+    <t xml:space="preserve">61.1291923522949</t>
   </si>
   <si>
     <t xml:space="preserve">61.4161720275879</t>
@@ -2351,40 +2351,40 @@
     <t xml:space="preserve">62.6598091125488</t>
   </si>
   <si>
-    <t xml:space="preserve">63.5207901000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5641479492188</t>
+    <t xml:space="preserve">63.5207748413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.564151763916</t>
   </si>
   <si>
     <t xml:space="preserve">63.138126373291</t>
   </si>
   <si>
-    <t xml:space="preserve">63.0424652099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9901657104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.033519744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.2684898376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9081382751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.7279586791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.7051887512207</t>
+    <t xml:space="preserve">63.0424690246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9901580810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0335235595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.2684860229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9081420898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.7279624938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.705192565918</t>
   </si>
   <si>
     <t xml:space="preserve">64.7179107666016</t>
   </si>
   <si>
-    <t xml:space="preserve">63.367603302002</t>
+    <t xml:space="preserve">63.3676109313965</t>
   </si>
   <si>
     <t xml:space="preserve">63.6569595336914</t>
@@ -2393,13 +2393,13 @@
     <t xml:space="preserve">64.0909805297852</t>
   </si>
   <si>
-    <t xml:space="preserve">64.4285659790039</t>
+    <t xml:space="preserve">64.4285583496094</t>
   </si>
   <si>
     <t xml:space="preserve">64.9108123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">68.4312286376953</t>
+    <t xml:space="preserve">68.4312210083008</t>
   </si>
   <si>
     <t xml:space="preserve">68.0936508178711</t>
@@ -2411,7 +2411,7 @@
     <t xml:space="preserve">68.6241302490234</t>
   </si>
   <si>
-    <t xml:space="preserve">69.9744415283203</t>
+    <t xml:space="preserve">69.9744338989258</t>
   </si>
   <si>
     <t xml:space="preserve">73.3984069824219</t>
@@ -2420,13 +2420,13 @@
     <t xml:space="preserve">74.1217803955078</t>
   </si>
   <si>
-    <t xml:space="preserve">73.9288787841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.3628997802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.8578720092773</t>
+    <t xml:space="preserve">73.9288864135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.362907409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.8578796386719</t>
   </si>
   <si>
     <t xml:space="preserve">74.6522598266602</t>
@@ -2435,19 +2435,19 @@
     <t xml:space="preserve">71.8552017211914</t>
   </si>
   <si>
-    <t xml:space="preserve">70.6013488769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.1318283081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.2155532836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.9235305786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.0326995849609</t>
+    <t xml:space="preserve">70.6013565063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.1318206787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.2155456542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.9235382080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.0327072143555</t>
   </si>
   <si>
     <t xml:space="preserve">67.2256088256836</t>
@@ -2456,22 +2456,22 @@
     <t xml:space="preserve">64.8625869750977</t>
   </si>
   <si>
-    <t xml:space="preserve">66.5504608154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.3220672607422</t>
+    <t xml:space="preserve">66.5504531860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.3220596313477</t>
   </si>
   <si>
     <t xml:space="preserve">69.9262084960938</t>
   </si>
   <si>
-    <t xml:space="preserve">71.180061340332</t>
+    <t xml:space="preserve">71.180046081543</t>
   </si>
   <si>
     <t xml:space="preserve">70.4084548950195</t>
   </si>
   <si>
-    <t xml:space="preserve">71.3729629516602</t>
+    <t xml:space="preserve">71.3729553222656</t>
   </si>
   <si>
     <t xml:space="preserve">69.4921798706055</t>
@@ -2483,49 +2483,49 @@
     <t xml:space="preserve">68.5276794433594</t>
   </si>
   <si>
-    <t xml:space="preserve">68.2865524291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.67236328125</t>
+    <t xml:space="preserve">68.2865600585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.6723556518555</t>
   </si>
   <si>
     <t xml:space="preserve">69.0099334716797</t>
   </si>
   <si>
-    <t xml:space="preserve">69.2992782592773</t>
+    <t xml:space="preserve">69.2992858886719</t>
   </si>
   <si>
     <t xml:space="preserve">72.1445541381836</t>
   </si>
   <si>
-    <t xml:space="preserve">71.2765045166016</t>
+    <t xml:space="preserve">71.2765121459961</t>
   </si>
   <si>
     <t xml:space="preserve">71.8069763183594</t>
   </si>
   <si>
-    <t xml:space="preserve">70.1673355102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.5531311035156</t>
+    <t xml:space="preserve">70.1673202514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.5531234741211</t>
   </si>
   <si>
     <t xml:space="preserve">70.3602294921875</t>
   </si>
   <si>
-    <t xml:space="preserve">71.6623153686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.3374557495117</t>
+    <t xml:space="preserve">71.6623001098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.3374633789062</t>
   </si>
   <si>
     <t xml:space="preserve">72.8679351806641</t>
   </si>
   <si>
-    <t xml:space="preserve">73.4466247558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.5430679321289</t>
+    <t xml:space="preserve">73.4466400146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.5430755615234</t>
   </si>
   <si>
     <t xml:space="preserve">71.999885559082</t>
@@ -2534,34 +2534,34 @@
     <t xml:space="preserve">73.0608291625977</t>
   </si>
   <si>
-    <t xml:space="preserve">73.6877517700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.5913162231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.9643783569336</t>
+    <t xml:space="preserve">73.6877593994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.5913009643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.9643936157227</t>
   </si>
   <si>
     <t xml:space="preserve">74.7487030029297</t>
   </si>
   <si>
-    <t xml:space="preserve">81.934211730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.9469528198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1170654296875</t>
+    <t xml:space="preserve">81.9342193603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.9469451904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.117073059082</t>
   </si>
   <si>
     <t xml:space="preserve">86.0815658569336</t>
   </si>
   <si>
-    <t xml:space="preserve">85.3581924438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1398468017578</t>
+    <t xml:space="preserve">85.3582000732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1398544311523</t>
   </si>
   <si>
     <t xml:space="preserve">81.017951965332</t>
@@ -2570,10 +2570,10 @@
     <t xml:space="preserve">81.0661773681641</t>
   </si>
   <si>
-    <t xml:space="preserve">82.6093673706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.8732757568359</t>
+    <t xml:space="preserve">82.609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80.8732681274414</t>
   </si>
   <si>
     <t xml:space="preserve">83.0916290283203</t>
@@ -2582,16 +2582,16 @@
     <t xml:space="preserve">85.3099746704102</t>
   </si>
   <si>
-    <t xml:space="preserve">84.5865859985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.6348190307617</t>
+    <t xml:space="preserve">84.5865936279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.6348266601562</t>
   </si>
   <si>
     <t xml:space="preserve">83.6703262329102</t>
   </si>
   <si>
-    <t xml:space="preserve">84.7795028686523</t>
+    <t xml:space="preserve">84.7794952392578</t>
   </si>
   <si>
     <t xml:space="preserve">84.6830596923828</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">87.3836441040039</t>
   </si>
   <si>
-    <t xml:space="preserve">86.2262420654297</t>
+    <t xml:space="preserve">86.2262496948242</t>
   </si>
   <si>
     <t xml:space="preserve">87.7212219238281</t>
@@ -2609,13 +2609,13 @@
     <t xml:space="preserve">89.6984405517578</t>
   </si>
   <si>
-    <t xml:space="preserve">89.3126373291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.6629333496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1070251464844</t>
+    <t xml:space="preserve">89.3126525878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.6629409790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1070098876953</t>
   </si>
   <si>
     <t xml:space="preserve">87.8658981323242</t>
@@ -2624,13 +2624,13 @@
     <t xml:space="preserve">91.2416458129883</t>
   </si>
   <si>
-    <t xml:space="preserve">90.2771377563477</t>
+    <t xml:space="preserve">90.2771530151367</t>
   </si>
   <si>
     <t xml:space="preserve">90.5664901733398</t>
   </si>
   <si>
-    <t xml:space="preserve">90.8076248168945</t>
+    <t xml:space="preserve">90.8076171875</t>
   </si>
   <si>
     <t xml:space="preserve">92.9777374267578</t>
@@ -2639,16 +2639,16 @@
     <t xml:space="preserve">95.0031967163086</t>
   </si>
   <si>
-    <t xml:space="preserve">94.9067459106445</t>
+    <t xml:space="preserve">94.90673828125</t>
   </si>
   <si>
     <t xml:space="preserve">95.7265701293945</t>
   </si>
   <si>
-    <t xml:space="preserve">93.218864440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5082244873047</t>
+    <t xml:space="preserve">93.2188568115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5082092285156</t>
   </si>
   <si>
     <t xml:space="preserve">91.4827651977539</t>
@@ -2663,25 +2663,25 @@
     <t xml:space="preserve">92.1096878051758</t>
   </si>
   <si>
-    <t xml:space="preserve">93.3635482788086</t>
+    <t xml:space="preserve">93.3635406494141</t>
   </si>
   <si>
     <t xml:space="preserve">95.5336685180664</t>
   </si>
   <si>
-    <t xml:space="preserve">94.9549560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.8102874755859</t>
+    <t xml:space="preserve">94.9549713134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.8102951049805</t>
   </si>
   <si>
     <t xml:space="preserve">93.6046676635742</t>
   </si>
   <si>
-    <t xml:space="preserve">94.5209350585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6883850097656</t>
+    <t xml:space="preserve">94.5209426879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6883926391602</t>
   </si>
   <si>
     <t xml:space="preserve">91.4345474243164</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">93.0259628295898</t>
   </si>
   <si>
-    <t xml:space="preserve">95.2925415039062</t>
+    <t xml:space="preserve">95.2925491333008</t>
   </si>
   <si>
     <t xml:space="preserve">97.2215423583984</t>
@@ -2699,22 +2699,22 @@
     <t xml:space="preserve">100.115043640137</t>
   </si>
   <si>
-    <t xml:space="preserve">99.7292327880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.6073379516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.8966903686523</t>
+    <t xml:space="preserve">99.729248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.6073303222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.8966827392578</t>
   </si>
   <si>
     <t xml:space="preserve">98.3789367675781</t>
   </si>
   <si>
-    <t xml:space="preserve">96.3052597045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.7493438720703</t>
+    <t xml:space="preserve">96.3052673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7493286132812</t>
   </si>
   <si>
     <t xml:space="preserve">92.8330612182617</t>
@@ -2723,10 +2723,10 @@
     <t xml:space="preserve">92.8812942504883</t>
   </si>
   <si>
-    <t xml:space="preserve">88.444580078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.2034606933594</t>
+    <t xml:space="preserve">88.4445877075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.2034683227539</t>
   </si>
   <si>
     <t xml:space="preserve">89.0233001708984</t>
@@ -2735,10 +2735,10 @@
     <t xml:space="preserve">90.1324615478516</t>
   </si>
   <si>
-    <t xml:space="preserve">92.2061462402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.4499359130859</t>
+    <t xml:space="preserve">92.2061386108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.4499435424805</t>
   </si>
   <si>
     <t xml:space="preserve">95.4372177124023</t>
@@ -2747,19 +2747,19 @@
     <t xml:space="preserve">95.7747955322266</t>
   </si>
   <si>
-    <t xml:space="preserve">92.4472732543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0614700317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.8685607910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.8203430175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7111740112305</t>
+    <t xml:space="preserve">92.447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0614624023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.8685684204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.8203353881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7111663818359</t>
   </si>
   <si>
     <t xml:space="preserve">90.8558349609375</t>
@@ -2768,13 +2768,13 @@
     <t xml:space="preserve">91.3863220214844</t>
   </si>
   <si>
-    <t xml:space="preserve">90.7593841552734</t>
+    <t xml:space="preserve">90.759391784668</t>
   </si>
   <si>
     <t xml:space="preserve">87.7694473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">88.2516937255859</t>
+    <t xml:space="preserve">88.2517013549805</t>
   </si>
   <si>
     <t xml:space="preserve">89.3608703613281</t>
@@ -2783,16 +2783,16 @@
     <t xml:space="preserve">90.3735885620117</t>
   </si>
   <si>
-    <t xml:space="preserve">94.2798156738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.0842514038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.1451950073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.495491027832</t>
+    <t xml:space="preserve">94.2798233032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.0842361450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.1451873779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4954833984375</t>
   </si>
   <si>
     <t xml:space="preserve">89.4573211669922</t>
@@ -2804,46 +2804,46 @@
     <t xml:space="preserve">91.9168014526367</t>
   </si>
   <si>
-    <t xml:space="preserve">91.7238845825195</t>
+    <t xml:space="preserve">91.7238922119141</t>
   </si>
   <si>
     <t xml:space="preserve">91.0969619750977</t>
   </si>
   <si>
-    <t xml:space="preserve">90.9040679931641</t>
+    <t xml:space="preserve">90.9040756225586</t>
   </si>
   <si>
     <t xml:space="preserve">92.3508224487305</t>
   </si>
   <si>
-    <t xml:space="preserve">93.4599914550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.5437164306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9194641113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.26708984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5564422607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.5691757202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.0641403198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.4753952026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.018592834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.1860504150391</t>
+    <t xml:space="preserve">93.4599838256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.5437088012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9194564819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.2670822143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5564346313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.5691680908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.0641479492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.4753875732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.018577575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.1860427856445</t>
   </si>
   <si>
     <t xml:space="preserve">97.414436340332</t>
@@ -2852,25 +2852,25 @@
     <t xml:space="preserve">100.790184020996</t>
   </si>
   <si>
-    <t xml:space="preserve">102.912078857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.465324401855</t>
+    <t xml:space="preserve">102.912086486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.46533203125</t>
   </si>
   <si>
     <t xml:space="preserve">102.719184875488</t>
   </si>
   <si>
-    <t xml:space="preserve">102.526290893555</t>
+    <t xml:space="preserve">102.52628326416</t>
   </si>
   <si>
     <t xml:space="preserve">102.140495300293</t>
   </si>
   <si>
-    <t xml:space="preserve">104.937538146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.104995727539</t>
+    <t xml:space="preserve">104.937530517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.104988098145</t>
   </si>
   <si>
     <t xml:space="preserve">103.58723449707</t>
@@ -2882,61 +2882,61 @@
     <t xml:space="preserve">103.201431274414</t>
   </si>
   <si>
-    <t xml:space="preserve">100.500831604004</t>
+    <t xml:space="preserve">100.500823974609</t>
   </si>
   <si>
     <t xml:space="preserve">100.404388427734</t>
   </si>
   <si>
-    <t xml:space="preserve">98.5718383789062</t>
+    <t xml:space="preserve">98.5718307495117</t>
   </si>
   <si>
     <t xml:space="preserve">95.0514221191406</t>
   </si>
   <si>
-    <t xml:space="preserve">94.1351470947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.5919342041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2162017822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.297889709473</t>
+    <t xml:space="preserve">94.135139465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.5919418334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.216194152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.297882080078</t>
   </si>
   <si>
     <t xml:space="preserve">99.3434371948242</t>
   </si>
   <si>
-    <t xml:space="preserve">101.561790466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.973037719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.780128479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.323333740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.490791320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.069473266602</t>
+    <t xml:space="preserve">101.561782836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.973030090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.780136108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.323341369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.490783691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.069480895996</t>
   </si>
   <si>
     <t xml:space="preserve">108.023933410645</t>
   </si>
   <si>
-    <t xml:space="preserve">110.145820617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.699073791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.28783416748</t>
+    <t xml:space="preserve">110.14582824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.699081420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.287841796875</t>
   </si>
   <si>
     <t xml:space="preserve">107.445236206055</t>
@@ -2951,10 +2951,10 @@
     <t xml:space="preserve">107.831039428711</t>
   </si>
   <si>
-    <t xml:space="preserve">108.795532226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.084884643555</t>
+    <t xml:space="preserve">108.795524597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.08487701416</t>
   </si>
   <si>
     <t xml:space="preserve">107.059432983398</t>
@@ -2975,46 +2975,46 @@
     <t xml:space="preserve">107.786018371582</t>
   </si>
   <si>
-    <t xml:space="preserve">108.755317687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.046112060547</t>
+    <t xml:space="preserve">108.755310058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.046104431152</t>
   </si>
   <si>
     <t xml:space="preserve">109.918487548828</t>
   </si>
   <si>
-    <t xml:space="preserve">110.500061035156</t>
+    <t xml:space="preserve">110.500053405762</t>
   </si>
   <si>
     <t xml:space="preserve">109.821548461914</t>
   </si>
   <si>
-    <t xml:space="preserve">110.887771606445</t>
+    <t xml:space="preserve">110.88777923584</t>
   </si>
   <si>
     <t xml:space="preserve">111.663215637207</t>
   </si>
   <si>
-    <t xml:space="preserve">113.117164611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.831192016602</t>
+    <t xml:space="preserve">113.117156982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.831207275391</t>
   </si>
   <si>
     <t xml:space="preserve">113.795669555664</t>
   </si>
   <si>
-    <t xml:space="preserve">114.764976501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.668045043945</t>
+    <t xml:space="preserve">114.76496887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.668037414551</t>
   </si>
   <si>
     <t xml:space="preserve">114.280326843262</t>
   </si>
   <si>
-    <t xml:space="preserve">114.474182128906</t>
+    <t xml:space="preserve">114.474174499512</t>
   </si>
   <si>
     <t xml:space="preserve">116.509704589844</t>
@@ -3023,16 +3023,16 @@
     <t xml:space="preserve">121.453140258789</t>
   </si>
   <si>
-    <t xml:space="preserve">126.59041595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.819793701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.365837097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.268928527832</t>
+    <t xml:space="preserve">126.590408325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.819808959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.365859985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.268920898438</t>
   </si>
   <si>
     <t xml:space="preserve">128.432083129883</t>
@@ -3041,43 +3041,43 @@
     <t xml:space="preserve">133.181655883789</t>
   </si>
   <si>
-    <t xml:space="preserve">130.467620849609</t>
+    <t xml:space="preserve">130.46760559082</t>
   </si>
   <si>
     <t xml:space="preserve">130.273742675781</t>
   </si>
   <si>
-    <t xml:space="preserve">128.916748046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.635589599609</t>
+    <t xml:space="preserve">128.916717529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.63557434082</t>
   </si>
   <si>
     <t xml:space="preserve">135.70182800293</t>
   </si>
   <si>
-    <t xml:space="preserve">134.44172668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.375518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.798782348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.314117431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.574203491211</t>
+    <t xml:space="preserve">134.441741943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.375503540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.798751831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.314102172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.574172973633</t>
   </si>
   <si>
     <t xml:space="preserve">132.212341308594</t>
   </si>
   <si>
-    <t xml:space="preserve">135.023300170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.763229370117</t>
+    <t xml:space="preserve">135.023330688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.763214111328</t>
   </si>
   <si>
     <t xml:space="preserve">137.446563720703</t>
@@ -3086,25 +3086,25 @@
     <t xml:space="preserve">135.89567565918</t>
   </si>
   <si>
-    <t xml:space="preserve">134.344833374023</t>
+    <t xml:space="preserve">134.344818115234</t>
   </si>
   <si>
     <t xml:space="preserve">138.22200012207</t>
   </si>
   <si>
-    <t xml:space="preserve">142.293075561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.032974243164</t>
+    <t xml:space="preserve">142.293060302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.032958984375</t>
   </si>
   <si>
     <t xml:space="preserve">143.359268188477</t>
   </si>
   <si>
-    <t xml:space="preserve">140.063690185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.803588867188</t>
+    <t xml:space="preserve">140.063674926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.803573608398</t>
   </si>
   <si>
     <t xml:space="preserve">140.548324584961</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">139.579025268555</t>
   </si>
   <si>
-    <t xml:space="preserve">136.671112060547</t>
+    <t xml:space="preserve">136.671127319336</t>
   </si>
   <si>
     <t xml:space="preserve">138.609725952148</t>
@@ -3128,16 +3128,16 @@
     <t xml:space="preserve">137.640426635742</t>
   </si>
   <si>
-    <t xml:space="preserve">139.094360351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.226821899414</t>
+    <t xml:space="preserve">139.094375610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.226837158203</t>
   </si>
   <si>
     <t xml:space="preserve">142.583847045898</t>
   </si>
   <si>
-    <t xml:space="preserve">141.905319213867</t>
+    <t xml:space="preserve">141.905334472656</t>
   </si>
   <si>
     <t xml:space="preserve">143.262359619141</t>
@@ -3146,34 +3146,34 @@
     <t xml:space="preserve">142.486923217773</t>
   </si>
   <si>
-    <t xml:space="preserve">146.073303222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.884292602539</t>
+    <t xml:space="preserve">146.073318481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.88427734375</t>
   </si>
   <si>
     <t xml:space="preserve">148.011917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">149.175094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.75666809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.36408996582</t>
+    <t xml:space="preserve">149.175064086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.756652832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.364120483398</t>
   </si>
   <si>
     <t xml:space="preserve">147.236465454102</t>
   </si>
   <si>
-    <t xml:space="preserve">148.205764770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.81803894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.532104492188</t>
+    <t xml:space="preserve">148.205749511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.818054199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.532119750977</t>
   </si>
   <si>
     <t xml:space="preserve">150.629028320312</t>
@@ -3185,10 +3185,10 @@
     <t xml:space="preserve">154.893951416016</t>
   </si>
   <si>
-    <t xml:space="preserve">152.955337524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.898773193359</t>
+    <t xml:space="preserve">152.955352783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.89875793457</t>
   </si>
   <si>
     <t xml:space="preserve">161.67903137207</t>
@@ -3197,7 +3197,7 @@
     <t xml:space="preserve">166.816314697266</t>
   </si>
   <si>
-    <t xml:space="preserve">166.428573608398</t>
+    <t xml:space="preserve">166.428588867188</t>
   </si>
   <si>
     <t xml:space="preserve">165.847015380859</t>
@@ -3206,70 +3206,70 @@
     <t xml:space="preserve">165.459289550781</t>
   </si>
   <si>
-    <t xml:space="preserve">165.653137207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.397888183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.851837158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.142623901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.627288818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.305770874023</t>
+    <t xml:space="preserve">165.65315246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.397903442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.851821899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.142639160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.62727355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.305786132812</t>
   </si>
   <si>
     <t xml:space="preserve">169.23957824707</t>
   </si>
   <si>
-    <t xml:space="preserve">169.724227905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.948776245117</t>
+    <t xml:space="preserve">169.724212646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.948760986328</t>
   </si>
   <si>
     <t xml:space="preserve">163.811477661133</t>
   </si>
   <si>
-    <t xml:space="preserve">167.204040527344</t>
+    <t xml:space="preserve">167.204025268555</t>
   </si>
   <si>
     <t xml:space="preserve">165.071578979492</t>
   </si>
   <si>
-    <t xml:space="preserve">167.9794921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.989135742188</t>
+    <t xml:space="preserve">167.979476928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.989105224609</t>
   </si>
   <si>
     <t xml:space="preserve">176.606231689453</t>
   </si>
   <si>
-    <t xml:space="preserve">171.372024536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.470687866211</t>
+    <t xml:space="preserve">171.372009277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.470703125</t>
   </si>
   <si>
     <t xml:space="preserve">152.567611694336</t>
   </si>
   <si>
-    <t xml:space="preserve">154.506210327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.827697753906</t>
+    <t xml:space="preserve">154.506195068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.827713012695</t>
   </si>
   <si>
     <t xml:space="preserve">149.465866088867</t>
   </si>
   <si>
-    <t xml:space="preserve">153.633865356445</t>
+    <t xml:space="preserve">153.633850097656</t>
   </si>
   <si>
     <t xml:space="preserve">147.430358886719</t>
@@ -3278,13 +3278,13 @@
     <t xml:space="preserve">147.721130371094</t>
   </si>
   <si>
-    <t xml:space="preserve">145.97639465332</t>
+    <t xml:space="preserve">145.976379394531</t>
   </si>
   <si>
     <t xml:space="preserve">157.026397705078</t>
   </si>
   <si>
-    <t xml:space="preserve">159.643508911133</t>
+    <t xml:space="preserve">159.643493652344</t>
   </si>
   <si>
     <t xml:space="preserve">162.842193603516</t>
@@ -3296,28 +3296,28 @@
     <t xml:space="preserve">160.418930053711</t>
   </si>
   <si>
-    <t xml:space="preserve">161.097457885742</t>
+    <t xml:space="preserve">161.097442626953</t>
   </si>
   <si>
     <t xml:space="preserve">160.806655883789</t>
   </si>
   <si>
-    <t xml:space="preserve">160.61279296875</t>
+    <t xml:space="preserve">160.612808227539</t>
   </si>
   <si>
     <t xml:space="preserve">161.582092285156</t>
   </si>
   <si>
-    <t xml:space="preserve">162.551406860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.872894287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.39306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.27507019043</t>
+    <t xml:space="preserve">162.551391601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.872909545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.393081665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.275085449219</t>
   </si>
   <si>
     <t xml:space="preserve">173.213684082031</t>
@@ -3329,49 +3329,49 @@
     <t xml:space="preserve">174.182983398438</t>
   </si>
   <si>
-    <t xml:space="preserve">171.662826538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172.34130859375</t>
+    <t xml:space="preserve">171.662811279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.341323852539</t>
   </si>
   <si>
     <t xml:space="preserve">176.703170776367</t>
   </si>
   <si>
-    <t xml:space="preserve">179.804916381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.892196655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.754928588867</t>
+    <t xml:space="preserve">179.804931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.892181396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.754913330078</t>
   </si>
   <si>
     <t xml:space="preserve">168.561050415039</t>
   </si>
   <si>
-    <t xml:space="preserve">167.010192871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.934280395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.454467773438</t>
+    <t xml:space="preserve">167.010177612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.934310913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.454483032227</t>
   </si>
   <si>
     <t xml:space="preserve">159.837356567383</t>
   </si>
   <si>
-    <t xml:space="preserve">166.040863037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.882537841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.709732055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.745269775391</t>
+    <t xml:space="preserve">166.040893554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.882522583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.709716796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.745254516602</t>
   </si>
   <si>
     <t xml:space="preserve">159.158843994141</t>
@@ -3389,40 +3389,40 @@
     <t xml:space="preserve">174.570709228516</t>
   </si>
   <si>
-    <t xml:space="preserve">169.433441162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.076385498047</t>
+    <t xml:space="preserve">169.433410644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.076400756836</t>
   </si>
   <si>
     <t xml:space="preserve">163.617630004883</t>
   </si>
   <si>
-    <t xml:space="preserve">164.877731323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.714569091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.596572875977</t>
+    <t xml:space="preserve">164.877716064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.714553833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.596588134766</t>
   </si>
   <si>
     <t xml:space="preserve">169.821136474609</t>
   </si>
   <si>
-    <t xml:space="preserve">174.473785400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.005355834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.317184448242</t>
+    <t xml:space="preserve">174.473770141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.005340576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.317199707031</t>
   </si>
   <si>
     <t xml:space="preserve">155.572448730469</t>
   </si>
   <si>
-    <t xml:space="preserve">155.863250732422</t>
+    <t xml:space="preserve">155.863235473633</t>
   </si>
   <si>
     <t xml:space="preserve">155.669387817383</t>
@@ -3437,7 +3437,7 @@
     <t xml:space="preserve">157.220245361328</t>
   </si>
   <si>
-    <t xml:space="preserve">151.113677978516</t>
+    <t xml:space="preserve">151.113662719727</t>
   </si>
   <si>
     <t xml:space="preserve">152.858413696289</t>
@@ -3446,28 +3446,28 @@
     <t xml:space="preserve">154.990859985352</t>
   </si>
   <si>
-    <t xml:space="preserve">137.931213378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.747009277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.553146362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.5224609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.910171508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.385162353516</t>
+    <t xml:space="preserve">137.931198120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.747024536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.553161621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.522445678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.91015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.385177612305</t>
   </si>
   <si>
     <t xml:space="preserve">136.089553833008</t>
   </si>
   <si>
-    <t xml:space="preserve">132.600082397461</t>
+    <t xml:space="preserve">132.600067138672</t>
   </si>
   <si>
     <t xml:space="preserve">132.309280395508</t>
@@ -3476,13 +3476,13 @@
     <t xml:space="preserve">138.997421264648</t>
   </si>
   <si>
-    <t xml:space="preserve">137.834289550781</t>
+    <t xml:space="preserve">137.834274291992</t>
   </si>
   <si>
     <t xml:space="preserve">137.543487548828</t>
   </si>
   <si>
-    <t xml:space="preserve">138.125061035156</t>
+    <t xml:space="preserve">138.125076293945</t>
   </si>
   <si>
     <t xml:space="preserve">138.512786865234</t>
@@ -3491,13 +3491,13 @@
     <t xml:space="preserve">142.680770874023</t>
   </si>
   <si>
-    <t xml:space="preserve">129.692184448242</t>
+    <t xml:space="preserve">129.692169189453</t>
   </si>
   <si>
     <t xml:space="preserve">125.039535522461</t>
   </si>
   <si>
-    <t xml:space="preserve">136.9619140625</t>
+    <t xml:space="preserve">136.961898803711</t>
   </si>
   <si>
     <t xml:space="preserve">135.507965087891</t>
@@ -3506,10 +3506,10 @@
     <t xml:space="preserve">142.874633789062</t>
   </si>
   <si>
-    <t xml:space="preserve">149.562789916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.986053466797</t>
+    <t xml:space="preserve">149.562805175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.986038208008</t>
   </si>
   <si>
     <t xml:space="preserve">150.919815063477</t>
@@ -3518,16 +3518,16 @@
     <t xml:space="preserve">149.368942260742</t>
   </si>
   <si>
-    <t xml:space="preserve">146.267181396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.104019165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.690414428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.394805908203</t>
+    <t xml:space="preserve">146.267166137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.10400390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.6904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.394821166992</t>
   </si>
   <si>
     <t xml:space="preserve">146.751831054688</t>
@@ -3536,10 +3536,10 @@
     <t xml:space="preserve">149.659729003906</t>
   </si>
   <si>
-    <t xml:space="preserve">145.200958251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.517608642578</t>
+    <t xml:space="preserve">145.200942993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.517623901367</t>
   </si>
   <si>
     <t xml:space="preserve">141.323760986328</t>
@@ -3551,10 +3551,10 @@
     <t xml:space="preserve">134.538665771484</t>
   </si>
   <si>
-    <t xml:space="preserve">136.477249145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.824615478516</t>
+    <t xml:space="preserve">136.477264404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.824630737305</t>
   </si>
   <si>
     <t xml:space="preserve">136.186477661133</t>
@@ -3563,16 +3563,16 @@
     <t xml:space="preserve">135.217178344727</t>
   </si>
   <si>
-    <t xml:space="preserve">130.952285766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.753578186035</t>
+    <t xml:space="preserve">130.952270507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.75358581543</t>
   </si>
   <si>
     <t xml:space="preserve">121.16234588623</t>
   </si>
   <si>
-    <t xml:space="preserve">113.601806640625</t>
+    <t xml:space="preserve">113.60181427002</t>
   </si>
   <si>
     <t xml:space="preserve">117.285148620605</t>
@@ -3581,10 +3581,10 @@
     <t xml:space="preserve">114.958824157715</t>
   </si>
   <si>
-    <t xml:space="preserve">117.575942993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.12198638916</t>
+    <t xml:space="preserve">117.57593536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.121994018555</t>
   </si>
   <si>
     <t xml:space="preserve">119.708396911621</t>
@@ -3599,10 +3599,10 @@
     <t xml:space="preserve">115.443473815918</t>
   </si>
   <si>
-    <t xml:space="preserve">116.516914367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.003852844238</t>
+    <t xml:space="preserve">116.51692199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.003845214844</t>
   </si>
   <si>
     <t xml:space="preserve">117.102432250977</t>
@@ -3617,28 +3617,28 @@
     <t xml:space="preserve">124.909255981445</t>
   </si>
   <si>
-    <t xml:space="preserve">123.640640258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.834823608398</t>
+    <t xml:space="preserve">123.640647888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.834815979004</t>
   </si>
   <si>
     <t xml:space="preserve">120.225158691406</t>
   </si>
   <si>
-    <t xml:space="preserve">119.346900939941</t>
+    <t xml:space="preserve">119.346893310547</t>
   </si>
   <si>
     <t xml:space="preserve">121.005844116211</t>
   </si>
   <si>
-    <t xml:space="preserve">114.857963562012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.539054870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.367034912109</t>
+    <t xml:space="preserve">114.857971191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.5390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.367050170898</t>
   </si>
   <si>
     <t xml:space="preserve">100.512916564941</t>
@@ -3653,19 +3653,19 @@
     <t xml:space="preserve">103.147720336914</t>
   </si>
   <si>
-    <t xml:space="preserve">103.830825805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.07527923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.417335510254</t>
+    <t xml:space="preserve">103.83081817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.075286865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.417327880859</t>
   </si>
   <si>
     <t xml:space="preserve">108.319747924805</t>
   </si>
   <si>
-    <t xml:space="preserve">112.418334960938</t>
+    <t xml:space="preserve">112.418327331543</t>
   </si>
   <si>
     <t xml:space="preserve">113.296600341797</t>
@@ -3674,13 +3674,13 @@
     <t xml:space="preserve">115.541069030762</t>
   </si>
   <si>
-    <t xml:space="preserve">114.272445678711</t>
+    <t xml:space="preserve">114.272453308105</t>
   </si>
   <si>
     <t xml:space="preserve">112.906257629395</t>
   </si>
   <si>
-    <t xml:space="preserve">113.882102966309</t>
+    <t xml:space="preserve">113.882110595703</t>
   </si>
   <si>
     <t xml:space="preserve">111.24730682373</t>
@@ -3698,70 +3698,70 @@
     <t xml:space="preserve">120.615501403809</t>
   </si>
   <si>
-    <t xml:space="preserve">119.054130554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.95654296875</t>
+    <t xml:space="preserve">119.054138183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.956550598145</t>
   </si>
   <si>
     <t xml:space="preserve">113.101432800293</t>
   </si>
   <si>
-    <t xml:space="preserve">116.907257080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.469627380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.323745727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.885108947754</t>
+    <t xml:space="preserve">116.907264709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.469619750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.323753356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.885116577148</t>
   </si>
   <si>
     <t xml:space="preserve">125.006851196289</t>
   </si>
   <si>
-    <t xml:space="preserve">122.66478729248</t>
+    <t xml:space="preserve">122.664794921875</t>
   </si>
   <si>
     <t xml:space="preserve">125.68994140625</t>
   </si>
   <si>
-    <t xml:space="preserve">124.616500854492</t>
+    <t xml:space="preserve">124.616493225098</t>
   </si>
   <si>
     <t xml:space="preserve">119.249305725098</t>
   </si>
   <si>
-    <t xml:space="preserve">123.055137634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.470634460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.957550048828</t>
+    <t xml:space="preserve">123.055130004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.47061920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.957542419434</t>
   </si>
   <si>
     <t xml:space="preserve">125.494773864746</t>
   </si>
   <si>
-    <t xml:space="preserve">134.082275390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.960540771484</t>
+    <t xml:space="preserve">134.082290649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.960571289062</t>
   </si>
   <si>
     <t xml:space="preserve">134.179870605469</t>
   </si>
   <si>
-    <t xml:space="preserve">127.544059753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.177871704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.20100402832</t>
+    <t xml:space="preserve">127.544075012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.177864074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.201011657715</t>
   </si>
   <si>
     <t xml:space="preserve">120.420333862305</t>
@@ -3782,19 +3782,19 @@
     <t xml:space="preserve">114.955558776855</t>
   </si>
   <si>
-    <t xml:space="preserve">110.271453857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.05313873291</t>
+    <t xml:space="preserve">110.271461486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.053131103516</t>
   </si>
   <si>
     <t xml:space="preserve">112.711090087891</t>
   </si>
   <si>
-    <t xml:space="preserve">113.686943054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.46662902832</t>
+    <t xml:space="preserve">113.686935424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.466621398926</t>
   </si>
   <si>
     <t xml:space="preserve">115.443481445312</t>
@@ -3803,646 +3803,649 @@
     <t xml:space="preserve">117.590354919434</t>
   </si>
   <si>
-    <t xml:space="preserve">113.394180297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.832817077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.369041442871</t>
+    <t xml:space="preserve">113.394187927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.832824707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.369033813477</t>
   </si>
   <si>
     <t xml:space="preserve">105.977699279785</t>
   </si>
   <si>
-    <t xml:space="preserve">106.953552246094</t>
+    <t xml:space="preserve">106.953559875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.025985717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.928413391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.70809173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.391189575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.904258728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.513916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.196006774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.001846313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.734237670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.83381652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.150718688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.12557220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.75838470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.440483093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.270454406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.026985168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.100433349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.514923095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.636657714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.978691101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.612510681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.441474914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.172874450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.905250549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.685943603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.320747375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.274452209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.738235473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.028991699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.076286315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.929405212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.223167419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.78352355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.856964111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.588363647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.198020935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.759384155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.200012207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.784530639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.587356567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.831825256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.197021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.099426269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.221160888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.465621948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.41633605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.880111694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.343887329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.052139282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.467628479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.419342041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.883110046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.761375427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.93140411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.39518737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.273445129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.760383605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.98070526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.933403015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.226165771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.152717590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.493766784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.663795471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.6396484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.85897064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.37003326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.515922546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.149726867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.199020385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.540061950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.613502502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.124580383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.954551696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.027992248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.490768432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.148727416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.58935546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.88111114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.051139831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.123573303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.562210083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.464622497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.683937072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.95255279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.781532287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.610504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.342895507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.000839233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.415336608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.074279785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.040893554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.237915039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.3960494995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.2975387573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.184120178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.8885955810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.6915740966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.563255310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.124496459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.139404296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.449844360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.351333618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.252830505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.769355773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.724639892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.670845031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.163391113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.217185974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.641036987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.390213012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.267730712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.381141662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.1005172729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.0661773681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.479652404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.775184631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.548347473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.434936523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.685752868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.420036315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.957290649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.858787536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.011085510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.730461120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.631950378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.4945526123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.7064819335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.2288360595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.2631912231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.164680480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.4258575439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.9035034179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.1303329467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.5198287963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9974670410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.7660980224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4213180541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7317504882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0421829223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.2048568725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.8451690673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.1212463378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.9093322753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.0719909667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.8853378295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.7868347167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.0972747802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.4913177490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.8211898803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.7375869750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.4809417724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7123107910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6630554199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.1556015014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.1705169677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.3331756591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.6585159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.0331115722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.6883239746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.5405654907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.7032318115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.5898208618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.4271469116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.9838638305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.1465225219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.1316146850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.8509979248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.2106857299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.1717987060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.915153503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.2255859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7226791381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.3137359619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2942886352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.2644805908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.6734237670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.806282043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.0032958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.1063461303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.4420547485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3584442138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.3390045166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.0823669433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.9793167114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.6688766479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.1763305664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.7822952270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.521125793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.5256576538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.8898849487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6481475830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3228149414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.3033676147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.0765380859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.460205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.6079711914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.336433410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.661766052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.154304504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.715560913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.223014831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.208106994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.518539428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.942390441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.814064025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.602142333984</t>
   </si>
   <si>
     <t xml:space="preserve">104.025993347168</t>
   </si>
   <si>
-    <t xml:space="preserve">103.928405761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.708084106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.391189575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.904251098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.513916015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.196022033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.001838684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.734230041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.83381652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.150726318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.125579833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.75838470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.440483093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.270462036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.026985168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.100433349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.514923095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.636650085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.978691101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.612503051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.441474914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.172874450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.905258178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.685935974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.320739746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.274459838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.738227844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.028991699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.076286315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.929412841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.223152160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.78352355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.856964111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.588356018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.198013305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.759384155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.200019836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.784523010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.587348937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.831817626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.19701385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.099426269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.221168518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.465621948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.416328430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.88011932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.343894958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.052146911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.467620849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.419326782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.883117675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.761375427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.93140411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.39518737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.273452758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.760383605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.980697631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.933410644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.226165771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.152709960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.493766784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.663787841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.6396484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.85897064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.37003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.515922546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.149719238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.199020385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.540069580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.613510131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.124580383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.954551696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.027992248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.490768432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.148719787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.589363098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.88111114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.051132202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.123573303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.562210083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.464622497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.683944702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.952545166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.781532287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.610504150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.342895507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.000839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.415328979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.074287414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.040893554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.237922668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.3960494995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.2975387573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.184120178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.8885955810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.6915740966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.563255310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.124496459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.139404296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.449836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.351333618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.252830505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.769355773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.724639892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.670845031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.163391113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.217185974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.641036987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.39022064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.267730712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.381141662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.1005172729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.0661697387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.479652404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.775184631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.548347473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.434936523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.685752868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.420028686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.957298278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.858787536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.011085510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.730461120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.631950378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.4945602416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.7064743041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.2288360595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.26318359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.164680480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.4258575439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.9035034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.1303329467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.5198211669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9974670410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.7661056518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.4213180541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.7317581176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0421905517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.2048568725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.8451690673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.1212539672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.9093322753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.0719909667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.8853454589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.7868347167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.0972747802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.4913101196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.8211898803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.7375869750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.4809417724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7123107910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6630630493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.1556015014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.1705093383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.3331756591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.6585235595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.0331039428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.6883239746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.5405654907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.7032318115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.5898208618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.4271469116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.9838562011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.1465225219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.1316146850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.8509979248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.2106857299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.1717987060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.9151611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.2255935668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7226791381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.3137359619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2942810058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.2644805908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.6734161376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.806282043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.003303527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.1063461303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.4420547485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3584518432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.3390045166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.0823669433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.9793167114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.6688766479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.0136642456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.1763381958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.7823028564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.521125793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.5256576538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.8898849487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6481552124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3228073120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.3033676147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.0765380859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.460205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.6079711914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.336433410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.661758422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.154312133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.71556854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.223014831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.208106994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.518539428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.942390441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.814071655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.602142333984</t>
-  </si>
-  <si>
     <t xml:space="preserve">105.306617736816</t>
   </si>
   <si>
-    <t xml:space="preserve">106.78426361084</t>
+    <t xml:space="preserve">106.784255981445</t>
   </si>
   <si>
     <t xml:space="preserve">108.557426452637</t>
@@ -4451,28 +4454,28 @@
     <t xml:space="preserve">108.951461791992</t>
   </si>
   <si>
-    <t xml:space="preserve">107.473815917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.778427124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.28588104248</t>
+    <t xml:space="preserve">107.473823547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.778434753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.285888671875</t>
   </si>
   <si>
     <t xml:space="preserve">111.808242797852</t>
   </si>
   <si>
-    <t xml:space="preserve">115.35457611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.029251098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.438179016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.521789550781</t>
+    <t xml:space="preserve">115.354583740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.029243469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.438186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.521797180176</t>
   </si>
   <si>
     <t xml:space="preserve">119.491981506348</t>
@@ -4487,7 +4490,7 @@
     <t xml:space="preserve">114.763519287109</t>
   </si>
   <si>
-    <t xml:space="preserve">112.30078125</t>
+    <t xml:space="preserve">112.300788879395</t>
   </si>
   <si>
     <t xml:space="preserve">112.596313476562</t>
@@ -4499,7 +4502,7 @@
     <t xml:space="preserve">115.847129821777</t>
   </si>
   <si>
-    <t xml:space="preserve">116.33967590332</t>
+    <t xml:space="preserve">116.339668273926</t>
   </si>
   <si>
     <t xml:space="preserve">118.112846374512</t>
@@ -4508,13 +4511,13 @@
     <t xml:space="preserve">119.886009216309</t>
   </si>
   <si>
-    <t xml:space="preserve">120.181541442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.787498474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.39347076416</t>
+    <t xml:space="preserve">120.181549072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.787506103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.393463134766</t>
   </si>
   <si>
     <t xml:space="preserve">121.757698059082</t>
@@ -4535,13 +4538,13 @@
     <t xml:space="preserve">125.10701751709</t>
   </si>
   <si>
-    <t xml:space="preserve">125.30403137207</t>
+    <t xml:space="preserve">125.304039001465</t>
   </si>
   <si>
     <t xml:space="preserve">125.599563598633</t>
   </si>
   <si>
-    <t xml:space="preserve">124.811485290527</t>
+    <t xml:space="preserve">124.811492919922</t>
   </si>
   <si>
     <t xml:space="preserve">125.008506774902</t>
@@ -4553,16 +4556,16 @@
     <t xml:space="preserve">126.584663391113</t>
   </si>
   <si>
-    <t xml:space="preserve">123.727882385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.796585083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.121925354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.462173461914</t>
+    <t xml:space="preserve">123.727890014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.796577453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.121917724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.46216583252</t>
   </si>
   <si>
     <t xml:space="preserve">120.280052185059</t>
@@ -4571,7 +4574,7 @@
     <t xml:space="preserve">121.659187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">120.575584411621</t>
+    <t xml:space="preserve">120.575576782227</t>
   </si>
   <si>
     <t xml:space="preserve">122.64427947998</t>
@@ -4580,7 +4583,7 @@
     <t xml:space="preserve">122.742790222168</t>
   </si>
   <si>
-    <t xml:space="preserve">125.205528259277</t>
+    <t xml:space="preserve">125.205520629883</t>
   </si>
   <si>
     <t xml:space="preserve">126.190628051758</t>
@@ -4595,10 +4598,10 @@
     <t xml:space="preserve">123.235336303711</t>
   </si>
   <si>
-    <t xml:space="preserve">124.515968322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.151741027832</t>
+    <t xml:space="preserve">124.515960693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.151733398438</t>
   </si>
   <si>
     <t xml:space="preserve">122.841300964355</t>
@@ -4613,10 +4616,10 @@
     <t xml:space="preserve">130.032501220703</t>
   </si>
   <si>
-    <t xml:space="preserve">130.820571899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.722061157227</t>
+    <t xml:space="preserve">130.820556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.722045898438</t>
   </si>
   <si>
     <t xml:space="preserve">129.835479736328</t>
@@ -4631,7 +4634,7 @@
     <t xml:space="preserve">127.569747924805</t>
   </si>
   <si>
-    <t xml:space="preserve">127.668266296387</t>
+    <t xml:space="preserve">127.668258666992</t>
   </si>
   <si>
     <t xml:space="preserve">129.244415283203</t>
@@ -4643,7 +4646,7 @@
     <t xml:space="preserve">130.131011962891</t>
   </si>
   <si>
-    <t xml:space="preserve">129.441436767578</t>
+    <t xml:space="preserve">129.441421508789</t>
   </si>
   <si>
     <t xml:space="preserve">126.486145019531</t>
@@ -4652,22 +4655,22 @@
     <t xml:space="preserve">128.16081237793</t>
   </si>
   <si>
-    <t xml:space="preserve">126.387641906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.909996032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.053230285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.265144348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.25023651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.166633605957</t>
+    <t xml:space="preserve">126.387649536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.910003662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.05322265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.265151977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.250244140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.166641235352</t>
   </si>
   <si>
     <t xml:space="preserve">133.677337646484</t>
@@ -4676,7 +4679,7 @@
     <t xml:space="preserve">131.116104125977</t>
   </si>
   <si>
-    <t xml:space="preserve">134.760955810547</t>
+    <t xml:space="preserve">134.760940551758</t>
   </si>
   <si>
     <t xml:space="preserve">135.058654785156</t>
@@ -4779,9 +4782,6 @@
   </si>
   <si>
     <t xml:space="preserve">134.860168457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.760940551758</t>
   </si>
   <si>
     <t xml:space="preserve">136.944107055664</t>
@@ -58284,7 +58284,7 @@
         <v>105.599998474121</v>
       </c>
       <c r="G2019" t="s">
-        <v>1268</v>
+        <v>1475</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -58310,7 +58310,7 @@
         <v>106.900001525879</v>
       </c>
       <c r="G2020" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -58336,7 +58336,7 @@
         <v>108.400001525879</v>
       </c>
       <c r="G2021" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -58388,7 +58388,7 @@
         <v>110.199996948242</v>
       </c>
       <c r="G2023" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -58414,7 +58414,7 @@
         <v>110.199996948242</v>
       </c>
       <c r="G2024" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -58440,7 +58440,7 @@
         <v>110.599998474121</v>
       </c>
       <c r="G2025" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -58466,7 +58466,7 @@
         <v>109.099998474121</v>
       </c>
       <c r="G2026" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -58492,7 +58492,7 @@
         <v>115.5</v>
       </c>
       <c r="G2027" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -58518,7 +58518,7 @@
         <v>115</v>
       </c>
       <c r="G2028" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -58544,7 +58544,7 @@
         <v>113.5</v>
       </c>
       <c r="G2029" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -58570,7 +58570,7 @@
         <v>117.099998474121</v>
       </c>
       <c r="G2030" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -58596,7 +58596,7 @@
         <v>118.800003051758</v>
       </c>
       <c r="G2031" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -58622,7 +58622,7 @@
         <v>118.199996948242</v>
       </c>
       <c r="G2032" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -58648,7 +58648,7 @@
         <v>119.300003051758</v>
       </c>
       <c r="G2033" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -58674,7 +58674,7 @@
         <v>121.300003051758</v>
       </c>
       <c r="G2034" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -58700,7 +58700,7 @@
         <v>119.800003051758</v>
       </c>
       <c r="G2035" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -58726,7 +58726,7 @@
         <v>119.5</v>
       </c>
       <c r="G2036" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -58752,7 +58752,7 @@
         <v>116.5</v>
       </c>
       <c r="G2037" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -58778,7 +58778,7 @@
         <v>114</v>
       </c>
       <c r="G2038" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -58804,7 +58804,7 @@
         <v>114.300003051758</v>
       </c>
       <c r="G2039" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -58830,7 +58830,7 @@
         <v>113.099998474121</v>
       </c>
       <c r="G2040" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -58856,7 +58856,7 @@
         <v>115.5</v>
       </c>
       <c r="G2041" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -58882,7 +58882,7 @@
         <v>117.599998474121</v>
       </c>
       <c r="G2042" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -58908,7 +58908,7 @@
         <v>118.099998474121</v>
       </c>
       <c r="G2043" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -58934,7 +58934,7 @@
         <v>119.900001525879</v>
       </c>
       <c r="G2044" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -58960,7 +58960,7 @@
         <v>121.699996948242</v>
       </c>
       <c r="G2045" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -58986,7 +58986,7 @@
         <v>122</v>
       </c>
       <c r="G2046" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -59012,7 +59012,7 @@
         <v>121.599998474121</v>
       </c>
       <c r="G2047" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -59038,7 +59038,7 @@
         <v>121.199996948242</v>
       </c>
       <c r="G2048" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -59064,7 +59064,7 @@
         <v>122</v>
       </c>
       <c r="G2049" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -59090,7 +59090,7 @@
         <v>119.900001525879</v>
       </c>
       <c r="G2050" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -59116,7 +59116,7 @@
         <v>123.599998474121</v>
       </c>
       <c r="G2051" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -59142,7 +59142,7 @@
         <v>121.900001525879</v>
       </c>
       <c r="G2052" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -59168,7 +59168,7 @@
         <v>123.199996948242</v>
       </c>
       <c r="G2053" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -59194,7 +59194,7 @@
         <v>125.699996948242</v>
       </c>
       <c r="G2054" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -59220,7 +59220,7 @@
         <v>126.099998474121</v>
       </c>
       <c r="G2055" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -59246,7 +59246,7 @@
         <v>127</v>
       </c>
       <c r="G2056" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -59272,7 +59272,7 @@
         <v>127.199996948242</v>
       </c>
       <c r="G2057" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -59298,7 +59298,7 @@
         <v>127.5</v>
       </c>
       <c r="G2058" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -59324,7 +59324,7 @@
         <v>126.699996948242</v>
       </c>
       <c r="G2059" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -59350,7 +59350,7 @@
         <v>126.900001525879</v>
       </c>
       <c r="G2060" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -59376,7 +59376,7 @@
         <v>125.900001525879</v>
       </c>
       <c r="G2061" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -59402,7 +59402,7 @@
         <v>128.5</v>
       </c>
       <c r="G2062" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -59428,7 +59428,7 @@
         <v>127.199996948242</v>
       </c>
       <c r="G2063" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -59454,7 +59454,7 @@
         <v>125.599998474121</v>
       </c>
       <c r="G2064" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -59480,7 +59480,7 @@
         <v>127.699996948242</v>
       </c>
       <c r="G2065" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -59506,7 +59506,7 @@
         <v>126</v>
       </c>
       <c r="G2066" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -59532,7 +59532,7 @@
         <v>121.599998474121</v>
       </c>
       <c r="G2067" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -59558,7 +59558,7 @@
         <v>123.300003051758</v>
       </c>
       <c r="G2068" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -59584,7 +59584,7 @@
         <v>121.599998474121</v>
       </c>
       <c r="G2069" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -59610,7 +59610,7 @@
         <v>122.099998474121</v>
       </c>
       <c r="G2070" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -59636,7 +59636,7 @@
         <v>123.5</v>
       </c>
       <c r="G2071" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -59662,7 +59662,7 @@
         <v>122.400001525879</v>
       </c>
       <c r="G2072" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -59688,7 +59688,7 @@
         <v>121.199996948242</v>
       </c>
       <c r="G2073" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -59714,7 +59714,7 @@
         <v>124.5</v>
       </c>
       <c r="G2074" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -59740,7 +59740,7 @@
         <v>124.599998474121</v>
       </c>
       <c r="G2075" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -59766,7 +59766,7 @@
         <v>127.099998474121</v>
       </c>
       <c r="G2076" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -59792,7 +59792,7 @@
         <v>128.100006103516</v>
       </c>
       <c r="G2077" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -59818,7 +59818,7 @@
         <v>128.5</v>
       </c>
       <c r="G2078" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -59844,7 +59844,7 @@
         <v>128.199996948242</v>
       </c>
       <c r="G2079" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -59870,7 +59870,7 @@
         <v>127.599998474121</v>
       </c>
       <c r="G2080" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -59896,7 +59896,7 @@
         <v>128.100006103516</v>
       </c>
       <c r="G2081" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -59922,7 +59922,7 @@
         <v>122.400001525879</v>
       </c>
       <c r="G2082" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -59948,7 +59948,7 @@
         <v>125.099998474121</v>
       </c>
       <c r="G2083" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -59974,7 +59974,7 @@
         <v>126.400001525879</v>
       </c>
       <c r="G2084" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -60000,7 +60000,7 @@
         <v>127.599998474121</v>
       </c>
       <c r="G2085" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -60026,7 +60026,7 @@
         <v>124</v>
       </c>
       <c r="G2086" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -60052,7 +60052,7 @@
         <v>124.699996948242</v>
       </c>
       <c r="G2087" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -60078,7 +60078,7 @@
         <v>132.5</v>
       </c>
       <c r="G2088" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -60104,7 +60104,7 @@
         <v>130.899993896484</v>
       </c>
       <c r="G2089" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -60130,7 +60130,7 @@
         <v>132</v>
       </c>
       <c r="G2090" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -60156,7 +60156,7 @@
         <v>132.800003051758</v>
       </c>
       <c r="G2091" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -60182,7 +60182,7 @@
         <v>132.699996948242</v>
       </c>
       <c r="G2092" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -60208,7 +60208,7 @@
         <v>131.800003051758</v>
       </c>
       <c r="G2093" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -60234,7 +60234,7 @@
         <v>131</v>
       </c>
       <c r="G2094" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -60260,7 +60260,7 @@
         <v>131.699996948242</v>
       </c>
       <c r="G2095" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -60286,7 +60286,7 @@
         <v>129.5</v>
       </c>
       <c r="G2096" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -60312,7 +60312,7 @@
         <v>129.600006103516</v>
       </c>
       <c r="G2097" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -60338,7 +60338,7 @@
         <v>132.800003051758</v>
       </c>
       <c r="G2098" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -60364,7 +60364,7 @@
         <v>131.199996948242</v>
       </c>
       <c r="G2099" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -60390,7 +60390,7 @@
         <v>129.899993896484</v>
       </c>
       <c r="G2100" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -60416,7 +60416,7 @@
         <v>132.100006103516</v>
       </c>
       <c r="G2101" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -60442,7 +60442,7 @@
         <v>131.399993896484</v>
       </c>
       <c r="G2102" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -60468,7 +60468,7 @@
         <v>128.399993896484</v>
       </c>
       <c r="G2103" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -60494,7 +60494,7 @@
         <v>130.100006103516</v>
       </c>
       <c r="G2104" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -60520,7 +60520,7 @@
         <v>128.300003051758</v>
       </c>
       <c r="G2105" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -60546,7 +60546,7 @@
         <v>127.699996948242</v>
       </c>
       <c r="G2106" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -60572,7 +60572,7 @@
         <v>127.5</v>
       </c>
       <c r="G2107" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -60598,7 +60598,7 @@
         <v>126.800003051758</v>
       </c>
       <c r="G2108" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -60624,7 +60624,7 @@
         <v>127</v>
       </c>
       <c r="G2109" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -60650,7 +60650,7 @@
         <v>124.599998474121</v>
       </c>
       <c r="G2110" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -60676,7 +60676,7 @@
         <v>123.900001525879</v>
       </c>
       <c r="G2111" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -60702,7 +60702,7 @@
         <v>123.300003051758</v>
       </c>
       <c r="G2112" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -60728,7 +60728,7 @@
         <v>121.300003051758</v>
       </c>
       <c r="G2113" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -60754,7 +60754,7 @@
         <v>123.099998474121</v>
       </c>
       <c r="G2114" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -60780,7 +60780,7 @@
         <v>125.699996948242</v>
       </c>
       <c r="G2115" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -60806,7 +60806,7 @@
         <v>124.599998474121</v>
       </c>
       <c r="G2116" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -60832,7 +60832,7 @@
         <v>124.099998474121</v>
       </c>
       <c r="G2117" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -60858,7 +60858,7 @@
         <v>124.099998474121</v>
       </c>
       <c r="G2118" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -60884,7 +60884,7 @@
         <v>123.900001525879</v>
       </c>
       <c r="G2119" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -60910,7 +60910,7 @@
         <v>123</v>
       </c>
       <c r="G2120" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -60936,7 +60936,7 @@
         <v>123.300003051758</v>
       </c>
       <c r="G2121" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -60962,7 +60962,7 @@
         <v>124.099998474121</v>
       </c>
       <c r="G2122" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -60988,7 +60988,7 @@
         <v>124.5</v>
       </c>
       <c r="G2123" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -61014,7 +61014,7 @@
         <v>126.900001525879</v>
       </c>
       <c r="G2124" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -61040,7 +61040,7 @@
         <v>127</v>
       </c>
       <c r="G2125" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -61066,7 +61066,7 @@
         <v>127</v>
       </c>
       <c r="G2126" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -61092,7 +61092,7 @@
         <v>127.099998474121</v>
       </c>
       <c r="G2127" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -61118,7 +61118,7 @@
         <v>125.900001525879</v>
       </c>
       <c r="G2128" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -61144,7 +61144,7 @@
         <v>135.699996948242</v>
       </c>
       <c r="G2129" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -61170,7 +61170,7 @@
         <v>133.100006103516</v>
       </c>
       <c r="G2130" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -61196,7 +61196,7 @@
         <v>136.800003051758</v>
       </c>
       <c r="G2131" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -61222,7 +61222,7 @@
         <v>136.800003051758</v>
       </c>
       <c r="G2132" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -61248,7 +61248,7 @@
         <v>136.100006103516</v>
       </c>
       <c r="G2133" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -61274,7 +61274,7 @@
         <v>136.5</v>
       </c>
       <c r="G2134" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -61300,7 +61300,7 @@
         <v>136</v>
       </c>
       <c r="G2135" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -61326,7 +61326,7 @@
         <v>136</v>
       </c>
       <c r="G2136" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -61352,7 +61352,7 @@
         <v>136.399993896484</v>
       </c>
       <c r="G2137" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -61378,7 +61378,7 @@
         <v>137.600006103516</v>
       </c>
       <c r="G2138" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -61404,7 +61404,7 @@
         <v>137.5</v>
       </c>
       <c r="G2139" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -61430,7 +61430,7 @@
         <v>133.600006103516</v>
       </c>
       <c r="G2140" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -61456,7 +61456,7 @@
         <v>133.300003051758</v>
       </c>
       <c r="G2141" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -61482,7 +61482,7 @@
         <v>126.400001525879</v>
       </c>
       <c r="G2142" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -61508,7 +61508,7 @@
         <v>128.399993896484</v>
       </c>
       <c r="G2143" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -61534,7 +61534,7 @@
         <v>128.5</v>
       </c>
       <c r="G2144" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -61560,7 +61560,7 @@
         <v>130.800003051758</v>
       </c>
       <c r="G2145" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -61586,7 +61586,7 @@
         <v>134.100006103516</v>
       </c>
       <c r="G2146" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -61612,7 +61612,7 @@
         <v>136.600006103516</v>
       </c>
       <c r="G2147" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -61638,7 +61638,7 @@
         <v>136</v>
       </c>
       <c r="G2148" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -61664,7 +61664,7 @@
         <v>133.399993896484</v>
       </c>
       <c r="G2149" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -61690,7 +61690,7 @@
         <v>136.5</v>
       </c>
       <c r="G2150" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -61716,7 +61716,7 @@
         <v>134.399993896484</v>
       </c>
       <c r="G2151" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -61742,7 +61742,7 @@
         <v>133.399993896484</v>
       </c>
       <c r="G2152" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -61768,7 +61768,7 @@
         <v>133.800003051758</v>
       </c>
       <c r="G2153" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -61794,7 +61794,7 @@
         <v>135.199996948242</v>
       </c>
       <c r="G2154" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -61820,7 +61820,7 @@
         <v>133.800003051758</v>
       </c>
       <c r="G2155" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -61846,7 +61846,7 @@
         <v>139</v>
       </c>
       <c r="G2156" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -61872,7 +61872,7 @@
         <v>138.100006103516</v>
       </c>
       <c r="G2157" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -61898,7 +61898,7 @@
         <v>142.199996948242</v>
       </c>
       <c r="G2158" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -61924,7 +61924,7 @@
         <v>140.399993896484</v>
       </c>
       <c r="G2159" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -61950,7 +61950,7 @@
         <v>137.5</v>
       </c>
       <c r="G2160" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -61976,7 +61976,7 @@
         <v>138.199996948242</v>
       </c>
       <c r="G2161" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -62002,7 +62002,7 @@
         <v>137.800003051758</v>
       </c>
       <c r="G2162" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -62028,7 +62028,7 @@
         <v>136.100006103516</v>
       </c>
       <c r="G2163" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -62054,7 +62054,7 @@
         <v>136.300003051758</v>
       </c>
       <c r="G2164" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -62080,7 +62080,7 @@
         <v>139.600006103516</v>
       </c>
       <c r="G2165" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -62106,7 +62106,7 @@
         <v>140.199996948242</v>
       </c>
       <c r="G2166" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -62132,7 +62132,7 @@
         <v>141.399993896484</v>
       </c>
       <c r="G2167" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -62158,7 +62158,7 @@
         <v>140.199996948242</v>
       </c>
       <c r="G2168" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -62184,7 +62184,7 @@
         <v>139.199996948242</v>
       </c>
       <c r="G2169" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -62210,7 +62210,7 @@
         <v>140</v>
       </c>
       <c r="G2170" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -62236,7 +62236,7 @@
         <v>140</v>
       </c>
       <c r="G2171" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -62262,7 +62262,7 @@
         <v>141.600006103516</v>
       </c>
       <c r="G2172" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -62288,7 +62288,7 @@
         <v>140.199996948242</v>
       </c>
       <c r="G2173" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -62314,7 +62314,7 @@
         <v>139.800003051758</v>
       </c>
       <c r="G2174" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -62340,7 +62340,7 @@
         <v>137.300003051758</v>
       </c>
       <c r="G2175" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -62366,7 +62366,7 @@
         <v>135.899993896484</v>
       </c>
       <c r="G2176" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -62392,7 +62392,7 @@
         <v>135.800003051758</v>
       </c>
       <c r="G2177" t="s">
-        <v>1589</v>
+        <v>1555</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -62444,7 +62444,7 @@
         <v>139</v>
       </c>
       <c r="G2179" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -62470,7 +62470,7 @@
         <v>135.800003051758</v>
       </c>
       <c r="G2180" t="s">
-        <v>1589</v>
+        <v>1555</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -62808,7 +62808,7 @@
         <v>128.399993896484</v>
       </c>
       <c r="G2193" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -62886,7 +62886,7 @@
         <v>134.399993896484</v>
       </c>
       <c r="G2196" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -62938,7 +62938,7 @@
         <v>136.100006103516</v>
       </c>
       <c r="G2198" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -62990,7 +62990,7 @@
         <v>137.800003051758</v>
       </c>
       <c r="G2200" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -63016,7 +63016,7 @@
         <v>138.199996948242</v>
       </c>
       <c r="G2201" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -63068,7 +63068,7 @@
         <v>139.800003051758</v>
       </c>
       <c r="G2203" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -63094,7 +63094,7 @@
         <v>140.199996948242</v>
       </c>
       <c r="G2204" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -63224,7 +63224,7 @@
         <v>136.300003051758</v>
       </c>
       <c r="G2209" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -63250,7 +63250,7 @@
         <v>134.100006103516</v>
       </c>
       <c r="G2210" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -63380,7 +63380,7 @@
         <v>137.800003051758</v>
       </c>
       <c r="G2215" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -63406,7 +63406,7 @@
         <v>137.600006103516</v>
       </c>
       <c r="G2216" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -63562,7 +63562,7 @@
         <v>135.800003051758</v>
       </c>
       <c r="G2222" t="s">
-        <v>1589</v>
+        <v>1555</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -63588,7 +63588,7 @@
         <v>133.600006103516</v>
       </c>
       <c r="G2223" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -63692,7 +63692,7 @@
         <v>135.199996948242</v>
       </c>
       <c r="G2227" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -63900,7 +63900,7 @@
         <v>133.600006103516</v>
       </c>
       <c r="G2235" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -63926,7 +63926,7 @@
         <v>133.300003051758</v>
       </c>
       <c r="G2236" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -63978,7 +63978,7 @@
         <v>140.399993896484</v>
       </c>
       <c r="G2238" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -64524,7 +64524,7 @@
         <v>140.399993896484</v>
       </c>
       <c r="G2259" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -67072,7 +67072,7 @@
         <v>136.100006103516</v>
       </c>
       <c r="G2357" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -70512,7 +70512,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6499884259</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>60211</v>
@@ -70533,6 +70533,32 @@
         <v>1815</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6495601852</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>55985</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>120</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>117.800003051758</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>119.099998474121</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>118.300003051758</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>1810</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/REY.MI.xlsx
+++ b/data/REY.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1816" uniqueCount="1816">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="1817">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,76 +44,76 @@
     <t xml:space="preserve">REY.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8380279541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3272113800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6306419372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8396091461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2111167907715</t>
+    <t xml:space="preserve">28.8380298614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.327205657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6306400299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8396110534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2111148834229</t>
   </si>
   <si>
     <t xml:space="preserve">29.0005626678467</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5594005584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1414566040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1198253631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9789257049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8644104003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4448852539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9324893951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8163967132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2807731628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6770763397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0950183868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8628311157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2591361999512</t>
+    <t xml:space="preserve">28.5594024658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1414585113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1198196411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9789237976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8644123077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4448833465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9324855804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8163928985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2807769775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6770782470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0950222015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.862829208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2591342926025</t>
   </si>
   <si>
     <t xml:space="preserve">26.7018795013428</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1678371429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2855186462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3799743652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6121692657471</t>
+    <t xml:space="preserve">26.167839050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2855167388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.379976272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6121673583984</t>
   </si>
   <si>
     <t xml:space="preserve">26.0053081512451</t>
@@ -122,52 +122,52 @@
     <t xml:space="preserve">25.517707824707</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6570205688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6074180603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3071556091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0733833312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2142772674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4696922302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0517444610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7034606933594</t>
+    <t xml:space="preserve">25.6570243835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6074199676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3071594238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0733871459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2142791748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4696884155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0517482757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7034587860107</t>
   </si>
   <si>
     <t xml:space="preserve">25.7266807556152</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7483158111572</t>
+    <t xml:space="preserve">26.7483196258545</t>
   </si>
   <si>
     <t xml:space="preserve">26.4929065704346</t>
   </si>
   <si>
-    <t xml:space="preserve">27.352014541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1894760131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2359199523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1662578582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9092674255371</t>
+    <t xml:space="preserve">27.3520107269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1894817352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2359142303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.166259765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9092693328857</t>
   </si>
   <si>
     <t xml:space="preserve">29.0237789154053</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">31.5546493530273</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3008232116699</t>
+    <t xml:space="preserve">30.3008251190186</t>
   </si>
   <si>
     <t xml:space="preserve">30.4169235229492</t>
@@ -191,28 +191,28 @@
     <t xml:space="preserve">29.7900085449219</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9525413513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2311706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7203502655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0686378479004</t>
+    <t xml:space="preserve">29.952543258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2311687469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7203521728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0686359405518</t>
   </si>
   <si>
     <t xml:space="preserve">29.8596668243408</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5578212738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3256282806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4881610870361</t>
+    <t xml:space="preserve">29.5578193664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3256301879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4881649017334</t>
   </si>
   <si>
     <t xml:space="preserve">29.511381149292</t>
@@ -221,82 +221,82 @@
     <t xml:space="preserve">29.2095336914062</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1615161895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3720645904541</t>
+    <t xml:space="preserve">30.1615123748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3720664978027</t>
   </si>
   <si>
     <t xml:space="preserve">29.5345993041992</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4433040618896</t>
+    <t xml:space="preserve">28.4433059692383</t>
   </si>
   <si>
     <t xml:space="preserve">28.6754970550537</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8612480163574</t>
+    <t xml:space="preserve">28.8612499237061</t>
   </si>
   <si>
     <t xml:space="preserve">28.814811706543</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9076862335205</t>
+    <t xml:space="preserve">28.9076843261719</t>
   </si>
   <si>
     <t xml:space="preserve">28.6290607452393</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4200839996338</t>
+    <t xml:space="preserve">28.4200878143311</t>
   </si>
   <si>
     <t xml:space="preserve">28.6775989532471</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5605487823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.028751373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3264446258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.513729095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7946510314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0053424835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2628555297852</t>
+    <t xml:space="preserve">28.5605449676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0287551879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3264465332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5137329101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7946529388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0053405761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2628536224365</t>
   </si>
   <si>
     <t xml:space="preserve">30.1992683410645</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5036010742188</t>
+    <t xml:space="preserve">30.503604888916</t>
   </si>
   <si>
     <t xml:space="preserve">30.5504188537598</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9015769958496</t>
+    <t xml:space="preserve">30.9015789031982</t>
   </si>
   <si>
     <t xml:space="preserve">30.6674747467041</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7142925262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4567852020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4333724975586</t>
+    <t xml:space="preserve">30.7142944335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4567832946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.43337059021</t>
   </si>
   <si>
     <t xml:space="preserve">30.2694988250732</t>
@@ -305,31 +305,31 @@
     <t xml:space="preserve">29.8949337005615</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1859836578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3096771240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4969596862793</t>
+    <t xml:space="preserve">28.1859874725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3096752166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4969615936279</t>
   </si>
   <si>
     <t xml:space="preserve">27.6943702697754</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7747211456299</t>
+    <t xml:space="preserve">25.7747192382812</t>
   </si>
   <si>
     <t xml:space="preserve">26.8047771453857</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3198013305664</t>
+    <t xml:space="preserve">27.319803237915</t>
   </si>
   <si>
     <t xml:space="preserve">26.9218292236328</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5070877075195</t>
+    <t xml:space="preserve">27.5070838928223</t>
   </si>
   <si>
     <t xml:space="preserve">26.9452381134033</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">26.2195205688477</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1091136932373</t>
+    <t xml:space="preserve">27.1091117858887</t>
   </si>
   <si>
     <t xml:space="preserve">27.624137878418</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3666229248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3030338287354</t>
+    <t xml:space="preserve">27.366626739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.303035736084</t>
   </si>
   <si>
     <t xml:space="preserve">28.8882923126221</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">28.7478313446045</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4434986114502</t>
+    <t xml:space="preserve">28.4434967041016</t>
   </si>
   <si>
     <t xml:space="preserve">28.98193359375</t>
@@ -368,97 +368,97 @@
     <t xml:space="preserve">28.9117050170898</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3799076080322</t>
+    <t xml:space="preserve">29.3799095153809</t>
   </si>
   <si>
     <t xml:space="preserve">29.4501399993896</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8481140136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1524467468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9651641845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7244205474854</t>
+    <t xml:space="preserve">29.8481159210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1524505615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9651660919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7244186401367</t>
   </si>
   <si>
     <t xml:space="preserve">29.1458053588867</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0989856719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9351119995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4903182983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9752922058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3732643127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0923442840576</t>
+    <t xml:space="preserve">29.0989875793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9351100921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4903163909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9752941131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3732662200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.092342376709</t>
   </si>
   <si>
     <t xml:space="preserve">27.2729835510254</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0622901916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0388813018799</t>
+    <t xml:space="preserve">27.0622882843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0388793945312</t>
   </si>
   <si>
     <t xml:space="preserve">26.898416519165</t>
   </si>
   <si>
-    <t xml:space="preserve">26.149284362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7981338500977</t>
+    <t xml:space="preserve">26.1492881774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7981300354004</t>
   </si>
   <si>
     <t xml:space="preserve">25.8917751312256</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7579555511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9518814086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8816528320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8114223480225</t>
+    <t xml:space="preserve">26.7579574584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.95188331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8816509246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8114204406738</t>
   </si>
   <si>
     <t xml:space="preserve">27.9050598144531</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2963943481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8582420349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.577320098877</t>
+    <t xml:space="preserve">27.2963981628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8582401275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5773162841797</t>
   </si>
   <si>
     <t xml:space="preserve">27.7177772521973</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7411880493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0455265045166</t>
+    <t xml:space="preserve">27.7411918640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0455226898193</t>
   </si>
   <si>
     <t xml:space="preserve">27.7880058288574</t>
@@ -467,124 +467,124 @@
     <t xml:space="preserve">27.3900337219238</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1223945617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6541881561279</t>
+    <t xml:space="preserve">29.1223964691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6541900634766</t>
   </si>
   <si>
     <t xml:space="preserve">28.2093944549561</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4134426116943</t>
+    <t xml:space="preserve">27.4134464263916</t>
   </si>
   <si>
     <t xml:space="preserve">27.0856990814209</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8515968322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4368515014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6877288818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2261638641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8281860351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6409072875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4536247253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5706748962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.523853302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3365726470947</t>
+    <t xml:space="preserve">26.851598739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4368534088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6877269744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2261619567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8281879425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6409091949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4536190032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5706729888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5238590240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3365707397461</t>
   </si>
   <si>
     <t xml:space="preserve">25.751314163208</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3299312591553</t>
+    <t xml:space="preserve">25.329927444458</t>
   </si>
   <si>
     <t xml:space="preserve">24.7446727752686</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7680816650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8851318359375</t>
+    <t xml:space="preserve">24.7680854797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8851337432861</t>
   </si>
   <si>
     <t xml:space="preserve">24.2530555725098</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0490093231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4703903198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5172100067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2831077575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1660575866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.446985244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0958271026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.931957244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0724182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6342639923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1961078643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1727027893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8348274230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9284744262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4602680206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9987010955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6307792663574</t>
+    <t xml:space="preserve">25.0490055084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4703922271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5172119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.283109664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1660556793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4469795227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0958290100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9319553375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.072416305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6342620849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1961135864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.172700881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8348293304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9284725189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4602642059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9986991882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6307773590088</t>
   </si>
   <si>
     <t xml:space="preserve">29.2160358428955</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3330879211426</t>
+    <t xml:space="preserve">29.3330841064453</t>
   </si>
   <si>
     <t xml:space="preserve">28.8648853302002</t>
@@ -596,10 +596,10 @@
     <t xml:space="preserve">28.6073684692383</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4735488891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2394466400146</t>
+    <t xml:space="preserve">29.4735507965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2394485473633</t>
   </si>
   <si>
     <t xml:space="preserve">29.7076511383057</t>
@@ -608,85 +608,85 @@
     <t xml:space="preserve">29.4267292022705</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8313426971436</t>
+    <t xml:space="preserve">30.8313446044922</t>
   </si>
   <si>
     <t xml:space="preserve">30.9952182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4868316650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2527294158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3697872161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1356792449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1891441345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3061943054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2660179138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0619621276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6472244262695</t>
+    <t xml:space="preserve">31.4868354797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2527275085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.369779586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1356830596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1891479492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3061866760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2660140991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0619659423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6472206115723</t>
   </si>
   <si>
     <t xml:space="preserve">34.4599456787109</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7408638000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6706314086914</t>
+    <t xml:space="preserve">34.7408599853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6706352233887</t>
   </si>
   <si>
     <t xml:space="preserve">34.9983749389648</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8579139709473</t>
+    <t xml:space="preserve">34.85791015625</t>
   </si>
   <si>
     <t xml:space="preserve">34.1790199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7642669677734</t>
+    <t xml:space="preserve">34.7642707824707</t>
   </si>
   <si>
     <t xml:space="preserve">34.8813285827637</t>
   </si>
   <si>
-    <t xml:space="preserve">34.389705657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4131240844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6070442199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4665794372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7943229675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.8243751525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6671485900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8778381347656</t>
+    <t xml:space="preserve">34.3897132873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4131202697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.607048034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4665832519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7943267822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.8243789672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6671524047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8778419494629</t>
   </si>
   <si>
     <t xml:space="preserve">36.9882507324219</t>
@@ -695,130 +695,130 @@
     <t xml:space="preserve">37.5735054016113</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6203308105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6085395812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7264289855957</t>
+    <t xml:space="preserve">37.6203269958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6085357666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7264404296875</t>
   </si>
   <si>
     <t xml:space="preserve">37.9150733947754</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1980133056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9386405944824</t>
+    <t xml:space="preserve">38.1980094909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.938648223877</t>
   </si>
   <si>
     <t xml:space="preserve">38.1508560180664</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4906463623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0232810974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0843353271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0607528686523</t>
+    <t xml:space="preserve">37.4906425476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0232849121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0843391418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0607604980469</t>
   </si>
   <si>
     <t xml:space="preserve">39.8013916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2397041320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0274925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4519157409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7112922668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4990730285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8056106567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3243446350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1828727722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.088550567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2771873474121</t>
+    <t xml:space="preserve">41.2397079467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0274963378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4519233703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7112884521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.499080657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.805606842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3243408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1828689575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0885543823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2771835327148</t>
   </si>
   <si>
     <t xml:space="preserve">41.8291816711426</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9664459228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5891761779785</t>
+    <t xml:space="preserve">39.9664421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5891799926758</t>
   </si>
   <si>
     <t xml:space="preserve">38.4338073730469</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9997024536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6363334655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9428634643555</t>
+    <t xml:space="preserve">38.999698638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6363296508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9428596496582</t>
   </si>
   <si>
     <t xml:space="preserve">40.4380226135254</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5517044067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0565376281738</t>
+    <t xml:space="preserve">38.551700592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0565452575684</t>
   </si>
   <si>
     <t xml:space="preserve">39.1411781311035</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3298072814941</t>
+    <t xml:space="preserve">39.3298110961914</t>
   </si>
   <si>
     <t xml:space="preserve">39.0704383850098</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1647567749023</t>
+    <t xml:space="preserve">39.1647529602051</t>
   </si>
   <si>
     <t xml:space="preserve">38.6695938110352</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8346481323242</t>
+    <t xml:space="preserve">38.8346519470215</t>
   </si>
   <si>
     <t xml:space="preserve">38.905387878418</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0940170288086</t>
+    <t xml:space="preserve">39.0940246582031</t>
   </si>
   <si>
     <t xml:space="preserve">38.8110694885254</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2687492370605</t>
+    <t xml:space="preserve">38.2687530517578</t>
   </si>
   <si>
     <t xml:space="preserve">38.7403335571289</t>
@@ -827,25 +827,25 @@
     <t xml:space="preserve">38.6931762695312</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2354888916016</t>
+    <t xml:space="preserve">39.2354927062988</t>
   </si>
   <si>
     <t xml:space="preserve">39.2590675354004</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1357154846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5129737854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7765579223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8001403808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5075149536133</t>
+    <t xml:space="preserve">42.1357078552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5129814147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7765617370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8001365661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.507511138916</t>
   </si>
   <si>
     <t xml:space="preserve">45.3188781738281</t>
@@ -854,19 +854,19 @@
     <t xml:space="preserve">45.8140411376953</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6822471618652</t>
+    <t xml:space="preserve">44.6822509765625</t>
   </si>
   <si>
     <t xml:space="preserve">43.7862434387207</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7529830932617</t>
+    <t xml:space="preserve">44.752986907959</t>
   </si>
   <si>
     <t xml:space="preserve">45.1302452087402</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4464569091797</t>
+    <t xml:space="preserve">44.4464530944824</t>
   </si>
   <si>
     <t xml:space="preserve">44.5879325866699</t>
@@ -875,31 +875,31 @@
     <t xml:space="preserve">44.328556060791</t>
   </si>
   <si>
-    <t xml:space="preserve">44.3049736022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6211891174316</t>
+    <t xml:space="preserve">44.3049812316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6211929321289</t>
   </si>
   <si>
     <t xml:space="preserve">43.1731948852539</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0788726806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5837173461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2675018310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3660354614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9887733459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4936141967773</t>
+    <t xml:space="preserve">43.0788764953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5837135314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.267505645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3660316467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.98876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4936180114746</t>
   </si>
   <si>
     <t xml:space="preserve">44.5171928405762</t>
@@ -908,31 +908,31 @@
     <t xml:space="preserve">45.6254081726074</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8611946105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4035186767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5824661254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0637283325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.134464263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1580390930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9125709533691</t>
+    <t xml:space="preserve">45.861198425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4035148620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.582462310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0637321472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1344680786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1580467224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9125747680664</t>
   </si>
   <si>
     <t xml:space="preserve">49.3508949279785</t>
   </si>
   <si>
-    <t xml:space="preserve">48.7378425598145</t>
+    <t xml:space="preserve">48.7378349304199</t>
   </si>
   <si>
     <t xml:space="preserve">48.101203918457</t>
@@ -941,22 +941,22 @@
     <t xml:space="preserve">48.8321571350098</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6296195983887</t>
+    <t xml:space="preserve">47.6296234130859</t>
   </si>
   <si>
     <t xml:space="preserve">48.0540504455566</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8654136657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9597282409668</t>
+    <t xml:space="preserve">47.8654174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9597244262695</t>
   </si>
   <si>
     <t xml:space="preserve">49.1858444213867</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2717170715332</t>
+    <t xml:space="preserve">45.2717208862305</t>
   </si>
   <si>
     <t xml:space="preserve">45.0359306335449</t>
@@ -968,43 +968,43 @@
     <t xml:space="preserve">43.9748725891113</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5601348876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.913818359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7251930236816</t>
+    <t xml:space="preserve">42.560131072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9138221740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7251892089844</t>
   </si>
   <si>
     <t xml:space="preserve">42.2064514160156</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4328117370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1781539916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3476753234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9800910949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3010101318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0838356018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7534790039062</t>
+    <t xml:space="preserve">42.432804107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1781578063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3476715087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.980094909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3010177612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0838394165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7534866333008</t>
   </si>
   <si>
     <t xml:space="preserve">42.5931434631348</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4799652099609</t>
+    <t xml:space="preserve">42.4799613952637</t>
   </si>
   <si>
     <t xml:space="preserve">43.0081329345703</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">43.0458602905273</t>
   </si>
   <si>
-    <t xml:space="preserve">43.3288078308105</t>
+    <t xml:space="preserve">43.3288116455078</t>
   </si>
   <si>
     <t xml:space="preserve">41.3953285217285</t>
@@ -1025,25 +1025,25 @@
     <t xml:space="preserve">44.2342491149902</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1210632324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2439231872559</t>
+    <t xml:space="preserve">44.1210670471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2439193725586</t>
   </si>
   <si>
     <t xml:space="preserve">42.1027030944824</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1689720153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2729644775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4045104980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7626647949219</t>
+    <t xml:space="preserve">41.1689758300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2729721069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4045066833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7626686096191</t>
   </si>
   <si>
     <t xml:space="preserve">44.2531089782715</t>
@@ -1055,34 +1055,34 @@
     <t xml:space="preserve">44.9510498046875</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2809066772461</t>
+    <t xml:space="preserve">46.2809028625488</t>
   </si>
   <si>
     <t xml:space="preserve">46.1488609313965</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3094482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9981994628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5358009338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1679763793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.592399597168</t>
+    <t xml:space="preserve">45.3094520568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9982070922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5358047485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1679725646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5923957824707</t>
   </si>
   <si>
     <t xml:space="preserve">44.6586685180664</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2533645629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6683464050293</t>
+    <t xml:space="preserve">43.2533569335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6683502197266</t>
   </si>
   <si>
     <t xml:space="preserve">44.2248115539551</t>
@@ -1091,37 +1091,37 @@
     <t xml:space="preserve">45.0830879211426</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2056999206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3280563354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0356864929199</t>
+    <t xml:space="preserve">45.2057075500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3280639648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0356826782227</t>
   </si>
   <si>
     <t xml:space="preserve">45.6584167480469</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5169372558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1682281494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8664093017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5457382202148</t>
+    <t xml:space="preserve">45.5169410705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1682243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8664054870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5457420349121</t>
   </si>
   <si>
     <t xml:space="preserve">43.8852729797363</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4606018066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6112594604492</t>
+    <t xml:space="preserve">44.4606056213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6112632751465</t>
   </si>
   <si>
     <t xml:space="preserve">45.630126953125</t>
@@ -1139,10 +1139,10 @@
     <t xml:space="preserve">46.2148818969727</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6487350463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.705322265625</t>
+    <t xml:space="preserve">46.6487312316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7053298950195</t>
   </si>
   <si>
     <t xml:space="preserve">46.5921478271484</t>
@@ -1154,19 +1154,19 @@
     <t xml:space="preserve">47.7710990905762</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8182563781738</t>
+    <t xml:space="preserve">47.8182640075684</t>
   </si>
   <si>
     <t xml:space="preserve">48.1955184936523</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9972114562988</t>
+    <t xml:space="preserve">48.9972076416016</t>
   </si>
   <si>
     <t xml:space="preserve">48.5727806091309</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3273162841797</t>
+    <t xml:space="preserve">49.3273124694824</t>
   </si>
   <si>
     <t xml:space="preserve">50.3176307678223</t>
@@ -1175,10 +1175,10 @@
     <t xml:space="preserve">50.4119491577148</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8460464477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3744735717773</t>
+    <t xml:space="preserve">49.8460540771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3744773864746</t>
   </si>
   <si>
     <t xml:space="preserve">50.223316192627</t>
@@ -1187,28 +1187,28 @@
     <t xml:space="preserve">50.0818405151367</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5353088378906</t>
+    <t xml:space="preserve">47.5353050231934</t>
   </si>
   <si>
     <t xml:space="preserve">46.1960182189941</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2052001953125</t>
+    <t xml:space="preserve">47.2052040100098</t>
   </si>
   <si>
     <t xml:space="preserve">48.0068893432617</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2523574829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4223785400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8376159667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6489868164062</t>
+    <t xml:space="preserve">47.2523612976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4223823547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8376197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6489906311035</t>
   </si>
   <si>
     <t xml:space="preserve">45.8753433227539</t>
@@ -1217,25 +1217,25 @@
     <t xml:space="preserve">46.5732841491699</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4687957763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8085823059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4789657592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3938293457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5166969299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1774101257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7812805175781</t>
+    <t xml:space="preserve">49.4687919616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8085746765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4789619445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3938331604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5166931152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1774063110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7812767028809</t>
   </si>
   <si>
     <t xml:space="preserve">44.8378715515137</t>
@@ -1244,7 +1244,7 @@
     <t xml:space="preserve">44.4983291625977</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1776542663574</t>
+    <t xml:space="preserve">44.1776580810547</t>
   </si>
   <si>
     <t xml:space="preserve">41.8952026367188</t>
@@ -1253,79 +1253,79 @@
     <t xml:space="preserve">42.291332244873</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4988327026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0652198791504</t>
+    <t xml:space="preserve">42.4988250732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0652236938477</t>
   </si>
   <si>
     <t xml:space="preserve">41.9517936706543</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3283157348633</t>
+    <t xml:space="preserve">45.328311920166</t>
   </si>
   <si>
     <t xml:space="preserve">45.4414901733398</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4603538513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4037666320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1017074584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.988525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3846549987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.0443649291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9028930664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.2898368835449</t>
+    <t xml:space="preserve">45.4603500366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4037628173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1017036437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9885215759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3846473693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.044361114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.902889251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.2898406982422</t>
   </si>
   <si>
     <t xml:space="preserve">51.1193199157715</t>
   </si>
   <si>
-    <t xml:space="preserve">50.694896697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6005783081055</t>
+    <t xml:space="preserve">50.6948928833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6005821228027</t>
   </si>
   <si>
     <t xml:space="preserve">50.9328575134277</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4107055664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0277938842773</t>
+    <t xml:space="preserve">50.4107093811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0277900695801</t>
   </si>
   <si>
     <t xml:space="preserve">52.2144813537598</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1195487976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7398071289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8410987854004</t>
+    <t xml:space="preserve">52.1195526123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7398109436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8410949707031</t>
   </si>
   <si>
     <t xml:space="preserve">51.5024681091309</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2714881896973</t>
+    <t xml:space="preserve">49.2714920043945</t>
   </si>
   <si>
     <t xml:space="preserve">49.3664207458496</t>
@@ -1334,7 +1334,7 @@
     <t xml:space="preserve">49.0816192626953</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7936363220215</t>
+    <t xml:space="preserve">49.7936325073242</t>
   </si>
   <si>
     <t xml:space="preserve">48.2746620178223</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">46.822151184082</t>
   </si>
   <si>
-    <t xml:space="preserve">48.0847969055176</t>
+    <t xml:space="preserve">48.0848007202148</t>
   </si>
   <si>
     <t xml:space="preserve">48.6544036865234</t>
@@ -1352,10 +1352,10 @@
     <t xml:space="preserve">49.3189506530762</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6512298583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9835052490234</t>
+    <t xml:space="preserve">49.6512336730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9835014343262</t>
   </si>
   <si>
     <t xml:space="preserve">50.3632431030273</t>
@@ -1364,31 +1364,31 @@
     <t xml:space="preserve">51.217658996582</t>
   </si>
   <si>
-    <t xml:space="preserve">50.1733665466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4550018310547</t>
+    <t xml:space="preserve">50.1733703613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.455005645752</t>
   </si>
   <si>
     <t xml:space="preserve">52.0246162414551</t>
   </si>
   <si>
-    <t xml:space="preserve">53.0689010620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.7840995788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4422874450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.6828002929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1100120544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5846977233887</t>
+    <t xml:space="preserve">53.068904876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.7840919494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4422950744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.682804107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1100158691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5846862792969</t>
   </si>
   <si>
     <t xml:space="preserve">56.3916435241699</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">54.7302742004395</t>
   </si>
   <si>
-    <t xml:space="preserve">55.0625457763672</t>
+    <t xml:space="preserve">55.0625495910645</t>
   </si>
   <si>
     <t xml:space="preserve">55.4897613525391</t>
@@ -1406,76 +1406,76 @@
     <t xml:space="preserve">55.2524147033691</t>
   </si>
   <si>
-    <t xml:space="preserve">53.1638412475586</t>
+    <t xml:space="preserve">53.1638374328613</t>
   </si>
   <si>
     <t xml:space="preserve">53.6385192871094</t>
   </si>
   <si>
-    <t xml:space="preserve">54.018253326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3030624389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1131896972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8283920288086</t>
+    <t xml:space="preserve">54.0182571411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3030700683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1131935119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8283882141113</t>
   </si>
   <si>
     <t xml:space="preserve">54.7777366638184</t>
   </si>
   <si>
-    <t xml:space="preserve">56.4391136169434</t>
+    <t xml:space="preserve">56.4391098022461</t>
   </si>
   <si>
     <t xml:space="preserve">56.9137878417969</t>
   </si>
   <si>
-    <t xml:space="preserve">56.296703338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0119018554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2017707824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5340385437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.676456451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9676170349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5942306518555</t>
+    <t xml:space="preserve">56.2967071533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.011905670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.201774597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5340461730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6764526367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9676132202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5942268371582</t>
   </si>
   <si>
     <t xml:space="preserve">53.0214309692383</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1574821472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.350528717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9264984130859</t>
+    <t xml:space="preserve">55.1574783325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3505325317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9265022277832</t>
   </si>
   <si>
     <t xml:space="preserve">52.8790321350098</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0657272338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5878715515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4486465454102</t>
+    <t xml:space="preserve">54.0657234191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5878639221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4486427307129</t>
   </si>
   <si>
     <t xml:space="preserve">53.6859855651855</t>
@@ -1484,22 +1484,22 @@
     <t xml:space="preserve">53.3062438964844</t>
   </si>
   <si>
-    <t xml:space="preserve">52.4043579101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0752639770508</t>
+    <t xml:space="preserve">52.404354095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0752601623535</t>
   </si>
   <si>
     <t xml:space="preserve">50.458179473877</t>
   </si>
   <si>
-    <t xml:space="preserve">52.2619438171387</t>
+    <t xml:space="preserve">52.2619476318359</t>
   </si>
   <si>
     <t xml:space="preserve">51.882209777832</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1606559753418</t>
+    <t xml:space="preserve">54.1606597900391</t>
   </si>
   <si>
     <t xml:space="preserve">54.208122253418</t>
@@ -1508,7 +1508,7 @@
     <t xml:space="preserve">53.5435791015625</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5404014587402</t>
+    <t xml:space="preserve">54.540397644043</t>
   </si>
   <si>
     <t xml:space="preserve">55.204948425293</t>
@@ -1523,10 +1523,10 @@
     <t xml:space="preserve">57.2460632324219</t>
   </si>
   <si>
-    <t xml:space="preserve">57.9106101989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9612503051758</t>
+    <t xml:space="preserve">57.9106063842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.961254119873</t>
   </si>
   <si>
     <t xml:space="preserve">50.790454864502</t>
@@ -1535,43 +1535,43 @@
     <t xml:space="preserve">49.4138870239258</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0120162963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0499992370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.2271957397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.467716217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0309715270996</t>
+    <t xml:space="preserve">47.0120239257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0500030517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.2271919250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4677200317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0309677124023</t>
   </si>
   <si>
     <t xml:space="preserve">50.3157768249512</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3474731445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7525596618652</t>
+    <t xml:space="preserve">46.3474769592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7525634765625</t>
   </si>
   <si>
     <t xml:space="preserve">44.6766128540039</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6955986022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1955757141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5563316345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4803810119629</t>
+    <t xml:space="preserve">44.6956024169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1955795288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5563354492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4803848266602</t>
   </si>
   <si>
     <t xml:space="preserve">45.9487457275391</t>
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">47.4107475280762</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5373420715332</t>
+    <t xml:space="preserve">46.5373458862305</t>
   </si>
   <si>
     <t xml:space="preserve">46.5183563232422</t>
@@ -1592,22 +1592,22 @@
     <t xml:space="preserve">46.4424057006836</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4930572509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1322975158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5690078735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7019157409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3601837158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4677925109863</t>
+    <t xml:space="preserve">45.4930534362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1323013305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5690040588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7019081115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3601875305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4677963256836</t>
   </si>
   <si>
     <t xml:space="preserve">41.9234848022461</t>
@@ -1616,13 +1616,13 @@
     <t xml:space="preserve">42.8728370666504</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7462463378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2968711853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8601722717285</t>
+    <t xml:space="preserve">43.7462425231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2968635559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8601684570312</t>
   </si>
   <si>
     <t xml:space="preserve">45.7209014892578</t>
@@ -1631,19 +1631,19 @@
     <t xml:space="preserve">46.7841682434082</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7050552368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2398643493652</t>
+    <t xml:space="preserve">47.7050514221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.239860534668</t>
   </si>
   <si>
     <t xml:space="preserve">46.2905082702637</t>
   </si>
   <si>
-    <t xml:space="preserve">45.189266204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2082481384277</t>
+    <t xml:space="preserve">45.1892623901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2082443237305</t>
   </si>
   <si>
     <t xml:space="preserve">45.2841987609863</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">47.3158149719238</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3727798461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6132926940918</t>
+    <t xml:space="preserve">47.3727836608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6132888793945</t>
   </si>
   <si>
     <t xml:space="preserve">44.4867401123047</t>
@@ -1670,13 +1670,13 @@
     <t xml:space="preserve">42.0753784179688</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5627326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2146453857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8475341796875</t>
+    <t xml:space="preserve">41.5627250671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2146492004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.847541809082</t>
   </si>
   <si>
     <t xml:space="preserve">42.4551239013672</t>
@@ -1688,10 +1688,10 @@
     <t xml:space="preserve">41.8095588684082</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1956214904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0310478210449</t>
+    <t xml:space="preserve">43.195613861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0310516357422</t>
   </si>
   <si>
     <t xml:space="preserve">44.3158569335938</t>
@@ -1700,16 +1700,16 @@
     <t xml:space="preserve">44.3348388671875</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8791580200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7398910522461</t>
+    <t xml:space="preserve">43.8791542053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7398872375488</t>
   </si>
   <si>
     <t xml:space="preserve">45.8348236083984</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8031692504883</t>
+    <t xml:space="preserve">46.8031616210938</t>
   </si>
   <si>
     <t xml:space="preserve">46.3854522705078</t>
@@ -1724,13 +1724,13 @@
     <t xml:space="preserve">49.1765480041504</t>
   </si>
   <si>
-    <t xml:space="preserve">48.3695945739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.436092376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0753364562988</t>
+    <t xml:space="preserve">48.3696022033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4360961914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0753402709961</t>
   </si>
   <si>
     <t xml:space="preserve">45.6449546813965</t>
@@ -1739,7 +1739,7 @@
     <t xml:space="preserve">47.2588539123535</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4645347595215</t>
+    <t xml:space="preserve">48.4645385742188</t>
   </si>
   <si>
     <t xml:space="preserve">49.8885650634766</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">50.1259002685547</t>
   </si>
   <si>
-    <t xml:space="preserve">50.6955184936523</t>
+    <t xml:space="preserve">50.6955223083496</t>
   </si>
   <si>
     <t xml:space="preserve">50.2208404541016</t>
@@ -1763,31 +1763,31 @@
     <t xml:space="preserve">52.1670150756836</t>
   </si>
   <si>
-    <t xml:space="preserve">52.6891593933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9739685058594</t>
+    <t xml:space="preserve">52.6891632080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9739646911621</t>
   </si>
   <si>
     <t xml:space="preserve">54.2555999755859</t>
   </si>
   <si>
-    <t xml:space="preserve">53.2587738037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.9707870483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.7334518432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2998847961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3979988098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4011764526367</t>
+    <t xml:space="preserve">53.2587776184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9707908630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.7334480285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.2998886108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3980026245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4011726379395</t>
   </si>
   <si>
     <t xml:space="preserve">53.9233207702637</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">54.4929351806641</t>
   </si>
   <si>
-    <t xml:space="preserve">54.4454650878906</t>
+    <t xml:space="preserve">54.4454689025879</t>
   </si>
   <si>
     <t xml:space="preserve">53.4961090087891</t>
@@ -1805,7 +1805,7 @@
     <t xml:space="preserve">54.6353378295898</t>
   </si>
   <si>
-    <t xml:space="preserve">55.964427947998</t>
+    <t xml:space="preserve">55.9644317626953</t>
   </si>
   <si>
     <t xml:space="preserve">55.7270965576172</t>
@@ -1814,34 +1814,34 @@
     <t xml:space="preserve">56.1068344116211</t>
   </si>
   <si>
-    <t xml:space="preserve">55.5328483581543</t>
+    <t xml:space="preserve">55.5328521728516</t>
   </si>
   <si>
     <t xml:space="preserve">53.5239143371582</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5717430114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6151008605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5194396972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4671401977539</t>
+    <t xml:space="preserve">53.5717506408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.615104675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5194435119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4671363830566</t>
   </si>
   <si>
     <t xml:space="preserve">54.5283851623535</t>
   </si>
   <si>
-    <t xml:space="preserve">55.9633407592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0590019226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1980323791504</t>
+    <t xml:space="preserve">55.9633445739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0590057373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1980285644531</t>
   </si>
   <si>
     <t xml:space="preserve">56.7764778137207</t>
@@ -1850,40 +1850,40 @@
     <t xml:space="preserve">56.0111694335938</t>
   </si>
   <si>
-    <t xml:space="preserve">55.6285209655762</t>
+    <t xml:space="preserve">55.6285171508789</t>
   </si>
   <si>
     <t xml:space="preserve">56.2024993896484</t>
   </si>
   <si>
-    <t xml:space="preserve">55.9155082702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4416542053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5806846618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3459968566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1501998901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5762100219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4327163696289</t>
+    <t xml:space="preserve">55.9155044555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4416580200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.580680847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3459930419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1501960754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5762176513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4327201843262</t>
   </si>
   <si>
     <t xml:space="preserve">54.8632049560547</t>
   </si>
   <si>
-    <t xml:space="preserve">56.919979095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8243141174316</t>
+    <t xml:space="preserve">56.9199829101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8243179321289</t>
   </si>
   <si>
     <t xml:space="preserve">57.2547988891602</t>
@@ -1892,28 +1892,28 @@
     <t xml:space="preserve">56.6808204650879</t>
   </si>
   <si>
-    <t xml:space="preserve">56.7286491394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.2114372253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.6374588012695</t>
+    <t xml:space="preserve">56.7286529541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.2114410400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.637451171875</t>
   </si>
   <si>
     <t xml:space="preserve">58.5462646484375</t>
   </si>
   <si>
-    <t xml:space="preserve">57.924446105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.3549346923828</t>
+    <t xml:space="preserve">57.9244499206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.3549308776855</t>
   </si>
   <si>
     <t xml:space="preserve">57.7331161499023</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3504676818848</t>
+    <t xml:space="preserve">57.3504638671875</t>
   </si>
   <si>
     <t xml:space="preserve">58.3071098327637</t>
@@ -1925,25 +1925,25 @@
     <t xml:space="preserve">60.172550201416</t>
   </si>
   <si>
-    <t xml:space="preserve">59.7420616149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.2159080505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.1202507019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3026390075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.8287887573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.1157722473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.7809524536133</t>
+    <t xml:space="preserve">59.742057800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.2159118652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.1202430725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3026313781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.828784942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.1157760620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.7809562683105</t>
   </si>
   <si>
     <t xml:space="preserve">59.0245819091797</t>
@@ -1961,31 +1961,31 @@
     <t xml:space="preserve">59.0724143981934</t>
   </si>
   <si>
-    <t xml:space="preserve">58.2592735290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0201148986816</t>
+    <t xml:space="preserve">58.2592697143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0201110839844</t>
   </si>
   <si>
     <t xml:space="preserve">50.9888229370117</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4148406982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2279777526855</t>
+    <t xml:space="preserve">50.4148368835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2279815673828</t>
   </si>
   <si>
     <t xml:space="preserve">51.3236465454102</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8931579589844</t>
+    <t xml:space="preserve">50.8931617736816</t>
   </si>
   <si>
     <t xml:space="preserve">49.7930221557617</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8408508300781</t>
+    <t xml:space="preserve">49.8408546447754</t>
   </si>
   <si>
     <t xml:space="preserve">48.6928901672363</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">49.2668724060059</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9843521118164</t>
+    <t xml:space="preserve">49.9843482971191</t>
   </si>
   <si>
     <t xml:space="preserve">49.9365196228027</t>
@@ -2006,64 +2006,64 @@
     <t xml:space="preserve">50.6539993286133</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2235107421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8453216552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4193115234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.940990447998</t>
+    <t xml:space="preserve">50.2235145568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8453254699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4193077087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9409866333008</t>
   </si>
   <si>
     <t xml:space="preserve">51.514965057373</t>
   </si>
   <si>
-    <t xml:space="preserve">50.7974853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1323165893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6973571777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3147048950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.4581985473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7451858520508</t>
+    <t xml:space="preserve">50.7974891662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1323204040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6973609924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3147010803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.458194732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.745189666748</t>
   </si>
   <si>
     <t xml:space="preserve">50.0321846008301</t>
   </si>
   <si>
-    <t xml:space="preserve">48.8363800048828</t>
+    <t xml:space="preserve">48.8363838195801</t>
   </si>
   <si>
     <t xml:space="preserve">48.5972213745117</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3625373840332</t>
+    <t xml:space="preserve">49.3625335693359</t>
   </si>
   <si>
     <t xml:space="preserve">54.0022315979004</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4282493591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.2892265319824</t>
+    <t xml:space="preserve">53.4282455444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.2892227172852</t>
   </si>
   <si>
     <t xml:space="preserve">54.1935577392578</t>
   </si>
   <si>
-    <t xml:space="preserve">53.0934219360352</t>
+    <t xml:space="preserve">53.0934257507324</t>
   </si>
   <si>
     <t xml:space="preserve">52.4716110229492</t>
@@ -2075,13 +2075,13 @@
     <t xml:space="preserve">54.0978965759277</t>
   </si>
   <si>
-    <t xml:space="preserve">54.9110412597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3370513916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8587379455566</t>
+    <t xml:space="preserve">54.9110374450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3370552062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8587341308594</t>
   </si>
   <si>
     <t xml:space="preserve">54.4805526733398</t>
@@ -2096,28 +2096,28 @@
     <t xml:space="preserve">55.8676795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">56.5373229980469</t>
+    <t xml:space="preserve">56.5373191833496</t>
   </si>
   <si>
     <t xml:space="preserve">56.632984161377</t>
   </si>
   <si>
-    <t xml:space="preserve">58.4027671813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0679512023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6942291259766</t>
+    <t xml:space="preserve">58.4027709960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.067943572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6942329406738</t>
   </si>
   <si>
     <t xml:space="preserve">59.3115730285645</t>
   </si>
   <si>
-    <t xml:space="preserve">62.8511276245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6164512634277</t>
+    <t xml:space="preserve">62.851131439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6164398193359</t>
   </si>
   <si>
     <t xml:space="preserve">65.3383941650391</t>
@@ -2126,40 +2126,40 @@
     <t xml:space="preserve">66.3428573608398</t>
   </si>
   <si>
-    <t xml:space="preserve">66.9646759033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.9213180541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.2606201171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.0692825317383</t>
+    <t xml:space="preserve">66.9646835327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.9213256835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.260612487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.0692749023438</t>
   </si>
   <si>
     <t xml:space="preserve">67.3951644897461</t>
   </si>
   <si>
-    <t xml:space="preserve">68.016975402832</t>
+    <t xml:space="preserve">68.0169830322266</t>
   </si>
   <si>
     <t xml:space="preserve">66.8690185546875</t>
   </si>
   <si>
-    <t xml:space="preserve">67.2995071411133</t>
+    <t xml:space="preserve">67.2994995117188</t>
   </si>
   <si>
     <t xml:space="preserve">67.5386581420898</t>
   </si>
   <si>
-    <t xml:space="preserve">68.9257888793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.2127838134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.4474716186523</t>
+    <t xml:space="preserve">68.9257965087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.212776184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.4474792480469</t>
   </si>
   <si>
     <t xml:space="preserve">67.8734817504883</t>
@@ -2171,10 +2171,10 @@
     <t xml:space="preserve">67.0603408813477</t>
   </si>
   <si>
-    <t xml:space="preserve">66.0080337524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.4385223388672</t>
+    <t xml:space="preserve">66.0080413818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.4385299682617</t>
   </si>
   <si>
     <t xml:space="preserve">65.5775604248047</t>
@@ -2183,16 +2183,16 @@
     <t xml:space="preserve">65.9123840332031</t>
   </si>
   <si>
-    <t xml:space="preserve">67.2516860961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.8256530761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.6343307495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.7688903808594</t>
+    <t xml:space="preserve">67.2516784667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.8256607055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.6343231201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.7688827514648</t>
   </si>
   <si>
     <t xml:space="preserve">66.1036987304688</t>
@@ -2201,82 +2201,82 @@
     <t xml:space="preserve">69.4519348144531</t>
   </si>
   <si>
-    <t xml:space="preserve">68.2083206176758</t>
+    <t xml:space="preserve">68.2083129882812</t>
   </si>
   <si>
     <t xml:space="preserve">70.3129119873047</t>
   </si>
   <si>
-    <t xml:space="preserve">73.3263320922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.2306747436523</t>
+    <t xml:space="preserve">73.3263244628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.2306671142578</t>
   </si>
   <si>
     <t xml:space="preserve">74.0916290283203</t>
   </si>
   <si>
-    <t xml:space="preserve">73.6611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.3741607666016</t>
+    <t xml:space="preserve">73.6611557006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.3741455078125</t>
   </si>
   <si>
     <t xml:space="preserve">70.6955718994141</t>
   </si>
   <si>
-    <t xml:space="preserve">70.7912445068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.4653472900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.2650756835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.638801574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3173980712891</t>
+    <t xml:space="preserve">70.7912216186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.4653549194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.2650833129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.638786315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3173904418945</t>
   </si>
   <si>
     <t xml:space="preserve">71.9391937255859</t>
   </si>
   <si>
-    <t xml:space="preserve">72.7045059204102</t>
+    <t xml:space="preserve">72.7045135498047</t>
   </si>
   <si>
     <t xml:space="preserve">72.7523498535156</t>
   </si>
   <si>
-    <t xml:space="preserve">72.6088485717773</t>
+    <t xml:space="preserve">72.6088562011719</t>
   </si>
   <si>
     <t xml:space="preserve">74.4264602661133</t>
   </si>
   <si>
-    <t xml:space="preserve">74.1394653320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7478713989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9870300292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.2784957885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.4130554199219</t>
+    <t xml:space="preserve">74.1394729614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7478790283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9870376586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.2784881591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.4130477905273</t>
   </si>
   <si>
     <t xml:space="preserve">66.821174621582</t>
   </si>
   <si>
-    <t xml:space="preserve">65.7210464477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.1336555480957</t>
+    <t xml:space="preserve">65.7210540771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.1336517333984</t>
   </si>
   <si>
     <t xml:space="preserve">63.8077659606934</t>
@@ -2285,31 +2285,31 @@
     <t xml:space="preserve">61.8944931030273</t>
   </si>
   <si>
-    <t xml:space="preserve">60.937858581543</t>
+    <t xml:space="preserve">60.9378547668457</t>
   </si>
   <si>
     <t xml:space="preserve">57.8766174316406</t>
   </si>
   <si>
-    <t xml:space="preserve">52.5672721862793</t>
+    <t xml:space="preserve">52.5672760009766</t>
   </si>
   <si>
     <t xml:space="preserve">52.0889587402344</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3778190612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7407188415527</t>
+    <t xml:space="preserve">46.3778228759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7407264709473</t>
   </si>
   <si>
     <t xml:space="preserve">45.4594497680664</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7094230651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8714332580566</t>
+    <t xml:space="preserve">41.7094306945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8714294433594</t>
   </si>
   <si>
     <t xml:space="preserve">45.2107238769531</t>
@@ -2327,40 +2327,40 @@
     <t xml:space="preserve">49.2190399169922</t>
   </si>
   <si>
-    <t xml:space="preserve">59.1680793762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.6852874755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.2637405395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.0813522338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.3638725280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.1291885375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4161758422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.6598091125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.5207824707031</t>
+    <t xml:space="preserve">59.168083190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.6852912902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.263744354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.081356048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.3638763427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.1291847229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4161796569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.6598052978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.5207901000977</t>
   </si>
   <si>
     <t xml:space="preserve">62.5641479492188</t>
   </si>
   <si>
-    <t xml:space="preserve">63.1381301879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0424690246582</t>
+    <t xml:space="preserve">63.138126373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0424652099609</t>
   </si>
   <si>
     <t xml:space="preserve">61.9901580810547</t>
@@ -2378,25 +2378,25 @@
     <t xml:space="preserve">61.7279586791992</t>
   </si>
   <si>
-    <t xml:space="preserve">63.7051887512207</t>
+    <t xml:space="preserve">63.7051963806152</t>
   </si>
   <si>
     <t xml:space="preserve">64.7179107666016</t>
   </si>
   <si>
-    <t xml:space="preserve">63.367603302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6569671630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.0909881591797</t>
+    <t xml:space="preserve">63.3676109313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6569595336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.0909805297852</t>
   </si>
   <si>
     <t xml:space="preserve">64.4285583496094</t>
   </si>
   <si>
-    <t xml:space="preserve">64.9108047485352</t>
+    <t xml:space="preserve">64.9108123779297</t>
   </si>
   <si>
     <t xml:space="preserve">68.4312286376953</t>
@@ -2405,31 +2405,31 @@
     <t xml:space="preserve">68.0936508178711</t>
   </si>
   <si>
-    <t xml:space="preserve">68.3830108642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.6241226196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.9744338989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.3984069824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.1217803955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.9288864135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.3628997802734</t>
+    <t xml:space="preserve">68.3830184936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.624137878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.9744415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.3983993530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.1217727661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.9288787841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.3628921508789</t>
   </si>
   <si>
     <t xml:space="preserve">75.8578720092773</t>
   </si>
   <si>
-    <t xml:space="preserve">74.6522521972656</t>
+    <t xml:space="preserve">74.6522598266602</t>
   </si>
   <si>
     <t xml:space="preserve">71.8552017211914</t>
@@ -2438,49 +2438,49 @@
     <t xml:space="preserve">70.6013565063477</t>
   </si>
   <si>
-    <t xml:space="preserve">71.1318283081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.2155532836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.9235382080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.0327072143555</t>
+    <t xml:space="preserve">71.1318206787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.2155609130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.9235305786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.0326995849609</t>
   </si>
   <si>
     <t xml:space="preserve">67.2256088256836</t>
   </si>
   <si>
-    <t xml:space="preserve">64.8625869750977</t>
+    <t xml:space="preserve">64.8625793457031</t>
   </si>
   <si>
     <t xml:space="preserve">66.5504531860352</t>
   </si>
   <si>
-    <t xml:space="preserve">67.3220596313477</t>
+    <t xml:space="preserve">67.3220672607422</t>
   </si>
   <si>
     <t xml:space="preserve">69.9262008666992</t>
   </si>
   <si>
-    <t xml:space="preserve">71.180046081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.4084625244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3729629516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.4921798706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.31201171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.5276794433594</t>
+    <t xml:space="preserve">71.1800537109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.4084548950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3729476928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.4921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.3120193481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.5276870727539</t>
   </si>
   <si>
     <t xml:space="preserve">68.2865676879883</t>
@@ -2489,10 +2489,10 @@
     <t xml:space="preserve">68.6723556518555</t>
   </si>
   <si>
-    <t xml:space="preserve">69.0099334716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.2992858886719</t>
+    <t xml:space="preserve">69.0099411010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.2992782592773</t>
   </si>
   <si>
     <t xml:space="preserve">72.1445541381836</t>
@@ -2501,13 +2501,13 @@
     <t xml:space="preserve">71.2765045166016</t>
   </si>
   <si>
-    <t xml:space="preserve">71.8069839477539</t>
+    <t xml:space="preserve">71.8069763183594</t>
   </si>
   <si>
     <t xml:space="preserve">70.1673278808594</t>
   </si>
   <si>
-    <t xml:space="preserve">70.5531311035156</t>
+    <t xml:space="preserve">70.5531387329102</t>
   </si>
   <si>
     <t xml:space="preserve">70.3602294921875</t>
@@ -2519,10 +2519,10 @@
     <t xml:space="preserve">72.3374633789062</t>
   </si>
   <si>
-    <t xml:space="preserve">72.8679428100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.4466323852539</t>
+    <t xml:space="preserve">72.8679351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.4466247558594</t>
   </si>
   <si>
     <t xml:space="preserve">73.5430755615234</t>
@@ -2531,43 +2531,43 @@
     <t xml:space="preserve">71.999885559082</t>
   </si>
   <si>
-    <t xml:space="preserve">73.0608291625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.6877593994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.5913009643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.9643859863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.7487030029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9342193603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.9469528198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.117073059082</t>
+    <t xml:space="preserve">73.0608367919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.6877517700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.59130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.9643936157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.7487106323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.934211730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.9469451904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1170654296875</t>
   </si>
   <si>
     <t xml:space="preserve">86.0815658569336</t>
   </si>
   <si>
-    <t xml:space="preserve">85.3582000732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1398468017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0179595947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0661849975586</t>
+    <t xml:space="preserve">85.3581924438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1398391723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.017951965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0661773681641</t>
   </si>
   <si>
     <t xml:space="preserve">82.609375</t>
@@ -2582,31 +2582,31 @@
     <t xml:space="preserve">85.3099746704102</t>
   </si>
   <si>
-    <t xml:space="preserve">84.5865859985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.6348190307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.6703262329102</t>
+    <t xml:space="preserve">84.5865936279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.6348266601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.6703186035156</t>
   </si>
   <si>
     <t xml:space="preserve">84.7795028686523</t>
   </si>
   <si>
-    <t xml:space="preserve">84.6830596923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.3836441040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2262573242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7212219238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.6984405517578</t>
+    <t xml:space="preserve">84.6830520629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.3836364746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2262496948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7212142944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.6984329223633</t>
   </si>
   <si>
     <t xml:space="preserve">89.3126449584961</t>
@@ -2615,13 +2615,13 @@
     <t xml:space="preserve">90.6629333496094</t>
   </si>
   <si>
-    <t xml:space="preserve">88.1070098876953</t>
+    <t xml:space="preserve">88.1070175170898</t>
   </si>
   <si>
     <t xml:space="preserve">87.8658981323242</t>
   </si>
   <si>
-    <t xml:space="preserve">91.2416381835938</t>
+    <t xml:space="preserve">91.2416458129883</t>
   </si>
   <si>
     <t xml:space="preserve">90.2771453857422</t>
@@ -2630,37 +2630,37 @@
     <t xml:space="preserve">90.5664901733398</t>
   </si>
   <si>
-    <t xml:space="preserve">90.8076248168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9777450561523</t>
+    <t xml:space="preserve">90.8076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9777374267578</t>
   </si>
   <si>
     <t xml:space="preserve">95.0031967163086</t>
   </si>
   <si>
-    <t xml:space="preserve">94.9067459106445</t>
+    <t xml:space="preserve">94.90673828125</t>
   </si>
   <si>
     <t xml:space="preserve">95.7265625</t>
   </si>
   <si>
-    <t xml:space="preserve">93.218864440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5082168579102</t>
+    <t xml:space="preserve">93.2188568115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5082244873047</t>
   </si>
   <si>
     <t xml:space="preserve">91.4827728271484</t>
   </si>
   <si>
-    <t xml:space="preserve">89.9395751953125</t>
+    <t xml:space="preserve">89.9395599365234</t>
   </si>
   <si>
     <t xml:space="preserve">91.62744140625</t>
   </si>
   <si>
-    <t xml:space="preserve">92.1096954345703</t>
+    <t xml:space="preserve">92.1096878051758</t>
   </si>
   <si>
     <t xml:space="preserve">93.3635482788086</t>
@@ -2669,16 +2669,16 @@
     <t xml:space="preserve">95.5336761474609</t>
   </si>
   <si>
-    <t xml:space="preserve">94.954963684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.8102874755859</t>
+    <t xml:space="preserve">94.9549560546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.8102951049805</t>
   </si>
   <si>
     <t xml:space="preserve">93.6046752929688</t>
   </si>
   <si>
-    <t xml:space="preserve">94.5209426879883</t>
+    <t xml:space="preserve">94.5209350585938</t>
   </si>
   <si>
     <t xml:space="preserve">92.6883850097656</t>
@@ -2690,19 +2690,19 @@
     <t xml:space="preserve">93.0259628295898</t>
   </si>
   <si>
-    <t xml:space="preserve">95.2925338745117</t>
+    <t xml:space="preserve">95.2925491333008</t>
   </si>
   <si>
     <t xml:space="preserve">97.2215423583984</t>
   </si>
   <si>
-    <t xml:space="preserve">100.115051269531</t>
+    <t xml:space="preserve">100.115043640137</t>
   </si>
   <si>
     <t xml:space="preserve">99.7292327880859</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6073303222656</t>
+    <t xml:space="preserve">97.6073379516602</t>
   </si>
   <si>
     <t xml:space="preserve">97.8966827392578</t>
@@ -2711,16 +2711,16 @@
     <t xml:space="preserve">98.3789367675781</t>
   </si>
   <si>
-    <t xml:space="preserve">96.3052520751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.7493286132812</t>
+    <t xml:space="preserve">96.3052673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7493438720703</t>
   </si>
   <si>
     <t xml:space="preserve">92.8330612182617</t>
   </si>
   <si>
-    <t xml:space="preserve">92.8812942504883</t>
+    <t xml:space="preserve">92.8813018798828</t>
   </si>
   <si>
     <t xml:space="preserve">88.4445877075195</t>
@@ -2738,7 +2738,7 @@
     <t xml:space="preserve">92.2061386108398</t>
   </si>
   <si>
-    <t xml:space="preserve">96.4499435424805</t>
+    <t xml:space="preserve">96.4499359130859</t>
   </si>
   <si>
     <t xml:space="preserve">95.4372177124023</t>
@@ -2750,28 +2750,28 @@
     <t xml:space="preserve">92.447265625</t>
   </si>
   <si>
-    <t xml:space="preserve">92.0614700317383</t>
+    <t xml:space="preserve">92.0614624023438</t>
   </si>
   <si>
     <t xml:space="preserve">91.8685684204102</t>
   </si>
   <si>
-    <t xml:space="preserve">91.8203430175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7111663818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8558502197266</t>
+    <t xml:space="preserve">91.8203506469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7111740112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.855842590332</t>
   </si>
   <si>
     <t xml:space="preserve">91.3863220214844</t>
   </si>
   <si>
-    <t xml:space="preserve">90.7593841552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7694549560547</t>
+    <t xml:space="preserve">90.759391784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7694473266602</t>
   </si>
   <si>
     <t xml:space="preserve">88.2516937255859</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">89.3608703613281</t>
   </si>
   <si>
-    <t xml:space="preserve">90.3735961914062</t>
+    <t xml:space="preserve">90.3735885620117</t>
   </si>
   <si>
     <t xml:space="preserve">94.2798156738281</t>
@@ -2792,13 +2792,13 @@
     <t xml:space="preserve">91.1451950073242</t>
   </si>
   <si>
-    <t xml:space="preserve">92.4954986572266</t>
+    <t xml:space="preserve">92.495491027832</t>
   </si>
   <si>
     <t xml:space="preserve">89.4573211669922</t>
   </si>
   <si>
-    <t xml:space="preserve">91.675666809082</t>
+    <t xml:space="preserve">91.6756744384766</t>
   </si>
   <si>
     <t xml:space="preserve">91.9168014526367</t>
@@ -2813,22 +2813,22 @@
     <t xml:space="preserve">90.9040679931641</t>
   </si>
   <si>
-    <t xml:space="preserve">92.3508224487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4599990844727</t>
+    <t xml:space="preserve">92.3508148193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4599838256836</t>
   </si>
   <si>
     <t xml:space="preserve">92.5437164306641</t>
   </si>
   <si>
-    <t xml:space="preserve">95.9194564819336</t>
+    <t xml:space="preserve">95.9194641113281</t>
   </si>
   <si>
     <t xml:space="preserve">93.26708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">93.5564346313477</t>
+    <t xml:space="preserve">93.5564422607422</t>
   </si>
   <si>
     <t xml:space="preserve">94.5691757202148</t>
@@ -2837,16 +2837,16 @@
     <t xml:space="preserve">96.0641403198242</t>
   </si>
   <si>
-    <t xml:space="preserve">98.4753799438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.018585205078</t>
+    <t xml:space="preserve">98.4753875732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.018592834473</t>
   </si>
   <si>
     <t xml:space="preserve">98.1860427856445</t>
   </si>
   <si>
-    <t xml:space="preserve">97.4144287109375</t>
+    <t xml:space="preserve">97.414436340332</t>
   </si>
   <si>
     <t xml:space="preserve">100.790184020996</t>
@@ -2855,10 +2855,10 @@
     <t xml:space="preserve">102.912078857422</t>
   </si>
   <si>
-    <t xml:space="preserve">101.46533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.719192504883</t>
+    <t xml:space="preserve">101.465324401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.719184875488</t>
   </si>
   <si>
     <t xml:space="preserve">102.526290893555</t>
@@ -2867,55 +2867,55 @@
     <t xml:space="preserve">102.140487670898</t>
   </si>
   <si>
-    <t xml:space="preserve">104.937538146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.104988098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.58723449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.815628051758</t>
+    <t xml:space="preserve">104.937530517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.104995727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.587242126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.815635681152</t>
   </si>
   <si>
     <t xml:space="preserve">103.201438903809</t>
   </si>
   <si>
-    <t xml:space="preserve">100.500831604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.404388427734</t>
+    <t xml:space="preserve">100.500839233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.40438079834</t>
   </si>
   <si>
     <t xml:space="preserve">98.5718383789062</t>
   </si>
   <si>
-    <t xml:space="preserve">95.0514144897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.135139465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.5919418334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.2161865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.297882080078</t>
+    <t xml:space="preserve">95.0514221191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.1351470947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.5919342041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.216194152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.297889709473</t>
   </si>
   <si>
     <t xml:space="preserve">99.3434371948242</t>
   </si>
   <si>
-    <t xml:space="preserve">101.561782836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.973037719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.780136108398</t>
+    <t xml:space="preserve">101.561790466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.973030090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.780128479004</t>
   </si>
   <si>
     <t xml:space="preserve">105.323333740234</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">104.069480895996</t>
   </si>
   <si>
-    <t xml:space="preserve">108.023933410645</t>
+    <t xml:space="preserve">108.023941040039</t>
   </si>
   <si>
     <t xml:space="preserve">110.145820617676</t>
@@ -2939,52 +2939,52 @@
     <t xml:space="preserve">106.28783416748</t>
   </si>
   <si>
-    <t xml:space="preserve">107.445243835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.384292602539</t>
+    <t xml:space="preserve">107.445236206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.384284973145</t>
   </si>
   <si>
     <t xml:space="preserve">108.891983032227</t>
   </si>
   <si>
-    <t xml:space="preserve">107.831031799316</t>
+    <t xml:space="preserve">107.831039428711</t>
   </si>
   <si>
     <t xml:space="preserve">108.795532226562</t>
   </si>
   <si>
-    <t xml:space="preserve">109.08487701416</t>
+    <t xml:space="preserve">109.084884643555</t>
   </si>
   <si>
     <t xml:space="preserve">107.059432983398</t>
   </si>
   <si>
-    <t xml:space="preserve">107.348793029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.56713104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.50617980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.53076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.786026000977</t>
+    <t xml:space="preserve">107.348785400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.567138671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.506187438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.530754089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.786018371582</t>
   </si>
   <si>
     <t xml:space="preserve">108.755317687988</t>
   </si>
   <si>
-    <t xml:space="preserve">109.046104431152</t>
+    <t xml:space="preserve">109.046112060547</t>
   </si>
   <si>
     <t xml:space="preserve">109.918479919434</t>
   </si>
   <si>
-    <t xml:space="preserve">110.500053405762</t>
+    <t xml:space="preserve">110.500061035156</t>
   </si>
   <si>
     <t xml:space="preserve">109.821548461914</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">111.663208007812</t>
   </si>
   <si>
-    <t xml:space="preserve">113.117164611816</t>
+    <t xml:space="preserve">113.117172241211</t>
   </si>
   <si>
     <t xml:space="preserve">115.831199645996</t>
@@ -3005,7 +3005,7 @@
     <t xml:space="preserve">113.795669555664</t>
   </si>
   <si>
-    <t xml:space="preserve">114.764976501465</t>
+    <t xml:space="preserve">114.76496887207</t>
   </si>
   <si>
     <t xml:space="preserve">114.668045043945</t>
@@ -3014,22 +3014,22 @@
     <t xml:space="preserve">114.280319213867</t>
   </si>
   <si>
-    <t xml:space="preserve">114.474174499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.509712219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.453132629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.590408325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.819808959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.365837097168</t>
+    <t xml:space="preserve">114.474182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.509704589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.453140258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.590423583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.819793701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.365852355957</t>
   </si>
   <si>
     <t xml:space="preserve">127.268928527832</t>
@@ -3041,46 +3041,46 @@
     <t xml:space="preserve">133.181655883789</t>
   </si>
   <si>
-    <t xml:space="preserve">130.46760559082</t>
+    <t xml:space="preserve">130.467620849609</t>
   </si>
   <si>
     <t xml:space="preserve">130.273742675781</t>
   </si>
   <si>
-    <t xml:space="preserve">128.916732788086</t>
+    <t xml:space="preserve">128.916717529297</t>
   </si>
   <si>
     <t xml:space="preserve">134.635589599609</t>
   </si>
   <si>
-    <t xml:space="preserve">135.701812744141</t>
+    <t xml:space="preserve">135.70182800293</t>
   </si>
   <si>
     <t xml:space="preserve">134.44172668457</t>
   </si>
   <si>
-    <t xml:space="preserve">133.375503540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.798751831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.314102172852</t>
+    <t xml:space="preserve">133.375518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.798767089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.314117431641</t>
   </si>
   <si>
     <t xml:space="preserve">136.574188232422</t>
   </si>
   <si>
-    <t xml:space="preserve">132.212341308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.023330688477</t>
+    <t xml:space="preserve">132.212356567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.023315429688</t>
   </si>
   <si>
     <t xml:space="preserve">133.763214111328</t>
   </si>
   <si>
-    <t xml:space="preserve">137.446563720703</t>
+    <t xml:space="preserve">137.446578979492</t>
   </si>
   <si>
     <t xml:space="preserve">135.89567565918</t>
@@ -3092,19 +3092,19 @@
     <t xml:space="preserve">138.22200012207</t>
   </si>
   <si>
-    <t xml:space="preserve">142.293060302734</t>
+    <t xml:space="preserve">142.293075561523</t>
   </si>
   <si>
     <t xml:space="preserve">141.032958984375</t>
   </si>
   <si>
-    <t xml:space="preserve">143.359283447266</t>
+    <t xml:space="preserve">143.359268188477</t>
   </si>
   <si>
     <t xml:space="preserve">140.063659667969</t>
   </si>
   <si>
-    <t xml:space="preserve">138.803558349609</t>
+    <t xml:space="preserve">138.803573608398</t>
   </si>
   <si>
     <t xml:space="preserve">140.548309326172</t>
@@ -3128,10 +3128,10 @@
     <t xml:space="preserve">137.640426635742</t>
   </si>
   <si>
-    <t xml:space="preserve">139.094375610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.226837158203</t>
+    <t xml:space="preserve">139.094345092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.226821899414</t>
   </si>
   <si>
     <t xml:space="preserve">142.583847045898</t>
@@ -3143,28 +3143,28 @@
     <t xml:space="preserve">143.262359619141</t>
   </si>
   <si>
-    <t xml:space="preserve">142.486923217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.073318481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.884307861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.011917114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.175064086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.756652832031</t>
+    <t xml:space="preserve">142.486907958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.073303222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.884292602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.011901855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.175079345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.75666809082</t>
   </si>
   <si>
     <t xml:space="preserve">146.364120483398</t>
   </si>
   <si>
-    <t xml:space="preserve">147.236465454102</t>
+    <t xml:space="preserve">147.236480712891</t>
   </si>
   <si>
     <t xml:space="preserve">148.205764770508</t>
@@ -3176,16 +3176,16 @@
     <t xml:space="preserve">150.532104492188</t>
   </si>
   <si>
-    <t xml:space="preserve">150.629028320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.087814331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.893936157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.955352783203</t>
+    <t xml:space="preserve">150.629013061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.087799072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.893951416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.955337524414</t>
   </si>
   <si>
     <t xml:space="preserve">157.89875793457</t>
@@ -3194,16 +3194,16 @@
     <t xml:space="preserve">161.679016113281</t>
   </si>
   <si>
-    <t xml:space="preserve">166.816329956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">166.428604125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.847015380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.459289550781</t>
+    <t xml:space="preserve">166.816314697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">166.428588867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.847030639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.45930480957</t>
   </si>
   <si>
     <t xml:space="preserve">165.653137207031</t>
@@ -3212,16 +3212,16 @@
     <t xml:space="preserve">167.397888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">168.851837158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.142639160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.62727355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.305786132812</t>
+    <t xml:space="preserve">168.851852416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.142623901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.627288818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.305801391602</t>
   </si>
   <si>
     <t xml:space="preserve">169.239562988281</t>
@@ -3233,19 +3233,19 @@
     <t xml:space="preserve">168.948776245117</t>
   </si>
   <si>
-    <t xml:space="preserve">163.811477661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.204040527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.071594238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.979461669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.989120483398</t>
+    <t xml:space="preserve">163.811492919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.204025268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.071578979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.979476928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.989135742188</t>
   </si>
   <si>
     <t xml:space="preserve">176.606231689453</t>
@@ -3257,22 +3257,22 @@
     <t xml:space="preserve">152.470687866211</t>
   </si>
   <si>
-    <t xml:space="preserve">152.567611694336</t>
+    <t xml:space="preserve">152.567596435547</t>
   </si>
   <si>
     <t xml:space="preserve">154.506210327148</t>
   </si>
   <si>
-    <t xml:space="preserve">153.827713012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.465866088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.633865356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.43034362793</t>
+    <t xml:space="preserve">153.827697753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.465850830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.633850097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.430358886719</t>
   </si>
   <si>
     <t xml:space="preserve">147.721115112305</t>
@@ -3281,16 +3281,16 @@
     <t xml:space="preserve">145.97639465332</t>
   </si>
   <si>
-    <t xml:space="preserve">157.026382446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.643493652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.842208862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.229904174805</t>
+    <t xml:space="preserve">157.026397705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.643508911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.842193603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.229888916016</t>
   </si>
   <si>
     <t xml:space="preserve">160.4189453125</t>
@@ -3317,10 +3317,10 @@
     <t xml:space="preserve">164.393081665039</t>
   </si>
   <si>
-    <t xml:space="preserve">171.275100708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.213668823242</t>
+    <t xml:space="preserve">171.27507019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.213684082031</t>
   </si>
   <si>
     <t xml:space="preserve">172.825973510742</t>
@@ -3329,10 +3329,10 @@
     <t xml:space="preserve">174.182983398438</t>
   </si>
   <si>
-    <t xml:space="preserve">171.662811279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172.34130859375</t>
+    <t xml:space="preserve">171.662796020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.341323852539</t>
   </si>
   <si>
     <t xml:space="preserve">176.703155517578</t>
@@ -3341,13 +3341,13 @@
     <t xml:space="preserve">179.804916381836</t>
   </si>
   <si>
-    <t xml:space="preserve">173.892181396484</t>
+    <t xml:space="preserve">173.892196655273</t>
   </si>
   <si>
     <t xml:space="preserve">168.754913330078</t>
   </si>
   <si>
-    <t xml:space="preserve">168.56103515625</t>
+    <t xml:space="preserve">168.561050415039</t>
   </si>
   <si>
     <t xml:space="preserve">167.010177612305</t>
@@ -3356,22 +3356,22 @@
     <t xml:space="preserve">159.934295654297</t>
   </si>
   <si>
-    <t xml:space="preserve">162.454483032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.837371826172</t>
+    <t xml:space="preserve">162.454467773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.837356567383</t>
   </si>
   <si>
     <t xml:space="preserve">166.040878295898</t>
   </si>
   <si>
-    <t xml:space="preserve">167.882522583008</t>
+    <t xml:space="preserve">167.882553100586</t>
   </si>
   <si>
     <t xml:space="preserve">160.709732055664</t>
   </si>
   <si>
-    <t xml:space="preserve">162.745239257812</t>
+    <t xml:space="preserve">162.745254516602</t>
   </si>
   <si>
     <t xml:space="preserve">159.158843994141</t>
@@ -3380,13 +3380,13 @@
     <t xml:space="preserve">172.535171508789</t>
   </si>
   <si>
-    <t xml:space="preserve">174.958404541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.698348999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.570724487305</t>
+    <t xml:space="preserve">174.958435058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.698333740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.570709228516</t>
   </si>
   <si>
     <t xml:space="preserve">169.43342590332</t>
@@ -3395,28 +3395,28 @@
     <t xml:space="preserve">168.076400756836</t>
   </si>
   <si>
-    <t xml:space="preserve">163.617614746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.877716064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.714553833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.596572875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.821136474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.473770141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.005340576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.317199707031</t>
+    <t xml:space="preserve">163.617630004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.877731323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.714538574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.596588134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.821151733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.473785400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.005355834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.317184448242</t>
   </si>
   <si>
     <t xml:space="preserve">155.572448730469</t>
@@ -3425,7 +3425,7 @@
     <t xml:space="preserve">155.863250732422</t>
   </si>
   <si>
-    <t xml:space="preserve">155.669387817383</t>
+    <t xml:space="preserve">155.669372558594</t>
   </si>
   <si>
     <t xml:space="preserve">153.149200439453</t>
@@ -3437,16 +3437,16 @@
     <t xml:space="preserve">157.220260620117</t>
   </si>
   <si>
-    <t xml:space="preserve">151.113677978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.858413696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.990875244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.931198120117</t>
+    <t xml:space="preserve">151.113662719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.8583984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.990859985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.931228637695</t>
   </si>
   <si>
     <t xml:space="preserve">143.747009277344</t>
@@ -3455,49 +3455,49 @@
     <t xml:space="preserve">143.553146362305</t>
   </si>
   <si>
-    <t xml:space="preserve">144.5224609375</t>
+    <t xml:space="preserve">144.522445678711</t>
   </si>
   <si>
     <t xml:space="preserve">144.910171508789</t>
   </si>
   <si>
-    <t xml:space="preserve">139.385177612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.089538574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.600067138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.309295654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.997436523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.834274291992</t>
+    <t xml:space="preserve">139.385162353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.089553833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.600082397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.309280395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.997421264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.834289550781</t>
   </si>
   <si>
     <t xml:space="preserve">137.543487548828</t>
   </si>
   <si>
-    <t xml:space="preserve">138.125076293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.512786865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142.680770874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.692184448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.039543151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.9619140625</t>
+    <t xml:space="preserve">138.125061035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.512771606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142.680786132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.692169189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.039527893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.961929321289</t>
   </si>
   <si>
     <t xml:space="preserve">135.507965087891</t>
@@ -3506,7 +3506,7 @@
     <t xml:space="preserve">142.874618530273</t>
   </si>
   <si>
-    <t xml:space="preserve">149.562805175781</t>
+    <t xml:space="preserve">149.562789916992</t>
   </si>
   <si>
     <t xml:space="preserve">151.986053466797</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">145.10400390625</t>
   </si>
   <si>
-    <t xml:space="preserve">148.6904296875</t>
+    <t xml:space="preserve">148.690414428711</t>
   </si>
   <si>
     <t xml:space="preserve">145.394821166992</t>
@@ -3536,28 +3536,28 @@
     <t xml:space="preserve">149.659713745117</t>
   </si>
   <si>
-    <t xml:space="preserve">145.200942993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.517623901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.323760986328</t>
+    <t xml:space="preserve">145.200958251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.517608642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.323776245117</t>
   </si>
   <si>
     <t xml:space="preserve">137.058837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">134.538681030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.477249145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.824615478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.186462402344</t>
+    <t xml:space="preserve">134.538665771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.477264404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.824630737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.186477661133</t>
   </si>
   <si>
     <t xml:space="preserve">135.217178344727</t>
@@ -3569,10 +3569,10 @@
     <t xml:space="preserve">127.753578186035</t>
   </si>
   <si>
-    <t xml:space="preserve">121.16234588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.601806640625</t>
+    <t xml:space="preserve">121.162338256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.60181427002</t>
   </si>
   <si>
     <t xml:space="preserve">117.285148620605</t>
@@ -3584,16 +3584,16 @@
     <t xml:space="preserve">117.57593536377</t>
   </si>
   <si>
-    <t xml:space="preserve">116.121994018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.708389282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.152687072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.86190032959</t>
+    <t xml:space="preserve">116.12198638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.708396911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.152694702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.861907958984</t>
   </si>
   <si>
     <t xml:space="preserve">115.443481445312</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">117.102432250977</t>
   </si>
   <si>
-    <t xml:space="preserve">116.71208190918</t>
+    <t xml:space="preserve">116.712089538574</t>
   </si>
   <si>
     <t xml:space="preserve">120.713081359863</t>
@@ -3617,10 +3617,10 @@
     <t xml:space="preserve">124.909255981445</t>
   </si>
   <si>
-    <t xml:space="preserve">123.640647888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.834815979004</t>
+    <t xml:space="preserve">123.640640258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.834823608398</t>
   </si>
   <si>
     <t xml:space="preserve">120.225158691406</t>
@@ -3629,16 +3629,16 @@
     <t xml:space="preserve">119.346893310547</t>
   </si>
   <si>
-    <t xml:space="preserve">121.005844116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.857971191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.5390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.367050170898</t>
+    <t xml:space="preserve">121.005851745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.857963562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.539054870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.367042541504</t>
   </si>
   <si>
     <t xml:space="preserve">100.512916564941</t>
@@ -3653,13 +3653,13 @@
     <t xml:space="preserve">103.147720336914</t>
   </si>
   <si>
-    <t xml:space="preserve">103.83081817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.075286865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.417327880859</t>
+    <t xml:space="preserve">103.830825805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.07527923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.417335510254</t>
   </si>
   <si>
     <t xml:space="preserve">108.319747924805</t>
@@ -3668,22 +3668,22 @@
     <t xml:space="preserve">112.418327331543</t>
   </si>
   <si>
-    <t xml:space="preserve">113.296600341797</t>
+    <t xml:space="preserve">113.296592712402</t>
   </si>
   <si>
     <t xml:space="preserve">115.541069030762</t>
   </si>
   <si>
-    <t xml:space="preserve">114.272453308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.906257629395</t>
+    <t xml:space="preserve">114.272445678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.90625</t>
   </si>
   <si>
     <t xml:space="preserve">113.882110595703</t>
   </si>
   <si>
-    <t xml:space="preserve">111.24730682373</t>
+    <t xml:space="preserve">111.247299194336</t>
   </si>
   <si>
     <t xml:space="preserve">110.661796569824</t>
@@ -3698,7 +3698,7 @@
     <t xml:space="preserve">120.615501403809</t>
   </si>
   <si>
-    <t xml:space="preserve">119.054138183594</t>
+    <t xml:space="preserve">119.054130554199</t>
   </si>
   <si>
     <t xml:space="preserve">118.956550598145</t>
@@ -3710,13 +3710,13 @@
     <t xml:space="preserve">116.907264709473</t>
   </si>
   <si>
-    <t xml:space="preserve">122.469619750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.323753356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.885116577148</t>
+    <t xml:space="preserve">122.469627380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.323745727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.885108947754</t>
   </si>
   <si>
     <t xml:space="preserve">125.006851196289</t>
@@ -3725,40 +3725,40 @@
     <t xml:space="preserve">122.664794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">125.68994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.616493225098</t>
+    <t xml:space="preserve">125.689949035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.616500854492</t>
   </si>
   <si>
     <t xml:space="preserve">119.249305725098</t>
   </si>
   <si>
-    <t xml:space="preserve">123.055130004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.47061920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.957542419434</t>
+    <t xml:space="preserve">123.055137634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.470626831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.957557678223</t>
   </si>
   <si>
     <t xml:space="preserve">125.494773864746</t>
   </si>
   <si>
-    <t xml:space="preserve">134.082290649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.960571289062</t>
+    <t xml:space="preserve">134.082275390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.960556030273</t>
   </si>
   <si>
     <t xml:space="preserve">134.179870605469</t>
   </si>
   <si>
-    <t xml:space="preserve">127.544075012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.177864074707</t>
+    <t xml:space="preserve">127.544059753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.177879333496</t>
   </si>
   <si>
     <t xml:space="preserve">121.201011657715</t>
@@ -3773,58 +3773,58 @@
     <t xml:space="preserve">122.176864624023</t>
   </si>
   <si>
-    <t xml:space="preserve">120.029991149902</t>
+    <t xml:space="preserve">120.029983520508</t>
   </si>
   <si>
     <t xml:space="preserve">115.736236572266</t>
   </si>
   <si>
-    <t xml:space="preserve">114.955558776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.271461486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.053131103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.711090087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.686935424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.466621398926</t>
+    <t xml:space="preserve">114.955551147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.271453857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.05313873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.711082458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.686943054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.46662902832</t>
   </si>
   <si>
     <t xml:space="preserve">117.590354919434</t>
   </si>
   <si>
-    <t xml:space="preserve">113.394187927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.832824707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.369033813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.977699279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.953559875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.025985717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.928413391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.70809173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.391189575195</t>
+    <t xml:space="preserve">113.394180297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.832817077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.369041442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.977691650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.953552246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.025993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.928405761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.708084106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.391181945801</t>
   </si>
   <si>
     <t xml:space="preserve">104.904258728027</t>
@@ -3833,7 +3833,7 @@
     <t xml:space="preserve">104.513916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">101.196006774902</t>
+    <t xml:space="preserve">101.196014404297</t>
   </si>
   <si>
     <t xml:space="preserve">105.001846313477</t>
@@ -3845,16 +3845,16 @@
     <t xml:space="preserve">115.83381652832</t>
   </si>
   <si>
-    <t xml:space="preserve">115.150718688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.12557220459</t>
+    <t xml:space="preserve">115.150726318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.125579833984</t>
   </si>
   <si>
     <t xml:space="preserve">106.75838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">103.440483093262</t>
+    <t xml:space="preserve">103.440475463867</t>
   </si>
   <si>
     <t xml:space="preserve">106.270454406738</t>
@@ -3866,61 +3866,61 @@
     <t xml:space="preserve">109.100433349609</t>
   </si>
   <si>
-    <t xml:space="preserve">108.514923095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.636657714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.978691101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.612510681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.441474914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.172874450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.905250549316</t>
+    <t xml:space="preserve">108.514915466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.636650085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.978698730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.612503051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.441482543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.172866821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.905258178711</t>
   </si>
   <si>
     <t xml:space="preserve">109.685943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">112.320747375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.274452209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.738235473633</t>
+    <t xml:space="preserve">112.320739746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.274459838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.738227844238</t>
   </si>
   <si>
     <t xml:space="preserve">116.028991699219</t>
   </si>
   <si>
-    <t xml:space="preserve">110.076286315918</t>
+    <t xml:space="preserve">110.076293945312</t>
   </si>
   <si>
     <t xml:space="preserve">107.929405212402</t>
   </si>
   <si>
-    <t xml:space="preserve">112.223167419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.78352355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.856964111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.588363647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.198020935059</t>
+    <t xml:space="preserve">112.223152160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.783531188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.856971740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.588356018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.198013305664</t>
   </si>
   <si>
     <t xml:space="preserve">110.759384155273</t>
@@ -3929,25 +3929,25 @@
     <t xml:space="preserve">117.200012207031</t>
   </si>
   <si>
-    <t xml:space="preserve">113.784530639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.587356567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.831825256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.197021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.099426269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.221160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.465621948242</t>
+    <t xml:space="preserve">113.784523010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.587348937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.831817626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.19701385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.099433898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.221168518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.465614318848</t>
   </si>
   <si>
     <t xml:space="preserve">104.41633605957</t>
@@ -3956,52 +3956,52 @@
     <t xml:space="preserve">105.880111694336</t>
   </si>
   <si>
-    <t xml:space="preserve">107.343887329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.052139282227</t>
+    <t xml:space="preserve">107.343894958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.052146911621</t>
   </si>
   <si>
     <t xml:space="preserve">114.467628479004</t>
   </si>
   <si>
-    <t xml:space="preserve">116.419342041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.883110046387</t>
+    <t xml:space="preserve">116.419334411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.883117675781</t>
   </si>
   <si>
     <t xml:space="preserve">118.761375427246</t>
   </si>
   <si>
-    <t xml:space="preserve">115.93140411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.39518737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.273445129395</t>
+    <t xml:space="preserve">115.931411743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.395179748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.273452758789</t>
   </si>
   <si>
     <t xml:space="preserve">114.760383605957</t>
   </si>
   <si>
-    <t xml:space="preserve">117.98070526123</t>
+    <t xml:space="preserve">117.980690002441</t>
   </si>
   <si>
     <t xml:space="preserve">123.933403015137</t>
   </si>
   <si>
-    <t xml:space="preserve">124.226165771484</t>
+    <t xml:space="preserve">124.22615814209</t>
   </si>
   <si>
     <t xml:space="preserve">123.152717590332</t>
   </si>
   <si>
-    <t xml:space="preserve">121.493766784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.663795471191</t>
+    <t xml:space="preserve">121.493774414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.663787841797</t>
   </si>
   <si>
     <t xml:space="preserve">119.6396484375</t>
@@ -4016,7 +4016,7 @@
     <t xml:space="preserve">112.515922546387</t>
   </si>
   <si>
-    <t xml:space="preserve">111.149726867676</t>
+    <t xml:space="preserve">111.149719238281</t>
   </si>
   <si>
     <t xml:space="preserve">113.199020385742</t>
@@ -4037,10 +4037,10 @@
     <t xml:space="preserve">112.027992248535</t>
   </si>
   <si>
-    <t xml:space="preserve">109.490768432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.148727416992</t>
+    <t xml:space="preserve">109.490776062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.148719787598</t>
   </si>
   <si>
     <t xml:space="preserve">113.58935546875</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">109.88111114502</t>
   </si>
   <si>
-    <t xml:space="preserve">107.051139831543</t>
+    <t xml:space="preserve">107.051132202148</t>
   </si>
   <si>
     <t xml:space="preserve">104.123573303223</t>
@@ -4061,13 +4061,13 @@
     <t xml:space="preserve">102.464622497559</t>
   </si>
   <si>
-    <t xml:space="preserve">101.683937072754</t>
+    <t xml:space="preserve">101.683944702148</t>
   </si>
   <si>
     <t xml:space="preserve">102.95255279541</t>
   </si>
   <si>
-    <t xml:space="preserve">101.781532287598</t>
+    <t xml:space="preserve">101.781524658203</t>
   </si>
   <si>
     <t xml:space="preserve">100.610504150391</t>
@@ -4076,10 +4076,10 @@
     <t xml:space="preserve">103.342895507812</t>
   </si>
   <si>
-    <t xml:space="preserve">101.000839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.415336608887</t>
+    <t xml:space="preserve">101.000846862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.415328979492</t>
   </si>
   <si>
     <t xml:space="preserve">102.074279785156</t>
@@ -4088,7 +4088,7 @@
     <t xml:space="preserve">103.040893554688</t>
   </si>
   <si>
-    <t xml:space="preserve">103.237915039062</t>
+    <t xml:space="preserve">103.237922668457</t>
   </si>
   <si>
     <t xml:space="preserve">99.3960494995117</t>
@@ -4115,7 +4115,7 @@
     <t xml:space="preserve">103.139404296875</t>
   </si>
   <si>
-    <t xml:space="preserve">102.449844360352</t>
+    <t xml:space="preserve">102.449836730957</t>
   </si>
   <si>
     <t xml:space="preserve">102.351333618164</t>
@@ -4142,7 +4142,7 @@
     <t xml:space="preserve">109.641036987305</t>
   </si>
   <si>
-    <t xml:space="preserve">106.390213012695</t>
+    <t xml:space="preserve">106.39022064209</t>
   </si>
   <si>
     <t xml:space="preserve">101.267730712891</t>
@@ -4154,7 +4154,7 @@
     <t xml:space="preserve">99.1005172729492</t>
   </si>
   <si>
-    <t xml:space="preserve">98.0661773681641</t>
+    <t xml:space="preserve">98.0661697387695</t>
   </si>
   <si>
     <t xml:space="preserve">100.479652404785</t>
@@ -4172,10 +4172,10 @@
     <t xml:space="preserve">106.685752868652</t>
   </si>
   <si>
-    <t xml:space="preserve">104.420036315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.957290649414</t>
+    <t xml:space="preserve">104.420028686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.957298278809</t>
   </si>
   <si>
     <t xml:space="preserve">101.858787536621</t>
@@ -4190,16 +4190,16 @@
     <t xml:space="preserve">103.631950378418</t>
   </si>
   <si>
-    <t xml:space="preserve">99.4945526123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.7064819335938</t>
+    <t xml:space="preserve">99.4945602416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.7064743041992</t>
   </si>
   <si>
     <t xml:space="preserve">97.2288360595703</t>
   </si>
   <si>
-    <t xml:space="preserve">98.2631912231445</t>
+    <t xml:space="preserve">98.26318359375</t>
   </si>
   <si>
     <t xml:space="preserve">98.164680480957</t>
@@ -4214,22 +4214,22 @@
     <t xml:space="preserve">97.1303329467773</t>
   </si>
   <si>
-    <t xml:space="preserve">94.5198287963867</t>
+    <t xml:space="preserve">94.5198211669922</t>
   </si>
   <si>
     <t xml:space="preserve">95.9974670410156</t>
   </si>
   <si>
-    <t xml:space="preserve">94.7660980224609</t>
+    <t xml:space="preserve">94.7661056518555</t>
   </si>
   <si>
     <t xml:space="preserve">94.4213180541992</t>
   </si>
   <si>
-    <t xml:space="preserve">93.7317504882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0421829223633</t>
+    <t xml:space="preserve">93.7317581176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0421905517578</t>
   </si>
   <si>
     <t xml:space="preserve">92.2048568725586</t>
@@ -4238,7 +4238,7 @@
     <t xml:space="preserve">92.8451690673828</t>
   </si>
   <si>
-    <t xml:space="preserve">91.1212463378906</t>
+    <t xml:space="preserve">91.1212539672852</t>
   </si>
   <si>
     <t xml:space="preserve">91.9093322753906</t>
@@ -4247,7 +4247,7 @@
     <t xml:space="preserve">91.0719909667969</t>
   </si>
   <si>
-    <t xml:space="preserve">86.8853378295898</t>
+    <t xml:space="preserve">86.8853454589844</t>
   </si>
   <si>
     <t xml:space="preserve">86.7868347167969</t>
@@ -4256,7 +4256,7 @@
     <t xml:space="preserve">86.0972747802734</t>
   </si>
   <si>
-    <t xml:space="preserve">86.4913177490234</t>
+    <t xml:space="preserve">86.4913101196289</t>
   </si>
   <si>
     <t xml:space="preserve">87.8211898803711</t>
@@ -4271,22 +4271,22 @@
     <t xml:space="preserve">91.7123107910156</t>
   </si>
   <si>
-    <t xml:space="preserve">91.6630554199219</t>
+    <t xml:space="preserve">91.6630630493164</t>
   </si>
   <si>
     <t xml:space="preserve">92.1556015014648</t>
   </si>
   <si>
-    <t xml:space="preserve">91.1705169677734</t>
+    <t xml:space="preserve">91.1705093383789</t>
   </si>
   <si>
     <t xml:space="preserve">90.3331756591797</t>
   </si>
   <si>
-    <t xml:space="preserve">88.6585159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.0331115722656</t>
+    <t xml:space="preserve">88.6585235595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.0331039428711</t>
   </si>
   <si>
     <t xml:space="preserve">86.6883239746094</t>
@@ -4304,7 +4304,7 @@
     <t xml:space="preserve">87.4271469116211</t>
   </si>
   <si>
-    <t xml:space="preserve">86.9838638305664</t>
+    <t xml:space="preserve">86.9838562011719</t>
   </si>
   <si>
     <t xml:space="preserve">86.1465225219727</t>
@@ -4322,10 +4322,10 @@
     <t xml:space="preserve">81.1717987060547</t>
   </si>
   <si>
-    <t xml:space="preserve">84.915153503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.2255859375</t>
+    <t xml:space="preserve">84.9151611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.2255935668945</t>
   </si>
   <si>
     <t xml:space="preserve">87.7226791381836</t>
@@ -4334,19 +4334,19 @@
     <t xml:space="preserve">88.3137359619141</t>
   </si>
   <si>
-    <t xml:space="preserve">86.2942886352539</t>
+    <t xml:space="preserve">86.2942810058594</t>
   </si>
   <si>
     <t xml:space="preserve">88.2644805908203</t>
   </si>
   <si>
-    <t xml:space="preserve">87.6734237670898</t>
+    <t xml:space="preserve">87.6734161376953</t>
   </si>
   <si>
     <t xml:space="preserve">88.806282043457</t>
   </si>
   <si>
-    <t xml:space="preserve">89.0032958984375</t>
+    <t xml:space="preserve">89.003303527832</t>
   </si>
   <si>
     <t xml:space="preserve">92.1063461303711</t>
@@ -4355,7 +4355,7 @@
     <t xml:space="preserve">86.4420547485352</t>
   </si>
   <si>
-    <t xml:space="preserve">85.3584442138672</t>
+    <t xml:space="preserve">85.3584518432617</t>
   </si>
   <si>
     <t xml:space="preserve">83.3390045166016</t>
@@ -4370,13 +4370,13 @@
     <t xml:space="preserve">84.6688766479492</t>
   </si>
   <si>
-    <t xml:space="preserve">85.013671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.1763305664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.7822952270508</t>
+    <t xml:space="preserve">85.0136642456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.1763381958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.7823028564453</t>
   </si>
   <si>
     <t xml:space="preserve">84.521125793457</t>
@@ -4388,10 +4388,10 @@
     <t xml:space="preserve">89.8898849487305</t>
   </si>
   <si>
-    <t xml:space="preserve">92.6481475830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3228149414062</t>
+    <t xml:space="preserve">92.6481552124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3228073120117</t>
   </si>
   <si>
     <t xml:space="preserve">92.3033676147461</t>
@@ -4409,13 +4409,13 @@
     <t xml:space="preserve">103.336433410645</t>
   </si>
   <si>
-    <t xml:space="preserve">101.661766052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.154304504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.715560913086</t>
+    <t xml:space="preserve">101.661758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.154312133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.71556854248</t>
   </si>
   <si>
     <t xml:space="preserve">104.223014831543</t>
@@ -4430,19 +4430,16 @@
     <t xml:space="preserve">102.942390441895</t>
   </si>
   <si>
-    <t xml:space="preserve">104.814064025879</t>
+    <t xml:space="preserve">104.814071655273</t>
   </si>
   <si>
     <t xml:space="preserve">105.602142333984</t>
   </si>
   <si>
-    <t xml:space="preserve">104.025993347168</t>
-  </si>
-  <si>
     <t xml:space="preserve">105.306617736816</t>
   </si>
   <si>
-    <t xml:space="preserve">106.784255981445</t>
+    <t xml:space="preserve">106.78426361084</t>
   </si>
   <si>
     <t xml:space="preserve">108.557426452637</t>
@@ -4451,28 +4448,28 @@
     <t xml:space="preserve">108.951461791992</t>
   </si>
   <si>
-    <t xml:space="preserve">107.473823547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.778434753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.285888671875</t>
+    <t xml:space="preserve">107.473815917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.778427124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.28588104248</t>
   </si>
   <si>
     <t xml:space="preserve">111.808242797852</t>
   </si>
   <si>
-    <t xml:space="preserve">115.354583740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.029243469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.438186645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.521797180176</t>
+    <t xml:space="preserve">115.35457611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.029251098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.438179016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.521789550781</t>
   </si>
   <si>
     <t xml:space="preserve">119.491981506348</t>
@@ -4487,7 +4484,7 @@
     <t xml:space="preserve">114.763519287109</t>
   </si>
   <si>
-    <t xml:space="preserve">112.300788879395</t>
+    <t xml:space="preserve">112.30078125</t>
   </si>
   <si>
     <t xml:space="preserve">112.596313476562</t>
@@ -4499,7 +4496,7 @@
     <t xml:space="preserve">115.847129821777</t>
   </si>
   <si>
-    <t xml:space="preserve">116.339668273926</t>
+    <t xml:space="preserve">116.33967590332</t>
   </si>
   <si>
     <t xml:space="preserve">118.112846374512</t>
@@ -4508,13 +4505,13 @@
     <t xml:space="preserve">119.886009216309</t>
   </si>
   <si>
-    <t xml:space="preserve">120.181549072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.787506103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.393463134766</t>
+    <t xml:space="preserve">120.181541442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.787498474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.39347076416</t>
   </si>
   <si>
     <t xml:space="preserve">121.757698059082</t>
@@ -4535,13 +4532,13 @@
     <t xml:space="preserve">125.10701751709</t>
   </si>
   <si>
-    <t xml:space="preserve">125.304039001465</t>
+    <t xml:space="preserve">125.30403137207</t>
   </si>
   <si>
     <t xml:space="preserve">125.599563598633</t>
   </si>
   <si>
-    <t xml:space="preserve">124.811492919922</t>
+    <t xml:space="preserve">124.811485290527</t>
   </si>
   <si>
     <t xml:space="preserve">125.008506774902</t>
@@ -4553,16 +4550,16 @@
     <t xml:space="preserve">126.584663391113</t>
   </si>
   <si>
-    <t xml:space="preserve">123.727890014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.796577453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.121917724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.46216583252</t>
+    <t xml:space="preserve">123.727882385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.796585083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.121925354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.462173461914</t>
   </si>
   <si>
     <t xml:space="preserve">120.280052185059</t>
@@ -4571,7 +4568,7 @@
     <t xml:space="preserve">121.659187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">120.575576782227</t>
+    <t xml:space="preserve">120.575584411621</t>
   </si>
   <si>
     <t xml:space="preserve">122.64427947998</t>
@@ -4580,7 +4577,7 @@
     <t xml:space="preserve">122.742790222168</t>
   </si>
   <si>
-    <t xml:space="preserve">125.205520629883</t>
+    <t xml:space="preserve">125.205528259277</t>
   </si>
   <si>
     <t xml:space="preserve">126.190628051758</t>
@@ -4595,10 +4592,10 @@
     <t xml:space="preserve">123.235336303711</t>
   </si>
   <si>
-    <t xml:space="preserve">124.515960693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.151733398438</t>
+    <t xml:space="preserve">124.515968322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.151741027832</t>
   </si>
   <si>
     <t xml:space="preserve">122.841300964355</t>
@@ -4613,10 +4610,10 @@
     <t xml:space="preserve">130.032501220703</t>
   </si>
   <si>
-    <t xml:space="preserve">130.820556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.722045898438</t>
+    <t xml:space="preserve">130.820571899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.722061157227</t>
   </si>
   <si>
     <t xml:space="preserve">129.835479736328</t>
@@ -4631,7 +4628,7 @@
     <t xml:space="preserve">127.569747924805</t>
   </si>
   <si>
-    <t xml:space="preserve">127.668258666992</t>
+    <t xml:space="preserve">127.668266296387</t>
   </si>
   <si>
     <t xml:space="preserve">129.244415283203</t>
@@ -4643,7 +4640,7 @@
     <t xml:space="preserve">130.131011962891</t>
   </si>
   <si>
-    <t xml:space="preserve">129.441421508789</t>
+    <t xml:space="preserve">129.441436767578</t>
   </si>
   <si>
     <t xml:space="preserve">126.486145019531</t>
@@ -4652,22 +4649,22 @@
     <t xml:space="preserve">128.16081237793</t>
   </si>
   <si>
-    <t xml:space="preserve">126.387649536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.910003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.05322265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.265151977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.250244140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.166641235352</t>
+    <t xml:space="preserve">126.387641906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.909996032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.053230285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.265144348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.25023651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.166633605957</t>
   </si>
   <si>
     <t xml:space="preserve">133.677337646484</t>
@@ -4676,111 +4673,114 @@
     <t xml:space="preserve">131.116104125977</t>
   </si>
   <si>
+    <t xml:space="preserve">134.760955810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.058654785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.455581665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.959411621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.356338500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.547180175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.447937011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.577774047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.280075073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.43286895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.417556762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.516799926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.799194335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.073959350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.554824829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.379302978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.371643066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.776245117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.16552734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.936462402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.043350219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.111968994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.325744628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.142578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.745635986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.257125854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.531875610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.12727355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.318084716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.134918212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.928802490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.516571044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.730331420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.249465942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.860168457031</t>
+  </si>
+  <si>
     <t xml:space="preserve">134.760940551758</t>
   </si>
   <si>
-    <t xml:space="preserve">135.058654785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.455581665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.959411621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.356338500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.547180175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.447937011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.577774047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.280075073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.43286895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.417556762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.516799926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.799194335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.073959350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.554824829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.379302978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.371643066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.776245117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.16552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.936462402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.043350219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.111968994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.325744628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.142578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.745635986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.257125854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.531875610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.12727355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.318084716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.134918212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.928802490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.516571044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.730331420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.249465942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.860168457031</t>
-  </si>
-  <si>
     <t xml:space="preserve">136.944107055664</t>
   </si>
   <si>
@@ -5460,6 +5460,9 @@
   </si>
   <si>
     <t xml:space="preserve">118.099998474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.5</t>
   </si>
 </sst>
 </file>
@@ -58284,7 +58287,7 @@
         <v>105.599998474121</v>
       </c>
       <c r="G2019" t="s">
-        <v>1474</v>
+        <v>1267</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -58310,7 +58313,7 @@
         <v>106.900001525879</v>
       </c>
       <c r="G2020" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -58336,7 +58339,7 @@
         <v>108.400001525879</v>
       </c>
       <c r="G2021" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -58388,7 +58391,7 @@
         <v>110.199996948242</v>
       </c>
       <c r="G2023" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -58414,7 +58417,7 @@
         <v>110.199996948242</v>
       </c>
       <c r="G2024" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -58440,7 +58443,7 @@
         <v>110.599998474121</v>
       </c>
       <c r="G2025" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -58466,7 +58469,7 @@
         <v>109.099998474121</v>
       </c>
       <c r="G2026" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -58492,7 +58495,7 @@
         <v>115.5</v>
       </c>
       <c r="G2027" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -58518,7 +58521,7 @@
         <v>115</v>
       </c>
       <c r="G2028" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -58544,7 +58547,7 @@
         <v>113.5</v>
       </c>
       <c r="G2029" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -58570,7 +58573,7 @@
         <v>117.099998474121</v>
       </c>
       <c r="G2030" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -58596,7 +58599,7 @@
         <v>118.800003051758</v>
       </c>
       <c r="G2031" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -58622,7 +58625,7 @@
         <v>118.199996948242</v>
       </c>
       <c r="G2032" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -58648,7 +58651,7 @@
         <v>119.300003051758</v>
       </c>
       <c r="G2033" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -58674,7 +58677,7 @@
         <v>121.300003051758</v>
       </c>
       <c r="G2034" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -58700,7 +58703,7 @@
         <v>119.800003051758</v>
       </c>
       <c r="G2035" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -58726,7 +58729,7 @@
         <v>119.5</v>
       </c>
       <c r="G2036" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -58752,7 +58755,7 @@
         <v>116.5</v>
       </c>
       <c r="G2037" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -58778,7 +58781,7 @@
         <v>114</v>
       </c>
       <c r="G2038" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -58804,7 +58807,7 @@
         <v>114.300003051758</v>
       </c>
       <c r="G2039" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -58830,7 +58833,7 @@
         <v>113.099998474121</v>
       </c>
       <c r="G2040" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -58856,7 +58859,7 @@
         <v>115.5</v>
       </c>
       <c r="G2041" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -58882,7 +58885,7 @@
         <v>117.599998474121</v>
       </c>
       <c r="G2042" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -58908,7 +58911,7 @@
         <v>118.099998474121</v>
       </c>
       <c r="G2043" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -58934,7 +58937,7 @@
         <v>119.900001525879</v>
       </c>
       <c r="G2044" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -58960,7 +58963,7 @@
         <v>121.699996948242</v>
       </c>
       <c r="G2045" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -58986,7 +58989,7 @@
         <v>122</v>
       </c>
       <c r="G2046" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -59012,7 +59015,7 @@
         <v>121.599998474121</v>
       </c>
       <c r="G2047" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -59038,7 +59041,7 @@
         <v>121.199996948242</v>
       </c>
       <c r="G2048" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -59064,7 +59067,7 @@
         <v>122</v>
       </c>
       <c r="G2049" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -59090,7 +59093,7 @@
         <v>119.900001525879</v>
       </c>
       <c r="G2050" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -59116,7 +59119,7 @@
         <v>123.599998474121</v>
       </c>
       <c r="G2051" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -59142,7 +59145,7 @@
         <v>121.900001525879</v>
       </c>
       <c r="G2052" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -59168,7 +59171,7 @@
         <v>123.199996948242</v>
       </c>
       <c r="G2053" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -59194,7 +59197,7 @@
         <v>125.699996948242</v>
       </c>
       <c r="G2054" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -59220,7 +59223,7 @@
         <v>126.099998474121</v>
       </c>
       <c r="G2055" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -59246,7 +59249,7 @@
         <v>127</v>
       </c>
       <c r="G2056" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -59272,7 +59275,7 @@
         <v>127.199996948242</v>
       </c>
       <c r="G2057" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -59298,7 +59301,7 @@
         <v>127.5</v>
       </c>
       <c r="G2058" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -59324,7 +59327,7 @@
         <v>126.699996948242</v>
       </c>
       <c r="G2059" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -59350,7 +59353,7 @@
         <v>126.900001525879</v>
       </c>
       <c r="G2060" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -59376,7 +59379,7 @@
         <v>125.900001525879</v>
       </c>
       <c r="G2061" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -59402,7 +59405,7 @@
         <v>128.5</v>
       </c>
       <c r="G2062" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -59428,7 +59431,7 @@
         <v>127.199996948242</v>
       </c>
       <c r="G2063" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -59454,7 +59457,7 @@
         <v>125.599998474121</v>
       </c>
       <c r="G2064" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -59480,7 +59483,7 @@
         <v>127.699996948242</v>
       </c>
       <c r="G2065" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -59506,7 +59509,7 @@
         <v>126</v>
       </c>
       <c r="G2066" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -59532,7 +59535,7 @@
         <v>121.599998474121</v>
       </c>
       <c r="G2067" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -59558,7 +59561,7 @@
         <v>123.300003051758</v>
       </c>
       <c r="G2068" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -59584,7 +59587,7 @@
         <v>121.599998474121</v>
       </c>
       <c r="G2069" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -59610,7 +59613,7 @@
         <v>122.099998474121</v>
       </c>
       <c r="G2070" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -59636,7 +59639,7 @@
         <v>123.5</v>
       </c>
       <c r="G2071" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -59662,7 +59665,7 @@
         <v>122.400001525879</v>
       </c>
       <c r="G2072" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -59688,7 +59691,7 @@
         <v>121.199996948242</v>
       </c>
       <c r="G2073" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -59714,7 +59717,7 @@
         <v>124.5</v>
       </c>
       <c r="G2074" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -59740,7 +59743,7 @@
         <v>124.599998474121</v>
       </c>
       <c r="G2075" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -59766,7 +59769,7 @@
         <v>127.099998474121</v>
       </c>
       <c r="G2076" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -59792,7 +59795,7 @@
         <v>128.100006103516</v>
       </c>
       <c r="G2077" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -59818,7 +59821,7 @@
         <v>128.5</v>
       </c>
       <c r="G2078" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -59844,7 +59847,7 @@
         <v>128.199996948242</v>
       </c>
       <c r="G2079" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -59870,7 +59873,7 @@
         <v>127.599998474121</v>
       </c>
       <c r="G2080" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -59896,7 +59899,7 @@
         <v>128.100006103516</v>
       </c>
       <c r="G2081" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -59922,7 +59925,7 @@
         <v>122.400001525879</v>
       </c>
       <c r="G2082" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -59948,7 +59951,7 @@
         <v>125.099998474121</v>
       </c>
       <c r="G2083" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -59974,7 +59977,7 @@
         <v>126.400001525879</v>
       </c>
       <c r="G2084" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -60000,7 +60003,7 @@
         <v>127.599998474121</v>
       </c>
       <c r="G2085" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -60026,7 +60029,7 @@
         <v>124</v>
       </c>
       <c r="G2086" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -60052,7 +60055,7 @@
         <v>124.699996948242</v>
       </c>
       <c r="G2087" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -60078,7 +60081,7 @@
         <v>132.5</v>
       </c>
       <c r="G2088" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -60104,7 +60107,7 @@
         <v>130.899993896484</v>
       </c>
       <c r="G2089" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -60130,7 +60133,7 @@
         <v>132</v>
       </c>
       <c r="G2090" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -60156,7 +60159,7 @@
         <v>132.800003051758</v>
       </c>
       <c r="G2091" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -60182,7 +60185,7 @@
         <v>132.699996948242</v>
       </c>
       <c r="G2092" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -60208,7 +60211,7 @@
         <v>131.800003051758</v>
       </c>
       <c r="G2093" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -60234,7 +60237,7 @@
         <v>131</v>
       </c>
       <c r="G2094" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -60260,7 +60263,7 @@
         <v>131.699996948242</v>
       </c>
       <c r="G2095" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -60286,7 +60289,7 @@
         <v>129.5</v>
       </c>
       <c r="G2096" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -60312,7 +60315,7 @@
         <v>129.600006103516</v>
       </c>
       <c r="G2097" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -60338,7 +60341,7 @@
         <v>132.800003051758</v>
       </c>
       <c r="G2098" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -60364,7 +60367,7 @@
         <v>131.199996948242</v>
       </c>
       <c r="G2099" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -60390,7 +60393,7 @@
         <v>129.899993896484</v>
       </c>
       <c r="G2100" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -60416,7 +60419,7 @@
         <v>132.100006103516</v>
       </c>
       <c r="G2101" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -60442,7 +60445,7 @@
         <v>131.399993896484</v>
       </c>
       <c r="G2102" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -60468,7 +60471,7 @@
         <v>128.399993896484</v>
       </c>
       <c r="G2103" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -60494,7 +60497,7 @@
         <v>130.100006103516</v>
       </c>
       <c r="G2104" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -60520,7 +60523,7 @@
         <v>128.300003051758</v>
       </c>
       <c r="G2105" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -60546,7 +60549,7 @@
         <v>127.699996948242</v>
       </c>
       <c r="G2106" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -60572,7 +60575,7 @@
         <v>127.5</v>
       </c>
       <c r="G2107" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -60598,7 +60601,7 @@
         <v>126.800003051758</v>
       </c>
       <c r="G2108" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -60624,7 +60627,7 @@
         <v>127</v>
       </c>
       <c r="G2109" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -60650,7 +60653,7 @@
         <v>124.599998474121</v>
       </c>
       <c r="G2110" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -60676,7 +60679,7 @@
         <v>123.900001525879</v>
       </c>
       <c r="G2111" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -60702,7 +60705,7 @@
         <v>123.300003051758</v>
       </c>
       <c r="G2112" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -60728,7 +60731,7 @@
         <v>121.300003051758</v>
       </c>
       <c r="G2113" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -60754,7 +60757,7 @@
         <v>123.099998474121</v>
       </c>
       <c r="G2114" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -60780,7 +60783,7 @@
         <v>125.699996948242</v>
       </c>
       <c r="G2115" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -60806,7 +60809,7 @@
         <v>124.599998474121</v>
       </c>
       <c r="G2116" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -60832,7 +60835,7 @@
         <v>124.099998474121</v>
       </c>
       <c r="G2117" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -60858,7 +60861,7 @@
         <v>124.099998474121</v>
       </c>
       <c r="G2118" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -60884,7 +60887,7 @@
         <v>123.900001525879</v>
       </c>
       <c r="G2119" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -60910,7 +60913,7 @@
         <v>123</v>
       </c>
       <c r="G2120" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -60936,7 +60939,7 @@
         <v>123.300003051758</v>
       </c>
       <c r="G2121" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -60962,7 +60965,7 @@
         <v>124.099998474121</v>
       </c>
       <c r="G2122" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -60988,7 +60991,7 @@
         <v>124.5</v>
       </c>
       <c r="G2123" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -61014,7 +61017,7 @@
         <v>126.900001525879</v>
       </c>
       <c r="G2124" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -61040,7 +61043,7 @@
         <v>127</v>
       </c>
       <c r="G2125" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -61066,7 +61069,7 @@
         <v>127</v>
       </c>
       <c r="G2126" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -61092,7 +61095,7 @@
         <v>127.099998474121</v>
       </c>
       <c r="G2127" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -61118,7 +61121,7 @@
         <v>125.900001525879</v>
       </c>
       <c r="G2128" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -61144,7 +61147,7 @@
         <v>135.699996948242</v>
       </c>
       <c r="G2129" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -61170,7 +61173,7 @@
         <v>133.100006103516</v>
       </c>
       <c r="G2130" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -61196,7 +61199,7 @@
         <v>136.800003051758</v>
       </c>
       <c r="G2131" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -61222,7 +61225,7 @@
         <v>136.800003051758</v>
       </c>
       <c r="G2132" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -61248,7 +61251,7 @@
         <v>136.100006103516</v>
       </c>
       <c r="G2133" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -61274,7 +61277,7 @@
         <v>136.5</v>
       </c>
       <c r="G2134" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -61300,7 +61303,7 @@
         <v>136</v>
       </c>
       <c r="G2135" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -61326,7 +61329,7 @@
         <v>136</v>
       </c>
       <c r="G2136" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -61352,7 +61355,7 @@
         <v>136.399993896484</v>
       </c>
       <c r="G2137" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -61378,7 +61381,7 @@
         <v>137.600006103516</v>
       </c>
       <c r="G2138" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -61404,7 +61407,7 @@
         <v>137.5</v>
       </c>
       <c r="G2139" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -61430,7 +61433,7 @@
         <v>133.600006103516</v>
       </c>
       <c r="G2140" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -61456,7 +61459,7 @@
         <v>133.300003051758</v>
       </c>
       <c r="G2141" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -61482,7 +61485,7 @@
         <v>126.400001525879</v>
       </c>
       <c r="G2142" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -61508,7 +61511,7 @@
         <v>128.399993896484</v>
       </c>
       <c r="G2143" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -61534,7 +61537,7 @@
         <v>128.5</v>
       </c>
       <c r="G2144" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -61560,7 +61563,7 @@
         <v>130.800003051758</v>
       </c>
       <c r="G2145" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -61586,7 +61589,7 @@
         <v>134.100006103516</v>
       </c>
       <c r="G2146" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -61612,7 +61615,7 @@
         <v>136.600006103516</v>
       </c>
       <c r="G2147" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -61638,7 +61641,7 @@
         <v>136</v>
       </c>
       <c r="G2148" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -61664,7 +61667,7 @@
         <v>133.399993896484</v>
       </c>
       <c r="G2149" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -61690,7 +61693,7 @@
         <v>136.5</v>
       </c>
       <c r="G2150" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -61716,7 +61719,7 @@
         <v>134.399993896484</v>
       </c>
       <c r="G2151" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -61742,7 +61745,7 @@
         <v>133.399993896484</v>
       </c>
       <c r="G2152" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -61768,7 +61771,7 @@
         <v>133.800003051758</v>
       </c>
       <c r="G2153" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -61794,7 +61797,7 @@
         <v>135.199996948242</v>
       </c>
       <c r="G2154" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -61820,7 +61823,7 @@
         <v>133.800003051758</v>
       </c>
       <c r="G2155" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -61846,7 +61849,7 @@
         <v>139</v>
       </c>
       <c r="G2156" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -61872,7 +61875,7 @@
         <v>138.100006103516</v>
       </c>
       <c r="G2157" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -61898,7 +61901,7 @@
         <v>142.199996948242</v>
       </c>
       <c r="G2158" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -61924,7 +61927,7 @@
         <v>140.399993896484</v>
       </c>
       <c r="G2159" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -61950,7 +61953,7 @@
         <v>137.5</v>
       </c>
       <c r="G2160" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -61976,7 +61979,7 @@
         <v>138.199996948242</v>
       </c>
       <c r="G2161" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -62002,7 +62005,7 @@
         <v>137.800003051758</v>
       </c>
       <c r="G2162" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -62028,7 +62031,7 @@
         <v>136.100006103516</v>
       </c>
       <c r="G2163" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -62054,7 +62057,7 @@
         <v>136.300003051758</v>
       </c>
       <c r="G2164" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -62080,7 +62083,7 @@
         <v>139.600006103516</v>
       </c>
       <c r="G2165" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -62106,7 +62109,7 @@
         <v>140.199996948242</v>
       </c>
       <c r="G2166" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -62132,7 +62135,7 @@
         <v>141.399993896484</v>
       </c>
       <c r="G2167" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -62158,7 +62161,7 @@
         <v>140.199996948242</v>
       </c>
       <c r="G2168" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -62184,7 +62187,7 @@
         <v>139.199996948242</v>
       </c>
       <c r="G2169" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -62210,7 +62213,7 @@
         <v>140</v>
       </c>
       <c r="G2170" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -62236,7 +62239,7 @@
         <v>140</v>
       </c>
       <c r="G2171" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -62262,7 +62265,7 @@
         <v>141.600006103516</v>
       </c>
       <c r="G2172" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -62288,7 +62291,7 @@
         <v>140.199996948242</v>
       </c>
       <c r="G2173" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -62314,7 +62317,7 @@
         <v>139.800003051758</v>
       </c>
       <c r="G2174" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -62340,7 +62343,7 @@
         <v>137.300003051758</v>
       </c>
       <c r="G2175" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -62366,7 +62369,7 @@
         <v>135.899993896484</v>
       </c>
       <c r="G2176" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -62392,7 +62395,7 @@
         <v>135.800003051758</v>
       </c>
       <c r="G2177" t="s">
-        <v>1554</v>
+        <v>1588</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -62444,7 +62447,7 @@
         <v>139</v>
       </c>
       <c r="G2179" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -62470,7 +62473,7 @@
         <v>135.800003051758</v>
       </c>
       <c r="G2180" t="s">
-        <v>1554</v>
+        <v>1588</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -62808,7 +62811,7 @@
         <v>128.399993896484</v>
       </c>
       <c r="G2193" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -62886,7 +62889,7 @@
         <v>134.399993896484</v>
       </c>
       <c r="G2196" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -62938,7 +62941,7 @@
         <v>136.100006103516</v>
       </c>
       <c r="G2198" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -62990,7 +62993,7 @@
         <v>137.800003051758</v>
       </c>
       <c r="G2200" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -63016,7 +63019,7 @@
         <v>138.199996948242</v>
       </c>
       <c r="G2201" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -63068,7 +63071,7 @@
         <v>139.800003051758</v>
       </c>
       <c r="G2203" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -63094,7 +63097,7 @@
         <v>140.199996948242</v>
       </c>
       <c r="G2204" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -63224,7 +63227,7 @@
         <v>136.300003051758</v>
       </c>
       <c r="G2209" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -63250,7 +63253,7 @@
         <v>134.100006103516</v>
       </c>
       <c r="G2210" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -63380,7 +63383,7 @@
         <v>137.800003051758</v>
       </c>
       <c r="G2215" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -63406,7 +63409,7 @@
         <v>137.600006103516</v>
       </c>
       <c r="G2216" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -63562,7 +63565,7 @@
         <v>135.800003051758</v>
       </c>
       <c r="G2222" t="s">
-        <v>1554</v>
+        <v>1588</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -63588,7 +63591,7 @@
         <v>133.600006103516</v>
       </c>
       <c r="G2223" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -63692,7 +63695,7 @@
         <v>135.199996948242</v>
       </c>
       <c r="G2227" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -63900,7 +63903,7 @@
         <v>133.600006103516</v>
       </c>
       <c r="G2235" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -63926,7 +63929,7 @@
         <v>133.300003051758</v>
       </c>
       <c r="G2236" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -63978,7 +63981,7 @@
         <v>140.399993896484</v>
       </c>
       <c r="G2238" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -64524,7 +64527,7 @@
         <v>140.399993896484</v>
       </c>
       <c r="G2259" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -67072,7 +67075,7 @@
         <v>136.100006103516</v>
       </c>
       <c r="G2357" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -70564,7 +70567,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6493171296</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>50777</v>
@@ -70585,6 +70588,32 @@
         <v>1815</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.649537037</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>58490</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>119.300003051758</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>117.599998474121</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>1816</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/REY.MI.xlsx
+++ b/data/REY.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="1817">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="1818">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2559719085693</t>
+    <t xml:space="preserve">29.2559680938721</t>
   </si>
   <si>
     <t xml:space="preserve">REY.MI</t>
@@ -47,31 +47,31 @@
     <t xml:space="preserve">28.8380298614502</t>
   </si>
   <si>
-    <t xml:space="preserve">28.327205657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6306400299072</t>
+    <t xml:space="preserve">28.3272113800049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6306381225586</t>
   </si>
   <si>
     <t xml:space="preserve">27.8396110534668</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2111148834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0005626678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5594024658203</t>
+    <t xml:space="preserve">28.2111129760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.000560760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.559398651123</t>
   </si>
   <si>
     <t xml:space="preserve">28.1414585113525</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1198196411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9789237976074</t>
+    <t xml:space="preserve">27.1198234558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9789257049561</t>
   </si>
   <si>
     <t xml:space="preserve">26.8644123077393</t>
@@ -80,109 +80,109 @@
     <t xml:space="preserve">27.4448833465576</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9324855804443</t>
+    <t xml:space="preserve">27.9324893951416</t>
   </si>
   <si>
     <t xml:space="preserve">27.8163928985596</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2807769775391</t>
+    <t xml:space="preserve">28.2807750701904</t>
   </si>
   <si>
     <t xml:space="preserve">27.6770782470703</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0950222015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.862829208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2591342926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7018795013428</t>
+    <t xml:space="preserve">28.0950202941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8628311157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2591361999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7018756866455</t>
   </si>
   <si>
     <t xml:space="preserve">26.167839050293</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2855167388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.379976272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6121673583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0053081512451</t>
+    <t xml:space="preserve">25.285514831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3799781799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6121635437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0053062438965</t>
   </si>
   <si>
     <t xml:space="preserve">25.517707824707</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6570243835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6074199676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3071594238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0733871459961</t>
+    <t xml:space="preserve">25.6570262908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6074180603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3071537017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0733833312988</t>
   </si>
   <si>
     <t xml:space="preserve">26.2142791748047</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4696884155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0517482757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7034587860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7266807556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7483196258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4929065704346</t>
+    <t xml:space="preserve">26.4696865081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0517444610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.703462600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.726676940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7483158111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4929103851318</t>
   </si>
   <si>
     <t xml:space="preserve">27.3520107269287</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1894817352295</t>
+    <t xml:space="preserve">27.1894779205322</t>
   </si>
   <si>
     <t xml:space="preserve">27.2359142303467</t>
   </si>
   <si>
-    <t xml:space="preserve">27.166259765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9092693328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0237789154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5546493530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3008251190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4169235229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9989776611328</t>
+    <t xml:space="preserve">27.1662616729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9092674255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0237808227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5546569824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3008308410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4169216156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9989795684814</t>
   </si>
   <si>
     <t xml:space="preserve">29.9757614135742</t>
@@ -191,16 +191,16 @@
     <t xml:space="preserve">29.7900085449219</t>
   </si>
   <si>
-    <t xml:space="preserve">29.952543258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2311687469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7203521728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0686359405518</t>
+    <t xml:space="preserve">29.9525413513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2311706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7203502655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0686340332031</t>
   </si>
   <si>
     <t xml:space="preserve">29.8596668243408</t>
@@ -212,25 +212,25 @@
     <t xml:space="preserve">29.3256301879883</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4881649017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.511381149292</t>
+    <t xml:space="preserve">29.4881610870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5113792419434</t>
   </si>
   <si>
     <t xml:space="preserve">29.2095336914062</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1615123748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3720664978027</t>
+    <t xml:space="preserve">30.1615085601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3720684051514</t>
   </si>
   <si>
     <t xml:space="preserve">29.5345993041992</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4433059692383</t>
+    <t xml:space="preserve">28.4433097839355</t>
   </si>
   <si>
     <t xml:space="preserve">28.6754970550537</t>
@@ -239,115 +239,115 @@
     <t xml:space="preserve">28.8612499237061</t>
   </si>
   <si>
-    <t xml:space="preserve">28.814811706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9076843261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6290607452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4200878143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6775989532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5605449676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0287551879883</t>
+    <t xml:space="preserve">28.8148097991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9076881408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.629056930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4200859069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6776027679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5605506896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0287532806396</t>
   </si>
   <si>
     <t xml:space="preserve">28.3264465332031</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5137329101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7946529388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0053405761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2628536224365</t>
+    <t xml:space="preserve">28.5137310028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7946510314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0053443908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2628574371338</t>
   </si>
   <si>
     <t xml:space="preserve">30.1992683410645</t>
   </si>
   <si>
-    <t xml:space="preserve">30.503604888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5504188537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9015789031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6674747467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7142944335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4567832946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.43337059021</t>
+    <t xml:space="preserve">30.5036029815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5504264831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.901575088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6674728393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7142963409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4567852020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4333724975586</t>
   </si>
   <si>
     <t xml:space="preserve">30.2694988250732</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8949337005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1859874725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3096752166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4969615936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6943702697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7747192382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8047771453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.319803237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9218292236328</t>
+    <t xml:space="preserve">29.8949375152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1859855651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3096790313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4969577789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6943683624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7747249603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8047790527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3198013305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9218273162842</t>
   </si>
   <si>
     <t xml:space="preserve">27.5070838928223</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9452381134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8215446472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2195205688477</t>
+    <t xml:space="preserve">26.945240020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8215484619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.219518661499</t>
   </si>
   <si>
     <t xml:space="preserve">27.1091117858887</t>
   </si>
   <si>
-    <t xml:space="preserve">27.624137878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.366626739502</t>
+    <t xml:space="preserve">27.6241359710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3666229248047</t>
   </si>
   <si>
     <t xml:space="preserve">28.303035736084</t>
@@ -359,7 +359,7 @@
     <t xml:space="preserve">28.7478313446045</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4434967041016</t>
+    <t xml:space="preserve">28.4434947967529</t>
   </si>
   <si>
     <t xml:space="preserve">28.98193359375</t>
@@ -368,49 +368,49 @@
     <t xml:space="preserve">28.9117050170898</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3799095153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4501399993896</t>
+    <t xml:space="preserve">29.3799057006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4501419067383</t>
   </si>
   <si>
     <t xml:space="preserve">29.8481159210205</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1524505615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9651660919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7244186401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1458053588867</t>
+    <t xml:space="preserve">30.1524467468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9651641845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.724422454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1458072662354</t>
   </si>
   <si>
     <t xml:space="preserve">29.0989875793457</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9351100921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4903163909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9752941131592</t>
+    <t xml:space="preserve">28.9351139068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4903144836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9752922058105</t>
   </si>
   <si>
     <t xml:space="preserve">28.3732662200928</t>
   </si>
   <si>
-    <t xml:space="preserve">28.092342376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2729835510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0622882843018</t>
+    <t xml:space="preserve">28.0923442840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2729816436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0622901916504</t>
   </si>
   <si>
     <t xml:space="preserve">27.0388793945312</t>
@@ -422,121 +422,121 @@
     <t xml:space="preserve">26.1492881774902</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7981300354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8917751312256</t>
+    <t xml:space="preserve">25.7981357574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.891773223877</t>
   </si>
   <si>
     <t xml:space="preserve">26.7579574584961</t>
   </si>
   <si>
-    <t xml:space="preserve">27.95188331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8816509246826</t>
+    <t xml:space="preserve">27.9518814086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.881649017334</t>
   </si>
   <si>
     <t xml:space="preserve">27.8114204406738</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9050598144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2963981628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8582401275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5773162841797</t>
+    <t xml:space="preserve">27.9050617218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2963924407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8582382202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5773181915283</t>
   </si>
   <si>
     <t xml:space="preserve">27.7177772521973</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7411918640137</t>
+    <t xml:space="preserve">27.741189956665</t>
   </si>
   <si>
     <t xml:space="preserve">28.0455226898193</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7880058288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3900337219238</t>
+    <t xml:space="preserve">27.7880077362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3900356292725</t>
   </si>
   <si>
     <t xml:space="preserve">29.1223964691162</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6541900634766</t>
+    <t xml:space="preserve">28.6541881561279</t>
   </si>
   <si>
     <t xml:space="preserve">28.2093944549561</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4134464263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0856990814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.851598739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4368534088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6877269744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2261619567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8281879425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6409091949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4536190032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5706729888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5238590240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3365707397461</t>
+    <t xml:space="preserve">27.413444519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0857009887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8515968322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4368553161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.68772315979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2261657714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8281860351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.640905380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4536247253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5706768035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5238513946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3365726470947</t>
   </si>
   <si>
     <t xml:space="preserve">25.751314163208</t>
   </si>
   <si>
-    <t xml:space="preserve">25.329927444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7446727752686</t>
+    <t xml:space="preserve">25.3299293518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7446708679199</t>
   </si>
   <si>
     <t xml:space="preserve">24.7680854797363</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8851337432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2530555725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0490055084229</t>
+    <t xml:space="preserve">24.8851356506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2530574798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0490074157715</t>
   </si>
   <si>
     <t xml:space="preserve">25.4703922271729</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5172119140625</t>
+    <t xml:space="preserve">25.5172138214111</t>
   </si>
   <si>
     <t xml:space="preserve">25.283109664917</t>
@@ -545,115 +545,115 @@
     <t xml:space="preserve">25.1660556793213</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4469795227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0958290100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9319553375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.072416305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6342620849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1961135864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.172700881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8348293304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9284725189209</t>
+    <t xml:space="preserve">25.4469776153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0958309173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.931957244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0724143981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6342639923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1961097717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1726989746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8348274230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9284706115723</t>
   </si>
   <si>
     <t xml:space="preserve">27.4602642059326</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9986991882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6307773590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2160358428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3330841064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8648853302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3498554229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6073684692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4735507965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2394485473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7076511383057</t>
+    <t xml:space="preserve">27.9987030029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6307811737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2160339355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3330879211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8648815155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.349853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6073665618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4735527038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2394466400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7076568603516</t>
   </si>
   <si>
     <t xml:space="preserve">29.4267292022705</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8313446044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9952182769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4868354797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2527275085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.369779586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1356830596924</t>
+    <t xml:space="preserve">30.8313465118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9952163696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4868335723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2527313232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3697814941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1356754302979</t>
   </si>
   <si>
     <t xml:space="preserve">32.1891479492188</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3061866760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2660140991211</t>
+    <t xml:space="preserve">32.3061943054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2660179138184</t>
   </si>
   <si>
     <t xml:space="preserve">34.0619659423828</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6472206115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4599456787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7408599853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6706352233887</t>
+    <t xml:space="preserve">34.6472282409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4599418640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7408676147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6706314086914</t>
   </si>
   <si>
     <t xml:space="preserve">34.9983749389648</t>
   </si>
   <si>
-    <t xml:space="preserve">34.85791015625</t>
+    <t xml:space="preserve">34.8579139709473</t>
   </si>
   <si>
     <t xml:space="preserve">34.1790199279785</t>
@@ -662,10 +662,10 @@
     <t xml:space="preserve">34.7642707824707</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8813285827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3897132873535</t>
+    <t xml:space="preserve">34.8813209533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.389705657959</t>
   </si>
   <si>
     <t xml:space="preserve">34.4131202697754</t>
@@ -680,40 +680,40 @@
     <t xml:space="preserve">35.7943267822266</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8243789672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6671524047852</t>
+    <t xml:space="preserve">36.8243827819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6671409606934</t>
   </si>
   <si>
     <t xml:space="preserve">37.8778419494629</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9882507324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5735054016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6203269958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6085357666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7264404296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9150733947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1980094909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.938648223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1508560180664</t>
+    <t xml:space="preserve">36.9882545471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5735092163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6203231811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6085395812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7264366149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9150695800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1980133056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9386444091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1508598327637</t>
   </si>
   <si>
     <t xml:space="preserve">37.4906425476074</t>
@@ -725,22 +725,22 @@
     <t xml:space="preserve">40.0843391418457</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0607604980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8013916015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2397079467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0274963378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4519233703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7112884521484</t>
+    <t xml:space="preserve">40.0607528686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8013954162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2397041320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0275001525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4519157409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7112922668457</t>
   </si>
   <si>
     <t xml:space="preserve">41.499080657959</t>
@@ -752,43 +752,43 @@
     <t xml:space="preserve">42.3243408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1828689575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0885543823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2771835327148</t>
+    <t xml:space="preserve">42.1828727722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0885581970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2771911621094</t>
   </si>
   <si>
     <t xml:space="preserve">41.8291816711426</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9664421081543</t>
+    <t xml:space="preserve">39.966438293457</t>
   </si>
   <si>
     <t xml:space="preserve">39.5891799926758</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4338073730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.999698638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6363296508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9428596496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4380226135254</t>
+    <t xml:space="preserve">38.4338035583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9997024536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6363410949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9428558349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4380187988281</t>
   </si>
   <si>
     <t xml:space="preserve">38.551700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0565452575684</t>
+    <t xml:space="preserve">38.0565414428711</t>
   </si>
   <si>
     <t xml:space="preserve">39.1411781311035</t>
@@ -797,31 +797,31 @@
     <t xml:space="preserve">39.3298110961914</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0704383850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1647529602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6695938110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8346519470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.905387878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0940246582031</t>
+    <t xml:space="preserve">39.0704307556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1647567749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6695899963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8346481323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9053802490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0940208435059</t>
   </si>
   <si>
     <t xml:space="preserve">38.8110694885254</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2687530517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7403335571289</t>
+    <t xml:space="preserve">38.2687492370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7403373718262</t>
   </si>
   <si>
     <t xml:space="preserve">38.6931762695312</t>
@@ -836,19 +836,19 @@
     <t xml:space="preserve">42.1357078552246</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5129814147949</t>
+    <t xml:space="preserve">42.5129776000977</t>
   </si>
   <si>
     <t xml:space="preserve">44.7765617370605</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8001365661621</t>
+    <t xml:space="preserve">44.8001441955566</t>
   </si>
   <si>
     <t xml:space="preserve">45.507511138916</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3188781738281</t>
+    <t xml:space="preserve">45.3188743591309</t>
   </si>
   <si>
     <t xml:space="preserve">45.8140411376953</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">43.7862434387207</t>
   </si>
   <si>
-    <t xml:space="preserve">44.752986907959</t>
+    <t xml:space="preserve">44.7529830932617</t>
   </si>
   <si>
     <t xml:space="preserve">45.1302452087402</t>
@@ -869,37 +869,37 @@
     <t xml:space="preserve">44.4464530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5879325866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.328556060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3049812316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6211929321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1731948852539</t>
+    <t xml:space="preserve">44.5879364013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3285598754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3049774169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6211891174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1731872558594</t>
   </si>
   <si>
     <t xml:space="preserve">43.0788764953613</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5837135314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.267505645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3660316467285</t>
+    <t xml:space="preserve">42.5837173461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2675018310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.366039276123</t>
   </si>
   <si>
     <t xml:space="preserve">44.98876953125</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4936180114746</t>
+    <t xml:space="preserve">44.4936103820801</t>
   </si>
   <si>
     <t xml:space="preserve">44.5171928405762</t>
@@ -908,34 +908,34 @@
     <t xml:space="preserve">45.6254081726074</t>
   </si>
   <si>
-    <t xml:space="preserve">45.861198425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4035148620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.582462310791</t>
+    <t xml:space="preserve">45.8612022399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4035186767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5824661254883</t>
   </si>
   <si>
     <t xml:space="preserve">47.0637321472168</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1344680786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1580467224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9125747680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3508949279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7378349304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.101203918457</t>
+    <t xml:space="preserve">47.134464263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1580429077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9125671386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3508911132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7378387451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1012001037598</t>
   </si>
   <si>
     <t xml:space="preserve">48.8321571350098</t>
@@ -947,22 +947,22 @@
     <t xml:space="preserve">48.0540504455566</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8654174804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9597244262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1858444213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2717208862305</t>
+    <t xml:space="preserve">47.8654136657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9597282409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1858406066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2717247009277</t>
   </si>
   <si>
     <t xml:space="preserve">45.0359306335449</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5643501281738</t>
+    <t xml:space="preserve">44.5643539428711</t>
   </si>
   <si>
     <t xml:space="preserve">43.9748725891113</t>
@@ -971,31 +971,31 @@
     <t xml:space="preserve">42.560131072998</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9138221740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7251892089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2064514160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.432804107666</t>
+    <t xml:space="preserve">42.9138145446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7251815795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2064552307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4328079223633</t>
   </si>
   <si>
     <t xml:space="preserve">42.1781578063965</t>
   </si>
   <si>
-    <t xml:space="preserve">43.3476715087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.980094909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3010177612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0838394165039</t>
+    <t xml:space="preserve">43.3476791381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9800910949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3010139465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0838356018066</t>
   </si>
   <si>
     <t xml:space="preserve">42.7534866333008</t>
@@ -1004,31 +1004,31 @@
     <t xml:space="preserve">42.5931434631348</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4799613952637</t>
+    <t xml:space="preserve">42.4799652099609</t>
   </si>
   <si>
     <t xml:space="preserve">43.0081329345703</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0458602905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3288116455078</t>
+    <t xml:space="preserve">43.0458641052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3288078308105</t>
   </si>
   <si>
     <t xml:space="preserve">41.3953285217285</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4891510009766</t>
+    <t xml:space="preserve">43.489143371582</t>
   </si>
   <si>
     <t xml:space="preserve">44.2342491149902</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1210670471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2439193725586</t>
+    <t xml:space="preserve">44.1210708618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2439270019531</t>
   </si>
   <si>
     <t xml:space="preserve">42.1027030944824</t>
@@ -1037,10 +1037,10 @@
     <t xml:space="preserve">41.1689758300781</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2729721069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4045066833496</t>
+    <t xml:space="preserve">40.2729682922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4045104980469</t>
   </si>
   <si>
     <t xml:space="preserve">43.7626686096191</t>
@@ -1049,25 +1049,25 @@
     <t xml:space="preserve">44.2531089782715</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0547943115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9510498046875</t>
+    <t xml:space="preserve">45.0547904968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9510459899902</t>
   </si>
   <si>
     <t xml:space="preserve">46.2809028625488</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1488609313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3094520568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9982070922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5358047485352</t>
+    <t xml:space="preserve">46.1488571166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.309455871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9981994628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5358085632324</t>
   </si>
   <si>
     <t xml:space="preserve">45.1679725646973</t>
@@ -1076,85 +1076,85 @@
     <t xml:space="preserve">45.5923957824707</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6586685180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2533569335938</t>
+    <t xml:space="preserve">44.6586608886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.253360748291</t>
   </si>
   <si>
     <t xml:space="preserve">43.6683502197266</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2248115539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0830879211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2057075500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3280639648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0356826782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6584167480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5169410705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1682243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8664054870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5457420349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8852729797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4606056213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6112632751465</t>
+    <t xml:space="preserve">44.2248153686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0830917358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2056999206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3280563354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0356864929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6584205627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5169486999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1682281494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8664093017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5457305908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8852691650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4606018066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.611255645752</t>
   </si>
   <si>
     <t xml:space="preserve">45.630126953125</t>
   </si>
   <si>
-    <t xml:space="preserve">45.724437713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2903366088867</t>
+    <t xml:space="preserve">45.7244415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.290340423584</t>
   </si>
   <si>
     <t xml:space="preserve">46.026252746582</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2148818969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6487312316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7053298950195</t>
+    <t xml:space="preserve">46.2148857116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6487350463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.705322265625</t>
   </si>
   <si>
     <t xml:space="preserve">46.5921478271484</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8939628601074</t>
+    <t xml:space="preserve">46.8939590454102</t>
   </si>
   <si>
     <t xml:space="preserve">47.7710990905762</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8182640075684</t>
+    <t xml:space="preserve">47.8182563781738</t>
   </si>
   <si>
     <t xml:space="preserve">48.1955184936523</t>
@@ -1163,10 +1163,10 @@
     <t xml:space="preserve">48.9972076416016</t>
   </si>
   <si>
-    <t xml:space="preserve">48.5727806091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3273124694824</t>
+    <t xml:space="preserve">48.5727844238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3273162841797</t>
   </si>
   <si>
     <t xml:space="preserve">50.3176307678223</t>
@@ -1175,10 +1175,10 @@
     <t xml:space="preserve">50.4119491577148</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8460540771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3744773864746</t>
+    <t xml:space="preserve">49.8460464477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3744659423828</t>
   </si>
   <si>
     <t xml:space="preserve">50.223316192627</t>
@@ -1187,25 +1187,25 @@
     <t xml:space="preserve">50.0818405151367</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5353050231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1960182189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2052040100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0068893432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2523612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4223823547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8376197814941</t>
+    <t xml:space="preserve">47.5353126525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1960220336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2052001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.006893157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2523536682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4223785400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8376159667969</t>
   </si>
   <si>
     <t xml:space="preserve">45.6489906311035</t>
@@ -1217,28 +1217,28 @@
     <t xml:space="preserve">46.5732841491699</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4687919616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8085746765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4789619445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3938331604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5166931152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1774063110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7812767028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8378715515137</t>
+    <t xml:space="preserve">49.4687881469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8085784912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4789657592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3938369750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5166893005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1774139404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7812728881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8378639221191</t>
   </si>
   <si>
     <t xml:space="preserve">44.4983291625977</t>
@@ -1250,13 +1250,13 @@
     <t xml:space="preserve">41.8952026367188</t>
   </si>
   <si>
-    <t xml:space="preserve">42.291332244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4988250732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0652236938477</t>
+    <t xml:space="preserve">42.2913360595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4988288879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0652275085449</t>
   </si>
   <si>
     <t xml:space="preserve">41.9517936706543</t>
@@ -1268,7 +1268,7 @@
     <t xml:space="preserve">45.4414901733398</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4603500366211</t>
+    <t xml:space="preserve">45.4603576660156</t>
   </si>
   <si>
     <t xml:space="preserve">45.4037628173828</t>
@@ -1277,25 +1277,25 @@
     <t xml:space="preserve">46.1017036437988</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9885215759277</t>
+    <t xml:space="preserve">45.988525390625</t>
   </si>
   <si>
     <t xml:space="preserve">46.3846473693848</t>
   </si>
   <si>
-    <t xml:space="preserve">49.044361114502</t>
+    <t xml:space="preserve">49.0443649291992</t>
   </si>
   <si>
     <t xml:space="preserve">48.902889251709</t>
   </si>
   <si>
-    <t xml:space="preserve">48.2898406982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1193199157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6948928833008</t>
+    <t xml:space="preserve">48.2898368835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1193237304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.694896697998</t>
   </si>
   <si>
     <t xml:space="preserve">50.6005821228027</t>
@@ -1307,19 +1307,19 @@
     <t xml:space="preserve">50.4107093811035</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0277900695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.2144813537598</t>
+    <t xml:space="preserve">51.0277938842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.214485168457</t>
   </si>
   <si>
     <t xml:space="preserve">52.1195526123047</t>
   </si>
   <si>
-    <t xml:space="preserve">51.7398109436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8410949707031</t>
+    <t xml:space="preserve">51.7398147583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8410987854004</t>
   </si>
   <si>
     <t xml:space="preserve">51.5024681091309</t>
@@ -1331,7 +1331,7 @@
     <t xml:space="preserve">49.3664207458496</t>
   </si>
   <si>
-    <t xml:space="preserve">49.0816192626953</t>
+    <t xml:space="preserve">49.081615447998</t>
   </si>
   <si>
     <t xml:space="preserve">49.7936325073242</t>
@@ -1340,19 +1340,19 @@
     <t xml:space="preserve">48.2746620178223</t>
   </si>
   <si>
-    <t xml:space="preserve">46.822151184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0848007202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6544036865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3189506530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6512336730957</t>
+    <t xml:space="preserve">46.8221549987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0847930908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6544075012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3189544677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6512298583984</t>
   </si>
   <si>
     <t xml:space="preserve">49.9835014343262</t>
@@ -1361,61 +1361,61 @@
     <t xml:space="preserve">50.3632431030273</t>
   </si>
   <si>
-    <t xml:space="preserve">51.217658996582</t>
+    <t xml:space="preserve">51.2176628112793</t>
   </si>
   <si>
     <t xml:space="preserve">50.1733703613281</t>
   </si>
   <si>
-    <t xml:space="preserve">51.455005645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.0246162414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.068904876709</t>
+    <t xml:space="preserve">51.4550018310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.0246047973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0689086914062</t>
   </si>
   <si>
     <t xml:space="preserve">52.7840919494629</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4422950744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.682804107666</t>
+    <t xml:space="preserve">55.4422912597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6828079223633</t>
   </si>
   <si>
     <t xml:space="preserve">55.1100158691406</t>
   </si>
   <si>
-    <t xml:space="preserve">55.5846862792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3916435241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.7302742004395</t>
+    <t xml:space="preserve">55.5846900939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3916473388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.7302780151367</t>
   </si>
   <si>
     <t xml:space="preserve">55.0625495910645</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4897613525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2524147033691</t>
+    <t xml:space="preserve">55.4897575378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.2524185180664</t>
   </si>
   <si>
     <t xml:space="preserve">53.1638374328613</t>
   </si>
   <si>
-    <t xml:space="preserve">53.6385192871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0182571411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3030700683594</t>
+    <t xml:space="preserve">53.6385154724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0182609558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3030662536621</t>
   </si>
   <si>
     <t xml:space="preserve">54.1131935119629</t>
@@ -1424,64 +1424,64 @@
     <t xml:space="preserve">53.8283882141113</t>
   </si>
   <si>
-    <t xml:space="preserve">54.7777366638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4391098022461</t>
+    <t xml:space="preserve">54.7777404785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4391174316406</t>
   </si>
   <si>
     <t xml:space="preserve">56.9137878417969</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2967071533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.011905670166</t>
+    <t xml:space="preserve">56.2966995239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0119018554688</t>
   </si>
   <si>
     <t xml:space="preserve">56.201774597168</t>
   </si>
   <si>
-    <t xml:space="preserve">56.5340461730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6764526367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9676132202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5942268371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0214309692383</t>
+    <t xml:space="preserve">56.5340423583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6764488220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9676094055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5942306518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0214385986328</t>
   </si>
   <si>
     <t xml:space="preserve">55.1574783325195</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3505325317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9265022277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.8790321350098</t>
+    <t xml:space="preserve">54.3505363464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9264945983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.879035949707</t>
   </si>
   <si>
     <t xml:space="preserve">54.0657234191895</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5878639221191</t>
+    <t xml:space="preserve">54.5878677368164</t>
   </si>
   <si>
     <t xml:space="preserve">53.4486427307129</t>
   </si>
   <si>
-    <t xml:space="preserve">53.6859855651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3062438964844</t>
+    <t xml:space="preserve">53.685977935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3062400817871</t>
   </si>
   <si>
     <t xml:space="preserve">52.404354095459</t>
@@ -1496,88 +1496,88 @@
     <t xml:space="preserve">52.2619476318359</t>
   </si>
   <si>
-    <t xml:space="preserve">51.882209777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1606597900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.208122253418</t>
+    <t xml:space="preserve">51.8822135925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1606559753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.2081260681152</t>
   </si>
   <si>
     <t xml:space="preserve">53.5435791015625</t>
   </si>
   <si>
-    <t xml:space="preserve">54.540397644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.204948425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2492408752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.1036605834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.2460632324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9106063842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.961254119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.790454864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.4138870239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0120239257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0500030517578</t>
+    <t xml:space="preserve">54.5404052734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.2049522399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2492370605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1036643981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.2460594177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9106101989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9612579345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7904510498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.413890838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.012020111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0499954223633</t>
   </si>
   <si>
     <t xml:space="preserve">48.2271919250488</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4677200317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0309677124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3157768249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3474769592285</t>
+    <t xml:space="preserve">47.4677085876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0309715270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3157730102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3474731445312</t>
   </si>
   <si>
     <t xml:space="preserve">44.7525634765625</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6766128540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6956024169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1955795288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5563354492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4803848266602</t>
+    <t xml:space="preserve">44.6766090393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6955986022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1955833435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5563316345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4803810119629</t>
   </si>
   <si>
     <t xml:space="preserve">45.9487457275391</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4107475280762</t>
+    <t xml:space="preserve">47.4107513427734</t>
   </si>
   <si>
     <t xml:space="preserve">46.5373458862305</t>
@@ -1589,37 +1589,37 @@
     <t xml:space="preserve">46.7462043762207</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4424057006836</t>
+    <t xml:space="preserve">46.4424095153809</t>
   </si>
   <si>
     <t xml:space="preserve">45.4930534362793</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1323013305664</t>
+    <t xml:space="preserve">45.1322975158691</t>
   </si>
   <si>
     <t xml:space="preserve">45.5690040588379</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7019081115723</t>
+    <t xml:space="preserve">45.7019119262695</t>
   </si>
   <si>
     <t xml:space="preserve">42.3601875305176</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4677963256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9234848022461</t>
+    <t xml:space="preserve">41.4677925109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9234809875488</t>
   </si>
   <si>
     <t xml:space="preserve">42.8728370666504</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7462425231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2968635559082</t>
+    <t xml:space="preserve">43.7462501525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2968673706055</t>
   </si>
   <si>
     <t xml:space="preserve">43.8601684570312</t>
@@ -1628,37 +1628,37 @@
     <t xml:space="preserve">45.7209014892578</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7841682434082</t>
+    <t xml:space="preserve">46.7841758728027</t>
   </si>
   <si>
     <t xml:space="preserve">47.7050514221191</t>
   </si>
   <si>
-    <t xml:space="preserve">47.239860534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2905082702637</t>
+    <t xml:space="preserve">47.2398643493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2905120849609</t>
   </si>
   <si>
     <t xml:space="preserve">45.1892623901367</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2082443237305</t>
+    <t xml:space="preserve">45.2082557678223</t>
   </si>
   <si>
     <t xml:space="preserve">45.2841987609863</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3158149719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3727836608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6132888793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4867401123047</t>
+    <t xml:space="preserve">47.3158264160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3727798461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6132926940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.486743927002</t>
   </si>
   <si>
     <t xml:space="preserve">43.5373878479004</t>
@@ -1670,25 +1670,25 @@
     <t xml:space="preserve">42.0753784179688</t>
   </si>
   <si>
-    <t xml:space="preserve">41.5627250671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2146492004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.847541809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4551239013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2526206970215</t>
+    <t xml:space="preserve">41.5627288818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2146453857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8475379943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4551200866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2526168823242</t>
   </si>
   <si>
     <t xml:space="preserve">41.8095588684082</t>
   </si>
   <si>
-    <t xml:space="preserve">43.195613861084</t>
+    <t xml:space="preserve">43.1956176757812</t>
   </si>
   <si>
     <t xml:space="preserve">44.0310516357422</t>
@@ -1697,10 +1697,10 @@
     <t xml:space="preserve">44.3158569335938</t>
   </si>
   <si>
-    <t xml:space="preserve">44.3348388671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8791542053223</t>
+    <t xml:space="preserve">44.3348426818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8791580200195</t>
   </si>
   <si>
     <t xml:space="preserve">45.7398872375488</t>
@@ -1709,16 +1709,16 @@
     <t xml:space="preserve">45.8348236083984</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8031616210938</t>
+    <t xml:space="preserve">46.803165435791</t>
   </si>
   <si>
     <t xml:space="preserve">46.3854522705078</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4234237670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1829071044922</t>
+    <t xml:space="preserve">46.4234275817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1829109191895</t>
   </si>
   <si>
     <t xml:space="preserve">49.1765480041504</t>
@@ -1730,25 +1730,25 @@
     <t xml:space="preserve">45.4360961914062</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0753402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6449546813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2588539123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4645385742188</t>
+    <t xml:space="preserve">45.0753364562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6449584960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2588500976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4645347595215</t>
   </si>
   <si>
     <t xml:space="preserve">49.8885650634766</t>
   </si>
   <si>
-    <t xml:space="preserve">50.1259002685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6955223083496</t>
+    <t xml:space="preserve">50.125904083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6955184936523</t>
   </si>
   <si>
     <t xml:space="preserve">50.2208404541016</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">49.9360313415527</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0784339904785</t>
+    <t xml:space="preserve">50.0784378051758</t>
   </si>
   <si>
     <t xml:space="preserve">52.1670150756836</t>
@@ -1766,10 +1766,10 @@
     <t xml:space="preserve">52.6891632080078</t>
   </si>
   <si>
-    <t xml:space="preserve">52.9739646911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.2555999755859</t>
+    <t xml:space="preserve">52.9739608764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.2555961608887</t>
   </si>
   <si>
     <t xml:space="preserve">53.2587776184082</t>
@@ -1778,40 +1778,40 @@
     <t xml:space="preserve">53.9707908630371</t>
   </si>
   <si>
-    <t xml:space="preserve">53.7334480285645</t>
+    <t xml:space="preserve">53.7334518432617</t>
   </si>
   <si>
     <t xml:space="preserve">55.2998886108398</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3980026245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4011726379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.9233207702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4929351806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4454689025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4961090087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.6353378295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.9644317626953</t>
+    <t xml:space="preserve">54.3979949951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4011764526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9233169555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4929389953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4454650878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4961128234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6353302001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.9644393920898</t>
   </si>
   <si>
     <t xml:space="preserve">55.7270965576172</t>
   </si>
   <si>
-    <t xml:space="preserve">56.1068344116211</t>
+    <t xml:space="preserve">56.1068305969238</t>
   </si>
   <si>
     <t xml:space="preserve">55.5328521728516</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">53.5239143371582</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5717506408691</t>
+    <t xml:space="preserve">53.5717391967773</t>
   </si>
   <si>
     <t xml:space="preserve">52.615104675293</t>
@@ -1832,106 +1832,106 @@
     <t xml:space="preserve">51.4671363830566</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5283851623535</t>
+    <t xml:space="preserve">54.5283889770508</t>
   </si>
   <si>
     <t xml:space="preserve">55.9633445739746</t>
   </si>
   <si>
-    <t xml:space="preserve">56.0590057373047</t>
+    <t xml:space="preserve">56.0589981079102</t>
   </si>
   <si>
     <t xml:space="preserve">55.1980285644531</t>
   </si>
   <si>
-    <t xml:space="preserve">56.7764778137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0111694335938</t>
+    <t xml:space="preserve">56.776481628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.011173248291</t>
   </si>
   <si>
     <t xml:space="preserve">55.6285171508789</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2024993896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.9155044555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4416580200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.580680847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3459930419922</t>
+    <t xml:space="preserve">56.2024955749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.9155120849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4416542053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5806884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3459968566895</t>
   </si>
   <si>
     <t xml:space="preserve">55.1501960754395</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5762176513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4327201843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8632049560547</t>
+    <t xml:space="preserve">54.5762138366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4327239990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.863208770752</t>
   </si>
   <si>
     <t xml:space="preserve">56.9199829101562</t>
   </si>
   <si>
-    <t xml:space="preserve">56.8243179321289</t>
+    <t xml:space="preserve">56.8243141174316</t>
   </si>
   <si>
     <t xml:space="preserve">57.2547988891602</t>
   </si>
   <si>
-    <t xml:space="preserve">56.6808204650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.7286529541016</t>
+    <t xml:space="preserve">56.6808166503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.728645324707</t>
   </si>
   <si>
     <t xml:space="preserve">58.2114410400391</t>
   </si>
   <si>
-    <t xml:space="preserve">57.637451171875</t>
+    <t xml:space="preserve">57.6374549865723</t>
   </si>
   <si>
     <t xml:space="preserve">58.5462646484375</t>
   </si>
   <si>
-    <t xml:space="preserve">57.9244499206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.3549308776855</t>
+    <t xml:space="preserve">57.924446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.3549346923828</t>
   </si>
   <si>
     <t xml:space="preserve">57.7331161499023</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3504638671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.3071098327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.2682113647461</t>
+    <t xml:space="preserve">57.3504600524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.3071060180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.2682151794434</t>
   </si>
   <si>
     <t xml:space="preserve">60.172550201416</t>
   </si>
   <si>
-    <t xml:space="preserve">59.742057800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.2159118652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.1202430725098</t>
+    <t xml:space="preserve">59.7420616149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.2159156799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.120246887207</t>
   </si>
   <si>
     <t xml:space="preserve">57.3026313781738</t>
@@ -1940,55 +1940,55 @@
     <t xml:space="preserve">57.828784942627</t>
   </si>
   <si>
-    <t xml:space="preserve">58.1157760620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.7809562683105</t>
+    <t xml:space="preserve">58.115779876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.7809524536133</t>
   </si>
   <si>
     <t xml:space="preserve">59.0245819091797</t>
   </si>
   <si>
-    <t xml:space="preserve">59.4550704956055</t>
+    <t xml:space="preserve">59.4550743103027</t>
   </si>
   <si>
     <t xml:space="preserve">60.3160438537598</t>
   </si>
   <si>
-    <t xml:space="preserve">60.029052734375</t>
+    <t xml:space="preserve">60.0290489196777</t>
   </si>
   <si>
     <t xml:space="preserve">59.0724143981934</t>
   </si>
   <si>
-    <t xml:space="preserve">58.2592697143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0201110839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9888229370117</t>
+    <t xml:space="preserve">58.2592735290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0201148986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9888153076172</t>
   </si>
   <si>
     <t xml:space="preserve">50.4148368835449</t>
   </si>
   <si>
-    <t xml:space="preserve">51.2279815673828</t>
+    <t xml:space="preserve">51.2279853820801</t>
   </si>
   <si>
     <t xml:space="preserve">51.3236465454102</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8931617736816</t>
+    <t xml:space="preserve">50.8931541442871</t>
   </si>
   <si>
     <t xml:space="preserve">49.7930221557617</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8408546447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6928901672363</t>
+    <t xml:space="preserve">49.8408508300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6928939819336</t>
   </si>
   <si>
     <t xml:space="preserve">49.2668724060059</t>
@@ -2000,16 +2000,16 @@
     <t xml:space="preserve">49.9365196228027</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0800094604492</t>
+    <t xml:space="preserve">50.0800132751465</t>
   </si>
   <si>
     <t xml:space="preserve">50.6539993286133</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2235145568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8453254699707</t>
+    <t xml:space="preserve">50.2235107421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.845329284668</t>
   </si>
   <si>
     <t xml:space="preserve">51.4193077087402</t>
@@ -2021,22 +2021,22 @@
     <t xml:space="preserve">51.514965057373</t>
   </si>
   <si>
-    <t xml:space="preserve">50.7974891662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1323204040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6973609924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3147010803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.458194732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.745189666748</t>
+    <t xml:space="preserve">50.7974967956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1323165893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6973571777344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3147048950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.4581985473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7451934814453</t>
   </si>
   <si>
     <t xml:space="preserve">50.0321846008301</t>
@@ -2045,7 +2045,7 @@
     <t xml:space="preserve">48.8363838195801</t>
   </si>
   <si>
-    <t xml:space="preserve">48.5972213745117</t>
+    <t xml:space="preserve">48.597225189209</t>
   </si>
   <si>
     <t xml:space="preserve">49.3625335693359</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">54.0022315979004</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4282455444336</t>
+    <t xml:space="preserve">53.4282493591309</t>
   </si>
   <si>
     <t xml:space="preserve">54.2892227172852</t>
@@ -2063,25 +2063,25 @@
     <t xml:space="preserve">54.1935577392578</t>
   </si>
   <si>
-    <t xml:space="preserve">53.0934257507324</t>
+    <t xml:space="preserve">53.0934219360352</t>
   </si>
   <si>
     <t xml:space="preserve">52.4716110229492</t>
   </si>
   <si>
-    <t xml:space="preserve">53.2847518920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0978965759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9110374450684</t>
+    <t xml:space="preserve">53.2847557067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0978927612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9110336303711</t>
   </si>
   <si>
     <t xml:space="preserve">54.3370552062988</t>
   </si>
   <si>
-    <t xml:space="preserve">53.8587341308594</t>
+    <t xml:space="preserve">53.8587303161621</t>
   </si>
   <si>
     <t xml:space="preserve">54.4805526733398</t>
@@ -2093,31 +2093,31 @@
     <t xml:space="preserve">55.3415222167969</t>
   </si>
   <si>
-    <t xml:space="preserve">55.8676795959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5373191833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.632984161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.4027709960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.067943572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6942329406738</t>
+    <t xml:space="preserve">55.8676834106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5373229980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6329917907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.4027671813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0679473876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6942291259766</t>
   </si>
   <si>
     <t xml:space="preserve">59.3115730285645</t>
   </si>
   <si>
-    <t xml:space="preserve">62.851131439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6164398193359</t>
+    <t xml:space="preserve">62.8511352539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6164436340332</t>
   </si>
   <si>
     <t xml:space="preserve">65.3383941650391</t>
@@ -2132,7 +2132,7 @@
     <t xml:space="preserve">67.9213256835938</t>
   </si>
   <si>
-    <t xml:space="preserve">69.260612487793</t>
+    <t xml:space="preserve">69.2606201171875</t>
   </si>
   <si>
     <t xml:space="preserve">69.0692749023438</t>
@@ -2141,7 +2141,7 @@
     <t xml:space="preserve">67.3951644897461</t>
   </si>
   <si>
-    <t xml:space="preserve">68.0169830322266</t>
+    <t xml:space="preserve">68.0169906616211</t>
   </si>
   <si>
     <t xml:space="preserve">66.8690185546875</t>
@@ -2159,13 +2159,13 @@
     <t xml:space="preserve">69.212776184082</t>
   </si>
   <si>
-    <t xml:space="preserve">68.4474792480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.8734817504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.7778167724609</t>
+    <t xml:space="preserve">68.4474639892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.8734893798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.7778244018555</t>
   </si>
   <si>
     <t xml:space="preserve">67.0603408813477</t>
@@ -2180,7 +2180,7 @@
     <t xml:space="preserve">65.5775604248047</t>
   </si>
   <si>
-    <t xml:space="preserve">65.9123840332031</t>
+    <t xml:space="preserve">65.9123764038086</t>
   </si>
   <si>
     <t xml:space="preserve">67.2516784667969</t>
@@ -2192,115 +2192,115 @@
     <t xml:space="preserve">67.6343231201172</t>
   </si>
   <si>
-    <t xml:space="preserve">65.7688827514648</t>
+    <t xml:space="preserve">65.7688903808594</t>
   </si>
   <si>
     <t xml:space="preserve">66.1036987304688</t>
   </si>
   <si>
-    <t xml:space="preserve">69.4519348144531</t>
+    <t xml:space="preserve">69.4519424438477</t>
   </si>
   <si>
     <t xml:space="preserve">68.2083129882812</t>
   </si>
   <si>
-    <t xml:space="preserve">70.3129119873047</t>
+    <t xml:space="preserve">70.3129272460938</t>
   </si>
   <si>
     <t xml:space="preserve">73.3263244628906</t>
   </si>
   <si>
-    <t xml:space="preserve">73.2306671142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.0916290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.6611557006836</t>
+    <t xml:space="preserve">73.2306594848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.0916366577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.6611404418945</t>
   </si>
   <si>
     <t xml:space="preserve">73.3741455078125</t>
   </si>
   <si>
-    <t xml:space="preserve">70.6955718994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.7912216186523</t>
+    <t xml:space="preserve">70.6955642700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.7912292480469</t>
   </si>
   <si>
     <t xml:space="preserve">72.4653549194336</t>
   </si>
   <si>
-    <t xml:space="preserve">70.2650833129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.638786315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3173904418945</t>
+    <t xml:space="preserve">70.2650756835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.638801574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3173828125</t>
   </si>
   <si>
     <t xml:space="preserve">71.9391937255859</t>
   </si>
   <si>
-    <t xml:space="preserve">72.7045135498047</t>
+    <t xml:space="preserve">72.7045059204102</t>
   </si>
   <si>
     <t xml:space="preserve">72.7523498535156</t>
   </si>
   <si>
-    <t xml:space="preserve">72.6088562011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.4264602661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.1394729614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7478790283203</t>
+    <t xml:space="preserve">72.6088485717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.4264678955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.1394653320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7478713989258</t>
   </si>
   <si>
     <t xml:space="preserve">71.9870376586914</t>
   </si>
   <si>
-    <t xml:space="preserve">73.2784881591797</t>
+    <t xml:space="preserve">73.2784957885742</t>
   </si>
   <si>
     <t xml:space="preserve">71.4130477905273</t>
   </si>
   <si>
-    <t xml:space="preserve">66.821174621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.7210540771484</t>
+    <t xml:space="preserve">66.8211898803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.7210464477539</t>
   </si>
   <si>
     <t xml:space="preserve">62.1336517333984</t>
   </si>
   <si>
-    <t xml:space="preserve">63.8077659606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8944931030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9378547668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.8766174316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5672760009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.0889587402344</t>
+    <t xml:space="preserve">63.8077697753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8944892883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.937858581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.8766136169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.567268371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.0889549255371</t>
   </si>
   <si>
     <t xml:space="preserve">46.3778228759766</t>
   </si>
   <si>
-    <t xml:space="preserve">48.7407264709473</t>
+    <t xml:space="preserve">48.74072265625</t>
   </si>
   <si>
     <t xml:space="preserve">45.4594497680664</t>
@@ -2327,13 +2327,13 @@
     <t xml:space="preserve">49.2190399169922</t>
   </si>
   <si>
-    <t xml:space="preserve">59.168083190918</t>
+    <t xml:space="preserve">59.1680793762207</t>
   </si>
   <si>
     <t xml:space="preserve">57.6852912902832</t>
   </si>
   <si>
-    <t xml:space="preserve">59.263744354248</t>
+    <t xml:space="preserve">59.2637481689453</t>
   </si>
   <si>
     <t xml:space="preserve">61.081356048584</t>
@@ -2345,40 +2345,40 @@
     <t xml:space="preserve">61.1291847229004</t>
   </si>
   <si>
-    <t xml:space="preserve">61.4161796569824</t>
+    <t xml:space="preserve">61.4161758422852</t>
   </si>
   <si>
     <t xml:space="preserve">62.6598052978516</t>
   </si>
   <si>
-    <t xml:space="preserve">63.5207901000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5641479492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.138126373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0424652099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9901580810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.033519744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.2684898376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9081420898438</t>
+    <t xml:space="preserve">63.5207862854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5641403198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.1381225585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0424728393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.990161895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0335235595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.2684860229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9081382751465</t>
   </si>
   <si>
     <t xml:space="preserve">61.7279586791992</t>
   </si>
   <si>
-    <t xml:space="preserve">63.7051963806152</t>
+    <t xml:space="preserve">63.705192565918</t>
   </si>
   <si>
     <t xml:space="preserve">64.7179107666016</t>
@@ -2387,7 +2387,7 @@
     <t xml:space="preserve">63.3676109313965</t>
   </si>
   <si>
-    <t xml:space="preserve">63.6569595336914</t>
+    <t xml:space="preserve">63.6569557189941</t>
   </si>
   <si>
     <t xml:space="preserve">64.0909805297852</t>
@@ -2399,13 +2399,13 @@
     <t xml:space="preserve">64.9108123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">68.4312286376953</t>
+    <t xml:space="preserve">68.4312362670898</t>
   </si>
   <si>
     <t xml:space="preserve">68.0936508178711</t>
   </si>
   <si>
-    <t xml:space="preserve">68.3830184936523</t>
+    <t xml:space="preserve">68.3830108642578</t>
   </si>
   <si>
     <t xml:space="preserve">68.624137878418</t>
@@ -2414,7 +2414,7 @@
     <t xml:space="preserve">69.9744415283203</t>
   </si>
   <si>
-    <t xml:space="preserve">73.3983993530273</t>
+    <t xml:space="preserve">73.3983917236328</t>
   </si>
   <si>
     <t xml:space="preserve">74.1217727661133</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">73.9288787841797</t>
   </si>
   <si>
-    <t xml:space="preserve">74.3628921508789</t>
+    <t xml:space="preserve">74.3628997802734</t>
   </si>
   <si>
     <t xml:space="preserve">75.8578720092773</t>
@@ -2453,43 +2453,43 @@
     <t xml:space="preserve">67.2256088256836</t>
   </si>
   <si>
-    <t xml:space="preserve">64.8625793457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.5504531860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.3220672607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.9262008666992</t>
+    <t xml:space="preserve">64.8625869750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.5504608154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.3220520019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.9262084960938</t>
   </si>
   <si>
     <t xml:space="preserve">71.1800537109375</t>
   </si>
   <si>
-    <t xml:space="preserve">70.4084548950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3729476928711</t>
+    <t xml:space="preserve">70.408447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3729553222656</t>
   </si>
   <si>
     <t xml:space="preserve">69.4921875</t>
   </si>
   <si>
-    <t xml:space="preserve">70.3120193481445</t>
+    <t xml:space="preserve">70.3120040893555</t>
   </si>
   <si>
     <t xml:space="preserve">68.5276870727539</t>
   </si>
   <si>
-    <t xml:space="preserve">68.2865676879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.6723556518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.0099411010742</t>
+    <t xml:space="preserve">68.2865600585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.67236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.0099258422852</t>
   </si>
   <si>
     <t xml:space="preserve">69.2992782592773</t>
@@ -2498,25 +2498,25 @@
     <t xml:space="preserve">72.1445541381836</t>
   </si>
   <si>
-    <t xml:space="preserve">71.2765045166016</t>
+    <t xml:space="preserve">71.276496887207</t>
   </si>
   <si>
     <t xml:space="preserve">71.8069763183594</t>
   </si>
   <si>
-    <t xml:space="preserve">70.1673278808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.5531387329102</t>
+    <t xml:space="preserve">70.1673355102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.5531311035156</t>
   </si>
   <si>
     <t xml:space="preserve">70.3602294921875</t>
   </si>
   <si>
-    <t xml:space="preserve">71.6623077392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.3374633789062</t>
+    <t xml:space="preserve">71.6623153686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.3374557495117</t>
   </si>
   <si>
     <t xml:space="preserve">72.8679351806641</t>
@@ -2528,7 +2528,7 @@
     <t xml:space="preserve">73.5430755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">71.999885559082</t>
+    <t xml:space="preserve">71.9998779296875</t>
   </si>
   <si>
     <t xml:space="preserve">73.0608367919922</t>
@@ -2537,31 +2537,31 @@
     <t xml:space="preserve">73.6877517700195</t>
   </si>
   <si>
-    <t xml:space="preserve">73.59130859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.9643936157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.7487106323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.934211730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.9469451904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1170654296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.0815658569336</t>
+    <t xml:space="preserve">73.5913009643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.9643783569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.7487030029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9342269897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.9469375610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.117073059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.0815734863281</t>
   </si>
   <si>
     <t xml:space="preserve">85.3581924438477</t>
   </si>
   <si>
-    <t xml:space="preserve">83.1398391723633</t>
+    <t xml:space="preserve">83.1398468017578</t>
   </si>
   <si>
     <t xml:space="preserve">81.017951965332</t>
@@ -2573,13 +2573,13 @@
     <t xml:space="preserve">82.609375</t>
   </si>
   <si>
-    <t xml:space="preserve">80.8732681274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.0916290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3099746704102</t>
+    <t xml:space="preserve">80.8732757568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.0916213989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3099594116211</t>
   </si>
   <si>
     <t xml:space="preserve">84.5865936279297</t>
@@ -2591,13 +2591,13 @@
     <t xml:space="preserve">83.6703186035156</t>
   </si>
   <si>
-    <t xml:space="preserve">84.7795028686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.6830520629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.3836364746094</t>
+    <t xml:space="preserve">84.7794952392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.6830596923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.3836441040039</t>
   </si>
   <si>
     <t xml:space="preserve">86.2262496948242</t>
@@ -2606,13 +2606,13 @@
     <t xml:space="preserve">87.7212142944336</t>
   </si>
   <si>
-    <t xml:space="preserve">89.6984329223633</t>
+    <t xml:space="preserve">89.6984405517578</t>
   </si>
   <si>
     <t xml:space="preserve">89.3126449584961</t>
   </si>
   <si>
-    <t xml:space="preserve">90.6629333496094</t>
+    <t xml:space="preserve">90.6629486083984</t>
   </si>
   <si>
     <t xml:space="preserve">88.1070175170898</t>
@@ -2624,28 +2624,28 @@
     <t xml:space="preserve">91.2416458129883</t>
   </si>
   <si>
-    <t xml:space="preserve">90.2771453857422</t>
+    <t xml:space="preserve">90.2771301269531</t>
   </si>
   <si>
     <t xml:space="preserve">90.5664901733398</t>
   </si>
   <si>
-    <t xml:space="preserve">90.8076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9777374267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.0031967163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.90673828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.2188568115234</t>
+    <t xml:space="preserve">90.8076248168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9777450561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.0031890869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9067459106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7265701293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.2188720703125</t>
   </si>
   <si>
     <t xml:space="preserve">93.5082244873047</t>
@@ -2654,7 +2654,7 @@
     <t xml:space="preserve">91.4827728271484</t>
   </si>
   <si>
-    <t xml:space="preserve">89.9395599365234</t>
+    <t xml:space="preserve">89.939567565918</t>
   </si>
   <si>
     <t xml:space="preserve">91.62744140625</t>
@@ -2666,13 +2666,13 @@
     <t xml:space="preserve">93.3635482788086</t>
   </si>
   <si>
-    <t xml:space="preserve">95.5336761474609</t>
+    <t xml:space="preserve">95.5336685180664</t>
   </si>
   <si>
     <t xml:space="preserve">94.9549560546875</t>
   </si>
   <si>
-    <t xml:space="preserve">94.8102951049805</t>
+    <t xml:space="preserve">94.8102874755859</t>
   </si>
   <si>
     <t xml:space="preserve">93.6046752929688</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">93.0259628295898</t>
   </si>
   <si>
-    <t xml:space="preserve">95.2925491333008</t>
+    <t xml:space="preserve">95.2925415039062</t>
   </si>
   <si>
     <t xml:space="preserve">97.2215423583984</t>
@@ -2702,10 +2702,10 @@
     <t xml:space="preserve">99.7292327880859</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6073379516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.8966827392578</t>
+    <t xml:space="preserve">97.6073303222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.8966903686523</t>
   </si>
   <si>
     <t xml:space="preserve">98.3789367675781</t>
@@ -2720,28 +2720,28 @@
     <t xml:space="preserve">92.8330612182617</t>
   </si>
   <si>
-    <t xml:space="preserve">92.8813018798828</t>
+    <t xml:space="preserve">92.8812942504883</t>
   </si>
   <si>
     <t xml:space="preserve">88.4445877075195</t>
   </si>
   <si>
-    <t xml:space="preserve">88.2034606933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.0233001708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.1324615478516</t>
+    <t xml:space="preserve">88.2034683227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.0232925415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.132453918457</t>
   </si>
   <si>
     <t xml:space="preserve">92.2061386108398</t>
   </si>
   <si>
-    <t xml:space="preserve">96.4499359130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4372177124023</t>
+    <t xml:space="preserve">96.4499435424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4372100830078</t>
   </si>
   <si>
     <t xml:space="preserve">95.7747955322266</t>
@@ -2756,19 +2756,19 @@
     <t xml:space="preserve">91.8685684204102</t>
   </si>
   <si>
-    <t xml:space="preserve">91.8203506469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7111740112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.855842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3863220214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.759391784668</t>
+    <t xml:space="preserve">91.8203430175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7111663818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8558349609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3863296508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7593994140625</t>
   </si>
   <si>
     <t xml:space="preserve">87.7694473266602</t>
@@ -2777,19 +2777,19 @@
     <t xml:space="preserve">88.2516937255859</t>
   </si>
   <si>
-    <t xml:space="preserve">89.3608703613281</t>
+    <t xml:space="preserve">89.3608779907227</t>
   </si>
   <si>
     <t xml:space="preserve">90.3735885620117</t>
   </si>
   <si>
-    <t xml:space="preserve">94.2798156738281</t>
+    <t xml:space="preserve">94.2798233032227</t>
   </si>
   <si>
     <t xml:space="preserve">90.0842437744141</t>
   </si>
   <si>
-    <t xml:space="preserve">91.1451950073242</t>
+    <t xml:space="preserve">91.1451873779297</t>
   </si>
   <si>
     <t xml:space="preserve">92.495491027832</t>
@@ -2798,16 +2798,16 @@
     <t xml:space="preserve">89.4573211669922</t>
   </si>
   <si>
-    <t xml:space="preserve">91.6756744384766</t>
+    <t xml:space="preserve">91.675666809082</t>
   </si>
   <si>
     <t xml:space="preserve">91.9168014526367</t>
   </si>
   <si>
-    <t xml:space="preserve">91.7238845825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.0969619750977</t>
+    <t xml:space="preserve">91.7238922119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.0969696044922</t>
   </si>
   <si>
     <t xml:space="preserve">90.9040679931641</t>
@@ -2816,22 +2816,22 @@
     <t xml:space="preserve">92.3508148193359</t>
   </si>
   <si>
-    <t xml:space="preserve">93.4599838256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.5437164306641</t>
+    <t xml:space="preserve">93.4599914550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.5437088012695</t>
   </si>
   <si>
     <t xml:space="preserve">95.9194641113281</t>
   </si>
   <si>
-    <t xml:space="preserve">93.26708984375</t>
+    <t xml:space="preserve">93.2670822143555</t>
   </si>
   <si>
     <t xml:space="preserve">93.5564422607422</t>
   </si>
   <si>
-    <t xml:space="preserve">94.5691757202148</t>
+    <t xml:space="preserve">94.5691680908203</t>
   </si>
   <si>
     <t xml:space="preserve">96.0641403198242</t>
@@ -2840,10 +2840,10 @@
     <t xml:space="preserve">98.4753875732422</t>
   </si>
   <si>
-    <t xml:space="preserve">100.018592834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.1860427856445</t>
+    <t xml:space="preserve">100.018585205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.1860504150391</t>
   </si>
   <si>
     <t xml:space="preserve">97.414436340332</t>
@@ -2855,13 +2855,13 @@
     <t xml:space="preserve">102.912078857422</t>
   </si>
   <si>
-    <t xml:space="preserve">101.465324401855</t>
+    <t xml:space="preserve">101.46533203125</t>
   </si>
   <si>
     <t xml:space="preserve">102.719184875488</t>
   </si>
   <si>
-    <t xml:space="preserve">102.526290893555</t>
+    <t xml:space="preserve">102.526298522949</t>
   </si>
   <si>
     <t xml:space="preserve">102.140487670898</t>
@@ -2870,22 +2870,22 @@
     <t xml:space="preserve">104.937530517578</t>
   </si>
   <si>
-    <t xml:space="preserve">103.104995727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.587242126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.815635681152</t>
+    <t xml:space="preserve">103.104988098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.58723449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.815628051758</t>
   </si>
   <si>
     <t xml:space="preserve">103.201438903809</t>
   </si>
   <si>
-    <t xml:space="preserve">100.500839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.40438079834</t>
+    <t xml:space="preserve">100.500831604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.404388427734</t>
   </si>
   <si>
     <t xml:space="preserve">98.5718383789062</t>
@@ -2897,13 +2897,13 @@
     <t xml:space="preserve">94.1351470947266</t>
   </si>
   <si>
-    <t xml:space="preserve">92.5919342041016</t>
+    <t xml:space="preserve">92.5919418334961</t>
   </si>
   <si>
     <t xml:space="preserve">89.216194152832</t>
   </si>
   <si>
-    <t xml:space="preserve">103.297889709473</t>
+    <t xml:space="preserve">103.297897338867</t>
   </si>
   <si>
     <t xml:space="preserve">99.3434371948242</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">101.561790466309</t>
   </si>
   <si>
-    <t xml:space="preserve">103.973030090332</t>
+    <t xml:space="preserve">103.973037719727</t>
   </si>
   <si>
     <t xml:space="preserve">103.780128479004</t>
@@ -2924,10 +2924,10 @@
     <t xml:space="preserve">103.490791320801</t>
   </si>
   <si>
-    <t xml:space="preserve">104.069480895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.023941040039</t>
+    <t xml:space="preserve">104.069488525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.02392578125</t>
   </si>
   <si>
     <t xml:space="preserve">110.145820617676</t>
@@ -2936,7 +2936,7 @@
     <t xml:space="preserve">108.699073791504</t>
   </si>
   <si>
-    <t xml:space="preserve">106.28783416748</t>
+    <t xml:space="preserve">106.287826538086</t>
   </si>
   <si>
     <t xml:space="preserve">107.445236206055</t>
@@ -2951,22 +2951,22 @@
     <t xml:space="preserve">107.831039428711</t>
   </si>
   <si>
-    <t xml:space="preserve">108.795532226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.084884643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.059432983398</t>
+    <t xml:space="preserve">108.795539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.08487701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.059425354004</t>
   </si>
   <si>
     <t xml:space="preserve">107.348785400391</t>
   </si>
   <si>
-    <t xml:space="preserve">109.567138671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.506187438965</t>
+    <t xml:space="preserve">109.56713104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.50617980957</t>
   </si>
   <si>
     <t xml:space="preserve">109.530754089355</t>
@@ -2978,16 +2978,16 @@
     <t xml:space="preserve">108.755317687988</t>
   </si>
   <si>
-    <t xml:space="preserve">109.046112060547</t>
+    <t xml:space="preserve">109.046104431152</t>
   </si>
   <si>
     <t xml:space="preserve">109.918479919434</t>
   </si>
   <si>
-    <t xml:space="preserve">110.500061035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.821548461914</t>
+    <t xml:space="preserve">110.500068664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.82154083252</t>
   </si>
   <si>
     <t xml:space="preserve">110.88777923584</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">111.663208007812</t>
   </si>
   <si>
-    <t xml:space="preserve">113.117172241211</t>
+    <t xml:space="preserve">113.117164611816</t>
   </si>
   <si>
     <t xml:space="preserve">115.831199645996</t>
@@ -3005,7 +3005,7 @@
     <t xml:space="preserve">113.795669555664</t>
   </si>
   <si>
-    <t xml:space="preserve">114.76496887207</t>
+    <t xml:space="preserve">114.764976501465</t>
   </si>
   <si>
     <t xml:space="preserve">114.668045043945</t>
@@ -3017,13 +3017,13 @@
     <t xml:space="preserve">114.474182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">116.509704589844</t>
+    <t xml:space="preserve">116.509696960449</t>
   </si>
   <si>
     <t xml:space="preserve">121.453140258789</t>
   </si>
   <si>
-    <t xml:space="preserve">126.590423583984</t>
+    <t xml:space="preserve">126.59041595459</t>
   </si>
   <si>
     <t xml:space="preserve">128.819793701172</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">130.273742675781</t>
   </si>
   <si>
-    <t xml:space="preserve">128.916717529297</t>
+    <t xml:space="preserve">128.916732788086</t>
   </si>
   <si>
     <t xml:space="preserve">134.635589599609</t>
@@ -3065,10 +3065,10 @@
     <t xml:space="preserve">135.798767089844</t>
   </si>
   <si>
-    <t xml:space="preserve">135.314117431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.574188232422</t>
+    <t xml:space="preserve">135.314102172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.574203491211</t>
   </si>
   <si>
     <t xml:space="preserve">132.212356567383</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">135.023315429688</t>
   </si>
   <si>
-    <t xml:space="preserve">133.763214111328</t>
+    <t xml:space="preserve">133.763229370117</t>
   </si>
   <si>
     <t xml:space="preserve">137.446578979492</t>
@@ -3095,25 +3095,25 @@
     <t xml:space="preserve">142.293075561523</t>
   </si>
   <si>
-    <t xml:space="preserve">141.032958984375</t>
+    <t xml:space="preserve">141.032974243164</t>
   </si>
   <si>
     <t xml:space="preserve">143.359268188477</t>
   </si>
   <si>
-    <t xml:space="preserve">140.063659667969</t>
+    <t xml:space="preserve">140.063674926758</t>
   </si>
   <si>
     <t xml:space="preserve">138.803573608398</t>
   </si>
   <si>
-    <t xml:space="preserve">140.548309326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.160614013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.579010009766</t>
+    <t xml:space="preserve">140.548324584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.160598754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.579025268555</t>
   </si>
   <si>
     <t xml:space="preserve">136.671127319336</t>
@@ -3128,22 +3128,22 @@
     <t xml:space="preserve">137.640426635742</t>
   </si>
   <si>
-    <t xml:space="preserve">139.094345092773</t>
+    <t xml:space="preserve">139.094360351562</t>
   </si>
   <si>
     <t xml:space="preserve">141.226821899414</t>
   </si>
   <si>
-    <t xml:space="preserve">142.583847045898</t>
+    <t xml:space="preserve">142.583862304688</t>
   </si>
   <si>
     <t xml:space="preserve">141.905334472656</t>
   </si>
   <si>
-    <t xml:space="preserve">143.262359619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142.486907958984</t>
+    <t xml:space="preserve">143.262344360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142.486923217773</t>
   </si>
   <si>
     <t xml:space="preserve">146.073303222656</t>
@@ -3152,7 +3152,7 @@
     <t xml:space="preserve">148.884292602539</t>
   </si>
   <si>
-    <t xml:space="preserve">148.011901855469</t>
+    <t xml:space="preserve">148.011917114258</t>
   </si>
   <si>
     <t xml:space="preserve">149.175079345703</t>
@@ -3161,22 +3161,22 @@
     <t xml:space="preserve">149.75666809082</t>
   </si>
   <si>
-    <t xml:space="preserve">146.364120483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.236480712891</t>
+    <t xml:space="preserve">146.364105224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.236465454102</t>
   </si>
   <si>
     <t xml:space="preserve">148.205764770508</t>
   </si>
   <si>
-    <t xml:space="preserve">147.818054199219</t>
+    <t xml:space="preserve">147.81803894043</t>
   </si>
   <si>
     <t xml:space="preserve">150.532104492188</t>
   </si>
   <si>
-    <t xml:space="preserve">150.629013061523</t>
+    <t xml:space="preserve">150.629028320312</t>
   </si>
   <si>
     <t xml:space="preserve">155.087799072266</t>
@@ -3191,22 +3191,22 @@
     <t xml:space="preserve">157.89875793457</t>
   </si>
   <si>
-    <t xml:space="preserve">161.679016113281</t>
+    <t xml:space="preserve">161.67903137207</t>
   </si>
   <si>
     <t xml:space="preserve">166.816314697266</t>
   </si>
   <si>
-    <t xml:space="preserve">166.428588867188</t>
+    <t xml:space="preserve">166.428573608398</t>
   </si>
   <si>
     <t xml:space="preserve">165.847030639648</t>
   </si>
   <si>
-    <t xml:space="preserve">165.45930480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.653137207031</t>
+    <t xml:space="preserve">165.459289550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.65315246582</t>
   </si>
   <si>
     <t xml:space="preserve">167.397888183594</t>
@@ -3215,25 +3215,25 @@
     <t xml:space="preserve">168.851852416992</t>
   </si>
   <si>
-    <t xml:space="preserve">169.142623901367</t>
+    <t xml:space="preserve">169.142639160156</t>
   </si>
   <si>
     <t xml:space="preserve">169.627288818359</t>
   </si>
   <si>
-    <t xml:space="preserve">170.305801391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.239562988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.724212646484</t>
+    <t xml:space="preserve">170.305786132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.23957824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.724227905273</t>
   </si>
   <si>
     <t xml:space="preserve">168.948776245117</t>
   </si>
   <si>
-    <t xml:space="preserve">163.811492919922</t>
+    <t xml:space="preserve">163.811477661133</t>
   </si>
   <si>
     <t xml:space="preserve">167.204025268555</t>
@@ -3257,7 +3257,7 @@
     <t xml:space="preserve">152.470687866211</t>
   </si>
   <si>
-    <t xml:space="preserve">152.567596435547</t>
+    <t xml:space="preserve">152.567611694336</t>
   </si>
   <si>
     <t xml:space="preserve">154.506210327148</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">153.827697753906</t>
   </si>
   <si>
-    <t xml:space="preserve">149.465850830078</t>
+    <t xml:space="preserve">149.465866088867</t>
   </si>
   <si>
     <t xml:space="preserve">153.633850097656</t>
@@ -3290,10 +3290,10 @@
     <t xml:space="preserve">162.842193603516</t>
   </si>
   <si>
-    <t xml:space="preserve">163.229888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.4189453125</t>
+    <t xml:space="preserve">163.229904174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.418930053711</t>
   </si>
   <si>
     <t xml:space="preserve">161.097457885742</t>
@@ -3302,7 +3302,7 @@
     <t xml:space="preserve">160.806655883789</t>
   </si>
   <si>
-    <t xml:space="preserve">160.612808227539</t>
+    <t xml:space="preserve">160.61279296875</t>
   </si>
   <si>
     <t xml:space="preserve">161.582092285156</t>
@@ -3329,10 +3329,10 @@
     <t xml:space="preserve">174.182983398438</t>
   </si>
   <si>
-    <t xml:space="preserve">171.662796020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172.341323852539</t>
+    <t xml:space="preserve">171.662811279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.34130859375</t>
   </si>
   <si>
     <t xml:space="preserve">176.703155517578</t>
@@ -3341,10 +3341,10 @@
     <t xml:space="preserve">179.804916381836</t>
   </si>
   <si>
-    <t xml:space="preserve">173.892196655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.754913330078</t>
+    <t xml:space="preserve">173.892181396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.754928588867</t>
   </si>
   <si>
     <t xml:space="preserve">168.561050415039</t>
@@ -3365,7 +3365,7 @@
     <t xml:space="preserve">166.040878295898</t>
   </si>
   <si>
-    <t xml:space="preserve">167.882553100586</t>
+    <t xml:space="preserve">167.882537841797</t>
   </si>
   <si>
     <t xml:space="preserve">160.709732055664</t>
@@ -3383,16 +3383,16 @@
     <t xml:space="preserve">174.958435058594</t>
   </si>
   <si>
-    <t xml:space="preserve">173.698333740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.570709228516</t>
+    <t xml:space="preserve">173.698348999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.570724487305</t>
   </si>
   <si>
     <t xml:space="preserve">169.43342590332</t>
   </si>
   <si>
-    <t xml:space="preserve">168.076400756836</t>
+    <t xml:space="preserve">168.076385498047</t>
   </si>
   <si>
     <t xml:space="preserve">163.617630004883</t>
@@ -3401,13 +3401,13 @@
     <t xml:space="preserve">164.877731323242</t>
   </si>
   <si>
-    <t xml:space="preserve">163.714538574219</t>
+    <t xml:space="preserve">163.714553833008</t>
   </si>
   <si>
     <t xml:space="preserve">170.596588134766</t>
   </si>
   <si>
-    <t xml:space="preserve">169.821151733398</t>
+    <t xml:space="preserve">169.821136474609</t>
   </si>
   <si>
     <t xml:space="preserve">174.473785400391</t>
@@ -3425,7 +3425,7 @@
     <t xml:space="preserve">155.863250732422</t>
   </si>
   <si>
-    <t xml:space="preserve">155.669372558594</t>
+    <t xml:space="preserve">155.669387817383</t>
   </si>
   <si>
     <t xml:space="preserve">153.149200439453</t>
@@ -3434,13 +3434,13 @@
     <t xml:space="preserve">151.016754150391</t>
   </si>
   <si>
-    <t xml:space="preserve">157.220260620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.113662719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.8583984375</t>
+    <t xml:space="preserve">157.220245361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.113677978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.858413696289</t>
   </si>
   <si>
     <t xml:space="preserve">154.990859985352</t>
@@ -3470,7 +3470,7 @@
     <t xml:space="preserve">132.600082397461</t>
   </si>
   <si>
-    <t xml:space="preserve">132.309280395508</t>
+    <t xml:space="preserve">132.309295654297</t>
   </si>
   <si>
     <t xml:space="preserve">138.997421264648</t>
@@ -3488,16 +3488,16 @@
     <t xml:space="preserve">138.512771606445</t>
   </si>
   <si>
-    <t xml:space="preserve">142.680786132812</t>
+    <t xml:space="preserve">142.680770874023</t>
   </si>
   <si>
     <t xml:space="preserve">129.692169189453</t>
   </si>
   <si>
-    <t xml:space="preserve">125.039527893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.961929321289</t>
+    <t xml:space="preserve">125.039535522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.9619140625</t>
   </si>
   <si>
     <t xml:space="preserve">135.507965087891</t>
@@ -3521,10 +3521,10 @@
     <t xml:space="preserve">146.267181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">145.10400390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.690414428711</t>
+    <t xml:space="preserve">145.104019165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.690399169922</t>
   </si>
   <si>
     <t xml:space="preserve">145.394821166992</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">146.751831054688</t>
   </si>
   <si>
-    <t xml:space="preserve">149.659713745117</t>
+    <t xml:space="preserve">149.659729003906</t>
   </si>
   <si>
     <t xml:space="preserve">145.200958251953</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">141.517608642578</t>
   </si>
   <si>
-    <t xml:space="preserve">141.323776245117</t>
+    <t xml:space="preserve">141.323760986328</t>
   </si>
   <si>
     <t xml:space="preserve">137.058837890625</t>
@@ -3560,28 +3560,28 @@
     <t xml:space="preserve">136.186477661133</t>
   </si>
   <si>
-    <t xml:space="preserve">135.217178344727</t>
+    <t xml:space="preserve">135.217193603516</t>
   </si>
   <si>
     <t xml:space="preserve">130.952270507812</t>
   </si>
   <si>
-    <t xml:space="preserve">127.753578186035</t>
+    <t xml:space="preserve">127.753593444824</t>
   </si>
   <si>
     <t xml:space="preserve">121.162338256836</t>
   </si>
   <si>
-    <t xml:space="preserve">113.60181427002</t>
+    <t xml:space="preserve">113.601806640625</t>
   </si>
   <si>
     <t xml:space="preserve">117.285148620605</t>
   </si>
   <si>
-    <t xml:space="preserve">114.958831787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.57593536377</t>
+    <t xml:space="preserve">114.958824157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.575942993164</t>
   </si>
   <si>
     <t xml:space="preserve">116.12198638916</t>
@@ -3599,16 +3599,16 @@
     <t xml:space="preserve">115.443481445312</t>
   </si>
   <si>
-    <t xml:space="preserve">116.51692199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.003845214844</t>
+    <t xml:space="preserve">116.516914367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.003852844238</t>
   </si>
   <si>
     <t xml:space="preserve">117.102432250977</t>
   </si>
   <si>
-    <t xml:space="preserve">116.712089538574</t>
+    <t xml:space="preserve">116.71208190918</t>
   </si>
   <si>
     <t xml:space="preserve">120.713081359863</t>
@@ -3626,10 +3626,10 @@
     <t xml:space="preserve">120.225158691406</t>
   </si>
   <si>
-    <t xml:space="preserve">119.346893310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.005851745605</t>
+    <t xml:space="preserve">119.346900939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.005844116211</t>
   </si>
   <si>
     <t xml:space="preserve">114.857963562012</t>
@@ -3638,7 +3638,7 @@
     <t xml:space="preserve">107.539054870605</t>
   </si>
   <si>
-    <t xml:space="preserve">102.367042541504</t>
+    <t xml:space="preserve">102.367034912109</t>
   </si>
   <si>
     <t xml:space="preserve">100.512916564941</t>
@@ -3665,10 +3665,10 @@
     <t xml:space="preserve">108.319747924805</t>
   </si>
   <si>
-    <t xml:space="preserve">112.418327331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.296592712402</t>
+    <t xml:space="preserve">112.418334960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.296600341797</t>
   </si>
   <si>
     <t xml:space="preserve">115.541069030762</t>
@@ -3677,13 +3677,13 @@
     <t xml:space="preserve">114.272445678711</t>
   </si>
   <si>
-    <t xml:space="preserve">112.90625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.882110595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.247299194336</t>
+    <t xml:space="preserve">112.906257629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.882102966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.24730682373</t>
   </si>
   <si>
     <t xml:space="preserve">110.661796569824</t>
@@ -3701,13 +3701,13 @@
     <t xml:space="preserve">119.054130554199</t>
   </si>
   <si>
-    <t xml:space="preserve">118.956550598145</t>
+    <t xml:space="preserve">118.95654296875</t>
   </si>
   <si>
     <t xml:space="preserve">113.101432800293</t>
   </si>
   <si>
-    <t xml:space="preserve">116.907264709473</t>
+    <t xml:space="preserve">116.907257080078</t>
   </si>
   <si>
     <t xml:space="preserve">122.469627380371</t>
@@ -3722,10 +3722,10 @@
     <t xml:space="preserve">125.006851196289</t>
   </si>
   <si>
-    <t xml:space="preserve">122.664794921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.689949035645</t>
+    <t xml:space="preserve">122.66478729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.68994140625</t>
   </si>
   <si>
     <t xml:space="preserve">124.616500854492</t>
@@ -3737,10 +3737,10 @@
     <t xml:space="preserve">123.055137634277</t>
   </si>
   <si>
-    <t xml:space="preserve">126.470626831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.957557678223</t>
+    <t xml:space="preserve">126.470634460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.957550048828</t>
   </si>
   <si>
     <t xml:space="preserve">125.494773864746</t>
@@ -3749,7 +3749,7 @@
     <t xml:space="preserve">134.082275390625</t>
   </si>
   <si>
-    <t xml:space="preserve">134.960556030273</t>
+    <t xml:space="preserve">134.960540771484</t>
   </si>
   <si>
     <t xml:space="preserve">134.179870605469</t>
@@ -3758,10 +3758,10 @@
     <t xml:space="preserve">127.544059753418</t>
   </si>
   <si>
-    <t xml:space="preserve">126.177879333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.201011657715</t>
+    <t xml:space="preserve">126.177871704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.20100402832</t>
   </si>
   <si>
     <t xml:space="preserve">120.420333862305</t>
@@ -3773,13 +3773,13 @@
     <t xml:space="preserve">122.176864624023</t>
   </si>
   <si>
-    <t xml:space="preserve">120.029983520508</t>
+    <t xml:space="preserve">120.029991149902</t>
   </si>
   <si>
     <t xml:space="preserve">115.736236572266</t>
   </si>
   <si>
-    <t xml:space="preserve">114.955551147461</t>
+    <t xml:space="preserve">114.955558776855</t>
   </si>
   <si>
     <t xml:space="preserve">110.271453857422</t>
@@ -3788,7 +3788,7 @@
     <t xml:space="preserve">115.05313873291</t>
   </si>
   <si>
-    <t xml:space="preserve">112.711082458496</t>
+    <t xml:space="preserve">112.711090087891</t>
   </si>
   <si>
     <t xml:space="preserve">113.686943054199</t>
@@ -3809,7 +3809,7 @@
     <t xml:space="preserve">110.369041442871</t>
   </si>
   <si>
-    <t xml:space="preserve">105.977691650391</t>
+    <t xml:space="preserve">105.977699279785</t>
   </si>
   <si>
     <t xml:space="preserve">106.953552246094</t>
@@ -3824,22 +3824,22 @@
     <t xml:space="preserve">100.708084106445</t>
   </si>
   <si>
-    <t xml:space="preserve">101.391181945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.904258728027</t>
+    <t xml:space="preserve">101.391189575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.904251098633</t>
   </si>
   <si>
     <t xml:space="preserve">104.513916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">101.196014404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.001846313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.734237670898</t>
+    <t xml:space="preserve">101.196022033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.001838684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.734230041504</t>
   </si>
   <si>
     <t xml:space="preserve">115.83381652832</t>
@@ -3854,10 +3854,10 @@
     <t xml:space="preserve">106.75838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">103.440475463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.270454406738</t>
+    <t xml:space="preserve">103.440483093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.270462036133</t>
   </si>
   <si>
     <t xml:space="preserve">108.026985168457</t>
@@ -3866,28 +3866,28 @@
     <t xml:space="preserve">109.100433349609</t>
   </si>
   <si>
-    <t xml:space="preserve">108.514915466309</t>
+    <t xml:space="preserve">108.514923095703</t>
   </si>
   <si>
     <t xml:space="preserve">107.636650085449</t>
   </si>
   <si>
-    <t xml:space="preserve">109.978698730469</t>
+    <t xml:space="preserve">109.978691101074</t>
   </si>
   <si>
     <t xml:space="preserve">108.612503051758</t>
   </si>
   <si>
-    <t xml:space="preserve">107.441482543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.172866821289</t>
+    <t xml:space="preserve">107.441474914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.172874450684</t>
   </si>
   <si>
     <t xml:space="preserve">108.905258178711</t>
   </si>
   <si>
-    <t xml:space="preserve">109.685943603516</t>
+    <t xml:space="preserve">109.685935974121</t>
   </si>
   <si>
     <t xml:space="preserve">112.320739746094</t>
@@ -3902,19 +3902,19 @@
     <t xml:space="preserve">116.028991699219</t>
   </si>
   <si>
-    <t xml:space="preserve">110.076293945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.929405212402</t>
+    <t xml:space="preserve">110.076286315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.929412841797</t>
   </si>
   <si>
     <t xml:space="preserve">112.223152160645</t>
   </si>
   <si>
-    <t xml:space="preserve">109.783531188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.856971740723</t>
+    <t xml:space="preserve">109.78352355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.856964111328</t>
   </si>
   <si>
     <t xml:space="preserve">109.588356018066</t>
@@ -3926,7 +3926,7 @@
     <t xml:space="preserve">110.759384155273</t>
   </si>
   <si>
-    <t xml:space="preserve">117.200012207031</t>
+    <t xml:space="preserve">117.200019836426</t>
   </si>
   <si>
     <t xml:space="preserve">113.784523010254</t>
@@ -3941,19 +3941,19 @@
     <t xml:space="preserve">105.19701385498</t>
   </si>
   <si>
-    <t xml:space="preserve">105.099433898926</t>
+    <t xml:space="preserve">105.099426269531</t>
   </si>
   <si>
     <t xml:space="preserve">104.221168518066</t>
   </si>
   <si>
-    <t xml:space="preserve">106.465614318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.41633605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.880111694336</t>
+    <t xml:space="preserve">106.465621948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.416328430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.88011932373</t>
   </si>
   <si>
     <t xml:space="preserve">107.343894958496</t>
@@ -3962,10 +3962,10 @@
     <t xml:space="preserve">111.052146911621</t>
   </si>
   <si>
-    <t xml:space="preserve">114.467628479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.419334411621</t>
+    <t xml:space="preserve">114.467620849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.419326782227</t>
   </si>
   <si>
     <t xml:space="preserve">117.883117675781</t>
@@ -3974,10 +3974,10 @@
     <t xml:space="preserve">118.761375427246</t>
   </si>
   <si>
-    <t xml:space="preserve">115.931411743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.395179748535</t>
+    <t xml:space="preserve">115.93140411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.39518737793</t>
   </si>
   <si>
     <t xml:space="preserve">118.273452758789</t>
@@ -3986,19 +3986,19 @@
     <t xml:space="preserve">114.760383605957</t>
   </si>
   <si>
-    <t xml:space="preserve">117.980690002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.933403015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.22615814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.152717590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.493774414062</t>
+    <t xml:space="preserve">117.980697631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.933410644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.226165771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.152709960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.493766784668</t>
   </si>
   <si>
     <t xml:space="preserve">118.663787841797</t>
@@ -4022,10 +4022,10 @@
     <t xml:space="preserve">113.199020385742</t>
   </si>
   <si>
-    <t xml:space="preserve">111.540061950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.613502502441</t>
+    <t xml:space="preserve">111.540069580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.613510131836</t>
   </si>
   <si>
     <t xml:space="preserve">108.124580383301</t>
@@ -4037,13 +4037,13 @@
     <t xml:space="preserve">112.027992248535</t>
   </si>
   <si>
-    <t xml:space="preserve">109.490776062012</t>
+    <t xml:space="preserve">109.490768432617</t>
   </si>
   <si>
     <t xml:space="preserve">107.148719787598</t>
   </si>
   <si>
-    <t xml:space="preserve">113.58935546875</t>
+    <t xml:space="preserve">113.589363098145</t>
   </si>
   <si>
     <t xml:space="preserve">109.88111114502</t>
@@ -4064,10 +4064,10 @@
     <t xml:space="preserve">101.683944702148</t>
   </si>
   <si>
-    <t xml:space="preserve">102.95255279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.781524658203</t>
+    <t xml:space="preserve">102.952545166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.781532287598</t>
   </si>
   <si>
     <t xml:space="preserve">100.610504150391</t>
@@ -4076,13 +4076,13 @@
     <t xml:space="preserve">103.342895507812</t>
   </si>
   <si>
-    <t xml:space="preserve">101.000846862793</t>
+    <t xml:space="preserve">101.000839233398</t>
   </si>
   <si>
     <t xml:space="preserve">100.415328979492</t>
   </si>
   <si>
-    <t xml:space="preserve">102.074279785156</t>
+    <t xml:space="preserve">102.074287414551</t>
   </si>
   <si>
     <t xml:space="preserve">103.040893554688</t>
@@ -5463,6 +5463,9 @@
   </si>
   <si>
     <t xml:space="preserve">118.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.099998474121</t>
   </si>
 </sst>
 </file>
@@ -70593,7 +70596,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.649537037</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>58490</v>
@@ -70614,6 +70617,32 @@
         <v>1816</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6493171296</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>57076</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>121.099998474121</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>118.400001525879</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>119.199996948242</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>121.099998474121</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>1817</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/REY.MI.xlsx
+++ b/data/REY.MI.xlsx
@@ -44,40 +44,40 @@
     <t xml:space="preserve">REY.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8380298614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3272113800049</t>
+    <t xml:space="preserve">28.8380241394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3272094726562</t>
   </si>
   <si>
     <t xml:space="preserve">27.6306381225586</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8396110534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2111129760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.000560760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.559398651123</t>
+    <t xml:space="preserve">27.8396129608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2111167907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0005626678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5594005584717</t>
   </si>
   <si>
     <t xml:space="preserve">28.1414585113525</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1198234558105</t>
+    <t xml:space="preserve">27.1198215484619</t>
   </si>
   <si>
     <t xml:space="preserve">27.9789257049561</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8644123077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4448833465576</t>
+    <t xml:space="preserve">26.8644142150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4448871612549</t>
   </si>
   <si>
     <t xml:space="preserve">27.9324893951416</t>
@@ -86,34 +86,34 @@
     <t xml:space="preserve">27.8163928985596</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2807750701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6770782470703</t>
+    <t xml:space="preserve">28.2807712554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6770763397217</t>
   </si>
   <si>
     <t xml:space="preserve">28.0950202941895</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8628311157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2591361999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7018756866455</t>
+    <t xml:space="preserve">27.8628330230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2591342926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7018795013428</t>
   </si>
   <si>
     <t xml:space="preserve">26.167839050293</t>
   </si>
   <si>
-    <t xml:space="preserve">25.285514831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3799781799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6121635437012</t>
+    <t xml:space="preserve">25.2855186462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.379976272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6121673583984</t>
   </si>
   <si>
     <t xml:space="preserve">26.0053062438965</t>
@@ -122,67 +122,67 @@
     <t xml:space="preserve">25.517707824707</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6570262908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6074180603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3071537017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0733833312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2142791748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4696865081787</t>
+    <t xml:space="preserve">25.6570224761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6074199676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3071575164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0733814239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.214282989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4696884155273</t>
   </si>
   <si>
     <t xml:space="preserve">26.0517444610596</t>
   </si>
   <si>
-    <t xml:space="preserve">25.703462600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.726676940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7483158111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4929103851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3520107269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1894779205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2359142303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1662616729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9092674255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0237808227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5546569824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3008308410645</t>
+    <t xml:space="preserve">25.7034606933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7266788482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7483177185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4929065704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3520126342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1894760131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2359180450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1662578582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9092655181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0237827301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5546531677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3008327484131</t>
   </si>
   <si>
     <t xml:space="preserve">30.4169216156006</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9989795684814</t>
+    <t xml:space="preserve">29.9989814758301</t>
   </si>
   <si>
     <t xml:space="preserve">29.9757614135742</t>
@@ -191,124 +191,124 @@
     <t xml:space="preserve">29.7900085449219</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9525413513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2311706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7203502655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0686340332031</t>
+    <t xml:space="preserve">29.9525394439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2311725616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7203540802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0686359405518</t>
   </si>
   <si>
     <t xml:space="preserve">29.8596668243408</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5578193664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3256301879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4881610870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5113792419434</t>
+    <t xml:space="preserve">29.5578212738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3256282806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4881629943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.511381149292</t>
   </si>
   <si>
     <t xml:space="preserve">29.2095336914062</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1615085601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3720684051514</t>
+    <t xml:space="preserve">30.1615104675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3720664978027</t>
   </si>
   <si>
     <t xml:space="preserve">29.5345993041992</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4433097839355</t>
+    <t xml:space="preserve">28.4433040618896</t>
   </si>
   <si>
     <t xml:space="preserve">28.6754970550537</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8612499237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8148097991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9076881408691</t>
+    <t xml:space="preserve">28.8612461090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8148078918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9076862335205</t>
   </si>
   <si>
     <t xml:space="preserve">28.629056930542</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4200859069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6776027679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5605506896973</t>
+    <t xml:space="preserve">28.4200897216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6775989532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5605487823486</t>
   </si>
   <si>
     <t xml:space="preserve">29.0287532806396</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3264465332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5137310028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7946510314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0053443908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2628574371338</t>
+    <t xml:space="preserve">28.3264446258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5137271881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7946529388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0053424835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2628593444824</t>
   </si>
   <si>
     <t xml:space="preserve">30.1992683410645</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5036029815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5504264831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.901575088501</t>
+    <t xml:space="preserve">30.5035972595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5504283905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9015769958496</t>
   </si>
   <si>
     <t xml:space="preserve">30.6674728393555</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7142963409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4567852020264</t>
+    <t xml:space="preserve">30.7142944335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4567813873291</t>
   </si>
   <si>
     <t xml:space="preserve">30.4333724975586</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2694988250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8949375152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1859855651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3096790313721</t>
+    <t xml:space="preserve">30.2694969177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8949356079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1859836578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3096771240234</t>
   </si>
   <si>
     <t xml:space="preserve">29.4969577789307</t>
@@ -320,37 +320,37 @@
     <t xml:space="preserve">25.7747249603271</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8047790527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3198013305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9218273162842</t>
+    <t xml:space="preserve">26.8047771453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3198051452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9218292236328</t>
   </si>
   <si>
     <t xml:space="preserve">27.5070838928223</t>
   </si>
   <si>
-    <t xml:space="preserve">26.945240020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8215484619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.219518661499</t>
+    <t xml:space="preserve">26.9452381134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8215446472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2195205688477</t>
   </si>
   <si>
     <t xml:space="preserve">27.1091117858887</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6241359710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3666229248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.303035736084</t>
+    <t xml:space="preserve">27.624137878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3666210174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3030376434326</t>
   </si>
   <si>
     <t xml:space="preserve">28.8882923126221</t>
@@ -359,43 +359,43 @@
     <t xml:space="preserve">28.7478313446045</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4434947967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.98193359375</t>
+    <t xml:space="preserve">28.4434986114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9819355010986</t>
   </si>
   <si>
     <t xml:space="preserve">28.9117050170898</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3799057006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4501419067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8481159210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1524467468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9651641845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.724422454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1458072662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0989875793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9351139068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4903144836426</t>
+    <t xml:space="preserve">29.3799095153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4501399993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8481140136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1524486541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9651660919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7244205474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1458053588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0989837646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9351119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4903163909912</t>
   </si>
   <si>
     <t xml:space="preserve">27.9752922058105</t>
@@ -404,10 +404,10 @@
     <t xml:space="preserve">28.3732662200928</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0923442840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2729816436768</t>
+    <t xml:space="preserve">28.0923461914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2729835510254</t>
   </si>
   <si>
     <t xml:space="preserve">27.0622901916504</t>
@@ -419,13 +419,13 @@
     <t xml:space="preserve">26.898416519165</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1492881774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7981357574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.891773223877</t>
+    <t xml:space="preserve">26.1492900848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.798131942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8917770385742</t>
   </si>
   <si>
     <t xml:space="preserve">26.7579574584961</t>
@@ -434,13 +434,13 @@
     <t xml:space="preserve">27.9518814086914</t>
   </si>
   <si>
-    <t xml:space="preserve">27.881649017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8114204406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9050617218018</t>
+    <t xml:space="preserve">27.8816471099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8114223480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9050579071045</t>
   </si>
   <si>
     <t xml:space="preserve">27.2963924407959</t>
@@ -464,19 +464,19 @@
     <t xml:space="preserve">27.7880077362061</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3900356292725</t>
+    <t xml:space="preserve">27.3900337219238</t>
   </si>
   <si>
     <t xml:space="preserve">29.1223964691162</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6541881561279</t>
+    <t xml:space="preserve">28.6541919708252</t>
   </si>
   <si>
     <t xml:space="preserve">28.2093944549561</t>
   </si>
   <si>
-    <t xml:space="preserve">27.413444519043</t>
+    <t xml:space="preserve">27.4134426116943</t>
   </si>
   <si>
     <t xml:space="preserve">27.0857009887695</t>
@@ -485,43 +485,43 @@
     <t xml:space="preserve">26.8515968322754</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4368553161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.68772315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2261657714844</t>
+    <t xml:space="preserve">27.4368534088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6877269744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2261619567871</t>
   </si>
   <si>
     <t xml:space="preserve">26.8281860351562</t>
   </si>
   <si>
-    <t xml:space="preserve">26.640905380249</t>
+    <t xml:space="preserve">26.6409091949463</t>
   </si>
   <si>
     <t xml:space="preserve">26.4536247253418</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5706768035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5238513946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3365726470947</t>
+    <t xml:space="preserve">26.5706748962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5238571166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3365707397461</t>
   </si>
   <si>
     <t xml:space="preserve">25.751314163208</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3299293518066</t>
+    <t xml:space="preserve">25.329927444458</t>
   </si>
   <si>
     <t xml:space="preserve">24.7446708679199</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7680854797363</t>
+    <t xml:space="preserve">24.7680816650391</t>
   </si>
   <si>
     <t xml:space="preserve">24.8851356506348</t>
@@ -530,16 +530,16 @@
     <t xml:space="preserve">24.2530574798584</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0490074157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4703922271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5172138214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.283109664917</t>
+    <t xml:space="preserve">25.0490055084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4703941345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5172119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2831077575684</t>
   </si>
   <si>
     <t xml:space="preserve">25.1660556793213</t>
@@ -548,112 +548,112 @@
     <t xml:space="preserve">25.4469776153564</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0958309173584</t>
+    <t xml:space="preserve">25.0958271026611</t>
   </si>
   <si>
     <t xml:space="preserve">24.931957244873</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0724143981934</t>
+    <t xml:space="preserve">25.0724182128906</t>
   </si>
   <si>
     <t xml:space="preserve">25.6342639923096</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1961097717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1726989746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8348274230957</t>
+    <t xml:space="preserve">26.1961078643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.172700881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8348293304443</t>
   </si>
   <si>
     <t xml:space="preserve">27.9284706115723</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4602642059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9987030029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6307811737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2160339355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3330879211426</t>
+    <t xml:space="preserve">27.4602680206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9986991882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6307830810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2160358428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3330860137939</t>
   </si>
   <si>
     <t xml:space="preserve">28.8648815155029</t>
   </si>
   <si>
-    <t xml:space="preserve">28.349853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6073665618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4735527038574</t>
+    <t xml:space="preserve">28.3498554229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6073703765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4735488891602</t>
   </si>
   <si>
     <t xml:space="preserve">29.2394466400146</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7076568603516</t>
+    <t xml:space="preserve">29.7076511383057</t>
   </si>
   <si>
     <t xml:space="preserve">29.4267292022705</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8313465118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9952163696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4868335723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2527313232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3697814941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1356754302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1891479492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3061943054199</t>
+    <t xml:space="preserve">30.8313503265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9952144622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4868354797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2527275085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3697853088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1356830596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1891441345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3061981201172</t>
   </si>
   <si>
     <t xml:space="preserve">33.2660179138184</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0619659423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6472282409668</t>
+    <t xml:space="preserve">34.0619621276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6472244262695</t>
   </si>
   <si>
     <t xml:space="preserve">34.4599418640137</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7408676147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6706314086914</t>
+    <t xml:space="preserve">34.7408638000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6706352233887</t>
   </si>
   <si>
     <t xml:space="preserve">34.9983749389648</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8579139709473</t>
+    <t xml:space="preserve">34.85791015625</t>
   </si>
   <si>
     <t xml:space="preserve">34.1790199279785</t>
@@ -662,40 +662,40 @@
     <t xml:space="preserve">34.7642707824707</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8813209533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.389705657959</t>
+    <t xml:space="preserve">34.8813247680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3897094726562</t>
   </si>
   <si>
     <t xml:space="preserve">34.4131202697754</t>
   </si>
   <si>
-    <t xml:space="preserve">35.607048034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4665832519531</t>
+    <t xml:space="preserve">35.6070404052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4665870666504</t>
   </si>
   <si>
     <t xml:space="preserve">35.7943267822266</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8243827819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6671409606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8778419494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9882545471191</t>
+    <t xml:space="preserve">36.8243751525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6671485900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8778495788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9882469177246</t>
   </si>
   <si>
     <t xml:space="preserve">37.5735092163086</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6203231811523</t>
+    <t xml:space="preserve">37.6203269958496</t>
   </si>
   <si>
     <t xml:space="preserve">37.6085395812988</t>
@@ -707,25 +707,25 @@
     <t xml:space="preserve">37.9150695800781</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1980133056641</t>
+    <t xml:space="preserve">38.1980171203613</t>
   </si>
   <si>
     <t xml:space="preserve">37.9386444091797</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1508598327637</t>
+    <t xml:space="preserve">38.1508636474609</t>
   </si>
   <si>
     <t xml:space="preserve">37.4906425476074</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0232849121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0843391418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0607528686523</t>
+    <t xml:space="preserve">39.0232772827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.084342956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0607604980469</t>
   </si>
   <si>
     <t xml:space="preserve">39.8013954162598</t>
@@ -734,10 +734,10 @@
     <t xml:space="preserve">41.2397041320801</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0275001525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4519157409668</t>
+    <t xml:space="preserve">41.0274925231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4519195556641</t>
   </si>
   <si>
     <t xml:space="preserve">41.7112922668457</t>
@@ -749,40 +749,40 @@
     <t xml:space="preserve">41.805606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3243408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1828727722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0885581970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2771911621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8291816711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.966438293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5891799926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4338035583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9997024536133</t>
+    <t xml:space="preserve">42.3243446350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1828651428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0885543823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2771873474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8291854858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9664421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5891761779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4338073730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9997062683105</t>
   </si>
   <si>
     <t xml:space="preserve">39.6363410949707</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9428558349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4380187988281</t>
+    <t xml:space="preserve">39.9428634643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4380264282227</t>
   </si>
   <si>
     <t xml:space="preserve">38.551700592041</t>
@@ -791,13 +791,13 @@
     <t xml:space="preserve">38.0565414428711</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1411781311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3298110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0704307556152</t>
+    <t xml:space="preserve">39.1411743164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3298072814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0704383850098</t>
   </si>
   <si>
     <t xml:space="preserve">39.1647567749023</t>
@@ -806,28 +806,28 @@
     <t xml:space="preserve">38.6695899963379</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8346481323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9053802490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0940208435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8110694885254</t>
+    <t xml:space="preserve">38.8346519470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9053764343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0940170288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8110656738281</t>
   </si>
   <si>
     <t xml:space="preserve">38.2687492370605</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7403373718262</t>
+    <t xml:space="preserve">38.7403297424316</t>
   </si>
   <si>
     <t xml:space="preserve">38.6931762695312</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2354927062988</t>
+    <t xml:space="preserve">39.2354850769043</t>
   </si>
   <si>
     <t xml:space="preserve">39.2590675354004</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">42.1357078552246</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5129776000977</t>
+    <t xml:space="preserve">42.5129737854004</t>
   </si>
   <si>
     <t xml:space="preserve">44.7765617370605</t>
@@ -845,70 +845,70 @@
     <t xml:space="preserve">44.8001441955566</t>
   </si>
   <si>
-    <t xml:space="preserve">45.507511138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3188743591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8140411376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6822509765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7862434387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7529830932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1302452087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4464530944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.5879364013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3285598754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3049774169922</t>
+    <t xml:space="preserve">45.5075073242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3188781738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.814037322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.682243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7862396240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.752986907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.130241394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4464569091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.5879325866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.328556060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3049812316895</t>
   </si>
   <si>
     <t xml:space="preserve">43.6211891174316</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1731872558594</t>
+    <t xml:space="preserve">43.1731910705566</t>
   </si>
   <si>
     <t xml:space="preserve">43.0788764953613</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5837173461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2675018310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.366039276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.98876953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4936103820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.5171928405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6254081726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8612022399902</t>
+    <t xml:space="preserve">42.5837135314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.267505645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3660354614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9887771606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4936141967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.5172004699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6254043579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.861198425293</t>
   </si>
   <si>
     <t xml:space="preserve">46.4035186767578</t>
@@ -917,37 +917,37 @@
     <t xml:space="preserve">47.5824661254883</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0637321472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.134464263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1580429077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9125671386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3508911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7378387451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1012001037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8321571350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6296234130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0540504455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8654136657715</t>
+    <t xml:space="preserve">47.0637283325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1344604492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1580467224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9125747680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.350887298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7378349304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.101203918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8321533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6296195983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0540428161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8654174804688</t>
   </si>
   <si>
     <t xml:space="preserve">47.9597282409668</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">49.1858406066895</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2717247009277</t>
+    <t xml:space="preserve">45.2717208862305</t>
   </si>
   <si>
     <t xml:space="preserve">45.0359306335449</t>
@@ -965,34 +965,34 @@
     <t xml:space="preserve">44.5643539428711</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9748725891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.560131072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9138145446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7251815795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2064552307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4328079223633</t>
+    <t xml:space="preserve">43.9748764038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5601387023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9138221740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7251892089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2064476013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4328117370605</t>
   </si>
   <si>
     <t xml:space="preserve">42.1781578063965</t>
   </si>
   <si>
-    <t xml:space="preserve">43.3476791381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9800910949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3010139465332</t>
+    <t xml:space="preserve">43.3476715087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9800872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3010101318359</t>
   </si>
   <si>
     <t xml:space="preserve">42.0838356018066</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">42.7534866333008</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5931434631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4799652099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0081329345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0458641052246</t>
+    <t xml:space="preserve">42.593147277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4799728393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.008129119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0458679199219</t>
   </si>
   <si>
     <t xml:space="preserve">43.3288078308105</t>
@@ -1019,16 +1019,16 @@
     <t xml:space="preserve">41.3953285217285</t>
   </si>
   <si>
-    <t xml:space="preserve">43.489143371582</t>
+    <t xml:space="preserve">43.4891471862793</t>
   </si>
   <si>
     <t xml:space="preserve">44.2342491149902</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1210708618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2439270019531</t>
+    <t xml:space="preserve">44.1210670471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2439231872559</t>
   </si>
   <si>
     <t xml:space="preserve">42.1027030944824</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">41.1689758300781</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2729682922363</t>
+    <t xml:space="preserve">40.2729721069336</t>
   </si>
   <si>
     <t xml:space="preserve">42.4045104980469</t>
@@ -1046,46 +1046,46 @@
     <t xml:space="preserve">43.7626686096191</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2531089782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0547904968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9510459899902</t>
+    <t xml:space="preserve">44.2531051635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0547943115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9510498046875</t>
   </si>
   <si>
     <t xml:space="preserve">46.2809028625488</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1488571166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.309455871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9981994628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5358085632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1679725646973</t>
+    <t xml:space="preserve">46.148853302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3094482421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9982032775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5358047485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1679763793945</t>
   </si>
   <si>
     <t xml:space="preserve">45.5923957824707</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6586608886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.253360748291</t>
+    <t xml:space="preserve">44.6586647033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2533569335938</t>
   </si>
   <si>
     <t xml:space="preserve">43.6683502197266</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2248153686523</t>
+    <t xml:space="preserve">44.2248077392578</t>
   </si>
   <si>
     <t xml:space="preserve">45.0830917358398</t>
@@ -1094,46 +1094,46 @@
     <t xml:space="preserve">45.2056999206543</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3280563354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0356864929199</t>
+    <t xml:space="preserve">46.3280639648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0356826782227</t>
   </si>
   <si>
     <t xml:space="preserve">45.6584205627441</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5169486999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1682281494141</t>
+    <t xml:space="preserve">45.5169410705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1682243347168</t>
   </si>
   <si>
     <t xml:space="preserve">43.8664093017578</t>
   </si>
   <si>
-    <t xml:space="preserve">43.5457305908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8852691650391</t>
+    <t xml:space="preserve">43.5457382202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8852729797363</t>
   </si>
   <si>
     <t xml:space="preserve">44.4606018066406</t>
   </si>
   <si>
-    <t xml:space="preserve">45.611255645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.630126953125</t>
+    <t xml:space="preserve">45.6112632751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6301231384277</t>
   </si>
   <si>
     <t xml:space="preserve">45.7244415283203</t>
   </si>
   <si>
-    <t xml:space="preserve">46.290340423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.026252746582</t>
+    <t xml:space="preserve">46.2903366088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0262451171875</t>
   </si>
   <si>
     <t xml:space="preserve">46.2148857116699</t>
@@ -1142,16 +1142,16 @@
     <t xml:space="preserve">46.6487350463867</t>
   </si>
   <si>
-    <t xml:space="preserve">46.705322265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5921478271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8939590454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7710990905762</t>
+    <t xml:space="preserve">46.7053260803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5921516418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8939628601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7711029052734</t>
   </si>
   <si>
     <t xml:space="preserve">47.8182563781738</t>
@@ -1160,124 +1160,124 @@
     <t xml:space="preserve">48.1955184936523</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9972076416016</t>
+    <t xml:space="preserve">48.9972038269043</t>
   </si>
   <si>
     <t xml:space="preserve">48.5727844238281</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3273162841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3176307678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4119491577148</t>
+    <t xml:space="preserve">49.3273048400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3176345825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4119453430176</t>
   </si>
   <si>
     <t xml:space="preserve">49.8460464477539</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3744659423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.223316192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0818405151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5353126525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1960220336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2052001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.006893157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2523536682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4223785400391</t>
+    <t xml:space="preserve">49.3744697570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2233200073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.081844329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5353088378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1960182189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2052040100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0068893432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2523574829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4223747253418</t>
   </si>
   <si>
     <t xml:space="preserve">45.8376159667969</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6489906311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8753433227539</t>
+    <t xml:space="preserve">45.6489868164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8753471374512</t>
   </si>
   <si>
     <t xml:space="preserve">46.5732841491699</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4687881469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8085784912109</t>
+    <t xml:space="preserve">49.4687843322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8085746765137</t>
   </si>
   <si>
     <t xml:space="preserve">46.4789657592773</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3938369750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5166893005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1774139404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7812728881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8378639221191</t>
+    <t xml:space="preserve">47.3938293457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5166931152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1774024963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7812805175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8378677368164</t>
   </si>
   <si>
     <t xml:space="preserve">44.4983291625977</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1776580810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8952026367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2913360595703</t>
+    <t xml:space="preserve">44.1776542663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.895206451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.291332244873</t>
   </si>
   <si>
     <t xml:space="preserve">42.4988288879395</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0652275085449</t>
+    <t xml:space="preserve">41.0652236938477</t>
   </si>
   <si>
     <t xml:space="preserve">41.9517936706543</t>
   </si>
   <si>
-    <t xml:space="preserve">45.328311920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4414901733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4603576660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4037628173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1017036437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.988525390625</t>
+    <t xml:space="preserve">45.3283157348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4414939880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4603500366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4037666320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1016998291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9885215759277</t>
   </si>
   <si>
     <t xml:space="preserve">46.3846473693848</t>
@@ -1292,31 +1292,31 @@
     <t xml:space="preserve">48.2898368835449</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1193237304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.694896697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6005821228027</t>
+    <t xml:space="preserve">51.1193199157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6948928833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6005897521973</t>
   </si>
   <si>
     <t xml:space="preserve">50.9328575134277</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4107093811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0277938842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.214485168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1195526123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.7398147583008</t>
+    <t xml:space="preserve">50.4107055664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0277862548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.2144813537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1195449829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.739803314209</t>
   </si>
   <si>
     <t xml:space="preserve">49.8410987854004</t>
@@ -1331,61 +1331,61 @@
     <t xml:space="preserve">49.3664207458496</t>
   </si>
   <si>
-    <t xml:space="preserve">49.081615447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7936325073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.2746620178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8221549987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0847930908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6544075012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3189544677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6512298583984</t>
+    <t xml:space="preserve">49.0816116333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.793628692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.2746658325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.822151184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0848007202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6544036865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3189506530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6512260437012</t>
   </si>
   <si>
     <t xml:space="preserve">49.9835014343262</t>
   </si>
   <si>
-    <t xml:space="preserve">50.3632431030273</t>
+    <t xml:space="preserve">50.3632469177246</t>
   </si>
   <si>
     <t xml:space="preserve">51.2176628112793</t>
   </si>
   <si>
-    <t xml:space="preserve">50.1733703613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4550018310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.0246047973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0689086914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.7840919494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4422912597656</t>
+    <t xml:space="preserve">50.1733665466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.455005645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.0246086120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0689010620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.7840995788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4422874450684</t>
   </si>
   <si>
     <t xml:space="preserve">54.6828079223633</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1100158691406</t>
+    <t xml:space="preserve">55.1100120544434</t>
   </si>
   <si>
     <t xml:space="preserve">55.5846900939941</t>
@@ -1394,25 +1394,25 @@
     <t xml:space="preserve">56.3916473388672</t>
   </si>
   <si>
-    <t xml:space="preserve">54.7302780151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.0625495910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4897575378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2524185180664</t>
+    <t xml:space="preserve">54.7302742004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.0625457763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4897537231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.2524147033691</t>
   </si>
   <si>
     <t xml:space="preserve">53.1638374328613</t>
   </si>
   <si>
-    <t xml:space="preserve">53.6385154724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0182609558105</t>
+    <t xml:space="preserve">53.6385192871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0182571411133</t>
   </si>
   <si>
     <t xml:space="preserve">54.3030662536621</t>
@@ -1424,22 +1424,22 @@
     <t xml:space="preserve">53.8283882141113</t>
   </si>
   <si>
-    <t xml:space="preserve">54.7777404785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4391174316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9137878417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2966995239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0119018554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.201774597168</t>
+    <t xml:space="preserve">54.7777442932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4391059875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9137916564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2967109680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.011905670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2017707824707</t>
   </si>
   <si>
     <t xml:space="preserve">56.5340423583984</t>
@@ -1448,10 +1448,10 @@
     <t xml:space="preserve">56.6764488220215</t>
   </si>
   <si>
-    <t xml:space="preserve">54.9676094055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5942306518555</t>
+    <t xml:space="preserve">54.9676170349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5942268371582</t>
   </si>
   <si>
     <t xml:space="preserve">53.0214385986328</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">55.1574783325195</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3505363464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9264945983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.879035949707</t>
+    <t xml:space="preserve">54.3505325317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9265022277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.8790321350098</t>
   </si>
   <si>
     <t xml:space="preserve">54.0657234191895</t>
@@ -1478,25 +1478,25 @@
     <t xml:space="preserve">53.4486427307129</t>
   </si>
   <si>
-    <t xml:space="preserve">53.685977935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3062400817871</t>
+    <t xml:space="preserve">53.6859855651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3062438964844</t>
   </si>
   <si>
     <t xml:space="preserve">52.404354095459</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0752601623535</t>
+    <t xml:space="preserve">51.0752563476562</t>
   </si>
   <si>
     <t xml:space="preserve">50.458179473877</t>
   </si>
   <si>
-    <t xml:space="preserve">52.2619476318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8822135925293</t>
+    <t xml:space="preserve">52.2619514465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8822174072266</t>
   </si>
   <si>
     <t xml:space="preserve">54.1606559753418</t>
@@ -1508,52 +1508,52 @@
     <t xml:space="preserve">53.5435791015625</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5404052734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2049522399902</t>
+    <t xml:space="preserve">54.5404014587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.2049560546875</t>
   </si>
   <si>
     <t xml:space="preserve">56.2492370605469</t>
   </si>
   <si>
-    <t xml:space="preserve">57.1036643981934</t>
+    <t xml:space="preserve">57.1036605834961</t>
   </si>
   <si>
     <t xml:space="preserve">57.2460594177246</t>
   </si>
   <si>
-    <t xml:space="preserve">57.9106101989746</t>
+    <t xml:space="preserve">57.9106063842773</t>
   </si>
   <si>
     <t xml:space="preserve">56.9612579345703</t>
   </si>
   <si>
-    <t xml:space="preserve">50.7904510498047</t>
+    <t xml:space="preserve">50.790454864502</t>
   </si>
   <si>
     <t xml:space="preserve">49.413890838623</t>
   </si>
   <si>
-    <t xml:space="preserve">47.012020111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0499954223633</t>
+    <t xml:space="preserve">47.0120239257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0499992370605</t>
   </si>
   <si>
     <t xml:space="preserve">48.2271919250488</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4677085876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0309715270996</t>
+    <t xml:space="preserve">47.467716217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0309677124023</t>
   </si>
   <si>
     <t xml:space="preserve">50.3157730102539</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3474731445312</t>
+    <t xml:space="preserve">46.3474769592285</t>
   </si>
   <si>
     <t xml:space="preserve">44.7525634765625</t>
@@ -1562,34 +1562,34 @@
     <t xml:space="preserve">44.6766090393066</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6955986022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1955833435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5563316345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4803810119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9487457275391</t>
+    <t xml:space="preserve">44.6956024169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1955757141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5563354492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4803848266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9487495422363</t>
   </si>
   <si>
     <t xml:space="preserve">47.4107513427734</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5373458862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5183563232422</t>
+    <t xml:space="preserve">46.5373497009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5183601379395</t>
   </si>
   <si>
     <t xml:space="preserve">46.7462043762207</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4424095153809</t>
+    <t xml:space="preserve">46.4424018859863</t>
   </si>
   <si>
     <t xml:space="preserve">45.4930534362793</t>
@@ -1598,7 +1598,7 @@
     <t xml:space="preserve">45.1322975158691</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5690040588379</t>
+    <t xml:space="preserve">45.5690002441406</t>
   </si>
   <si>
     <t xml:space="preserve">45.7019119262695</t>
@@ -1607,85 +1607,85 @@
     <t xml:space="preserve">42.3601875305176</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4677925109863</t>
+    <t xml:space="preserve">41.4677963256836</t>
   </si>
   <si>
     <t xml:space="preserve">41.9234809875488</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8728370666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7462501525879</t>
+    <t xml:space="preserve">42.8728408813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7462425231934</t>
   </si>
   <si>
     <t xml:space="preserve">44.2968673706055</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8601684570312</t>
+    <t xml:space="preserve">43.8601722717285</t>
   </si>
   <si>
     <t xml:space="preserve">45.7209014892578</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7841758728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7050514221191</t>
+    <t xml:space="preserve">46.7841796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7050476074219</t>
   </si>
   <si>
     <t xml:space="preserve">47.2398643493652</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2905120849609</t>
+    <t xml:space="preserve">46.2905082702637</t>
   </si>
   <si>
     <t xml:space="preserve">45.1892623901367</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2082557678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2841987609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3158264160156</t>
+    <t xml:space="preserve">45.208251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2842025756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3158111572266</t>
   </si>
   <si>
     <t xml:space="preserve">47.3727798461914</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6132926940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.486743927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5373878479004</t>
+    <t xml:space="preserve">46.6132888793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4867362976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5373916625977</t>
   </si>
   <si>
     <t xml:space="preserve">43.5183982849121</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0753784179688</t>
+    <t xml:space="preserve">42.075382232666</t>
   </si>
   <si>
     <t xml:space="preserve">41.5627288818359</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2146453857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8475379943848</t>
+    <t xml:space="preserve">40.2146492004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8475341796875</t>
   </si>
   <si>
     <t xml:space="preserve">42.4551200866699</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2526168823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8095588684082</t>
+    <t xml:space="preserve">40.2526206970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8095550537109</t>
   </si>
   <si>
     <t xml:space="preserve">43.1956176757812</t>
@@ -1700,28 +1700,28 @@
     <t xml:space="preserve">44.3348426818848</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8791580200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7398872375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8348236083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.803165435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3854522705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4234275817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1829109191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1765480041504</t>
+    <t xml:space="preserve">43.8791618347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7398948669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8348197937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8031616210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3854484558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4234237670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1829071044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1765556335449</t>
   </si>
   <si>
     <t xml:space="preserve">48.3696022033691</t>
@@ -1730,19 +1730,19 @@
     <t xml:space="preserve">45.4360961914062</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0753364562988</t>
+    <t xml:space="preserve">45.0753440856934</t>
   </si>
   <si>
     <t xml:space="preserve">45.6449584960938</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2588500976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4645347595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8885650634766</t>
+    <t xml:space="preserve">47.2588539123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4645309448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8885688781738</t>
   </si>
   <si>
     <t xml:space="preserve">50.125904083252</t>
@@ -1751,7 +1751,7 @@
     <t xml:space="preserve">50.6955184936523</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2208404541016</t>
+    <t xml:space="preserve">50.2208366394043</t>
   </si>
   <si>
     <t xml:space="preserve">49.9360313415527</t>
@@ -1760,25 +1760,25 @@
     <t xml:space="preserve">50.0784378051758</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1670150756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6891632080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9739608764648</t>
+    <t xml:space="preserve">52.1670188903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6891593933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9739685058594</t>
   </si>
   <si>
     <t xml:space="preserve">54.2555961608887</t>
   </si>
   <si>
-    <t xml:space="preserve">53.2587776184082</t>
+    <t xml:space="preserve">53.2587738037109</t>
   </si>
   <si>
     <t xml:space="preserve">53.9707908630371</t>
   </si>
   <si>
-    <t xml:space="preserve">53.7334518432617</t>
+    <t xml:space="preserve">53.7334480285645</t>
   </si>
   <si>
     <t xml:space="preserve">55.2998886108398</t>
@@ -1796,130 +1796,130 @@
     <t xml:space="preserve">54.4929389953613</t>
   </si>
   <si>
-    <t xml:space="preserve">54.4454650878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4961128234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.6353302001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.9644393920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.7270965576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1068305969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5328521728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5239143371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5717391967773</t>
+    <t xml:space="preserve">54.4454612731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4961090087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6353340148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.9644317626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.7270889282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1068382263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5328483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5239105224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5717430114746</t>
   </si>
   <si>
     <t xml:space="preserve">52.615104675293</t>
   </si>
   <si>
-    <t xml:space="preserve">52.5194435119629</t>
+    <t xml:space="preserve">52.5194396972656</t>
   </si>
   <si>
     <t xml:space="preserve">51.4671363830566</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5283889770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.9633445739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0589981079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1980285644531</t>
+    <t xml:space="preserve">54.5283851623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.9633407592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0590019226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1980323791504</t>
   </si>
   <si>
     <t xml:space="preserve">56.776481628418</t>
   </si>
   <si>
-    <t xml:space="preserve">56.011173248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.6285171508789</t>
+    <t xml:space="preserve">56.0111694335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.6285209655762</t>
   </si>
   <si>
     <t xml:space="preserve">56.2024955749512</t>
   </si>
   <si>
-    <t xml:space="preserve">55.9155120849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4416542053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5806884765625</t>
+    <t xml:space="preserve">55.9155044555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4416618347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.580680847168</t>
   </si>
   <si>
     <t xml:space="preserve">56.3459968566895</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1501960754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5762138366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4327239990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.863208770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9199829101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8243141174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.2547988891602</t>
+    <t xml:space="preserve">55.1501998901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5762100219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4327201843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8632011413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9199752807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8243179321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.2547950744629</t>
   </si>
   <si>
     <t xml:space="preserve">56.6808166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">56.728645324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.2114410400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.6374549865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5462646484375</t>
+    <t xml:space="preserve">56.7286529541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.2114334106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.6374588012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5462684631348</t>
   </si>
   <si>
     <t xml:space="preserve">57.924446105957</t>
   </si>
   <si>
-    <t xml:space="preserve">58.3549346923828</t>
+    <t xml:space="preserve">58.3549308776855</t>
   </si>
   <si>
     <t xml:space="preserve">57.7331161499023</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3504600524902</t>
+    <t xml:space="preserve">57.3504676818848</t>
   </si>
   <si>
     <t xml:space="preserve">58.3071060180664</t>
   </si>
   <si>
-    <t xml:space="preserve">60.2682151794434</t>
+    <t xml:space="preserve">60.2682075500488</t>
   </si>
   <si>
     <t xml:space="preserve">60.172550201416</t>
@@ -1928,64 +1928,64 @@
     <t xml:space="preserve">59.7420616149902</t>
   </si>
   <si>
-    <t xml:space="preserve">59.2159156799316</t>
+    <t xml:space="preserve">59.2159118652344</t>
   </si>
   <si>
     <t xml:space="preserve">59.120246887207</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3026313781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.828784942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.115779876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.7809524536133</t>
+    <t xml:space="preserve">57.3026351928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.8287925720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.1157760620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.7809562683105</t>
   </si>
   <si>
     <t xml:space="preserve">59.0245819091797</t>
   </si>
   <si>
-    <t xml:space="preserve">59.4550743103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.3160438537598</t>
+    <t xml:space="preserve">59.4550666809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.3160400390625</t>
   </si>
   <si>
     <t xml:space="preserve">60.0290489196777</t>
   </si>
   <si>
-    <t xml:space="preserve">59.0724143981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.2592735290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0201148986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9888153076172</t>
+    <t xml:space="preserve">59.0724105834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.2592697143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0201110839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.988826751709</t>
   </si>
   <si>
     <t xml:space="preserve">50.4148368835449</t>
   </si>
   <si>
-    <t xml:space="preserve">51.2279853820801</t>
+    <t xml:space="preserve">51.2279815673828</t>
   </si>
   <si>
     <t xml:space="preserve">51.3236465454102</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8931541442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7930221557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8408508300781</t>
+    <t xml:space="preserve">50.8931617736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.793025970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8408546447754</t>
   </si>
   <si>
     <t xml:space="preserve">48.6928939819336</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">49.2668724060059</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9843482971191</t>
+    <t xml:space="preserve">49.9843521118164</t>
   </si>
   <si>
     <t xml:space="preserve">49.9365196228027</t>
@@ -2003,25 +2003,25 @@
     <t xml:space="preserve">50.0800132751465</t>
   </si>
   <si>
-    <t xml:space="preserve">50.6539993286133</t>
+    <t xml:space="preserve">50.6540031433105</t>
   </si>
   <si>
     <t xml:space="preserve">50.2235107421875</t>
   </si>
   <si>
-    <t xml:space="preserve">50.845329284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4193077087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9409866333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.514965057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7974967956543</t>
+    <t xml:space="preserve">50.8453254699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.419303894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.940990447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5149688720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7974891662598</t>
   </si>
   <si>
     <t xml:space="preserve">51.1323165893555</t>
@@ -2033,31 +2033,31 @@
     <t xml:space="preserve">49.3147048950195</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4581985473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7451934814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0321846008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8363838195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.597225189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3625335693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0022315979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4282493591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.2892227172852</t>
+    <t xml:space="preserve">49.458194732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.745189666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0321807861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8363800048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5972213745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3625297546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0022354125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4282531738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.2892265319824</t>
   </si>
   <si>
     <t xml:space="preserve">54.1935577392578</t>
@@ -2066,40 +2066,40 @@
     <t xml:space="preserve">53.0934219360352</t>
   </si>
   <si>
-    <t xml:space="preserve">52.4716110229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2847557067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0978927612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9110336303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3370552062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8587303161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4805526733398</t>
+    <t xml:space="preserve">52.471607208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2847518920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0978965759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9110412597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3370513916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8587341308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4805488586426</t>
   </si>
   <si>
     <t xml:space="preserve">55.0545310974121</t>
   </si>
   <si>
-    <t xml:space="preserve">55.3415222167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.8676834106445</t>
+    <t xml:space="preserve">55.3415260314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.86767578125</t>
   </si>
   <si>
     <t xml:space="preserve">56.5373229980469</t>
   </si>
   <si>
-    <t xml:space="preserve">56.6329917907715</t>
+    <t xml:space="preserve">56.632984161377</t>
   </si>
   <si>
     <t xml:space="preserve">58.4027671813965</t>
@@ -2111,19 +2111,19 @@
     <t xml:space="preserve">59.6942291259766</t>
   </si>
   <si>
-    <t xml:space="preserve">59.3115730285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8511352539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6164436340332</t>
+    <t xml:space="preserve">59.3115692138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8511276245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6164512634277</t>
   </si>
   <si>
     <t xml:space="preserve">65.3383941650391</t>
   </si>
   <si>
-    <t xml:space="preserve">66.3428573608398</t>
+    <t xml:space="preserve">66.3428649902344</t>
   </si>
   <si>
     <t xml:space="preserve">66.9646835327148</t>
@@ -2132,40 +2132,40 @@
     <t xml:space="preserve">67.9213256835938</t>
   </si>
   <si>
-    <t xml:space="preserve">69.2606201171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.0692749023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.3951644897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.0169906616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.8690185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.2994995117188</t>
+    <t xml:space="preserve">69.260612487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.0692901611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.3951721191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.0169830322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.869026184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.2994918823242</t>
   </si>
   <si>
     <t xml:space="preserve">67.5386581420898</t>
   </si>
   <si>
-    <t xml:space="preserve">68.9257965087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.212776184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.4474639892578</t>
+    <t xml:space="preserve">68.9257888793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.2127838134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.4474716186523</t>
   </si>
   <si>
     <t xml:space="preserve">67.8734893798828</t>
   </si>
   <si>
-    <t xml:space="preserve">67.7778244018555</t>
+    <t xml:space="preserve">67.7778167724609</t>
   </si>
   <si>
     <t xml:space="preserve">67.0603408813477</t>
@@ -2177,16 +2177,16 @@
     <t xml:space="preserve">66.4385299682617</t>
   </si>
   <si>
-    <t xml:space="preserve">65.5775604248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.9123764038086</t>
+    <t xml:space="preserve">65.5775527954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.9123840332031</t>
   </si>
   <si>
     <t xml:space="preserve">67.2516784667969</t>
   </si>
   <si>
-    <t xml:space="preserve">67.8256607055664</t>
+    <t xml:space="preserve">67.8256454467773</t>
   </si>
   <si>
     <t xml:space="preserve">67.6343231201172</t>
@@ -2198,64 +2198,64 @@
     <t xml:space="preserve">66.1036987304688</t>
   </si>
   <si>
-    <t xml:space="preserve">69.4519424438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.2083129882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.3129272460938</t>
+    <t xml:space="preserve">69.4519348144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.2083206176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.3129196166992</t>
   </si>
   <si>
     <t xml:space="preserve">73.3263244628906</t>
   </si>
   <si>
-    <t xml:space="preserve">73.2306594848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.0916366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.6611404418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.3741455078125</t>
+    <t xml:space="preserve">73.2306671142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.0916290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.6611480712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.374153137207</t>
   </si>
   <si>
     <t xml:space="preserve">70.6955642700195</t>
   </si>
   <si>
-    <t xml:space="preserve">70.7912292480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.4653549194336</t>
+    <t xml:space="preserve">70.7912368774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.4653472900391</t>
   </si>
   <si>
     <t xml:space="preserve">70.2650756835938</t>
   </si>
   <si>
-    <t xml:space="preserve">68.638801574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3173828125</t>
+    <t xml:space="preserve">68.6387939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3173980712891</t>
   </si>
   <si>
     <t xml:space="preserve">71.9391937255859</t>
   </si>
   <si>
-    <t xml:space="preserve">72.7045059204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.7523498535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.6088485717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.4264678955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.1394653320312</t>
+    <t xml:space="preserve">72.7045135498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.7523422241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.6088638305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.4264602661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.1394577026367</t>
   </si>
   <si>
     <t xml:space="preserve">71.7478713989258</t>
@@ -2270,31 +2270,31 @@
     <t xml:space="preserve">71.4130477905273</t>
   </si>
   <si>
-    <t xml:space="preserve">66.8211898803711</t>
+    <t xml:space="preserve">66.8211822509766</t>
   </si>
   <si>
     <t xml:space="preserve">65.7210464477539</t>
   </si>
   <si>
-    <t xml:space="preserve">62.1336517333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.8077697753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8944892883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.937858581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.8766136169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.567268371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.0889549255371</t>
+    <t xml:space="preserve">62.1336479187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.8077735900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8944931030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9378662109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.8766174316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5672760009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.0889587402344</t>
   </si>
   <si>
     <t xml:space="preserve">46.3778228759766</t>
@@ -2306,70 +2306,70 @@
     <t xml:space="preserve">45.4594497680664</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7094306945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8714294433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2107238769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3446578979492</t>
+    <t xml:space="preserve">41.7094230651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8714370727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2107276916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.344654083252</t>
   </si>
   <si>
     <t xml:space="preserve">47.1048698425293</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0844879150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2190399169922</t>
+    <t xml:space="preserve">51.0844841003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2190361022949</t>
   </si>
   <si>
     <t xml:space="preserve">59.1680793762207</t>
   </si>
   <si>
-    <t xml:space="preserve">57.6852912902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.2637481689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.081356048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.3638763427734</t>
+    <t xml:space="preserve">57.6852874755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.2637405395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0813522338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.3638725280762</t>
   </si>
   <si>
     <t xml:space="preserve">61.1291847229004</t>
   </si>
   <si>
-    <t xml:space="preserve">61.4161758422852</t>
+    <t xml:space="preserve">61.4161720275879</t>
   </si>
   <si>
     <t xml:space="preserve">62.6598052978516</t>
   </si>
   <si>
-    <t xml:space="preserve">63.5207862854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5641403198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.1381225585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0424728393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.990161895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.0335235595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.2684860229492</t>
+    <t xml:space="preserve">63.5207901000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5641479492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.1381301879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0424690246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9901657104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.033519744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.2684898376465</t>
   </si>
   <si>
     <t xml:space="preserve">60.9081382751465</t>
@@ -2378,7 +2378,7 @@
     <t xml:space="preserve">61.7279586791992</t>
   </si>
   <si>
-    <t xml:space="preserve">63.705192565918</t>
+    <t xml:space="preserve">63.7051963806152</t>
   </si>
   <si>
     <t xml:space="preserve">64.7179107666016</t>
@@ -2387,19 +2387,19 @@
     <t xml:space="preserve">63.3676109313965</t>
   </si>
   <si>
-    <t xml:space="preserve">63.6569557189941</t>
+    <t xml:space="preserve">63.6569595336914</t>
   </si>
   <si>
     <t xml:space="preserve">64.0909805297852</t>
   </si>
   <si>
-    <t xml:space="preserve">64.4285583496094</t>
+    <t xml:space="preserve">64.4285659790039</t>
   </si>
   <si>
     <t xml:space="preserve">64.9108123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">68.4312362670898</t>
+    <t xml:space="preserve">68.4312286376953</t>
   </si>
   <si>
     <t xml:space="preserve">68.0936508178711</t>
@@ -2408,46 +2408,46 @@
     <t xml:space="preserve">68.3830108642578</t>
   </si>
   <si>
-    <t xml:space="preserve">68.624137878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.9744415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.3983917236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.1217727661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.9288787841797</t>
+    <t xml:space="preserve">68.6241302490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.9744338989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.3984069824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.1217880249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.9288864135742</t>
   </si>
   <si>
     <t xml:space="preserve">74.3628997802734</t>
   </si>
   <si>
-    <t xml:space="preserve">75.8578720092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.6522598266602</t>
+    <t xml:space="preserve">75.8578643798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.6522521972656</t>
   </si>
   <si>
     <t xml:space="preserve">71.8552017211914</t>
   </si>
   <si>
-    <t xml:space="preserve">70.6013565063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.1318206787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.2155609130859</t>
+    <t xml:space="preserve">70.6013488769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.1318283081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.2155532836914</t>
   </si>
   <si>
     <t xml:space="preserve">65.9235305786133</t>
   </si>
   <si>
-    <t xml:space="preserve">67.0326995849609</t>
+    <t xml:space="preserve">67.0327072143555</t>
   </si>
   <si>
     <t xml:space="preserve">67.2256088256836</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">66.5504608154297</t>
   </si>
   <si>
-    <t xml:space="preserve">67.3220520019531</t>
+    <t xml:space="preserve">67.3220596313477</t>
   </si>
   <si>
     <t xml:space="preserve">69.9262084960938</t>
@@ -2468,16 +2468,16 @@
     <t xml:space="preserve">71.1800537109375</t>
   </si>
   <si>
-    <t xml:space="preserve">70.408447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3729553222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.4921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.3120040893555</t>
+    <t xml:space="preserve">70.4084548950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3729629516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.4921798706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.31201171875</t>
   </si>
   <si>
     <t xml:space="preserve">68.5276870727539</t>
@@ -2486,70 +2486,70 @@
     <t xml:space="preserve">68.2865600585938</t>
   </si>
   <si>
-    <t xml:space="preserve">68.67236328125</t>
+    <t xml:space="preserve">68.6723556518555</t>
   </si>
   <si>
     <t xml:space="preserve">69.0099258422852</t>
   </si>
   <si>
-    <t xml:space="preserve">69.2992782592773</t>
+    <t xml:space="preserve">69.2992858886719</t>
   </si>
   <si>
     <t xml:space="preserve">72.1445541381836</t>
   </si>
   <si>
-    <t xml:space="preserve">71.276496887207</t>
+    <t xml:space="preserve">71.2765045166016</t>
   </si>
   <si>
     <t xml:space="preserve">71.8069763183594</t>
   </si>
   <si>
-    <t xml:space="preserve">70.1673355102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.5531311035156</t>
+    <t xml:space="preserve">70.1673278808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.5531387329102</t>
   </si>
   <si>
     <t xml:space="preserve">70.3602294921875</t>
   </si>
   <si>
-    <t xml:space="preserve">71.6623153686523</t>
+    <t xml:space="preserve">71.6623077392578</t>
   </si>
   <si>
     <t xml:space="preserve">72.3374557495117</t>
   </si>
   <si>
-    <t xml:space="preserve">72.8679351806641</t>
+    <t xml:space="preserve">72.8679428100586</t>
   </si>
   <si>
     <t xml:space="preserve">73.4466247558594</t>
   </si>
   <si>
-    <t xml:space="preserve">73.5430755615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9998779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.0608367919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.6877517700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.5913009643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.9643783569336</t>
+    <t xml:space="preserve">73.5430679321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.999885559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.0608291625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.6877593994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.59130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.9643859863281</t>
   </si>
   <si>
     <t xml:space="preserve">74.7487030029297</t>
   </si>
   <si>
-    <t xml:space="preserve">81.9342269897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.9469375610352</t>
+    <t xml:space="preserve">81.9342193603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.9469528198242</t>
   </si>
   <si>
     <t xml:space="preserve">85.117073059082</t>
@@ -2561,37 +2561,37 @@
     <t xml:space="preserve">85.3581924438477</t>
   </si>
   <si>
-    <t xml:space="preserve">83.1398468017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.017951965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0661773681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.609375</t>
+    <t xml:space="preserve">83.1398391723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0179443359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0661849975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.6093673706055</t>
   </si>
   <si>
     <t xml:space="preserve">80.8732757568359</t>
   </si>
   <si>
-    <t xml:space="preserve">83.0916213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3099594116211</t>
+    <t xml:space="preserve">83.0916290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3099746704102</t>
   </si>
   <si>
     <t xml:space="preserve">84.5865936279297</t>
   </si>
   <si>
-    <t xml:space="preserve">84.6348266601562</t>
+    <t xml:space="preserve">84.6348190307617</t>
   </si>
   <si>
     <t xml:space="preserve">83.6703186035156</t>
   </si>
   <si>
-    <t xml:space="preserve">84.7794952392578</t>
+    <t xml:space="preserve">84.7795028686523</t>
   </si>
   <si>
     <t xml:space="preserve">84.6830596923828</t>
@@ -2603,7 +2603,7 @@
     <t xml:space="preserve">86.2262496948242</t>
   </si>
   <si>
-    <t xml:space="preserve">87.7212142944336</t>
+    <t xml:space="preserve">87.7212219238281</t>
   </si>
   <si>
     <t xml:space="preserve">89.6984405517578</t>
@@ -2612,10 +2612,10 @@
     <t xml:space="preserve">89.3126449584961</t>
   </si>
   <si>
-    <t xml:space="preserve">90.6629486083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1070175170898</t>
+    <t xml:space="preserve">90.6629333496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1070098876953</t>
   </si>
   <si>
     <t xml:space="preserve">87.8658981323242</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">91.2416458129883</t>
   </si>
   <si>
-    <t xml:space="preserve">90.2771301269531</t>
+    <t xml:space="preserve">90.2771377563477</t>
   </si>
   <si>
     <t xml:space="preserve">90.5664901733398</t>
@@ -2633,7 +2633,7 @@
     <t xml:space="preserve">90.8076248168945</t>
   </si>
   <si>
-    <t xml:space="preserve">92.9777450561523</t>
+    <t xml:space="preserve">92.9777374267578</t>
   </si>
   <si>
     <t xml:space="preserve">95.0031890869141</t>
@@ -2642,31 +2642,31 @@
     <t xml:space="preserve">94.9067459106445</t>
   </si>
   <si>
-    <t xml:space="preserve">95.7265701293945</t>
+    <t xml:space="preserve">95.7265625</t>
   </si>
   <si>
     <t xml:space="preserve">93.2188720703125</t>
   </si>
   <si>
-    <t xml:space="preserve">93.5082244873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4827728271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.939567565918</t>
+    <t xml:space="preserve">93.5082168579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4827651977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9395751953125</t>
   </si>
   <si>
     <t xml:space="preserve">91.62744140625</t>
   </si>
   <si>
-    <t xml:space="preserve">92.1096878051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3635482788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.5336685180664</t>
+    <t xml:space="preserve">92.1096954345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3635559082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.5336761474609</t>
   </si>
   <si>
     <t xml:space="preserve">94.9549560546875</t>
@@ -2675,10 +2675,10 @@
     <t xml:space="preserve">94.8102874755859</t>
   </si>
   <si>
-    <t xml:space="preserve">93.6046752929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.5209350585938</t>
+    <t xml:space="preserve">93.6046676635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.5209426879883</t>
   </si>
   <si>
     <t xml:space="preserve">92.6883850097656</t>
@@ -2690,13 +2690,13 @@
     <t xml:space="preserve">93.0259628295898</t>
   </si>
   <si>
-    <t xml:space="preserve">95.2925415039062</t>
+    <t xml:space="preserve">95.2925338745117</t>
   </si>
   <si>
     <t xml:space="preserve">97.2215423583984</t>
   </si>
   <si>
-    <t xml:space="preserve">100.115043640137</t>
+    <t xml:space="preserve">100.115051269531</t>
   </si>
   <si>
     <t xml:space="preserve">99.7292327880859</t>
@@ -2711,73 +2711,73 @@
     <t xml:space="preserve">98.3789367675781</t>
   </si>
   <si>
-    <t xml:space="preserve">96.3052673339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.7493438720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.8330612182617</t>
+    <t xml:space="preserve">96.3052597045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7493362426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.8330688476562</t>
   </si>
   <si>
     <t xml:space="preserve">92.8812942504883</t>
   </si>
   <si>
-    <t xml:space="preserve">88.4445877075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.2034683227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.0232925415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.132453918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.2061386108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.4499435424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4372100830078</t>
+    <t xml:space="preserve">88.444580078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.2034606933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.023307800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.1324615478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.2061462402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.4499359130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4372177124023</t>
   </si>
   <si>
     <t xml:space="preserve">95.7747955322266</t>
   </si>
   <si>
-    <t xml:space="preserve">92.447265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.0614624023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.8685684204102</t>
+    <t xml:space="preserve">92.4472732543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.0614700317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.8685607910156</t>
   </si>
   <si>
     <t xml:space="preserve">91.8203430175781</t>
   </si>
   <si>
-    <t xml:space="preserve">90.7111663818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8558349609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3863296508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7593994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7694473266602</t>
+    <t xml:space="preserve">90.7111740112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.855842590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3863143920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7593841552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7694549560547</t>
   </si>
   <si>
     <t xml:space="preserve">88.2516937255859</t>
   </si>
   <si>
-    <t xml:space="preserve">89.3608779907227</t>
+    <t xml:space="preserve">89.3608627319336</t>
   </si>
   <si>
     <t xml:space="preserve">90.3735885620117</t>
@@ -2786,10 +2786,10 @@
     <t xml:space="preserve">94.2798233032227</t>
   </si>
   <si>
-    <t xml:space="preserve">90.0842437744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.1451873779297</t>
+    <t xml:space="preserve">90.0842514038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.1452026367188</t>
   </si>
   <si>
     <t xml:space="preserve">92.495491027832</t>
@@ -2804,34 +2804,34 @@
     <t xml:space="preserve">91.9168014526367</t>
   </si>
   <si>
-    <t xml:space="preserve">91.7238922119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.0969696044922</t>
+    <t xml:space="preserve">91.7238845825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.0969619750977</t>
   </si>
   <si>
     <t xml:space="preserve">90.9040679931641</t>
   </si>
   <si>
-    <t xml:space="preserve">92.3508148193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4599914550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.5437088012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9194641113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.2670822143555</t>
+    <t xml:space="preserve">92.3508224487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4599990844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.5437164306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9194564819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.26708984375</t>
   </si>
   <si>
     <t xml:space="preserve">93.5564422607422</t>
   </si>
   <si>
-    <t xml:space="preserve">94.5691680908203</t>
+    <t xml:space="preserve">94.5691757202148</t>
   </si>
   <si>
     <t xml:space="preserve">96.0641403198242</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">98.4753875732422</t>
   </si>
   <si>
-    <t xml:space="preserve">100.018585205078</t>
+    <t xml:space="preserve">100.018592834473</t>
   </si>
   <si>
     <t xml:space="preserve">98.1860504150391</t>
@@ -2867,34 +2867,34 @@
     <t xml:space="preserve">102.140487670898</t>
   </si>
   <si>
-    <t xml:space="preserve">104.937530517578</t>
+    <t xml:space="preserve">104.937538146973</t>
   </si>
   <si>
     <t xml:space="preserve">103.104988098145</t>
   </si>
   <si>
-    <t xml:space="preserve">103.58723449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.815628051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.201438903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.500831604004</t>
+    <t xml:space="preserve">103.587242126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.815635681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.201431274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.500839233398</t>
   </si>
   <si>
     <t xml:space="preserve">100.404388427734</t>
   </si>
   <si>
-    <t xml:space="preserve">98.5718383789062</t>
+    <t xml:space="preserve">98.5718307495117</t>
   </si>
   <si>
     <t xml:space="preserve">95.0514221191406</t>
   </si>
   <si>
-    <t xml:space="preserve">94.1351470947266</t>
+    <t xml:space="preserve">94.135139465332</t>
   </si>
   <si>
     <t xml:space="preserve">92.5919418334961</t>
@@ -2903,7 +2903,7 @@
     <t xml:space="preserve">89.216194152832</t>
   </si>
   <si>
-    <t xml:space="preserve">103.297897338867</t>
+    <t xml:space="preserve">103.297882080078</t>
   </si>
   <si>
     <t xml:space="preserve">99.3434371948242</t>
@@ -2912,10 +2912,10 @@
     <t xml:space="preserve">101.561790466309</t>
   </si>
   <si>
-    <t xml:space="preserve">103.973037719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.780128479004</t>
+    <t xml:space="preserve">103.973030090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.780136108398</t>
   </si>
   <si>
     <t xml:space="preserve">105.323333740234</t>
@@ -2924,13 +2924,13 @@
     <t xml:space="preserve">103.490791320801</t>
   </si>
   <si>
-    <t xml:space="preserve">104.069488525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.02392578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.145820617676</t>
+    <t xml:space="preserve">104.069480895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.023933410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.14582824707</t>
   </si>
   <si>
     <t xml:space="preserve">108.699073791504</t>
@@ -2948,19 +2948,19 @@
     <t xml:space="preserve">108.891983032227</t>
   </si>
   <si>
-    <t xml:space="preserve">107.831039428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.795539855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.08487701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.059425354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.348785400391</t>
+    <t xml:space="preserve">107.831024169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.795524597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.084884643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.059432983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.348793029785</t>
   </si>
   <si>
     <t xml:space="preserve">109.56713104248</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">108.50617980957</t>
   </si>
   <si>
-    <t xml:space="preserve">109.530754089355</t>
+    <t xml:space="preserve">109.53076171875</t>
   </si>
   <si>
     <t xml:space="preserve">107.786018371582</t>
@@ -2984,10 +2984,10 @@
     <t xml:space="preserve">109.918479919434</t>
   </si>
   <si>
-    <t xml:space="preserve">110.500068664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.82154083252</t>
+    <t xml:space="preserve">110.500053405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.821556091309</t>
   </si>
   <si>
     <t xml:space="preserve">110.88777923584</t>
@@ -3005,19 +3005,19 @@
     <t xml:space="preserve">113.795669555664</t>
   </si>
   <si>
-    <t xml:space="preserve">114.764976501465</t>
+    <t xml:space="preserve">114.76496887207</t>
   </si>
   <si>
     <t xml:space="preserve">114.668045043945</t>
   </si>
   <si>
-    <t xml:space="preserve">114.280319213867</t>
+    <t xml:space="preserve">114.280334472656</t>
   </si>
   <si>
     <t xml:space="preserve">114.474182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">116.509696960449</t>
+    <t xml:space="preserve">116.509712219238</t>
   </si>
   <si>
     <t xml:space="preserve">121.453140258789</t>
@@ -3038,13 +3038,13 @@
     <t xml:space="preserve">128.432083129883</t>
   </si>
   <si>
-    <t xml:space="preserve">133.181655883789</t>
+    <t xml:space="preserve">133.181640625</t>
   </si>
   <si>
     <t xml:space="preserve">130.467620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">130.273742675781</t>
+    <t xml:space="preserve">130.27375793457</t>
   </si>
   <si>
     <t xml:space="preserve">128.916732788086</t>
@@ -3053,7 +3053,7 @@
     <t xml:space="preserve">134.635589599609</t>
   </si>
   <si>
-    <t xml:space="preserve">135.70182800293</t>
+    <t xml:space="preserve">135.701812744141</t>
   </si>
   <si>
     <t xml:space="preserve">134.44172668457</t>
@@ -3068,10 +3068,10 @@
     <t xml:space="preserve">135.314102172852</t>
   </si>
   <si>
-    <t xml:space="preserve">136.574203491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.212356567383</t>
+    <t xml:space="preserve">136.574188232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.212341308594</t>
   </si>
   <si>
     <t xml:space="preserve">135.023315429688</t>
@@ -3080,7 +3080,7 @@
     <t xml:space="preserve">133.763229370117</t>
   </si>
   <si>
-    <t xml:space="preserve">137.446578979492</t>
+    <t xml:space="preserve">137.446563720703</t>
   </si>
   <si>
     <t xml:space="preserve">135.89567565918</t>
@@ -3089,13 +3089,13 @@
     <t xml:space="preserve">134.344818115234</t>
   </si>
   <si>
-    <t xml:space="preserve">138.22200012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142.293075561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.032974243164</t>
+    <t xml:space="preserve">138.222015380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142.293060302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.032958984375</t>
   </si>
   <si>
     <t xml:space="preserve">143.359268188477</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">136.671127319336</t>
   </si>
   <si>
-    <t xml:space="preserve">138.609710693359</t>
+    <t xml:space="preserve">138.609725952148</t>
   </si>
   <si>
     <t xml:space="preserve">135.992614746094</t>
@@ -3134,19 +3134,19 @@
     <t xml:space="preserve">141.226821899414</t>
   </si>
   <si>
-    <t xml:space="preserve">142.583862304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.905334472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.262344360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142.486923217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.073303222656</t>
+    <t xml:space="preserve">142.583847045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.905319213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.262359619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142.486907958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.073333740234</t>
   </si>
   <si>
     <t xml:space="preserve">148.884292602539</t>
@@ -3158,7 +3158,7 @@
     <t xml:space="preserve">149.175079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">149.75666809082</t>
+    <t xml:space="preserve">149.756652832031</t>
   </si>
   <si>
     <t xml:space="preserve">146.364105224609</t>
@@ -3173,22 +3173,22 @@
     <t xml:space="preserve">147.81803894043</t>
   </si>
   <si>
-    <t xml:space="preserve">150.532104492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.629028320312</t>
+    <t xml:space="preserve">150.532119750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.629013061523</t>
   </si>
   <si>
     <t xml:space="preserve">155.087799072266</t>
   </si>
   <si>
-    <t xml:space="preserve">154.893951416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.955337524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.89875793457</t>
+    <t xml:space="preserve">154.893936157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.955352783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.898773193359</t>
   </si>
   <si>
     <t xml:space="preserve">161.67903137207</t>
@@ -3197,22 +3197,22 @@
     <t xml:space="preserve">166.816314697266</t>
   </si>
   <si>
-    <t xml:space="preserve">166.428573608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.847030639648</t>
+    <t xml:space="preserve">166.428604125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.847015380859</t>
   </si>
   <si>
     <t xml:space="preserve">165.459289550781</t>
   </si>
   <si>
-    <t xml:space="preserve">165.65315246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.397888183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.851852416992</t>
+    <t xml:space="preserve">165.653137207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.397903442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.851837158203</t>
   </si>
   <si>
     <t xml:space="preserve">169.142639160156</t>
@@ -3221,22 +3221,22 @@
     <t xml:space="preserve">169.627288818359</t>
   </si>
   <si>
-    <t xml:space="preserve">170.305786132812</t>
+    <t xml:space="preserve">170.305770874023</t>
   </si>
   <si>
     <t xml:space="preserve">169.23957824707</t>
   </si>
   <si>
-    <t xml:space="preserve">169.724227905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.948776245117</t>
+    <t xml:space="preserve">169.724212646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.948791503906</t>
   </si>
   <si>
     <t xml:space="preserve">163.811477661133</t>
   </si>
   <si>
-    <t xml:space="preserve">167.204025268555</t>
+    <t xml:space="preserve">167.204040527344</t>
   </si>
   <si>
     <t xml:space="preserve">165.071578979492</t>
@@ -3245,7 +3245,7 @@
     <t xml:space="preserve">167.979476928711</t>
   </si>
   <si>
-    <t xml:space="preserve">173.989135742188</t>
+    <t xml:space="preserve">173.989120483398</t>
   </si>
   <si>
     <t xml:space="preserve">176.606231689453</t>
@@ -3254,7 +3254,7 @@
     <t xml:space="preserve">171.372024536133</t>
   </si>
   <si>
-    <t xml:space="preserve">152.470687866211</t>
+    <t xml:space="preserve">152.470672607422</t>
   </si>
   <si>
     <t xml:space="preserve">152.567611694336</t>
@@ -3263,19 +3263,19 @@
     <t xml:space="preserve">154.506210327148</t>
   </si>
   <si>
-    <t xml:space="preserve">153.827697753906</t>
+    <t xml:space="preserve">153.827713012695</t>
   </si>
   <si>
     <t xml:space="preserve">149.465866088867</t>
   </si>
   <si>
-    <t xml:space="preserve">153.633850097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.430358886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.721115112305</t>
+    <t xml:space="preserve">153.633865356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.43034362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.721130371094</t>
   </si>
   <si>
     <t xml:space="preserve">145.97639465332</t>
@@ -3287,13 +3287,13 @@
     <t xml:space="preserve">159.643508911133</t>
   </si>
   <si>
-    <t xml:space="preserve">162.842193603516</t>
+    <t xml:space="preserve">162.842178344727</t>
   </si>
   <si>
     <t xml:space="preserve">163.229904174805</t>
   </si>
   <si>
-    <t xml:space="preserve">160.418930053711</t>
+    <t xml:space="preserve">160.4189453125</t>
   </si>
   <si>
     <t xml:space="preserve">161.097457885742</t>
@@ -3305,43 +3305,43 @@
     <t xml:space="preserve">160.61279296875</t>
   </si>
   <si>
-    <t xml:space="preserve">161.582092285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.551391601562</t>
+    <t xml:space="preserve">161.582077026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.551406860352</t>
   </si>
   <si>
     <t xml:space="preserve">161.872894287109</t>
   </si>
   <si>
-    <t xml:space="preserve">164.393081665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.27507019043</t>
+    <t xml:space="preserve">164.39306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.275085449219</t>
   </si>
   <si>
     <t xml:space="preserve">173.213684082031</t>
   </si>
   <si>
-    <t xml:space="preserve">172.825973510742</t>
+    <t xml:space="preserve">172.825958251953</t>
   </si>
   <si>
     <t xml:space="preserve">174.182983398438</t>
   </si>
   <si>
-    <t xml:space="preserve">171.662811279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172.34130859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.703155517578</t>
+    <t xml:space="preserve">171.662826538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.341323852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.703170776367</t>
   </si>
   <si>
     <t xml:space="preserve">179.804916381836</t>
   </si>
   <si>
-    <t xml:space="preserve">173.892181396484</t>
+    <t xml:space="preserve">173.892196655273</t>
   </si>
   <si>
     <t xml:space="preserve">168.754928588867</t>
@@ -3350,25 +3350,25 @@
     <t xml:space="preserve">168.561050415039</t>
   </si>
   <si>
-    <t xml:space="preserve">167.010177612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.934295654297</t>
+    <t xml:space="preserve">167.010192871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.934280395508</t>
   </si>
   <si>
     <t xml:space="preserve">162.454467773438</t>
   </si>
   <si>
-    <t xml:space="preserve">159.837356567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">166.040878295898</t>
+    <t xml:space="preserve">159.837371826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">166.040863037109</t>
   </si>
   <si>
     <t xml:space="preserve">167.882537841797</t>
   </si>
   <si>
-    <t xml:space="preserve">160.709732055664</t>
+    <t xml:space="preserve">160.709747314453</t>
   </si>
   <si>
     <t xml:space="preserve">162.745254516602</t>
@@ -3380,13 +3380,13 @@
     <t xml:space="preserve">172.535171508789</t>
   </si>
   <si>
-    <t xml:space="preserve">174.958435058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.698348999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.570724487305</t>
+    <t xml:space="preserve">174.958404541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.698333740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.570709228516</t>
   </si>
   <si>
     <t xml:space="preserve">169.43342590332</t>
@@ -3401,28 +3401,28 @@
     <t xml:space="preserve">164.877731323242</t>
   </si>
   <si>
-    <t xml:space="preserve">163.714553833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.596588134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.821136474609</t>
+    <t xml:space="preserve">163.714538574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.596572875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.821151733398</t>
   </si>
   <si>
     <t xml:space="preserve">174.473785400391</t>
   </si>
   <si>
-    <t xml:space="preserve">164.005355834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.317184448242</t>
+    <t xml:space="preserve">164.005325317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.317199707031</t>
   </si>
   <si>
     <t xml:space="preserve">155.572448730469</t>
   </si>
   <si>
-    <t xml:space="preserve">155.863250732422</t>
+    <t xml:space="preserve">155.863235473633</t>
   </si>
   <si>
     <t xml:space="preserve">155.669387817383</t>
@@ -3431,10 +3431,10 @@
     <t xml:space="preserve">153.149200439453</t>
   </si>
   <si>
-    <t xml:space="preserve">151.016754150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.220245361328</t>
+    <t xml:space="preserve">151.016738891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.220260620117</t>
   </si>
   <si>
     <t xml:space="preserve">151.113677978516</t>
@@ -3443,19 +3443,19 @@
     <t xml:space="preserve">152.858413696289</t>
   </si>
   <si>
-    <t xml:space="preserve">154.990859985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.931228637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.747009277344</t>
+    <t xml:space="preserve">154.990875244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.931213378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.746994018555</t>
   </si>
   <si>
     <t xml:space="preserve">143.553146362305</t>
   </si>
   <si>
-    <t xml:space="preserve">144.522445678711</t>
+    <t xml:space="preserve">144.5224609375</t>
   </si>
   <si>
     <t xml:space="preserve">144.910171508789</t>
@@ -3464,19 +3464,19 @@
     <t xml:space="preserve">139.385162353516</t>
   </si>
   <si>
-    <t xml:space="preserve">136.089553833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.600082397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.309295654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.997421264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.834289550781</t>
+    <t xml:space="preserve">136.089538574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.600067138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.309280395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.997451782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.834274291992</t>
   </si>
   <si>
     <t xml:space="preserve">137.543487548828</t>
@@ -3488,10 +3488,10 @@
     <t xml:space="preserve">138.512771606445</t>
   </si>
   <si>
-    <t xml:space="preserve">142.680770874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.692169189453</t>
+    <t xml:space="preserve">142.680786132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.692184448242</t>
   </si>
   <si>
     <t xml:space="preserve">125.039535522461</t>
@@ -3503,10 +3503,10 @@
     <t xml:space="preserve">135.507965087891</t>
   </si>
   <si>
-    <t xml:space="preserve">142.874618530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.562789916992</t>
+    <t xml:space="preserve">142.874633789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.562805175781</t>
   </si>
   <si>
     <t xml:space="preserve">151.986053466797</t>
@@ -3524,16 +3524,16 @@
     <t xml:space="preserve">145.104019165039</t>
   </si>
   <si>
-    <t xml:space="preserve">148.690399169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.394821166992</t>
+    <t xml:space="preserve">148.690414428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.394805908203</t>
   </si>
   <si>
     <t xml:space="preserve">146.751831054688</t>
   </si>
   <si>
-    <t xml:space="preserve">149.659729003906</t>
+    <t xml:space="preserve">149.659713745117</t>
   </si>
   <si>
     <t xml:space="preserve">145.200958251953</t>
@@ -3548,7 +3548,7 @@
     <t xml:space="preserve">137.058837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">134.538665771484</t>
+    <t xml:space="preserve">134.538681030273</t>
   </si>
   <si>
     <t xml:space="preserve">136.477264404297</t>
@@ -3560,28 +3560,28 @@
     <t xml:space="preserve">136.186477661133</t>
   </si>
   <si>
-    <t xml:space="preserve">135.217193603516</t>
+    <t xml:space="preserve">135.217178344727</t>
   </si>
   <si>
     <t xml:space="preserve">130.952270507812</t>
   </si>
   <si>
-    <t xml:space="preserve">127.753593444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.162338256836</t>
+    <t xml:space="preserve">127.753578186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.16234588623</t>
   </si>
   <si>
     <t xml:space="preserve">113.601806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">117.285148620605</t>
+    <t xml:space="preserve">117.285140991211</t>
   </si>
   <si>
     <t xml:space="preserve">114.958824157715</t>
   </si>
   <si>
-    <t xml:space="preserve">117.575942993164</t>
+    <t xml:space="preserve">117.57593536377</t>
   </si>
   <si>
     <t xml:space="preserve">116.12198638916</t>
@@ -3593,7 +3593,7 @@
     <t xml:space="preserve">115.152694702148</t>
   </si>
   <si>
-    <t xml:space="preserve">114.861907958984</t>
+    <t xml:space="preserve">114.86190032959</t>
   </si>
   <si>
     <t xml:space="preserve">115.443481445312</t>
@@ -3632,13 +3632,13 @@
     <t xml:space="preserve">121.005844116211</t>
   </si>
   <si>
-    <t xml:space="preserve">114.857963562012</t>
+    <t xml:space="preserve">114.857971191406</t>
   </si>
   <si>
     <t xml:space="preserve">107.539054870605</t>
   </si>
   <si>
-    <t xml:space="preserve">102.367034912109</t>
+    <t xml:space="preserve">102.367042541504</t>
   </si>
   <si>
     <t xml:space="preserve">100.512916564941</t>
@@ -3650,13 +3650,13 @@
     <t xml:space="preserve">99.146728515625</t>
   </si>
   <si>
-    <t xml:space="preserve">103.147720336914</t>
+    <t xml:space="preserve">103.14771270752</t>
   </si>
   <si>
     <t xml:space="preserve">103.830825805664</t>
   </si>
   <si>
-    <t xml:space="preserve">106.07527923584</t>
+    <t xml:space="preserve">106.075286865234</t>
   </si>
   <si>
     <t xml:space="preserve">108.417335510254</t>
@@ -3665,22 +3665,22 @@
     <t xml:space="preserve">108.319747924805</t>
   </si>
   <si>
-    <t xml:space="preserve">112.418334960938</t>
+    <t xml:space="preserve">112.418327331543</t>
   </si>
   <si>
     <t xml:space="preserve">113.296600341797</t>
   </si>
   <si>
-    <t xml:space="preserve">115.541069030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.272445678711</t>
+    <t xml:space="preserve">115.541061401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.272453308105</t>
   </si>
   <si>
     <t xml:space="preserve">112.906257629395</t>
   </si>
   <si>
-    <t xml:space="preserve">113.882102966309</t>
+    <t xml:space="preserve">113.882110595703</t>
   </si>
   <si>
     <t xml:space="preserve">111.24730682373</t>
@@ -3689,7 +3689,7 @@
     <t xml:space="preserve">110.661796569824</t>
   </si>
   <si>
-    <t xml:space="preserve">116.321746826172</t>
+    <t xml:space="preserve">116.321739196777</t>
   </si>
   <si>
     <t xml:space="preserve">118.566207885742</t>
@@ -3701,7 +3701,7 @@
     <t xml:space="preserve">119.054130554199</t>
   </si>
   <si>
-    <t xml:space="preserve">118.95654296875</t>
+    <t xml:space="preserve">118.956550598145</t>
   </si>
   <si>
     <t xml:space="preserve">113.101432800293</t>
@@ -3710,10 +3710,10 @@
     <t xml:space="preserve">116.907257080078</t>
   </si>
   <si>
-    <t xml:space="preserve">122.469627380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.323745727539</t>
+    <t xml:space="preserve">122.469619750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.323753356934</t>
   </si>
   <si>
     <t xml:space="preserve">125.885108947754</t>
@@ -3755,7 +3755,7 @@
     <t xml:space="preserve">134.179870605469</t>
   </si>
   <si>
-    <t xml:space="preserve">127.544059753418</t>
+    <t xml:space="preserve">127.544067382812</t>
   </si>
   <si>
     <t xml:space="preserve">126.177871704102</t>
@@ -3764,10 +3764,10 @@
     <t xml:space="preserve">121.20100402832</t>
   </si>
   <si>
-    <t xml:space="preserve">120.420333862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.151718139648</t>
+    <t xml:space="preserve">120.42032623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.151710510254</t>
   </si>
   <si>
     <t xml:space="preserve">122.176864624023</t>
@@ -3776,16 +3776,16 @@
     <t xml:space="preserve">120.029991149902</t>
   </si>
   <si>
-    <t xml:space="preserve">115.736236572266</t>
+    <t xml:space="preserve">115.736228942871</t>
   </si>
   <si>
     <t xml:space="preserve">114.955558776855</t>
   </si>
   <si>
-    <t xml:space="preserve">110.271453857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.05313873291</t>
+    <t xml:space="preserve">110.271461486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.053146362305</t>
   </si>
   <si>
     <t xml:space="preserve">112.711090087891</t>
@@ -3827,16 +3827,16 @@
     <t xml:space="preserve">101.391189575195</t>
   </si>
   <si>
-    <t xml:space="preserve">104.904251098633</t>
+    <t xml:space="preserve">104.904258728027</t>
   </si>
   <si>
     <t xml:space="preserve">104.513916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">101.196022033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.001838684082</t>
+    <t xml:space="preserve">101.196014404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.001846313477</t>
   </si>
   <si>
     <t xml:space="preserve">107.734230041504</t>
@@ -3848,25 +3848,25 @@
     <t xml:space="preserve">115.150726318359</t>
   </si>
   <si>
-    <t xml:space="preserve">112.125579833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.75838470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.440483093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.270462036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.026985168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.100433349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.514923095703</t>
+    <t xml:space="preserve">112.12557220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.758377075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.440475463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.270454406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.026992797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.100425720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.514915466309</t>
   </si>
   <si>
     <t xml:space="preserve">107.636650085449</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">109.978691101074</t>
   </si>
   <si>
-    <t xml:space="preserve">108.612503051758</t>
+    <t xml:space="preserve">108.612510681152</t>
   </si>
   <si>
     <t xml:space="preserve">107.441474914551</t>
@@ -3887,7 +3887,7 @@
     <t xml:space="preserve">108.905258178711</t>
   </si>
   <si>
-    <t xml:space="preserve">109.685935974121</t>
+    <t xml:space="preserve">109.685943603516</t>
   </si>
   <si>
     <t xml:space="preserve">112.320739746094</t>
@@ -3902,13 +3902,13 @@
     <t xml:space="preserve">116.028991699219</t>
   </si>
   <si>
-    <t xml:space="preserve">110.076286315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.929412841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.223152160645</t>
+    <t xml:space="preserve">110.076278686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.929405212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.223159790039</t>
   </si>
   <si>
     <t xml:space="preserve">109.78352355957</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">109.588356018066</t>
   </si>
   <si>
-    <t xml:space="preserve">109.198013305664</t>
+    <t xml:space="preserve">109.198020935059</t>
   </si>
   <si>
     <t xml:space="preserve">110.759384155273</t>
@@ -3929,7 +3929,7 @@
     <t xml:space="preserve">117.200019836426</t>
   </si>
   <si>
-    <t xml:space="preserve">113.784523010254</t>
+    <t xml:space="preserve">113.784530639648</t>
   </si>
   <si>
     <t xml:space="preserve">105.587348937988</t>
@@ -3944,7 +3944,7 @@
     <t xml:space="preserve">105.099426269531</t>
   </si>
   <si>
-    <t xml:space="preserve">104.221168518066</t>
+    <t xml:space="preserve">104.221160888672</t>
   </si>
   <si>
     <t xml:space="preserve">106.465621948242</t>
@@ -3959,13 +3959,13 @@
     <t xml:space="preserve">107.343894958496</t>
   </si>
   <si>
-    <t xml:space="preserve">111.052146911621</t>
+    <t xml:space="preserve">111.052139282227</t>
   </si>
   <si>
     <t xml:space="preserve">114.467620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">116.419326782227</t>
+    <t xml:space="preserve">116.419334411621</t>
   </si>
   <si>
     <t xml:space="preserve">117.883117675781</t>
@@ -3974,16 +3974,16 @@
     <t xml:space="preserve">118.761375427246</t>
   </si>
   <si>
-    <t xml:space="preserve">115.93140411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.39518737793</t>
+    <t xml:space="preserve">115.931411743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.395195007324</t>
   </si>
   <si>
     <t xml:space="preserve">118.273452758789</t>
   </si>
   <si>
-    <t xml:space="preserve">114.760383605957</t>
+    <t xml:space="preserve">114.760375976562</t>
   </si>
   <si>
     <t xml:space="preserve">117.980697631836</t>
@@ -3995,31 +3995,31 @@
     <t xml:space="preserve">124.226165771484</t>
   </si>
   <si>
-    <t xml:space="preserve">123.152709960938</t>
+    <t xml:space="preserve">123.152717590332</t>
   </si>
   <si>
     <t xml:space="preserve">121.493766784668</t>
   </si>
   <si>
-    <t xml:space="preserve">118.663787841797</t>
+    <t xml:space="preserve">118.663795471191</t>
   </si>
   <si>
     <t xml:space="preserve">119.6396484375</t>
   </si>
   <si>
-    <t xml:space="preserve">118.85897064209</t>
+    <t xml:space="preserve">118.858963012695</t>
   </si>
   <si>
     <t xml:space="preserve">114.37003326416</t>
   </si>
   <si>
-    <t xml:space="preserve">112.515922546387</t>
+    <t xml:space="preserve">112.515930175781</t>
   </si>
   <si>
     <t xml:space="preserve">111.149719238281</t>
   </si>
   <si>
-    <t xml:space="preserve">113.199020385742</t>
+    <t xml:space="preserve">113.199012756348</t>
   </si>
   <si>
     <t xml:space="preserve">111.540069580078</t>
@@ -4028,7 +4028,7 @@
     <t xml:space="preserve">112.613510131836</t>
   </si>
   <si>
-    <t xml:space="preserve">108.124580383301</t>
+    <t xml:space="preserve">108.124588012695</t>
   </si>
   <si>
     <t xml:space="preserve">110.954551696777</t>
@@ -4040,13 +4040,13 @@
     <t xml:space="preserve">109.490768432617</t>
   </si>
   <si>
-    <t xml:space="preserve">107.148719787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.589363098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.88111114502</t>
+    <t xml:space="preserve">107.148727416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.58935546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.881103515625</t>
   </si>
   <si>
     <t xml:space="preserve">107.051132202148</t>
@@ -4058,19 +4058,19 @@
     <t xml:space="preserve">102.562210083008</t>
   </si>
   <si>
-    <t xml:space="preserve">102.464622497559</t>
+    <t xml:space="preserve">102.464630126953</t>
   </si>
   <si>
     <t xml:space="preserve">101.683944702148</t>
   </si>
   <si>
-    <t xml:space="preserve">102.952545166016</t>
+    <t xml:space="preserve">102.95255279541</t>
   </si>
   <si>
     <t xml:space="preserve">101.781532287598</t>
   </si>
   <si>
-    <t xml:space="preserve">100.610504150391</t>
+    <t xml:space="preserve">100.610496520996</t>
   </si>
   <si>
     <t xml:space="preserve">103.342895507812</t>
@@ -4079,16 +4079,16 @@
     <t xml:space="preserve">101.000839233398</t>
   </si>
   <si>
-    <t xml:space="preserve">100.415328979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.074287414551</t>
+    <t xml:space="preserve">100.415336608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.074279785156</t>
   </si>
   <si>
     <t xml:space="preserve">103.040893554688</t>
   </si>
   <si>
-    <t xml:space="preserve">103.237922668457</t>
+    <t xml:space="preserve">103.237915039062</t>
   </si>
   <si>
     <t xml:space="preserve">99.3960494995117</t>
@@ -4115,7 +4115,7 @@
     <t xml:space="preserve">103.139404296875</t>
   </si>
   <si>
-    <t xml:space="preserve">102.449836730957</t>
+    <t xml:space="preserve">102.449844360352</t>
   </si>
   <si>
     <t xml:space="preserve">102.351333618164</t>
@@ -4142,7 +4142,7 @@
     <t xml:space="preserve">109.641036987305</t>
   </si>
   <si>
-    <t xml:space="preserve">106.39022064209</t>
+    <t xml:space="preserve">106.390213012695</t>
   </si>
   <si>
     <t xml:space="preserve">101.267730712891</t>
@@ -4154,7 +4154,7 @@
     <t xml:space="preserve">99.1005172729492</t>
   </si>
   <si>
-    <t xml:space="preserve">98.0661697387695</t>
+    <t xml:space="preserve">98.0661773681641</t>
   </si>
   <si>
     <t xml:space="preserve">100.479652404785</t>
@@ -4172,10 +4172,10 @@
     <t xml:space="preserve">106.685752868652</t>
   </si>
   <si>
-    <t xml:space="preserve">104.420028686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.957298278809</t>
+    <t xml:space="preserve">104.420036315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.957290649414</t>
   </si>
   <si>
     <t xml:space="preserve">101.858787536621</t>
@@ -4190,16 +4190,16 @@
     <t xml:space="preserve">103.631950378418</t>
   </si>
   <si>
-    <t xml:space="preserve">99.4945602416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.7064743041992</t>
+    <t xml:space="preserve">99.4945526123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.7064819335938</t>
   </si>
   <si>
     <t xml:space="preserve">97.2288360595703</t>
   </si>
   <si>
-    <t xml:space="preserve">98.26318359375</t>
+    <t xml:space="preserve">98.2631912231445</t>
   </si>
   <si>
     <t xml:space="preserve">98.164680480957</t>
@@ -4214,22 +4214,22 @@
     <t xml:space="preserve">97.1303329467773</t>
   </si>
   <si>
-    <t xml:space="preserve">94.5198211669922</t>
+    <t xml:space="preserve">94.5198287963867</t>
   </si>
   <si>
     <t xml:space="preserve">95.9974670410156</t>
   </si>
   <si>
-    <t xml:space="preserve">94.7661056518555</t>
+    <t xml:space="preserve">94.7660980224609</t>
   </si>
   <si>
     <t xml:space="preserve">94.4213180541992</t>
   </si>
   <si>
-    <t xml:space="preserve">93.7317581176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0421905517578</t>
+    <t xml:space="preserve">93.7317504882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0421829223633</t>
   </si>
   <si>
     <t xml:space="preserve">92.2048568725586</t>
@@ -4238,7 +4238,7 @@
     <t xml:space="preserve">92.8451690673828</t>
   </si>
   <si>
-    <t xml:space="preserve">91.1212539672852</t>
+    <t xml:space="preserve">91.1212463378906</t>
   </si>
   <si>
     <t xml:space="preserve">91.9093322753906</t>
@@ -4247,7 +4247,7 @@
     <t xml:space="preserve">91.0719909667969</t>
   </si>
   <si>
-    <t xml:space="preserve">86.8853454589844</t>
+    <t xml:space="preserve">86.8853378295898</t>
   </si>
   <si>
     <t xml:space="preserve">86.7868347167969</t>
@@ -4256,7 +4256,7 @@
     <t xml:space="preserve">86.0972747802734</t>
   </si>
   <si>
-    <t xml:space="preserve">86.4913101196289</t>
+    <t xml:space="preserve">86.4913177490234</t>
   </si>
   <si>
     <t xml:space="preserve">87.8211898803711</t>
@@ -4271,22 +4271,22 @@
     <t xml:space="preserve">91.7123107910156</t>
   </si>
   <si>
-    <t xml:space="preserve">91.6630630493164</t>
+    <t xml:space="preserve">91.6630554199219</t>
   </si>
   <si>
     <t xml:space="preserve">92.1556015014648</t>
   </si>
   <si>
-    <t xml:space="preserve">91.1705093383789</t>
+    <t xml:space="preserve">91.1705169677734</t>
   </si>
   <si>
     <t xml:space="preserve">90.3331756591797</t>
   </si>
   <si>
-    <t xml:space="preserve">88.6585235595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.0331039428711</t>
+    <t xml:space="preserve">88.6585159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.0331115722656</t>
   </si>
   <si>
     <t xml:space="preserve">86.6883239746094</t>
@@ -4304,7 +4304,7 @@
     <t xml:space="preserve">87.4271469116211</t>
   </si>
   <si>
-    <t xml:space="preserve">86.9838562011719</t>
+    <t xml:space="preserve">86.9838638305664</t>
   </si>
   <si>
     <t xml:space="preserve">86.1465225219727</t>
@@ -4322,10 +4322,10 @@
     <t xml:space="preserve">81.1717987060547</t>
   </si>
   <si>
-    <t xml:space="preserve">84.9151611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.2255935668945</t>
+    <t xml:space="preserve">84.915153503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.2255859375</t>
   </si>
   <si>
     <t xml:space="preserve">87.7226791381836</t>
@@ -4334,19 +4334,19 @@
     <t xml:space="preserve">88.3137359619141</t>
   </si>
   <si>
-    <t xml:space="preserve">86.2942810058594</t>
+    <t xml:space="preserve">86.2942886352539</t>
   </si>
   <si>
     <t xml:space="preserve">88.2644805908203</t>
   </si>
   <si>
-    <t xml:space="preserve">87.6734161376953</t>
+    <t xml:space="preserve">87.6734237670898</t>
   </si>
   <si>
     <t xml:space="preserve">88.806282043457</t>
   </si>
   <si>
-    <t xml:space="preserve">89.003303527832</t>
+    <t xml:space="preserve">89.0032958984375</t>
   </si>
   <si>
     <t xml:space="preserve">92.1063461303711</t>
@@ -4355,7 +4355,7 @@
     <t xml:space="preserve">86.4420547485352</t>
   </si>
   <si>
-    <t xml:space="preserve">85.3584518432617</t>
+    <t xml:space="preserve">85.3584442138672</t>
   </si>
   <si>
     <t xml:space="preserve">83.3390045166016</t>
@@ -4370,13 +4370,13 @@
     <t xml:space="preserve">84.6688766479492</t>
   </si>
   <si>
-    <t xml:space="preserve">85.0136642456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.1763381958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.7823028564453</t>
+    <t xml:space="preserve">85.013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.1763305664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.7822952270508</t>
   </si>
   <si>
     <t xml:space="preserve">84.521125793457</t>
@@ -4388,10 +4388,10 @@
     <t xml:space="preserve">89.8898849487305</t>
   </si>
   <si>
-    <t xml:space="preserve">92.6481552124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3228073120117</t>
+    <t xml:space="preserve">92.6481475830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3228149414062</t>
   </si>
   <si>
     <t xml:space="preserve">92.3033676147461</t>
@@ -4409,13 +4409,13 @@
     <t xml:space="preserve">103.336433410645</t>
   </si>
   <si>
-    <t xml:space="preserve">101.661758422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.154312133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.71556854248</t>
+    <t xml:space="preserve">101.661766052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.154304504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.715560913086</t>
   </si>
   <si>
     <t xml:space="preserve">104.223014831543</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">102.942390441895</t>
   </si>
   <si>
-    <t xml:space="preserve">104.814071655273</t>
+    <t xml:space="preserve">104.814064025879</t>
   </si>
   <si>
     <t xml:space="preserve">105.602142333984</t>
@@ -4439,7 +4439,7 @@
     <t xml:space="preserve">105.306617736816</t>
   </si>
   <si>
-    <t xml:space="preserve">106.78426361084</t>
+    <t xml:space="preserve">106.784255981445</t>
   </si>
   <si>
     <t xml:space="preserve">108.557426452637</t>
@@ -4448,28 +4448,28 @@
     <t xml:space="preserve">108.951461791992</t>
   </si>
   <si>
-    <t xml:space="preserve">107.473815917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.778427124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.28588104248</t>
+    <t xml:space="preserve">107.473823547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.778434753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.285888671875</t>
   </si>
   <si>
     <t xml:space="preserve">111.808242797852</t>
   </si>
   <si>
-    <t xml:space="preserve">115.35457611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.029251098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.438179016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.521789550781</t>
+    <t xml:space="preserve">115.354583740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.029243469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.438186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.521797180176</t>
   </si>
   <si>
     <t xml:space="preserve">119.491981506348</t>
@@ -4484,7 +4484,7 @@
     <t xml:space="preserve">114.763519287109</t>
   </si>
   <si>
-    <t xml:space="preserve">112.30078125</t>
+    <t xml:space="preserve">112.300788879395</t>
   </si>
   <si>
     <t xml:space="preserve">112.596313476562</t>
@@ -4496,7 +4496,7 @@
     <t xml:space="preserve">115.847129821777</t>
   </si>
   <si>
-    <t xml:space="preserve">116.33967590332</t>
+    <t xml:space="preserve">116.339668273926</t>
   </si>
   <si>
     <t xml:space="preserve">118.112846374512</t>
@@ -4505,13 +4505,13 @@
     <t xml:space="preserve">119.886009216309</t>
   </si>
   <si>
-    <t xml:space="preserve">120.181541442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.787498474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.39347076416</t>
+    <t xml:space="preserve">120.181549072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.787506103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.393463134766</t>
   </si>
   <si>
     <t xml:space="preserve">121.757698059082</t>
@@ -4532,13 +4532,13 @@
     <t xml:space="preserve">125.10701751709</t>
   </si>
   <si>
-    <t xml:space="preserve">125.30403137207</t>
+    <t xml:space="preserve">125.304039001465</t>
   </si>
   <si>
     <t xml:space="preserve">125.599563598633</t>
   </si>
   <si>
-    <t xml:space="preserve">124.811485290527</t>
+    <t xml:space="preserve">124.811492919922</t>
   </si>
   <si>
     <t xml:space="preserve">125.008506774902</t>
@@ -4550,16 +4550,16 @@
     <t xml:space="preserve">126.584663391113</t>
   </si>
   <si>
-    <t xml:space="preserve">123.727882385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.796585083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.121925354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.462173461914</t>
+    <t xml:space="preserve">123.727890014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.796577453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.121917724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.46216583252</t>
   </si>
   <si>
     <t xml:space="preserve">120.280052185059</t>
@@ -4568,7 +4568,7 @@
     <t xml:space="preserve">121.659187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">120.575584411621</t>
+    <t xml:space="preserve">120.575576782227</t>
   </si>
   <si>
     <t xml:space="preserve">122.64427947998</t>
@@ -4577,7 +4577,7 @@
     <t xml:space="preserve">122.742790222168</t>
   </si>
   <si>
-    <t xml:space="preserve">125.205528259277</t>
+    <t xml:space="preserve">125.205520629883</t>
   </si>
   <si>
     <t xml:space="preserve">126.190628051758</t>
@@ -4592,10 +4592,10 @@
     <t xml:space="preserve">123.235336303711</t>
   </si>
   <si>
-    <t xml:space="preserve">124.515968322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.151741027832</t>
+    <t xml:space="preserve">124.515960693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.151733398438</t>
   </si>
   <si>
     <t xml:space="preserve">122.841300964355</t>
@@ -4610,10 +4610,10 @@
     <t xml:space="preserve">130.032501220703</t>
   </si>
   <si>
-    <t xml:space="preserve">130.820571899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.722061157227</t>
+    <t xml:space="preserve">130.820556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.722045898438</t>
   </si>
   <si>
     <t xml:space="preserve">129.835479736328</t>
@@ -4628,7 +4628,7 @@
     <t xml:space="preserve">127.569747924805</t>
   </si>
   <si>
-    <t xml:space="preserve">127.668266296387</t>
+    <t xml:space="preserve">127.668258666992</t>
   </si>
   <si>
     <t xml:space="preserve">129.244415283203</t>
@@ -4640,7 +4640,7 @@
     <t xml:space="preserve">130.131011962891</t>
   </si>
   <si>
-    <t xml:space="preserve">129.441436767578</t>
+    <t xml:space="preserve">129.441421508789</t>
   </si>
   <si>
     <t xml:space="preserve">126.486145019531</t>
@@ -4649,22 +4649,22 @@
     <t xml:space="preserve">128.16081237793</t>
   </si>
   <si>
-    <t xml:space="preserve">126.387641906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.909996032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.053230285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.265144348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.25023651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.166633605957</t>
+    <t xml:space="preserve">126.387649536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.910003662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.05322265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.265151977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.250244140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.166641235352</t>
   </si>
   <si>
     <t xml:space="preserve">133.677337646484</t>
@@ -4673,7 +4673,7 @@
     <t xml:space="preserve">131.116104125977</t>
   </si>
   <si>
-    <t xml:space="preserve">134.760955810547</t>
+    <t xml:space="preserve">134.760940551758</t>
   </si>
   <si>
     <t xml:space="preserve">135.058654785156</t>
@@ -4778,9 +4778,6 @@
     <t xml:space="preserve">134.860168457031</t>
   </si>
   <si>
-    <t xml:space="preserve">134.760940551758</t>
-  </si>
-  <si>
     <t xml:space="preserve">136.944107055664</t>
   </si>
   <si>
@@ -5466,6 +5463,9 @@
   </si>
   <si>
     <t xml:space="preserve">121.099998474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.199996948242</t>
   </si>
 </sst>
 </file>
@@ -62398,7 +62398,7 @@
         <v>135.800003051758</v>
       </c>
       <c r="G2177" t="s">
-        <v>1588</v>
+        <v>1553</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -62424,7 +62424,7 @@
         <v>138</v>
       </c>
       <c r="G2178" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -62476,7 +62476,7 @@
         <v>135.800003051758</v>
       </c>
       <c r="G2180" t="s">
-        <v>1588</v>
+        <v>1553</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -62502,7 +62502,7 @@
         <v>132.699996948242</v>
       </c>
       <c r="G2181" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -62528,7 +62528,7 @@
         <v>133.100006103516</v>
       </c>
       <c r="G2182" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -62554,7 +62554,7 @@
         <v>131.800003051758</v>
       </c>
       <c r="G2183" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -62580,7 +62580,7 @@
         <v>131.800003051758</v>
       </c>
       <c r="G2184" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -62606,7 +62606,7 @@
         <v>131.199996948242</v>
       </c>
       <c r="G2185" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -62632,7 +62632,7 @@
         <v>129</v>
       </c>
       <c r="G2186" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -62658,7 +62658,7 @@
         <v>126.599998474121</v>
       </c>
       <c r="G2187" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -62684,7 +62684,7 @@
         <v>124.300003051758</v>
       </c>
       <c r="G2188" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -62710,7 +62710,7 @@
         <v>125.099998474121</v>
       </c>
       <c r="G2189" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -62736,7 +62736,7 @@
         <v>125.599998474121</v>
       </c>
       <c r="G2190" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -62762,7 +62762,7 @@
         <v>124.900001525879</v>
       </c>
       <c r="G2191" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -62788,7 +62788,7 @@
         <v>127.199996948242</v>
       </c>
       <c r="G2192" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -62840,7 +62840,7 @@
         <v>129.899993896484</v>
       </c>
       <c r="G2194" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -62866,7 +62866,7 @@
         <v>131.5</v>
       </c>
       <c r="G2195" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -62918,7 +62918,7 @@
         <v>135.300003051758</v>
       </c>
       <c r="G2197" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -62970,7 +62970,7 @@
         <v>138.699996948242</v>
       </c>
       <c r="G2199" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -63048,7 +63048,7 @@
         <v>140.899993896484</v>
       </c>
       <c r="G2202" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -63126,7 +63126,7 @@
         <v>141.800003051758</v>
       </c>
       <c r="G2205" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -63152,7 +63152,7 @@
         <v>142.699996948242</v>
       </c>
       <c r="G2206" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -63178,7 +63178,7 @@
         <v>141</v>
       </c>
       <c r="G2207" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -63204,7 +63204,7 @@
         <v>140.699996948242</v>
       </c>
       <c r="G2208" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -63282,7 +63282,7 @@
         <v>134</v>
       </c>
       <c r="G2211" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -63308,7 +63308,7 @@
         <v>134.899993896484</v>
       </c>
       <c r="G2212" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -63334,7 +63334,7 @@
         <v>135</v>
       </c>
       <c r="G2213" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -63360,7 +63360,7 @@
         <v>135.100006103516</v>
       </c>
       <c r="G2214" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -63438,7 +63438,7 @@
         <v>135.699996948242</v>
       </c>
       <c r="G2217" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -63464,7 +63464,7 @@
         <v>137.100006103516</v>
       </c>
       <c r="G2218" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -63490,7 +63490,7 @@
         <v>134.899993896484</v>
       </c>
       <c r="G2219" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -63516,7 +63516,7 @@
         <v>136.899993896484</v>
       </c>
       <c r="G2220" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -63542,7 +63542,7 @@
         <v>135.5</v>
       </c>
       <c r="G2221" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -63568,7 +63568,7 @@
         <v>135.800003051758</v>
       </c>
       <c r="G2222" t="s">
-        <v>1588</v>
+        <v>1553</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -63620,7 +63620,7 @@
         <v>134.800003051758</v>
       </c>
       <c r="G2224" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -63646,7 +63646,7 @@
         <v>136.699996948242</v>
       </c>
       <c r="G2225" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -63672,7 +63672,7 @@
         <v>136.800003051758</v>
       </c>
       <c r="G2226" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -63724,7 +63724,7 @@
         <v>132.899993896484</v>
       </c>
       <c r="G2228" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -63750,7 +63750,7 @@
         <v>134</v>
       </c>
       <c r="G2229" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -63776,7 +63776,7 @@
         <v>132</v>
       </c>
       <c r="G2230" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -63802,7 +63802,7 @@
         <v>132</v>
       </c>
       <c r="G2231" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -63828,7 +63828,7 @@
         <v>131.800003051758</v>
       </c>
       <c r="G2232" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -63854,7 +63854,7 @@
         <v>131.600006103516</v>
       </c>
       <c r="G2233" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -63880,7 +63880,7 @@
         <v>135.699996948242</v>
       </c>
       <c r="G2234" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -63958,7 +63958,7 @@
         <v>138.300003051758</v>
       </c>
       <c r="G2237" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -64010,7 +64010,7 @@
         <v>139.399993896484</v>
       </c>
       <c r="G2239" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -64036,7 +64036,7 @@
         <v>141</v>
       </c>
       <c r="G2240" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -64062,7 +64062,7 @@
         <v>143.100006103516</v>
       </c>
       <c r="G2241" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -64088,7 +64088,7 @@
         <v>142.100006103516</v>
       </c>
       <c r="G2242" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -64114,7 +64114,7 @@
         <v>143.399993896484</v>
       </c>
       <c r="G2243" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -64140,7 +64140,7 @@
         <v>143.199996948242</v>
       </c>
       <c r="G2244" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -64166,7 +64166,7 @@
         <v>147.300003051758</v>
       </c>
       <c r="G2245" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -64192,7 +64192,7 @@
         <v>143.300003051758</v>
       </c>
       <c r="G2246" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -64218,7 +64218,7 @@
         <v>144.600006103516</v>
       </c>
       <c r="G2247" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -64244,7 +64244,7 @@
         <v>142.899993896484</v>
       </c>
       <c r="G2248" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -64270,7 +64270,7 @@
         <v>143</v>
       </c>
       <c r="G2249" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -64296,7 +64296,7 @@
         <v>140.300003051758</v>
       </c>
       <c r="G2250" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -64322,7 +64322,7 @@
         <v>142</v>
       </c>
       <c r="G2251" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -64348,7 +64348,7 @@
         <v>139.100006103516</v>
       </c>
       <c r="G2252" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -64374,7 +64374,7 @@
         <v>139.300003051758</v>
       </c>
       <c r="G2253" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -64400,7 +64400,7 @@
         <v>136.899993896484</v>
       </c>
       <c r="G2254" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -64426,7 +64426,7 @@
         <v>140.5</v>
       </c>
       <c r="G2255" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -64452,7 +64452,7 @@
         <v>140.300003051758</v>
       </c>
       <c r="G2256" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -64478,7 +64478,7 @@
         <v>143.300003051758</v>
       </c>
       <c r="G2257" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -64504,7 +64504,7 @@
         <v>141.800003051758</v>
       </c>
       <c r="G2258" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -64556,7 +64556,7 @@
         <v>150.800003051758</v>
       </c>
       <c r="G2260" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -64582,7 +64582,7 @@
         <v>152.800003051758</v>
       </c>
       <c r="G2261" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -64608,7 +64608,7 @@
         <v>152.300003051758</v>
       </c>
       <c r="G2262" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -64634,7 +64634,7 @@
         <v>153.899993896484</v>
       </c>
       <c r="G2263" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -64660,7 +64660,7 @@
         <v>152.899993896484</v>
       </c>
       <c r="G2264" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -64686,7 +64686,7 @@
         <v>154.600006103516</v>
       </c>
       <c r="G2265" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -64712,7 +64712,7 @@
         <v>149.899993896484</v>
       </c>
       <c r="G2266" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -64738,7 +64738,7 @@
         <v>153.399993896484</v>
       </c>
       <c r="G2267" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -64764,7 +64764,7 @@
         <v>152.300003051758</v>
       </c>
       <c r="G2268" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -64790,7 +64790,7 @@
         <v>150.399993896484</v>
       </c>
       <c r="G2269" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -64816,7 +64816,7 @@
         <v>150.899993896484</v>
       </c>
       <c r="G2270" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -64842,7 +64842,7 @@
         <v>151.5</v>
       </c>
       <c r="G2271" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -64868,7 +64868,7 @@
         <v>151.5</v>
       </c>
       <c r="G2272" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -64894,7 +64894,7 @@
         <v>152.699996948242</v>
       </c>
       <c r="G2273" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -64920,7 +64920,7 @@
         <v>157.100006103516</v>
       </c>
       <c r="G2274" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -64946,7 +64946,7 @@
         <v>155.5</v>
       </c>
       <c r="G2275" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -64972,7 +64972,7 @@
         <v>156.899993896484</v>
       </c>
       <c r="G2276" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -64998,7 +64998,7 @@
         <v>154.199996948242</v>
       </c>
       <c r="G2277" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -65024,7 +65024,7 @@
         <v>154.899993896484</v>
       </c>
       <c r="G2278" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -65050,7 +65050,7 @@
         <v>157.800003051758</v>
       </c>
       <c r="G2279" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -65076,7 +65076,7 @@
         <v>155</v>
       </c>
       <c r="G2280" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -65102,7 +65102,7 @@
         <v>156</v>
       </c>
       <c r="G2281" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -65128,7 +65128,7 @@
         <v>155.600006103516</v>
       </c>
       <c r="G2282" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -65154,7 +65154,7 @@
         <v>156.800003051758</v>
       </c>
       <c r="G2283" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -65180,7 +65180,7 @@
         <v>156.399993896484</v>
       </c>
       <c r="G2284" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -65206,7 +65206,7 @@
         <v>152.300003051758</v>
       </c>
       <c r="G2285" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -65232,7 +65232,7 @@
         <v>155</v>
       </c>
       <c r="G2286" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -65258,7 +65258,7 @@
         <v>153.600006103516</v>
       </c>
       <c r="G2287" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -65284,7 +65284,7 @@
         <v>155.5</v>
       </c>
       <c r="G2288" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -65310,7 +65310,7 @@
         <v>153.399993896484</v>
       </c>
       <c r="G2289" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -65336,7 +65336,7 @@
         <v>155.800003051758</v>
       </c>
       <c r="G2290" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -65362,7 +65362,7 @@
         <v>154.800003051758</v>
       </c>
       <c r="G2291" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -65388,7 +65388,7 @@
         <v>157.600006103516</v>
       </c>
       <c r="G2292" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -65414,7 +65414,7 @@
         <v>157.800003051758</v>
       </c>
       <c r="G2293" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -65440,7 +65440,7 @@
         <v>152.199996948242</v>
       </c>
       <c r="G2294" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -65466,7 +65466,7 @@
         <v>149.5</v>
       </c>
       <c r="G2295" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -65492,7 +65492,7 @@
         <v>148.100006103516</v>
       </c>
       <c r="G2296" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -65518,7 +65518,7 @@
         <v>146.199996948242</v>
       </c>
       <c r="G2297" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -65544,7 +65544,7 @@
         <v>144.800003051758</v>
       </c>
       <c r="G2298" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -65570,7 +65570,7 @@
         <v>149.699996948242</v>
       </c>
       <c r="G2299" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -65596,7 +65596,7 @@
         <v>151</v>
       </c>
       <c r="G2300" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -65622,7 +65622,7 @@
         <v>150.5</v>
       </c>
       <c r="G2301" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -65648,7 +65648,7 @@
         <v>151.600006103516</v>
       </c>
       <c r="G2302" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -65674,7 +65674,7 @@
         <v>152.600006103516</v>
       </c>
       <c r="G2303" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -65700,7 +65700,7 @@
         <v>155.600006103516</v>
       </c>
       <c r="G2304" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -65726,7 +65726,7 @@
         <v>153.699996948242</v>
       </c>
       <c r="G2305" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -65752,7 +65752,7 @@
         <v>155.899993896484</v>
       </c>
       <c r="G2306" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -65778,7 +65778,7 @@
         <v>153.699996948242</v>
       </c>
       <c r="G2307" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -65804,7 +65804,7 @@
         <v>156.300003051758</v>
       </c>
       <c r="G2308" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -65830,7 +65830,7 @@
         <v>157.699996948242</v>
       </c>
       <c r="G2309" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -65856,7 +65856,7 @@
         <v>157.199996948242</v>
       </c>
       <c r="G2310" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -65882,7 +65882,7 @@
         <v>159.600006103516</v>
       </c>
       <c r="G2311" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -65908,7 +65908,7 @@
         <v>158.100006103516</v>
       </c>
       <c r="G2312" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -65934,7 +65934,7 @@
         <v>158</v>
       </c>
       <c r="G2313" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -65960,7 +65960,7 @@
         <v>158.199996948242</v>
       </c>
       <c r="G2314" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -65986,7 +65986,7 @@
         <v>161.399993896484</v>
       </c>
       <c r="G2315" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -66012,7 +66012,7 @@
         <v>159.800003051758</v>
       </c>
       <c r="G2316" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -66038,7 +66038,7 @@
         <v>160.100006103516</v>
       </c>
       <c r="G2317" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -66064,7 +66064,7 @@
         <v>159.800003051758</v>
       </c>
       <c r="G2318" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -66090,7 +66090,7 @@
         <v>161.300003051758</v>
       </c>
       <c r="G2319" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -66116,7 +66116,7 @@
         <v>164.100006103516</v>
       </c>
       <c r="G2320" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -66142,7 +66142,7 @@
         <v>163.699996948242</v>
       </c>
       <c r="G2321" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -66168,7 +66168,7 @@
         <v>165.300003051758</v>
       </c>
       <c r="G2322" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -66194,7 +66194,7 @@
         <v>164.399993896484</v>
       </c>
       <c r="G2323" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -66220,7 +66220,7 @@
         <v>159.600006103516</v>
       </c>
       <c r="G2324" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -66246,7 +66246,7 @@
         <v>158.399993896484</v>
       </c>
       <c r="G2325" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -66272,7 +66272,7 @@
         <v>159.699996948242</v>
       </c>
       <c r="G2326" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -66298,7 +66298,7 @@
         <v>158</v>
       </c>
       <c r="G2327" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -66324,7 +66324,7 @@
         <v>157.899993896484</v>
       </c>
       <c r="G2328" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -66350,7 +66350,7 @@
         <v>157.5</v>
       </c>
       <c r="G2329" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -66376,7 +66376,7 @@
         <v>156.699996948242</v>
       </c>
       <c r="G2330" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -66402,7 +66402,7 @@
         <v>154.199996948242</v>
       </c>
       <c r="G2331" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -66428,7 +66428,7 @@
         <v>154.800003051758</v>
       </c>
       <c r="G2332" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -66454,7 +66454,7 @@
         <v>150</v>
       </c>
       <c r="G2333" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -66480,7 +66480,7 @@
         <v>153.5</v>
       </c>
       <c r="G2334" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -66506,7 +66506,7 @@
         <v>153.899993896484</v>
       </c>
       <c r="G2335" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -66532,7 +66532,7 @@
         <v>153.800003051758</v>
       </c>
       <c r="G2336" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -66558,7 +66558,7 @@
         <v>153.300003051758</v>
       </c>
       <c r="G2337" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -66584,7 +66584,7 @@
         <v>146.199996948242</v>
       </c>
       <c r="G2338" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -66610,7 +66610,7 @@
         <v>149.100006103516</v>
       </c>
       <c r="G2339" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -66636,7 +66636,7 @@
         <v>157.199996948242</v>
       </c>
       <c r="G2340" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -66662,7 +66662,7 @@
         <v>164</v>
       </c>
       <c r="G2341" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -66688,7 +66688,7 @@
         <v>164.100006103516</v>
       </c>
       <c r="G2342" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -66714,7 +66714,7 @@
         <v>165.399993896484</v>
       </c>
       <c r="G2343" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -66740,7 +66740,7 @@
         <v>167.5</v>
       </c>
       <c r="G2344" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -66766,7 +66766,7 @@
         <v>164.699996948242</v>
       </c>
       <c r="G2345" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -66792,7 +66792,7 @@
         <v>163.100006103516</v>
       </c>
       <c r="G2346" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -66818,7 +66818,7 @@
         <v>162.699996948242</v>
       </c>
       <c r="G2347" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -66844,7 +66844,7 @@
         <v>163.699996948242</v>
       </c>
       <c r="G2348" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -66870,7 +66870,7 @@
         <v>160.600006103516</v>
       </c>
       <c r="G2349" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -66896,7 +66896,7 @@
         <v>159.5</v>
       </c>
       <c r="G2350" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -66922,7 +66922,7 @@
         <v>156.600006103516</v>
       </c>
       <c r="G2351" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -66948,7 +66948,7 @@
         <v>150.800003051758</v>
       </c>
       <c r="G2352" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -66974,7 +66974,7 @@
         <v>153</v>
       </c>
       <c r="G2353" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -67000,7 +67000,7 @@
         <v>152.899993896484</v>
       </c>
       <c r="G2354" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -67026,7 +67026,7 @@
         <v>147.600006103516</v>
       </c>
       <c r="G2355" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -67052,7 +67052,7 @@
         <v>143.800003051758</v>
       </c>
       <c r="G2356" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -67104,7 +67104,7 @@
         <v>141.800003051758</v>
       </c>
       <c r="G2358" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -67130,7 +67130,7 @@
         <v>135.5</v>
       </c>
       <c r="G2359" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -67156,7 +67156,7 @@
         <v>142.899993896484</v>
       </c>
       <c r="G2360" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -67182,7 +67182,7 @@
         <v>143.800003051758</v>
       </c>
       <c r="G2361" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -67208,7 +67208,7 @@
         <v>146.899993896484</v>
       </c>
       <c r="G2362" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -67234,7 +67234,7 @@
         <v>149</v>
       </c>
       <c r="G2363" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -67260,7 +67260,7 @@
         <v>149.699996948242</v>
       </c>
       <c r="G2364" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -67286,7 +67286,7 @@
         <v>148.899993896484</v>
       </c>
       <c r="G2365" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -67312,7 +67312,7 @@
         <v>147.399993896484</v>
       </c>
       <c r="G2366" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -67338,7 +67338,7 @@
         <v>150.800003051758</v>
       </c>
       <c r="G2367" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -67364,7 +67364,7 @@
         <v>149.399993896484</v>
       </c>
       <c r="G2368" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -67390,7 +67390,7 @@
         <v>149.399993896484</v>
       </c>
       <c r="G2369" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -67416,7 +67416,7 @@
         <v>151.899993896484</v>
       </c>
       <c r="G2370" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -67442,7 +67442,7 @@
         <v>153.600006103516</v>
       </c>
       <c r="G2371" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -67468,7 +67468,7 @@
         <v>156.800003051758</v>
       </c>
       <c r="G2372" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -67494,7 +67494,7 @@
         <v>158.699996948242</v>
       </c>
       <c r="G2373" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -67520,7 +67520,7 @@
         <v>157.699996948242</v>
       </c>
       <c r="G2374" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -67546,7 +67546,7 @@
         <v>158.899993896484</v>
       </c>
       <c r="G2375" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -67572,7 +67572,7 @@
         <v>156.399993896484</v>
       </c>
       <c r="G2376" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -67598,7 +67598,7 @@
         <v>159.600006103516</v>
       </c>
       <c r="G2377" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -67624,7 +67624,7 @@
         <v>161.600006103516</v>
       </c>
       <c r="G2378" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -67650,7 +67650,7 @@
         <v>157.600006103516</v>
       </c>
       <c r="G2379" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -67676,7 +67676,7 @@
         <v>154.100006103516</v>
       </c>
       <c r="G2380" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -67702,7 +67702,7 @@
         <v>150.699996948242</v>
       </c>
       <c r="G2381" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -67728,7 +67728,7 @@
         <v>150.600006103516</v>
       </c>
       <c r="G2382" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -67754,7 +67754,7 @@
         <v>150.300003051758</v>
       </c>
       <c r="G2383" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -67780,7 +67780,7 @@
         <v>147.5</v>
       </c>
       <c r="G2384" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -67806,7 +67806,7 @@
         <v>147.100006103516</v>
       </c>
       <c r="G2385" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -67832,7 +67832,7 @@
         <v>147</v>
       </c>
       <c r="G2386" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -67858,7 +67858,7 @@
         <v>144.5</v>
       </c>
       <c r="G2387" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -67884,7 +67884,7 @@
         <v>142.899993896484</v>
       </c>
       <c r="G2388" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -67910,7 +67910,7 @@
         <v>146.5</v>
       </c>
       <c r="G2389" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -67936,7 +67936,7 @@
         <v>145.300003051758</v>
       </c>
       <c r="G2390" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -67962,7 +67962,7 @@
         <v>148.199996948242</v>
       </c>
       <c r="G2391" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -67988,7 +67988,7 @@
         <v>147</v>
       </c>
       <c r="G2392" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -68014,7 +68014,7 @@
         <v>148.5</v>
       </c>
       <c r="G2393" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -68040,7 +68040,7 @@
         <v>146.100006103516</v>
       </c>
       <c r="G2394" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -68066,7 +68066,7 @@
         <v>146.5</v>
       </c>
       <c r="G2395" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -68092,7 +68092,7 @@
         <v>148.399993896484</v>
       </c>
       <c r="G2396" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -68118,7 +68118,7 @@
         <v>150.399993896484</v>
       </c>
       <c r="G2397" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -68144,7 +68144,7 @@
         <v>149.100006103516</v>
       </c>
       <c r="G2398" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -68170,7 +68170,7 @@
         <v>149.300003051758</v>
       </c>
       <c r="G2399" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -68196,7 +68196,7 @@
         <v>151.600006103516</v>
       </c>
       <c r="G2400" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -68222,7 +68222,7 @@
         <v>151.899993896484</v>
       </c>
       <c r="G2401" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -68248,7 +68248,7 @@
         <v>148.800003051758</v>
       </c>
       <c r="G2402" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -68274,7 +68274,7 @@
         <v>145.100006103516</v>
       </c>
       <c r="G2403" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -68300,7 +68300,7 @@
         <v>145.600006103516</v>
       </c>
       <c r="G2404" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -68326,7 +68326,7 @@
         <v>144.800003051758</v>
       </c>
       <c r="G2405" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -68352,7 +68352,7 @@
         <v>145.800003051758</v>
       </c>
       <c r="G2406" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -68378,7 +68378,7 @@
         <v>142.899993896484</v>
       </c>
       <c r="G2407" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -68404,7 +68404,7 @@
         <v>142.5</v>
       </c>
       <c r="G2408" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -68430,7 +68430,7 @@
         <v>142.100006103516</v>
       </c>
       <c r="G2409" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -68456,7 +68456,7 @@
         <v>142.600006103516</v>
       </c>
       <c r="G2410" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -68482,7 +68482,7 @@
         <v>141.899993896484</v>
       </c>
       <c r="G2411" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -68508,7 +68508,7 @@
         <v>143.100006103516</v>
       </c>
       <c r="G2412" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -68534,7 +68534,7 @@
         <v>143.699996948242</v>
       </c>
       <c r="G2413" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -68560,7 +68560,7 @@
         <v>146.600006103516</v>
       </c>
       <c r="G2414" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -68586,7 +68586,7 @@
         <v>145.5</v>
       </c>
       <c r="G2415" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -68612,7 +68612,7 @@
         <v>142.100006103516</v>
       </c>
       <c r="G2416" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -68638,7 +68638,7 @@
         <v>143.5</v>
       </c>
       <c r="G2417" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -68664,7 +68664,7 @@
         <v>141.5</v>
       </c>
       <c r="G2418" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -68690,7 +68690,7 @@
         <v>141.5</v>
       </c>
       <c r="G2419" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -68716,7 +68716,7 @@
         <v>145.300003051758</v>
       </c>
       <c r="G2420" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -68742,7 +68742,7 @@
         <v>144.399993896484</v>
       </c>
       <c r="G2421" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -68768,7 +68768,7 @@
         <v>144.600006103516</v>
       </c>
       <c r="G2422" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -68794,7 +68794,7 @@
         <v>142.600006103516</v>
       </c>
       <c r="G2423" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -68820,7 +68820,7 @@
         <v>140.800003051758</v>
       </c>
       <c r="G2424" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -68846,7 +68846,7 @@
         <v>142.5</v>
       </c>
       <c r="G2425" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -68872,7 +68872,7 @@
         <v>140.800003051758</v>
       </c>
       <c r="G2426" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -68898,7 +68898,7 @@
         <v>143.399993896484</v>
       </c>
       <c r="G2427" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -68924,7 +68924,7 @@
         <v>142</v>
       </c>
       <c r="G2428" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -68950,7 +68950,7 @@
         <v>140.899993896484</v>
       </c>
       <c r="G2429" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -68976,7 +68976,7 @@
         <v>139.100006103516</v>
       </c>
       <c r="G2430" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -69002,7 +69002,7 @@
         <v>139</v>
       </c>
       <c r="G2431" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -69028,7 +69028,7 @@
         <v>136.899993896484</v>
       </c>
       <c r="G2432" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -69054,7 +69054,7 @@
         <v>136.800003051758</v>
       </c>
       <c r="G2433" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -69080,7 +69080,7 @@
         <v>139.899993896484</v>
       </c>
       <c r="G2434" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -69106,7 +69106,7 @@
         <v>138.300003051758</v>
       </c>
       <c r="G2435" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -69132,7 +69132,7 @@
         <v>137.399993896484</v>
       </c>
       <c r="G2436" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -69158,7 +69158,7 @@
         <v>137.600006103516</v>
       </c>
       <c r="G2437" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -69184,7 +69184,7 @@
         <v>131.699996948242</v>
       </c>
       <c r="G2438" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -69210,7 +69210,7 @@
         <v>131.600006103516</v>
       </c>
       <c r="G2439" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -69236,7 +69236,7 @@
         <v>133.199996948242</v>
       </c>
       <c r="G2440" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -69262,7 +69262,7 @@
         <v>128.199996948242</v>
       </c>
       <c r="G2441" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -69288,7 +69288,7 @@
         <v>128</v>
       </c>
       <c r="G2442" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -69314,7 +69314,7 @@
         <v>128.600006103516</v>
       </c>
       <c r="G2443" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -69340,7 +69340,7 @@
         <v>127</v>
       </c>
       <c r="G2444" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -69366,7 +69366,7 @@
         <v>122.5</v>
       </c>
       <c r="G2445" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -69392,7 +69392,7 @@
         <v>122.300003051758</v>
       </c>
       <c r="G2446" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -69418,7 +69418,7 @@
         <v>121.599998474121</v>
       </c>
       <c r="G2447" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -69444,7 +69444,7 @@
         <v>123</v>
       </c>
       <c r="G2448" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -69470,7 +69470,7 @@
         <v>125.599998474121</v>
       </c>
       <c r="G2449" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -69496,7 +69496,7 @@
         <v>123.300003051758</v>
       </c>
       <c r="G2450" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -69522,7 +69522,7 @@
         <v>121.800003051758</v>
       </c>
       <c r="G2451" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -69548,7 +69548,7 @@
         <v>122.699996948242</v>
       </c>
       <c r="G2452" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -69574,7 +69574,7 @@
         <v>124</v>
       </c>
       <c r="G2453" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -69600,7 +69600,7 @@
         <v>122.900001525879</v>
       </c>
       <c r="G2454" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -69626,7 +69626,7 @@
         <v>123.800003051758</v>
       </c>
       <c r="G2455" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -69652,7 +69652,7 @@
         <v>124.300003051758</v>
       </c>
       <c r="G2456" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -69678,7 +69678,7 @@
         <v>123.099998474121</v>
       </c>
       <c r="G2457" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -69704,7 +69704,7 @@
         <v>123</v>
       </c>
       <c r="G2458" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -69730,7 +69730,7 @@
         <v>119</v>
       </c>
       <c r="G2459" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -69756,7 +69756,7 @@
         <v>119</v>
       </c>
       <c r="G2460" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -69782,7 +69782,7 @@
         <v>119.099998474121</v>
       </c>
       <c r="G2461" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -69808,7 +69808,7 @@
         <v>119.699996948242</v>
       </c>
       <c r="G2462" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -69834,7 +69834,7 @@
         <v>120</v>
       </c>
       <c r="G2463" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -69860,7 +69860,7 @@
         <v>119.900001525879</v>
       </c>
       <c r="G2464" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -69886,7 +69886,7 @@
         <v>115.300003051758</v>
       </c>
       <c r="G2465" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -69912,7 +69912,7 @@
         <v>115.099998474121</v>
       </c>
       <c r="G2466" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -69938,7 +69938,7 @@
         <v>116.5</v>
       </c>
       <c r="G2467" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -69964,7 +69964,7 @@
         <v>117.199996948242</v>
       </c>
       <c r="G2468" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -69990,7 +69990,7 @@
         <v>117.5</v>
       </c>
       <c r="G2469" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -70016,7 +70016,7 @@
         <v>120.400001525879</v>
       </c>
       <c r="G2470" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -70042,7 +70042,7 @@
         <v>123.199996948242</v>
       </c>
       <c r="G2471" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -70068,7 +70068,7 @@
         <v>121.900001525879</v>
       </c>
       <c r="G2472" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -70094,7 +70094,7 @@
         <v>121.800003051758</v>
       </c>
       <c r="G2473" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -70120,7 +70120,7 @@
         <v>122.699996948242</v>
       </c>
       <c r="G2474" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -70146,7 +70146,7 @@
         <v>122.599998474121</v>
       </c>
       <c r="G2475" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -70172,7 +70172,7 @@
         <v>120.300003051758</v>
       </c>
       <c r="G2476" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -70198,7 +70198,7 @@
         <v>118.300003051758</v>
       </c>
       <c r="G2477" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -70224,7 +70224,7 @@
         <v>120.699996948242</v>
       </c>
       <c r="G2478" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -70250,7 +70250,7 @@
         <v>121.199996948242</v>
       </c>
       <c r="G2479" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -70276,7 +70276,7 @@
         <v>121.199996948242</v>
       </c>
       <c r="G2480" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -70302,7 +70302,7 @@
         <v>124</v>
       </c>
       <c r="G2481" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -70328,7 +70328,7 @@
         <v>123</v>
       </c>
       <c r="G2482" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -70354,7 +70354,7 @@
         <v>123</v>
       </c>
       <c r="G2483" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -70380,7 +70380,7 @@
         <v>123.699996948242</v>
       </c>
       <c r="G2484" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -70406,7 +70406,7 @@
         <v>123.5</v>
       </c>
       <c r="G2485" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -70432,7 +70432,7 @@
         <v>123.300003051758</v>
       </c>
       <c r="G2486" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -70458,7 +70458,7 @@
         <v>121.800003051758</v>
       </c>
       <c r="G2487" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -70484,7 +70484,7 @@
         <v>120.400001525879</v>
       </c>
       <c r="G2488" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -70510,7 +70510,7 @@
         <v>118.300003051758</v>
       </c>
       <c r="G2489" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -70536,7 +70536,7 @@
         <v>118.900001525879</v>
       </c>
       <c r="G2490" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -70562,7 +70562,7 @@
         <v>118.300003051758</v>
       </c>
       <c r="G2491" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -70588,7 +70588,7 @@
         <v>118.099998474121</v>
       </c>
       <c r="G2492" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -70614,7 +70614,7 @@
         <v>118.5</v>
       </c>
       <c r="G2493" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -70622,7 +70622,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6493171296</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>57076</v>
@@ -70640,9 +70640,35 @@
         <v>121.099998474121</v>
       </c>
       <c r="G2494" t="s">
+        <v>1816</v>
+      </c>
+      <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6494791667</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>50937</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>120.800003051758</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>120.199996948242</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>120.199996948242</v>
+      </c>
+      <c r="G2495" t="s">
         <v>1817</v>
       </c>
-      <c r="H2494" t="s">
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/REY.MI.xlsx
+++ b/data/REY.MI.xlsx
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2559680938721</t>
+    <t xml:space="preserve">29.2559700012207</t>
   </si>
   <si>
     <t xml:space="preserve">REY.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8380241394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3272094726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6306381225586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8396129608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2111167907715</t>
+    <t xml:space="preserve">28.8380298614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3272113800049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6306400299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8396091461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2111129760742</t>
   </si>
   <si>
     <t xml:space="preserve">29.0005626678467</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5594005584717</t>
+    <t xml:space="preserve">28.559398651123</t>
   </si>
   <si>
     <t xml:space="preserve">28.1414585113525</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">27.9789257049561</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8644142150879</t>
+    <t xml:space="preserve">26.8644123077393</t>
   </si>
   <si>
     <t xml:space="preserve">27.4448871612549</t>
@@ -83,31 +83,31 @@
     <t xml:space="preserve">27.9324893951416</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8163928985596</t>
+    <t xml:space="preserve">27.8163909912109</t>
   </si>
   <si>
     <t xml:space="preserve">28.2807712554932</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6770763397217</t>
+    <t xml:space="preserve">27.6770782470703</t>
   </si>
   <si>
     <t xml:space="preserve">28.0950202941895</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8628330230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2591342926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7018795013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.167839050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2855186462402</t>
+    <t xml:space="preserve">27.862829208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2591361999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7018737792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1678409576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2855205535889</t>
   </si>
   <si>
     <t xml:space="preserve">24.379976272583</t>
@@ -116,16 +116,16 @@
     <t xml:space="preserve">24.6121673583984</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0053062438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.517707824707</t>
+    <t xml:space="preserve">26.0053100585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5177116394043</t>
   </si>
   <si>
     <t xml:space="preserve">25.6570224761963</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6074199676514</t>
+    <t xml:space="preserve">27.607421875</t>
   </si>
   <si>
     <t xml:space="preserve">26.3071575164795</t>
@@ -134,22 +134,22 @@
     <t xml:space="preserve">27.0733814239502</t>
   </si>
   <si>
-    <t xml:space="preserve">26.214282989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4696884155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0517444610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7034606933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7266788482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7483177185059</t>
+    <t xml:space="preserve">26.2142753601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4696846008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0517425537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.703462600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7266826629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7483158111572</t>
   </si>
   <si>
     <t xml:space="preserve">26.4929065704346</t>
@@ -161,85 +161,85 @@
     <t xml:space="preserve">27.1894760131836</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2359180450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1662578582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9092655181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0237827301025</t>
+    <t xml:space="preserve">27.2359161376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.166259765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9092674255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0237808227539</t>
   </si>
   <si>
     <t xml:space="preserve">31.5546531677246</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3008327484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4169216156006</t>
+    <t xml:space="preserve">30.3008308410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4169254302979</t>
   </si>
   <si>
     <t xml:space="preserve">29.9989814758301</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9757614135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7900085449219</t>
+    <t xml:space="preserve">29.9757633209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7900104522705</t>
   </si>
   <si>
     <t xml:space="preserve">29.9525394439697</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2311725616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7203540802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0686359405518</t>
+    <t xml:space="preserve">30.2311687469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7203483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0686378479004</t>
   </si>
   <si>
     <t xml:space="preserve">29.8596668243408</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5578212738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3256282806396</t>
+    <t xml:space="preserve">29.5578231811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3256320953369</t>
   </si>
   <si>
     <t xml:space="preserve">29.4881629943848</t>
   </si>
   <si>
-    <t xml:space="preserve">29.511381149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2095336914062</t>
+    <t xml:space="preserve">29.5113773345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2095317840576</t>
   </si>
   <si>
     <t xml:space="preserve">30.1615104675293</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3720664978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5345993041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4433040618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6754970550537</t>
+    <t xml:space="preserve">29.3720645904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5346012115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4433059692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6754989624023</t>
   </si>
   <si>
     <t xml:space="preserve">28.8612461090088</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8148078918457</t>
+    <t xml:space="preserve">28.8148097991943</t>
   </si>
   <si>
     <t xml:space="preserve">28.9076862335205</t>
@@ -248,13 +248,13 @@
     <t xml:space="preserve">28.629056930542</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4200897216797</t>
+    <t xml:space="preserve">28.4200878143311</t>
   </si>
   <si>
     <t xml:space="preserve">28.6775989532471</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5605487823486</t>
+    <t xml:space="preserve">28.560546875</t>
   </si>
   <si>
     <t xml:space="preserve">29.0287532806396</t>
@@ -266,28 +266,28 @@
     <t xml:space="preserve">28.5137271881104</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7946529388428</t>
+    <t xml:space="preserve">28.7946491241455</t>
   </si>
   <si>
     <t xml:space="preserve">29.0053424835205</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2628593444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1992683410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5035972595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5504283905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9015769958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6674728393555</t>
+    <t xml:space="preserve">29.2628574371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1992664337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5036010742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.550422668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9015731811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6674747467041</t>
   </si>
   <si>
     <t xml:space="preserve">30.7142944335938</t>
@@ -299,22 +299,22 @@
     <t xml:space="preserve">30.4333724975586</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2694969177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8949356079102</t>
+    <t xml:space="preserve">30.2694988250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8949337005615</t>
   </si>
   <si>
     <t xml:space="preserve">28.1859836578369</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3096771240234</t>
+    <t xml:space="preserve">29.3096752166748</t>
   </si>
   <si>
     <t xml:space="preserve">29.4969577789307</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6943683624268</t>
+    <t xml:space="preserve">27.6943664550781</t>
   </si>
   <si>
     <t xml:space="preserve">25.7747249603271</t>
@@ -323,22 +323,22 @@
     <t xml:space="preserve">26.8047771453857</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3198051452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9218292236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5070838928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9452381134033</t>
+    <t xml:space="preserve">27.3198013305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9218273162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5070858001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9452362060547</t>
   </si>
   <si>
     <t xml:space="preserve">25.8215446472168</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2195205688477</t>
+    <t xml:space="preserve">26.2195167541504</t>
   </si>
   <si>
     <t xml:space="preserve">27.1091117858887</t>
@@ -347,10 +347,10 @@
     <t xml:space="preserve">27.624137878418</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3666210174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3030376434326</t>
+    <t xml:space="preserve">27.3666229248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3030338287354</t>
   </si>
   <si>
     <t xml:space="preserve">28.8882923126221</t>
@@ -359,16 +359,16 @@
     <t xml:space="preserve">28.7478313446045</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4434986114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9819355010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9117050170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3799095153809</t>
+    <t xml:space="preserve">28.4434947967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.98193359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9117031097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3799076080322</t>
   </si>
   <si>
     <t xml:space="preserve">29.4501399993896</t>
@@ -377,19 +377,19 @@
     <t xml:space="preserve">29.8481140136719</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1524486541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9651660919189</t>
+    <t xml:space="preserve">30.1524467468262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9651641845703</t>
   </si>
   <si>
     <t xml:space="preserve">28.7244205474854</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1458053588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0989837646484</t>
+    <t xml:space="preserve">29.1458015441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0989856719971</t>
   </si>
   <si>
     <t xml:space="preserve">28.9351119995117</t>
@@ -398,34 +398,34 @@
     <t xml:space="preserve">28.4903163909912</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9752922058105</t>
+    <t xml:space="preserve">27.9752883911133</t>
   </si>
   <si>
     <t xml:space="preserve">28.3732662200928</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0923461914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2729835510254</t>
+    <t xml:space="preserve">28.0923404693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2729816436768</t>
   </si>
   <si>
     <t xml:space="preserve">27.0622901916504</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0388793945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.898416519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1492900848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.798131942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8917770385742</t>
+    <t xml:space="preserve">27.0388813018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8984203338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1492881774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7981338500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.891773223877</t>
   </si>
   <si>
     <t xml:space="preserve">26.7579574584961</t>
@@ -434,16 +434,16 @@
     <t xml:space="preserve">27.9518814086914</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8816471099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8114223480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9050579071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2963924407959</t>
+    <t xml:space="preserve">27.8816509246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8114204406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9050598144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2963943481445</t>
   </si>
   <si>
     <t xml:space="preserve">27.8582382202148</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">27.741189956665</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0455226898193</t>
+    <t xml:space="preserve">28.0455207824707</t>
   </si>
   <si>
     <t xml:space="preserve">27.7880077362061</t>
@@ -467,10 +467,10 @@
     <t xml:space="preserve">27.3900337219238</t>
   </si>
   <si>
-    <t xml:space="preserve">29.1223964691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6541919708252</t>
+    <t xml:space="preserve">29.1223945617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6541881561279</t>
   </si>
   <si>
     <t xml:space="preserve">28.2093944549561</t>
@@ -479,55 +479,55 @@
     <t xml:space="preserve">27.4134426116943</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0857009887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8515968322754</t>
+    <t xml:space="preserve">27.0856990814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8515949249268</t>
   </si>
   <si>
     <t xml:space="preserve">27.4368534088135</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6877269744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2261619567871</t>
+    <t xml:space="preserve">26.6877250671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2261600494385</t>
   </si>
   <si>
     <t xml:space="preserve">26.8281860351562</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6409091949463</t>
+    <t xml:space="preserve">26.6409072875977</t>
   </si>
   <si>
     <t xml:space="preserve">26.4536247253418</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5706748962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5238571166992</t>
+    <t xml:space="preserve">26.5706729888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5238552093506</t>
   </si>
   <si>
     <t xml:space="preserve">26.3365707397461</t>
   </si>
   <si>
-    <t xml:space="preserve">25.751314163208</t>
+    <t xml:space="preserve">25.7513122558594</t>
   </si>
   <si>
     <t xml:space="preserve">25.329927444458</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7446708679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7680816650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8851356506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2530574798584</t>
+    <t xml:space="preserve">24.7446689605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7680797576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8851337432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2530536651611</t>
   </si>
   <si>
     <t xml:space="preserve">25.0490055084229</t>
@@ -536,43 +536,43 @@
     <t xml:space="preserve">25.4703941345215</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5172119140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2831077575684</t>
+    <t xml:space="preserve">25.5172100067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2831058502197</t>
   </si>
   <si>
     <t xml:space="preserve">25.1660556793213</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4469776153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0958271026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.931957244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0724182128906</t>
+    <t xml:space="preserve">25.4469795227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0958251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9319553375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0724143981934</t>
   </si>
   <si>
     <t xml:space="preserve">25.6342639923096</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1961078643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.172700881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8348293304443</t>
+    <t xml:space="preserve">26.1961097717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1726989746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8348274230957</t>
   </si>
   <si>
     <t xml:space="preserve">27.9284706115723</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4602680206299</t>
+    <t xml:space="preserve">27.4602661132812</t>
   </si>
   <si>
     <t xml:space="preserve">27.9986991882324</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">29.2160358428955</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3330860137939</t>
+    <t xml:space="preserve">29.3330898284912</t>
   </si>
   <si>
     <t xml:space="preserve">28.8648815155029</t>
@@ -593,61 +593,61 @@
     <t xml:space="preserve">28.3498554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6073703765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4735488891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2394466400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7076511383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4267292022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8313503265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9952144622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4868354797363</t>
+    <t xml:space="preserve">28.6073684692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4735507965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2394485473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7076549530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4267253875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8313465118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9952125549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.486837387085</t>
   </si>
   <si>
     <t xml:space="preserve">31.2527275085449</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3697853088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1356830596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1891441345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3061981201172</t>
+    <t xml:space="preserve">31.369779586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1356811523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.189136505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3062019348145</t>
   </si>
   <si>
     <t xml:space="preserve">33.2660179138184</t>
   </si>
   <si>
-    <t xml:space="preserve">34.0619621276855</t>
+    <t xml:space="preserve">34.0619659423828</t>
   </si>
   <si>
     <t xml:space="preserve">34.6472244262695</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4599418640137</t>
+    <t xml:space="preserve">34.4599456787109</t>
   </si>
   <si>
     <t xml:space="preserve">34.7408638000488</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6706352233887</t>
+    <t xml:space="preserve">34.6706314086914</t>
   </si>
   <si>
     <t xml:space="preserve">34.9983749389648</t>
@@ -656,19 +656,19 @@
     <t xml:space="preserve">34.85791015625</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1790199279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7642707824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8813247680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3897094726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4131202697754</t>
+    <t xml:space="preserve">34.179012298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7642784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8813209533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.389705657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4131278991699</t>
   </si>
   <si>
     <t xml:space="preserve">35.6070404052734</t>
@@ -677,34 +677,34 @@
     <t xml:space="preserve">35.4665870666504</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7943267822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.8243751525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6671485900879</t>
+    <t xml:space="preserve">35.794319152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.8243713378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6671524047852</t>
   </si>
   <si>
     <t xml:space="preserve">37.8778495788574</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9882469177246</t>
+    <t xml:space="preserve">36.9882507324219</t>
   </si>
   <si>
     <t xml:space="preserve">37.5735092163086</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6203269958496</t>
+    <t xml:space="preserve">37.6203308105469</t>
   </si>
   <si>
     <t xml:space="preserve">37.6085395812988</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7264366149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9150695800781</t>
+    <t xml:space="preserve">37.726432800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9150733947754</t>
   </si>
   <si>
     <t xml:space="preserve">38.1980171203613</t>
@@ -722,127 +722,127 @@
     <t xml:space="preserve">39.0232772827148</t>
   </si>
   <si>
-    <t xml:space="preserve">40.084342956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0607604980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8013954162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2397041320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0274925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4519195556641</t>
+    <t xml:space="preserve">40.0843315124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0607566833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8013877868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2397117614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0274963378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4519233703613</t>
   </si>
   <si>
     <t xml:space="preserve">41.7112922668457</t>
   </si>
   <si>
-    <t xml:space="preserve">41.499080657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.805606842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3243446350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1828651428223</t>
+    <t xml:space="preserve">41.4990768432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8056106567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3243408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1828689575195</t>
   </si>
   <si>
     <t xml:space="preserve">42.0885543823242</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2771873474121</t>
+    <t xml:space="preserve">42.2771911621094</t>
   </si>
   <si>
     <t xml:space="preserve">41.8291854858398</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9664421081543</t>
+    <t xml:space="preserve">39.9664459228516</t>
   </si>
   <si>
     <t xml:space="preserve">39.5891761779785</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4338073730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9997062683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6363410949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9428634643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4380264282227</t>
+    <t xml:space="preserve">38.4338035583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9997024536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6363372802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9428558349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4380187988281</t>
   </si>
   <si>
     <t xml:space="preserve">38.551700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0565414428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1411743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3298072814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0704383850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1647567749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6695899963379</t>
+    <t xml:space="preserve">38.0565452575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1411781311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3298149108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0704345703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1647529602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6695976257324</t>
   </si>
   <si>
     <t xml:space="preserve">38.8346519470215</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9053764343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0940170288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8110656738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2687492370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7403297424316</t>
+    <t xml:space="preserve">38.9053840637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0940208435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8110694885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2687568664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7403335571289</t>
   </si>
   <si>
     <t xml:space="preserve">38.6931762695312</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2354850769043</t>
+    <t xml:space="preserve">39.2354888916016</t>
   </si>
   <si>
     <t xml:space="preserve">39.2590675354004</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1357078552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5129737854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7765617370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8001441955566</t>
+    <t xml:space="preserve">42.1357154846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5129776000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7765579223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8001403808594</t>
   </si>
   <si>
     <t xml:space="preserve">45.5075073242188</t>
@@ -857,25 +857,25 @@
     <t xml:space="preserve">44.682243347168</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7862396240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.752986907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.130241394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4464569091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.5879325866699</t>
+    <t xml:space="preserve">43.7862434387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7529830932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1302490234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4464530944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.5879287719727</t>
   </si>
   <si>
     <t xml:space="preserve">44.328556060791</t>
   </si>
   <si>
-    <t xml:space="preserve">44.3049812316895</t>
+    <t xml:space="preserve">44.3049850463867</t>
   </si>
   <si>
     <t xml:space="preserve">43.6211891174316</t>
@@ -884,76 +884,76 @@
     <t xml:space="preserve">43.1731910705566</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0788764953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5837135314941</t>
+    <t xml:space="preserve">43.0788726806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5837173461914</t>
   </si>
   <si>
     <t xml:space="preserve">43.267505645752</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3660354614258</t>
+    <t xml:space="preserve">45.366039276123</t>
   </si>
   <si>
     <t xml:space="preserve">44.9887771606445</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4936141967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.5172004699707</t>
+    <t xml:space="preserve">44.4936180114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.5171966552734</t>
   </si>
   <si>
     <t xml:space="preserve">45.6254043579102</t>
   </si>
   <si>
-    <t xml:space="preserve">45.861198425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4035186767578</t>
+    <t xml:space="preserve">45.8611907958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4035148620605</t>
   </si>
   <si>
     <t xml:space="preserve">47.5824661254883</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0637283325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1344604492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1580467224121</t>
+    <t xml:space="preserve">47.0637245178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.134464263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1580390930176</t>
   </si>
   <si>
     <t xml:space="preserve">47.9125747680664</t>
   </si>
   <si>
-    <t xml:space="preserve">49.350887298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7378349304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.101203918457</t>
+    <t xml:space="preserve">49.3508949279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7378387451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1012077331543</t>
   </si>
   <si>
     <t xml:space="preserve">48.8321533203125</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6296195983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0540428161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8654174804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9597282409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1858406066895</t>
+    <t xml:space="preserve">47.6296234130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0540466308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8654136657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9597358703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1858444213867</t>
   </si>
   <si>
     <t xml:space="preserve">45.2717208862305</t>
@@ -962,28 +962,28 @@
     <t xml:space="preserve">45.0359306335449</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5643539428711</t>
+    <t xml:space="preserve">44.5643501281738</t>
   </si>
   <si>
     <t xml:space="preserve">43.9748764038086</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5601387023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9138221740723</t>
+    <t xml:space="preserve">42.5601272583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.913818359375</t>
   </si>
   <si>
     <t xml:space="preserve">42.7251892089844</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2064476013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4328117370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1781578063965</t>
+    <t xml:space="preserve">42.2064437866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4328079223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.178150177002</t>
   </si>
   <si>
     <t xml:space="preserve">43.3476715087891</t>
@@ -992,7 +992,7 @@
     <t xml:space="preserve">41.9800872802734</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3010101318359</t>
+    <t xml:space="preserve">41.3010139465332</t>
   </si>
   <si>
     <t xml:space="preserve">42.0838356018066</t>
@@ -1001,31 +1001,31 @@
     <t xml:space="preserve">42.7534866333008</t>
   </si>
   <si>
-    <t xml:space="preserve">42.593147277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4799728393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.008129119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0458679199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3288078308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3953285217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.4891471862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2342491149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1210670471191</t>
+    <t xml:space="preserve">42.5931434631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4799652099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0081367492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0458641052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3288040161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3953323364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.4891510009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2342414855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1210632324219</t>
   </si>
   <si>
     <t xml:space="preserve">43.2439231872559</t>
@@ -1034,16 +1034,16 @@
     <t xml:space="preserve">42.1027030944824</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1689758300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2729721069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4045104980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7626686096191</t>
+    <t xml:space="preserve">41.1689720153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2729759216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4045143127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7626609802246</t>
   </si>
   <si>
     <t xml:space="preserve">44.2531051635742</t>
@@ -1052,16 +1052,16 @@
     <t xml:space="preserve">45.0547943115234</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9510498046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2809028625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.148853302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3094482421875</t>
+    <t xml:space="preserve">44.9510459899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2809066772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1488571166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3094520568848</t>
   </si>
   <si>
     <t xml:space="preserve">44.9982032775879</t>
@@ -1073,43 +1073,43 @@
     <t xml:space="preserve">45.1679763793945</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5923957824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6586647033691</t>
+    <t xml:space="preserve">45.5923919677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6586723327637</t>
   </si>
   <si>
     <t xml:space="preserve">43.2533569335938</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6683502197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2248077392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0830917358398</t>
+    <t xml:space="preserve">43.6683540344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2248191833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0830879211426</t>
   </si>
   <si>
     <t xml:space="preserve">45.2056999206543</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3280639648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0356826782227</t>
+    <t xml:space="preserve">46.3280601501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0356864929199</t>
   </si>
   <si>
     <t xml:space="preserve">45.6584205627441</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5169410705566</t>
+    <t xml:space="preserve">45.5169372558594</t>
   </si>
   <si>
     <t xml:space="preserve">44.1682243347168</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8664093017578</t>
+    <t xml:space="preserve">43.8664054870605</t>
   </si>
   <si>
     <t xml:space="preserve">43.5457382202148</t>
@@ -1121,58 +1121,58 @@
     <t xml:space="preserve">44.4606018066406</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6112632751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6301231384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7244415283203</t>
+    <t xml:space="preserve">45.611255645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.630126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7244453430176</t>
   </si>
   <si>
     <t xml:space="preserve">46.2903366088867</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0262451171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2148857116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6487350463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7053260803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5921516418457</t>
+    <t xml:space="preserve">46.026252746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2148818969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6487312316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.705322265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5921440124512</t>
   </si>
   <si>
     <t xml:space="preserve">46.8939628601074</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7711029052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8182563781738</t>
+    <t xml:space="preserve">47.7710952758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8182640075684</t>
   </si>
   <si>
     <t xml:space="preserve">48.1955184936523</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9972038269043</t>
+    <t xml:space="preserve">48.9972114562988</t>
   </si>
   <si>
     <t xml:space="preserve">48.5727844238281</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3273048400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3176345825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4119453430176</t>
+    <t xml:space="preserve">49.3273124694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3176307678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4119491577148</t>
   </si>
   <si>
     <t xml:space="preserve">49.8460464477539</t>
@@ -1187,13 +1187,13 @@
     <t xml:space="preserve">50.081844329834</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5353088378906</t>
+    <t xml:space="preserve">47.5353050231934</t>
   </si>
   <si>
     <t xml:space="preserve">46.1960182189941</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2052040100098</t>
+    <t xml:space="preserve">47.2052001953125</t>
   </si>
   <si>
     <t xml:space="preserve">48.0068893432617</t>
@@ -1205,19 +1205,19 @@
     <t xml:space="preserve">46.4223747253418</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8376159667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6489868164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8753471374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5732841491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.4687843322754</t>
+    <t xml:space="preserve">45.8376197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6489906311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8753433227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5732879638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.4687881469727</t>
   </si>
   <si>
     <t xml:space="preserve">48.8085746765137</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">46.4789657592773</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3938293457031</t>
+    <t xml:space="preserve">47.3938331604004</t>
   </si>
   <si>
     <t xml:space="preserve">46.5166931152344</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">45.1774024963379</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7812805175781</t>
+    <t xml:space="preserve">44.7812728881836</t>
   </si>
   <si>
     <t xml:space="preserve">44.8378677368164</t>
@@ -1244,46 +1244,46 @@
     <t xml:space="preserve">44.4983291625977</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1776542663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.895206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.291332244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4988288879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0652236938477</t>
+    <t xml:space="preserve">44.1776580810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8952026367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2913284301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4988327026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0652198791504</t>
   </si>
   <si>
     <t xml:space="preserve">41.9517936706543</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3283157348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4414939880371</t>
+    <t xml:space="preserve">45.3283195495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4414901733398</t>
   </si>
   <si>
     <t xml:space="preserve">45.4603500366211</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4037666320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1016998291016</t>
+    <t xml:space="preserve">45.4037628173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1017036437988</t>
   </si>
   <si>
     <t xml:space="preserve">45.9885215759277</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3846473693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.0443649291992</t>
+    <t xml:space="preserve">46.384651184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.0443687438965</t>
   </si>
   <si>
     <t xml:space="preserve">48.902889251709</t>
@@ -1292,40 +1292,40 @@
     <t xml:space="preserve">48.2898368835449</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1193199157715</t>
+    <t xml:space="preserve">51.1193237304688</t>
   </si>
   <si>
     <t xml:space="preserve">50.6948928833008</t>
   </si>
   <si>
-    <t xml:space="preserve">50.6005897521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9328575134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4107055664062</t>
+    <t xml:space="preserve">50.6005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.932861328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4107093811035</t>
   </si>
   <si>
     <t xml:space="preserve">51.0277862548828</t>
   </si>
   <si>
-    <t xml:space="preserve">52.2144813537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1195449829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.739803314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8410987854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5024681091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2714920043945</t>
+    <t xml:space="preserve">52.214485168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1195487976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7398071289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8411026000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5024719238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2714958190918</t>
   </si>
   <si>
     <t xml:space="preserve">49.3664207458496</t>
@@ -1334,31 +1334,31 @@
     <t xml:space="preserve">49.0816116333008</t>
   </si>
   <si>
-    <t xml:space="preserve">49.793628692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.2746658325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.822151184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0848007202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6544036865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3189506530762</t>
+    <t xml:space="preserve">49.7936325073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.2746696472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8221549987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0847930908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6544075012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3189582824707</t>
   </si>
   <si>
     <t xml:space="preserve">49.6512260437012</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9835014343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3632469177246</t>
+    <t xml:space="preserve">49.9835052490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3632431030273</t>
   </si>
   <si>
     <t xml:space="preserve">51.2176628112793</t>
@@ -1370,25 +1370,25 @@
     <t xml:space="preserve">51.455005645752</t>
   </si>
   <si>
-    <t xml:space="preserve">52.0246086120605</t>
+    <t xml:space="preserve">52.0246124267578</t>
   </si>
   <si>
     <t xml:space="preserve">53.0689010620117</t>
   </si>
   <si>
-    <t xml:space="preserve">52.7840995788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4422874450684</t>
+    <t xml:space="preserve">52.7840957641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4422836303711</t>
   </si>
   <si>
     <t xml:space="preserve">54.6828079223633</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1100120544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5846900939941</t>
+    <t xml:space="preserve">55.1100158691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5846862792969</t>
   </si>
   <si>
     <t xml:space="preserve">56.3916473388672</t>
@@ -1397,22 +1397,22 @@
     <t xml:space="preserve">54.7302742004395</t>
   </si>
   <si>
-    <t xml:space="preserve">55.0625457763672</t>
+    <t xml:space="preserve">55.0625495910645</t>
   </si>
   <si>
     <t xml:space="preserve">55.4897537231445</t>
   </si>
   <si>
-    <t xml:space="preserve">55.2524147033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.1638374328613</t>
+    <t xml:space="preserve">55.2524185180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1638412475586</t>
   </si>
   <si>
     <t xml:space="preserve">53.6385192871094</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0182571411133</t>
+    <t xml:space="preserve">54.0182609558105</t>
   </si>
   <si>
     <t xml:space="preserve">54.3030662536621</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">56.4391059875488</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9137916564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2967109680176</t>
+    <t xml:space="preserve">56.9137878417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.296703338623</t>
   </si>
   <si>
     <t xml:space="preserve">56.011905670166</t>
@@ -1442,19 +1442,19 @@
     <t xml:space="preserve">56.2017707824707</t>
   </si>
   <si>
-    <t xml:space="preserve">56.5340423583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6764488220215</t>
+    <t xml:space="preserve">56.534049987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6764526367188</t>
   </si>
   <si>
     <t xml:space="preserve">54.9676170349121</t>
   </si>
   <si>
-    <t xml:space="preserve">52.5942268371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0214385986328</t>
+    <t xml:space="preserve">52.5942306518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0214309692383</t>
   </si>
   <si>
     <t xml:space="preserve">55.1574783325195</t>
@@ -1463,22 +1463,22 @@
     <t xml:space="preserve">54.3505325317383</t>
   </si>
   <si>
-    <t xml:space="preserve">52.9265022277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.8790321350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0657234191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5878677368164</t>
+    <t xml:space="preserve">52.9264984130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.8790283203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0657272338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5878639221191</t>
   </si>
   <si>
     <t xml:space="preserve">53.4486427307129</t>
   </si>
   <si>
-    <t xml:space="preserve">53.6859855651855</t>
+    <t xml:space="preserve">53.6859893798828</t>
   </si>
   <si>
     <t xml:space="preserve">53.3062438964844</t>
@@ -1496,7 +1496,7 @@
     <t xml:space="preserve">52.2619514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">51.8822174072266</t>
+    <t xml:space="preserve">51.882209777832</t>
   </si>
   <si>
     <t xml:space="preserve">54.1606559753418</t>
@@ -1511,16 +1511,16 @@
     <t xml:space="preserve">54.5404014587402</t>
   </si>
   <si>
-    <t xml:space="preserve">55.2049560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2492370605469</t>
+    <t xml:space="preserve">55.204948425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2492408752441</t>
   </si>
   <si>
     <t xml:space="preserve">57.1036605834961</t>
   </si>
   <si>
-    <t xml:space="preserve">57.2460594177246</t>
+    <t xml:space="preserve">57.2460632324219</t>
   </si>
   <si>
     <t xml:space="preserve">57.9106063842773</t>
@@ -1529,76 +1529,76 @@
     <t xml:space="preserve">56.9612579345703</t>
   </si>
   <si>
-    <t xml:space="preserve">50.790454864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.413890838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0120239257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0499992370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.2271919250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.467716217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0309677124023</t>
+    <t xml:space="preserve">50.7904510498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.4138870239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0120162963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0500030517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.2271995544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4677085876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0309638977051</t>
   </si>
   <si>
     <t xml:space="preserve">50.3157730102539</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3474769592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7525634765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6766090393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6956024169922</t>
+    <t xml:space="preserve">46.3474731445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7525596618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6766128540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6956062316895</t>
   </si>
   <si>
     <t xml:space="preserve">46.1955757141113</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5563354492188</t>
+    <t xml:space="preserve">46.5563316345215</t>
   </si>
   <si>
     <t xml:space="preserve">46.4803848266602</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9487495422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4107513427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5373497009277</t>
+    <t xml:space="preserve">45.9487533569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4107475280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.537353515625</t>
   </si>
   <si>
     <t xml:space="preserve">46.5183601379395</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7462043762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4424018859863</t>
+    <t xml:space="preserve">46.746208190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4424057006836</t>
   </si>
   <si>
     <t xml:space="preserve">45.4930534362793</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1322975158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5690002441406</t>
+    <t xml:space="preserve">45.1323013305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5690078735352</t>
   </si>
   <si>
     <t xml:space="preserve">45.7019119262695</t>
@@ -1610,28 +1610,28 @@
     <t xml:space="preserve">41.4677963256836</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9234809875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8728408813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7462425231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2968673706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8601722717285</t>
+    <t xml:space="preserve">41.9234848022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8728370666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7462463378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2968711853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8601760864258</t>
   </si>
   <si>
     <t xml:space="preserve">45.7209014892578</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7841796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7050476074219</t>
+    <t xml:space="preserve">46.7841758728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7050514221191</t>
   </si>
   <si>
     <t xml:space="preserve">47.2398643493652</t>
@@ -1640,34 +1640,34 @@
     <t xml:space="preserve">46.2905082702637</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1892623901367</t>
+    <t xml:space="preserve">45.1892585754395</t>
   </si>
   <si>
     <t xml:space="preserve">45.208251953125</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2842025756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3158111572266</t>
+    <t xml:space="preserve">45.2841987609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3158149719238</t>
   </si>
   <si>
     <t xml:space="preserve">47.3727798461914</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6132888793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4867362976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5373916625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5183982849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.075382232666</t>
+    <t xml:space="preserve">46.6132926940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.486743927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5373878479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5184020996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0753784179688</t>
   </si>
   <si>
     <t xml:space="preserve">41.5627288818359</t>
@@ -1685,25 +1685,25 @@
     <t xml:space="preserve">40.2526206970215</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8095550537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1956176757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0310516357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3158569335938</t>
+    <t xml:space="preserve">41.8095664978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1956214904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0310554504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.315860748291</t>
   </si>
   <si>
     <t xml:space="preserve">44.3348426818848</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8791618347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7398948669434</t>
+    <t xml:space="preserve">43.8791580200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7398872375488</t>
   </si>
   <si>
     <t xml:space="preserve">45.8348197937012</t>
@@ -1715,28 +1715,28 @@
     <t xml:space="preserve">46.3854484558105</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4234237670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1829071044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1765556335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.3696022033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4360961914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0753440856934</t>
+    <t xml:space="preserve">46.4234275817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1829109191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1765480041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.3695983886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4361000061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0753326416016</t>
   </si>
   <si>
     <t xml:space="preserve">45.6449584960938</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2588539123535</t>
+    <t xml:space="preserve">47.2588577270508</t>
   </si>
   <si>
     <t xml:space="preserve">48.4645309448242</t>
@@ -1751,25 +1751,25 @@
     <t xml:space="preserve">50.6955184936523</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2208366394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9360313415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0784378051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1670188903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6891593933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9739685058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.2555961608887</t>
+    <t xml:space="preserve">50.2208404541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.93603515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0784339904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1670150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6891670227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9739646911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.2555999755859</t>
   </si>
   <si>
     <t xml:space="preserve">53.2587738037109</t>
@@ -1784,19 +1784,19 @@
     <t xml:space="preserve">55.2998886108398</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3979949951172</t>
+    <t xml:space="preserve">54.3979988098145</t>
   </si>
   <si>
     <t xml:space="preserve">53.4011764526367</t>
   </si>
   <si>
-    <t xml:space="preserve">53.9233169555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4929389953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4454612731934</t>
+    <t xml:space="preserve">53.9233207702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4929313659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4454650878906</t>
   </si>
   <si>
     <t xml:space="preserve">53.4961090087891</t>
@@ -1805,19 +1805,19 @@
     <t xml:space="preserve">54.6353340148926</t>
   </si>
   <si>
-    <t xml:space="preserve">55.9644317626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.7270889282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1068382263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5328483581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5239105224609</t>
+    <t xml:space="preserve">55.9644393920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.7270927429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1068344116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5328521728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5239143371582</t>
   </si>
   <si>
     <t xml:space="preserve">53.5717430114746</t>
@@ -1826,61 +1826,61 @@
     <t xml:space="preserve">52.615104675293</t>
   </si>
   <si>
-    <t xml:space="preserve">52.5194396972656</t>
+    <t xml:space="preserve">52.5194435119629</t>
   </si>
   <si>
     <t xml:space="preserve">51.4671363830566</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5283851623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.9633407592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0590019226074</t>
+    <t xml:space="preserve">54.5283813476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.9633369445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0589981079102</t>
   </si>
   <si>
     <t xml:space="preserve">55.1980323791504</t>
   </si>
   <si>
-    <t xml:space="preserve">56.776481628418</t>
+    <t xml:space="preserve">56.7764778137207</t>
   </si>
   <si>
     <t xml:space="preserve">56.0111694335938</t>
   </si>
   <si>
-    <t xml:space="preserve">55.6285209655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2024955749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.9155044555664</t>
+    <t xml:space="preserve">55.6285133361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2024993896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.9155120849609</t>
   </si>
   <si>
     <t xml:space="preserve">56.4416618347168</t>
   </si>
   <si>
-    <t xml:space="preserve">55.580680847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3459968566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1501998901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5762100219727</t>
+    <t xml:space="preserve">55.5806846618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3459930419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.150203704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5762138366699</t>
   </si>
   <si>
     <t xml:space="preserve">54.4327201843262</t>
   </si>
   <si>
-    <t xml:space="preserve">54.8632011413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9199752807617</t>
+    <t xml:space="preserve">54.8632049560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9199829101562</t>
   </si>
   <si>
     <t xml:space="preserve">56.8243179321289</t>
@@ -1892,10 +1892,10 @@
     <t xml:space="preserve">56.6808166503906</t>
   </si>
   <si>
-    <t xml:space="preserve">56.7286529541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.2114334106445</t>
+    <t xml:space="preserve">56.7286491394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.2114372253418</t>
   </si>
   <si>
     <t xml:space="preserve">57.6374588012695</t>
@@ -1907,28 +1907,28 @@
     <t xml:space="preserve">57.924446105957</t>
   </si>
   <si>
-    <t xml:space="preserve">58.3549308776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.7331161499023</t>
+    <t xml:space="preserve">58.3549346923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.7331199645996</t>
   </si>
   <si>
     <t xml:space="preserve">57.3504676818848</t>
   </si>
   <si>
-    <t xml:space="preserve">58.3071060180664</t>
+    <t xml:space="preserve">58.3071022033691</t>
   </si>
   <si>
     <t xml:space="preserve">60.2682075500488</t>
   </si>
   <si>
-    <t xml:space="preserve">60.172550201416</t>
+    <t xml:space="preserve">60.1725540161133</t>
   </si>
   <si>
     <t xml:space="preserve">59.7420616149902</t>
   </si>
   <si>
-    <t xml:space="preserve">59.2159118652344</t>
+    <t xml:space="preserve">59.2159080505371</t>
   </si>
   <si>
     <t xml:space="preserve">59.120246887207</t>
@@ -1937,19 +1937,19 @@
     <t xml:space="preserve">57.3026351928711</t>
   </si>
   <si>
-    <t xml:space="preserve">57.8287925720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.1157760620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.7809562683105</t>
+    <t xml:space="preserve">57.828784942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.1157722473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.7809524536133</t>
   </si>
   <si>
     <t xml:space="preserve">59.0245819091797</t>
   </si>
   <si>
-    <t xml:space="preserve">59.4550666809082</t>
+    <t xml:space="preserve">59.4550704956055</t>
   </si>
   <si>
     <t xml:space="preserve">60.3160400390625</t>
@@ -1958,25 +1958,25 @@
     <t xml:space="preserve">60.0290489196777</t>
   </si>
   <si>
-    <t xml:space="preserve">59.0724105834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.2592697143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0201110839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.988826751709</t>
+    <t xml:space="preserve">59.0724182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.2592735290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0201187133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9888191223145</t>
   </si>
   <si>
     <t xml:space="preserve">50.4148368835449</t>
   </si>
   <si>
-    <t xml:space="preserve">51.2279815673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3236465454102</t>
+    <t xml:space="preserve">51.2279777526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3236427307129</t>
   </si>
   <si>
     <t xml:space="preserve">50.8931617736816</t>
@@ -1985,7 +1985,7 @@
     <t xml:space="preserve">49.793025970459</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8408546447754</t>
+    <t xml:space="preserve">49.8408508300781</t>
   </si>
   <si>
     <t xml:space="preserve">48.6928939819336</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">49.2668724060059</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9843521118164</t>
+    <t xml:space="preserve">49.9843482971191</t>
   </si>
   <si>
     <t xml:space="preserve">49.9365196228027</t>
@@ -2003,58 +2003,58 @@
     <t xml:space="preserve">50.0800132751465</t>
   </si>
   <si>
-    <t xml:space="preserve">50.6540031433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2235107421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8453254699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.419303894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.940990447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5149688720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7974891662598</t>
+    <t xml:space="preserve">50.6539993286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2235069274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8453330993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4193077087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9409866333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5149726867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.797492980957</t>
   </si>
   <si>
     <t xml:space="preserve">51.1323165893555</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6973571777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3147048950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.458194732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.745189666748</t>
+    <t xml:space="preserve">49.6973609924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3147010803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.4581985473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7451972961426</t>
   </si>
   <si>
     <t xml:space="preserve">50.0321807861328</t>
   </si>
   <si>
-    <t xml:space="preserve">48.8363800048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5972213745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3625297546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0022354125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4282531738281</t>
+    <t xml:space="preserve">48.8363838195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.597225189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3625335693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0022315979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4282417297363</t>
   </si>
   <si>
     <t xml:space="preserve">54.2892265319824</t>
@@ -2066,19 +2066,19 @@
     <t xml:space="preserve">53.0934219360352</t>
   </si>
   <si>
-    <t xml:space="preserve">52.471607208252</t>
+    <t xml:space="preserve">52.4716110229492</t>
   </si>
   <si>
     <t xml:space="preserve">53.2847518920898</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0978965759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9110412597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3370513916016</t>
+    <t xml:space="preserve">54.097900390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9110336303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3370552062988</t>
   </si>
   <si>
     <t xml:space="preserve">53.8587341308594</t>
@@ -2093,28 +2093,28 @@
     <t xml:space="preserve">55.3415260314941</t>
   </si>
   <si>
-    <t xml:space="preserve">55.86767578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5373229980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.632984161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.4027671813965</t>
+    <t xml:space="preserve">55.8676795959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5373191833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6329879760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.4027633666992</t>
   </si>
   <si>
     <t xml:space="preserve">58.0679473876953</t>
   </si>
   <si>
-    <t xml:space="preserve">59.6942291259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.3115692138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8511276245117</t>
+    <t xml:space="preserve">59.6942329406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.3115730285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.851131439209</t>
   </si>
   <si>
     <t xml:space="preserve">63.6164512634277</t>
@@ -2126,28 +2126,28 @@
     <t xml:space="preserve">66.3428649902344</t>
   </si>
   <si>
-    <t xml:space="preserve">66.9646835327148</t>
+    <t xml:space="preserve">66.9646759033203</t>
   </si>
   <si>
     <t xml:space="preserve">67.9213256835938</t>
   </si>
   <si>
-    <t xml:space="preserve">69.260612487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.0692901611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.3951721191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.0169830322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.869026184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.2994918823242</t>
+    <t xml:space="preserve">69.2606201171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.0692749023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.3951568603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.016975402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.869010925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.2994995117188</t>
   </si>
   <si>
     <t xml:space="preserve">67.5386581420898</t>
@@ -2156,46 +2156,46 @@
     <t xml:space="preserve">68.9257888793945</t>
   </si>
   <si>
-    <t xml:space="preserve">69.2127838134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.4474716186523</t>
+    <t xml:space="preserve">69.212776184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.4474639892578</t>
   </si>
   <si>
     <t xml:space="preserve">67.8734893798828</t>
   </si>
   <si>
-    <t xml:space="preserve">67.7778167724609</t>
+    <t xml:space="preserve">67.7778244018555</t>
   </si>
   <si>
     <t xml:space="preserve">67.0603408813477</t>
   </si>
   <si>
-    <t xml:space="preserve">66.0080413818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.4385299682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5775527954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.9123840332031</t>
+    <t xml:space="preserve">66.0080490112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.4385223388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5775604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.9123687744141</t>
   </si>
   <si>
     <t xml:space="preserve">67.2516784667969</t>
   </si>
   <si>
-    <t xml:space="preserve">67.8256454467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.6343231201172</t>
+    <t xml:space="preserve">67.8256607055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.6343154907227</t>
   </si>
   <si>
     <t xml:space="preserve">65.7688903808594</t>
   </si>
   <si>
-    <t xml:space="preserve">66.1036987304688</t>
+    <t xml:space="preserve">66.1037139892578</t>
   </si>
   <si>
     <t xml:space="preserve">69.4519348144531</t>
@@ -2213,7 +2213,7 @@
     <t xml:space="preserve">73.2306671142578</t>
   </si>
   <si>
-    <t xml:space="preserve">74.0916290283203</t>
+    <t xml:space="preserve">74.0916366577148</t>
   </si>
   <si>
     <t xml:space="preserve">73.6611480712891</t>
@@ -2222,22 +2222,22 @@
     <t xml:space="preserve">73.374153137207</t>
   </si>
   <si>
-    <t xml:space="preserve">70.6955642700195</t>
+    <t xml:space="preserve">70.6955795288086</t>
   </si>
   <si>
     <t xml:space="preserve">70.7912368774414</t>
   </si>
   <si>
-    <t xml:space="preserve">72.4653472900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.2650756835938</t>
+    <t xml:space="preserve">72.4653549194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.2650680541992</t>
   </si>
   <si>
     <t xml:space="preserve">68.6387939453125</t>
   </si>
   <si>
-    <t xml:space="preserve">71.3173980712891</t>
+    <t xml:space="preserve">71.3173904418945</t>
   </si>
   <si>
     <t xml:space="preserve">71.9391937255859</t>
@@ -2249,58 +2249,58 @@
     <t xml:space="preserve">72.7523422241211</t>
   </si>
   <si>
-    <t xml:space="preserve">72.6088638305664</t>
+    <t xml:space="preserve">72.6088562011719</t>
   </si>
   <si>
     <t xml:space="preserve">74.4264602661133</t>
   </si>
   <si>
-    <t xml:space="preserve">74.1394577026367</t>
+    <t xml:space="preserve">74.1394653320312</t>
   </si>
   <si>
     <t xml:space="preserve">71.7478713989258</t>
   </si>
   <si>
-    <t xml:space="preserve">71.9870376586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.2784957885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.4130477905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.8211822509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.7210464477539</t>
+    <t xml:space="preserve">71.9870300292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.2784881591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.4130630493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.8211898803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.7210540771484</t>
   </si>
   <si>
     <t xml:space="preserve">62.1336479187012</t>
   </si>
   <si>
-    <t xml:space="preserve">63.8077735900879</t>
+    <t xml:space="preserve">63.8077697753906</t>
   </si>
   <si>
     <t xml:space="preserve">61.8944931030273</t>
   </si>
   <si>
-    <t xml:space="preserve">60.9378662109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.8766174316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5672760009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.0889587402344</t>
+    <t xml:space="preserve">60.9378623962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.8766136169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5672721862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.0889549255371</t>
   </si>
   <si>
     <t xml:space="preserve">46.3778228759766</t>
   </si>
   <si>
-    <t xml:space="preserve">48.74072265625</t>
+    <t xml:space="preserve">48.7407264709473</t>
   </si>
   <si>
     <t xml:space="preserve">45.4594497680664</t>
@@ -2309,22 +2309,22 @@
     <t xml:space="preserve">41.7094230651855</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8714370727539</t>
+    <t xml:space="preserve">43.8714332580566</t>
   </si>
   <si>
     <t xml:space="preserve">45.2107276916504</t>
   </si>
   <si>
-    <t xml:space="preserve">45.344654083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1048698425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0844841003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2190361022949</t>
+    <t xml:space="preserve">45.3446578979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1048736572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0844879150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2190437316895</t>
   </si>
   <si>
     <t xml:space="preserve">59.1680793762207</t>
@@ -2339,58 +2339,58 @@
     <t xml:space="preserve">61.0813522338867</t>
   </si>
   <si>
-    <t xml:space="preserve">60.3638725280762</t>
+    <t xml:space="preserve">60.3638763427734</t>
   </si>
   <si>
     <t xml:space="preserve">61.1291847229004</t>
   </si>
   <si>
-    <t xml:space="preserve">61.4161720275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.6598052978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.5207901000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5641479492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.1381301879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0424690246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9901657104492</t>
+    <t xml:space="preserve">61.4161758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.6598129272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.5207862854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5641403198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.1381225585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0424652099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9901695251465</t>
   </si>
   <si>
     <t xml:space="preserve">61.033519744873</t>
   </si>
   <si>
-    <t xml:space="preserve">59.2684898376465</t>
+    <t xml:space="preserve">59.2684936523438</t>
   </si>
   <si>
     <t xml:space="preserve">60.9081382751465</t>
   </si>
   <si>
-    <t xml:space="preserve">61.7279586791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.7051963806152</t>
+    <t xml:space="preserve">61.7279624938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.705192565918</t>
   </si>
   <si>
     <t xml:space="preserve">64.7179107666016</t>
   </si>
   <si>
-    <t xml:space="preserve">63.3676109313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6569595336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.0909805297852</t>
+    <t xml:space="preserve">63.367603302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6569557189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.0909881591797</t>
   </si>
   <si>
     <t xml:space="preserve">64.4285659790039</t>
@@ -2399,7 +2399,7 @@
     <t xml:space="preserve">64.9108123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">68.4312286376953</t>
+    <t xml:space="preserve">68.4312362670898</t>
   </si>
   <si>
     <t xml:space="preserve">68.0936508178711</t>
@@ -2411,7 +2411,7 @@
     <t xml:space="preserve">68.6241302490234</t>
   </si>
   <si>
-    <t xml:space="preserve">69.9744338989258</t>
+    <t xml:space="preserve">69.9744415283203</t>
   </si>
   <si>
     <t xml:space="preserve">73.3984069824219</t>
@@ -2420,16 +2420,16 @@
     <t xml:space="preserve">74.1217880249023</t>
   </si>
   <si>
-    <t xml:space="preserve">73.9288864135742</t>
+    <t xml:space="preserve">73.9288787841797</t>
   </si>
   <si>
     <t xml:space="preserve">74.3628997802734</t>
   </si>
   <si>
-    <t xml:space="preserve">75.8578643798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.6522521972656</t>
+    <t xml:space="preserve">75.8578720092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.6522598266602</t>
   </si>
   <si>
     <t xml:space="preserve">71.8552017211914</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">67.0327072143555</t>
   </si>
   <si>
-    <t xml:space="preserve">67.2256088256836</t>
+    <t xml:space="preserve">67.2256011962891</t>
   </si>
   <si>
     <t xml:space="preserve">64.8625869750977</t>
@@ -2462,22 +2462,22 @@
     <t xml:space="preserve">67.3220596313477</t>
   </si>
   <si>
-    <t xml:space="preserve">69.9262084960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.1800537109375</t>
+    <t xml:space="preserve">69.9262161254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.180061340332</t>
   </si>
   <si>
     <t xml:space="preserve">70.4084548950195</t>
   </si>
   <si>
-    <t xml:space="preserve">71.3729629516602</t>
+    <t xml:space="preserve">71.3729553222656</t>
   </si>
   <si>
     <t xml:space="preserve">69.4921798706055</t>
   </si>
   <si>
-    <t xml:space="preserve">70.31201171875</t>
+    <t xml:space="preserve">70.3120040893555</t>
   </si>
   <si>
     <t xml:space="preserve">68.5276870727539</t>
@@ -2486,19 +2486,19 @@
     <t xml:space="preserve">68.2865600585938</t>
   </si>
   <si>
-    <t xml:space="preserve">68.6723556518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.0099258422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.2992858886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.1445541381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.2765045166016</t>
+    <t xml:space="preserve">68.6723480224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.0099334716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.2992782592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.1445617675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.2765121459961</t>
   </si>
   <si>
     <t xml:space="preserve">71.8069763183594</t>
@@ -2516,19 +2516,19 @@
     <t xml:space="preserve">71.6623077392578</t>
   </si>
   <si>
-    <t xml:space="preserve">72.3374557495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.8679428100586</t>
+    <t xml:space="preserve">72.3374481201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.8679351806641</t>
   </si>
   <si>
     <t xml:space="preserve">73.4466247558594</t>
   </si>
   <si>
-    <t xml:space="preserve">73.5430679321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.999885559082</t>
+    <t xml:space="preserve">73.5430755615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9998931884766</t>
   </si>
   <si>
     <t xml:space="preserve">73.0608291625977</t>
@@ -2537,10 +2537,10 @@
     <t xml:space="preserve">73.6877593994141</t>
   </si>
   <si>
-    <t xml:space="preserve">73.59130859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.9643859863281</t>
+    <t xml:space="preserve">73.5913162231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.9643783569336</t>
   </si>
   <si>
     <t xml:space="preserve">74.7487030029297</t>
@@ -2549,7 +2549,7 @@
     <t xml:space="preserve">81.9342193603516</t>
   </si>
   <si>
-    <t xml:space="preserve">82.9469528198242</t>
+    <t xml:space="preserve">82.9469451904297</t>
   </si>
   <si>
     <t xml:space="preserve">85.117073059082</t>
@@ -2564,7 +2564,7 @@
     <t xml:space="preserve">83.1398391723633</t>
   </si>
   <si>
-    <t xml:space="preserve">81.0179443359375</t>
+    <t xml:space="preserve">81.017936706543</t>
   </si>
   <si>
     <t xml:space="preserve">81.0661849975586</t>
@@ -2573,34 +2573,34 @@
     <t xml:space="preserve">82.6093673706055</t>
   </si>
   <si>
-    <t xml:space="preserve">80.8732757568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.0916290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3099746704102</t>
+    <t xml:space="preserve">80.8732833862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.0916213989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3099670410156</t>
   </si>
   <si>
     <t xml:space="preserve">84.5865936279297</t>
   </si>
   <si>
-    <t xml:space="preserve">84.6348190307617</t>
+    <t xml:space="preserve">84.6348114013672</t>
   </si>
   <si>
     <t xml:space="preserve">83.6703186035156</t>
   </si>
   <si>
-    <t xml:space="preserve">84.7795028686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.6830596923828</t>
+    <t xml:space="preserve">84.7794952392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.6830520629883</t>
   </si>
   <si>
     <t xml:space="preserve">87.3836441040039</t>
   </si>
   <si>
-    <t xml:space="preserve">86.2262496948242</t>
+    <t xml:space="preserve">86.2262420654297</t>
   </si>
   <si>
     <t xml:space="preserve">87.7212219238281</t>
@@ -2612,19 +2612,19 @@
     <t xml:space="preserve">89.3126449584961</t>
   </si>
   <si>
-    <t xml:space="preserve">90.6629333496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1070098876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.8658981323242</t>
+    <t xml:space="preserve">90.6629409790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1070251464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.8658905029297</t>
   </si>
   <si>
     <t xml:space="preserve">91.2416458129883</t>
   </si>
   <si>
-    <t xml:space="preserve">90.2771377563477</t>
+    <t xml:space="preserve">90.2771453857422</t>
   </si>
   <si>
     <t xml:space="preserve">90.5664901733398</t>
@@ -2633,43 +2633,43 @@
     <t xml:space="preserve">90.8076248168945</t>
   </si>
   <si>
-    <t xml:space="preserve">92.9777374267578</t>
+    <t xml:space="preserve">92.9777450561523</t>
   </si>
   <si>
     <t xml:space="preserve">95.0031890869141</t>
   </si>
   <si>
-    <t xml:space="preserve">94.9067459106445</t>
+    <t xml:space="preserve">94.90673828125</t>
   </si>
   <si>
     <t xml:space="preserve">95.7265625</t>
   </si>
   <si>
-    <t xml:space="preserve">93.2188720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5082168579102</t>
+    <t xml:space="preserve">93.218864440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5082092285156</t>
   </si>
   <si>
     <t xml:space="preserve">91.4827651977539</t>
   </si>
   <si>
-    <t xml:space="preserve">89.9395751953125</t>
+    <t xml:space="preserve">89.939567565918</t>
   </si>
   <si>
     <t xml:space="preserve">91.62744140625</t>
   </si>
   <si>
-    <t xml:space="preserve">92.1096954345703</t>
+    <t xml:space="preserve">92.1096878051758</t>
   </si>
   <si>
     <t xml:space="preserve">93.3635559082031</t>
   </si>
   <si>
-    <t xml:space="preserve">95.5336761474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9549560546875</t>
+    <t xml:space="preserve">95.5336685180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.954963684082</t>
   </si>
   <si>
     <t xml:space="preserve">94.8102874755859</t>
@@ -2678,7 +2678,7 @@
     <t xml:space="preserve">93.6046676635742</t>
   </si>
   <si>
-    <t xml:space="preserve">94.5209426879883</t>
+    <t xml:space="preserve">94.5209503173828</t>
   </si>
   <si>
     <t xml:space="preserve">92.6883850097656</t>
@@ -2687,25 +2687,25 @@
     <t xml:space="preserve">91.4345474243164</t>
   </si>
   <si>
-    <t xml:space="preserve">93.0259628295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.2925338745117</t>
+    <t xml:space="preserve">93.0259704589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.2925415039062</t>
   </si>
   <si>
     <t xml:space="preserve">97.2215423583984</t>
   </si>
   <si>
-    <t xml:space="preserve">100.115051269531</t>
+    <t xml:space="preserve">100.115043640137</t>
   </si>
   <si>
     <t xml:space="preserve">99.7292327880859</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6073303222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.8966903686523</t>
+    <t xml:space="preserve">97.6073226928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.8966979980469</t>
   </si>
   <si>
     <t xml:space="preserve">98.3789367675781</t>
@@ -2714,34 +2714,34 @@
     <t xml:space="preserve">96.3052597045898</t>
   </si>
   <si>
-    <t xml:space="preserve">93.7493362426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.8330688476562</t>
+    <t xml:space="preserve">93.7493438720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.8330764770508</t>
   </si>
   <si>
     <t xml:space="preserve">92.8812942504883</t>
   </si>
   <si>
-    <t xml:space="preserve">88.444580078125</t>
+    <t xml:space="preserve">88.4445877075195</t>
   </si>
   <si>
     <t xml:space="preserve">88.2034606933594</t>
   </si>
   <si>
-    <t xml:space="preserve">89.023307800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.1324615478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.2061462402344</t>
+    <t xml:space="preserve">89.0233001708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.1324691772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.2061386108398</t>
   </si>
   <si>
     <t xml:space="preserve">96.4499359130859</t>
   </si>
   <si>
-    <t xml:space="preserve">95.4372177124023</t>
+    <t xml:space="preserve">95.4372100830078</t>
   </si>
   <si>
     <t xml:space="preserve">95.7747955322266</t>
@@ -2753,25 +2753,25 @@
     <t xml:space="preserve">92.0614700317383</t>
   </si>
   <si>
-    <t xml:space="preserve">91.8685607910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.8203430175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7111740112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.855842590332</t>
+    <t xml:space="preserve">91.8685684204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.8203353881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.711181640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8558349609375</t>
   </si>
   <si>
     <t xml:space="preserve">91.3863143920898</t>
   </si>
   <si>
-    <t xml:space="preserve">90.7593841552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7694549560547</t>
+    <t xml:space="preserve">90.759391784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7694473266602</t>
   </si>
   <si>
     <t xml:space="preserve">88.2516937255859</t>
@@ -2783,13 +2783,13 @@
     <t xml:space="preserve">90.3735885620117</t>
   </si>
   <si>
-    <t xml:space="preserve">94.2798233032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.0842514038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.1452026367188</t>
+    <t xml:space="preserve">94.2798156738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.0842437744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.1451950073242</t>
   </si>
   <si>
     <t xml:space="preserve">92.495491027832</t>
@@ -2798,19 +2798,19 @@
     <t xml:space="preserve">89.4573211669922</t>
   </si>
   <si>
-    <t xml:space="preserve">91.675666809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.9168014526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7238845825195</t>
+    <t xml:space="preserve">91.6756744384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.9167938232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7238922119141</t>
   </si>
   <si>
     <t xml:space="preserve">91.0969619750977</t>
   </si>
   <si>
-    <t xml:space="preserve">90.9040679931641</t>
+    <t xml:space="preserve">90.9040756225586</t>
   </si>
   <si>
     <t xml:space="preserve">92.3508224487305</t>
@@ -2819,28 +2819,28 @@
     <t xml:space="preserve">93.4599990844727</t>
   </si>
   <si>
-    <t xml:space="preserve">92.5437164306641</t>
+    <t xml:space="preserve">92.5437088012695</t>
   </si>
   <si>
     <t xml:space="preserve">95.9194564819336</t>
   </si>
   <si>
-    <t xml:space="preserve">93.26708984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5564422607422</t>
+    <t xml:space="preserve">93.2670822143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5564498901367</t>
   </si>
   <si>
     <t xml:space="preserve">94.5691757202148</t>
   </si>
   <si>
-    <t xml:space="preserve">96.0641403198242</t>
+    <t xml:space="preserve">96.0641479492188</t>
   </si>
   <si>
     <t xml:space="preserve">98.4753875732422</t>
   </si>
   <si>
-    <t xml:space="preserve">100.018592834473</t>
+    <t xml:space="preserve">100.018585205078</t>
   </si>
   <si>
     <t xml:space="preserve">98.1860504150391</t>
@@ -2879,13 +2879,13 @@
     <t xml:space="preserve">102.815635681152</t>
   </si>
   <si>
-    <t xml:space="preserve">103.201431274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.500839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.404388427734</t>
+    <t xml:space="preserve">103.201438903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.500831604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.404396057129</t>
   </si>
   <si>
     <t xml:space="preserve">98.5718307495117</t>
@@ -2897,10 +2897,10 @@
     <t xml:space="preserve">94.135139465332</t>
   </si>
   <si>
-    <t xml:space="preserve">92.5919418334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.216194152832</t>
+    <t xml:space="preserve">92.5919342041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.2162017822266</t>
   </si>
   <si>
     <t xml:space="preserve">103.297882080078</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">101.561790466309</t>
   </si>
   <si>
-    <t xml:space="preserve">103.973030090332</t>
+    <t xml:space="preserve">103.973037719727</t>
   </si>
   <si>
     <t xml:space="preserve">103.780136108398</t>
@@ -2921,10 +2921,10 @@
     <t xml:space="preserve">105.323333740234</t>
   </si>
   <si>
-    <t xml:space="preserve">103.490791320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.069480895996</t>
+    <t xml:space="preserve">103.490783691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.069488525391</t>
   </si>
   <si>
     <t xml:space="preserve">108.023933410645</t>
@@ -2942,25 +2942,25 @@
     <t xml:space="preserve">107.445236206055</t>
   </si>
   <si>
-    <t xml:space="preserve">106.384284973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.891983032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.831024169922</t>
+    <t xml:space="preserve">106.38427734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.891990661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.831031799316</t>
   </si>
   <si>
     <t xml:space="preserve">108.795524597168</t>
   </si>
   <si>
-    <t xml:space="preserve">109.084884643555</t>
+    <t xml:space="preserve">109.084892272949</t>
   </si>
   <si>
     <t xml:space="preserve">107.059432983398</t>
   </si>
   <si>
-    <t xml:space="preserve">107.348793029785</t>
+    <t xml:space="preserve">107.348785400391</t>
   </si>
   <si>
     <t xml:space="preserve">109.56713104248</t>
@@ -70648,7 +70648,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6494791667</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>50937</v>
@@ -70669,6 +70669,32 @@
         <v>1817</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6496296296</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>59867</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>121.199996948242</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>118.699996948242</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>120.099998474121</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>120.400001525879</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>1803</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/REY.MI.xlsx
+++ b/data/REY.MI.xlsx
@@ -44,64 +44,64 @@
     <t xml:space="preserve">REY.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8380298614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3272094726562</t>
+    <t xml:space="preserve">28.8380279541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3272132873535</t>
   </si>
   <si>
     <t xml:space="preserve">27.6306400299072</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8396072387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2111167907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.000560760498</t>
+    <t xml:space="preserve">27.8396129608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2111148834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0005626678467</t>
   </si>
   <si>
     <t xml:space="preserve">28.5594005584717</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1414585113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1198215484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9789276123047</t>
+    <t xml:space="preserve">28.1414546966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1198196411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9789237976074</t>
   </si>
   <si>
     <t xml:space="preserve">26.8644104003906</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4448852539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9324893951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8163948059082</t>
+    <t xml:space="preserve">27.4448890686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.932487487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8163928985596</t>
   </si>
   <si>
     <t xml:space="preserve">28.2807731628418</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6770763397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0950183868408</t>
+    <t xml:space="preserve">27.6770782470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0950202941895</t>
   </si>
   <si>
     <t xml:space="preserve">27.862829208374</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2591342926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7018775939941</t>
+    <t xml:space="preserve">27.2591323852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7018795013428</t>
   </si>
   <si>
     <t xml:space="preserve">26.167839050293</t>
@@ -110,46 +110,46 @@
     <t xml:space="preserve">25.2855167388916</t>
   </si>
   <si>
-    <t xml:space="preserve">24.379976272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6121654510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0053100585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5177059173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6570224761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6074199676514</t>
+    <t xml:space="preserve">24.3799781799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6121692657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0053081512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5177097320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6570205688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6074237823486</t>
   </si>
   <si>
     <t xml:space="preserve">26.3071556091309</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0733814239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2142791748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4696922302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0517463684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7034587860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7266826629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7483139038086</t>
+    <t xml:space="preserve">27.0733833312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.214282989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4696884155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0517425537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7034606933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7266788482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7483158111572</t>
   </si>
   <si>
     <t xml:space="preserve">26.4929065704346</t>
@@ -161,25 +161,25 @@
     <t xml:space="preserve">27.1894779205322</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2359161376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1662616729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9092674255371</t>
+    <t xml:space="preserve">27.2359142303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.166259765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9092655181885</t>
   </si>
   <si>
     <t xml:space="preserve">29.0237827301025</t>
   </si>
   <si>
-    <t xml:space="preserve">31.554651260376</t>
+    <t xml:space="preserve">31.5546531677246</t>
   </si>
   <si>
     <t xml:space="preserve">30.3008289337158</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4169216156006</t>
+    <t xml:space="preserve">30.4169254302979</t>
   </si>
   <si>
     <t xml:space="preserve">29.9989776611328</t>
@@ -188,16 +188,16 @@
     <t xml:space="preserve">29.9757614135742</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7900104522705</t>
+    <t xml:space="preserve">29.7900085449219</t>
   </si>
   <si>
     <t xml:space="preserve">29.9525394439697</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2311706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7203540802002</t>
+    <t xml:space="preserve">30.2311687469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7203521728516</t>
   </si>
   <si>
     <t xml:space="preserve">30.0686359405518</t>
@@ -209,49 +209,49 @@
     <t xml:space="preserve">29.5578212738037</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3256301879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4881629943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5113792419434</t>
+    <t xml:space="preserve">29.325626373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4881610870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.511381149292</t>
   </si>
   <si>
     <t xml:space="preserve">29.2095336914062</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1615123748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3720645904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5345973968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4433040618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6754951477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8612518310547</t>
+    <t xml:space="preserve">30.1615104675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3720664978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5345993041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4433059692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6754970550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8612480163574</t>
   </si>
   <si>
     <t xml:space="preserve">28.8148097991943</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9076843261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6290588378906</t>
+    <t xml:space="preserve">28.9076881408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6290607452393</t>
   </si>
   <si>
     <t xml:space="preserve">28.4200859069824</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6775989532471</t>
+    <t xml:space="preserve">28.6775970458984</t>
   </si>
   <si>
     <t xml:space="preserve">28.5605487823486</t>
@@ -260,61 +260,61 @@
     <t xml:space="preserve">29.0287532806396</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3264446258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5137310028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7946529388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0053462982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2628593444824</t>
+    <t xml:space="preserve">28.3264465332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.513729095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7946491241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0053443908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2628574371338</t>
   </si>
   <si>
     <t xml:space="preserve">30.1992664337158</t>
   </si>
   <si>
-    <t xml:space="preserve">30.503604888916</t>
+    <t xml:space="preserve">30.5036029815674</t>
   </si>
   <si>
     <t xml:space="preserve">30.550422668457</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9015808105469</t>
+    <t xml:space="preserve">30.901575088501</t>
   </si>
   <si>
     <t xml:space="preserve">30.6674747467041</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7142963409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4567813873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.43337059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2695007324219</t>
+    <t xml:space="preserve">30.7142925262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4567852020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4333686828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2695026397705</t>
   </si>
   <si>
     <t xml:space="preserve">29.8949337005615</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1859836578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3096752166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4969596862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6943702697754</t>
+    <t xml:space="preserve">28.1859874725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3096771240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4969577789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6943683624268</t>
   </si>
   <si>
     <t xml:space="preserve">25.7747230529785</t>
@@ -323,37 +323,37 @@
     <t xml:space="preserve">26.8047771453857</t>
   </si>
   <si>
-    <t xml:space="preserve">27.319803237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9218273162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5070877075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.945240020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8215446472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2195224761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.10910987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6241359710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3666248321533</t>
+    <t xml:space="preserve">27.3197994232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9218292236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5070858001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9452381134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8215465545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.219518661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1091156005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6241340637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3666229248047</t>
   </si>
   <si>
     <t xml:space="preserve">28.303035736084</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8882923126221</t>
+    <t xml:space="preserve">28.8882942199707</t>
   </si>
   <si>
     <t xml:space="preserve">28.7478332519531</t>
@@ -365,46 +365,46 @@
     <t xml:space="preserve">28.9819355010986</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9117050170898</t>
+    <t xml:space="preserve">28.9117031097412</t>
   </si>
   <si>
     <t xml:space="preserve">29.3799076080322</t>
   </si>
   <si>
-    <t xml:space="preserve">29.450138092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8481101989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1524467468262</t>
+    <t xml:space="preserve">29.4501399993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8481159210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1524505615234</t>
   </si>
   <si>
     <t xml:space="preserve">29.9651660919189</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7244167327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1458015441895</t>
+    <t xml:space="preserve">28.7244205474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1458053588867</t>
   </si>
   <si>
     <t xml:space="preserve">29.0989856719971</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9351100921631</t>
+    <t xml:space="preserve">28.9351139068604</t>
   </si>
   <si>
     <t xml:space="preserve">28.4903182983398</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9752922058105</t>
+    <t xml:space="preserve">27.9752902984619</t>
   </si>
   <si>
     <t xml:space="preserve">28.3732643127441</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0923442840576</t>
+    <t xml:space="preserve">28.092342376709</t>
   </si>
   <si>
     <t xml:space="preserve">27.2729835510254</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">27.0622882843018</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0388832092285</t>
+    <t xml:space="preserve">27.0388793945312</t>
   </si>
   <si>
     <t xml:space="preserve">26.8984184265137</t>
@@ -422,103 +422,103 @@
     <t xml:space="preserve">26.1492881774902</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7981338500977</t>
+    <t xml:space="preserve">25.7981357574463</t>
   </si>
   <si>
     <t xml:space="preserve">25.891773223877</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7579574584961</t>
+    <t xml:space="preserve">26.7579593658447</t>
   </si>
   <si>
     <t xml:space="preserve">27.95188331604</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8816509246826</t>
+    <t xml:space="preserve">27.881649017334</t>
   </si>
   <si>
     <t xml:space="preserve">27.8114223480225</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9050598144531</t>
+    <t xml:space="preserve">27.9050636291504</t>
   </si>
   <si>
     <t xml:space="preserve">27.2963924407959</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8582420349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5773181915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7177772521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.741189956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.045524597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7880096435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3900356292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1223964691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6541900634766</t>
+    <t xml:space="preserve">27.8582382202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.577320098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7177791595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7411861419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0455226898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7880077362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3900337219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1223945617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6541881561279</t>
   </si>
   <si>
     <t xml:space="preserve">28.2093944549561</t>
   </si>
   <si>
-    <t xml:space="preserve">27.413444519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0856990814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.851598739624</t>
+    <t xml:space="preserve">27.4134464263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0857009887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8515968322754</t>
   </si>
   <si>
     <t xml:space="preserve">27.4368534088135</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6877269744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2261619567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8281879425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6409072875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4536228179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5706748962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.523853302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3365726470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.751314163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3299312591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7446727752686</t>
+    <t xml:space="preserve">26.6877212524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2261638641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8281898498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.640905380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4536209106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5706729888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5238552093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3365707397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7513179779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.329927444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7446689605713</t>
   </si>
   <si>
     <t xml:space="preserve">24.7680835723877</t>
@@ -536,25 +536,25 @@
     <t xml:space="preserve">25.4703903198242</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5172100067139</t>
+    <t xml:space="preserve">25.5172119140625</t>
   </si>
   <si>
     <t xml:space="preserve">25.2831077575684</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1660537719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4469814300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0958271026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9319534301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0724182128906</t>
+    <t xml:space="preserve">25.1660556793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4469795227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0958251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9319515228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0724143981934</t>
   </si>
   <si>
     <t xml:space="preserve">25.6342639923096</t>
@@ -563,28 +563,28 @@
     <t xml:space="preserve">26.1961097717285</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1726989746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8348293304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9284725189209</t>
+    <t xml:space="preserve">26.172700881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.834831237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9284706115723</t>
   </si>
   <si>
     <t xml:space="preserve">27.4602661132812</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9986991882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6307773590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2160396575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3330879211426</t>
+    <t xml:space="preserve">27.9987010955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6307830810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2160358428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3330898284912</t>
   </si>
   <si>
     <t xml:space="preserve">28.8648853302002</t>
@@ -593,49 +593,49 @@
     <t xml:space="preserve">28.3498554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6073684692383</t>
+    <t xml:space="preserve">28.6073703765869</t>
   </si>
   <si>
     <t xml:space="preserve">29.4735507965088</t>
   </si>
   <si>
-    <t xml:space="preserve">29.239444732666</t>
+    <t xml:space="preserve">29.2394485473633</t>
   </si>
   <si>
     <t xml:space="preserve">29.7076530456543</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4267311096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8313484191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9952163696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4868354797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2527294158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3697834014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1356773376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1891441345215</t>
+    <t xml:space="preserve">29.4267292022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8313446044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9952125549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4868335723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2527351379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3697814941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1356830596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1891479492188</t>
   </si>
   <si>
     <t xml:space="preserve">32.3061943054199</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2660179138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0619659423828</t>
+    <t xml:space="preserve">33.2660217285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0619621276855</t>
   </si>
   <si>
     <t xml:space="preserve">34.6472244262695</t>
@@ -644,7 +644,7 @@
     <t xml:space="preserve">34.4599418640137</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7408638000488</t>
+    <t xml:space="preserve">34.7408599853516</t>
   </si>
   <si>
     <t xml:space="preserve">34.6706352233887</t>
@@ -653,19 +653,19 @@
     <t xml:space="preserve">34.9983749389648</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8579139709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1790161132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7642707824707</t>
+    <t xml:space="preserve">34.8579177856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1790199279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.764274597168</t>
   </si>
   <si>
     <t xml:space="preserve">34.8813247680664</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3897132873535</t>
+    <t xml:space="preserve">34.3897018432617</t>
   </si>
   <si>
     <t xml:space="preserve">34.4131202697754</t>
@@ -674,28 +674,28 @@
     <t xml:space="preserve">35.6070442199707</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4665794372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7943229675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.8243751525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6671524047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8778495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9882469177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5735130310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6203231811523</t>
+    <t xml:space="preserve">35.4665908813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7943305969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.8243789672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6671409606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8778457641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9882583618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5735092163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6203346252441</t>
   </si>
   <si>
     <t xml:space="preserve">37.6085433959961</t>
@@ -704,151 +704,151 @@
     <t xml:space="preserve">37.7264404296875</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9150733947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1980133056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.938648223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1508636474609</t>
+    <t xml:space="preserve">37.9150619506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1980209350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9386405944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1508598327637</t>
   </si>
   <si>
     <t xml:space="preserve">37.4906425476074</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0232849121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.084342956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0607566833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8013916015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2397079467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0275001525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4519233703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7112884521484</t>
+    <t xml:space="preserve">39.0232810974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0843353271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0607528686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8013877868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2397041320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0275039672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4519195556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.711296081543</t>
   </si>
   <si>
     <t xml:space="preserve">41.499080657959</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8056030273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.324348449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1828651428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.088550567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2771873474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8291816711426</t>
+    <t xml:space="preserve">41.805606842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3243446350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1828689575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0885581970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2771911621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8291854858398</t>
   </si>
   <si>
     <t xml:space="preserve">39.9664421081543</t>
   </si>
   <si>
-    <t xml:space="preserve">39.5891761779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4338073730469</t>
+    <t xml:space="preserve">39.5891799926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4338035583496</t>
   </si>
   <si>
     <t xml:space="preserve">38.9997024536133</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6363372802734</t>
+    <t xml:space="preserve">39.6363334655762</t>
   </si>
   <si>
     <t xml:space="preserve">39.9428634643555</t>
   </si>
   <si>
-    <t xml:space="preserve">40.4380226135254</t>
+    <t xml:space="preserve">40.4380187988281</t>
   </si>
   <si>
     <t xml:space="preserve">38.551700592041</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0565414428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1411819458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3298034667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0704345703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1647567749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6696014404297</t>
+    <t xml:space="preserve">38.0565376281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1411743164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3298110961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.070442199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1647529602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6695976257324</t>
   </si>
   <si>
     <t xml:space="preserve">38.834644317627</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9053802490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0940208435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8110656738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2687568664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7403335571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6931800842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2354965209961</t>
+    <t xml:space="preserve">38.905387878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0940246582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8110733032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2687454223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7403297424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.693172454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2354888916016</t>
   </si>
   <si>
     <t xml:space="preserve">39.2590713500977</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1357154846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5129776000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7765617370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8001441955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5075149536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3188819885254</t>
+    <t xml:space="preserve">42.1357116699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5129737854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7765655517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8001403808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.507511138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3188743591309</t>
   </si>
   <si>
     <t xml:space="preserve">45.8140411376953</t>
@@ -857,82 +857,82 @@
     <t xml:space="preserve">44.6822509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7862510681152</t>
+    <t xml:space="preserve">43.7862434387207</t>
   </si>
   <si>
     <t xml:space="preserve">44.7529830932617</t>
   </si>
   <si>
-    <t xml:space="preserve">45.130241394043</t>
+    <t xml:space="preserve">45.1302490234375</t>
   </si>
   <si>
     <t xml:space="preserve">44.4464530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5879325866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3285598754883</t>
+    <t xml:space="preserve">44.5879364013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3285636901855</t>
   </si>
   <si>
     <t xml:space="preserve">44.3049812316895</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6211967468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1731948852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0788688659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5837211608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2675094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3660354614258</t>
+    <t xml:space="preserve">43.6211929321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1731872558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0788726806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5837173461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2675018310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.366039276123</t>
   </si>
   <si>
     <t xml:space="preserve">44.9887733459473</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4936180114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.5171890258789</t>
+    <t xml:space="preserve">44.4936141967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.5171966552734</t>
   </si>
   <si>
     <t xml:space="preserve">45.6254081726074</t>
   </si>
   <si>
-    <t xml:space="preserve">45.861198425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4035148620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5824699401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0637359619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1344680786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1580429077148</t>
+    <t xml:space="preserve">45.8611946105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4035186767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5824737548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0637283325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1344604492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1580352783203</t>
   </si>
   <si>
     <t xml:space="preserve">47.9125709533691</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3508987426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7378387451172</t>
+    <t xml:space="preserve">49.3508949279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7378349304199</t>
   </si>
   <si>
     <t xml:space="preserve">48.101203918457</t>
@@ -950,52 +950,52 @@
     <t xml:space="preserve">47.8654174804688</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9597244262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1858444213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2717170715332</t>
+    <t xml:space="preserve">47.9597282409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1858367919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2717208862305</t>
   </si>
   <si>
     <t xml:space="preserve">45.0359306335449</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5643539428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9748764038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5601387023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9138221740723</t>
+    <t xml:space="preserve">44.5643501281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9748725891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.560131072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9138145446777</t>
   </si>
   <si>
     <t xml:space="preserve">42.7251853942871</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2064552307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4328117370605</t>
+    <t xml:space="preserve">42.2064437866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4328079223633</t>
   </si>
   <si>
     <t xml:space="preserve">42.1781578063965</t>
   </si>
   <si>
-    <t xml:space="preserve">43.3476753234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9800834655762</t>
+    <t xml:space="preserve">43.3476715087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9800872802734</t>
   </si>
   <si>
     <t xml:space="preserve">41.3010139465332</t>
   </si>
   <si>
-    <t xml:space="preserve">42.0838432312012</t>
+    <t xml:space="preserve">42.0838394165039</t>
   </si>
   <si>
     <t xml:space="preserve">42.7534828186035</t>
@@ -1004,13 +1004,13 @@
     <t xml:space="preserve">42.5931434631348</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4799652099609</t>
+    <t xml:space="preserve">42.4799690246582</t>
   </si>
   <si>
     <t xml:space="preserve">43.0081329345703</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0458641052246</t>
+    <t xml:space="preserve">43.0458602905273</t>
   </si>
   <si>
     <t xml:space="preserve">43.3288078308105</t>
@@ -1019,22 +1019,22 @@
     <t xml:space="preserve">41.3953285217285</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4891471862793</t>
+    <t xml:space="preserve">43.4891510009766</t>
   </si>
   <si>
     <t xml:space="preserve">44.2342491149902</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1210670471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2439231872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1027030944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1689758300781</t>
+    <t xml:space="preserve">44.1210632324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2439308166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1026992797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1689720153809</t>
   </si>
   <si>
     <t xml:space="preserve">40.2729682922363</t>
@@ -1043,25 +1043,25 @@
     <t xml:space="preserve">42.4045104980469</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7626686096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.253101348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0547981262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.951042175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2809028625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1488647460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3094482421875</t>
+    <t xml:space="preserve">43.7626647949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2531051635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0547943115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9510459899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2809066772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1488609313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3094520568848</t>
   </si>
   <si>
     <t xml:space="preserve">44.9982032775879</t>
@@ -1073,25 +1073,25 @@
     <t xml:space="preserve">45.1679725646973</t>
   </si>
   <si>
-    <t xml:space="preserve">45.592399597168</t>
+    <t xml:space="preserve">45.5923957824707</t>
   </si>
   <si>
     <t xml:space="preserve">44.6586608886719</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2533531188965</t>
+    <t xml:space="preserve">43.253360748291</t>
   </si>
   <si>
     <t xml:space="preserve">43.6683502197266</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2248077392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0830879211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2057037353516</t>
+    <t xml:space="preserve">44.2248115539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0830917358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.205696105957</t>
   </si>
   <si>
     <t xml:space="preserve">46.3280601501465</t>
@@ -1100,13 +1100,13 @@
     <t xml:space="preserve">46.0356826782227</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6584091186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5169372558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1682243347168</t>
+    <t xml:space="preserve">45.6584167480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5169410705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1682281494141</t>
   </si>
   <si>
     <t xml:space="preserve">43.8664093017578</t>
@@ -1118,91 +1118,91 @@
     <t xml:space="preserve">43.8852729797363</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4606018066406</t>
+    <t xml:space="preserve">44.4605979919434</t>
   </si>
   <si>
     <t xml:space="preserve">45.6112594604492</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6301193237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7244338989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2903442382812</t>
+    <t xml:space="preserve">45.6301231384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7244415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.290340423584</t>
   </si>
   <si>
     <t xml:space="preserve">46.026252746582</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2148780822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6487350463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.705322265625</t>
+    <t xml:space="preserve">46.2148818969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.648738861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7053260803223</t>
   </si>
   <si>
     <t xml:space="preserve">46.5921478271484</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8939590454102</t>
+    <t xml:space="preserve">46.8939552307129</t>
   </si>
   <si>
     <t xml:space="preserve">47.7710990905762</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8182601928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1955146789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9972076416016</t>
+    <t xml:space="preserve">47.8182525634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1955261230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9972114562988</t>
   </si>
   <si>
     <t xml:space="preserve">48.5727844238281</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3273124694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3176345825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4119529724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8460540771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3744697570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.223316192627</t>
+    <t xml:space="preserve">49.3273162841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3176307678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4119491577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8460464477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3744735717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2233123779297</t>
   </si>
   <si>
     <t xml:space="preserve">50.0818405151367</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5353088378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1960182189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2052040100098</t>
+    <t xml:space="preserve">47.5353126525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1960220336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2052001953125</t>
   </si>
   <si>
     <t xml:space="preserve">48.0068893432617</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2523612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4223823547363</t>
+    <t xml:space="preserve">47.2523536682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4223785400391</t>
   </si>
   <si>
     <t xml:space="preserve">45.8376159667969</t>
@@ -1214,13 +1214,13 @@
     <t xml:space="preserve">45.8753471374512</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5732841491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.4687919616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8085708618164</t>
+    <t xml:space="preserve">46.5732879638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.4687881469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8085784912109</t>
   </si>
   <si>
     <t xml:space="preserve">46.4789657592773</t>
@@ -1229,25 +1229,25 @@
     <t xml:space="preserve">47.3938331604004</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5166893005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1774063110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7812767028809</t>
+    <t xml:space="preserve">46.5166854858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1774101257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7812805175781</t>
   </si>
   <si>
     <t xml:space="preserve">44.8378639221191</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4983291625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1776580810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.895206451416</t>
+    <t xml:space="preserve">44.4983329772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1776504516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8952026367188</t>
   </si>
   <si>
     <t xml:space="preserve">42.291332244873</t>
@@ -1256,7 +1256,7 @@
     <t xml:space="preserve">42.4988288879395</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0652275085449</t>
+    <t xml:space="preserve">41.0652313232422</t>
   </si>
   <si>
     <t xml:space="preserve">41.9517936706543</t>
@@ -1265,19 +1265,19 @@
     <t xml:space="preserve">45.3283157348633</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4414863586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4603500366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4037628173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1017074584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.988525390625</t>
+    <t xml:space="preserve">45.4414939880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4603576660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4037590026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1017036437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9885292053223</t>
   </si>
   <si>
     <t xml:space="preserve">46.3846473693848</t>
@@ -1286,19 +1286,19 @@
     <t xml:space="preserve">49.0443649291992</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9028854370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.2898406982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1193237304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6948928833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6005783081055</t>
+    <t xml:space="preserve">48.902889251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.2898330688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1193199157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6949005126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6005859375</t>
   </si>
   <si>
     <t xml:space="preserve">50.9328575134277</t>
@@ -1307,28 +1307,28 @@
     <t xml:space="preserve">50.4107093811035</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0277900695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.2144813537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1195487976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.739803314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8410949707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5024642944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2714881896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3664169311523</t>
+    <t xml:space="preserve">51.0277938842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.2144775390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.119556427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.7398071289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8410987854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5024719238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2714920043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3664207458496</t>
   </si>
   <si>
     <t xml:space="preserve">49.0816192626953</t>
@@ -1340,31 +1340,31 @@
     <t xml:space="preserve">48.2746620178223</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8221473693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.084789276123</t>
+    <t xml:space="preserve">46.8221549987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0847969055176</t>
   </si>
   <si>
     <t xml:space="preserve">48.6544075012207</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3189506530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6512260437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9835014343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3632431030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2176628112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1733703613281</t>
+    <t xml:space="preserve">49.3189582824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6512298583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9835052490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3632469177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2176551818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1733741760254</t>
   </si>
   <si>
     <t xml:space="preserve">51.455005645752</t>
@@ -1385,37 +1385,37 @@
     <t xml:space="preserve">54.6828002929688</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1100120544434</t>
+    <t xml:space="preserve">55.1100196838379</t>
   </si>
   <si>
     <t xml:space="preserve">55.5846900939941</t>
   </si>
   <si>
-    <t xml:space="preserve">56.3916511535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.7302742004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.0625495910645</t>
+    <t xml:space="preserve">56.3916435241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.7302703857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.0625457763672</t>
   </si>
   <si>
     <t xml:space="preserve">55.4897575378418</t>
   </si>
   <si>
-    <t xml:space="preserve">55.2524223327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.1638450622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.6385154724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0182609558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3030662536621</t>
+    <t xml:space="preserve">55.2524185180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.1638412475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.6385192871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0182571411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3030624389648</t>
   </si>
   <si>
     <t xml:space="preserve">54.1131973266602</t>
@@ -1424,49 +1424,49 @@
     <t xml:space="preserve">53.8283882141113</t>
   </si>
   <si>
-    <t xml:space="preserve">54.7777404785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4391098022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9137840270996</t>
+    <t xml:space="preserve">54.7777442932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4391136169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9137916564941</t>
   </si>
   <si>
     <t xml:space="preserve">56.296703338623</t>
   </si>
   <si>
-    <t xml:space="preserve">56.0118980407715</t>
+    <t xml:space="preserve">56.0119018554688</t>
   </si>
   <si>
     <t xml:space="preserve">56.2017707824707</t>
   </si>
   <si>
-    <t xml:space="preserve">56.5340423583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6764526367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9676094055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5942268371582</t>
+    <t xml:space="preserve">56.5340461730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.676441192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9676170349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5942306518555</t>
   </si>
   <si>
     <t xml:space="preserve">53.0214347839355</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1574821472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3505325317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9265022277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.879035949707</t>
+    <t xml:space="preserve">55.1574783325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.350528717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9264984130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.8790321350098</t>
   </si>
   <si>
     <t xml:space="preserve">54.0657234191895</t>
@@ -1475,55 +1475,55 @@
     <t xml:space="preserve">54.5878715515137</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4486389160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.685977935791</t>
+    <t xml:space="preserve">53.4486465454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.6859817504883</t>
   </si>
   <si>
     <t xml:space="preserve">53.3062400817871</t>
   </si>
   <si>
-    <t xml:space="preserve">52.404354095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.075252532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4581756591797</t>
+    <t xml:space="preserve">52.4043502807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0752563476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.458179473877</t>
   </si>
   <si>
     <t xml:space="preserve">52.2619514465332</t>
   </si>
   <si>
-    <t xml:space="preserve">51.882209777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1606597900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.2081298828125</t>
+    <t xml:space="preserve">51.8822059631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1606636047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.2081260681152</t>
   </si>
   <si>
     <t xml:space="preserve">53.5435791015625</t>
   </si>
   <si>
-    <t xml:space="preserve">54.540397644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2049522399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2492370605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.1036605834961</t>
+    <t xml:space="preserve">54.5404014587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.204948425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2492408752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1036643981934</t>
   </si>
   <si>
     <t xml:space="preserve">57.2460632324219</t>
   </si>
   <si>
-    <t xml:space="preserve">57.9106063842773</t>
+    <t xml:space="preserve">57.9106101989746</t>
   </si>
   <si>
     <t xml:space="preserve">56.9612579345703</t>
@@ -1532,10 +1532,10 @@
     <t xml:space="preserve">50.7904510498047</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4138946533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.012020111084</t>
+    <t xml:space="preserve">49.4138832092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0120239257812</t>
   </si>
   <si>
     <t xml:space="preserve">47.0499992370605</t>
@@ -1544,43 +1544,43 @@
     <t xml:space="preserve">48.2271957397461</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4677124023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0309753417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3157768249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3474731445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7525596618652</t>
+    <t xml:space="preserve">47.4677085876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0309715270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3157730102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3474769592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.752555847168</t>
   </si>
   <si>
     <t xml:space="preserve">44.6766128540039</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6955986022949</t>
+    <t xml:space="preserve">44.6956024169922</t>
   </si>
   <si>
     <t xml:space="preserve">46.1955757141113</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5563278198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4803848266602</t>
+    <t xml:space="preserve">46.556339263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4803771972656</t>
   </si>
   <si>
     <t xml:space="preserve">45.9487495422363</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4107475280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5373420715332</t>
+    <t xml:space="preserve">47.4107513427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5373458862305</t>
   </si>
   <si>
     <t xml:space="preserve">46.5183563232422</t>
@@ -1589,64 +1589,64 @@
     <t xml:space="preserve">46.746208190918</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4424133300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4930534362793</t>
+    <t xml:space="preserve">46.4424095153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4930572509766</t>
   </si>
   <si>
     <t xml:space="preserve">45.1322975158691</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5690002441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7019119262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3601913452148</t>
+    <t xml:space="preserve">45.5690040588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7019157409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3601875305176</t>
   </si>
   <si>
     <t xml:space="preserve">41.4677963256836</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9234848022461</t>
+    <t xml:space="preserve">41.9234809875488</t>
   </si>
   <si>
     <t xml:space="preserve">42.8728370666504</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7462463378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2968711853027</t>
+    <t xml:space="preserve">43.7462501525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2968673706055</t>
   </si>
   <si>
     <t xml:space="preserve">43.8601684570312</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7209053039551</t>
+    <t xml:space="preserve">45.7209014892578</t>
   </si>
   <si>
     <t xml:space="preserve">46.7841758728027</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7050514221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2398643493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2905082702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.189266204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2082481384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2841911315918</t>
+    <t xml:space="preserve">47.7050476074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2398681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2905120849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1892623901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.208251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2841987609863</t>
   </si>
   <si>
     <t xml:space="preserve">47.3158149719238</t>
@@ -1655,46 +1655,46 @@
     <t xml:space="preserve">47.3727798461914</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6132926940918</t>
+    <t xml:space="preserve">46.6132965087891</t>
   </si>
   <si>
     <t xml:space="preserve">44.4867401123047</t>
   </si>
   <si>
-    <t xml:space="preserve">43.5373840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5184020996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0753784179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5627365112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2146415710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8475379943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4551239013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2526206970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8095588684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1956176757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0310516357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.315860748291</t>
+    <t xml:space="preserve">43.5373878479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5183982849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.075382232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5627288818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2146492004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8475341796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4551200866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2526168823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8095626831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.195613861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0310478210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3158531188965</t>
   </si>
   <si>
     <t xml:space="preserve">44.3348426818848</t>
@@ -1703,49 +1703,49 @@
     <t xml:space="preserve">43.8791580200195</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7398872375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8348197937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.803165435791</t>
+    <t xml:space="preserve">45.7398910522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8348236083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8031616210938</t>
   </si>
   <si>
     <t xml:space="preserve">46.3854484558105</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4234275817871</t>
+    <t xml:space="preserve">46.4234237670898</t>
   </si>
   <si>
     <t xml:space="preserve">47.1829071044922</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1765518188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.3696022033691</t>
+    <t xml:space="preserve">49.1765480041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.3695983886719</t>
   </si>
   <si>
     <t xml:space="preserve">45.4360961914062</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0753364562988</t>
+    <t xml:space="preserve">45.0753440856934</t>
   </si>
   <si>
     <t xml:space="preserve">45.6449584960938</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2588500976562</t>
+    <t xml:space="preserve">47.2588539123535</t>
   </si>
   <si>
     <t xml:space="preserve">48.4645347595215</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8885650634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.125904083252</t>
+    <t xml:space="preserve">49.8885612487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1259002685547</t>
   </si>
   <si>
     <t xml:space="preserve">50.6955184936523</t>
@@ -1757,25 +1757,25 @@
     <t xml:space="preserve">49.9360313415527</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0784339904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1670150756836</t>
+    <t xml:space="preserve">50.0784301757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1670188903809</t>
   </si>
   <si>
     <t xml:space="preserve">52.6891632080078</t>
   </si>
   <si>
-    <t xml:space="preserve">52.9739646911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.2555923461914</t>
+    <t xml:space="preserve">52.9739685058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.2555961608887</t>
   </si>
   <si>
     <t xml:space="preserve">53.2587738037109</t>
   </si>
   <si>
-    <t xml:space="preserve">53.9707870483398</t>
+    <t xml:space="preserve">53.9707908630371</t>
   </si>
   <si>
     <t xml:space="preserve">53.7334480285645</t>
@@ -1784,43 +1784,43 @@
     <t xml:space="preserve">55.2998886108398</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3979988098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4011764526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.9233207702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4929313659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4454689025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4961128234863</t>
+    <t xml:space="preserve">54.3979949951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4011726379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9233245849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4929351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4454650878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4961090087891</t>
   </si>
   <si>
     <t xml:space="preserve">54.6353378295898</t>
   </si>
   <si>
-    <t xml:space="preserve">55.9644317626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.7270965576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1068344116211</t>
+    <t xml:space="preserve">55.9644355773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.7270889282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1068382263184</t>
   </si>
   <si>
     <t xml:space="preserve">55.5328521728516</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5239143371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5717506408691</t>
+    <t xml:space="preserve">53.5239105224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5717430114746</t>
   </si>
   <si>
     <t xml:space="preserve">52.615104675293</t>
@@ -1835,43 +1835,43 @@
     <t xml:space="preserve">54.5283851623535</t>
   </si>
   <si>
-    <t xml:space="preserve">55.9633445739746</t>
+    <t xml:space="preserve">55.9633407592773</t>
   </si>
   <si>
     <t xml:space="preserve">56.0590019226074</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1980285644531</t>
+    <t xml:space="preserve">55.1980323791504</t>
   </si>
   <si>
     <t xml:space="preserve">56.776481628418</t>
   </si>
   <si>
-    <t xml:space="preserve">56.0111694335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.6285171508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2024993896484</t>
+    <t xml:space="preserve">56.0111656188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.6285209655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2024955749512</t>
   </si>
   <si>
     <t xml:space="preserve">55.9155082702637</t>
   </si>
   <si>
-    <t xml:space="preserve">56.4416618347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5806846618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3459968566895</t>
+    <t xml:space="preserve">56.4416580200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.580680847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3460006713867</t>
   </si>
   <si>
     <t xml:space="preserve">55.1501998901367</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5762100219727</t>
+    <t xml:space="preserve">54.5762176513672</t>
   </si>
   <si>
     <t xml:space="preserve">54.4327201843262</t>
@@ -1880,10 +1880,10 @@
     <t xml:space="preserve">54.8632049560547</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9199829101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8243217468262</t>
+    <t xml:space="preserve">56.9199752807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8243141174316</t>
   </si>
   <si>
     <t xml:space="preserve">57.2547988891602</t>
@@ -1898,28 +1898,28 @@
     <t xml:space="preserve">58.2114372253418</t>
   </si>
   <si>
-    <t xml:space="preserve">57.6374549865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5462608337402</t>
+    <t xml:space="preserve">57.6374588012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5462646484375</t>
   </si>
   <si>
     <t xml:space="preserve">57.924446105957</t>
   </si>
   <si>
-    <t xml:space="preserve">58.3549346923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.7331199645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3504638671875</t>
+    <t xml:space="preserve">58.3549385070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.7331161499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3504676818848</t>
   </si>
   <si>
     <t xml:space="preserve">58.3071022033691</t>
   </si>
   <si>
-    <t xml:space="preserve">60.2682151794434</t>
+    <t xml:space="preserve">60.2682113647461</t>
   </si>
   <si>
     <t xml:space="preserve">60.172550201416</t>
@@ -1928,16 +1928,16 @@
     <t xml:space="preserve">59.7420616149902</t>
   </si>
   <si>
-    <t xml:space="preserve">59.2159118652344</t>
+    <t xml:space="preserve">59.2159080505371</t>
   </si>
   <si>
     <t xml:space="preserve">59.1202430725098</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3026351928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.8287811279297</t>
+    <t xml:space="preserve">57.3026275634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.828784942627</t>
   </si>
   <si>
     <t xml:space="preserve">58.1157760620117</t>
@@ -1949,22 +1949,22 @@
     <t xml:space="preserve">59.0245819091797</t>
   </si>
   <si>
-    <t xml:space="preserve">59.4550743103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.316047668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.029052734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.0724143981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.25927734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0201148986816</t>
+    <t xml:space="preserve">59.4550704956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.3160438537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.0290489196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.0724105834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.2592697143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0201110839844</t>
   </si>
   <si>
     <t xml:space="preserve">50.9888191223145</t>
@@ -1982,10 +1982,10 @@
     <t xml:space="preserve">50.8931579589844</t>
   </si>
   <si>
-    <t xml:space="preserve">49.793025970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8408546447754</t>
+    <t xml:space="preserve">49.7930183410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8408508300781</t>
   </si>
   <si>
     <t xml:space="preserve">48.6928901672363</t>
@@ -1994,37 +1994,37 @@
     <t xml:space="preserve">49.2668724060059</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9843521118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9365234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0800132751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.653995513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2235069274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8453216552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.419303894043</t>
+    <t xml:space="preserve">49.9843482971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9365196228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0800170898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6539993286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2235107421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8453254699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4193115234375</t>
   </si>
   <si>
     <t xml:space="preserve">50.9409866333008</t>
   </si>
   <si>
-    <t xml:space="preserve">51.5149726867676</t>
+    <t xml:space="preserve">51.5149688720703</t>
   </si>
   <si>
     <t xml:space="preserve">50.797492980957</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1323204040527</t>
+    <t xml:space="preserve">51.1323165893555</t>
   </si>
   <si>
     <t xml:space="preserve">49.6973609924316</t>
@@ -2033,55 +2033,55 @@
     <t xml:space="preserve">49.3147048950195</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4582061767578</t>
+    <t xml:space="preserve">49.4582023620605</t>
   </si>
   <si>
     <t xml:space="preserve">49.745189666748</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0321846008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8363876342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.597225189209</t>
+    <t xml:space="preserve">50.0321769714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8363838195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5972290039062</t>
   </si>
   <si>
     <t xml:space="preserve">49.3625335693359</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0022277832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4282493591309</t>
+    <t xml:space="preserve">54.0022315979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4282455444336</t>
   </si>
   <si>
     <t xml:space="preserve">54.2892227172852</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1935539245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0934257507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.4716148376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2847557067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0978927612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9110336303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3370513916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8587303161621</t>
+    <t xml:space="preserve">54.1935615539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0934295654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.4716033935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2847518920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0978965759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9110374450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3370590209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8587379455566</t>
   </si>
   <si>
     <t xml:space="preserve">54.4805488586426</t>
@@ -2093,70 +2093,70 @@
     <t xml:space="preserve">55.3415260314941</t>
   </si>
   <si>
-    <t xml:space="preserve">55.8676795959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5373191833496</t>
+    <t xml:space="preserve">55.8676834106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5373229980469</t>
   </si>
   <si>
     <t xml:space="preserve">56.6329879760742</t>
   </si>
   <si>
-    <t xml:space="preserve">58.402759552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0679473876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6942291259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.3115730285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8511390686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6164360046387</t>
+    <t xml:space="preserve">58.4027671813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.067943572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6942367553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.3115692138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.851131439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6164512634277</t>
   </si>
   <si>
     <t xml:space="preserve">65.3383941650391</t>
   </si>
   <si>
-    <t xml:space="preserve">66.3428573608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.9646835327148</t>
+    <t xml:space="preserve">66.3428649902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.9646682739258</t>
   </si>
   <si>
     <t xml:space="preserve">67.9213256835938</t>
   </si>
   <si>
-    <t xml:space="preserve">69.2606201171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.0692749023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.3951568603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.0169830322266</t>
+    <t xml:space="preserve">69.260612487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.0692825317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.3951644897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.0169906616211</t>
   </si>
   <si>
     <t xml:space="preserve">66.8690185546875</t>
   </si>
   <si>
-    <t xml:space="preserve">67.2995071411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.5386581420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.9257888793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.212776184082</t>
+    <t xml:space="preserve">67.2994995117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.5386657714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.92578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.2127838134766</t>
   </si>
   <si>
     <t xml:space="preserve">68.4474716186523</t>
@@ -2183,10 +2183,10 @@
     <t xml:space="preserve">65.9123764038086</t>
   </si>
   <si>
-    <t xml:space="preserve">67.2516784667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.8256607055664</t>
+    <t xml:space="preserve">67.2516708374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.8256530761719</t>
   </si>
   <si>
     <t xml:space="preserve">67.6343231201172</t>
@@ -2195,13 +2195,13 @@
     <t xml:space="preserve">65.7688827514648</t>
   </si>
   <si>
-    <t xml:space="preserve">66.1036987304688</t>
+    <t xml:space="preserve">66.1037063598633</t>
   </si>
   <si>
     <t xml:space="preserve">69.4519348144531</t>
   </si>
   <si>
-    <t xml:space="preserve">68.2083129882812</t>
+    <t xml:space="preserve">68.2083053588867</t>
   </si>
   <si>
     <t xml:space="preserve">70.3129196166992</t>
@@ -2213,7 +2213,7 @@
     <t xml:space="preserve">73.2306594848633</t>
   </si>
   <si>
-    <t xml:space="preserve">74.0916366577148</t>
+    <t xml:space="preserve">74.0916442871094</t>
   </si>
   <si>
     <t xml:space="preserve">73.6611480712891</t>
@@ -2222,7 +2222,7 @@
     <t xml:space="preserve">73.374153137207</t>
   </si>
   <si>
-    <t xml:space="preserve">70.6955642700195</t>
+    <t xml:space="preserve">70.6955795288086</t>
   </si>
   <si>
     <t xml:space="preserve">70.7912292480469</t>
@@ -2231,19 +2231,19 @@
     <t xml:space="preserve">72.4653472900391</t>
   </si>
   <si>
-    <t xml:space="preserve">70.2650909423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.6387939453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3173828125</t>
+    <t xml:space="preserve">70.2650756835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.638801574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3173904418945</t>
   </si>
   <si>
     <t xml:space="preserve">71.9391937255859</t>
   </si>
   <si>
-    <t xml:space="preserve">72.7045059204102</t>
+    <t xml:space="preserve">72.7045135498047</t>
   </si>
   <si>
     <t xml:space="preserve">72.7523422241211</t>
@@ -2252,10 +2252,10 @@
     <t xml:space="preserve">72.6088485717773</t>
   </si>
   <si>
-    <t xml:space="preserve">74.4264602661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.1394653320312</t>
+    <t xml:space="preserve">74.4264526367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.1394729614258</t>
   </si>
   <si>
     <t xml:space="preserve">71.7478713989258</t>
@@ -2267,10 +2267,10 @@
     <t xml:space="preserve">73.2784957885742</t>
   </si>
   <si>
-    <t xml:space="preserve">71.4130477905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.8211898803711</t>
+    <t xml:space="preserve">71.4130554199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.8211975097656</t>
   </si>
   <si>
     <t xml:space="preserve">65.7210464477539</t>
@@ -2282,46 +2282,46 @@
     <t xml:space="preserve">63.8077697753906</t>
   </si>
   <si>
-    <t xml:space="preserve">61.8944892883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.937858581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.8766136169434</t>
+    <t xml:space="preserve">61.8944969177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9378623962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.8766212463379</t>
   </si>
   <si>
     <t xml:space="preserve">52.5672760009766</t>
   </si>
   <si>
-    <t xml:space="preserve">52.0889549255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3778190612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7407264709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4594497680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7094306945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8714256286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2107238769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3446617126465</t>
+    <t xml:space="preserve">52.0889625549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3778228759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7407188415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4594535827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7094268798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8714332580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2107200622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3446578979492</t>
   </si>
   <si>
     <t xml:space="preserve">47.1048736572266</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0844841003418</t>
+    <t xml:space="preserve">51.0844879150391</t>
   </si>
   <si>
     <t xml:space="preserve">49.2190399169922</t>
@@ -2330,10 +2330,10 @@
     <t xml:space="preserve">59.1680793762207</t>
   </si>
   <si>
-    <t xml:space="preserve">57.6852836608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.263744354248</t>
+    <t xml:space="preserve">57.6852912902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.2637405395508</t>
   </si>
   <si>
     <t xml:space="preserve">61.0813522338867</t>
@@ -2342,58 +2342,58 @@
     <t xml:space="preserve">60.3638725280762</t>
   </si>
   <si>
-    <t xml:space="preserve">61.1291885375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4161720275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.6598091125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.5207824707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.564151763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.1381340026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0424613952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.990161895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.0335273742676</t>
+    <t xml:space="preserve">61.1291847229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4161758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.6598052978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.5207939147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5641403198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.1381301879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0424690246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9901657104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.033519744873</t>
   </si>
   <si>
     <t xml:space="preserve">59.2684898376465</t>
   </si>
   <si>
-    <t xml:space="preserve">60.9081420898438</t>
+    <t xml:space="preserve">60.9081382751465</t>
   </si>
   <si>
     <t xml:space="preserve">61.7279624938965</t>
   </si>
   <si>
-    <t xml:space="preserve">63.705192565918</t>
+    <t xml:space="preserve">63.7051887512207</t>
   </si>
   <si>
     <t xml:space="preserve">64.7179107666016</t>
   </si>
   <si>
-    <t xml:space="preserve">63.3676109313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6569671630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.0909729003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.4285583496094</t>
+    <t xml:space="preserve">63.3676071166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6569633483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.0909881591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.4285659790039</t>
   </si>
   <si>
     <t xml:space="preserve">64.9108123779297</t>
@@ -2402,19 +2402,19 @@
     <t xml:space="preserve">68.4312286376953</t>
   </si>
   <si>
-    <t xml:space="preserve">68.0936508178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.3830108642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.6241455078125</t>
+    <t xml:space="preserve">68.0936584472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.3830032348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.6241302490234</t>
   </si>
   <si>
     <t xml:space="preserve">69.9744338989258</t>
   </si>
   <si>
-    <t xml:space="preserve">73.3983993530273</t>
+    <t xml:space="preserve">73.3984069824219</t>
   </si>
   <si>
     <t xml:space="preserve">74.1217803955078</t>
@@ -2423,28 +2423,28 @@
     <t xml:space="preserve">73.9288711547852</t>
   </si>
   <si>
-    <t xml:space="preserve">74.3628997802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.8578720092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.6522598266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.8551940917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6013565063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.1318206787109</t>
+    <t xml:space="preserve">74.362907409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.8578796386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.6522521972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.8552017211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6013488769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.1318283081055</t>
   </si>
   <si>
     <t xml:space="preserve">70.2155532836914</t>
   </si>
   <si>
-    <t xml:space="preserve">65.9235382080078</t>
+    <t xml:space="preserve">65.9235305786133</t>
   </si>
   <si>
     <t xml:space="preserve">67.0327072143555</t>
@@ -2453,7 +2453,7 @@
     <t xml:space="preserve">67.2256088256836</t>
   </si>
   <si>
-    <t xml:space="preserve">64.8625869750977</t>
+    <t xml:space="preserve">64.8625793457031</t>
   </si>
   <si>
     <t xml:space="preserve">66.5504608154297</t>
@@ -2462,10 +2462,10 @@
     <t xml:space="preserve">67.3220596313477</t>
   </si>
   <si>
-    <t xml:space="preserve">69.9262084960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.1800537109375</t>
+    <t xml:space="preserve">69.9262008666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.180061340332</t>
   </si>
   <si>
     <t xml:space="preserve">70.4084548950195</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">71.3729553222656</t>
   </si>
   <si>
-    <t xml:space="preserve">69.4921798706055</t>
+    <t xml:space="preserve">69.4921722412109</t>
   </si>
   <si>
     <t xml:space="preserve">70.31201171875</t>
@@ -2483,37 +2483,37 @@
     <t xml:space="preserve">68.5276794433594</t>
   </si>
   <si>
-    <t xml:space="preserve">68.2865676879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.6723556518555</t>
+    <t xml:space="preserve">68.2865600585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.67236328125</t>
   </si>
   <si>
     <t xml:space="preserve">69.0099334716797</t>
   </si>
   <si>
-    <t xml:space="preserve">69.2992858886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.1445541381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.2765045166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.8069839477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.1673278808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.5531387329102</t>
+    <t xml:space="preserve">69.2992782592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.1445617675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.2765121459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.8069763183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.1673355102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.5531311035156</t>
   </si>
   <si>
     <t xml:space="preserve">70.3602294921875</t>
   </si>
   <si>
-    <t xml:space="preserve">71.6623077392578</t>
+    <t xml:space="preserve">71.6623153686523</t>
   </si>
   <si>
     <t xml:space="preserve">72.3374557495117</t>
@@ -2522,7 +2522,7 @@
     <t xml:space="preserve">72.8679351806641</t>
   </si>
   <si>
-    <t xml:space="preserve">73.4466323852539</t>
+    <t xml:space="preserve">73.4466247558594</t>
   </si>
   <si>
     <t xml:space="preserve">73.5430679321289</t>
@@ -2540,31 +2540,31 @@
     <t xml:space="preserve">73.5913009643555</t>
   </si>
   <si>
-    <t xml:space="preserve">72.9643859863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.7487030029297</t>
+    <t xml:space="preserve">72.9643783569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.7487106323242</t>
   </si>
   <si>
     <t xml:space="preserve">81.9342193603516</t>
   </si>
   <si>
-    <t xml:space="preserve">82.9469451904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.117073059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.0815658569336</t>
+    <t xml:space="preserve">82.9469528198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.117057800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.0815811157227</t>
   </si>
   <si>
     <t xml:space="preserve">85.3582000732422</t>
   </si>
   <si>
-    <t xml:space="preserve">83.1398468017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0179443359375</t>
+    <t xml:space="preserve">83.1398391723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.017951965332</t>
   </si>
   <si>
     <t xml:space="preserve">81.0661773681641</t>
@@ -2573,49 +2573,49 @@
     <t xml:space="preserve">82.609375</t>
   </si>
   <si>
-    <t xml:space="preserve">80.8732681274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.0916290283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3099670410156</t>
+    <t xml:space="preserve">80.8732757568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.0916213989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3099746704102</t>
   </si>
   <si>
     <t xml:space="preserve">84.5865936279297</t>
   </si>
   <si>
-    <t xml:space="preserve">84.6348266601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.6703262329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.7794952392578</t>
+    <t xml:space="preserve">84.6348190307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.6703186035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.7795028686523</t>
   </si>
   <si>
     <t xml:space="preserve">84.6830520629883</t>
   </si>
   <si>
-    <t xml:space="preserve">87.3836364746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2262496948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7212066650391</t>
+    <t xml:space="preserve">87.3836517333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2262344360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7212219238281</t>
   </si>
   <si>
     <t xml:space="preserve">89.6984405517578</t>
   </si>
   <si>
-    <t xml:space="preserve">89.3126525878906</t>
+    <t xml:space="preserve">89.3126449584961</t>
   </si>
   <si>
     <t xml:space="preserve">90.6629409790039</t>
   </si>
   <si>
-    <t xml:space="preserve">88.1070098876953</t>
+    <t xml:space="preserve">88.1070175170898</t>
   </si>
   <si>
     <t xml:space="preserve">87.8658905029297</t>
@@ -2624,43 +2624,43 @@
     <t xml:space="preserve">91.2416458129883</t>
   </si>
   <si>
-    <t xml:space="preserve">90.2771453857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5664978027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9777374267578</t>
+    <t xml:space="preserve">90.2771377563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5664901733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8076095581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9777450561523</t>
   </si>
   <si>
     <t xml:space="preserve">95.0031890869141</t>
   </si>
   <si>
-    <t xml:space="preserve">94.90673828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7265701293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.218864440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5082168579102</t>
+    <t xml:space="preserve">94.9067459106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.2188720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5082092285156</t>
   </si>
   <si>
     <t xml:space="preserve">91.4827651977539</t>
   </si>
   <si>
-    <t xml:space="preserve">89.939567565918</t>
+    <t xml:space="preserve">89.9395751953125</t>
   </si>
   <si>
     <t xml:space="preserve">91.6274490356445</t>
   </si>
   <si>
-    <t xml:space="preserve">92.1096878051758</t>
+    <t xml:space="preserve">92.1096954345703</t>
   </si>
   <si>
     <t xml:space="preserve">93.3635482788086</t>
@@ -2675,46 +2675,46 @@
     <t xml:space="preserve">94.8102874755859</t>
   </si>
   <si>
-    <t xml:space="preserve">93.6046752929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.5209350585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6884002685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4345550537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0259628295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.2925491333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.2215423583984</t>
+    <t xml:space="preserve">93.6046676635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.5209426879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6883926391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4345474243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0259704589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.2925415039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.2215347290039</t>
   </si>
   <si>
     <t xml:space="preserve">100.115043640137</t>
   </si>
   <si>
-    <t xml:space="preserve">99.729248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.6073303222656</t>
+    <t xml:space="preserve">99.7292404174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.6073379516602</t>
   </si>
   <si>
     <t xml:space="preserve">97.8966903686523</t>
   </si>
   <si>
-    <t xml:space="preserve">98.3789367675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.3052673339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.7493362426758</t>
+    <t xml:space="preserve">98.3789443969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.3052597045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7493286132812</t>
   </si>
   <si>
     <t xml:space="preserve">92.8330612182617</t>
@@ -2726,13 +2726,13 @@
     <t xml:space="preserve">88.4445877075195</t>
   </si>
   <si>
-    <t xml:space="preserve">88.2034683227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.0233001708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.1324615478516</t>
+    <t xml:space="preserve">88.2034606933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.023307800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.1324691772461</t>
   </si>
   <si>
     <t xml:space="preserve">92.2061386108398</t>
@@ -2741,7 +2741,7 @@
     <t xml:space="preserve">96.4499359130859</t>
   </si>
   <si>
-    <t xml:space="preserve">95.4372100830078</t>
+    <t xml:space="preserve">95.4372177124023</t>
   </si>
   <si>
     <t xml:space="preserve">95.7747955322266</t>
@@ -2750,58 +2750,58 @@
     <t xml:space="preserve">92.447265625</t>
   </si>
   <si>
-    <t xml:space="preserve">92.0614624023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.8685607910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.8203430175781</t>
+    <t xml:space="preserve">92.0614700317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.8685684204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.8203353881836</t>
   </si>
   <si>
     <t xml:space="preserve">90.7111740112305</t>
   </si>
   <si>
-    <t xml:space="preserve">90.8558349609375</t>
+    <t xml:space="preserve">90.855842590332</t>
   </si>
   <si>
     <t xml:space="preserve">91.3863220214844</t>
   </si>
   <si>
-    <t xml:space="preserve">90.759391784668</t>
+    <t xml:space="preserve">90.7593841552734</t>
   </si>
   <si>
     <t xml:space="preserve">87.7694396972656</t>
   </si>
   <si>
-    <t xml:space="preserve">88.2517013549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3608703613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.3735885620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.2798233032227</t>
+    <t xml:space="preserve">88.2516860961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3608779907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.3735961914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.2798156738281</t>
   </si>
   <si>
     <t xml:space="preserve">90.0842361450195</t>
   </si>
   <si>
-    <t xml:space="preserve">91.1451950073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4954833984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.4573211669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6756744384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.9168014526367</t>
+    <t xml:space="preserve">91.1451873779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.495491027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.4573135375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.675666809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.9167938232422</t>
   </si>
   <si>
     <t xml:space="preserve">91.7238922119141</t>
@@ -2813,34 +2813,34 @@
     <t xml:space="preserve">90.9040679931641</t>
   </si>
   <si>
-    <t xml:space="preserve">92.3508148193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4599914550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.5437088012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9194564819336</t>
+    <t xml:space="preserve">92.350830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4599990844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.5437164306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9194641113281</t>
   </si>
   <si>
     <t xml:space="preserve">93.26708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">93.5564346313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.5691680908203</t>
+    <t xml:space="preserve">93.5564422607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.5691757202148</t>
   </si>
   <si>
     <t xml:space="preserve">96.0641403198242</t>
   </si>
   <si>
-    <t xml:space="preserve">98.4753952026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.018577575684</t>
+    <t xml:space="preserve">98.4753875732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.018592834473</t>
   </si>
   <si>
     <t xml:space="preserve">98.1860427856445</t>
@@ -2849,19 +2849,19 @@
     <t xml:space="preserve">97.414436340332</t>
   </si>
   <si>
-    <t xml:space="preserve">100.790191650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.912086486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.46533203125</t>
+    <t xml:space="preserve">100.790184020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.912078857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.465339660645</t>
   </si>
   <si>
     <t xml:space="preserve">102.719184875488</t>
   </si>
   <si>
-    <t xml:space="preserve">102.52628326416</t>
+    <t xml:space="preserve">102.526290893555</t>
   </si>
   <si>
     <t xml:space="preserve">102.140487670898</t>
@@ -2870,10 +2870,10 @@
     <t xml:space="preserve">104.937538146973</t>
   </si>
   <si>
-    <t xml:space="preserve">103.104995727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.587242126465</t>
+    <t xml:space="preserve">103.104988098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.58723449707</t>
   </si>
   <si>
     <t xml:space="preserve">102.815635681152</t>
@@ -2885,22 +2885,22 @@
     <t xml:space="preserve">100.500831604004</t>
   </si>
   <si>
-    <t xml:space="preserve">100.404396057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.5718307495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.0514144897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.1351470947266</t>
+    <t xml:space="preserve">100.40438079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.5718383789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.0514297485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.135139465332</t>
   </si>
   <si>
     <t xml:space="preserve">92.5919418334961</t>
   </si>
   <si>
-    <t xml:space="preserve">89.2162017822266</t>
+    <t xml:space="preserve">89.216194152832</t>
   </si>
   <si>
     <t xml:space="preserve">103.297889709473</t>
@@ -2909,10 +2909,10 @@
     <t xml:space="preserve">99.3434371948242</t>
   </si>
   <si>
-    <t xml:space="preserve">101.561782836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.973030090332</t>
+    <t xml:space="preserve">101.561790466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.973037719727</t>
   </si>
   <si>
     <t xml:space="preserve">103.780128479004</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">104.069480895996</t>
   </si>
   <si>
-    <t xml:space="preserve">108.023941040039</t>
+    <t xml:space="preserve">108.023933410645</t>
   </si>
   <si>
     <t xml:space="preserve">110.14582824707</t>
@@ -2939,40 +2939,40 @@
     <t xml:space="preserve">106.287826538086</t>
   </si>
   <si>
-    <t xml:space="preserve">107.445236206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.38427734375</t>
+    <t xml:space="preserve">107.44522857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.384284973145</t>
   </si>
   <si>
     <t xml:space="preserve">108.891983032227</t>
   </si>
   <si>
-    <t xml:space="preserve">107.831039428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.795524597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.08487701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.059432983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.348777770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.56713104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.506187438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.530754089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.786010742188</t>
+    <t xml:space="preserve">107.831031799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.795532226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.084884643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.059440612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.348793029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.567138671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.506172180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.53076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.786018371582</t>
   </si>
   <si>
     <t xml:space="preserve">108.755310058594</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">109.046104431152</t>
   </si>
   <si>
-    <t xml:space="preserve">109.918479919434</t>
+    <t xml:space="preserve">109.918487548828</t>
   </si>
   <si>
     <t xml:space="preserve">110.500053405762</t>
@@ -2990,25 +2990,25 @@
     <t xml:space="preserve">109.821556091309</t>
   </si>
   <si>
-    <t xml:space="preserve">110.887786865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.663208007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.117156982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.831207275391</t>
+    <t xml:space="preserve">110.887771606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.663215637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.117164611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.831192016602</t>
   </si>
   <si>
     <t xml:space="preserve">113.795669555664</t>
   </si>
   <si>
-    <t xml:space="preserve">114.76496887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.668037414551</t>
+    <t xml:space="preserve">114.764976501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.668045043945</t>
   </si>
   <si>
     <t xml:space="preserve">114.280326843262</t>
@@ -3020,37 +3020,37 @@
     <t xml:space="preserve">116.509704589844</t>
   </si>
   <si>
-    <t xml:space="preserve">121.453132629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.590423583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.819793701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.365859985352</t>
+    <t xml:space="preserve">121.453140258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.59041595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.819778442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.365844726562</t>
   </si>
   <si>
     <t xml:space="preserve">127.268936157227</t>
   </si>
   <si>
-    <t xml:space="preserve">128.432098388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.181655883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.46760559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.273727416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.916717529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.63557434082</t>
+    <t xml:space="preserve">128.432083129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.181640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.467620849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.273742675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.916732788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.635589599609</t>
   </si>
   <si>
     <t xml:space="preserve">135.70182800293</t>
@@ -3062,31 +3062,31 @@
     <t xml:space="preserve">133.375518798828</t>
   </si>
   <si>
-    <t xml:space="preserve">135.798751831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.314102172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.574172973633</t>
+    <t xml:space="preserve">135.798782348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.314117431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.574188232422</t>
   </si>
   <si>
     <t xml:space="preserve">132.212341308594</t>
   </si>
   <si>
-    <t xml:space="preserve">135.023330688477</t>
+    <t xml:space="preserve">135.023315429688</t>
   </si>
   <si>
     <t xml:space="preserve">133.763214111328</t>
   </si>
   <si>
-    <t xml:space="preserve">137.446563720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.895690917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.344818115234</t>
+    <t xml:space="preserve">137.446548461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.89567565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.344833374023</t>
   </si>
   <si>
     <t xml:space="preserve">138.22200012207</t>
@@ -3113,13 +3113,13 @@
     <t xml:space="preserve">140.160598754883</t>
   </si>
   <si>
-    <t xml:space="preserve">139.579010009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.671127319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.609710693359</t>
+    <t xml:space="preserve">139.579025268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.671112060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.609725952148</t>
   </si>
   <si>
     <t xml:space="preserve">135.992614746094</t>
@@ -3128,19 +3128,19 @@
     <t xml:space="preserve">137.640426635742</t>
   </si>
   <si>
-    <t xml:space="preserve">139.094360351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.226821899414</t>
+    <t xml:space="preserve">139.094375610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.226837158203</t>
   </si>
   <si>
     <t xml:space="preserve">142.583847045898</t>
   </si>
   <si>
-    <t xml:space="preserve">141.905334472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.262344360352</t>
+    <t xml:space="preserve">141.905319213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.262359619141</t>
   </si>
   <si>
     <t xml:space="preserve">142.486923217773</t>
@@ -3149,133 +3149,133 @@
     <t xml:space="preserve">146.073318481445</t>
   </si>
   <si>
-    <t xml:space="preserve">148.88427734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.011917114258</t>
+    <t xml:space="preserve">148.884292602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.011901855469</t>
   </si>
   <si>
     <t xml:space="preserve">149.175079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">149.756652832031</t>
+    <t xml:space="preserve">149.75666809082</t>
   </si>
   <si>
     <t xml:space="preserve">146.364105224609</t>
   </si>
   <si>
-    <t xml:space="preserve">147.236480712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.205749511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.818054199219</t>
+    <t xml:space="preserve">147.236465454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.205764770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.81803894043</t>
   </si>
   <si>
     <t xml:space="preserve">150.532104492188</t>
   </si>
   <si>
-    <t xml:space="preserve">150.629028320312</t>
+    <t xml:space="preserve">150.629013061523</t>
   </si>
   <si>
     <t xml:space="preserve">155.087799072266</t>
   </si>
   <si>
-    <t xml:space="preserve">154.893951416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.955352783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.89875793457</t>
+    <t xml:space="preserve">154.893936157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.955337524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.898773193359</t>
   </si>
   <si>
     <t xml:space="preserve">161.67903137207</t>
   </si>
   <si>
-    <t xml:space="preserve">166.816314697266</t>
+    <t xml:space="preserve">166.816299438477</t>
   </si>
   <si>
     <t xml:space="preserve">166.428573608398</t>
   </si>
   <si>
-    <t xml:space="preserve">165.847030639648</t>
+    <t xml:space="preserve">165.847015380859</t>
   </si>
   <si>
     <t xml:space="preserve">165.459289550781</t>
   </si>
   <si>
-    <t xml:space="preserve">165.65315246582</t>
+    <t xml:space="preserve">165.653137207031</t>
   </si>
   <si>
     <t xml:space="preserve">167.397903442383</t>
   </si>
   <si>
-    <t xml:space="preserve">168.851837158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.142639160156</t>
+    <t xml:space="preserve">168.851821899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.142623901367</t>
   </si>
   <si>
     <t xml:space="preserve">169.62727355957</t>
   </si>
   <si>
-    <t xml:space="preserve">170.305786132812</t>
+    <t xml:space="preserve">170.305770874023</t>
   </si>
   <si>
     <t xml:space="preserve">169.23957824707</t>
   </si>
   <si>
-    <t xml:space="preserve">169.724227905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.948760986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.811477661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.204025268555</t>
+    <t xml:space="preserve">169.724212646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.948776245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.811492919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.204055786133</t>
   </si>
   <si>
     <t xml:space="preserve">165.071578979492</t>
   </si>
   <si>
-    <t xml:space="preserve">167.979476928711</t>
+    <t xml:space="preserve">167.9794921875</t>
   </si>
   <si>
     <t xml:space="preserve">173.989120483398</t>
   </si>
   <si>
-    <t xml:space="preserve">176.606216430664</t>
+    <t xml:space="preserve">176.606231689453</t>
   </si>
   <si>
     <t xml:space="preserve">171.372009277344</t>
   </si>
   <si>
-    <t xml:space="preserve">152.470703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.567596435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.506195068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.827697753906</t>
+    <t xml:space="preserve">152.470687866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.567611694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.506210327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.827713012695</t>
   </si>
   <si>
     <t xml:space="preserve">149.465866088867</t>
   </si>
   <si>
-    <t xml:space="preserve">153.633850097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.430358886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.721115112305</t>
+    <t xml:space="preserve">153.633865356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.43034362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.721130371094</t>
   </si>
   <si>
     <t xml:space="preserve">145.97639465332</t>
@@ -3284,16 +3284,16 @@
     <t xml:space="preserve">157.026382446289</t>
   </si>
   <si>
-    <t xml:space="preserve">159.643493652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.842178344727</t>
+    <t xml:space="preserve">159.643508911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.842193603516</t>
   </si>
   <si>
     <t xml:space="preserve">163.229904174805</t>
   </si>
   <si>
-    <t xml:space="preserve">160.4189453125</t>
+    <t xml:space="preserve">160.418930053711</t>
   </si>
   <si>
     <t xml:space="preserve">161.097457885742</t>
@@ -3302,19 +3302,19 @@
     <t xml:space="preserve">160.806655883789</t>
   </si>
   <si>
-    <t xml:space="preserve">160.612823486328</t>
+    <t xml:space="preserve">160.61279296875</t>
   </si>
   <si>
     <t xml:space="preserve">161.582092285156</t>
   </si>
   <si>
-    <t xml:space="preserve">162.551391601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.872894287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.393081665039</t>
+    <t xml:space="preserve">162.551406860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.87287902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.39306640625</t>
   </si>
   <si>
     <t xml:space="preserve">171.27507019043</t>
@@ -3326,43 +3326,43 @@
     <t xml:space="preserve">172.825973510742</t>
   </si>
   <si>
-    <t xml:space="preserve">174.182998657227</t>
+    <t xml:space="preserve">174.182983398438</t>
   </si>
   <si>
     <t xml:space="preserve">171.662811279297</t>
   </si>
   <si>
-    <t xml:space="preserve">172.341323852539</t>
+    <t xml:space="preserve">172.34130859375</t>
   </si>
   <si>
     <t xml:space="preserve">176.703170776367</t>
   </si>
   <si>
-    <t xml:space="preserve">179.804931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.892181396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.754913330078</t>
+    <t xml:space="preserve">179.804916381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.892196655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.754928588867</t>
   </si>
   <si>
     <t xml:space="preserve">168.561050415039</t>
   </si>
   <si>
-    <t xml:space="preserve">167.010162353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.934310913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.454467773438</t>
+    <t xml:space="preserve">167.010177612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.934280395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.454483032227</t>
   </si>
   <si>
     <t xml:space="preserve">159.837356567383</t>
   </si>
   <si>
-    <t xml:space="preserve">166.040893554688</t>
+    <t xml:space="preserve">166.040863037109</t>
   </si>
   <si>
     <t xml:space="preserve">167.882537841797</t>
@@ -3371,7 +3371,7 @@
     <t xml:space="preserve">160.709732055664</t>
   </si>
   <si>
-    <t xml:space="preserve">162.745254516602</t>
+    <t xml:space="preserve">162.745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">159.158843994141</t>
@@ -3380,16 +3380,16 @@
     <t xml:space="preserve">172.535171508789</t>
   </si>
   <si>
-    <t xml:space="preserve">174.958435058594</t>
+    <t xml:space="preserve">174.958419799805</t>
   </si>
   <si>
     <t xml:space="preserve">173.698348999023</t>
   </si>
   <si>
-    <t xml:space="preserve">174.570709228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.433410644531</t>
+    <t xml:space="preserve">174.570693969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.433441162109</t>
   </si>
   <si>
     <t xml:space="preserve">168.076400756836</t>
@@ -3398,13 +3398,13 @@
     <t xml:space="preserve">163.617630004883</t>
   </si>
   <si>
-    <t xml:space="preserve">164.877731323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.714553833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.596588134766</t>
+    <t xml:space="preserve">164.877716064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.714569091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.596572875977</t>
   </si>
   <si>
     <t xml:space="preserve">169.821136474609</t>
@@ -3419,13 +3419,13 @@
     <t xml:space="preserve">157.317184448242</t>
   </si>
   <si>
-    <t xml:space="preserve">155.572463989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.863235473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.669372558594</t>
+    <t xml:space="preserve">155.572448730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.863250732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.669387817383</t>
   </si>
   <si>
     <t xml:space="preserve">153.149215698242</t>
@@ -3455,13 +3455,13 @@
     <t xml:space="preserve">143.553146362305</t>
   </si>
   <si>
-    <t xml:space="preserve">144.522445678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.91015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.385177612305</t>
+    <t xml:space="preserve">144.5224609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.910171508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.385162353516</t>
   </si>
   <si>
     <t xml:space="preserve">136.089538574219</t>
@@ -3473,13 +3473,13 @@
     <t xml:space="preserve">132.309280395508</t>
   </si>
   <si>
-    <t xml:space="preserve">138.997421264648</t>
+    <t xml:space="preserve">138.997436523438</t>
   </si>
   <si>
     <t xml:space="preserve">137.834289550781</t>
   </si>
   <si>
-    <t xml:space="preserve">137.543502807617</t>
+    <t xml:space="preserve">137.543487548828</t>
   </si>
   <si>
     <t xml:space="preserve">138.125061035156</t>
@@ -3488,13 +3488,13 @@
     <t xml:space="preserve">138.512786865234</t>
   </si>
   <si>
-    <t xml:space="preserve">142.680786132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.692169189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.039527893066</t>
+    <t xml:space="preserve">142.680770874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.692184448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.039535522461</t>
   </si>
   <si>
     <t xml:space="preserve">136.9619140625</t>
@@ -3503,13 +3503,13 @@
     <t xml:space="preserve">135.507965087891</t>
   </si>
   <si>
-    <t xml:space="preserve">142.874633789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.562789916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.986053466797</t>
+    <t xml:space="preserve">142.874618530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.562805175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.986038208008</t>
   </si>
   <si>
     <t xml:space="preserve">150.919815063477</t>
@@ -3521,10 +3521,10 @@
     <t xml:space="preserve">146.267181396484</t>
   </si>
   <si>
-    <t xml:space="preserve">145.10400390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.690414428711</t>
+    <t xml:space="preserve">145.104019165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.6904296875</t>
   </si>
   <si>
     <t xml:space="preserve">145.394805908203</t>
@@ -3536,10 +3536,10 @@
     <t xml:space="preserve">149.659729003906</t>
   </si>
   <si>
-    <t xml:space="preserve">145.200942993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.517623901367</t>
+    <t xml:space="preserve">145.200958251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.517608642578</t>
   </si>
   <si>
     <t xml:space="preserve">141.323760986328</t>
@@ -3554,40 +3554,40 @@
     <t xml:space="preserve">136.477264404297</t>
   </si>
   <si>
-    <t xml:space="preserve">131.824630737305</t>
+    <t xml:space="preserve">131.824615478516</t>
   </si>
   <si>
     <t xml:space="preserve">136.186477661133</t>
   </si>
   <si>
-    <t xml:space="preserve">135.217178344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.952255249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.75358581543</t>
+    <t xml:space="preserve">135.217163085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.952270507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.753570556641</t>
   </si>
   <si>
     <t xml:space="preserve">121.16234588623</t>
   </si>
   <si>
-    <t xml:space="preserve">113.601806640625</t>
+    <t xml:space="preserve">113.60179901123</t>
   </si>
   <si>
     <t xml:space="preserve">117.285148620605</t>
   </si>
   <si>
-    <t xml:space="preserve">114.958831787109</t>
+    <t xml:space="preserve">114.958824157715</t>
   </si>
   <si>
     <t xml:space="preserve">117.575942993164</t>
   </si>
   <si>
-    <t xml:space="preserve">116.121994018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.708389282227</t>
+    <t xml:space="preserve">116.12198638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.708396911621</t>
   </si>
   <si>
     <t xml:space="preserve">115.152694702148</t>
@@ -3596,232 +3596,235 @@
     <t xml:space="preserve">114.861907958984</t>
   </si>
   <si>
+    <t xml:space="preserve">115.443473815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.516914367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.003852844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.102432250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.71208190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.713081359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.909255981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.640640258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.834823608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.225158691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.346900939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.005844116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.857971191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.539054870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.367042541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.512916564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.586357116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.146728515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.14771270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.830825805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.075286865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.417335510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.319747924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.418327331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.296600341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.541061401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.272453308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.906257629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.882110595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.24730682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.661796569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.321739196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.566207885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.615501403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.054130554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.956550598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.101432800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.907257080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.469619750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.323753356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.885108947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.006851196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.66478729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.68994140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.616500854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.249305725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.055137634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.470634460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.957550048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.494773864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.082275390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.960540771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.179870605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.544067382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.177871704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.20100402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.42032623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.151710510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.176864624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.029991149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.736228942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.955558776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.271461486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.053146362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.711090087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.686943054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.46662902832</t>
+  </si>
+  <si>
     <t xml:space="preserve">115.443481445312</t>
   </si>
   <si>
-    <t xml:space="preserve">116.51692199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.003845214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.102432250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.71208190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.713081359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.909255981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.640647888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.834815979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.225158691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.346893310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.005844116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.857971191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.5390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.367050170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.512916564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.586357116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.146728515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.147720336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.83081817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.075286865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.417327880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.319747924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.418327331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.296600341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.541069030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.272453308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.906257629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.882110595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.24730682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.661796569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.321746826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.566207885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.615501403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.054138183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.956550598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.101432800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.907264709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.469619750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.323753356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.885116577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.006851196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.664794921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.68994140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.616493225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.249305725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.055130004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.47061920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.957542419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.494773864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.082290649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.960571289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.179870605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.544075012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.177864074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.201011657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.420333862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.151718139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.176864624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.029991149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.736236572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.955558776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.271461486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.053131103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.711090087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.686935424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.466621398926</t>
-  </si>
-  <si>
     <t xml:space="preserve">117.590354919434</t>
   </si>
   <si>
-    <t xml:space="preserve">113.394187927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.832824707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.369033813477</t>
+    <t xml:space="preserve">113.394180297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.832817077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.369041442871</t>
   </si>
   <si>
     <t xml:space="preserve">105.977699279785</t>
   </si>
   <si>
-    <t xml:space="preserve">106.953559875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.025985717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.928413391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.70809173584</t>
+    <t xml:space="preserve">106.953552246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.025993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.928405761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.708084106445</t>
   </si>
   <si>
     <t xml:space="preserve">101.391189575195</t>
@@ -3833,43 +3836,43 @@
     <t xml:space="preserve">104.513916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">101.196006774902</t>
+    <t xml:space="preserve">101.196014404297</t>
   </si>
   <si>
     <t xml:space="preserve">105.001846313477</t>
   </si>
   <si>
-    <t xml:space="preserve">107.734237670898</t>
+    <t xml:space="preserve">107.734230041504</t>
   </si>
   <si>
     <t xml:space="preserve">115.83381652832</t>
   </si>
   <si>
-    <t xml:space="preserve">115.150718688965</t>
+    <t xml:space="preserve">115.150726318359</t>
   </si>
   <si>
     <t xml:space="preserve">112.12557220459</t>
   </si>
   <si>
-    <t xml:space="preserve">106.75838470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.440483093262</t>
+    <t xml:space="preserve">106.758377075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.440475463867</t>
   </si>
   <si>
     <t xml:space="preserve">106.270454406738</t>
   </si>
   <si>
-    <t xml:space="preserve">108.026985168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.100433349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.514923095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.636657714844</t>
+    <t xml:space="preserve">108.026992797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.100425720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.514915466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.636650085449</t>
   </si>
   <si>
     <t xml:space="preserve">109.978691101074</t>
@@ -3884,31 +3887,31 @@
     <t xml:space="preserve">106.172874450684</t>
   </si>
   <si>
-    <t xml:space="preserve">108.905250549316</t>
+    <t xml:space="preserve">108.905258178711</t>
   </si>
   <si>
     <t xml:space="preserve">109.685943603516</t>
   </si>
   <si>
-    <t xml:space="preserve">112.320747375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.274452209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.738235473633</t>
+    <t xml:space="preserve">112.320739746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.274459838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.738227844238</t>
   </si>
   <si>
     <t xml:space="preserve">116.028991699219</t>
   </si>
   <si>
-    <t xml:space="preserve">110.076286315918</t>
+    <t xml:space="preserve">110.076278686523</t>
   </si>
   <si>
     <t xml:space="preserve">107.929405212402</t>
   </si>
   <si>
-    <t xml:space="preserve">112.223167419434</t>
+    <t xml:space="preserve">112.223159790039</t>
   </si>
   <si>
     <t xml:space="preserve">109.78352355957</t>
@@ -3917,7 +3920,7 @@
     <t xml:space="preserve">110.856964111328</t>
   </si>
   <si>
-    <t xml:space="preserve">109.588363647461</t>
+    <t xml:space="preserve">109.588356018066</t>
   </si>
   <si>
     <t xml:space="preserve">109.198020935059</t>
@@ -3926,19 +3929,19 @@
     <t xml:space="preserve">110.759384155273</t>
   </si>
   <si>
-    <t xml:space="preserve">117.200012207031</t>
+    <t xml:space="preserve">117.200019836426</t>
   </si>
   <si>
     <t xml:space="preserve">113.784530639648</t>
   </si>
   <si>
-    <t xml:space="preserve">105.587356567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.831825256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.197021484375</t>
+    <t xml:space="preserve">105.587348937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.831817626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.19701385498</t>
   </si>
   <si>
     <t xml:space="preserve">105.099426269531</t>
@@ -3950,46 +3953,46 @@
     <t xml:space="preserve">106.465621948242</t>
   </si>
   <si>
-    <t xml:space="preserve">104.41633605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.880111694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.343887329102</t>
+    <t xml:space="preserve">104.416328430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.88011932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.343894958496</t>
   </si>
   <si>
     <t xml:space="preserve">111.052139282227</t>
   </si>
   <si>
-    <t xml:space="preserve">114.467628479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.419342041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.883110046387</t>
+    <t xml:space="preserve">114.467620849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.419334411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.883117675781</t>
   </si>
   <si>
     <t xml:space="preserve">118.761375427246</t>
   </si>
   <si>
-    <t xml:space="preserve">115.93140411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.39518737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.273445129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.760383605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.98070526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.933403015137</t>
+    <t xml:space="preserve">115.931411743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.395195007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.273452758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.760375976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.980697631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.933410644531</t>
   </si>
   <si>
     <t xml:space="preserve">124.226165771484</t>
@@ -4007,28 +4010,28 @@
     <t xml:space="preserve">119.6396484375</t>
   </si>
   <si>
-    <t xml:space="preserve">118.85897064209</t>
+    <t xml:space="preserve">118.858963012695</t>
   </si>
   <si>
     <t xml:space="preserve">114.37003326416</t>
   </si>
   <si>
-    <t xml:space="preserve">112.515922546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.149726867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.199020385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.540061950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.613502502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.124580383301</t>
+    <t xml:space="preserve">112.515930175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.149719238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.199012756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.540069580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.613510131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.124588012695</t>
   </si>
   <si>
     <t xml:space="preserve">110.954551696777</t>
@@ -4046,10 +4049,10 @@
     <t xml:space="preserve">113.58935546875</t>
   </si>
   <si>
-    <t xml:space="preserve">109.88111114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.051139831543</t>
+    <t xml:space="preserve">109.881103515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.051132202148</t>
   </si>
   <si>
     <t xml:space="preserve">104.123573303223</t>
@@ -4058,10 +4061,10 @@
     <t xml:space="preserve">102.562210083008</t>
   </si>
   <si>
-    <t xml:space="preserve">102.464622497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.683937072754</t>
+    <t xml:space="preserve">102.464630126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.683944702148</t>
   </si>
   <si>
     <t xml:space="preserve">102.95255279541</t>
@@ -4070,7 +4073,7 @@
     <t xml:space="preserve">101.781532287598</t>
   </si>
   <si>
-    <t xml:space="preserve">100.610504150391</t>
+    <t xml:space="preserve">100.610496520996</t>
   </si>
   <si>
     <t xml:space="preserve">103.342895507812</t>
@@ -4434,9 +4437,6 @@
   </si>
   <si>
     <t xml:space="preserve">105.602142333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.025993347168</t>
   </si>
   <si>
     <t xml:space="preserve">105.306617736816</t>
@@ -50080,7 +50080,7 @@
         <v>118.300003051758</v>
       </c>
       <c r="G1703" t="s">
-        <v>1194</v>
+        <v>1261</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -50106,7 +50106,7 @@
         <v>120.5</v>
       </c>
       <c r="G1704" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -50132,7 +50132,7 @@
         <v>116.199996948242</v>
       </c>
       <c r="G1705" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -50158,7 +50158,7 @@
         <v>114.599998474121</v>
       </c>
       <c r="G1706" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -50184,7 +50184,7 @@
         <v>113.099998474121</v>
       </c>
       <c r="G1707" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -50210,7 +50210,7 @@
         <v>108.599998474121</v>
       </c>
       <c r="G1708" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -50236,7 +50236,7 @@
         <v>109.599998474121</v>
       </c>
       <c r="G1709" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -50262,7 +50262,7 @@
         <v>106.599998474121</v>
       </c>
       <c r="G1710" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -50288,7 +50288,7 @@
         <v>106.5</v>
       </c>
       <c r="G1711" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -50314,7 +50314,7 @@
         <v>103.199996948242</v>
       </c>
       <c r="G1712" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -50340,7 +50340,7 @@
         <v>103.900001525879</v>
       </c>
       <c r="G1713" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -50366,7 +50366,7 @@
         <v>107.5</v>
       </c>
       <c r="G1714" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -50418,7 +50418,7 @@
         <v>107.099998474121</v>
       </c>
       <c r="G1716" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -50444,7 +50444,7 @@
         <v>103.699996948242</v>
       </c>
       <c r="G1717" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -50470,7 +50470,7 @@
         <v>107.599998474121</v>
       </c>
       <c r="G1718" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -50496,7 +50496,7 @@
         <v>110.400001525879</v>
       </c>
       <c r="G1719" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -50522,7 +50522,7 @@
         <v>118.699996948242</v>
       </c>
       <c r="G1720" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -50548,7 +50548,7 @@
         <v>118</v>
       </c>
       <c r="G1721" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -50600,7 +50600,7 @@
         <v>114.900001525879</v>
       </c>
       <c r="G1723" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -50652,7 +50652,7 @@
         <v>109.400001525879</v>
       </c>
       <c r="G1725" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -50678,7 +50678,7 @@
         <v>106</v>
       </c>
       <c r="G1726" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -50704,7 +50704,7 @@
         <v>107.599998474121</v>
       </c>
       <c r="G1727" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -50730,7 +50730,7 @@
         <v>108.900001525879</v>
       </c>
       <c r="G1728" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -50756,7 +50756,7 @@
         <v>110.699996948242</v>
       </c>
       <c r="G1729" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -50782,7 +50782,7 @@
         <v>111.800003051758</v>
       </c>
       <c r="G1730" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -50808,7 +50808,7 @@
         <v>108.900001525879</v>
       </c>
       <c r="G1731" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -50834,7 +50834,7 @@
         <v>111.199996948242</v>
       </c>
       <c r="G1732" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -50860,7 +50860,7 @@
         <v>110.300003051758</v>
       </c>
       <c r="G1733" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -50886,7 +50886,7 @@
         <v>112.699996948242</v>
       </c>
       <c r="G1734" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -50938,7 +50938,7 @@
         <v>118.699996948242</v>
       </c>
       <c r="G1736" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -50990,7 +50990,7 @@
         <v>111.300003051758</v>
       </c>
       <c r="G1738" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -51016,7 +51016,7 @@
         <v>110.099998474121</v>
       </c>
       <c r="G1739" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -51042,7 +51042,7 @@
         <v>108.900001525879</v>
       </c>
       <c r="G1740" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -51068,7 +51068,7 @@
         <v>110.300003051758</v>
       </c>
       <c r="G1741" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -51094,7 +51094,7 @@
         <v>108.800003051758</v>
       </c>
       <c r="G1742" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -51120,7 +51120,7 @@
         <v>111.599998474121</v>
       </c>
       <c r="G1743" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -51146,7 +51146,7 @@
         <v>112.400001525879</v>
       </c>
       <c r="G1744" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -51172,7 +51172,7 @@
         <v>115.099998474121</v>
       </c>
       <c r="G1745" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -51224,7 +51224,7 @@
         <v>125.300003051758</v>
       </c>
       <c r="G1747" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -51250,7 +51250,7 @@
         <v>126.800003051758</v>
       </c>
       <c r="G1748" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -51276,7 +51276,7 @@
         <v>118.900001525879</v>
       </c>
       <c r="G1749" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -51328,7 +51328,7 @@
         <v>110.699996948242</v>
       </c>
       <c r="G1751" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -51380,7 +51380,7 @@
         <v>112.800003051758</v>
       </c>
       <c r="G1753" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -51406,7 +51406,7 @@
         <v>110.099998474121</v>
       </c>
       <c r="G1754" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -51432,7 +51432,7 @@
         <v>110.599998474121</v>
       </c>
       <c r="G1755" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -51484,7 +51484,7 @@
         <v>115</v>
       </c>
       <c r="G1757" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -51562,7 +51562,7 @@
         <v>112.5</v>
       </c>
       <c r="G1760" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -51588,7 +51588,7 @@
         <v>112.800003051758</v>
       </c>
       <c r="G1761" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -51614,7 +51614,7 @@
         <v>118.900001525879</v>
       </c>
       <c r="G1762" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -51692,7 +51692,7 @@
         <v>113.599998474121</v>
       </c>
       <c r="G1765" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -51718,7 +51718,7 @@
         <v>112.300003051758</v>
       </c>
       <c r="G1766" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -51744,7 +51744,7 @@
         <v>111.900001525879</v>
       </c>
       <c r="G1767" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -51770,7 +51770,7 @@
         <v>113.5</v>
       </c>
       <c r="G1768" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -51848,7 +51848,7 @@
         <v>120.099998474121</v>
       </c>
       <c r="G1771" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -51874,7 +51874,7 @@
         <v>116.599998474121</v>
       </c>
       <c r="G1772" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -51900,7 +51900,7 @@
         <v>108.599998474121</v>
       </c>
       <c r="G1773" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -51926,7 +51926,7 @@
         <v>108.800003051758</v>
       </c>
       <c r="G1774" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -51952,7 +51952,7 @@
         <v>108.199996948242</v>
       </c>
       <c r="G1775" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -51978,7 +51978,7 @@
         <v>110.5</v>
       </c>
       <c r="G1776" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -52004,7 +52004,7 @@
         <v>108.199996948242</v>
       </c>
       <c r="G1777" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -52030,7 +52030,7 @@
         <v>107.800003051758</v>
       </c>
       <c r="G1778" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -52056,7 +52056,7 @@
         <v>107.699996948242</v>
       </c>
       <c r="G1779" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -52082,7 +52082,7 @@
         <v>106.800003051758</v>
       </c>
       <c r="G1780" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -52108,7 +52108,7 @@
         <v>109.099998474121</v>
       </c>
       <c r="G1781" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -52134,7 +52134,7 @@
         <v>107</v>
       </c>
       <c r="G1782" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -52160,7 +52160,7 @@
         <v>107.099998474121</v>
       </c>
       <c r="G1783" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -52186,7 +52186,7 @@
         <v>108.5</v>
       </c>
       <c r="G1784" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -52212,7 +52212,7 @@
         <v>108.800003051758</v>
       </c>
       <c r="G1785" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -52238,7 +52238,7 @@
         <v>107.099998474121</v>
       </c>
       <c r="G1786" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -52264,7 +52264,7 @@
         <v>107.099998474121</v>
       </c>
       <c r="G1787" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -52290,7 +52290,7 @@
         <v>110</v>
       </c>
       <c r="G1788" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -52316,7 +52316,7 @@
         <v>108.599998474121</v>
       </c>
       <c r="G1789" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -52342,7 +52342,7 @@
         <v>113.800003051758</v>
       </c>
       <c r="G1790" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -52368,7 +52368,7 @@
         <v>112.300003051758</v>
       </c>
       <c r="G1791" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -52394,7 +52394,7 @@
         <v>117.300003051758</v>
       </c>
       <c r="G1792" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -52420,7 +52420,7 @@
         <v>119.300003051758</v>
       </c>
       <c r="G1793" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -52446,7 +52446,7 @@
         <v>120.800003051758</v>
       </c>
       <c r="G1794" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -52472,7 +52472,7 @@
         <v>121.699996948242</v>
       </c>
       <c r="G1795" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -52524,7 +52524,7 @@
         <v>118.800003051758</v>
       </c>
       <c r="G1797" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -52550,7 +52550,7 @@
         <v>120.5</v>
       </c>
       <c r="G1798" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -52576,7 +52576,7 @@
         <v>120.300003051758</v>
       </c>
       <c r="G1799" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -52628,7 +52628,7 @@
         <v>120.099998474121</v>
       </c>
       <c r="G1801" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -52654,7 +52654,7 @@
         <v>121.199996948242</v>
       </c>
       <c r="G1802" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -52680,7 +52680,7 @@
         <v>117.599998474121</v>
       </c>
       <c r="G1803" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -52706,7 +52706,7 @@
         <v>118.900001525879</v>
       </c>
       <c r="G1804" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -52732,7 +52732,7 @@
         <v>120.900001525879</v>
       </c>
       <c r="G1805" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -52758,7 +52758,7 @@
         <v>127</v>
       </c>
       <c r="G1806" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -52784,7 +52784,7 @@
         <v>127.300003051758</v>
       </c>
       <c r="G1807" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -52810,7 +52810,7 @@
         <v>126.199996948242</v>
       </c>
       <c r="G1808" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -52862,7 +52862,7 @@
         <v>125.300003051758</v>
       </c>
       <c r="G1810" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -52888,7 +52888,7 @@
         <v>124.5</v>
       </c>
       <c r="G1811" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -52914,7 +52914,7 @@
         <v>120.099998474121</v>
       </c>
       <c r="G1812" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -52940,7 +52940,7 @@
         <v>121.599998474121</v>
       </c>
       <c r="G1813" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -52992,7 +52992,7 @@
         <v>122.599998474121</v>
       </c>
       <c r="G1815" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -53018,7 +53018,7 @@
         <v>121.800003051758</v>
       </c>
       <c r="G1816" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -53044,7 +53044,7 @@
         <v>120.300003051758</v>
       </c>
       <c r="G1817" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -53096,7 +53096,7 @@
         <v>118.800003051758</v>
       </c>
       <c r="G1819" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -53122,7 +53122,7 @@
         <v>117.199996948242</v>
       </c>
       <c r="G1820" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -53148,7 +53148,7 @@
         <v>116.199996948242</v>
       </c>
       <c r="G1821" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -53174,7 +53174,7 @@
         <v>115.300003051758</v>
       </c>
       <c r="G1822" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -53200,7 +53200,7 @@
         <v>115.300003051758</v>
       </c>
       <c r="G1823" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -53226,7 +53226,7 @@
         <v>113.800003051758</v>
       </c>
       <c r="G1824" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -53252,7 +53252,7 @@
         <v>113.900001525879</v>
       </c>
       <c r="G1825" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -53278,7 +53278,7 @@
         <v>114.599998474121</v>
       </c>
       <c r="G1826" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -53304,7 +53304,7 @@
         <v>116</v>
       </c>
       <c r="G1827" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -53330,7 +53330,7 @@
         <v>115.300003051758</v>
       </c>
       <c r="G1828" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -53356,7 +53356,7 @@
         <v>113.900001525879</v>
       </c>
       <c r="G1829" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -53382,7 +53382,7 @@
         <v>114.300003051758</v>
       </c>
       <c r="G1830" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -53408,7 +53408,7 @@
         <v>115.400001525879</v>
       </c>
       <c r="G1831" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -53434,7 +53434,7 @@
         <v>111.599998474121</v>
       </c>
       <c r="G1832" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -53460,7 +53460,7 @@
         <v>112.699996948242</v>
       </c>
       <c r="G1833" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -53512,7 +53512,7 @@
         <v>110.800003051758</v>
       </c>
       <c r="G1835" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -53590,7 +53590,7 @@
         <v>113.699996948242</v>
       </c>
       <c r="G1838" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -53616,7 +53616,7 @@
         <v>114.800003051758</v>
       </c>
       <c r="G1839" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -53642,7 +53642,7 @@
         <v>112.199996948242</v>
       </c>
       <c r="G1840" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -53694,7 +53694,7 @@
         <v>109.800003051758</v>
       </c>
       <c r="G1842" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -53720,7 +53720,7 @@
         <v>109.800003051758</v>
       </c>
       <c r="G1843" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -53772,7 +53772,7 @@
         <v>112.199996948242</v>
       </c>
       <c r="G1845" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -53798,7 +53798,7 @@
         <v>116.400001525879</v>
       </c>
       <c r="G1846" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -53850,7 +53850,7 @@
         <v>113.699996948242</v>
       </c>
       <c r="G1848" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -53876,7 +53876,7 @@
         <v>112.5</v>
       </c>
       <c r="G1849" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -53902,7 +53902,7 @@
         <v>112.599998474121</v>
       </c>
       <c r="G1850" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -53928,7 +53928,7 @@
         <v>111.300003051758</v>
       </c>
       <c r="G1851" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -53954,7 +53954,7 @@
         <v>112.400001525879</v>
       </c>
       <c r="G1852" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -54006,7 +54006,7 @@
         <v>112.5</v>
       </c>
       <c r="G1854" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -54032,7 +54032,7 @@
         <v>111.300003051758</v>
       </c>
       <c r="G1855" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -54058,7 +54058,7 @@
         <v>109.699996948242</v>
       </c>
       <c r="G1856" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -54084,7 +54084,7 @@
         <v>110</v>
       </c>
       <c r="G1857" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -54110,7 +54110,7 @@
         <v>106.800003051758</v>
       </c>
       <c r="G1858" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -54162,7 +54162,7 @@
         <v>106.699996948242</v>
       </c>
       <c r="G1860" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -54214,7 +54214,7 @@
         <v>105.099998474121</v>
       </c>
       <c r="G1862" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -54240,7 +54240,7 @@
         <v>105</v>
       </c>
       <c r="G1863" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -54266,7 +54266,7 @@
         <v>104.199996948242</v>
       </c>
       <c r="G1864" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -54292,7 +54292,7 @@
         <v>105.5</v>
       </c>
       <c r="G1865" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -54318,7 +54318,7 @@
         <v>104.300003051758</v>
       </c>
       <c r="G1866" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -54370,7 +54370,7 @@
         <v>103.099998474121</v>
       </c>
       <c r="G1868" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -54396,7 +54396,7 @@
         <v>105</v>
       </c>
       <c r="G1869" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -54422,7 +54422,7 @@
         <v>105.900001525879</v>
       </c>
       <c r="G1870" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -54448,7 +54448,7 @@
         <v>103.5</v>
       </c>
       <c r="G1871" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -54474,7 +54474,7 @@
         <v>102.900001525879</v>
       </c>
       <c r="G1872" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -54552,7 +54552,7 @@
         <v>104.300003051758</v>
       </c>
       <c r="G1875" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -54578,7 +54578,7 @@
         <v>104.599998474121</v>
       </c>
       <c r="G1876" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -54604,7 +54604,7 @@
         <v>103.900001525879</v>
       </c>
       <c r="G1877" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -54630,7 +54630,7 @@
         <v>103.5</v>
       </c>
       <c r="G1878" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -54656,7 +54656,7 @@
         <v>106.599998474121</v>
       </c>
       <c r="G1879" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -54682,7 +54682,7 @@
         <v>104.599998474121</v>
       </c>
       <c r="G1880" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -54708,7 +54708,7 @@
         <v>104.800003051758</v>
       </c>
       <c r="G1881" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -54734,7 +54734,7 @@
         <v>100.900001525879</v>
       </c>
       <c r="G1882" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -54760,7 +54760,7 @@
         <v>100.800003051758</v>
       </c>
       <c r="G1883" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -54786,7 +54786,7 @@
         <v>101.699996948242</v>
       </c>
       <c r="G1884" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -54812,7 +54812,7 @@
         <v>101.400001525879</v>
       </c>
       <c r="G1885" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -54838,7 +54838,7 @@
         <v>101.699996948242</v>
       </c>
       <c r="G1886" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -54864,7 +54864,7 @@
         <v>101.199996948242</v>
       </c>
       <c r="G1887" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -54890,7 +54890,7 @@
         <v>103.099998474121</v>
       </c>
       <c r="G1888" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -54916,7 +54916,7 @@
         <v>105.699996948242</v>
       </c>
       <c r="G1889" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -54942,7 +54942,7 @@
         <v>104.699996948242</v>
       </c>
       <c r="G1890" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -54968,7 +54968,7 @@
         <v>104.800003051758</v>
       </c>
       <c r="G1891" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -54994,7 +54994,7 @@
         <v>104</v>
       </c>
       <c r="G1892" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -55020,7 +55020,7 @@
         <v>103.900001525879</v>
       </c>
       <c r="G1893" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -55046,7 +55046,7 @@
         <v>103.800003051758</v>
       </c>
       <c r="G1894" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -55072,7 +55072,7 @@
         <v>109.400001525879</v>
       </c>
       <c r="G1895" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -55098,7 +55098,7 @@
         <v>112.400001525879</v>
       </c>
       <c r="G1896" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -55124,7 +55124,7 @@
         <v>109.300003051758</v>
       </c>
       <c r="G1897" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -55150,7 +55150,7 @@
         <v>109.800003051758</v>
       </c>
       <c r="G1898" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -55176,7 +55176,7 @@
         <v>112.900001525879</v>
       </c>
       <c r="G1899" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -55202,7 +55202,7 @@
         <v>111.300003051758</v>
       </c>
       <c r="G1900" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -55228,7 +55228,7 @@
         <v>108</v>
       </c>
       <c r="G1901" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -55254,7 +55254,7 @@
         <v>103.099998474121</v>
       </c>
       <c r="G1902" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -55280,7 +55280,7 @@
         <v>102.800003051758</v>
       </c>
       <c r="G1903" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -55306,7 +55306,7 @@
         <v>101.900001525879</v>
       </c>
       <c r="G1904" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -55332,7 +55332,7 @@
         <v>100.599998474121</v>
       </c>
       <c r="G1905" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -55358,7 +55358,7 @@
         <v>99.5500030517578</v>
       </c>
       <c r="G1906" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -55384,7 +55384,7 @@
         <v>102</v>
       </c>
       <c r="G1907" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -55410,7 +55410,7 @@
         <v>102.300003051758</v>
       </c>
       <c r="G1908" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -55436,7 +55436,7 @@
         <v>104.099998474121</v>
       </c>
       <c r="G1909" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -55462,7 +55462,7 @@
         <v>105</v>
       </c>
       <c r="G1910" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -55488,7 +55488,7 @@
         <v>108.300003051758</v>
       </c>
       <c r="G1911" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -55514,7 +55514,7 @@
         <v>106</v>
       </c>
       <c r="G1912" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -55540,7 +55540,7 @@
         <v>103.900001525879</v>
       </c>
       <c r="G1913" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -55566,7 +55566,7 @@
         <v>104.699996948242</v>
       </c>
       <c r="G1914" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -55592,7 +55592,7 @@
         <v>103.5</v>
       </c>
       <c r="G1915" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -55618,7 +55618,7 @@
         <v>103.400001525879</v>
       </c>
       <c r="G1916" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -55644,7 +55644,7 @@
         <v>106.599998474121</v>
       </c>
       <c r="G1917" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -55670,7 +55670,7 @@
         <v>105.300003051758</v>
       </c>
       <c r="G1918" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -55696,7 +55696,7 @@
         <v>105.199996948242</v>
       </c>
       <c r="G1919" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -55722,7 +55722,7 @@
         <v>101.900001525879</v>
       </c>
       <c r="G1920" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -55748,7 +55748,7 @@
         <v>102</v>
       </c>
       <c r="G1921" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -55774,7 +55774,7 @@
         <v>101</v>
       </c>
       <c r="G1922" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -55800,7 +55800,7 @@
         <v>100.199996948242</v>
       </c>
       <c r="G1923" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -55826,7 +55826,7 @@
         <v>98.6999969482422</v>
       </c>
       <c r="G1924" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -55852,7 +55852,7 @@
         <v>99.75</v>
       </c>
       <c r="G1925" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -55878,7 +55878,7 @@
         <v>99.6500015258789</v>
       </c>
       <c r="G1926" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -55904,7 +55904,7 @@
         <v>98.9000015258789</v>
       </c>
       <c r="G1927" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -55930,7 +55930,7 @@
         <v>101.900001525879</v>
       </c>
       <c r="G1928" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -55956,7 +55956,7 @@
         <v>100.400001525879</v>
       </c>
       <c r="G1929" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -55982,7 +55982,7 @@
         <v>98.5999984741211</v>
       </c>
       <c r="G1930" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -56008,7 +56008,7 @@
         <v>95.9499969482422</v>
       </c>
       <c r="G1931" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -56034,7 +56034,7 @@
         <v>97.4499969482422</v>
       </c>
       <c r="G1932" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -56060,7 +56060,7 @@
         <v>96.1999969482422</v>
       </c>
       <c r="G1933" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -56086,7 +56086,7 @@
         <v>95.8499984741211</v>
       </c>
       <c r="G1934" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -56112,7 +56112,7 @@
         <v>95.1500015258789</v>
       </c>
       <c r="G1935" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -56138,7 +56138,7 @@
         <v>94.4499969482422</v>
       </c>
       <c r="G1936" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -56164,7 +56164,7 @@
         <v>93.5999984741211</v>
       </c>
       <c r="G1937" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -56190,7 +56190,7 @@
         <v>94.25</v>
       </c>
       <c r="G1938" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -56216,7 +56216,7 @@
         <v>92.5</v>
       </c>
       <c r="G1939" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -56242,7 +56242,7 @@
         <v>93.3000030517578</v>
       </c>
       <c r="G1940" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -56268,7 +56268,7 @@
         <v>92.4499969482422</v>
       </c>
       <c r="G1941" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -56294,7 +56294,7 @@
         <v>88.1999969482422</v>
       </c>
       <c r="G1942" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -56320,7 +56320,7 @@
         <v>88.0999984741211</v>
       </c>
       <c r="G1943" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -56346,7 +56346,7 @@
         <v>87.4000015258789</v>
       </c>
       <c r="G1944" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -56372,7 +56372,7 @@
         <v>87.8000030517578</v>
       </c>
       <c r="G1945" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -56398,7 +56398,7 @@
         <v>89.1500015258789</v>
       </c>
       <c r="G1946" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -56424,7 +56424,7 @@
         <v>88.0500030517578</v>
       </c>
       <c r="G1947" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -56450,7 +56450,7 @@
         <v>88.0500030517578</v>
       </c>
       <c r="G1948" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -56476,7 +56476,7 @@
         <v>91.8499984741211</v>
       </c>
       <c r="G1949" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -56502,7 +56502,7 @@
         <v>93.0999984741211</v>
       </c>
       <c r="G1950" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -56528,7 +56528,7 @@
         <v>93.0500030517578</v>
       </c>
       <c r="G1951" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -56554,7 +56554,7 @@
         <v>94.4499969482422</v>
       </c>
       <c r="G1952" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -56580,7 +56580,7 @@
         <v>93.5500030517578</v>
       </c>
       <c r="G1953" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -56606,7 +56606,7 @@
         <v>92.5500030517578</v>
       </c>
       <c r="G1954" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -56632,7 +56632,7 @@
         <v>91.6999969482422</v>
       </c>
       <c r="G1955" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -56658,7 +56658,7 @@
         <v>90</v>
       </c>
       <c r="G1956" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -56684,7 +56684,7 @@
         <v>88.3499984741211</v>
       </c>
       <c r="G1957" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -56710,7 +56710,7 @@
         <v>88</v>
       </c>
       <c r="G1958" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -56736,7 +56736,7 @@
         <v>87.8499984741211</v>
       </c>
       <c r="G1959" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -56762,7 +56762,7 @@
         <v>87</v>
       </c>
       <c r="G1960" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -56788,7 +56788,7 @@
         <v>87.9000015258789</v>
       </c>
       <c r="G1961" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -56814,7 +56814,7 @@
         <v>88.75</v>
       </c>
       <c r="G1962" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -56840,7 +56840,7 @@
         <v>88.3000030517578</v>
       </c>
       <c r="G1963" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -56866,7 +56866,7 @@
         <v>87.8499984741211</v>
       </c>
       <c r="G1964" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -56892,7 +56892,7 @@
         <v>87.4499969482422</v>
       </c>
       <c r="G1965" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -56918,7 +56918,7 @@
         <v>88.4499969482422</v>
       </c>
       <c r="G1966" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -56944,7 +56944,7 @@
         <v>87.1500015258789</v>
       </c>
       <c r="G1967" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -56970,7 +56970,7 @@
         <v>87</v>
       </c>
       <c r="G1968" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -56996,7 +56996,7 @@
         <v>86.5</v>
       </c>
       <c r="G1969" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -57022,7 +57022,7 @@
         <v>82.4000015258789</v>
       </c>
       <c r="G1970" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -57048,7 +57048,7 @@
         <v>86.1999969482422</v>
       </c>
       <c r="G1971" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -57074,7 +57074,7 @@
         <v>85.5</v>
       </c>
       <c r="G1972" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -57100,7 +57100,7 @@
         <v>89.0500030517578</v>
       </c>
       <c r="G1973" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -57126,7 +57126,7 @@
         <v>89.6500015258789</v>
       </c>
       <c r="G1974" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -57152,7 +57152,7 @@
         <v>87.5999984741211</v>
       </c>
       <c r="G1975" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -57178,7 +57178,7 @@
         <v>89.5999984741211</v>
       </c>
       <c r="G1976" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -57204,7 +57204,7 @@
         <v>88.3000030517578</v>
       </c>
       <c r="G1977" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -57230,7 +57230,7 @@
         <v>89</v>
       </c>
       <c r="G1978" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -57256,7 +57256,7 @@
         <v>88</v>
       </c>
       <c r="G1979" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -57282,7 +57282,7 @@
         <v>90.1500015258789</v>
       </c>
       <c r="G1980" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -57308,7 +57308,7 @@
         <v>90.3499984741211</v>
       </c>
       <c r="G1981" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -57334,7 +57334,7 @@
         <v>93.5</v>
       </c>
       <c r="G1982" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -57360,7 +57360,7 @@
         <v>87.8000030517578</v>
       </c>
       <c r="G1983" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -57386,7 +57386,7 @@
         <v>87.75</v>
       </c>
       <c r="G1984" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -57412,7 +57412,7 @@
         <v>86.6500015258789</v>
       </c>
       <c r="G1985" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -57438,7 +57438,7 @@
         <v>84.5999984741211</v>
       </c>
       <c r="G1986" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -57464,7 +57464,7 @@
         <v>88.4000015258789</v>
       </c>
       <c r="G1987" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -57490,7 +57490,7 @@
         <v>85.25</v>
       </c>
       <c r="G1988" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -57516,7 +57516,7 @@
         <v>85.9499969482422</v>
       </c>
       <c r="G1989" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -57542,7 +57542,7 @@
         <v>86.3000030517578</v>
       </c>
       <c r="G1990" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -57568,7 +57568,7 @@
         <v>85.4499969482422</v>
       </c>
       <c r="G1991" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -57594,7 +57594,7 @@
         <v>85.0500030517578</v>
       </c>
       <c r="G1992" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -57620,7 +57620,7 @@
         <v>85.4499969482422</v>
       </c>
       <c r="G1993" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -57646,7 +57646,7 @@
         <v>85.8000030517578</v>
       </c>
       <c r="G1994" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -57672,7 +57672,7 @@
         <v>88.8499984741211</v>
       </c>
       <c r="G1995" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -57698,7 +57698,7 @@
         <v>91.25</v>
       </c>
       <c r="G1996" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -57724,7 +57724,7 @@
         <v>94.0500030517578</v>
       </c>
       <c r="G1997" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -57750,7 +57750,7 @@
         <v>95.75</v>
       </c>
       <c r="G1998" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -57776,7 +57776,7 @@
         <v>93.6999969482422</v>
       </c>
       <c r="G1999" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -57802,7 +57802,7 @@
         <v>95.5</v>
       </c>
       <c r="G2000" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -57828,7 +57828,7 @@
         <v>99.9499969482422</v>
       </c>
       <c r="G2001" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -57854,7 +57854,7 @@
         <v>101</v>
       </c>
       <c r="G2002" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -57880,7 +57880,7 @@
         <v>100.099998474121</v>
       </c>
       <c r="G2003" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -57906,7 +57906,7 @@
         <v>101</v>
       </c>
       <c r="G2004" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -57932,7 +57932,7 @@
         <v>104.900001525879</v>
       </c>
       <c r="G2005" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -57958,7 +57958,7 @@
         <v>103.199996948242</v>
       </c>
       <c r="G2006" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -57984,7 +57984,7 @@
         <v>103.699996948242</v>
       </c>
       <c r="G2007" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -58010,7 +58010,7 @@
         <v>104.599998474121</v>
       </c>
       <c r="G2008" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -58036,7 +58036,7 @@
         <v>106.300003051758</v>
       </c>
       <c r="G2009" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -58062,7 +58062,7 @@
         <v>105.800003051758</v>
       </c>
       <c r="G2010" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -58088,7 +58088,7 @@
         <v>106.800003051758</v>
       </c>
       <c r="G2011" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -58114,7 +58114,7 @@
         <v>106.099998474121</v>
       </c>
       <c r="G2012" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -58140,7 +58140,7 @@
         <v>103.900001525879</v>
       </c>
       <c r="G2013" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -58166,7 +58166,7 @@
         <v>105</v>
       </c>
       <c r="G2014" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -58192,7 +58192,7 @@
         <v>104.5</v>
       </c>
       <c r="G2015" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -58218,7 +58218,7 @@
         <v>106.400001525879</v>
       </c>
       <c r="G2016" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -58244,7 +58244,7 @@
         <v>107.199996948242</v>
       </c>
       <c r="G2017" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -58270,7 +58270,7 @@
         <v>106.400001525879</v>
       </c>
       <c r="G2018" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -58296,7 +58296,7 @@
         <v>105.599998474121</v>
       </c>
       <c r="G2019" t="s">
-        <v>1474</v>
+        <v>1268</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -58374,7 +58374,7 @@
         <v>109.300003051758</v>
       </c>
       <c r="G2022" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -70706,7 +70706,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6495601852</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>42894</v>
@@ -70727,6 +70727,32 @@
         <v>1819</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6911574074</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>32419</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>122</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>119.800003051758</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>121.900001525879</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>120.300003051758</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>1808</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/REY.MI.xlsx
+++ b/data/REY.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2559719085693</t>
+    <t xml:space="preserve">29.255973815918</t>
   </si>
   <si>
     <t xml:space="preserve">REY.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8380279541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3272113800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6306400299072</t>
+    <t xml:space="preserve">28.8380260467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3272075653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6306419372559</t>
   </si>
   <si>
     <t xml:space="preserve">27.8396110534668</t>
@@ -62,34 +62,34 @@
     <t xml:space="preserve">29.0005626678467</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5594024658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1414604187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1198215484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9789257049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8644104003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4448852539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.932487487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8163948059082</t>
+    <t xml:space="preserve">28.5594005584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1414566040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1198234558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9789218902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8644123077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4448890686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9324855804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8163909912109</t>
   </si>
   <si>
     <t xml:space="preserve">28.2807731628418</t>
   </si>
   <si>
-    <t xml:space="preserve">27.677074432373</t>
+    <t xml:space="preserve">27.6770782470703</t>
   </si>
   <si>
     <t xml:space="preserve">28.0950202941895</t>
@@ -98,52 +98,52 @@
     <t xml:space="preserve">27.8628273010254</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2591342926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7018775939941</t>
+    <t xml:space="preserve">27.2591381072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7018795013428</t>
   </si>
   <si>
     <t xml:space="preserve">26.1678409576416</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2855186462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3799781799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6121654510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0053119659424</t>
+    <t xml:space="preserve">25.2855167388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.379976272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6121692657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0053081512451</t>
   </si>
   <si>
     <t xml:space="preserve">25.517707824707</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6570224761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6074180603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3071537017822</t>
+    <t xml:space="preserve">25.6570243835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.607421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3071556091309</t>
   </si>
   <si>
     <t xml:space="preserve">27.0733814239502</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2142772674561</t>
+    <t xml:space="preserve">26.2142810821533</t>
   </si>
   <si>
     <t xml:space="preserve">26.4696865081787</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0517425537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7034606933594</t>
+    <t xml:space="preserve">26.0517463684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7034587860107</t>
   </si>
   <si>
     <t xml:space="preserve">25.7266807556152</t>
@@ -152,16 +152,16 @@
     <t xml:space="preserve">26.7483158111572</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4929065704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3520107269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.189474105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2359180450439</t>
+    <t xml:space="preserve">26.4929046630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3520126342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1894779205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2359161376953</t>
   </si>
   <si>
     <t xml:space="preserve">27.1662578582764</t>
@@ -173,19 +173,19 @@
     <t xml:space="preserve">29.0237827301025</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5546569824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3008308410645</t>
+    <t xml:space="preserve">31.5546531677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3008289337158</t>
   </si>
   <si>
     <t xml:space="preserve">30.4169216156006</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9989795684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9757652282715</t>
+    <t xml:space="preserve">29.9989776611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9757633209229</t>
   </si>
   <si>
     <t xml:space="preserve">29.7900085449219</t>
@@ -194,22 +194,22 @@
     <t xml:space="preserve">29.952543258667</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2311706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7203521728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0686359405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8596668243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5578174591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3256301879883</t>
+    <t xml:space="preserve">30.2311744689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7203502655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0686378479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8596687316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5578231811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.325626373291</t>
   </si>
   <si>
     <t xml:space="preserve">29.4881591796875</t>
@@ -221,85 +221,85 @@
     <t xml:space="preserve">29.2095336914062</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1615142822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3720664978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5346012115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4433059692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6754970550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8612480163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8148078918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9076862335205</t>
+    <t xml:space="preserve">30.1615104675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3720645904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5345973968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4433078765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6754932403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8612461090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8148097991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9076843261719</t>
   </si>
   <si>
     <t xml:space="preserve">28.6290588378906</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4200859069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6775989532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5605506896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0287551879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3264446258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5137271881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7946529388428</t>
+    <t xml:space="preserve">28.4200878143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6776008605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.560546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0287532806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3264465332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.513729095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7946510314941</t>
   </si>
   <si>
     <t xml:space="preserve">29.0053424835205</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2628574371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1992683410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5036010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5504245758057</t>
+    <t xml:space="preserve">29.2628555297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1992702484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5036029815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5504207611084</t>
   </si>
   <si>
     <t xml:space="preserve">30.9015769958496</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6674709320068</t>
+    <t xml:space="preserve">30.6674747467041</t>
   </si>
   <si>
     <t xml:space="preserve">30.714298248291</t>
   </si>
   <si>
-    <t xml:space="preserve">30.4567813873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4333744049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2695026397705</t>
+    <t xml:space="preserve">30.4567852020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.43337059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2694988250732</t>
   </si>
   <si>
     <t xml:space="preserve">29.8949337005615</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">28.1859836578369</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3096771240234</t>
+    <t xml:space="preserve">29.3096752166748</t>
   </si>
   <si>
     <t xml:space="preserve">29.4969596862793</t>
@@ -317,34 +317,34 @@
     <t xml:space="preserve">27.6943683624268</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7747249603271</t>
+    <t xml:space="preserve">25.7747230529785</t>
   </si>
   <si>
     <t xml:space="preserve">26.8047771453857</t>
   </si>
   <si>
-    <t xml:space="preserve">27.319803237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9218273162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5070858001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.945240020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8215484619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.219518661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1091136932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6241359710693</t>
+    <t xml:space="preserve">27.3198051452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9218311309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5070838928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9452362060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8215446472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2195205688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1091117858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.624137878418</t>
   </si>
   <si>
     <t xml:space="preserve">27.3666229248047</t>
@@ -353,28 +353,28 @@
     <t xml:space="preserve">28.303035736084</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8882942199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7478313446045</t>
+    <t xml:space="preserve">28.8882904052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7478294372559</t>
   </si>
   <si>
     <t xml:space="preserve">28.4434986114502</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9819316864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9117031097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3799095153809</t>
+    <t xml:space="preserve">28.98193359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9117050170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3799076080322</t>
   </si>
   <si>
     <t xml:space="preserve">29.450138092041</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8481140136719</t>
+    <t xml:space="preserve">29.8481121063232</t>
   </si>
   <si>
     <t xml:space="preserve">30.1524486541748</t>
@@ -383,19 +383,19 @@
     <t xml:space="preserve">29.9651660919189</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7244205474854</t>
+    <t xml:space="preserve">28.7244167327881</t>
   </si>
   <si>
     <t xml:space="preserve">29.1458053588867</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0989856719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.935115814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4903163909912</t>
+    <t xml:space="preserve">29.0989875793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9351139068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4903144836426</t>
   </si>
   <si>
     <t xml:space="preserve">27.9752922058105</t>
@@ -413,49 +413,49 @@
     <t xml:space="preserve">27.0622901916504</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0388774871826</t>
+    <t xml:space="preserve">27.0388832092285</t>
   </si>
   <si>
     <t xml:space="preserve">26.8984184265137</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1492919921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7981357574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8917751312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7579555511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.95188331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.881649017334</t>
+    <t xml:space="preserve">26.1492881774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7981376647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.891773223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7579574584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9518814086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8816509246826</t>
   </si>
   <si>
     <t xml:space="preserve">27.8114223480225</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9050579071045</t>
+    <t xml:space="preserve">27.9050598144531</t>
   </si>
   <si>
     <t xml:space="preserve">27.2963924407959</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8582401275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5773181915283</t>
+    <t xml:space="preserve">27.8582420349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.577320098877</t>
   </si>
   <si>
     <t xml:space="preserve">27.7177772521973</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7411880493164</t>
+    <t xml:space="preserve">27.7411918640137</t>
   </si>
   <si>
     <t xml:space="preserve">28.045524597168</t>
@@ -473,16 +473,16 @@
     <t xml:space="preserve">28.6541862487793</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2093944549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4134426116943</t>
+    <t xml:space="preserve">28.2093963623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4134464263916</t>
   </si>
   <si>
     <t xml:space="preserve">27.0857009887695</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8515968322754</t>
+    <t xml:space="preserve">26.851598739624</t>
   </si>
   <si>
     <t xml:space="preserve">27.4368553161621</t>
@@ -497,16 +497,16 @@
     <t xml:space="preserve">26.8281879425049</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6409091949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4536209106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5706729888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.523853302002</t>
+    <t xml:space="preserve">26.640905380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4536228179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5706768035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5238552093506</t>
   </si>
   <si>
     <t xml:space="preserve">26.3365726470947</t>
@@ -518,40 +518,40 @@
     <t xml:space="preserve">25.329927444458</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7446689605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7680835723877</t>
+    <t xml:space="preserve">24.7446708679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7680816650391</t>
   </si>
   <si>
     <t xml:space="preserve">24.8851337432861</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2530517578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0490055084229</t>
+    <t xml:space="preserve">24.2530555725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0490036010742</t>
   </si>
   <si>
     <t xml:space="preserve">25.4703903198242</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5172119140625</t>
+    <t xml:space="preserve">25.5172100067139</t>
   </si>
   <si>
     <t xml:space="preserve">25.2831077575684</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1660575866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4469814300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0958232879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.931957244873</t>
+    <t xml:space="preserve">25.1660556793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4469795227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0958251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9319534301758</t>
   </si>
   <si>
     <t xml:space="preserve">25.0724143981934</t>
@@ -560,61 +560,61 @@
     <t xml:space="preserve">25.6342601776123</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1961097717285</t>
+    <t xml:space="preserve">26.1961116790771</t>
   </si>
   <si>
     <t xml:space="preserve">26.1726989746094</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8348274230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9284706115723</t>
+    <t xml:space="preserve">27.8348293304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9284725189209</t>
   </si>
   <si>
     <t xml:space="preserve">27.4602680206299</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9987010955811</t>
+    <t xml:space="preserve">27.9987030029297</t>
   </si>
   <si>
     <t xml:space="preserve">28.6307792663574</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2160358428955</t>
+    <t xml:space="preserve">29.2160377502441</t>
   </si>
   <si>
     <t xml:space="preserve">29.3330898284912</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8648834228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3498573303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6073703765869</t>
+    <t xml:space="preserve">28.8648815155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3498554229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.607364654541</t>
   </si>
   <si>
     <t xml:space="preserve">29.4735507965088</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2394485473633</t>
+    <t xml:space="preserve">29.2394466400146</t>
   </si>
   <si>
     <t xml:space="preserve">29.7076530456543</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4267311096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8313465118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9952144622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4868297576904</t>
+    <t xml:space="preserve">29.4267272949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8313484191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9952182769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4868335723877</t>
   </si>
   <si>
     <t xml:space="preserve">31.2527351379395</t>
@@ -626,28 +626,28 @@
     <t xml:space="preserve">31.1356830596924</t>
   </si>
   <si>
-    <t xml:space="preserve">32.1891441345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3061981201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2660179138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0619621276855</t>
+    <t xml:space="preserve">32.1891403198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3061943054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2660217285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0619697570801</t>
   </si>
   <si>
     <t xml:space="preserve">34.6472206115723</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4599380493164</t>
+    <t xml:space="preserve">34.4599418640137</t>
   </si>
   <si>
     <t xml:space="preserve">34.7408599853516</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6706390380859</t>
+    <t xml:space="preserve">34.6706352233887</t>
   </si>
   <si>
     <t xml:space="preserve">34.9983787536621</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">34.1790199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7642784118652</t>
+    <t xml:space="preserve">34.764274597168</t>
   </si>
   <si>
     <t xml:space="preserve">34.8813285827637</t>
   </si>
   <si>
-    <t xml:space="preserve">34.3897018432617</t>
+    <t xml:space="preserve">34.389705657959</t>
   </si>
   <si>
     <t xml:space="preserve">34.4131240844727</t>
@@ -677,94 +677,94 @@
     <t xml:space="preserve">35.4665870666504</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7943267822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.8243789672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6671485900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8778457641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9882469177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5735130310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6203308105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6085433959961</t>
+    <t xml:space="preserve">35.7943229675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.8243751525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6671447753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8778381347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9882507324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5735054016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6203346252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6085395812988</t>
   </si>
   <si>
     <t xml:space="preserve">37.7264366149902</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9150657653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1980171203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.938648223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1508598327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4906463623047</t>
+    <t xml:space="preserve">37.9150695800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1980133056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9386444091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1508636474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4906425476074</t>
   </si>
   <si>
     <t xml:space="preserve">39.0232810974121</t>
   </si>
   <si>
-    <t xml:space="preserve">40.084342956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0607566833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8013877868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2397079467773</t>
+    <t xml:space="preserve">40.0843391418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0607604980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.801383972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2397003173828</t>
   </si>
   <si>
     <t xml:space="preserve">41.0275001525879</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4519233703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7112846374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.499080657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8056030273438</t>
+    <t xml:space="preserve">41.4519195556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7112884521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4990844726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.805606842041</t>
   </si>
   <si>
     <t xml:space="preserve">42.3243408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1828689575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0885543823242</t>
+    <t xml:space="preserve">42.1828651428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.088550567627</t>
   </si>
   <si>
     <t xml:space="preserve">42.2771873474121</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8291816711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.966438293457</t>
+    <t xml:space="preserve">41.8291854858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9664421081543</t>
   </si>
   <si>
     <t xml:space="preserve">39.5891761779785</t>
@@ -773,40 +773,40 @@
     <t xml:space="preserve">38.4338035583496</t>
   </si>
   <si>
-    <t xml:space="preserve">38.999698638916</t>
+    <t xml:space="preserve">38.9997024536133</t>
   </si>
   <si>
     <t xml:space="preserve">39.6363372802734</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9428596496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4380187988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.551700592041</t>
+    <t xml:space="preserve">39.9428672790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4380226135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5517044067383</t>
   </si>
   <si>
     <t xml:space="preserve">38.0565452575684</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1411743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3298110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0704383850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1647567749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6695976257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.834644317627</t>
+    <t xml:space="preserve">39.1411819458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3298072814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.070442199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1647605895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6696014404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8346481323242</t>
   </si>
   <si>
     <t xml:space="preserve">38.9053840637207</t>
@@ -815,10 +815,10 @@
     <t xml:space="preserve">39.0940170288086</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8110733032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.2687530517578</t>
+    <t xml:space="preserve">38.8110656738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.2687454223633</t>
   </si>
   <si>
     <t xml:space="preserve">38.7403335571289</t>
@@ -827,109 +827,109 @@
     <t xml:space="preserve">38.6931762695312</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2354888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2590751647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1357116699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5129776000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7765579223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8001365661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5075149536133</t>
+    <t xml:space="preserve">39.2354850769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2590713500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1357040405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5129737854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7765617370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8001403808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.507511138916</t>
   </si>
   <si>
     <t xml:space="preserve">45.3188781738281</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8140335083008</t>
+    <t xml:space="preserve">45.8140411376953</t>
   </si>
   <si>
     <t xml:space="preserve">44.6822471618652</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7862396240234</t>
+    <t xml:space="preserve">43.7862434387207</t>
   </si>
   <si>
     <t xml:space="preserve">44.7529830932617</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1302375793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4464530944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.5879287719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.328556060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3049736022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6211891174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1731872558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0788764953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5837173461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2675094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.366039276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.98876953125</t>
+    <t xml:space="preserve">45.1302452087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4464569091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.5879325866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3285598754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3049774169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6211853027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1731910705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0788688659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5837135314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.267505645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3660354614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9887733459473</t>
   </si>
   <si>
     <t xml:space="preserve">44.4936103820801</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5171966552734</t>
+    <t xml:space="preserve">44.5171890258789</t>
   </si>
   <si>
     <t xml:space="preserve">45.6254081726074</t>
   </si>
   <si>
-    <t xml:space="preserve">45.861198425293</t>
+    <t xml:space="preserve">45.8611946105957</t>
   </si>
   <si>
     <t xml:space="preserve">46.4035110473633</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5824661254883</t>
+    <t xml:space="preserve">47.5824699401855</t>
   </si>
   <si>
     <t xml:space="preserve">47.0637245178223</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1344566345215</t>
+    <t xml:space="preserve">47.1344604492188</t>
   </si>
   <si>
     <t xml:space="preserve">47.1580467224121</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9125709533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3508949279785</t>
+    <t xml:space="preserve">47.9125747680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3508911132812</t>
   </si>
   <si>
     <t xml:space="preserve">48.7378349304199</t>
@@ -944,109 +944,109 @@
     <t xml:space="preserve">47.6296195983887</t>
   </si>
   <si>
-    <t xml:space="preserve">48.0540466308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8654174804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9597320556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1858406066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2717208862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0359306335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.5643577575684</t>
+    <t xml:space="preserve">48.0540428161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8654098510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9597282409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1858444213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2717247009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0359344482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.5643463134766</t>
   </si>
   <si>
     <t xml:space="preserve">43.9748764038086</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5601348876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9138259887695</t>
+    <t xml:space="preserve">42.560131072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9138221740723</t>
   </si>
   <si>
     <t xml:space="preserve">42.7251892089844</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2064437866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4328079223633</t>
+    <t xml:space="preserve">42.2064476013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4328155517578</t>
   </si>
   <si>
     <t xml:space="preserve">42.1781578063965</t>
   </si>
   <si>
-    <t xml:space="preserve">43.3476715087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9800872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3010215759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0838432312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7534828186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.593147277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4799613952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0081367492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0458602905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3288116455078</t>
+    <t xml:space="preserve">43.3476753234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9800834655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3010101318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0838394165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7534790039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5931396484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4799652099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0081329345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0458641052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3288078308105</t>
   </si>
   <si>
     <t xml:space="preserve">41.3953285217285</t>
   </si>
   <si>
-    <t xml:space="preserve">43.489143371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2342491149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1210594177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2439308166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1026992797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1689720153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2729721069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4045143127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7626609802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2531089782715</t>
+    <t xml:space="preserve">43.4891510009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.234245300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1210670471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2439270019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1027030944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1689758300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2729682922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4045104980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7626647949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2531051635742</t>
   </si>
   <si>
     <t xml:space="preserve">45.0547981262207</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">44.9510498046875</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2809028625488</t>
+    <t xml:space="preserve">46.2809104919434</t>
   </si>
   <si>
     <t xml:space="preserve">46.1488609313965</t>
@@ -1067,124 +1067,124 @@
     <t xml:space="preserve">44.9982070922852</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5358047485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1679801940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5923957824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6586647033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.253360748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6683464050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2248191833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0830841064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2057037353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3280563354492</t>
+    <t xml:space="preserve">45.5358009338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1679763793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5923919677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6586723327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2533569335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6683540344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2248115539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0830879211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.205696105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3280639648438</t>
   </si>
   <si>
     <t xml:space="preserve">46.0356826782227</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6584167480469</t>
+    <t xml:space="preserve">45.6584205627441</t>
   </si>
   <si>
     <t xml:space="preserve">45.5169410705566</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1682243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8664131164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5457382202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8852844238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4605979919434</t>
+    <t xml:space="preserve">44.1682281494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8664054870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5457420349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8852729797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4606018066406</t>
   </si>
   <si>
     <t xml:space="preserve">45.6112632751465</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6301193237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7244338989258</t>
+    <t xml:space="preserve">45.6301231384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.724437713623</t>
   </si>
   <si>
     <t xml:space="preserve">46.290340423584</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0262565612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2148818969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6487312316895</t>
+    <t xml:space="preserve">46.026252746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2148857116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6487350463867</t>
   </si>
   <si>
     <t xml:space="preserve">46.705322265625</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5921478271484</t>
+    <t xml:space="preserve">46.5921516418457</t>
   </si>
   <si>
     <t xml:space="preserve">46.8939628601074</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7710990905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8182601928711</t>
+    <t xml:space="preserve">47.7711029052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8182563781738</t>
   </si>
   <si>
     <t xml:space="preserve">48.1955184936523</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9972076416016</t>
+    <t xml:space="preserve">48.9972038269043</t>
   </si>
   <si>
     <t xml:space="preserve">48.5727844238281</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3273086547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3176307678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4119529724121</t>
+    <t xml:space="preserve">49.3273162841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3176345825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4119491577148</t>
   </si>
   <si>
     <t xml:space="preserve">49.8460502624512</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3744697570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2233123779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.081844329834</t>
+    <t xml:space="preserve">49.3744735717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.223316192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0818405151367</t>
   </si>
   <si>
     <t xml:space="preserve">47.5353088378906</t>
@@ -1193,22 +1193,22 @@
     <t xml:space="preserve">46.1960182189941</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2052001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.006893157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2523574829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4223747253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8376197814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6489868164062</t>
+    <t xml:space="preserve">47.2052040100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0068893432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2523536682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4223785400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8376159667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6489906311035</t>
   </si>
   <si>
     <t xml:space="preserve">45.8753471374512</t>
@@ -1217,31 +1217,31 @@
     <t xml:space="preserve">46.5732841491699</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4687881469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8085784912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4789733886719</t>
+    <t xml:space="preserve">49.4687919616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8085746765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4789619445801</t>
   </si>
   <si>
     <t xml:space="preserve">47.3938331604004</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5166931152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1774063110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7812728881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8378715515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4983329772949</t>
+    <t xml:space="preserve">46.5166969299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1774101257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7812767028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8378639221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4983291625977</t>
   </si>
   <si>
     <t xml:space="preserve">44.1776542663574</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">41.8952026367188</t>
   </si>
   <si>
-    <t xml:space="preserve">42.291332244873</t>
+    <t xml:space="preserve">42.2913284301758</t>
   </si>
   <si>
     <t xml:space="preserve">42.4988327026367</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">41.0652236938477</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9518013000488</t>
+    <t xml:space="preserve">41.951789855957</t>
   </si>
   <si>
     <t xml:space="preserve">45.328311920166</t>
@@ -1271,13 +1271,13 @@
     <t xml:space="preserve">45.4603538513184</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4037551879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1016998291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9885215759277</t>
+    <t xml:space="preserve">45.4037628173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1017036437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.988525390625</t>
   </si>
   <si>
     <t xml:space="preserve">46.384651184082</t>
@@ -1286,37 +1286,37 @@
     <t xml:space="preserve">49.044361114502</t>
   </si>
   <si>
-    <t xml:space="preserve">48.902889251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.2898368835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1193237304688</t>
+    <t xml:space="preserve">48.9028854370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.2898330688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1193199157715</t>
   </si>
   <si>
     <t xml:space="preserve">50.6949005126953</t>
   </si>
   <si>
-    <t xml:space="preserve">50.6005859375</t>
+    <t xml:space="preserve">50.6005821228027</t>
   </si>
   <si>
     <t xml:space="preserve">50.9328575134277</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4107093811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0277862548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.214485168457</t>
+    <t xml:space="preserve">50.410701751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0277938842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.2144813537598</t>
   </si>
   <si>
     <t xml:space="preserve">52.1195487976074</t>
   </si>
   <si>
-    <t xml:space="preserve">51.7398109436035</t>
+    <t xml:space="preserve">51.739803314209</t>
   </si>
   <si>
     <t xml:space="preserve">49.8410987854004</t>
@@ -1325,25 +1325,25 @@
     <t xml:space="preserve">51.5024719238281</t>
   </si>
   <si>
-    <t xml:space="preserve">49.271484375</t>
+    <t xml:space="preserve">49.2714881896973</t>
   </si>
   <si>
     <t xml:space="preserve">49.3664207458496</t>
   </si>
   <si>
-    <t xml:space="preserve">49.081615447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.793628692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.274658203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8221473693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0847930908203</t>
+    <t xml:space="preserve">49.0816192626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7936363220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.2746620178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.822151184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0847969055176</t>
   </si>
   <si>
     <t xml:space="preserve">48.6544075012207</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">49.3189544677734</t>
   </si>
   <si>
-    <t xml:space="preserve">49.6512260437012</t>
+    <t xml:space="preserve">49.6512298583984</t>
   </si>
   <si>
     <t xml:space="preserve">49.9835014343262</t>
@@ -1364,94 +1364,94 @@
     <t xml:space="preserve">51.217658996582</t>
   </si>
   <si>
-    <t xml:space="preserve">50.1733665466309</t>
+    <t xml:space="preserve">50.1733703613281</t>
   </si>
   <si>
     <t xml:space="preserve">51.4550018310547</t>
   </si>
   <si>
-    <t xml:space="preserve">52.0246200561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0689086914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.7840919494629</t>
+    <t xml:space="preserve">52.0246124267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.068904876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.7840995788574</t>
   </si>
   <si>
     <t xml:space="preserve">55.4422874450684</t>
   </si>
   <si>
-    <t xml:space="preserve">54.6828002929688</t>
+    <t xml:space="preserve">54.682804107666</t>
   </si>
   <si>
     <t xml:space="preserve">55.1100120544434</t>
   </si>
   <si>
-    <t xml:space="preserve">55.5846862792969</t>
+    <t xml:space="preserve">55.5846939086914</t>
   </si>
   <si>
     <t xml:space="preserve">56.3916473388672</t>
   </si>
   <si>
-    <t xml:space="preserve">54.730281829834</t>
+    <t xml:space="preserve">54.7302742004395</t>
   </si>
   <si>
     <t xml:space="preserve">55.0625495910645</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4897575378418</t>
+    <t xml:space="preserve">55.4897613525391</t>
   </si>
   <si>
     <t xml:space="preserve">55.2524185180664</t>
   </si>
   <si>
-    <t xml:space="preserve">53.1638412475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.6385116577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0182609558105</t>
+    <t xml:space="preserve">53.1638336181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.6385192871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.018253326416</t>
   </si>
   <si>
     <t xml:space="preserve">54.3030624389648</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1131973266602</t>
+    <t xml:space="preserve">54.1131896972656</t>
   </si>
   <si>
     <t xml:space="preserve">53.8283882141113</t>
   </si>
   <si>
-    <t xml:space="preserve">54.7777404785156</t>
+    <t xml:space="preserve">54.7777442932129</t>
   </si>
   <si>
     <t xml:space="preserve">56.4391098022461</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9137840270996</t>
+    <t xml:space="preserve">56.9137954711914</t>
   </si>
   <si>
     <t xml:space="preserve">56.2967071533203</t>
   </si>
   <si>
-    <t xml:space="preserve">56.011905670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2017707824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.534049987793</t>
+    <t xml:space="preserve">56.0119018554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2017784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5340385437012</t>
   </si>
   <si>
     <t xml:space="preserve">56.6764526367188</t>
   </si>
   <si>
-    <t xml:space="preserve">54.9676170349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5942268371582</t>
+    <t xml:space="preserve">54.9676132202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5942306518555</t>
   </si>
   <si>
     <t xml:space="preserve">53.0214347839355</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">55.1574783325195</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3505325317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9264984130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.8790321350098</t>
+    <t xml:space="preserve">54.3505363464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9265022277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.879035949707</t>
   </si>
   <si>
     <t xml:space="preserve">54.0657272338867</t>
@@ -1475,7 +1475,7 @@
     <t xml:space="preserve">54.5878715515137</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4486389160156</t>
+    <t xml:space="preserve">53.4486465454102</t>
   </si>
   <si>
     <t xml:space="preserve">53.6859817504883</t>
@@ -1484,40 +1484,40 @@
     <t xml:space="preserve">53.3062438964844</t>
   </si>
   <si>
-    <t xml:space="preserve">52.404354095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0752601623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4581832885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.2619552612305</t>
+    <t xml:space="preserve">52.4043579101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0752639770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.458179473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.2619476318359</t>
   </si>
   <si>
     <t xml:space="preserve">51.8822135925293</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1606559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.2081298828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5435829162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5404014587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2049560546875</t>
+    <t xml:space="preserve">54.1606597900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.2081260681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5435791015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.540397644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.2049522399902</t>
   </si>
   <si>
     <t xml:space="preserve">56.2492370605469</t>
   </si>
   <si>
-    <t xml:space="preserve">57.1036567687988</t>
+    <t xml:space="preserve">57.1036643981934</t>
   </si>
   <si>
     <t xml:space="preserve">57.2460556030273</t>
@@ -1526,31 +1526,31 @@
     <t xml:space="preserve">57.9106101989746</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9612579345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.790454864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.413890838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.012020111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0499992370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.2271919250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4677124023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0309677124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3157691955566</t>
+    <t xml:space="preserve">56.9612503051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7904586791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.4138832092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0120162963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0499954223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.2271995544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.467716217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0309753417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3157730102539</t>
   </si>
   <si>
     <t xml:space="preserve">46.3474769592285</t>
@@ -1559,19 +1559,19 @@
     <t xml:space="preserve">44.7525596618652</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6766166687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6955947875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1955757141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5563278198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4803848266602</t>
+    <t xml:space="preserve">44.6766128540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6955986022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1955718994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5563354492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4803810119629</t>
   </si>
   <si>
     <t xml:space="preserve">45.9487495422363</t>
@@ -1583,31 +1583,31 @@
     <t xml:space="preserve">46.5373458862305</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5183563232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7462005615234</t>
+    <t xml:space="preserve">46.5183601379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7462043762207</t>
   </si>
   <si>
     <t xml:space="preserve">46.4424057006836</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4930572509766</t>
+    <t xml:space="preserve">45.493049621582</t>
   </si>
   <si>
     <t xml:space="preserve">45.1323013305664</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5690002441406</t>
+    <t xml:space="preserve">45.5690040588379</t>
   </si>
   <si>
     <t xml:space="preserve">45.7019119262695</t>
   </si>
   <si>
-    <t xml:space="preserve">42.3601913452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4677963256836</t>
+    <t xml:space="preserve">42.3601875305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4678001403809</t>
   </si>
   <si>
     <t xml:space="preserve">41.9234809875488</t>
@@ -1619,31 +1619,31 @@
     <t xml:space="preserve">43.7462425231934</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2968673706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8601760864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7208976745605</t>
+    <t xml:space="preserve">44.2968711853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.860164642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7209014892578</t>
   </si>
   <si>
     <t xml:space="preserve">46.7841758728027</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7050476074219</t>
+    <t xml:space="preserve">47.7050514221191</t>
   </si>
   <si>
     <t xml:space="preserve">47.2398643493652</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2905120849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1892585754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2082443237305</t>
+    <t xml:space="preserve">46.2905158996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1892623901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2082481384277</t>
   </si>
   <si>
     <t xml:space="preserve">45.2841949462891</t>
@@ -1652,25 +1652,25 @@
     <t xml:space="preserve">47.3158187866211</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3727760314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6132965087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4867477416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5373916625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5183982849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0753746032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5627288818359</t>
+    <t xml:space="preserve">47.3727798461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6132888793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4867401123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5373878479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5183944702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.075382232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5627326965332</t>
   </si>
   <si>
     <t xml:space="preserve">40.2146453857422</t>
@@ -1679,97 +1679,97 @@
     <t xml:space="preserve">41.8475379943848</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4551200866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2526206970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8095626831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.195613861084</t>
+    <t xml:space="preserve">42.4551239013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2526245117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8095588684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1956214904785</t>
   </si>
   <si>
     <t xml:space="preserve">44.0310516357422</t>
   </si>
   <si>
-    <t xml:space="preserve">44.3158531188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.334846496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8791542053223</t>
+    <t xml:space="preserve">44.3158569335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3348426818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8791580200195</t>
   </si>
   <si>
     <t xml:space="preserve">45.7398872375488</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8348236083984</t>
+    <t xml:space="preserve">45.8348197937012</t>
   </si>
   <si>
     <t xml:space="preserve">46.8031692504883</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3854484558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4234275817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1829032897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1765556335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.3695983886719</t>
+    <t xml:space="preserve">46.3854522705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4234199523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1829071044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1765480041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.3696022033691</t>
   </si>
   <si>
     <t xml:space="preserve">45.4360961914062</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0753402709961</t>
+    <t xml:space="preserve">45.0753364562988</t>
   </si>
   <si>
     <t xml:space="preserve">45.6449546813965</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2588500976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4645347595215</t>
+    <t xml:space="preserve">47.2588539123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4645309448242</t>
   </si>
   <si>
     <t xml:space="preserve">49.8885650634766</t>
   </si>
   <si>
-    <t xml:space="preserve">50.1259078979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6955146789551</t>
+    <t xml:space="preserve">50.1259002685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6955184936523</t>
   </si>
   <si>
     <t xml:space="preserve">50.2208404541016</t>
   </si>
   <si>
-    <t xml:space="preserve">49.93603515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0784378051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1670188903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6891632080078</t>
+    <t xml:space="preserve">49.9360313415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0784454345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1670150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6891593933105</t>
   </si>
   <si>
     <t xml:space="preserve">52.9739685058594</t>
   </si>
   <si>
-    <t xml:space="preserve">54.2555999755859</t>
+    <t xml:space="preserve">54.2555961608887</t>
   </si>
   <si>
     <t xml:space="preserve">53.2587661743164</t>
@@ -1784,28 +1784,28 @@
     <t xml:space="preserve">55.2998847961426</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3979949951172</t>
+    <t xml:space="preserve">54.3979988098145</t>
   </si>
   <si>
     <t xml:space="preserve">53.4011764526367</t>
   </si>
   <si>
-    <t xml:space="preserve">53.9233283996582</t>
+    <t xml:space="preserve">53.9233245849609</t>
   </si>
   <si>
     <t xml:space="preserve">54.4929351806641</t>
   </si>
   <si>
-    <t xml:space="preserve">54.4454689025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4961090087891</t>
+    <t xml:space="preserve">54.4454650878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4961128234863</t>
   </si>
   <si>
     <t xml:space="preserve">54.6353378295898</t>
   </si>
   <si>
-    <t xml:space="preserve">55.964427947998</t>
+    <t xml:space="preserve">55.9644317626953</t>
   </si>
   <si>
     <t xml:space="preserve">55.7270965576172</t>
@@ -1814,13 +1814,13 @@
     <t xml:space="preserve">56.1068344116211</t>
   </si>
   <si>
-    <t xml:space="preserve">55.5328521728516</t>
+    <t xml:space="preserve">55.5328483581543</t>
   </si>
   <si>
     <t xml:space="preserve">53.5239105224609</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5717468261719</t>
+    <t xml:space="preserve">53.5717391967773</t>
   </si>
   <si>
     <t xml:space="preserve">52.615104675293</t>
@@ -1835,25 +1835,25 @@
     <t xml:space="preserve">54.5283813476562</t>
   </si>
   <si>
-    <t xml:space="preserve">55.9633445739746</t>
+    <t xml:space="preserve">55.9633369445801</t>
   </si>
   <si>
     <t xml:space="preserve">56.0590019226074</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1980285644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.7764854431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0111656188965</t>
+    <t xml:space="preserve">55.1980323791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.776481628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.011173248291</t>
   </si>
   <si>
     <t xml:space="preserve">55.6285171508789</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2024993896484</t>
+    <t xml:space="preserve">56.2025032043457</t>
   </si>
   <si>
     <t xml:space="preserve">55.9155120849609</t>
@@ -1871,40 +1871,40 @@
     <t xml:space="preserve">55.1501998901367</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5762100219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4327239990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8632011413574</t>
+    <t xml:space="preserve">54.5762138366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4327163696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8632049560547</t>
   </si>
   <si>
     <t xml:space="preserve">56.919979095459</t>
   </si>
   <si>
-    <t xml:space="preserve">56.8243217468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.2548027038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6808204650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.728645324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.2114372253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.6374626159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5462646484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9244499206543</t>
+    <t xml:space="preserve">56.8243179321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.2547988891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6808166503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.7286491394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.2114410400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.6374588012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5462608337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.924446105957</t>
   </si>
   <si>
     <t xml:space="preserve">58.3549346923828</t>
@@ -1913,22 +1913,22 @@
     <t xml:space="preserve">57.7331161499023</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3504638671875</t>
+    <t xml:space="preserve">57.350471496582</t>
   </si>
   <si>
     <t xml:space="preserve">58.3071060180664</t>
   </si>
   <si>
-    <t xml:space="preserve">60.2682189941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1725463867188</t>
+    <t xml:space="preserve">60.2682075500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.172550201416</t>
   </si>
   <si>
     <t xml:space="preserve">59.7420616149902</t>
   </si>
   <si>
-    <t xml:space="preserve">59.2159080505371</t>
+    <t xml:space="preserve">59.2159156799316</t>
   </si>
   <si>
     <t xml:space="preserve">59.120246887207</t>
@@ -1937,10 +1937,10 @@
     <t xml:space="preserve">57.3026390075684</t>
   </si>
   <si>
-    <t xml:space="preserve">57.8287811279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.115779876709</t>
+    <t xml:space="preserve">57.828784942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.1157760620117</t>
   </si>
   <si>
     <t xml:space="preserve">57.7809562683105</t>
@@ -1952,40 +1952,40 @@
     <t xml:space="preserve">59.4550704956055</t>
   </si>
   <si>
-    <t xml:space="preserve">60.3160400390625</t>
+    <t xml:space="preserve">60.3160438537598</t>
   </si>
   <si>
     <t xml:space="preserve">60.029052734375</t>
   </si>
   <si>
-    <t xml:space="preserve">59.0724143981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.25927734375</t>
+    <t xml:space="preserve">59.0724182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.2592735290527</t>
   </si>
   <si>
     <t xml:space="preserve">58.0201148986816</t>
   </si>
   <si>
-    <t xml:space="preserve">50.9888229370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4148330688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2279815673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3236503601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8931541442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7930221557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8408546447754</t>
+    <t xml:space="preserve">50.9888191223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4148445129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2279777526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3236465454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8931579589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7930183410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8408508300781</t>
   </si>
   <si>
     <t xml:space="preserve">48.6928901672363</t>
@@ -2000,7 +2000,7 @@
     <t xml:space="preserve">49.9365196228027</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0800170898438</t>
+    <t xml:space="preserve">50.0800094604492</t>
   </si>
   <si>
     <t xml:space="preserve">50.6539993286133</t>
@@ -2009,40 +2009,40 @@
     <t xml:space="preserve">50.2235107421875</t>
   </si>
   <si>
-    <t xml:space="preserve">50.845329284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4193077087402</t>
+    <t xml:space="preserve">50.8453254699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4193115234375</t>
   </si>
   <si>
     <t xml:space="preserve">50.940990447998</t>
   </si>
   <si>
-    <t xml:space="preserve">51.5149726867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.797492980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1323127746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6973533630371</t>
+    <t xml:space="preserve">51.5149688720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7974853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1323165893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6973609924316</t>
   </si>
   <si>
     <t xml:space="preserve">49.3147048950195</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4581985473633</t>
+    <t xml:space="preserve">49.4582023620605</t>
   </si>
   <si>
     <t xml:space="preserve">49.745189666748</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0321807861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8363838195801</t>
+    <t xml:space="preserve">50.0321846008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8363800048828</t>
   </si>
   <si>
     <t xml:space="preserve">48.5972290039062</t>
@@ -2054,34 +2054,34 @@
     <t xml:space="preserve">54.0022315979004</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4282455444336</t>
+    <t xml:space="preserve">53.4282493591309</t>
   </si>
   <si>
     <t xml:space="preserve">54.2892265319824</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1935615539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0934295654297</t>
+    <t xml:space="preserve">54.1935577392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0934219360352</t>
   </si>
   <si>
     <t xml:space="preserve">52.4716110229492</t>
   </si>
   <si>
-    <t xml:space="preserve">53.2847480773926</t>
+    <t xml:space="preserve">53.2847557067871</t>
   </si>
   <si>
     <t xml:space="preserve">54.0978927612305</t>
   </si>
   <si>
-    <t xml:space="preserve">54.9110412597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3370552062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8587303161621</t>
+    <t xml:space="preserve">54.9110374450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3370590209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8587379455566</t>
   </si>
   <si>
     <t xml:space="preserve">54.4805526733398</t>
@@ -2090,22 +2090,22 @@
     <t xml:space="preserve">55.0545349121094</t>
   </si>
   <si>
-    <t xml:space="preserve">55.3415222167969</t>
+    <t xml:space="preserve">55.3415260314941</t>
   </si>
   <si>
     <t xml:space="preserve">55.86767578125</t>
   </si>
   <si>
-    <t xml:space="preserve">56.5373229980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6329879760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.4027671813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0679473876953</t>
+    <t xml:space="preserve">56.5373191833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6329917907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.4027633666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0679512023926</t>
   </si>
   <si>
     <t xml:space="preserve">59.6942291259766</t>
@@ -2114,28 +2114,28 @@
     <t xml:space="preserve">59.3115730285645</t>
   </si>
   <si>
-    <t xml:space="preserve">62.8511428833008</t>
+    <t xml:space="preserve">62.8511276245117</t>
   </si>
   <si>
     <t xml:space="preserve">63.6164436340332</t>
   </si>
   <si>
-    <t xml:space="preserve">65.3384017944336</t>
+    <t xml:space="preserve">65.3383941650391</t>
   </si>
   <si>
     <t xml:space="preserve">66.3428573608398</t>
   </si>
   <si>
-    <t xml:space="preserve">66.9646759033203</t>
+    <t xml:space="preserve">66.9646835327148</t>
   </si>
   <si>
     <t xml:space="preserve">67.9213180541992</t>
   </si>
   <si>
-    <t xml:space="preserve">69.260612487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.0692901611328</t>
+    <t xml:space="preserve">69.2606201171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.0692749023438</t>
   </si>
   <si>
     <t xml:space="preserve">67.3951644897461</t>
@@ -2144,25 +2144,25 @@
     <t xml:space="preserve">68.016975402832</t>
   </si>
   <si>
-    <t xml:space="preserve">66.869010925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.2994995117188</t>
+    <t xml:space="preserve">66.8690185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.2995071411133</t>
   </si>
   <si>
     <t xml:space="preserve">67.5386581420898</t>
   </si>
   <si>
-    <t xml:space="preserve">68.92578125</t>
+    <t xml:space="preserve">68.9257888793945</t>
   </si>
   <si>
     <t xml:space="preserve">69.212776184082</t>
   </si>
   <si>
-    <t xml:space="preserve">68.4474716186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.8734741210938</t>
+    <t xml:space="preserve">68.4474639892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.8734817504883</t>
   </si>
   <si>
     <t xml:space="preserve">67.7778167724609</t>
@@ -2171,19 +2171,19 @@
     <t xml:space="preserve">67.0603408813477</t>
   </si>
   <si>
-    <t xml:space="preserve">66.0080490112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.4385299682617</t>
+    <t xml:space="preserve">66.0080413818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.4385223388672</t>
   </si>
   <si>
     <t xml:space="preserve">65.5775604248047</t>
   </si>
   <si>
-    <t xml:space="preserve">65.9123764038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.2516708374023</t>
+    <t xml:space="preserve">65.9123687744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.2516784667969</t>
   </si>
   <si>
     <t xml:space="preserve">67.8256607055664</t>
@@ -2192,7 +2192,7 @@
     <t xml:space="preserve">67.6343231201172</t>
   </si>
   <si>
-    <t xml:space="preserve">65.7688903808594</t>
+    <t xml:space="preserve">65.7688751220703</t>
   </si>
   <si>
     <t xml:space="preserve">66.1037063598633</t>
@@ -2204,67 +2204,67 @@
     <t xml:space="preserve">68.2083053588867</t>
   </si>
   <si>
-    <t xml:space="preserve">70.3129196166992</t>
+    <t xml:space="preserve">70.3129119873047</t>
   </si>
   <si>
     <t xml:space="preserve">73.3263244628906</t>
   </si>
   <si>
-    <t xml:space="preserve">73.2306594848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.0916366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.6611480712891</t>
+    <t xml:space="preserve">73.2306671142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.0916290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.6611404418945</t>
   </si>
   <si>
     <t xml:space="preserve">73.3741607666016</t>
   </si>
   <si>
-    <t xml:space="preserve">70.6955718994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.7912445068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.4653625488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.2650833129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.6387939453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3173828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9392013549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.7045135498047</t>
+    <t xml:space="preserve">70.6955795288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.7912368774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.4653549194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.2650756835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.638801574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3173904418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9391860961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.7045059204102</t>
   </si>
   <si>
     <t xml:space="preserve">72.7523498535156</t>
   </si>
   <si>
-    <t xml:space="preserve">72.6088409423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.4264602661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.1394653320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7478790283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9870376586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.2784881591797</t>
+    <t xml:space="preserve">72.6088485717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.4264678955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.1394577026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7478713989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9870300292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.2784957885742</t>
   </si>
   <si>
     <t xml:space="preserve">71.4130554199219</t>
@@ -2273,40 +2273,40 @@
     <t xml:space="preserve">66.8211898803711</t>
   </si>
   <si>
-    <t xml:space="preserve">65.7210464477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.1336555480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.8077774047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8944892883301</t>
+    <t xml:space="preserve">65.7210388183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.1336517333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.8077697753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8944931030273</t>
   </si>
   <si>
     <t xml:space="preserve">60.9378623962402</t>
   </si>
   <si>
-    <t xml:space="preserve">57.8766136169434</t>
+    <t xml:space="preserve">57.8766174316406</t>
   </si>
   <si>
     <t xml:space="preserve">52.5672721862793</t>
   </si>
   <si>
-    <t xml:space="preserve">52.0889587402344</t>
+    <t xml:space="preserve">52.0889549255371</t>
   </si>
   <si>
     <t xml:space="preserve">46.3778228759766</t>
   </si>
   <si>
-    <t xml:space="preserve">48.7407188415527</t>
+    <t xml:space="preserve">48.74072265625</t>
   </si>
   <si>
     <t xml:space="preserve">45.4594497680664</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7094345092773</t>
+    <t xml:space="preserve">41.7094268798828</t>
   </si>
   <si>
     <t xml:space="preserve">43.8714332580566</t>
@@ -2315,58 +2315,58 @@
     <t xml:space="preserve">45.2107238769531</t>
   </si>
   <si>
-    <t xml:space="preserve">45.344654083252</t>
+    <t xml:space="preserve">45.3446578979492</t>
   </si>
   <si>
     <t xml:space="preserve">47.1048698425293</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0844879150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2190399169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.1680755615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.6852874755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.263744354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.0813522338867</t>
+    <t xml:space="preserve">51.0844841003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2190437316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.1680793762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.6852836608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.2637405395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.081356048584</t>
   </si>
   <si>
     <t xml:space="preserve">60.3638763427734</t>
   </si>
   <si>
-    <t xml:space="preserve">61.1291923522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4161758422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.6598052978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.5207862854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.564136505127</t>
+    <t xml:space="preserve">61.1291885375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4161720275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.6598091125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.5207824707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5641441345215</t>
   </si>
   <si>
     <t xml:space="preserve">63.1381340026855</t>
   </si>
   <si>
-    <t xml:space="preserve">63.0424652099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9901657104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.033519744873</t>
+    <t xml:space="preserve">63.0424690246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.990161895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0335235595703</t>
   </si>
   <si>
     <t xml:space="preserve">59.2684898376465</t>
@@ -2381,19 +2381,19 @@
     <t xml:space="preserve">63.705192565918</t>
   </si>
   <si>
-    <t xml:space="preserve">64.7179107666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3676147460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6569633483887</t>
+    <t xml:space="preserve">64.717903137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.367603302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6569557189941</t>
   </si>
   <si>
     <t xml:space="preserve">64.0909881591797</t>
   </si>
   <si>
-    <t xml:space="preserve">64.4285583496094</t>
+    <t xml:space="preserve">64.4285659790039</t>
   </si>
   <si>
     <t xml:space="preserve">64.9108200073242</t>
@@ -2402,25 +2402,25 @@
     <t xml:space="preserve">68.4312286376953</t>
   </si>
   <si>
-    <t xml:space="preserve">68.0936508178711</t>
+    <t xml:space="preserve">68.0936584472656</t>
   </si>
   <si>
     <t xml:space="preserve">68.3830108642578</t>
   </si>
   <si>
-    <t xml:space="preserve">68.624137878418</t>
+    <t xml:space="preserve">68.6241302490234</t>
   </si>
   <si>
     <t xml:space="preserve">69.9744338989258</t>
   </si>
   <si>
-    <t xml:space="preserve">73.3983993530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.1217727661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.9288787841797</t>
+    <t xml:space="preserve">73.3984069824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.1217803955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.9288864135742</t>
   </si>
   <si>
     <t xml:space="preserve">74.3628997802734</t>
@@ -2429,13 +2429,13 @@
     <t xml:space="preserve">75.8578720092773</t>
   </si>
   <si>
-    <t xml:space="preserve">74.6522521972656</t>
+    <t xml:space="preserve">74.6522598266602</t>
   </si>
   <si>
     <t xml:space="preserve">71.8552093505859</t>
   </si>
   <si>
-    <t xml:space="preserve">70.6013488769531</t>
+    <t xml:space="preserve">70.6013565063477</t>
   </si>
   <si>
     <t xml:space="preserve">71.1318283081055</t>
@@ -2456,70 +2456,70 @@
     <t xml:space="preserve">64.8625869750977</t>
   </si>
   <si>
-    <t xml:space="preserve">66.5504608154297</t>
+    <t xml:space="preserve">66.5504531860352</t>
   </si>
   <si>
     <t xml:space="preserve">67.3220596313477</t>
   </si>
   <si>
-    <t xml:space="preserve">69.9262084960938</t>
+    <t xml:space="preserve">69.9262161254883</t>
   </si>
   <si>
     <t xml:space="preserve">71.1800537109375</t>
   </si>
   <si>
-    <t xml:space="preserve">70.4084625244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3729629516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.4921798706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.3120040893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.5276794433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.2865600585938</t>
+    <t xml:space="preserve">70.4084548950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3729553222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.4921722412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.31201171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.5276870727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.2865676879883</t>
   </si>
   <si>
     <t xml:space="preserve">68.6723556518555</t>
   </si>
   <si>
-    <t xml:space="preserve">69.0099334716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.2992782592773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.1445465087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.2765045166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.8069763183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.1673355102539</t>
+    <t xml:space="preserve">69.0099411010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.2992706298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.1445617675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.2765197753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.8069839477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.1673278808594</t>
   </si>
   <si>
     <t xml:space="preserve">70.5531311035156</t>
   </si>
   <si>
-    <t xml:space="preserve">70.360237121582</t>
+    <t xml:space="preserve">70.3602294921875</t>
   </si>
   <si>
     <t xml:space="preserve">71.6623077392578</t>
   </si>
   <si>
-    <t xml:space="preserve">72.3374633789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.867919921875</t>
+    <t xml:space="preserve">72.3374557495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.8679428100586</t>
   </si>
   <si>
     <t xml:space="preserve">73.4466323852539</t>
@@ -2531,67 +2531,67 @@
     <t xml:space="preserve">71.999885559082</t>
   </si>
   <si>
-    <t xml:space="preserve">73.0608367919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.6877593994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.5913009643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.9643859863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.7487106323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.9342269897461</t>
+    <t xml:space="preserve">73.0608291625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.6877517700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.59130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.9643783569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.7486953735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.9342193603516</t>
   </si>
   <si>
     <t xml:space="preserve">82.9469451904297</t>
   </si>
   <si>
-    <t xml:space="preserve">85.1170806884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.0815734863281</t>
+    <t xml:space="preserve">85.117073059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.0815658569336</t>
   </si>
   <si>
     <t xml:space="preserve">85.3581924438477</t>
   </si>
   <si>
-    <t xml:space="preserve">83.1398544311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0179443359375</t>
+    <t xml:space="preserve">83.1398468017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.017951965332</t>
   </si>
   <si>
     <t xml:space="preserve">81.0661849975586</t>
   </si>
   <si>
-    <t xml:space="preserve">82.609375</t>
+    <t xml:space="preserve">82.6093826293945</t>
   </si>
   <si>
     <t xml:space="preserve">80.8732757568359</t>
   </si>
   <si>
-    <t xml:space="preserve">83.0916290283203</t>
+    <t xml:space="preserve">83.0916213989258</t>
   </si>
   <si>
     <t xml:space="preserve">85.3099670410156</t>
   </si>
   <si>
-    <t xml:space="preserve">84.5866012573242</t>
+    <t xml:space="preserve">84.5865859985352</t>
   </si>
   <si>
     <t xml:space="preserve">84.6348190307617</t>
   </si>
   <si>
-    <t xml:space="preserve">83.6703186035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.7795028686523</t>
+    <t xml:space="preserve">83.6703262329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.7794952392578</t>
   </si>
   <si>
     <t xml:space="preserve">84.6830520629883</t>
@@ -2603,7 +2603,7 @@
     <t xml:space="preserve">86.2262496948242</t>
   </si>
   <si>
-    <t xml:space="preserve">87.7212066650391</t>
+    <t xml:space="preserve">87.7212219238281</t>
   </si>
   <si>
     <t xml:space="preserve">89.6984405517578</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">89.3126449584961</t>
   </si>
   <si>
-    <t xml:space="preserve">90.6629409790039</t>
+    <t xml:space="preserve">90.6629333496094</t>
   </si>
   <si>
     <t xml:space="preserve">88.1070251464844</t>
@@ -2639,16 +2639,16 @@
     <t xml:space="preserve">95.0031890869141</t>
   </si>
   <si>
-    <t xml:space="preserve">94.9067459106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7265701293945</t>
+    <t xml:space="preserve">94.90673828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7265625</t>
   </si>
   <si>
     <t xml:space="preserve">93.218864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">93.5082168579102</t>
+    <t xml:space="preserve">93.5082092285156</t>
   </si>
   <si>
     <t xml:space="preserve">91.4827728271484</t>
@@ -2669,25 +2669,25 @@
     <t xml:space="preserve">95.5336685180664</t>
   </si>
   <si>
-    <t xml:space="preserve">94.9549560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.810302734375</t>
+    <t xml:space="preserve">94.9549713134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.8102874755859</t>
   </si>
   <si>
     <t xml:space="preserve">93.6046676635742</t>
   </si>
   <si>
-    <t xml:space="preserve">94.5209350585938</t>
+    <t xml:space="preserve">94.5209426879883</t>
   </si>
   <si>
     <t xml:space="preserve">92.6883926391602</t>
   </si>
   <si>
-    <t xml:space="preserve">91.4345397949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0259628295898</t>
+    <t xml:space="preserve">91.4345474243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0259704589844</t>
   </si>
   <si>
     <t xml:space="preserve">95.2925491333008</t>
@@ -2699,52 +2699,52 @@
     <t xml:space="preserve">100.115043640137</t>
   </si>
   <si>
-    <t xml:space="preserve">99.7292327880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.6073303222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.8966827392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3789443969727</t>
+    <t xml:space="preserve">99.729248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.6073379516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.8966903686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3789291381836</t>
   </si>
   <si>
     <t xml:space="preserve">96.3052597045898</t>
   </si>
   <si>
-    <t xml:space="preserve">93.7493362426758</t>
+    <t xml:space="preserve">93.7493438720703</t>
   </si>
   <si>
     <t xml:space="preserve">92.8330688476562</t>
   </si>
   <si>
-    <t xml:space="preserve">92.8812942504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.4445877075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.2034606933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.0232925415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.1324691772461</t>
+    <t xml:space="preserve">92.8813018798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.4445953369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.2034530639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.0233001708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.1324615478516</t>
   </si>
   <si>
     <t xml:space="preserve">92.2061386108398</t>
   </si>
   <si>
-    <t xml:space="preserve">96.4499359130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.4372177124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7747955322266</t>
+    <t xml:space="preserve">96.4499435424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4372100830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.774787902832</t>
   </si>
   <si>
     <t xml:space="preserve">92.4472732543945</t>
@@ -2753,73 +2753,73 @@
     <t xml:space="preserve">92.0614624023438</t>
   </si>
   <si>
-    <t xml:space="preserve">91.8685607910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.8203430175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7111663818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8558349609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3863220214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7593994140625</t>
+    <t xml:space="preserve">91.8685684204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.8203353881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7111740112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.855842590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3863143920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.759391784668</t>
   </si>
   <si>
     <t xml:space="preserve">87.7694473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">88.2516860961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3608779907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.3735885620117</t>
+    <t xml:space="preserve">88.2517013549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3608703613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.3735961914062</t>
   </si>
   <si>
     <t xml:space="preserve">94.2798156738281</t>
   </si>
   <si>
-    <t xml:space="preserve">90.0842514038086</t>
+    <t xml:space="preserve">90.0842437744141</t>
   </si>
   <si>
     <t xml:space="preserve">91.1451873779297</t>
   </si>
   <si>
-    <t xml:space="preserve">92.4954986572266</t>
+    <t xml:space="preserve">92.495491027832</t>
   </si>
   <si>
     <t xml:space="preserve">89.4573287963867</t>
   </si>
   <si>
-    <t xml:space="preserve">91.675666809082</t>
+    <t xml:space="preserve">91.6756744384766</t>
   </si>
   <si>
     <t xml:space="preserve">91.9167938232422</t>
   </si>
   <si>
-    <t xml:space="preserve">91.7238998413086</t>
+    <t xml:space="preserve">91.7238922119141</t>
   </si>
   <si>
     <t xml:space="preserve">91.0969696044922</t>
   </si>
   <si>
-    <t xml:space="preserve">90.9040679931641</t>
+    <t xml:space="preserve">90.9040756225586</t>
   </si>
   <si>
     <t xml:space="preserve">92.3508224487305</t>
   </si>
   <si>
-    <t xml:space="preserve">93.4599990844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.5437164306641</t>
+    <t xml:space="preserve">93.4599914550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.5437088012695</t>
   </si>
   <si>
     <t xml:space="preserve">95.9194564819336</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">93.2670822143555</t>
   </si>
   <si>
-    <t xml:space="preserve">93.5564346313477</t>
+    <t xml:space="preserve">93.5564498901367</t>
   </si>
   <si>
     <t xml:space="preserve">94.5691680908203</t>
@@ -2843,16 +2843,16 @@
     <t xml:space="preserve">100.018577575684</t>
   </si>
   <si>
-    <t xml:space="preserve">98.1860504150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.414436340332</t>
+    <t xml:space="preserve">98.1860427856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.4144439697266</t>
   </si>
   <si>
     <t xml:space="preserve">100.790191650391</t>
   </si>
   <si>
-    <t xml:space="preserve">102.912071228027</t>
+    <t xml:space="preserve">102.912086486816</t>
   </si>
   <si>
     <t xml:space="preserve">101.46533203125</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">102.719184875488</t>
   </si>
   <si>
-    <t xml:space="preserve">102.526298522949</t>
+    <t xml:space="preserve">102.526290893555</t>
   </si>
   <si>
     <t xml:space="preserve">102.140487670898</t>
@@ -2870,10 +2870,10 @@
     <t xml:space="preserve">104.937538146973</t>
   </si>
   <si>
-    <t xml:space="preserve">103.10498046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.58723449707</t>
+    <t xml:space="preserve">103.104988098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.587242126465</t>
   </si>
   <si>
     <t xml:space="preserve">102.815635681152</t>
@@ -2882,46 +2882,46 @@
     <t xml:space="preserve">103.201438903809</t>
   </si>
   <si>
-    <t xml:space="preserve">100.500839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.404388427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.5718231201172</t>
+    <t xml:space="preserve">100.500823974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.404396057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.5718383789062</t>
   </si>
   <si>
     <t xml:space="preserve">95.0514144897461</t>
   </si>
   <si>
-    <t xml:space="preserve">94.1351470947266</t>
+    <t xml:space="preserve">94.135139465332</t>
   </si>
   <si>
     <t xml:space="preserve">92.5919342041016</t>
   </si>
   <si>
-    <t xml:space="preserve">89.2161865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.297882080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.3434448242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.561790466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.973037719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.780136108398</t>
+    <t xml:space="preserve">89.216194152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.297889709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.3434371948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.561782836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.973045349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.780143737793</t>
   </si>
   <si>
     <t xml:space="preserve">105.323333740234</t>
   </si>
   <si>
-    <t xml:space="preserve">103.490798950195</t>
+    <t xml:space="preserve">103.490783691406</t>
   </si>
   <si>
     <t xml:space="preserve">104.069480895996</t>
@@ -2933,52 +2933,52 @@
     <t xml:space="preserve">110.14582824707</t>
   </si>
   <si>
-    <t xml:space="preserve">108.699081420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.287826538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.44522857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.384284973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.891983032227</t>
+    <t xml:space="preserve">108.699073791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.28783416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.445236206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.38427734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.891990661621</t>
   </si>
   <si>
     <t xml:space="preserve">107.831039428711</t>
   </si>
   <si>
-    <t xml:space="preserve">108.795539855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.084869384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.059432983398</t>
+    <t xml:space="preserve">108.795532226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.084884643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.059425354004</t>
   </si>
   <si>
     <t xml:space="preserve">107.348785400391</t>
   </si>
   <si>
-    <t xml:space="preserve">109.56713104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.506187438965</t>
+    <t xml:space="preserve">109.567123413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.50617980957</t>
   </si>
   <si>
     <t xml:space="preserve">109.530754089355</t>
   </si>
   <si>
-    <t xml:space="preserve">107.786010742188</t>
+    <t xml:space="preserve">107.786018371582</t>
   </si>
   <si>
     <t xml:space="preserve">108.755317687988</t>
   </si>
   <si>
-    <t xml:space="preserve">109.046112060547</t>
+    <t xml:space="preserve">109.046104431152</t>
   </si>
   <si>
     <t xml:space="preserve">109.918479919434</t>
@@ -2987,7 +2987,7 @@
     <t xml:space="preserve">110.500061035156</t>
   </si>
   <si>
-    <t xml:space="preserve">109.82154083252</t>
+    <t xml:space="preserve">109.821548461914</t>
   </si>
   <si>
     <t xml:space="preserve">110.887771606445</t>
@@ -2996,25 +2996,25 @@
     <t xml:space="preserve">111.663208007812</t>
   </si>
   <si>
-    <t xml:space="preserve">113.117172241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.831207275391</t>
+    <t xml:space="preserve">113.117164611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.831199645996</t>
   </si>
   <si>
     <t xml:space="preserve">113.795677185059</t>
   </si>
   <si>
-    <t xml:space="preserve">114.764976501465</t>
+    <t xml:space="preserve">114.76496887207</t>
   </si>
   <si>
     <t xml:space="preserve">114.668045043945</t>
   </si>
   <si>
-    <t xml:space="preserve">114.280319213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.474189758301</t>
+    <t xml:space="preserve">114.280326843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.474174499512</t>
   </si>
   <si>
     <t xml:space="preserve">116.509704589844</t>
@@ -3023,7 +3023,7 @@
     <t xml:space="preserve">121.453140258789</t>
   </si>
   <si>
-    <t xml:space="preserve">126.590423583984</t>
+    <t xml:space="preserve">126.59041595459</t>
   </si>
   <si>
     <t xml:space="preserve">128.819793701172</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">127.268928527832</t>
   </si>
   <si>
-    <t xml:space="preserve">128.432083129883</t>
+    <t xml:space="preserve">128.432067871094</t>
   </si>
   <si>
     <t xml:space="preserve">133.181640625</t>
@@ -3044,28 +3044,28 @@
     <t xml:space="preserve">130.467620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">130.273742675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.916717529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.635589599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.70182800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.44172668457</t>
+    <t xml:space="preserve">130.27375793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.916732788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.635604858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.701812744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.441741943359</t>
   </si>
   <si>
     <t xml:space="preserve">133.375518798828</t>
   </si>
   <si>
-    <t xml:space="preserve">135.798767089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.314117431641</t>
+    <t xml:space="preserve">135.798751831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.314102172852</t>
   </si>
   <si>
     <t xml:space="preserve">136.574188232422</t>
@@ -3083,7 +3083,7 @@
     <t xml:space="preserve">137.446578979492</t>
   </si>
   <si>
-    <t xml:space="preserve">135.89567565918</t>
+    <t xml:space="preserve">135.895660400391</t>
   </si>
   <si>
     <t xml:space="preserve">134.344818115234</t>
@@ -3101,19 +3101,19 @@
     <t xml:space="preserve">143.359283447266</t>
   </si>
   <si>
-    <t xml:space="preserve">140.063674926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.803588867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.548309326172</t>
+    <t xml:space="preserve">140.063659667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.803558349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.548324584961</t>
   </si>
   <si>
     <t xml:space="preserve">140.160614013672</t>
   </si>
   <si>
-    <t xml:space="preserve">139.579010009766</t>
+    <t xml:space="preserve">139.579025268555</t>
   </si>
   <si>
     <t xml:space="preserve">136.671127319336</t>
@@ -3122,22 +3122,22 @@
     <t xml:space="preserve">138.609710693359</t>
   </si>
   <si>
-    <t xml:space="preserve">135.992630004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.640411376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.094360351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.226821899414</t>
+    <t xml:space="preserve">135.992614746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.640426635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.094375610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.226837158203</t>
   </si>
   <si>
     <t xml:space="preserve">142.583847045898</t>
   </si>
   <si>
-    <t xml:space="preserve">141.905334472656</t>
+    <t xml:space="preserve">141.905319213867</t>
   </si>
   <si>
     <t xml:space="preserve">143.262359619141</t>
@@ -3146,22 +3146,22 @@
     <t xml:space="preserve">142.486907958984</t>
   </si>
   <si>
-    <t xml:space="preserve">146.073303222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.884307861328</t>
+    <t xml:space="preserve">146.073318481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.884292602539</t>
   </si>
   <si>
     <t xml:space="preserve">148.011917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">149.175079345703</t>
+    <t xml:space="preserve">149.175064086914</t>
   </si>
   <si>
     <t xml:space="preserve">149.756652832031</t>
   </si>
   <si>
-    <t xml:space="preserve">146.364105224609</t>
+    <t xml:space="preserve">146.364120483398</t>
   </si>
   <si>
     <t xml:space="preserve">147.236465454102</t>
@@ -3173,25 +3173,25 @@
     <t xml:space="preserve">147.818054199219</t>
   </si>
   <si>
-    <t xml:space="preserve">150.532104492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.629013061523</t>
+    <t xml:space="preserve">150.532119750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.629028320312</t>
   </si>
   <si>
     <t xml:space="preserve">155.087799072266</t>
   </si>
   <si>
-    <t xml:space="preserve">154.893951416016</t>
+    <t xml:space="preserve">154.893936157227</t>
   </si>
   <si>
     <t xml:space="preserve">152.955352783203</t>
   </si>
   <si>
-    <t xml:space="preserve">157.89875793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.67903137207</t>
+    <t xml:space="preserve">157.898773193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.679016113281</t>
   </si>
   <si>
     <t xml:space="preserve">166.816314697266</t>
@@ -3203,31 +3203,31 @@
     <t xml:space="preserve">165.847015380859</t>
   </si>
   <si>
-    <t xml:space="preserve">165.45930480957</t>
+    <t xml:space="preserve">165.459289550781</t>
   </si>
   <si>
     <t xml:space="preserve">165.653137207031</t>
   </si>
   <si>
-    <t xml:space="preserve">167.397888183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.851852416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.142623901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.627288818359</t>
+    <t xml:space="preserve">167.397903442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.851837158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.142639160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.62727355957</t>
   </si>
   <si>
     <t xml:space="preserve">170.305786132812</t>
   </si>
   <si>
-    <t xml:space="preserve">169.239562988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.724227905273</t>
+    <t xml:space="preserve">169.23957824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.724212646484</t>
   </si>
   <si>
     <t xml:space="preserve">168.948776245117</t>
@@ -3236,7 +3236,7 @@
     <t xml:space="preserve">163.811477661133</t>
   </si>
   <si>
-    <t xml:space="preserve">167.204025268555</t>
+    <t xml:space="preserve">167.204040527344</t>
   </si>
   <si>
     <t xml:space="preserve">165.071578979492</t>
@@ -3251,10 +3251,10 @@
     <t xml:space="preserve">176.606231689453</t>
   </si>
   <si>
-    <t xml:space="preserve">171.372024536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.470687866211</t>
+    <t xml:space="preserve">171.372039794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.470672607422</t>
   </si>
   <si>
     <t xml:space="preserve">152.567611694336</t>
@@ -3263,10 +3263,10 @@
     <t xml:space="preserve">154.506210327148</t>
   </si>
   <si>
-    <t xml:space="preserve">153.827697753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.465850830078</t>
+    <t xml:space="preserve">153.827713012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.465866088867</t>
   </si>
   <si>
     <t xml:space="preserve">153.633865356445</t>
@@ -3275,7 +3275,7 @@
     <t xml:space="preserve">147.430358886719</t>
   </si>
   <si>
-    <t xml:space="preserve">147.721115112305</t>
+    <t xml:space="preserve">147.721130371094</t>
   </si>
   <si>
     <t xml:space="preserve">145.97639465332</t>
@@ -3284,28 +3284,28 @@
     <t xml:space="preserve">157.026397705078</t>
   </si>
   <si>
-    <t xml:space="preserve">159.643524169922</t>
+    <t xml:space="preserve">159.643493652344</t>
   </si>
   <si>
     <t xml:space="preserve">162.842193603516</t>
   </si>
   <si>
-    <t xml:space="preserve">163.229888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.418930053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.097442626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.806640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.612808227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.582107543945</t>
+    <t xml:space="preserve">163.229904174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.4189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.097457885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.806671142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160.61279296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.582077026367</t>
   </si>
   <si>
     <t xml:space="preserve">162.551391601562</t>
@@ -3317,13 +3317,13 @@
     <t xml:space="preserve">164.393081665039</t>
   </si>
   <si>
-    <t xml:space="preserve">171.275085449219</t>
+    <t xml:space="preserve">171.275100708008</t>
   </si>
   <si>
     <t xml:space="preserve">173.213684082031</t>
   </si>
   <si>
-    <t xml:space="preserve">172.825973510742</t>
+    <t xml:space="preserve">172.825958251953</t>
   </si>
   <si>
     <t xml:space="preserve">174.182983398438</t>
@@ -3335,19 +3335,19 @@
     <t xml:space="preserve">172.341323852539</t>
   </si>
   <si>
-    <t xml:space="preserve">176.703155517578</t>
+    <t xml:space="preserve">176.703170776367</t>
   </si>
   <si>
     <t xml:space="preserve">179.804916381836</t>
   </si>
   <si>
-    <t xml:space="preserve">173.892181396484</t>
+    <t xml:space="preserve">173.892196655273</t>
   </si>
   <si>
     <t xml:space="preserve">168.754913330078</t>
   </si>
   <si>
-    <t xml:space="preserve">168.561050415039</t>
+    <t xml:space="preserve">168.56103515625</t>
   </si>
   <si>
     <t xml:space="preserve">167.010192871094</t>
@@ -3359,19 +3359,19 @@
     <t xml:space="preserve">162.454467773438</t>
   </si>
   <si>
-    <t xml:space="preserve">159.837341308594</t>
+    <t xml:space="preserve">159.837371826172</t>
   </si>
   <si>
     <t xml:space="preserve">166.040878295898</t>
   </si>
   <si>
-    <t xml:space="preserve">167.882553100586</t>
+    <t xml:space="preserve">167.882537841797</t>
   </si>
   <si>
     <t xml:space="preserve">160.709732055664</t>
   </si>
   <si>
-    <t xml:space="preserve">162.745254516602</t>
+    <t xml:space="preserve">162.745239257812</t>
   </si>
   <si>
     <t xml:space="preserve">159.158843994141</t>
@@ -3380,13 +3380,13 @@
     <t xml:space="preserve">172.535171508789</t>
   </si>
   <si>
-    <t xml:space="preserve">174.958435058594</t>
+    <t xml:space="preserve">174.958404541016</t>
   </si>
   <si>
     <t xml:space="preserve">173.698333740234</t>
   </si>
   <si>
-    <t xml:space="preserve">174.570693969727</t>
+    <t xml:space="preserve">174.570724487305</t>
   </si>
   <si>
     <t xml:space="preserve">169.43342590332</t>
@@ -3395,13 +3395,13 @@
     <t xml:space="preserve">168.076400756836</t>
   </si>
   <si>
-    <t xml:space="preserve">163.617645263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.877731323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.714553833008</t>
+    <t xml:space="preserve">163.617630004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.877716064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.714538574219</t>
   </si>
   <si>
     <t xml:space="preserve">170.596572875977</t>
@@ -3413,13 +3413,13 @@
     <t xml:space="preserve">174.473785400391</t>
   </si>
   <si>
-    <t xml:space="preserve">164.005355834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.317184448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.572448730469</t>
+    <t xml:space="preserve">164.005340576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.317199707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.57243347168</t>
   </si>
   <si>
     <t xml:space="preserve">155.863235473633</t>
@@ -3437,7 +3437,7 @@
     <t xml:space="preserve">157.220260620117</t>
   </si>
   <si>
-    <t xml:space="preserve">151.113662719727</t>
+    <t xml:space="preserve">151.113677978516</t>
   </si>
   <si>
     <t xml:space="preserve">152.858413696289</t>
@@ -3446,7 +3446,7 @@
     <t xml:space="preserve">154.990859985352</t>
   </si>
   <si>
-    <t xml:space="preserve">137.931228637695</t>
+    <t xml:space="preserve">137.931213378906</t>
   </si>
   <si>
     <t xml:space="preserve">143.747009277344</t>
@@ -3455,16 +3455,16 @@
     <t xml:space="preserve">143.553161621094</t>
   </si>
   <si>
-    <t xml:space="preserve">144.522445678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.910171508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.385177612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.089553833008</t>
+    <t xml:space="preserve">144.5224609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.91015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.385162353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.089538574219</t>
   </si>
   <si>
     <t xml:space="preserve">132.600067138672</t>
@@ -3473,19 +3473,19 @@
     <t xml:space="preserve">132.309280395508</t>
   </si>
   <si>
-    <t xml:space="preserve">138.997421264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.834289550781</t>
+    <t xml:space="preserve">138.997436523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.834274291992</t>
   </si>
   <si>
     <t xml:space="preserve">137.543487548828</t>
   </si>
   <si>
-    <t xml:space="preserve">138.125061035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.512786865234</t>
+    <t xml:space="preserve">138.125076293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.512771606445</t>
   </si>
   <si>
     <t xml:space="preserve">142.680770874023</t>
@@ -3494,28 +3494,28 @@
     <t xml:space="preserve">129.692169189453</t>
   </si>
   <si>
-    <t xml:space="preserve">125.039535522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.961929321289</t>
+    <t xml:space="preserve">125.039543151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.9619140625</t>
   </si>
   <si>
     <t xml:space="preserve">135.507965087891</t>
   </si>
   <si>
-    <t xml:space="preserve">142.874633789062</t>
+    <t xml:space="preserve">142.874618530273</t>
   </si>
   <si>
     <t xml:space="preserve">149.562805175781</t>
   </si>
   <si>
-    <t xml:space="preserve">151.986053466797</t>
+    <t xml:space="preserve">151.986038208008</t>
   </si>
   <si>
     <t xml:space="preserve">150.919815063477</t>
   </si>
   <si>
-    <t xml:space="preserve">149.368942260742</t>
+    <t xml:space="preserve">149.368927001953</t>
   </si>
   <si>
     <t xml:space="preserve">146.267166137695</t>
@@ -3527,7 +3527,7 @@
     <t xml:space="preserve">148.690414428711</t>
   </si>
   <si>
-    <t xml:space="preserve">145.394821166992</t>
+    <t xml:space="preserve">145.394805908203</t>
   </si>
   <si>
     <t xml:space="preserve">146.751831054688</t>
@@ -3536,16 +3536,16 @@
     <t xml:space="preserve">149.659713745117</t>
   </si>
   <si>
-    <t xml:space="preserve">145.200958251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.517623901367</t>
+    <t xml:space="preserve">145.200942993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.517608642578</t>
   </si>
   <si>
     <t xml:space="preserve">141.323776245117</t>
   </si>
   <si>
-    <t xml:space="preserve">137.058837890625</t>
+    <t xml:space="preserve">137.058853149414</t>
   </si>
   <si>
     <t xml:space="preserve">134.538681030273</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">131.824630737305</t>
   </si>
   <si>
-    <t xml:space="preserve">136.186462402344</t>
+    <t xml:space="preserve">136.186477661133</t>
   </si>
   <si>
     <t xml:space="preserve">135.217178344727</t>
@@ -3566,7 +3566,7 @@
     <t xml:space="preserve">130.952270507812</t>
   </si>
   <si>
-    <t xml:space="preserve">127.753578186035</t>
+    <t xml:space="preserve">127.753593444824</t>
   </si>
   <si>
     <t xml:space="preserve">121.162338256836</t>
@@ -3578,13 +3578,13 @@
     <t xml:space="preserve">117.285148620605</t>
   </si>
   <si>
-    <t xml:space="preserve">114.958831787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.57593536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.12198638916</t>
+    <t xml:space="preserve">114.958824157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.575927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.121994018555</t>
   </si>
   <si>
     <t xml:space="preserve">119.708396911621</t>
@@ -3599,16 +3599,16 @@
     <t xml:space="preserve">115.443481445312</t>
   </si>
   <si>
-    <t xml:space="preserve">116.51692199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.003845214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.102432250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.712089538574</t>
+    <t xml:space="preserve">116.516914367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.003852844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.102424621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.71208190918</t>
   </si>
   <si>
     <t xml:space="preserve">120.713081359863</t>
@@ -3617,10 +3617,10 @@
     <t xml:space="preserve">124.909255981445</t>
   </si>
   <si>
-    <t xml:space="preserve">123.640640258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.834823608398</t>
+    <t xml:space="preserve">123.640647888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.834815979004</t>
   </si>
   <si>
     <t xml:space="preserve">120.225158691406</t>
@@ -3629,13 +3629,13 @@
     <t xml:space="preserve">119.346893310547</t>
   </si>
   <si>
-    <t xml:space="preserve">121.005851745605</t>
+    <t xml:space="preserve">121.005844116211</t>
   </si>
   <si>
     <t xml:space="preserve">114.857963562012</t>
   </si>
   <si>
-    <t xml:space="preserve">107.539054870605</t>
+    <t xml:space="preserve">107.5390625</t>
   </si>
   <si>
     <t xml:space="preserve">102.367042541504</t>
@@ -3644,46 +3644,46 @@
     <t xml:space="preserve">100.512916564941</t>
   </si>
   <si>
-    <t xml:space="preserve">101.586357116699</t>
+    <t xml:space="preserve">101.586349487305</t>
   </si>
   <si>
     <t xml:space="preserve">99.146728515625</t>
   </si>
   <si>
-    <t xml:space="preserve">103.147720336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.830825805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.07527923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.417335510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.319747924805</t>
+    <t xml:space="preserve">103.14771270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.83081817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.075286865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.417327880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.31974029541</t>
   </si>
   <si>
     <t xml:space="preserve">112.418327331543</t>
   </si>
   <si>
-    <t xml:space="preserve">113.296592712402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.541069030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.272445678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.90625</t>
+    <t xml:space="preserve">113.296600341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.541061401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.272453308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.906257629395</t>
   </si>
   <si>
     <t xml:space="preserve">113.882110595703</t>
   </si>
   <si>
-    <t xml:space="preserve">111.247299194336</t>
+    <t xml:space="preserve">111.247314453125</t>
   </si>
   <si>
     <t xml:space="preserve">110.661796569824</t>
@@ -3698,10 +3698,10 @@
     <t xml:space="preserve">120.615501403809</t>
   </si>
   <si>
-    <t xml:space="preserve">119.054130554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.956550598145</t>
+    <t xml:space="preserve">119.054138183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.956558227539</t>
   </si>
   <si>
     <t xml:space="preserve">113.101432800293</t>
@@ -3710,22 +3710,22 @@
     <t xml:space="preserve">116.907264709473</t>
   </si>
   <si>
-    <t xml:space="preserve">122.469627380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.323745727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.885108947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.006851196289</t>
+    <t xml:space="preserve">122.469619750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.323753356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.885116577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.006843566895</t>
   </si>
   <si>
     <t xml:space="preserve">122.664794921875</t>
   </si>
   <si>
-    <t xml:space="preserve">125.689949035645</t>
+    <t xml:space="preserve">125.68994140625</t>
   </si>
   <si>
     <t xml:space="preserve">124.616500854492</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">126.470626831055</t>
   </si>
   <si>
-    <t xml:space="preserve">122.957557678223</t>
+    <t xml:space="preserve">122.957550048828</t>
   </si>
   <si>
     <t xml:space="preserve">125.494773864746</t>
@@ -3755,16 +3755,16 @@
     <t xml:space="preserve">134.179870605469</t>
   </si>
   <si>
-    <t xml:space="preserve">127.544059753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126.177879333496</t>
+    <t xml:space="preserve">127.544067382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.177871704102</t>
   </si>
   <si>
     <t xml:space="preserve">121.201011657715</t>
   </si>
   <si>
-    <t xml:space="preserve">120.420333862305</t>
+    <t xml:space="preserve">120.42032623291</t>
   </si>
   <si>
     <t xml:space="preserve">119.151718139648</t>
@@ -3773,10 +3773,10 @@
     <t xml:space="preserve">122.176864624023</t>
   </si>
   <si>
-    <t xml:space="preserve">120.029983520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.736236572266</t>
+    <t xml:space="preserve">120.029991149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.736228942871</t>
   </si>
   <si>
     <t xml:space="preserve">114.955551147461</t>
@@ -3788,13 +3788,13 @@
     <t xml:space="preserve">115.05313873291</t>
   </si>
   <si>
-    <t xml:space="preserve">112.711082458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.686943054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.46662902832</t>
+    <t xml:space="preserve">112.711090087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.686935424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.466621398926</t>
   </si>
   <si>
     <t xml:space="preserve">117.590354919434</t>
@@ -3806,10 +3806,10 @@
     <t xml:space="preserve">111.832817077637</t>
   </si>
   <si>
-    <t xml:space="preserve">110.369041442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.977691650391</t>
+    <t xml:space="preserve">110.369033813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.977699279785</t>
   </si>
   <si>
     <t xml:space="preserve">106.953552246094</t>
@@ -3821,16 +3821,16 @@
     <t xml:space="preserve">103.928405761719</t>
   </si>
   <si>
-    <t xml:space="preserve">100.708084106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.391181945801</t>
+    <t xml:space="preserve">100.70809173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.391189575195</t>
   </si>
   <si>
     <t xml:space="preserve">104.904258728027</t>
   </si>
   <si>
-    <t xml:space="preserve">104.513916015625</t>
+    <t xml:space="preserve">104.51392364502</t>
   </si>
   <si>
     <t xml:space="preserve">101.196014404297</t>
@@ -3842,16 +3842,16 @@
     <t xml:space="preserve">107.734237670898</t>
   </si>
   <si>
-    <t xml:space="preserve">115.83381652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.150726318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.125579833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.75838470459</t>
+    <t xml:space="preserve">115.833824157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.150718688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.12557220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.758377075195</t>
   </si>
   <si>
     <t xml:space="preserve">103.440475463867</t>
@@ -3860,7 +3860,7 @@
     <t xml:space="preserve">106.270454406738</t>
   </si>
   <si>
-    <t xml:space="preserve">108.026985168457</t>
+    <t xml:space="preserve">108.026992797852</t>
   </si>
   <si>
     <t xml:space="preserve">109.100433349609</t>
@@ -3869,58 +3869,58 @@
     <t xml:space="preserve">108.514915466309</t>
   </si>
   <si>
-    <t xml:space="preserve">107.636650085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.978698730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.612503051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.441482543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.172866821289</t>
+    <t xml:space="preserve">107.636657714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.978691101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.612510681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.441474914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.172874450684</t>
   </si>
   <si>
     <t xml:space="preserve">108.905258178711</t>
   </si>
   <si>
-    <t xml:space="preserve">109.685943603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.320739746094</t>
+    <t xml:space="preserve">109.68595123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.320747375488</t>
   </si>
   <si>
     <t xml:space="preserve">122.274459838867</t>
   </si>
   <si>
-    <t xml:space="preserve">123.738227844238</t>
+    <t xml:space="preserve">123.738235473633</t>
   </si>
   <si>
     <t xml:space="preserve">116.028991699219</t>
   </si>
   <si>
-    <t xml:space="preserve">110.076293945312</t>
+    <t xml:space="preserve">110.076278686523</t>
   </si>
   <si>
     <t xml:space="preserve">107.929405212402</t>
   </si>
   <si>
-    <t xml:space="preserve">112.223152160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.783531188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.856971740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.588356018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.198013305664</t>
+    <t xml:space="preserve">112.223167419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.78352355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.856964111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.588363647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.198020935059</t>
   </si>
   <si>
     <t xml:space="preserve">110.759384155273</t>
@@ -3929,10 +3929,10 @@
     <t xml:space="preserve">117.200012207031</t>
   </si>
   <si>
-    <t xml:space="preserve">113.784523010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.587348937988</t>
+    <t xml:space="preserve">113.784530639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.587356567383</t>
   </si>
   <si>
     <t xml:space="preserve">107.831817626953</t>
@@ -3941,13 +3941,13 @@
     <t xml:space="preserve">105.19701385498</t>
   </si>
   <si>
-    <t xml:space="preserve">105.099433898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.221168518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.465614318848</t>
+    <t xml:space="preserve">105.099426269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.221160888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.465621948242</t>
   </si>
   <si>
     <t xml:space="preserve">104.41633605957</t>
@@ -3959,13 +3959,13 @@
     <t xml:space="preserve">107.343894958496</t>
   </si>
   <si>
-    <t xml:space="preserve">111.052146911621</t>
+    <t xml:space="preserve">111.052139282227</t>
   </si>
   <si>
     <t xml:space="preserve">114.467628479004</t>
   </si>
   <si>
-    <t xml:space="preserve">116.419334411621</t>
+    <t xml:space="preserve">116.419342041016</t>
   </si>
   <si>
     <t xml:space="preserve">117.883117675781</t>
@@ -3977,49 +3977,49 @@
     <t xml:space="preserve">115.931411743164</t>
   </si>
   <si>
-    <t xml:space="preserve">117.395179748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.273452758789</t>
+    <t xml:space="preserve">117.395195007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.273445129395</t>
   </si>
   <si>
     <t xml:space="preserve">114.760383605957</t>
   </si>
   <si>
-    <t xml:space="preserve">117.980690002441</t>
+    <t xml:space="preserve">117.98070526123</t>
   </si>
   <si>
     <t xml:space="preserve">123.933403015137</t>
   </si>
   <si>
-    <t xml:space="preserve">124.22615814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.152717590332</t>
+    <t xml:space="preserve">124.226165771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.152725219727</t>
   </si>
   <si>
     <t xml:space="preserve">121.493774414062</t>
   </si>
   <si>
-    <t xml:space="preserve">118.663787841797</t>
+    <t xml:space="preserve">118.663795471191</t>
   </si>
   <si>
     <t xml:space="preserve">119.6396484375</t>
   </si>
   <si>
-    <t xml:space="preserve">118.85897064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.37003326416</t>
+    <t xml:space="preserve">118.858963012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.370040893555</t>
   </si>
   <si>
     <t xml:space="preserve">112.515922546387</t>
   </si>
   <si>
-    <t xml:space="preserve">111.149719238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.199020385742</t>
+    <t xml:space="preserve">111.149726867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.199012756348</t>
   </si>
   <si>
     <t xml:space="preserve">111.540061950684</t>
@@ -4037,16 +4037,16 @@
     <t xml:space="preserve">112.027992248535</t>
   </si>
   <si>
-    <t xml:space="preserve">109.490776062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.148719787598</t>
+    <t xml:space="preserve">109.490768432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.148727416992</t>
   </si>
   <si>
     <t xml:space="preserve">113.58935546875</t>
   </si>
   <si>
-    <t xml:space="preserve">109.88111114502</t>
+    <t xml:space="preserve">109.881103515625</t>
   </si>
   <si>
     <t xml:space="preserve">107.051132202148</t>
@@ -4058,19 +4058,19 @@
     <t xml:space="preserve">102.562210083008</t>
   </si>
   <si>
-    <t xml:space="preserve">102.464622497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.683944702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.95255279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.781524658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.610504150391</t>
+    <t xml:space="preserve">102.464630126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.683937072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.952560424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.781532287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.610496520996</t>
   </si>
   <si>
     <t xml:space="preserve">103.342895507812</t>
@@ -4079,7 +4079,7 @@
     <t xml:space="preserve">101.000846862793</t>
   </si>
   <si>
-    <t xml:space="preserve">100.415328979492</t>
+    <t xml:space="preserve">100.415336608887</t>
   </si>
   <si>
     <t xml:space="preserve">102.074279785156</t>
@@ -4088,7 +4088,7 @@
     <t xml:space="preserve">103.040893554688</t>
   </si>
   <si>
-    <t xml:space="preserve">103.237922668457</t>
+    <t xml:space="preserve">103.237915039062</t>
   </si>
   <si>
     <t xml:space="preserve">99.3960494995117</t>
@@ -4115,7 +4115,7 @@
     <t xml:space="preserve">103.139404296875</t>
   </si>
   <si>
-    <t xml:space="preserve">102.449836730957</t>
+    <t xml:space="preserve">102.449844360352</t>
   </si>
   <si>
     <t xml:space="preserve">102.351333618164</t>
@@ -4142,7 +4142,7 @@
     <t xml:space="preserve">109.641036987305</t>
   </si>
   <si>
-    <t xml:space="preserve">106.39022064209</t>
+    <t xml:space="preserve">106.390213012695</t>
   </si>
   <si>
     <t xml:space="preserve">101.267730712891</t>
@@ -4154,7 +4154,7 @@
     <t xml:space="preserve">99.1005172729492</t>
   </si>
   <si>
-    <t xml:space="preserve">98.0661697387695</t>
+    <t xml:space="preserve">98.0661773681641</t>
   </si>
   <si>
     <t xml:space="preserve">100.479652404785</t>
@@ -4172,10 +4172,10 @@
     <t xml:space="preserve">106.685752868652</t>
   </si>
   <si>
-    <t xml:space="preserve">104.420028686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.957298278809</t>
+    <t xml:space="preserve">104.420036315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.957290649414</t>
   </si>
   <si>
     <t xml:space="preserve">101.858787536621</t>
@@ -4190,16 +4190,16 @@
     <t xml:space="preserve">103.631950378418</t>
   </si>
   <si>
-    <t xml:space="preserve">99.4945602416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.7064743041992</t>
+    <t xml:space="preserve">99.4945526123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.7064819335938</t>
   </si>
   <si>
     <t xml:space="preserve">97.2288360595703</t>
   </si>
   <si>
-    <t xml:space="preserve">98.26318359375</t>
+    <t xml:space="preserve">98.2631912231445</t>
   </si>
   <si>
     <t xml:space="preserve">98.164680480957</t>
@@ -4214,22 +4214,22 @@
     <t xml:space="preserve">97.1303329467773</t>
   </si>
   <si>
-    <t xml:space="preserve">94.5198211669922</t>
+    <t xml:space="preserve">94.5198287963867</t>
   </si>
   <si>
     <t xml:space="preserve">95.9974670410156</t>
   </si>
   <si>
-    <t xml:space="preserve">94.7661056518555</t>
+    <t xml:space="preserve">94.7660980224609</t>
   </si>
   <si>
     <t xml:space="preserve">94.4213180541992</t>
   </si>
   <si>
-    <t xml:space="preserve">93.7317581176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0421905517578</t>
+    <t xml:space="preserve">93.7317504882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0421829223633</t>
   </si>
   <si>
     <t xml:space="preserve">92.2048568725586</t>
@@ -4238,7 +4238,7 @@
     <t xml:space="preserve">92.8451690673828</t>
   </si>
   <si>
-    <t xml:space="preserve">91.1212539672852</t>
+    <t xml:space="preserve">91.1212463378906</t>
   </si>
   <si>
     <t xml:space="preserve">91.9093322753906</t>
@@ -4247,7 +4247,7 @@
     <t xml:space="preserve">91.0719909667969</t>
   </si>
   <si>
-    <t xml:space="preserve">86.8853454589844</t>
+    <t xml:space="preserve">86.8853378295898</t>
   </si>
   <si>
     <t xml:space="preserve">86.7868347167969</t>
@@ -4256,7 +4256,7 @@
     <t xml:space="preserve">86.0972747802734</t>
   </si>
   <si>
-    <t xml:space="preserve">86.4913101196289</t>
+    <t xml:space="preserve">86.4913177490234</t>
   </si>
   <si>
     <t xml:space="preserve">87.8211898803711</t>
@@ -4271,22 +4271,22 @@
     <t xml:space="preserve">91.7123107910156</t>
   </si>
   <si>
-    <t xml:space="preserve">91.6630630493164</t>
+    <t xml:space="preserve">91.6630554199219</t>
   </si>
   <si>
     <t xml:space="preserve">92.1556015014648</t>
   </si>
   <si>
-    <t xml:space="preserve">91.1705093383789</t>
+    <t xml:space="preserve">91.1705169677734</t>
   </si>
   <si>
     <t xml:space="preserve">90.3331756591797</t>
   </si>
   <si>
-    <t xml:space="preserve">88.6585235595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.0331039428711</t>
+    <t xml:space="preserve">88.6585159301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.0331115722656</t>
   </si>
   <si>
     <t xml:space="preserve">86.6883239746094</t>
@@ -4304,7 +4304,7 @@
     <t xml:space="preserve">87.4271469116211</t>
   </si>
   <si>
-    <t xml:space="preserve">86.9838562011719</t>
+    <t xml:space="preserve">86.9838638305664</t>
   </si>
   <si>
     <t xml:space="preserve">86.1465225219727</t>
@@ -4322,10 +4322,10 @@
     <t xml:space="preserve">81.1717987060547</t>
   </si>
   <si>
-    <t xml:space="preserve">84.9151611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.2255935668945</t>
+    <t xml:space="preserve">84.915153503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.2255859375</t>
   </si>
   <si>
     <t xml:space="preserve">87.7226791381836</t>
@@ -4334,19 +4334,19 @@
     <t xml:space="preserve">88.3137359619141</t>
   </si>
   <si>
-    <t xml:space="preserve">86.2942810058594</t>
+    <t xml:space="preserve">86.2942886352539</t>
   </si>
   <si>
     <t xml:space="preserve">88.2644805908203</t>
   </si>
   <si>
-    <t xml:space="preserve">87.6734161376953</t>
+    <t xml:space="preserve">87.6734237670898</t>
   </si>
   <si>
     <t xml:space="preserve">88.806282043457</t>
   </si>
   <si>
-    <t xml:space="preserve">89.003303527832</t>
+    <t xml:space="preserve">89.0032958984375</t>
   </si>
   <si>
     <t xml:space="preserve">92.1063461303711</t>
@@ -4355,7 +4355,7 @@
     <t xml:space="preserve">86.4420547485352</t>
   </si>
   <si>
-    <t xml:space="preserve">85.3584518432617</t>
+    <t xml:space="preserve">85.3584442138672</t>
   </si>
   <si>
     <t xml:space="preserve">83.3390045166016</t>
@@ -4370,13 +4370,13 @@
     <t xml:space="preserve">84.6688766479492</t>
   </si>
   <si>
-    <t xml:space="preserve">85.0136642456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.1763381958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.7823028564453</t>
+    <t xml:space="preserve">85.013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.1763305664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.7822952270508</t>
   </si>
   <si>
     <t xml:space="preserve">84.521125793457</t>
@@ -4388,10 +4388,10 @@
     <t xml:space="preserve">89.8898849487305</t>
   </si>
   <si>
-    <t xml:space="preserve">92.6481552124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3228073120117</t>
+    <t xml:space="preserve">92.6481475830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3228149414062</t>
   </si>
   <si>
     <t xml:space="preserve">92.3033676147461</t>
@@ -4409,13 +4409,13 @@
     <t xml:space="preserve">103.336433410645</t>
   </si>
   <si>
-    <t xml:space="preserve">101.661758422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.154312133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.71556854248</t>
+    <t xml:space="preserve">101.661766052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.154304504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.715560913086</t>
   </si>
   <si>
     <t xml:space="preserve">104.223014831543</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">102.942390441895</t>
   </si>
   <si>
-    <t xml:space="preserve">104.814071655273</t>
+    <t xml:space="preserve">104.814064025879</t>
   </si>
   <si>
     <t xml:space="preserve">105.602142333984</t>
@@ -4439,7 +4439,7 @@
     <t xml:space="preserve">105.306617736816</t>
   </si>
   <si>
-    <t xml:space="preserve">106.78426361084</t>
+    <t xml:space="preserve">106.784255981445</t>
   </si>
   <si>
     <t xml:space="preserve">108.557426452637</t>
@@ -4448,28 +4448,28 @@
     <t xml:space="preserve">108.951461791992</t>
   </si>
   <si>
-    <t xml:space="preserve">107.473815917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.778427124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.28588104248</t>
+    <t xml:space="preserve">107.473823547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.778434753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.285888671875</t>
   </si>
   <si>
     <t xml:space="preserve">111.808242797852</t>
   </si>
   <si>
-    <t xml:space="preserve">115.35457611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.029251098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.438179016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.521789550781</t>
+    <t xml:space="preserve">115.354583740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.029243469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.438186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.521797180176</t>
   </si>
   <si>
     <t xml:space="preserve">119.491981506348</t>
@@ -4484,7 +4484,7 @@
     <t xml:space="preserve">114.763519287109</t>
   </si>
   <si>
-    <t xml:space="preserve">112.30078125</t>
+    <t xml:space="preserve">112.300788879395</t>
   </si>
   <si>
     <t xml:space="preserve">112.596313476562</t>
@@ -4496,7 +4496,7 @@
     <t xml:space="preserve">115.847129821777</t>
   </si>
   <si>
-    <t xml:space="preserve">116.33967590332</t>
+    <t xml:space="preserve">116.339668273926</t>
   </si>
   <si>
     <t xml:space="preserve">118.112846374512</t>
@@ -4505,13 +4505,13 @@
     <t xml:space="preserve">119.886009216309</t>
   </si>
   <si>
-    <t xml:space="preserve">120.181541442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.787498474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.39347076416</t>
+    <t xml:space="preserve">120.181549072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.787506103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.393463134766</t>
   </si>
   <si>
     <t xml:space="preserve">121.757698059082</t>
@@ -4532,13 +4532,13 @@
     <t xml:space="preserve">125.10701751709</t>
   </si>
   <si>
-    <t xml:space="preserve">125.30403137207</t>
+    <t xml:space="preserve">125.304039001465</t>
   </si>
   <si>
     <t xml:space="preserve">125.599563598633</t>
   </si>
   <si>
-    <t xml:space="preserve">124.811485290527</t>
+    <t xml:space="preserve">124.811492919922</t>
   </si>
   <si>
     <t xml:space="preserve">125.008506774902</t>
@@ -4550,16 +4550,16 @@
     <t xml:space="preserve">126.584663391113</t>
   </si>
   <si>
-    <t xml:space="preserve">123.727882385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.796585083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.121925354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.462173461914</t>
+    <t xml:space="preserve">123.727890014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.796577453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.121917724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.46216583252</t>
   </si>
   <si>
     <t xml:space="preserve">120.280052185059</t>
@@ -4568,7 +4568,7 @@
     <t xml:space="preserve">121.659187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">120.575584411621</t>
+    <t xml:space="preserve">120.575576782227</t>
   </si>
   <si>
     <t xml:space="preserve">122.64427947998</t>
@@ -4577,7 +4577,7 @@
     <t xml:space="preserve">122.742790222168</t>
   </si>
   <si>
-    <t xml:space="preserve">125.205528259277</t>
+    <t xml:space="preserve">125.205520629883</t>
   </si>
   <si>
     <t xml:space="preserve">126.190628051758</t>
@@ -4592,10 +4592,10 @@
     <t xml:space="preserve">123.235336303711</t>
   </si>
   <si>
-    <t xml:space="preserve">124.515968322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.151741027832</t>
+    <t xml:space="preserve">124.515960693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.151733398438</t>
   </si>
   <si>
     <t xml:space="preserve">122.841300964355</t>
@@ -4610,10 +4610,10 @@
     <t xml:space="preserve">130.032501220703</t>
   </si>
   <si>
-    <t xml:space="preserve">130.820571899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.722061157227</t>
+    <t xml:space="preserve">130.820556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.722045898438</t>
   </si>
   <si>
     <t xml:space="preserve">129.835479736328</t>
@@ -4628,7 +4628,7 @@
     <t xml:space="preserve">127.569747924805</t>
   </si>
   <si>
-    <t xml:space="preserve">127.668266296387</t>
+    <t xml:space="preserve">127.668258666992</t>
   </si>
   <si>
     <t xml:space="preserve">129.244415283203</t>
@@ -4640,7 +4640,7 @@
     <t xml:space="preserve">130.131011962891</t>
   </si>
   <si>
-    <t xml:space="preserve">129.441436767578</t>
+    <t xml:space="preserve">129.441421508789</t>
   </si>
   <si>
     <t xml:space="preserve">126.486145019531</t>
@@ -4649,22 +4649,22 @@
     <t xml:space="preserve">128.16081237793</t>
   </si>
   <si>
-    <t xml:space="preserve">126.387641906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.909996032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.053230285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.265144348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.25023651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.166633605957</t>
+    <t xml:space="preserve">126.387649536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.910003662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.05322265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.265151977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.250244140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.166641235352</t>
   </si>
   <si>
     <t xml:space="preserve">133.677337646484</t>
@@ -4673,7 +4673,7 @@
     <t xml:space="preserve">131.116104125977</t>
   </si>
   <si>
-    <t xml:space="preserve">134.760955810547</t>
+    <t xml:space="preserve">134.760940551758</t>
   </si>
   <si>
     <t xml:space="preserve">135.058654785156</t>
@@ -4778,9 +4778,6 @@
     <t xml:space="preserve">134.860168457031</t>
   </si>
   <si>
-    <t xml:space="preserve">134.760940551758</t>
-  </si>
-  <si>
     <t xml:space="preserve">136.944107055664</t>
   </si>
   <si>
@@ -5472,6 +5469,9 @@
   </si>
   <si>
     <t xml:space="preserve">121.300003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121</t>
   </si>
 </sst>
 </file>
@@ -62404,7 +62404,7 @@
         <v>135.800003051758</v>
       </c>
       <c r="G2177" t="s">
-        <v>1588</v>
+        <v>1553</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -62430,7 +62430,7 @@
         <v>138</v>
       </c>
       <c r="G2178" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -62482,7 +62482,7 @@
         <v>135.800003051758</v>
       </c>
       <c r="G2180" t="s">
-        <v>1588</v>
+        <v>1553</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -62508,7 +62508,7 @@
         <v>132.699996948242</v>
       </c>
       <c r="G2181" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -62534,7 +62534,7 @@
         <v>133.100006103516</v>
       </c>
       <c r="G2182" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -62560,7 +62560,7 @@
         <v>131.800003051758</v>
       </c>
       <c r="G2183" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -62586,7 +62586,7 @@
         <v>131.800003051758</v>
       </c>
       <c r="G2184" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -62612,7 +62612,7 @@
         <v>131.199996948242</v>
       </c>
       <c r="G2185" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -62638,7 +62638,7 @@
         <v>129</v>
       </c>
       <c r="G2186" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -62664,7 +62664,7 @@
         <v>126.599998474121</v>
       </c>
       <c r="G2187" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -62690,7 +62690,7 @@
         <v>124.300003051758</v>
       </c>
       <c r="G2188" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -62716,7 +62716,7 @@
         <v>125.099998474121</v>
       </c>
       <c r="G2189" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -62742,7 +62742,7 @@
         <v>125.599998474121</v>
       </c>
       <c r="G2190" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -62768,7 +62768,7 @@
         <v>124.900001525879</v>
       </c>
       <c r="G2191" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -62794,7 +62794,7 @@
         <v>127.199996948242</v>
       </c>
       <c r="G2192" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -62846,7 +62846,7 @@
         <v>129.899993896484</v>
       </c>
       <c r="G2194" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -62872,7 +62872,7 @@
         <v>131.5</v>
       </c>
       <c r="G2195" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -62924,7 +62924,7 @@
         <v>135.300003051758</v>
       </c>
       <c r="G2197" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -62976,7 +62976,7 @@
         <v>138.699996948242</v>
       </c>
       <c r="G2199" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -63054,7 +63054,7 @@
         <v>140.899993896484</v>
       </c>
       <c r="G2202" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -63132,7 +63132,7 @@
         <v>141.800003051758</v>
       </c>
       <c r="G2205" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -63158,7 +63158,7 @@
         <v>142.699996948242</v>
       </c>
       <c r="G2206" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -63184,7 +63184,7 @@
         <v>141</v>
       </c>
       <c r="G2207" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -63210,7 +63210,7 @@
         <v>140.699996948242</v>
       </c>
       <c r="G2208" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -63288,7 +63288,7 @@
         <v>134</v>
       </c>
       <c r="G2211" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -63314,7 +63314,7 @@
         <v>134.899993896484</v>
       </c>
       <c r="G2212" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -63340,7 +63340,7 @@
         <v>135</v>
       </c>
       <c r="G2213" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -63366,7 +63366,7 @@
         <v>135.100006103516</v>
       </c>
       <c r="G2214" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -63444,7 +63444,7 @@
         <v>135.699996948242</v>
       </c>
       <c r="G2217" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -63470,7 +63470,7 @@
         <v>137.100006103516</v>
       </c>
       <c r="G2218" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -63496,7 +63496,7 @@
         <v>134.899993896484</v>
       </c>
       <c r="G2219" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -63522,7 +63522,7 @@
         <v>136.899993896484</v>
       </c>
       <c r="G2220" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -63548,7 +63548,7 @@
         <v>135.5</v>
       </c>
       <c r="G2221" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -63574,7 +63574,7 @@
         <v>135.800003051758</v>
       </c>
       <c r="G2222" t="s">
-        <v>1588</v>
+        <v>1553</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -63626,7 +63626,7 @@
         <v>134.800003051758</v>
       </c>
       <c r="G2224" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -63652,7 +63652,7 @@
         <v>136.699996948242</v>
       </c>
       <c r="G2225" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -63678,7 +63678,7 @@
         <v>136.800003051758</v>
       </c>
       <c r="G2226" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -63730,7 +63730,7 @@
         <v>132.899993896484</v>
       </c>
       <c r="G2228" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -63756,7 +63756,7 @@
         <v>134</v>
       </c>
       <c r="G2229" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -63782,7 +63782,7 @@
         <v>132</v>
       </c>
       <c r="G2230" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -63808,7 +63808,7 @@
         <v>132</v>
       </c>
       <c r="G2231" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -63834,7 +63834,7 @@
         <v>131.800003051758</v>
       </c>
       <c r="G2232" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -63860,7 +63860,7 @@
         <v>131.600006103516</v>
       </c>
       <c r="G2233" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -63886,7 +63886,7 @@
         <v>135.699996948242</v>
       </c>
       <c r="G2234" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -63964,7 +63964,7 @@
         <v>138.300003051758</v>
       </c>
       <c r="G2237" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -64016,7 +64016,7 @@
         <v>139.399993896484</v>
       </c>
       <c r="G2239" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -64042,7 +64042,7 @@
         <v>141</v>
       </c>
       <c r="G2240" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -64068,7 +64068,7 @@
         <v>143.100006103516</v>
       </c>
       <c r="G2241" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -64094,7 +64094,7 @@
         <v>142.100006103516</v>
       </c>
       <c r="G2242" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -64120,7 +64120,7 @@
         <v>143.399993896484</v>
       </c>
       <c r="G2243" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -64146,7 +64146,7 @@
         <v>143.199996948242</v>
       </c>
       <c r="G2244" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -64172,7 +64172,7 @@
         <v>147.300003051758</v>
       </c>
       <c r="G2245" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -64198,7 +64198,7 @@
         <v>143.300003051758</v>
       </c>
       <c r="G2246" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -64224,7 +64224,7 @@
         <v>144.600006103516</v>
       </c>
       <c r="G2247" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -64250,7 +64250,7 @@
         <v>142.899993896484</v>
       </c>
       <c r="G2248" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -64276,7 +64276,7 @@
         <v>143</v>
       </c>
       <c r="G2249" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -64302,7 +64302,7 @@
         <v>140.300003051758</v>
       </c>
       <c r="G2250" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -64328,7 +64328,7 @@
         <v>142</v>
       </c>
       <c r="G2251" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -64354,7 +64354,7 @@
         <v>139.100006103516</v>
       </c>
       <c r="G2252" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -64380,7 +64380,7 @@
         <v>139.300003051758</v>
       </c>
       <c r="G2253" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -64406,7 +64406,7 @@
         <v>136.899993896484</v>
       </c>
       <c r="G2254" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -64432,7 +64432,7 @@
         <v>140.5</v>
       </c>
       <c r="G2255" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -64458,7 +64458,7 @@
         <v>140.300003051758</v>
       </c>
       <c r="G2256" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -64484,7 +64484,7 @@
         <v>143.300003051758</v>
       </c>
       <c r="G2257" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -64510,7 +64510,7 @@
         <v>141.800003051758</v>
       </c>
       <c r="G2258" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -64562,7 +64562,7 @@
         <v>150.800003051758</v>
       </c>
       <c r="G2260" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -64588,7 +64588,7 @@
         <v>152.800003051758</v>
       </c>
       <c r="G2261" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -64614,7 +64614,7 @@
         <v>152.300003051758</v>
       </c>
       <c r="G2262" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -64640,7 +64640,7 @@
         <v>153.899993896484</v>
       </c>
       <c r="G2263" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -64666,7 +64666,7 @@
         <v>152.899993896484</v>
       </c>
       <c r="G2264" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -64692,7 +64692,7 @@
         <v>154.600006103516</v>
       </c>
       <c r="G2265" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -64718,7 +64718,7 @@
         <v>149.899993896484</v>
       </c>
       <c r="G2266" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -64744,7 +64744,7 @@
         <v>153.399993896484</v>
       </c>
       <c r="G2267" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -64770,7 +64770,7 @@
         <v>152.300003051758</v>
       </c>
       <c r="G2268" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -64796,7 +64796,7 @@
         <v>150.399993896484</v>
       </c>
       <c r="G2269" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -64822,7 +64822,7 @@
         <v>150.899993896484</v>
       </c>
       <c r="G2270" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -64848,7 +64848,7 @@
         <v>151.5</v>
       </c>
       <c r="G2271" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -64874,7 +64874,7 @@
         <v>151.5</v>
       </c>
       <c r="G2272" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -64900,7 +64900,7 @@
         <v>152.699996948242</v>
       </c>
       <c r="G2273" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -64926,7 +64926,7 @@
         <v>157.100006103516</v>
       </c>
       <c r="G2274" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -64952,7 +64952,7 @@
         <v>155.5</v>
       </c>
       <c r="G2275" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -64978,7 +64978,7 @@
         <v>156.899993896484</v>
       </c>
       <c r="G2276" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -65004,7 +65004,7 @@
         <v>154.199996948242</v>
       </c>
       <c r="G2277" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -65030,7 +65030,7 @@
         <v>154.899993896484</v>
       </c>
       <c r="G2278" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -65056,7 +65056,7 @@
         <v>157.800003051758</v>
       </c>
       <c r="G2279" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -65082,7 +65082,7 @@
         <v>155</v>
       </c>
       <c r="G2280" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -65108,7 +65108,7 @@
         <v>156</v>
       </c>
       <c r="G2281" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -65134,7 +65134,7 @@
         <v>155.600006103516</v>
       </c>
       <c r="G2282" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -65160,7 +65160,7 @@
         <v>156.800003051758</v>
       </c>
       <c r="G2283" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -65186,7 +65186,7 @@
         <v>156.399993896484</v>
       </c>
       <c r="G2284" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -65212,7 +65212,7 @@
         <v>152.300003051758</v>
       </c>
       <c r="G2285" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -65238,7 +65238,7 @@
         <v>155</v>
       </c>
       <c r="G2286" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -65264,7 +65264,7 @@
         <v>153.600006103516</v>
       </c>
       <c r="G2287" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -65290,7 +65290,7 @@
         <v>155.5</v>
       </c>
       <c r="G2288" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -65316,7 +65316,7 @@
         <v>153.399993896484</v>
       </c>
       <c r="G2289" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -65342,7 +65342,7 @@
         <v>155.800003051758</v>
       </c>
       <c r="G2290" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -65368,7 +65368,7 @@
         <v>154.800003051758</v>
       </c>
       <c r="G2291" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -65394,7 +65394,7 @@
         <v>157.600006103516</v>
       </c>
       <c r="G2292" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -65420,7 +65420,7 @@
         <v>157.800003051758</v>
       </c>
       <c r="G2293" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -65446,7 +65446,7 @@
         <v>152.199996948242</v>
       </c>
       <c r="G2294" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -65472,7 +65472,7 @@
         <v>149.5</v>
       </c>
       <c r="G2295" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -65498,7 +65498,7 @@
         <v>148.100006103516</v>
       </c>
       <c r="G2296" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -65524,7 +65524,7 @@
         <v>146.199996948242</v>
       </c>
       <c r="G2297" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -65550,7 +65550,7 @@
         <v>144.800003051758</v>
       </c>
       <c r="G2298" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -65576,7 +65576,7 @@
         <v>149.699996948242</v>
       </c>
       <c r="G2299" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -65602,7 +65602,7 @@
         <v>151</v>
       </c>
       <c r="G2300" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -65628,7 +65628,7 @@
         <v>150.5</v>
       </c>
       <c r="G2301" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -65654,7 +65654,7 @@
         <v>151.600006103516</v>
       </c>
       <c r="G2302" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -65680,7 +65680,7 @@
         <v>152.600006103516</v>
       </c>
       <c r="G2303" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -65706,7 +65706,7 @@
         <v>155.600006103516</v>
       </c>
       <c r="G2304" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -65732,7 +65732,7 @@
         <v>153.699996948242</v>
       </c>
       <c r="G2305" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -65758,7 +65758,7 @@
         <v>155.899993896484</v>
       </c>
       <c r="G2306" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -65784,7 +65784,7 @@
         <v>153.699996948242</v>
       </c>
       <c r="G2307" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -65810,7 +65810,7 @@
         <v>156.300003051758</v>
       </c>
       <c r="G2308" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -65836,7 +65836,7 @@
         <v>157.699996948242</v>
       </c>
       <c r="G2309" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -65862,7 +65862,7 @@
         <v>157.199996948242</v>
       </c>
       <c r="G2310" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -65888,7 +65888,7 @@
         <v>159.600006103516</v>
       </c>
       <c r="G2311" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -65914,7 +65914,7 @@
         <v>158.100006103516</v>
       </c>
       <c r="G2312" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -65940,7 +65940,7 @@
         <v>158</v>
       </c>
       <c r="G2313" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -65966,7 +65966,7 @@
         <v>158.199996948242</v>
       </c>
       <c r="G2314" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -65992,7 +65992,7 @@
         <v>161.399993896484</v>
       </c>
       <c r="G2315" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -66018,7 +66018,7 @@
         <v>159.800003051758</v>
       </c>
       <c r="G2316" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -66044,7 +66044,7 @@
         <v>160.100006103516</v>
       </c>
       <c r="G2317" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -66070,7 +66070,7 @@
         <v>159.800003051758</v>
       </c>
       <c r="G2318" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -66096,7 +66096,7 @@
         <v>161.300003051758</v>
       </c>
       <c r="G2319" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -66122,7 +66122,7 @@
         <v>164.100006103516</v>
       </c>
       <c r="G2320" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -66148,7 +66148,7 @@
         <v>163.699996948242</v>
       </c>
       <c r="G2321" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -66174,7 +66174,7 @@
         <v>165.300003051758</v>
       </c>
       <c r="G2322" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -66200,7 +66200,7 @@
         <v>164.399993896484</v>
       </c>
       <c r="G2323" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -66226,7 +66226,7 @@
         <v>159.600006103516</v>
       </c>
       <c r="G2324" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -66252,7 +66252,7 @@
         <v>158.399993896484</v>
       </c>
       <c r="G2325" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -66278,7 +66278,7 @@
         <v>159.699996948242</v>
       </c>
       <c r="G2326" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -66304,7 +66304,7 @@
         <v>158</v>
       </c>
       <c r="G2327" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -66330,7 +66330,7 @@
         <v>157.899993896484</v>
       </c>
       <c r="G2328" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -66356,7 +66356,7 @@
         <v>157.5</v>
       </c>
       <c r="G2329" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -66382,7 +66382,7 @@
         <v>156.699996948242</v>
       </c>
       <c r="G2330" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -66408,7 +66408,7 @@
         <v>154.199996948242</v>
       </c>
       <c r="G2331" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -66434,7 +66434,7 @@
         <v>154.800003051758</v>
       </c>
       <c r="G2332" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -66460,7 +66460,7 @@
         <v>150</v>
       </c>
       <c r="G2333" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -66486,7 +66486,7 @@
         <v>153.5</v>
       </c>
       <c r="G2334" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -66512,7 +66512,7 @@
         <v>153.899993896484</v>
       </c>
       <c r="G2335" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -66538,7 +66538,7 @@
         <v>153.800003051758</v>
       </c>
       <c r="G2336" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -66564,7 +66564,7 @@
         <v>153.300003051758</v>
       </c>
       <c r="G2337" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -66590,7 +66590,7 @@
         <v>146.199996948242</v>
       </c>
       <c r="G2338" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -66616,7 +66616,7 @@
         <v>149.100006103516</v>
       </c>
       <c r="G2339" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -66642,7 +66642,7 @@
         <v>157.199996948242</v>
       </c>
       <c r="G2340" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -66668,7 +66668,7 @@
         <v>164</v>
       </c>
       <c r="G2341" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -66694,7 +66694,7 @@
         <v>164.100006103516</v>
       </c>
       <c r="G2342" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -66720,7 +66720,7 @@
         <v>165.399993896484</v>
       </c>
       <c r="G2343" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -66746,7 +66746,7 @@
         <v>167.5</v>
       </c>
       <c r="G2344" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -66772,7 +66772,7 @@
         <v>164.699996948242</v>
       </c>
       <c r="G2345" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -66798,7 +66798,7 @@
         <v>163.100006103516</v>
       </c>
       <c r="G2346" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -66824,7 +66824,7 @@
         <v>162.699996948242</v>
       </c>
       <c r="G2347" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -66850,7 +66850,7 @@
         <v>163.699996948242</v>
       </c>
       <c r="G2348" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -66876,7 +66876,7 @@
         <v>160.600006103516</v>
       </c>
       <c r="G2349" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -66902,7 +66902,7 @@
         <v>159.5</v>
       </c>
       <c r="G2350" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -66928,7 +66928,7 @@
         <v>156.600006103516</v>
       </c>
       <c r="G2351" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -66954,7 +66954,7 @@
         <v>150.800003051758</v>
       </c>
       <c r="G2352" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -66980,7 +66980,7 @@
         <v>153</v>
       </c>
       <c r="G2353" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -67006,7 +67006,7 @@
         <v>152.899993896484</v>
       </c>
       <c r="G2354" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -67032,7 +67032,7 @@
         <v>147.600006103516</v>
       </c>
       <c r="G2355" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -67058,7 +67058,7 @@
         <v>143.800003051758</v>
       </c>
       <c r="G2356" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -67110,7 +67110,7 @@
         <v>141.800003051758</v>
       </c>
       <c r="G2358" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -67136,7 +67136,7 @@
         <v>135.5</v>
       </c>
       <c r="G2359" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -67162,7 +67162,7 @@
         <v>142.899993896484</v>
       </c>
       <c r="G2360" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -67188,7 +67188,7 @@
         <v>143.800003051758</v>
       </c>
       <c r="G2361" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -67214,7 +67214,7 @@
         <v>146.899993896484</v>
       </c>
       <c r="G2362" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -67240,7 +67240,7 @@
         <v>149</v>
       </c>
       <c r="G2363" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -67266,7 +67266,7 @@
         <v>149.699996948242</v>
       </c>
       <c r="G2364" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -67292,7 +67292,7 @@
         <v>148.899993896484</v>
       </c>
       <c r="G2365" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -67318,7 +67318,7 @@
         <v>147.399993896484</v>
       </c>
       <c r="G2366" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -67344,7 +67344,7 @@
         <v>150.800003051758</v>
       </c>
       <c r="G2367" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -67370,7 +67370,7 @@
         <v>149.399993896484</v>
       </c>
       <c r="G2368" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -67396,7 +67396,7 @@
         <v>149.399993896484</v>
       </c>
       <c r="G2369" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -67422,7 +67422,7 @@
         <v>151.899993896484</v>
       </c>
       <c r="G2370" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -67448,7 +67448,7 @@
         <v>153.600006103516</v>
       </c>
       <c r="G2371" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -67474,7 +67474,7 @@
         <v>156.800003051758</v>
       </c>
       <c r="G2372" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -67500,7 +67500,7 @@
         <v>158.699996948242</v>
       </c>
       <c r="G2373" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -67526,7 +67526,7 @@
         <v>157.699996948242</v>
       </c>
       <c r="G2374" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -67552,7 +67552,7 @@
         <v>158.899993896484</v>
       </c>
       <c r="G2375" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -67578,7 +67578,7 @@
         <v>156.399993896484</v>
       </c>
       <c r="G2376" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -67604,7 +67604,7 @@
         <v>159.600006103516</v>
       </c>
       <c r="G2377" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -67630,7 +67630,7 @@
         <v>161.600006103516</v>
       </c>
       <c r="G2378" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -67656,7 +67656,7 @@
         <v>157.600006103516</v>
       </c>
       <c r="G2379" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -67682,7 +67682,7 @@
         <v>154.100006103516</v>
       </c>
       <c r="G2380" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -67708,7 +67708,7 @@
         <v>150.699996948242</v>
       </c>
       <c r="G2381" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -67734,7 +67734,7 @@
         <v>150.600006103516</v>
       </c>
       <c r="G2382" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -67760,7 +67760,7 @@
         <v>150.300003051758</v>
       </c>
       <c r="G2383" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -67786,7 +67786,7 @@
         <v>147.5</v>
       </c>
       <c r="G2384" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -67812,7 +67812,7 @@
         <v>147.100006103516</v>
       </c>
       <c r="G2385" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -67838,7 +67838,7 @@
         <v>147</v>
       </c>
       <c r="G2386" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -67864,7 +67864,7 @@
         <v>144.5</v>
       </c>
       <c r="G2387" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -67890,7 +67890,7 @@
         <v>142.899993896484</v>
       </c>
       <c r="G2388" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -67916,7 +67916,7 @@
         <v>146.5</v>
       </c>
       <c r="G2389" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -67942,7 +67942,7 @@
         <v>145.300003051758</v>
       </c>
       <c r="G2390" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -67968,7 +67968,7 @@
         <v>148.199996948242</v>
       </c>
       <c r="G2391" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -67994,7 +67994,7 @@
         <v>147</v>
       </c>
       <c r="G2392" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -68020,7 +68020,7 @@
         <v>148.5</v>
       </c>
       <c r="G2393" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -68046,7 +68046,7 @@
         <v>146.100006103516</v>
       </c>
       <c r="G2394" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -68072,7 +68072,7 @@
         <v>146.5</v>
       </c>
       <c r="G2395" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -68098,7 +68098,7 @@
         <v>148.399993896484</v>
       </c>
       <c r="G2396" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -68124,7 +68124,7 @@
         <v>150.399993896484</v>
       </c>
       <c r="G2397" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -68150,7 +68150,7 @@
         <v>149.100006103516</v>
       </c>
       <c r="G2398" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -68176,7 +68176,7 @@
         <v>149.300003051758</v>
       </c>
       <c r="G2399" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -68202,7 +68202,7 @@
         <v>151.600006103516</v>
       </c>
       <c r="G2400" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -68228,7 +68228,7 @@
         <v>151.899993896484</v>
       </c>
       <c r="G2401" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -68254,7 +68254,7 @@
         <v>148.800003051758</v>
       </c>
       <c r="G2402" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -68280,7 +68280,7 @@
         <v>145.100006103516</v>
       </c>
       <c r="G2403" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -68306,7 +68306,7 @@
         <v>145.600006103516</v>
       </c>
       <c r="G2404" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -68332,7 +68332,7 @@
         <v>144.800003051758</v>
       </c>
       <c r="G2405" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -68358,7 +68358,7 @@
         <v>145.800003051758</v>
       </c>
       <c r="G2406" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -68384,7 +68384,7 @@
         <v>142.899993896484</v>
       </c>
       <c r="G2407" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -68410,7 +68410,7 @@
         <v>142.5</v>
       </c>
       <c r="G2408" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -68436,7 +68436,7 @@
         <v>142.100006103516</v>
       </c>
       <c r="G2409" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -68462,7 +68462,7 @@
         <v>142.600006103516</v>
       </c>
       <c r="G2410" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -68488,7 +68488,7 @@
         <v>141.899993896484</v>
       </c>
       <c r="G2411" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -68514,7 +68514,7 @@
         <v>143.100006103516</v>
       </c>
       <c r="G2412" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -68540,7 +68540,7 @@
         <v>143.699996948242</v>
       </c>
       <c r="G2413" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -68566,7 +68566,7 @@
         <v>146.600006103516</v>
       </c>
       <c r="G2414" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -68592,7 +68592,7 @@
         <v>145.5</v>
       </c>
       <c r="G2415" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -68618,7 +68618,7 @@
         <v>142.100006103516</v>
       </c>
       <c r="G2416" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -68644,7 +68644,7 @@
         <v>143.5</v>
       </c>
       <c r="G2417" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -68670,7 +68670,7 @@
         <v>141.5</v>
       </c>
       <c r="G2418" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -68696,7 +68696,7 @@
         <v>141.5</v>
       </c>
       <c r="G2419" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -68722,7 +68722,7 @@
         <v>145.300003051758</v>
       </c>
       <c r="G2420" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -68748,7 +68748,7 @@
         <v>144.399993896484</v>
       </c>
       <c r="G2421" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -68774,7 +68774,7 @@
         <v>144.600006103516</v>
       </c>
       <c r="G2422" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -68800,7 +68800,7 @@
         <v>142.600006103516</v>
       </c>
       <c r="G2423" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -68826,7 +68826,7 @@
         <v>140.800003051758</v>
       </c>
       <c r="G2424" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -68852,7 +68852,7 @@
         <v>142.5</v>
       </c>
       <c r="G2425" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -68878,7 +68878,7 @@
         <v>140.800003051758</v>
       </c>
       <c r="G2426" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -68904,7 +68904,7 @@
         <v>143.399993896484</v>
       </c>
       <c r="G2427" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -68930,7 +68930,7 @@
         <v>142</v>
       </c>
       <c r="G2428" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -68956,7 +68956,7 @@
         <v>140.899993896484</v>
       </c>
       <c r="G2429" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -68982,7 +68982,7 @@
         <v>139.100006103516</v>
       </c>
       <c r="G2430" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -69008,7 +69008,7 @@
         <v>139</v>
       </c>
       <c r="G2431" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -69034,7 +69034,7 @@
         <v>136.899993896484</v>
       </c>
       <c r="G2432" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -69060,7 +69060,7 @@
         <v>136.800003051758</v>
       </c>
       <c r="G2433" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -69086,7 +69086,7 @@
         <v>139.899993896484</v>
       </c>
       <c r="G2434" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -69112,7 +69112,7 @@
         <v>138.300003051758</v>
       </c>
       <c r="G2435" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -69138,7 +69138,7 @@
         <v>137.399993896484</v>
       </c>
       <c r="G2436" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -69164,7 +69164,7 @@
         <v>137.600006103516</v>
       </c>
       <c r="G2437" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -69190,7 +69190,7 @@
         <v>131.699996948242</v>
       </c>
       <c r="G2438" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -69216,7 +69216,7 @@
         <v>131.600006103516</v>
       </c>
       <c r="G2439" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -69242,7 +69242,7 @@
         <v>133.199996948242</v>
       </c>
       <c r="G2440" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -69268,7 +69268,7 @@
         <v>128.199996948242</v>
       </c>
       <c r="G2441" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -69294,7 +69294,7 @@
         <v>128</v>
       </c>
       <c r="G2442" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -69320,7 +69320,7 @@
         <v>128.600006103516</v>
       </c>
       <c r="G2443" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -69346,7 +69346,7 @@
         <v>127</v>
       </c>
       <c r="G2444" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -69372,7 +69372,7 @@
         <v>122.5</v>
       </c>
       <c r="G2445" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -69398,7 +69398,7 @@
         <v>122.300003051758</v>
       </c>
       <c r="G2446" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -69424,7 +69424,7 @@
         <v>121.599998474121</v>
       </c>
       <c r="G2447" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -69450,7 +69450,7 @@
         <v>123</v>
       </c>
       <c r="G2448" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -69476,7 +69476,7 @@
         <v>125.599998474121</v>
       </c>
       <c r="G2449" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -69502,7 +69502,7 @@
         <v>123.300003051758</v>
       </c>
       <c r="G2450" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -69528,7 +69528,7 @@
         <v>121.800003051758</v>
       </c>
       <c r="G2451" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -69554,7 +69554,7 @@
         <v>122.699996948242</v>
       </c>
       <c r="G2452" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -69580,7 +69580,7 @@
         <v>124</v>
       </c>
       <c r="G2453" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -69606,7 +69606,7 @@
         <v>122.900001525879</v>
       </c>
       <c r="G2454" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -69632,7 +69632,7 @@
         <v>123.800003051758</v>
       </c>
       <c r="G2455" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -69658,7 +69658,7 @@
         <v>124.300003051758</v>
       </c>
       <c r="G2456" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -69684,7 +69684,7 @@
         <v>123.099998474121</v>
       </c>
       <c r="G2457" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -69710,7 +69710,7 @@
         <v>123</v>
       </c>
       <c r="G2458" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -69736,7 +69736,7 @@
         <v>119</v>
       </c>
       <c r="G2459" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -69762,7 +69762,7 @@
         <v>119</v>
       </c>
       <c r="G2460" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -69788,7 +69788,7 @@
         <v>119.099998474121</v>
       </c>
       <c r="G2461" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -69814,7 +69814,7 @@
         <v>119.699996948242</v>
       </c>
       <c r="G2462" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -69840,7 +69840,7 @@
         <v>120</v>
       </c>
       <c r="G2463" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -69866,7 +69866,7 @@
         <v>119.900001525879</v>
       </c>
       <c r="G2464" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -69892,7 +69892,7 @@
         <v>115.300003051758</v>
       </c>
       <c r="G2465" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -69918,7 +69918,7 @@
         <v>115.099998474121</v>
       </c>
       <c r="G2466" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -69944,7 +69944,7 @@
         <v>116.5</v>
       </c>
       <c r="G2467" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -69970,7 +69970,7 @@
         <v>117.199996948242</v>
       </c>
       <c r="G2468" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -69996,7 +69996,7 @@
         <v>117.5</v>
       </c>
       <c r="G2469" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -70022,7 +70022,7 @@
         <v>120.400001525879</v>
       </c>
       <c r="G2470" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -70048,7 +70048,7 @@
         <v>123.199996948242</v>
       </c>
       <c r="G2471" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -70074,7 +70074,7 @@
         <v>121.900001525879</v>
       </c>
       <c r="G2472" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -70100,7 +70100,7 @@
         <v>121.800003051758</v>
       </c>
       <c r="G2473" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -70126,7 +70126,7 @@
         <v>122.699996948242</v>
       </c>
       <c r="G2474" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -70152,7 +70152,7 @@
         <v>122.599998474121</v>
       </c>
       <c r="G2475" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -70178,7 +70178,7 @@
         <v>120.300003051758</v>
       </c>
       <c r="G2476" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -70204,7 +70204,7 @@
         <v>118.300003051758</v>
       </c>
       <c r="G2477" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -70230,7 +70230,7 @@
         <v>120.699996948242</v>
       </c>
       <c r="G2478" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -70256,7 +70256,7 @@
         <v>121.199996948242</v>
       </c>
       <c r="G2479" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -70282,7 +70282,7 @@
         <v>121.199996948242</v>
       </c>
       <c r="G2480" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -70308,7 +70308,7 @@
         <v>124</v>
       </c>
       <c r="G2481" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -70334,7 +70334,7 @@
         <v>123</v>
       </c>
       <c r="G2482" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -70360,7 +70360,7 @@
         <v>123</v>
       </c>
       <c r="G2483" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -70386,7 +70386,7 @@
         <v>123.699996948242</v>
       </c>
       <c r="G2484" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -70412,7 +70412,7 @@
         <v>123.5</v>
       </c>
       <c r="G2485" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -70438,7 +70438,7 @@
         <v>123.300003051758</v>
       </c>
       <c r="G2486" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -70464,7 +70464,7 @@
         <v>121.800003051758</v>
       </c>
       <c r="G2487" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -70490,7 +70490,7 @@
         <v>120.400001525879</v>
       </c>
       <c r="G2488" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -70516,7 +70516,7 @@
         <v>118.300003051758</v>
       </c>
       <c r="G2489" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -70542,7 +70542,7 @@
         <v>118.900001525879</v>
       </c>
       <c r="G2490" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -70568,7 +70568,7 @@
         <v>118.300003051758</v>
       </c>
       <c r="G2491" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -70594,7 +70594,7 @@
         <v>118.099998474121</v>
       </c>
       <c r="G2492" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -70620,7 +70620,7 @@
         <v>118.5</v>
       </c>
       <c r="G2493" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -70646,7 +70646,7 @@
         <v>121.099998474121</v>
       </c>
       <c r="G2494" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -70672,7 +70672,7 @@
         <v>120.199996948242</v>
       </c>
       <c r="G2495" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -70698,7 +70698,7 @@
         <v>120.400001525879</v>
       </c>
       <c r="G2496" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -70724,7 +70724,7 @@
         <v>121.300003051758</v>
       </c>
       <c r="G2497" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -70750,7 +70750,7 @@
         <v>120.300003051758</v>
       </c>
       <c r="G2498" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -70758,7 +70758,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.6910532407</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>128127</v>
@@ -70776,9 +70776,35 @@
         <v>123.099998474121</v>
       </c>
       <c r="G2499" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.6928009259</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>51120</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>123.199996948242</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>120.599998474121</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>122.800003051758</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>121</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>1819</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/REY.MI.xlsx
+++ b/data/REY.MI.xlsx
@@ -38,112 +38,112 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2559700012207</t>
+    <t xml:space="preserve">29.2559719085693</t>
   </si>
   <si>
     <t xml:space="preserve">REY.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8380279541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3272094726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6306419372559</t>
+    <t xml:space="preserve">28.8380298614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3272075653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6306400299072</t>
   </si>
   <si>
     <t xml:space="preserve">27.8396091461182</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2111167907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.000560760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5594024658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1414604187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1198177337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9789257049561</t>
+    <t xml:space="preserve">28.2111148834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0005626678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5594005584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1414566040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1198196411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9789237976074</t>
   </si>
   <si>
     <t xml:space="preserve">26.8644104003906</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4448852539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9324836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8163948059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2807750701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.677074432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0950222015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8628311157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2591342926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7018795013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.167839050293</t>
+    <t xml:space="preserve">27.4448833465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.932487487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8163909912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2807731628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6770801544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0950183868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8628330230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2591361999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7018775939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1678409576416</t>
   </si>
   <si>
     <t xml:space="preserve">25.2855186462402</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3799743652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6121673583984</t>
+    <t xml:space="preserve">24.379976272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6121654510498</t>
   </si>
   <si>
     <t xml:space="preserve">26.0053062438965</t>
   </si>
   <si>
-    <t xml:space="preserve">25.517707824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6570224761963</t>
+    <t xml:space="preserve">25.5177097320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6570243835449</t>
   </si>
   <si>
     <t xml:space="preserve">27.6074199676514</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3071575164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0733852386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2142810821533</t>
+    <t xml:space="preserve">26.3071537017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0733833312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2142791748047</t>
   </si>
   <si>
     <t xml:space="preserve">26.4696865081787</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0517444610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7034587860107</t>
+    <t xml:space="preserve">26.0517463684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7034568786621</t>
   </si>
   <si>
     <t xml:space="preserve">25.7266826629639</t>
@@ -155,34 +155,34 @@
     <t xml:space="preserve">26.4929084777832</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3520107269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1894779205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2359161376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.166259765625</t>
+    <t xml:space="preserve">27.3520126342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1894760131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2359142303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1662616729736</t>
   </si>
   <si>
     <t xml:space="preserve">27.9092693328857</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0237808227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5546569824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3008289337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4169216156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9989776611328</t>
+    <t xml:space="preserve">29.0237827301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5546493530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3008308410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.416919708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9989795684814</t>
   </si>
   <si>
     <t xml:space="preserve">29.9757633209229</t>
@@ -191,28 +191,28 @@
     <t xml:space="preserve">29.7900104522705</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9525394439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2311687469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7203521728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0686378479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8596687316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5578212738037</t>
+    <t xml:space="preserve">29.952543258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2311668395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7203502655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0686359405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8596668243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5578193664551</t>
   </si>
   <si>
     <t xml:space="preserve">29.3256301879883</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4881649017334</t>
+    <t xml:space="preserve">29.4881610870361</t>
   </si>
   <si>
     <t xml:space="preserve">29.5113792419434</t>
@@ -221,34 +221,34 @@
     <t xml:space="preserve">29.2095336914062</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1615104675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3720664978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5345973968506</t>
+    <t xml:space="preserve">30.1615161895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3720684051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5345993041992</t>
   </si>
   <si>
     <t xml:space="preserve">28.4433059692383</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6754970550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8612480163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8148097991943</t>
+    <t xml:space="preserve">28.6754951477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8612499237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8148078918457</t>
   </si>
   <si>
     <t xml:space="preserve">28.9076843261719</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6290588378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4200820922852</t>
+    <t xml:space="preserve">28.6290607452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4200878143311</t>
   </si>
   <si>
     <t xml:space="preserve">28.6775989532471</t>
@@ -260,100 +260,100 @@
     <t xml:space="preserve">29.0287532806396</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3264446258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5137271881104</t>
+    <t xml:space="preserve">28.3264427185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.513729095459</t>
   </si>
   <si>
     <t xml:space="preserve">28.7946510314941</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0053462982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2628555297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1992664337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5036010742188</t>
+    <t xml:space="preserve">29.0053424835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2628574371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1992683410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5036029815674</t>
   </si>
   <si>
     <t xml:space="preserve">30.5504245758057</t>
   </si>
   <si>
-    <t xml:space="preserve">30.901575088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6674766540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7142925262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4567832946777</t>
+    <t xml:space="preserve">30.9015808105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6674709320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7142944335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4567794799805</t>
   </si>
   <si>
     <t xml:space="preserve">30.4333724975586</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2694988250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8949337005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1859874725342</t>
+    <t xml:space="preserve">30.2695007324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8949317932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1859817504883</t>
   </si>
   <si>
     <t xml:space="preserve">29.3096771240234</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4969596862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6943702697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7747211456299</t>
+    <t xml:space="preserve">29.4969615936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6943664550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7747230529785</t>
   </si>
   <si>
     <t xml:space="preserve">26.8047771453857</t>
   </si>
   <si>
-    <t xml:space="preserve">27.319803237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9218292236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5070838928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.945240020752</t>
+    <t xml:space="preserve">27.3198051452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9218273162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5070858001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9452381134033</t>
   </si>
   <si>
     <t xml:space="preserve">25.8215465545654</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2195205688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1091117858887</t>
+    <t xml:space="preserve">26.219518661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1091079711914</t>
   </si>
   <si>
     <t xml:space="preserve">27.624137878418</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3666229248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.303035736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8882904052734</t>
+    <t xml:space="preserve">27.3666248321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3030338287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8882923126221</t>
   </si>
   <si>
     <t xml:space="preserve">28.7478313446045</t>
@@ -365,55 +365,55 @@
     <t xml:space="preserve">28.98193359375</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9117069244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3799095153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4501419067383</t>
+    <t xml:space="preserve">28.9117031097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3799057006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4501399993896</t>
   </si>
   <si>
     <t xml:space="preserve">29.8481140136719</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1524467468262</t>
+    <t xml:space="preserve">30.1524486541748</t>
   </si>
   <si>
     <t xml:space="preserve">29.9651641845703</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7244186401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1458072662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0989856719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9351119995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4903182983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9752902984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3732662200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.092342376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2729816436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.062292098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0388813018799</t>
+    <t xml:space="preserve">28.724422454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1458053588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0989875793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9351100921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4903163909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9752960205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3732643127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0923461914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.272985458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0622901916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0388774871826</t>
   </si>
   <si>
     <t xml:space="preserve">26.8984203338623</t>
@@ -425,40 +425,40 @@
     <t xml:space="preserve">25.7981357574463</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8917751312256</t>
+    <t xml:space="preserve">25.8917770385742</t>
   </si>
   <si>
     <t xml:space="preserve">26.7579574584961</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9518814086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.881649017334</t>
+    <t xml:space="preserve">27.95188331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8816528320312</t>
   </si>
   <si>
     <t xml:space="preserve">27.8114204406738</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9050598144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2963905334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8582420349121</t>
+    <t xml:space="preserve">27.9050617218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2963943481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8582401275635</t>
   </si>
   <si>
     <t xml:space="preserve">27.5773181915283</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7177772521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.741189956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.045524597168</t>
+    <t xml:space="preserve">27.7177810668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7411861419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0455207824707</t>
   </si>
   <si>
     <t xml:space="preserve">27.7880077362061</t>
@@ -473,79 +473,79 @@
     <t xml:space="preserve">28.6541900634766</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2093925476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4134426116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0856990814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.851598739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4368553161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.68772315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2261657714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8281860351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.640905380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4536247253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.570671081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5238590240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3365707397461</t>
+    <t xml:space="preserve">28.2093944549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4134407043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0856971740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8515949249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4368534088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6877250671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2261619567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8281879425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6409072875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4536228179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5706748962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.523853302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3365726470947</t>
   </si>
   <si>
     <t xml:space="preserve">25.7513160705566</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3299293518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7446708679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7680835723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8851337432861</t>
+    <t xml:space="preserve">25.329927444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7446689605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7680816650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8851356506348</t>
   </si>
   <si>
     <t xml:space="preserve">24.2530555725098</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0490074157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4703922271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5172119140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.283109664917</t>
+    <t xml:space="preserve">25.0490055084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4703903198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5172100067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2831077575684</t>
   </si>
   <si>
     <t xml:space="preserve">25.1660556793213</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4469776153564</t>
+    <t xml:space="preserve">25.4469833374023</t>
   </si>
   <si>
     <t xml:space="preserve">25.0958271026611</t>
@@ -554,16 +554,16 @@
     <t xml:space="preserve">24.9319534301758</t>
   </si>
   <si>
-    <t xml:space="preserve">25.072416305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6342658996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1961116790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1726970672607</t>
+    <t xml:space="preserve">25.0724182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6342620849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1961078643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.172700881958</t>
   </si>
   <si>
     <t xml:space="preserve">27.8348293304443</t>
@@ -575,10 +575,10 @@
     <t xml:space="preserve">27.4602642059326</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9986991882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6307792663574</t>
+    <t xml:space="preserve">27.9987010955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6307773590088</t>
   </si>
   <si>
     <t xml:space="preserve">29.2160377502441</t>
@@ -587,7 +587,7 @@
     <t xml:space="preserve">29.3330898284912</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8648834228516</t>
+    <t xml:space="preserve">28.8648853302002</t>
   </si>
   <si>
     <t xml:space="preserve">28.3498573303223</t>
@@ -599,37 +599,37 @@
     <t xml:space="preserve">29.4735507965088</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2394466400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7076549530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4267272949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8313446044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9952144622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4868316650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2527275085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3697853088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1356830596924</t>
+    <t xml:space="preserve">29.2394485473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7076511383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4267292022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8313426971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9952182769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4868335723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2527351379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3697834014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1356792449951</t>
   </si>
   <si>
     <t xml:space="preserve">32.1891441345215</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3061943054199</t>
+    <t xml:space="preserve">32.3061904907227</t>
   </si>
   <si>
     <t xml:space="preserve">33.2660179138184</t>
@@ -650,46 +650,46 @@
     <t xml:space="preserve">34.6706352233887</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9983787536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8579139709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1790199279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7642784118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8813285827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3897094726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4131202697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6070404052734</t>
+    <t xml:space="preserve">34.9983825683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.85791015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1790161132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.764274597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8813247680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.389705657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4131278991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6070442199707</t>
   </si>
   <si>
     <t xml:space="preserve">35.4665832519531</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7943267822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.8243789672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6671447753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8778495788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9882507324219</t>
+    <t xml:space="preserve">35.7943305969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.8243751525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6671485900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8778419494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9882469177246</t>
   </si>
   <si>
     <t xml:space="preserve">37.5735054016113</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">37.6203308105469</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6085433959961</t>
+    <t xml:space="preserve">37.6085357666016</t>
   </si>
   <si>
     <t xml:space="preserve">37.7264366149902</t>
@@ -710,22 +710,22 @@
     <t xml:space="preserve">38.1980094909668</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9386405944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1508636474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4906463623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0232849121094</t>
+    <t xml:space="preserve">37.9386444091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1508560180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4906425476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0232772827148</t>
   </si>
   <si>
     <t xml:space="preserve">40.0843353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0607566833496</t>
+    <t xml:space="preserve">40.0607528686523</t>
   </si>
   <si>
     <t xml:space="preserve">39.8013916015625</t>
@@ -737,16 +737,16 @@
     <t xml:space="preserve">41.0274963378906</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4519233703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7112922668457</t>
+    <t xml:space="preserve">41.4519271850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7112846374512</t>
   </si>
   <si>
     <t xml:space="preserve">41.4990768432617</t>
   </si>
   <si>
-    <t xml:space="preserve">41.805606842041</t>
+    <t xml:space="preserve">41.8056030273438</t>
   </si>
   <si>
     <t xml:space="preserve">42.3243446350098</t>
@@ -758,91 +758,91 @@
     <t xml:space="preserve">42.0885543823242</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2771873474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8291893005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.966438293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5891723632812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.4338035583496</t>
+    <t xml:space="preserve">42.2771949768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8291816711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9664421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.5891799926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.4338073730469</t>
   </si>
   <si>
     <t xml:space="preserve">38.999698638916</t>
   </si>
   <si>
-    <t xml:space="preserve">39.6363410949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9428596496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4380226135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5516967773438</t>
+    <t xml:space="preserve">39.6363334655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9428634643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4380264282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.551700592041</t>
   </si>
   <si>
     <t xml:space="preserve">38.0565376281738</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1411781311035</t>
+    <t xml:space="preserve">39.1411743164062</t>
   </si>
   <si>
     <t xml:space="preserve">39.3298110961914</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0704383850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1647529602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6695976257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8346481323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9053802490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0940132141113</t>
+    <t xml:space="preserve">39.070442199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1647567749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6695938110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8346519470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.905387878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0940208435059</t>
   </si>
   <si>
     <t xml:space="preserve">38.8110694885254</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2687568664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7403335571289</t>
+    <t xml:space="preserve">38.2687530517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7403297424316</t>
   </si>
   <si>
     <t xml:space="preserve">38.6931762695312</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2354888916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2590713500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1357078552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5129776000977</t>
+    <t xml:space="preserve">39.2354927062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2590675354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1357154846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5129737854004</t>
   </si>
   <si>
     <t xml:space="preserve">44.7765579223633</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8001441955566</t>
+    <t xml:space="preserve">44.8001365661621</t>
   </si>
   <si>
     <t xml:space="preserve">45.5075149536133</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">45.3188781738281</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8140411376953</t>
+    <t xml:space="preserve">45.814037322998</t>
   </si>
   <si>
     <t xml:space="preserve">44.6822509765625</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">43.7862434387207</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7529830932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.130241394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4464569091797</t>
+    <t xml:space="preserve">44.7529792785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1302452087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4464530944824</t>
   </si>
   <si>
     <t xml:space="preserve">44.5879287719727</t>
@@ -878,82 +878,82 @@
     <t xml:space="preserve">44.3049812316895</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6211967468262</t>
+    <t xml:space="preserve">43.6211891174316</t>
   </si>
   <si>
     <t xml:space="preserve">43.1731910705566</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0788726806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5837097167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2675094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3660316467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9887771606445</t>
+    <t xml:space="preserve">43.0788764953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5837173461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.267505645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3660354614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9887733459473</t>
   </si>
   <si>
     <t xml:space="preserve">44.4936141967773</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5171890258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6254005432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.861198425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4035148620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5824661254883</t>
+    <t xml:space="preserve">44.5171966552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6254081726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8611946105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4035110473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5824699401855</t>
   </si>
   <si>
     <t xml:space="preserve">47.0637283325195</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1344604492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1580467224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9125671386719</t>
+    <t xml:space="preserve">47.134464263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1580429077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9125709533691</t>
   </si>
   <si>
     <t xml:space="preserve">49.3508911132812</t>
   </si>
   <si>
-    <t xml:space="preserve">48.7378425598145</t>
+    <t xml:space="preserve">48.7378387451172</t>
   </si>
   <si>
     <t xml:space="preserve">48.101203918457</t>
   </si>
   <si>
-    <t xml:space="preserve">48.8321571350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6296234130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0540428161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8654174804688</t>
+    <t xml:space="preserve">48.8321533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6296272277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0540466308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8654098510742</t>
   </si>
   <si>
     <t xml:space="preserve">47.9597282409668</t>
   </si>
   <si>
-    <t xml:space="preserve">49.185848236084</t>
+    <t xml:space="preserve">49.1858367919922</t>
   </si>
   <si>
     <t xml:space="preserve">45.2717208862305</t>
@@ -962,34 +962,34 @@
     <t xml:space="preserve">45.0359344482422</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5643501281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9748725891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5601348876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.9138221740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7251853942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2064514160156</t>
+    <t xml:space="preserve">44.5643539428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9748764038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.560131072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.913818359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7251892089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2064476013184</t>
   </si>
   <si>
     <t xml:space="preserve">42.4328079223633</t>
   </si>
   <si>
-    <t xml:space="preserve">42.178150177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3476715087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9800910949707</t>
+    <t xml:space="preserve">42.1781539916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3476753234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9800872802734</t>
   </si>
   <si>
     <t xml:space="preserve">41.3010177612305</t>
@@ -998,19 +998,19 @@
     <t xml:space="preserve">42.0838394165039</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7534866333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5931510925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4799690246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0081329345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0458602905273</t>
+    <t xml:space="preserve">42.7534828186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5931396484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4799728393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0081367492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0458641052246</t>
   </si>
   <si>
     <t xml:space="preserve">43.3288078308105</t>
@@ -1019,40 +1019,40 @@
     <t xml:space="preserve">41.3953323364258</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4891510009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.234245300293</t>
+    <t xml:space="preserve">43.4891471862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2342491149902</t>
   </si>
   <si>
     <t xml:space="preserve">44.1210632324219</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2439270019531</t>
+    <t xml:space="preserve">43.2439231872559</t>
   </si>
   <si>
     <t xml:space="preserve">42.1027030944824</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1689682006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2729759216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4045181274414</t>
+    <t xml:space="preserve">41.1689720153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2729721069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4045066833496</t>
   </si>
   <si>
     <t xml:space="preserve">43.7626647949219</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2531051635742</t>
+    <t xml:space="preserve">44.2531089782715</t>
   </si>
   <si>
     <t xml:space="preserve">45.0547943115234</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9510459899902</t>
+    <t xml:space="preserve">44.9510498046875</t>
   </si>
   <si>
     <t xml:space="preserve">46.2809028625488</t>
@@ -1061,16 +1061,16 @@
     <t xml:space="preserve">46.1488647460938</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3094520568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9982032775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5358085632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1679801940918</t>
+    <t xml:space="preserve">45.3094482421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9982070922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5358047485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1679725646973</t>
   </si>
   <si>
     <t xml:space="preserve">45.5923957824707</t>
@@ -1079,16 +1079,16 @@
     <t xml:space="preserve">44.6586647033691</t>
   </si>
   <si>
-    <t xml:space="preserve">43.253360748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.668342590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2248115539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0830879211426</t>
+    <t xml:space="preserve">43.2533531188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6683464050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2248153686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0830841064453</t>
   </si>
   <si>
     <t xml:space="preserve">45.2056999206543</t>
@@ -1097,76 +1097,76 @@
     <t xml:space="preserve">46.3280601501465</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0356826782227</t>
+    <t xml:space="preserve">46.0356864929199</t>
   </si>
   <si>
     <t xml:space="preserve">45.6584167480469</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5169334411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1682281494141</t>
+    <t xml:space="preserve">45.5169410705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1682243347168</t>
   </si>
   <si>
     <t xml:space="preserve">43.8664093017578</t>
   </si>
   <si>
-    <t xml:space="preserve">43.5457382202148</t>
+    <t xml:space="preserve">43.5457344055176</t>
   </si>
   <si>
     <t xml:space="preserve">43.8852767944336</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4606056213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6112594604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.630126953125</t>
+    <t xml:space="preserve">44.4606018066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.611255645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6301231384277</t>
   </si>
   <si>
     <t xml:space="preserve">45.724437713623</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2903366088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0262489318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2148857116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6487350463867</t>
+    <t xml:space="preserve">46.290340423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0262565612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2148818969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.648738861084</t>
   </si>
   <si>
     <t xml:space="preserve">46.705322265625</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5921478271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8939590454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7711067199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8182525634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1955184936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9972076416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5727882385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3273162841797</t>
+    <t xml:space="preserve">46.5921516418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8939552307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7710952758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8182563781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1955146789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9972114562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5727844238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3273086547852</t>
   </si>
   <si>
     <t xml:space="preserve">50.3176307678223</t>
@@ -1175,67 +1175,67 @@
     <t xml:space="preserve">50.4119491577148</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8460502624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3744659423828</t>
+    <t xml:space="preserve">49.8460464477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3744697570801</t>
   </si>
   <si>
     <t xml:space="preserve">50.2233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0818367004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5353088378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1960182189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2051963806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.006893157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2523574829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4223785400391</t>
+    <t xml:space="preserve">50.081844329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5353126525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1960258483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2052001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0068855285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2523612976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4223747253418</t>
   </si>
   <si>
     <t xml:space="preserve">45.8376197814941</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6489906311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8753433227539</t>
+    <t xml:space="preserve">45.6489868164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8753471374512</t>
   </si>
   <si>
     <t xml:space="preserve">46.5732841491699</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4687843322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8085784912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4789695739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3938369750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5166969299316</t>
+    <t xml:space="preserve">49.4687881469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8085746765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4789657592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3938331604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5166931152344</t>
   </si>
   <si>
     <t xml:space="preserve">45.1774101257324</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7812767028809</t>
+    <t xml:space="preserve">44.7812805175781</t>
   </si>
   <si>
     <t xml:space="preserve">44.8378677368164</t>
@@ -1244,52 +1244,52 @@
     <t xml:space="preserve">44.4983291625977</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1776542663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.895206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2913360595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4988327026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0652275085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9518013000488</t>
+    <t xml:space="preserve">44.1776504516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8952026367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.291332244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4988250732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0652198791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9517936706543</t>
   </si>
   <si>
     <t xml:space="preserve">45.3283157348633</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4414939880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4603576660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4037590026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1017036437988</t>
+    <t xml:space="preserve">45.4414863586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4603462219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4037666320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1017074584961</t>
   </si>
   <si>
     <t xml:space="preserve">45.988525390625</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3846549987793</t>
+    <t xml:space="preserve">46.3846473693848</t>
   </si>
   <si>
     <t xml:space="preserve">49.0443649291992</t>
   </si>
   <si>
-    <t xml:space="preserve">48.902889251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.2898368835449</t>
+    <t xml:space="preserve">48.9028930664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.2898330688477</t>
   </si>
   <si>
     <t xml:space="preserve">51.1193237304688</t>
@@ -1298,16 +1298,16 @@
     <t xml:space="preserve">50.6948928833008</t>
   </si>
   <si>
-    <t xml:space="preserve">50.6005821228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9328575134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4107131958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0277938842773</t>
+    <t xml:space="preserve">50.6005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.932861328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4107093811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0277900695801</t>
   </si>
   <si>
     <t xml:space="preserve">52.2144813537598</t>
@@ -1322,19 +1322,19 @@
     <t xml:space="preserve">49.8410949707031</t>
   </si>
   <si>
-    <t xml:space="preserve">51.5024642944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2714920043945</t>
+    <t xml:space="preserve">51.5024681091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2714881896973</t>
   </si>
   <si>
     <t xml:space="preserve">49.3664207458496</t>
   </si>
   <si>
-    <t xml:space="preserve">49.0816116333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.793628692627</t>
+    <t xml:space="preserve">49.081615447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7936325073242</t>
   </si>
   <si>
     <t xml:space="preserve">48.2746620178223</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">46.822151184082</t>
   </si>
   <si>
-    <t xml:space="preserve">48.0848007202148</t>
+    <t xml:space="preserve">48.0847930908203</t>
   </si>
   <si>
     <t xml:space="preserve">48.6544075012207</t>
@@ -1361,25 +1361,25 @@
     <t xml:space="preserve">50.3632431030273</t>
   </si>
   <si>
-    <t xml:space="preserve">51.2176666259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1733703613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4550018310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.0246162414551</t>
+    <t xml:space="preserve">51.217658996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1733665466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.455005645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.0246124267578</t>
   </si>
   <si>
     <t xml:space="preserve">53.068904876709</t>
   </si>
   <si>
-    <t xml:space="preserve">52.7840957641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4422950744629</t>
+    <t xml:space="preserve">52.7840919494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4422912597656</t>
   </si>
   <si>
     <t xml:space="preserve">54.682804107666</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">55.1100120544434</t>
   </si>
   <si>
-    <t xml:space="preserve">55.5846900939941</t>
+    <t xml:space="preserve">55.5846862792969</t>
   </si>
   <si>
     <t xml:space="preserve">56.3916435241699</t>
@@ -1397,13 +1397,13 @@
     <t xml:space="preserve">54.7302742004395</t>
   </si>
   <si>
-    <t xml:space="preserve">55.0625457763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4897613525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2524185180664</t>
+    <t xml:space="preserve">55.0625495910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4897537231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.2524147033691</t>
   </si>
   <si>
     <t xml:space="preserve">53.1638374328613</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">53.6385154724121</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0182609558105</t>
+    <t xml:space="preserve">54.0182571411133</t>
   </si>
   <si>
     <t xml:space="preserve">54.3030662536621</t>
@@ -1424,88 +1424,88 @@
     <t xml:space="preserve">53.8283882141113</t>
   </si>
   <si>
-    <t xml:space="preserve">54.7777366638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4391059875488</t>
+    <t xml:space="preserve">54.7777404785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4391136169434</t>
   </si>
   <si>
     <t xml:space="preserve">56.9137878417969</t>
   </si>
   <si>
-    <t xml:space="preserve">56.296703338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0118980407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.201774597168</t>
+    <t xml:space="preserve">56.2967071533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0119018554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2017784118652</t>
   </si>
   <si>
     <t xml:space="preserve">56.5340461730957</t>
   </si>
   <si>
-    <t xml:space="preserve">56.6764488220215</t>
+    <t xml:space="preserve">56.6764526367188</t>
   </si>
   <si>
     <t xml:space="preserve">54.9676094055176</t>
   </si>
   <si>
-    <t xml:space="preserve">52.5942268371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0214309692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1574821472168</t>
+    <t xml:space="preserve">52.5942306518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0214347839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1574783325195</t>
   </si>
   <si>
     <t xml:space="preserve">54.3505325317383</t>
   </si>
   <si>
-    <t xml:space="preserve">52.9265022277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.879035949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0657272338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5878715515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4486427307129</t>
+    <t xml:space="preserve">52.9264984130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.8790321350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0657234191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5878639221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4486389160156</t>
   </si>
   <si>
     <t xml:space="preserve">53.6859817504883</t>
   </si>
   <si>
-    <t xml:space="preserve">53.3062362670898</t>
+    <t xml:space="preserve">53.3062438964844</t>
   </si>
   <si>
     <t xml:space="preserve">52.404354095459</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0752601623535</t>
+    <t xml:space="preserve">51.0752563476562</t>
   </si>
   <si>
     <t xml:space="preserve">50.4581832885742</t>
   </si>
   <si>
-    <t xml:space="preserve">52.2619476318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8822135925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1606559753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.2081298828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5435829162598</t>
+    <t xml:space="preserve">52.2619514465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8822059631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1606597900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.2081260681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5435791015625</t>
   </si>
   <si>
     <t xml:space="preserve">54.5404052734375</t>
@@ -1514,10 +1514,10 @@
     <t xml:space="preserve">55.2049522399902</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2492408752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.1036567687988</t>
+    <t xml:space="preserve">56.2492370605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1036605834961</t>
   </si>
   <si>
     <t xml:space="preserve">57.2460594177246</t>
@@ -1532,7 +1532,7 @@
     <t xml:space="preserve">50.790454864502</t>
   </si>
   <si>
-    <t xml:space="preserve">49.413890838623</t>
+    <t xml:space="preserve">49.4138870239258</t>
   </si>
   <si>
     <t xml:space="preserve">47.0120162963867</t>
@@ -1541,10 +1541,10 @@
     <t xml:space="preserve">47.0499992370605</t>
   </si>
   <si>
-    <t xml:space="preserve">48.2271919250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4677124023438</t>
+    <t xml:space="preserve">48.2271957397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4677085876465</t>
   </si>
   <si>
     <t xml:space="preserve">50.0309677124023</t>
@@ -1553,7 +1553,7 @@
     <t xml:space="preserve">50.3157730102539</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3474807739258</t>
+    <t xml:space="preserve">46.3474769592285</t>
   </si>
   <si>
     <t xml:space="preserve">44.7525596618652</t>
@@ -1562,49 +1562,49 @@
     <t xml:space="preserve">44.6766128540039</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6955986022949</t>
+    <t xml:space="preserve">44.6956062316895</t>
   </si>
   <si>
     <t xml:space="preserve">46.1955757141113</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5563278198242</t>
+    <t xml:space="preserve">46.5563354492188</t>
   </si>
   <si>
     <t xml:space="preserve">46.4803848266602</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9487495422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4107475280762</t>
+    <t xml:space="preserve">45.9487457275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4107513427734</t>
   </si>
   <si>
     <t xml:space="preserve">46.5373458862305</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5183563232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.746208190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4424095153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4930534362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1323051452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5690002441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.701904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3601837158203</t>
+    <t xml:space="preserve">46.5183601379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7462005615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4424057006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4930572509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1323013305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5690040588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7019119262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3601875305176</t>
   </si>
   <si>
     <t xml:space="preserve">41.4677925109863</t>
@@ -1625,34 +1625,34 @@
     <t xml:space="preserve">43.8601684570312</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7209014892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7841796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7050552368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2398681640625</t>
+    <t xml:space="preserve">45.7208938598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7841758728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7050476074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2398643493652</t>
   </si>
   <si>
     <t xml:space="preserve">46.2905120849609</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1892623901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2082481384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2841949462891</t>
+    <t xml:space="preserve">45.189266204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2082443237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2841987609863</t>
   </si>
   <si>
     <t xml:space="preserve">47.3158149719238</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3727760314941</t>
+    <t xml:space="preserve">47.3727798461914</t>
   </si>
   <si>
     <t xml:space="preserve">46.6132926940918</t>
@@ -1661,46 +1661,46 @@
     <t xml:space="preserve">44.4867401123047</t>
   </si>
   <si>
-    <t xml:space="preserve">43.5373916625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5184059143066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0753746032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5627326965332</t>
+    <t xml:space="preserve">43.5373878479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5183982849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0753784179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5627288818359</t>
   </si>
   <si>
     <t xml:space="preserve">40.2146453857422</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8475379943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4551239013672</t>
+    <t xml:space="preserve">41.847541809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4551200866699</t>
   </si>
   <si>
     <t xml:space="preserve">40.2526245117188</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8095626831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1956214904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0310516357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3158569335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3348503112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8791542053223</t>
+    <t xml:space="preserve">41.8095588684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1956176757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0310554504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3158531188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.334846496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8791580200195</t>
   </si>
   <si>
     <t xml:space="preserve">45.7398872375488</t>
@@ -1709,19 +1709,19 @@
     <t xml:space="preserve">45.8348236083984</t>
   </si>
   <si>
-    <t xml:space="preserve">46.803165435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3854446411133</t>
+    <t xml:space="preserve">46.8031616210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3854484558105</t>
   </si>
   <si>
     <t xml:space="preserve">46.4234237670898</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1829071044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1765441894531</t>
+    <t xml:space="preserve">47.1829032897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1765480041504</t>
   </si>
   <si>
     <t xml:space="preserve">48.3695945739746</t>
@@ -1733,46 +1733,46 @@
     <t xml:space="preserve">45.0753402709961</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6449584960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2588500976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4645347595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8885612487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1259078979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6955184936523</t>
+    <t xml:space="preserve">45.6449546813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2588577270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4645385742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8885650634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.125904083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6955146789551</t>
   </si>
   <si>
     <t xml:space="preserve">50.2208404541016</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9360275268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0784339904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1670150756836</t>
+    <t xml:space="preserve">49.93603515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0784378051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1670188903809</t>
   </si>
   <si>
     <t xml:space="preserve">52.6891632080078</t>
   </si>
   <si>
-    <t xml:space="preserve">52.9739646911621</t>
+    <t xml:space="preserve">52.9739685058594</t>
   </si>
   <si>
     <t xml:space="preserve">54.2555961608887</t>
   </si>
   <si>
-    <t xml:space="preserve">53.2587699890137</t>
+    <t xml:space="preserve">53.2587738037109</t>
   </si>
   <si>
     <t xml:space="preserve">53.9707870483398</t>
@@ -1787,25 +1787,25 @@
     <t xml:space="preserve">54.3980026245117</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4011726379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.9233245849609</t>
+    <t xml:space="preserve">53.401180267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9233207702637</t>
   </si>
   <si>
     <t xml:space="preserve">54.4929389953613</t>
   </si>
   <si>
-    <t xml:space="preserve">54.4454650878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4961090087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.6353416442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.9644355773926</t>
+    <t xml:space="preserve">54.4454612731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4961128234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6353378295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.964427947998</t>
   </si>
   <si>
     <t xml:space="preserve">55.7270965576172</t>
@@ -1814,31 +1814,31 @@
     <t xml:space="preserve">56.1068344116211</t>
   </si>
   <si>
-    <t xml:space="preserve">55.5328559875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5239143371582</t>
+    <t xml:space="preserve">55.5328483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5239105224609</t>
   </si>
   <si>
     <t xml:space="preserve">53.5717430114746</t>
   </si>
   <si>
-    <t xml:space="preserve">52.615104675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5194396972656</t>
+    <t xml:space="preserve">52.6151008605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5194435119629</t>
   </si>
   <si>
     <t xml:space="preserve">51.4671401977539</t>
   </si>
   <si>
-    <t xml:space="preserve">54.528377532959</t>
+    <t xml:space="preserve">54.5283851623535</t>
   </si>
   <si>
     <t xml:space="preserve">55.9633407592773</t>
   </si>
   <si>
-    <t xml:space="preserve">56.0590019226074</t>
+    <t xml:space="preserve">56.0589981079102</t>
   </si>
   <si>
     <t xml:space="preserve">55.1980285644531</t>
@@ -1847,7 +1847,7 @@
     <t xml:space="preserve">56.7764778137207</t>
   </si>
   <si>
-    <t xml:space="preserve">56.0111694335938</t>
+    <t xml:space="preserve">56.0111656188965</t>
   </si>
   <si>
     <t xml:space="preserve">55.6285171508789</t>
@@ -1856,7 +1856,7 @@
     <t xml:space="preserve">56.2024993896484</t>
   </si>
   <si>
-    <t xml:space="preserve">55.9155120849609</t>
+    <t xml:space="preserve">55.9155082702637</t>
   </si>
   <si>
     <t xml:space="preserve">56.4416580200195</t>
@@ -1874,19 +1874,19 @@
     <t xml:space="preserve">54.5762100219727</t>
   </si>
   <si>
-    <t xml:space="preserve">54.4327201843262</t>
+    <t xml:space="preserve">54.4327125549316</t>
   </si>
   <si>
     <t xml:space="preserve">54.8632011413574</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9199714660645</t>
+    <t xml:space="preserve">56.919979095459</t>
   </si>
   <si>
     <t xml:space="preserve">56.8243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">57.2547950744629</t>
+    <t xml:space="preserve">57.2547988891602</t>
   </si>
   <si>
     <t xml:space="preserve">56.6808166503906</t>
@@ -1895,28 +1895,28 @@
     <t xml:space="preserve">56.7286491394043</t>
   </si>
   <si>
-    <t xml:space="preserve">58.2114372253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.6374549865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.5462646484375</t>
+    <t xml:space="preserve">58.2114334106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.6374588012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.5462684631348</t>
   </si>
   <si>
     <t xml:space="preserve">57.9244499206543</t>
   </si>
   <si>
-    <t xml:space="preserve">58.3549346923828</t>
+    <t xml:space="preserve">58.3549308776855</t>
   </si>
   <si>
     <t xml:space="preserve">57.7331199645996</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3504676818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.3071060180664</t>
+    <t xml:space="preserve">57.3504638671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.3071098327637</t>
   </si>
   <si>
     <t xml:space="preserve">60.2682151794434</t>
@@ -1925,19 +1925,19 @@
     <t xml:space="preserve">60.172550201416</t>
   </si>
   <si>
-    <t xml:space="preserve">59.7420654296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.2159118652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.120246887207</t>
+    <t xml:space="preserve">59.7420616149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.2159080505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.1202430725098</t>
   </si>
   <si>
     <t xml:space="preserve">57.3026351928711</t>
   </si>
   <si>
-    <t xml:space="preserve">57.8287811279297</t>
+    <t xml:space="preserve">57.828784942627</t>
   </si>
   <si>
     <t xml:space="preserve">58.1157722473145</t>
@@ -1952,22 +1952,22 @@
     <t xml:space="preserve">59.4550743103027</t>
   </si>
   <si>
-    <t xml:space="preserve">60.3160438537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.029052734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.0724182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.25927734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0201110839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9888191223145</t>
+    <t xml:space="preserve">60.3160400390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.0290489196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.0724143981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.2592735290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0201148986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9888229370117</t>
   </si>
   <si>
     <t xml:space="preserve">50.4148368835449</t>
@@ -1979,16 +1979,16 @@
     <t xml:space="preserve">51.3236465454102</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8931579589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7930183410645</t>
+    <t xml:space="preserve">50.8931617736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7930221557617</t>
   </si>
   <si>
     <t xml:space="preserve">49.8408546447754</t>
   </si>
   <si>
-    <t xml:space="preserve">48.6928863525391</t>
+    <t xml:space="preserve">48.6928939819336</t>
   </si>
   <si>
     <t xml:space="preserve">49.2668724060059</t>
@@ -2006,37 +2006,37 @@
     <t xml:space="preserve">50.6539993286133</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2235107421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.845329284668</t>
+    <t xml:space="preserve">50.2235069274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8453254699707</t>
   </si>
   <si>
     <t xml:space="preserve">51.4193077087402</t>
   </si>
   <si>
-    <t xml:space="preserve">50.940990447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5149765014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7974967956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.13232421875</t>
+    <t xml:space="preserve">50.9409866333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5149688720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7974891662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1323204040527</t>
   </si>
   <si>
     <t xml:space="preserve">49.6973571777344</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3147048950195</t>
+    <t xml:space="preserve">49.3147087097168</t>
   </si>
   <si>
     <t xml:space="preserve">49.4581985473633</t>
   </si>
   <si>
-    <t xml:space="preserve">49.745189666748</t>
+    <t xml:space="preserve">49.7451934814453</t>
   </si>
   <si>
     <t xml:space="preserve">50.0321807861328</t>
@@ -2045,25 +2045,25 @@
     <t xml:space="preserve">48.8363838195801</t>
   </si>
   <si>
-    <t xml:space="preserve">48.597225189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3625335693359</t>
+    <t xml:space="preserve">48.5972213745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3625297546387</t>
   </si>
   <si>
     <t xml:space="preserve">54.0022315979004</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4282417297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.2892227172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1935539245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0934219360352</t>
+    <t xml:space="preserve">53.4282455444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.2892265319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1935577392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0934257507324</t>
   </si>
   <si>
     <t xml:space="preserve">52.4716110229492</t>
@@ -2075,49 +2075,49 @@
     <t xml:space="preserve">54.0978965759277</t>
   </si>
   <si>
-    <t xml:space="preserve">54.9110374450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3370590209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8587379455566</t>
+    <t xml:space="preserve">54.9110412597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3370513916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8587341308594</t>
   </si>
   <si>
     <t xml:space="preserve">54.4805526733398</t>
   </si>
   <si>
-    <t xml:space="preserve">55.0545349121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.3415222167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.8676834106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5373153686523</t>
+    <t xml:space="preserve">55.0545310974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.3415184020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.8676719665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5373191833496</t>
   </si>
   <si>
     <t xml:space="preserve">56.6329879760742</t>
   </si>
   <si>
-    <t xml:space="preserve">58.4027633666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.067943572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6942329406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.3115768432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8511352539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6164436340332</t>
+    <t xml:space="preserve">58.4027671813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0679473876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6942291259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.3115730285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8511276245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6164398193359</t>
   </si>
   <si>
     <t xml:space="preserve">65.3384017944336</t>
@@ -2129,19 +2129,19 @@
     <t xml:space="preserve">66.9646835327148</t>
   </si>
   <si>
-    <t xml:space="preserve">67.9213104248047</t>
+    <t xml:space="preserve">67.9213180541992</t>
   </si>
   <si>
     <t xml:space="preserve">69.260612487793</t>
   </si>
   <si>
-    <t xml:space="preserve">69.0692749023438</t>
+    <t xml:space="preserve">69.0692825317383</t>
   </si>
   <si>
     <t xml:space="preserve">67.3951568603516</t>
   </si>
   <si>
-    <t xml:space="preserve">68.016975402832</t>
+    <t xml:space="preserve">68.0169830322266</t>
   </si>
   <si>
     <t xml:space="preserve">66.869010925293</t>
@@ -2150,58 +2150,58 @@
     <t xml:space="preserve">67.2994995117188</t>
   </si>
   <si>
-    <t xml:space="preserve">67.5386581420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.9257888793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.212776184082</t>
+    <t xml:space="preserve">67.5386505126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.9257965087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.2127685546875</t>
   </si>
   <si>
     <t xml:space="preserve">68.4474716186523</t>
   </si>
   <si>
-    <t xml:space="preserve">67.8734664916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.7778167724609</t>
+    <t xml:space="preserve">67.8734817504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.7778244018555</t>
   </si>
   <si>
     <t xml:space="preserve">67.0603408813477</t>
   </si>
   <si>
-    <t xml:space="preserve">66.0080490112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.4385223388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.5775527954102</t>
+    <t xml:space="preserve">66.0080413818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.4385299682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.5775451660156</t>
   </si>
   <si>
     <t xml:space="preserve">65.9123840332031</t>
   </si>
   <si>
-    <t xml:space="preserve">67.2516632080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.8256530761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.6343154907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.7688980102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.1037063598633</t>
+    <t xml:space="preserve">67.2516708374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.8256607055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.6343231201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.7688903808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.1036987304688</t>
   </si>
   <si>
     <t xml:space="preserve">69.4519348144531</t>
   </si>
   <si>
-    <t xml:space="preserve">68.2083129882812</t>
+    <t xml:space="preserve">68.2083206176758</t>
   </si>
   <si>
     <t xml:space="preserve">70.3129119873047</t>
@@ -2210,43 +2210,43 @@
     <t xml:space="preserve">73.3263244628906</t>
   </si>
   <si>
-    <t xml:space="preserve">73.2306594848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.0916290283203</t>
+    <t xml:space="preserve">73.2306671142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.0916366577148</t>
   </si>
   <si>
     <t xml:space="preserve">73.6611557006836</t>
   </si>
   <si>
-    <t xml:space="preserve">73.3741607666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6955718994141</t>
+    <t xml:space="preserve">73.374153137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6955642700195</t>
   </si>
   <si>
     <t xml:space="preserve">70.7912368774414</t>
   </si>
   <si>
-    <t xml:space="preserve">72.4653549194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.2650756835938</t>
+    <t xml:space="preserve">72.4653472900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.2650680541992</t>
   </si>
   <si>
     <t xml:space="preserve">68.638801574707</t>
   </si>
   <si>
-    <t xml:space="preserve">71.3173904418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9392013549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.7045135498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.7523574829102</t>
+    <t xml:space="preserve">71.3173828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9391937255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.7045059204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.7523498535156</t>
   </si>
   <si>
     <t xml:space="preserve">72.6088409423828</t>
@@ -2258,10 +2258,10 @@
     <t xml:space="preserve">74.1394653320312</t>
   </si>
   <si>
-    <t xml:space="preserve">71.7478790283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9870376586914</t>
+    <t xml:space="preserve">71.7478637695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9870300292969</t>
   </si>
   <si>
     <t xml:space="preserve">73.2784881591797</t>
@@ -2273,28 +2273,28 @@
     <t xml:space="preserve">66.8211822509766</t>
   </si>
   <si>
-    <t xml:space="preserve">65.7210540771484</t>
+    <t xml:space="preserve">65.7210464477539</t>
   </si>
   <si>
     <t xml:space="preserve">62.1336555480957</t>
   </si>
   <si>
-    <t xml:space="preserve">63.8077697753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8944854736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.937858581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.8766136169434</t>
+    <t xml:space="preserve">63.8077735900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8944931030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9378547668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.8766174316406</t>
   </si>
   <si>
     <t xml:space="preserve">52.5672760009766</t>
   </si>
   <si>
-    <t xml:space="preserve">52.0889587402344</t>
+    <t xml:space="preserve">52.0889549255371</t>
   </si>
   <si>
     <t xml:space="preserve">46.3778190612793</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">48.7407188415527</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4594497680664</t>
+    <t xml:space="preserve">45.4594535827637</t>
   </si>
   <si>
     <t xml:space="preserve">41.7094268798828</t>
@@ -2312,34 +2312,34 @@
     <t xml:space="preserve">43.8714332580566</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2107238769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3446578979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1048736572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0844841003418</t>
+    <t xml:space="preserve">45.2107276916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.344654083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1048698425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0844802856445</t>
   </si>
   <si>
     <t xml:space="preserve">49.2190361022949</t>
   </si>
   <si>
-    <t xml:space="preserve">59.1680755615234</t>
+    <t xml:space="preserve">59.1680793762207</t>
   </si>
   <si>
     <t xml:space="preserve">57.6852836608887</t>
   </si>
   <si>
-    <t xml:space="preserve">59.2637405395508</t>
+    <t xml:space="preserve">59.263744354248</t>
   </si>
   <si>
     <t xml:space="preserve">61.0813522338867</t>
   </si>
   <si>
-    <t xml:space="preserve">60.3638687133789</t>
+    <t xml:space="preserve">60.3638763427734</t>
   </si>
   <si>
     <t xml:space="preserve">61.1291885375977</t>
@@ -2348,7 +2348,7 @@
     <t xml:space="preserve">61.4161758422852</t>
   </si>
   <si>
-    <t xml:space="preserve">62.6598129272461</t>
+    <t xml:space="preserve">62.6598052978516</t>
   </si>
   <si>
     <t xml:space="preserve">63.5207901000977</t>
@@ -2360,25 +2360,25 @@
     <t xml:space="preserve">63.138126373291</t>
   </si>
   <si>
-    <t xml:space="preserve">63.0424652099609</t>
+    <t xml:space="preserve">63.0424728393555</t>
   </si>
   <si>
     <t xml:space="preserve">61.990161895752</t>
   </si>
   <si>
-    <t xml:space="preserve">61.033519744873</t>
+    <t xml:space="preserve">61.0335235595703</t>
   </si>
   <si>
     <t xml:space="preserve">59.2684898376465</t>
   </si>
   <si>
-    <t xml:space="preserve">60.9081344604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.7279624938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.705192565918</t>
+    <t xml:space="preserve">60.9081420898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.7279586791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.7051963806152</t>
   </si>
   <si>
     <t xml:space="preserve">64.7179107666016</t>
@@ -2396,34 +2396,34 @@
     <t xml:space="preserve">64.4285583496094</t>
   </si>
   <si>
-    <t xml:space="preserve">64.9108123779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.4312210083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.0936431884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.3830108642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.624137878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.9744338989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.3984069824219</t>
+    <t xml:space="preserve">64.9108047485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.4312286376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.0936508178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.3830184936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.6241302490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.9744415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.3984146118164</t>
   </si>
   <si>
     <t xml:space="preserve">74.1217727661133</t>
   </si>
   <si>
-    <t xml:space="preserve">73.9288711547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.362907409668</t>
+    <t xml:space="preserve">73.9288864135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.3628921508789</t>
   </si>
   <si>
     <t xml:space="preserve">75.8578720092773</t>
@@ -2444,10 +2444,10 @@
     <t xml:space="preserve">70.2155532836914</t>
   </si>
   <si>
-    <t xml:space="preserve">65.9235305786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.03271484375</t>
+    <t xml:space="preserve">65.9235382080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.0327072143555</t>
   </si>
   <si>
     <t xml:space="preserve">67.2256088256836</t>
@@ -2462,10 +2462,10 @@
     <t xml:space="preserve">67.3220596313477</t>
   </si>
   <si>
-    <t xml:space="preserve">69.9262161254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.1800537109375</t>
+    <t xml:space="preserve">69.9262008666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.180061340332</t>
   </si>
   <si>
     <t xml:space="preserve">70.4084625244141</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">71.3729629516602</t>
   </si>
   <si>
-    <t xml:space="preserve">69.4921722412109</t>
+    <t xml:space="preserve">69.4921798706055</t>
   </si>
   <si>
     <t xml:space="preserve">70.31201171875</t>
@@ -2483,25 +2483,25 @@
     <t xml:space="preserve">68.5276794433594</t>
   </si>
   <si>
-    <t xml:space="preserve">68.2865600585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.67236328125</t>
+    <t xml:space="preserve">68.2865676879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.6723556518555</t>
   </si>
   <si>
     <t xml:space="preserve">69.0099411010742</t>
   </si>
   <si>
-    <t xml:space="preserve">69.2992858886719</t>
+    <t xml:space="preserve">69.2992782592773</t>
   </si>
   <si>
     <t xml:space="preserve">72.1445541381836</t>
   </si>
   <si>
-    <t xml:space="preserve">71.2765121459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.8069763183594</t>
+    <t xml:space="preserve">71.276496887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.8069839477539</t>
   </si>
   <si>
     <t xml:space="preserve">70.1673278808594</t>
@@ -2510,19 +2510,19 @@
     <t xml:space="preserve">70.5531311035156</t>
   </si>
   <si>
-    <t xml:space="preserve">70.3602294921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.6623077392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.3374633789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.8679275512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.4466323852539</t>
+    <t xml:space="preserve">70.360221862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.6623153686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.3374557495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.8679351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.4466171264648</t>
   </si>
   <si>
     <t xml:space="preserve">73.5430755615234</t>
@@ -2537,19 +2537,19 @@
     <t xml:space="preserve">73.6877593994141</t>
   </si>
   <si>
-    <t xml:space="preserve">73.5913009643555</t>
+    <t xml:space="preserve">73.59130859375</t>
   </si>
   <si>
     <t xml:space="preserve">72.9643859863281</t>
   </si>
   <si>
-    <t xml:space="preserve">74.7487106323242</t>
+    <t xml:space="preserve">74.7487030029297</t>
   </si>
   <si>
     <t xml:space="preserve">81.9342193603516</t>
   </si>
   <si>
-    <t xml:space="preserve">82.9469451904297</t>
+    <t xml:space="preserve">82.9469528198242</t>
   </si>
   <si>
     <t xml:space="preserve">85.117073059082</t>
@@ -2558,31 +2558,31 @@
     <t xml:space="preserve">86.0815734863281</t>
   </si>
   <si>
-    <t xml:space="preserve">85.3581924438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1398544311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0179443359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0661773681641</t>
+    <t xml:space="preserve">85.3582000732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1398468017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.017951965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0661849975586</t>
   </si>
   <si>
     <t xml:space="preserve">82.609375</t>
   </si>
   <si>
-    <t xml:space="preserve">80.8732757568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.0916366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3099746704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.5865936279297</t>
+    <t xml:space="preserve">80.8732604980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.0916290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3099670410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.5865859985352</t>
   </si>
   <si>
     <t xml:space="preserve">84.6348190307617</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">83.6703186035156</t>
   </si>
   <si>
-    <t xml:space="preserve">84.7795028686523</t>
+    <t xml:space="preserve">84.7795104980469</t>
   </si>
   <si>
     <t xml:space="preserve">84.6830520629883</t>
@@ -2600,10 +2600,10 @@
     <t xml:space="preserve">87.3836441040039</t>
   </si>
   <si>
-    <t xml:space="preserve">86.2262496948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.7212066650391</t>
+    <t xml:space="preserve">86.2262420654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.7212142944336</t>
   </si>
   <si>
     <t xml:space="preserve">89.6984405517578</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">88.1070175170898</t>
   </si>
   <si>
-    <t xml:space="preserve">87.8658981323242</t>
+    <t xml:space="preserve">87.8658905029297</t>
   </si>
   <si>
     <t xml:space="preserve">91.2416381835938</t>
@@ -2627,13 +2627,13 @@
     <t xml:space="preserve">90.2771377563477</t>
   </si>
   <si>
-    <t xml:space="preserve">90.5664978027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8076248168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9777450561523</t>
+    <t xml:space="preserve">90.5664901733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9777374267578</t>
   </si>
   <si>
     <t xml:space="preserve">95.0031967163086</t>
@@ -2648,7 +2648,7 @@
     <t xml:space="preserve">93.218864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">93.5082092285156</t>
+    <t xml:space="preserve">93.5082244873047</t>
   </si>
   <si>
     <t xml:space="preserve">91.4827728271484</t>
@@ -2663,13 +2663,13 @@
     <t xml:space="preserve">92.1096954345703</t>
   </si>
   <si>
-    <t xml:space="preserve">93.3635482788086</t>
+    <t xml:space="preserve">93.3635406494141</t>
   </si>
   <si>
     <t xml:space="preserve">95.5336608886719</t>
   </si>
   <si>
-    <t xml:space="preserve">94.954963684082</t>
+    <t xml:space="preserve">94.9549560546875</t>
   </si>
   <si>
     <t xml:space="preserve">94.8102951049805</t>
@@ -2681,10 +2681,10 @@
     <t xml:space="preserve">94.5209350585938</t>
   </si>
   <si>
-    <t xml:space="preserve">92.6883926391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4345474243164</t>
+    <t xml:space="preserve">92.6883850097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4345397949219</t>
   </si>
   <si>
     <t xml:space="preserve">93.0259628295898</t>
@@ -2696,43 +2696,43 @@
     <t xml:space="preserve">97.2215423583984</t>
   </si>
   <si>
-    <t xml:space="preserve">100.115043640137</t>
+    <t xml:space="preserve">100.115036010742</t>
   </si>
   <si>
     <t xml:space="preserve">99.7292404174805</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6073303222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.8966827392578</t>
+    <t xml:space="preserve">97.6073379516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.8966903686523</t>
   </si>
   <si>
     <t xml:space="preserve">98.3789367675781</t>
   </si>
   <si>
-    <t xml:space="preserve">96.3052673339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.7493362426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.8330688476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.8812866210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.4445877075195</t>
+    <t xml:space="preserve">96.3052597045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7493438720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.8330764770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.8813018798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.4445953369141</t>
   </si>
   <si>
     <t xml:space="preserve">88.2034606933594</t>
   </si>
   <si>
-    <t xml:space="preserve">89.0232925415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.1324615478516</t>
+    <t xml:space="preserve">89.0233001708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.1324691772461</t>
   </si>
   <si>
     <t xml:space="preserve">92.2061386108398</t>
@@ -2741,16 +2741,16 @@
     <t xml:space="preserve">96.4499359130859</t>
   </si>
   <si>
-    <t xml:space="preserve">95.4372100830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7747955322266</t>
+    <t xml:space="preserve">95.4372253417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.774787902832</t>
   </si>
   <si>
     <t xml:space="preserve">92.4472732543945</t>
   </si>
   <si>
-    <t xml:space="preserve">92.0614624023438</t>
+    <t xml:space="preserve">92.0614547729492</t>
   </si>
   <si>
     <t xml:space="preserve">91.8685607910156</t>
@@ -2762,52 +2762,52 @@
     <t xml:space="preserve">90.7111740112305</t>
   </si>
   <si>
-    <t xml:space="preserve">90.8558349609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3863143920898</t>
+    <t xml:space="preserve">90.855842590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3863220214844</t>
   </si>
   <si>
     <t xml:space="preserve">90.759391784668</t>
   </si>
   <si>
-    <t xml:space="preserve">87.7694396972656</t>
+    <t xml:space="preserve">87.7694473266602</t>
   </si>
   <si>
     <t xml:space="preserve">88.2516937255859</t>
   </si>
   <si>
-    <t xml:space="preserve">89.3608703613281</t>
+    <t xml:space="preserve">89.3608779907227</t>
   </si>
   <si>
     <t xml:space="preserve">90.3735885620117</t>
   </si>
   <si>
-    <t xml:space="preserve">94.2798156738281</t>
+    <t xml:space="preserve">94.2798080444336</t>
   </si>
   <si>
     <t xml:space="preserve">90.0842514038086</t>
   </si>
   <si>
-    <t xml:space="preserve">91.1451950073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4954986572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.4573135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.675666809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.9167938232422</t>
+    <t xml:space="preserve">91.1451873779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.495491027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.4573211669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.6756744384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.9168014526367</t>
   </si>
   <si>
     <t xml:space="preserve">91.7238922119141</t>
   </si>
   <si>
-    <t xml:space="preserve">91.0969619750977</t>
+    <t xml:space="preserve">91.0969696044922</t>
   </si>
   <si>
     <t xml:space="preserve">90.9040679931641</t>
@@ -2819,19 +2819,19 @@
     <t xml:space="preserve">93.4599990844727</t>
   </si>
   <si>
-    <t xml:space="preserve">92.543701171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9194564819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.2670822143555</t>
+    <t xml:space="preserve">92.5437164306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9194641113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.26708984375</t>
   </si>
   <si>
     <t xml:space="preserve">93.5564346313477</t>
   </si>
   <si>
-    <t xml:space="preserve">94.5691604614258</t>
+    <t xml:space="preserve">94.5691680908203</t>
   </si>
   <si>
     <t xml:space="preserve">96.0641479492188</t>
@@ -2840,43 +2840,43 @@
     <t xml:space="preserve">98.4753952026367</t>
   </si>
   <si>
-    <t xml:space="preserve">100.018585205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.1860427856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.414436340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.790191650391</t>
+    <t xml:space="preserve">100.018592834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.1860504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.4144439697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.790184020996</t>
   </si>
   <si>
     <t xml:space="preserve">102.912078857422</t>
   </si>
   <si>
-    <t xml:space="preserve">101.465339660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.719192504883</t>
+    <t xml:space="preserve">101.46533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.719184875488</t>
   </si>
   <si>
     <t xml:space="preserve">102.526290893555</t>
   </si>
   <si>
-    <t xml:space="preserve">102.140487670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.937538146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.104988098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.587226867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.815643310547</t>
+    <t xml:space="preserve">102.140495300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.937530517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.104995727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.58723449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.815635681152</t>
   </si>
   <si>
     <t xml:space="preserve">103.201438903809</t>
@@ -2909,16 +2909,16 @@
     <t xml:space="preserve">99.3434371948242</t>
   </si>
   <si>
-    <t xml:space="preserve">101.561782836914</t>
+    <t xml:space="preserve">101.561790466309</t>
   </si>
   <si>
     <t xml:space="preserve">103.973037719727</t>
   </si>
   <si>
-    <t xml:space="preserve">103.780143737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.32332611084</t>
+    <t xml:space="preserve">103.780136108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.323333740234</t>
   </si>
   <si>
     <t xml:space="preserve">103.490791320801</t>
@@ -2933,40 +2933,40 @@
     <t xml:space="preserve">110.14582824707</t>
   </si>
   <si>
-    <t xml:space="preserve">108.699073791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.287826538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.44522857666</t>
+    <t xml:space="preserve">108.699081420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.28783416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.445236206055</t>
   </si>
   <si>
     <t xml:space="preserve">106.384284973145</t>
   </si>
   <si>
-    <t xml:space="preserve">108.891990661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.831047058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.795532226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.08487701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.059425354004</t>
+    <t xml:space="preserve">108.891983032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.831039428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.795539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.084884643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.059432983398</t>
   </si>
   <si>
     <t xml:space="preserve">107.348785400391</t>
   </si>
   <si>
-    <t xml:space="preserve">109.567138671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.506187438965</t>
+    <t xml:space="preserve">109.56713104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.50617980957</t>
   </si>
   <si>
     <t xml:space="preserve">109.530754089355</t>
@@ -2975,16 +2975,16 @@
     <t xml:space="preserve">107.786010742188</t>
   </si>
   <si>
-    <t xml:space="preserve">108.755317687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.046112060547</t>
+    <t xml:space="preserve">108.755310058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.046104431152</t>
   </si>
   <si>
     <t xml:space="preserve">109.918479919434</t>
   </si>
   <si>
-    <t xml:space="preserve">110.500053405762</t>
+    <t xml:space="preserve">110.500061035156</t>
   </si>
   <si>
     <t xml:space="preserve">109.821548461914</t>
@@ -2993,10 +2993,10 @@
     <t xml:space="preserve">110.88777923584</t>
   </si>
   <si>
-    <t xml:space="preserve">111.663215637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.117156982422</t>
+    <t xml:space="preserve">111.663208007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.117164611816</t>
   </si>
   <si>
     <t xml:space="preserve">115.831207275391</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">114.764976501465</t>
   </si>
   <si>
-    <t xml:space="preserve">114.668037414551</t>
+    <t xml:space="preserve">114.668045043945</t>
   </si>
   <si>
     <t xml:space="preserve">114.280319213867</t>
@@ -3017,7 +3017,7 @@
     <t xml:space="preserve">114.474182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">116.509712219238</t>
+    <t xml:space="preserve">116.509704589844</t>
   </si>
   <si>
     <t xml:space="preserve">121.453140258789</t>
@@ -3026,13 +3026,13 @@
     <t xml:space="preserve">126.590423583984</t>
   </si>
   <si>
-    <t xml:space="preserve">128.819808959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.365859985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.268920898438</t>
+    <t xml:space="preserve">128.819793701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.365844726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.268936157227</t>
   </si>
   <si>
     <t xml:space="preserve">128.432083129883</t>
@@ -3041,7 +3041,7 @@
     <t xml:space="preserve">133.181640625</t>
   </si>
   <si>
-    <t xml:space="preserve">130.467620849609</t>
+    <t xml:space="preserve">130.46760559082</t>
   </si>
   <si>
     <t xml:space="preserve">130.273742675781</t>
@@ -3059,19 +3059,19 @@
     <t xml:space="preserve">134.44172668457</t>
   </si>
   <si>
-    <t xml:space="preserve">133.375503540039</t>
+    <t xml:space="preserve">133.375518798828</t>
   </si>
   <si>
     <t xml:space="preserve">135.798751831055</t>
   </si>
   <si>
-    <t xml:space="preserve">135.314117431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.574188232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.212341308594</t>
+    <t xml:space="preserve">135.314102172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.574172973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.212326049805</t>
   </si>
   <si>
     <t xml:space="preserve">135.023315429688</t>
@@ -3089,13 +3089,13 @@
     <t xml:space="preserve">134.344818115234</t>
   </si>
   <si>
-    <t xml:space="preserve">138.221984863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142.293060302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.032974243164</t>
+    <t xml:space="preserve">138.22200012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142.293045043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.032958984375</t>
   </si>
   <si>
     <t xml:space="preserve">143.359283447266</t>
@@ -3110,7 +3110,7 @@
     <t xml:space="preserve">140.548309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">140.160614013672</t>
+    <t xml:space="preserve">140.160598754883</t>
   </si>
   <si>
     <t xml:space="preserve">139.579010009766</t>
@@ -3146,7 +3146,7 @@
     <t xml:space="preserve">142.486923217773</t>
   </si>
   <si>
-    <t xml:space="preserve">146.073333740234</t>
+    <t xml:space="preserve">146.073318481445</t>
   </si>
   <si>
     <t xml:space="preserve">148.884292602539</t>
@@ -3155,19 +3155,19 @@
     <t xml:space="preserve">148.011917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">149.175064086914</t>
+    <t xml:space="preserve">149.175079345703</t>
   </si>
   <si>
     <t xml:space="preserve">149.756652832031</t>
   </si>
   <si>
-    <t xml:space="preserve">146.364105224609</t>
+    <t xml:space="preserve">146.36408996582</t>
   </si>
   <si>
     <t xml:space="preserve">147.236465454102</t>
   </si>
   <si>
-    <t xml:space="preserve">148.205780029297</t>
+    <t xml:space="preserve">148.205764770508</t>
   </si>
   <si>
     <t xml:space="preserve">147.818054199219</t>
@@ -3176,7 +3176,7 @@
     <t xml:space="preserve">150.532104492188</t>
   </si>
   <si>
-    <t xml:space="preserve">150.629013061523</t>
+    <t xml:space="preserve">150.629028320312</t>
   </si>
   <si>
     <t xml:space="preserve">155.087783813477</t>
@@ -3191,13 +3191,13 @@
     <t xml:space="preserve">157.89875793457</t>
   </si>
   <si>
-    <t xml:space="preserve">161.679046630859</t>
+    <t xml:space="preserve">161.67903137207</t>
   </si>
   <si>
     <t xml:space="preserve">166.816329956055</t>
   </si>
   <si>
-    <t xml:space="preserve">166.428588867188</t>
+    <t xml:space="preserve">166.428604125977</t>
   </si>
   <si>
     <t xml:space="preserve">165.847015380859</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">165.45930480957</t>
   </si>
   <si>
-    <t xml:space="preserve">165.65315246582</t>
+    <t xml:space="preserve">165.653137207031</t>
   </si>
   <si>
     <t xml:space="preserve">167.397888183594</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">169.142623901367</t>
   </si>
   <si>
-    <t xml:space="preserve">169.627288818359</t>
+    <t xml:space="preserve">169.62727355957</t>
   </si>
   <si>
     <t xml:space="preserve">170.305786132812</t>
@@ -3245,16 +3245,16 @@
     <t xml:space="preserve">167.979476928711</t>
   </si>
   <si>
-    <t xml:space="preserve">173.989120483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.606231689453</t>
+    <t xml:space="preserve">173.989105224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.606216430664</t>
   </si>
   <si>
     <t xml:space="preserve">171.372009277344</t>
   </si>
   <si>
-    <t xml:space="preserve">152.470703125</t>
+    <t xml:space="preserve">152.470687866211</t>
   </si>
   <si>
     <t xml:space="preserve">152.567611694336</t>
@@ -3263,10 +3263,10 @@
     <t xml:space="preserve">154.506210327148</t>
   </si>
   <si>
-    <t xml:space="preserve">153.827682495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.465866088867</t>
+    <t xml:space="preserve">153.827697753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.465850830078</t>
   </si>
   <si>
     <t xml:space="preserve">153.633865356445</t>
@@ -3293,22 +3293,22 @@
     <t xml:space="preserve">163.229888916016</t>
   </si>
   <si>
-    <t xml:space="preserve">160.4189453125</t>
+    <t xml:space="preserve">160.418930053711</t>
   </si>
   <si>
     <t xml:space="preserve">161.097442626953</t>
   </si>
   <si>
-    <t xml:space="preserve">160.806655883789</t>
+    <t xml:space="preserve">160.806640625</t>
   </si>
   <si>
     <t xml:space="preserve">160.612808227539</t>
   </si>
   <si>
-    <t xml:space="preserve">161.582092285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.551391601562</t>
+    <t xml:space="preserve">161.582107543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.551376342773</t>
   </si>
   <si>
     <t xml:space="preserve">161.872894287109</t>
@@ -3317,10 +3317,10 @@
     <t xml:space="preserve">164.393081665039</t>
   </si>
   <si>
-    <t xml:space="preserve">171.27507019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.213684082031</t>
+    <t xml:space="preserve">171.275085449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.213668823242</t>
   </si>
   <si>
     <t xml:space="preserve">172.825973510742</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">174.182983398438</t>
   </si>
   <si>
-    <t xml:space="preserve">171.662811279297</t>
+    <t xml:space="preserve">171.662826538086</t>
   </si>
   <si>
     <t xml:space="preserve">172.341323852539</t>
@@ -3338,7 +3338,7 @@
     <t xml:space="preserve">176.703155517578</t>
   </si>
   <si>
-    <t xml:space="preserve">179.804931640625</t>
+    <t xml:space="preserve">179.804916381836</t>
   </si>
   <si>
     <t xml:space="preserve">173.892181396484</t>
@@ -3347,16 +3347,16 @@
     <t xml:space="preserve">168.754913330078</t>
   </si>
   <si>
-    <t xml:space="preserve">168.56103515625</t>
+    <t xml:space="preserve">168.561050415039</t>
   </si>
   <si>
     <t xml:space="preserve">167.010177612305</t>
   </si>
   <si>
-    <t xml:space="preserve">159.934280395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.454467773438</t>
+    <t xml:space="preserve">159.934295654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.454483032227</t>
   </si>
   <si>
     <t xml:space="preserve">159.837356567383</t>
@@ -3377,13 +3377,13 @@
     <t xml:space="preserve">159.158843994141</t>
   </si>
   <si>
-    <t xml:space="preserve">172.53515625</t>
+    <t xml:space="preserve">172.535171508789</t>
   </si>
   <si>
     <t xml:space="preserve">174.958435058594</t>
   </si>
   <si>
-    <t xml:space="preserve">173.698348999023</t>
+    <t xml:space="preserve">173.698333740234</t>
   </si>
   <si>
     <t xml:space="preserve">174.570693969727</t>
@@ -3401,16 +3401,16 @@
     <t xml:space="preserve">164.877731323242</t>
   </si>
   <si>
-    <t xml:space="preserve">163.714553833008</t>
+    <t xml:space="preserve">163.714569091797</t>
   </si>
   <si>
     <t xml:space="preserve">170.596572875977</t>
   </si>
   <si>
-    <t xml:space="preserve">169.82112121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.473785400391</t>
+    <t xml:space="preserve">169.821136474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.473770141602</t>
   </si>
   <si>
     <t xml:space="preserve">164.005340576172</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">157.317184448242</t>
   </si>
   <si>
-    <t xml:space="preserve">155.572463989258</t>
+    <t xml:space="preserve">155.572448730469</t>
   </si>
   <si>
     <t xml:space="preserve">155.863235473633</t>
@@ -3431,13 +3431,13 @@
     <t xml:space="preserve">153.149200439453</t>
   </si>
   <si>
-    <t xml:space="preserve">151.016738891602</t>
+    <t xml:space="preserve">151.016754150391</t>
   </si>
   <si>
     <t xml:space="preserve">157.220260620117</t>
   </si>
   <si>
-    <t xml:space="preserve">151.113677978516</t>
+    <t xml:space="preserve">151.113662719727</t>
   </si>
   <si>
     <t xml:space="preserve">152.858413696289</t>
@@ -3458,19 +3458,19 @@
     <t xml:space="preserve">144.522430419922</t>
   </si>
   <si>
-    <t xml:space="preserve">144.910171508789</t>
+    <t xml:space="preserve">144.910186767578</t>
   </si>
   <si>
     <t xml:space="preserve">139.385177612305</t>
   </si>
   <si>
-    <t xml:space="preserve">136.089538574219</t>
+    <t xml:space="preserve">136.089553833008</t>
   </si>
   <si>
     <t xml:space="preserve">132.600067138672</t>
   </si>
   <si>
-    <t xml:space="preserve">132.309265136719</t>
+    <t xml:space="preserve">132.309280395508</t>
   </si>
   <si>
     <t xml:space="preserve">138.997421264648</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">137.543487548828</t>
   </si>
   <si>
-    <t xml:space="preserve">138.125091552734</t>
+    <t xml:space="preserve">138.125076293945</t>
   </si>
   <si>
     <t xml:space="preserve">138.512786865234</t>
@@ -3497,7 +3497,7 @@
     <t xml:space="preserve">125.039535522461</t>
   </si>
   <si>
-    <t xml:space="preserve">136.961898803711</t>
+    <t xml:space="preserve">136.9619140625</t>
   </si>
   <si>
     <t xml:space="preserve">135.507965087891</t>
@@ -3506,7 +3506,7 @@
     <t xml:space="preserve">142.874633789062</t>
   </si>
   <si>
-    <t xml:space="preserve">149.562789916992</t>
+    <t xml:space="preserve">149.562805175781</t>
   </si>
   <si>
     <t xml:space="preserve">151.986038208008</t>
@@ -3518,7 +3518,7 @@
     <t xml:space="preserve">149.368942260742</t>
   </si>
   <si>
-    <t xml:space="preserve">146.267181396484</t>
+    <t xml:space="preserve">146.267166137695</t>
   </si>
   <si>
     <t xml:space="preserve">145.10400390625</t>
@@ -3542,10 +3542,10 @@
     <t xml:space="preserve">141.517623901367</t>
   </si>
   <si>
-    <t xml:space="preserve">141.323745727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.058837890625</t>
+    <t xml:space="preserve">141.323760986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.058822631836</t>
   </si>
   <si>
     <t xml:space="preserve">134.538665771484</t>
@@ -3557,10 +3557,10 @@
     <t xml:space="preserve">131.824630737305</t>
   </si>
   <si>
-    <t xml:space="preserve">136.186477661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.217163085938</t>
+    <t xml:space="preserve">136.186462402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.217178344727</t>
   </si>
   <si>
     <t xml:space="preserve">130.952255249023</t>
@@ -3569,7 +3569,7 @@
     <t xml:space="preserve">127.75358581543</t>
   </si>
   <si>
-    <t xml:space="preserve">121.162353515625</t>
+    <t xml:space="preserve">121.16234588623</t>
   </si>
   <si>
     <t xml:space="preserve">113.601806640625</t>
@@ -3581,16 +3581,16 @@
     <t xml:space="preserve">114.958824157715</t>
   </si>
   <si>
-    <t xml:space="preserve">117.575942993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.122001647949</t>
+    <t xml:space="preserve">117.57593536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.121994018555</t>
   </si>
   <si>
     <t xml:space="preserve">119.708396911621</t>
   </si>
   <si>
-    <t xml:space="preserve">115.152702331543</t>
+    <t xml:space="preserve">115.152694702148</t>
   </si>
   <si>
     <t xml:space="preserve">114.86190032959</t>
@@ -70816,7 +70816,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6911458333</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>38785</v>
@@ -70837,6 +70837,32 @@
         <v>1820</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6910648148</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>31849</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>121.699996948242</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>120.699996948242</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>120.900001525879</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>121.599998474121</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>1784</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/REY.MI.xlsx
+++ b/data/REY.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1822" uniqueCount="1822">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1823" uniqueCount="1823">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2559719085693</t>
+    <t xml:space="preserve">29.2559700012207</t>
   </si>
   <si>
     <t xml:space="preserve">REY.MI</t>
@@ -47,37 +47,37 @@
     <t xml:space="preserve">28.8380298614502</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3272075653076</t>
+    <t xml:space="preserve">28.3272113800049</t>
   </si>
   <si>
     <t xml:space="preserve">27.6306400299072</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8396091461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2111148834229</t>
+    <t xml:space="preserve">27.8396110534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2111167907715</t>
   </si>
   <si>
     <t xml:space="preserve">29.0005626678467</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5594005584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1414566040039</t>
+    <t xml:space="preserve">28.559398651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1414585113525</t>
   </si>
   <si>
     <t xml:space="preserve">27.1198196411133</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9789237976074</t>
+    <t xml:space="preserve">27.9789257049561</t>
   </si>
   <si>
     <t xml:space="preserve">26.8644104003906</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4448833465576</t>
+    <t xml:space="preserve">27.4448852539062</t>
   </si>
   <si>
     <t xml:space="preserve">27.932487487793</t>
@@ -86,49 +86,49 @@
     <t xml:space="preserve">27.8163909912109</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2807731628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6770801544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0950183868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8628330230713</t>
+    <t xml:space="preserve">28.2807712554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6770782470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0950222015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8628273010254</t>
   </si>
   <si>
     <t xml:space="preserve">27.2591361999512</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7018775939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1678409576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2855186462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.379976272583</t>
+    <t xml:space="preserve">26.7018814086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1678428649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2855167388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3799743652344</t>
   </si>
   <si>
     <t xml:space="preserve">24.6121654510498</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0053062438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5177097320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6570243835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6074199676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3071537017822</t>
+    <t xml:space="preserve">26.0053081512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.517707824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6570224761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6074237823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3071556091309</t>
   </si>
   <si>
     <t xml:space="preserve">27.0733833312988</t>
@@ -140,46 +140,46 @@
     <t xml:space="preserve">26.4696865081787</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0517463684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7034568786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7266826629639</t>
+    <t xml:space="preserve">26.0517444610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7034587860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7266788482666</t>
   </si>
   <si>
     <t xml:space="preserve">26.7483177185059</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4929084777832</t>
+    <t xml:space="preserve">26.4929065704346</t>
   </si>
   <si>
     <t xml:space="preserve">27.3520126342773</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1894760131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2359142303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1662616729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9092693328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0237827301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5546493530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3008308410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.416919708252</t>
+    <t xml:space="preserve">27.1894779205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2359161376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1662578582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9092655181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0237808227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5546531677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3008289337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4169254302979</t>
   </si>
   <si>
     <t xml:space="preserve">29.9989795684814</t>
@@ -194,13 +194,13 @@
     <t xml:space="preserve">29.952543258667</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2311668395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7203502655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0686359405518</t>
+    <t xml:space="preserve">30.2311687469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7203521728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.068639755249</t>
   </si>
   <si>
     <t xml:space="preserve">29.8596668243408</t>
@@ -212,43 +212,43 @@
     <t xml:space="preserve">29.3256301879883</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4881610870361</t>
+    <t xml:space="preserve">29.4881629943848</t>
   </si>
   <si>
     <t xml:space="preserve">29.5113792419434</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2095336914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1615161895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3720684051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5345993041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4433059692383</t>
+    <t xml:space="preserve">29.2095317840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1615104675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3720664978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5345973968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4433040618896</t>
   </si>
   <si>
     <t xml:space="preserve">28.6754951477051</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8612499237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8148078918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9076843261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6290607452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4200878143311</t>
+    <t xml:space="preserve">28.8612518310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8148097991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9076881408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.629056930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4200897216797</t>
   </si>
   <si>
     <t xml:space="preserve">28.6775989532471</t>
@@ -257,91 +257,91 @@
     <t xml:space="preserve">28.560546875</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0287532806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3264427185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.513729095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7946510314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0053424835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2628574371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1992683410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5036029815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5504245758057</t>
+    <t xml:space="preserve">29.0287551879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3264465332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5137252807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7946529388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0053443908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2628536224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1992702484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5036010742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.550422668457</t>
   </si>
   <si>
     <t xml:space="preserve">30.9015808105469</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6674709320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7142944335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4567794799805</t>
+    <t xml:space="preserve">30.6674766540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7142925262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4567852020264</t>
   </si>
   <si>
     <t xml:space="preserve">30.4333724975586</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2695007324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8949317932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1859817504883</t>
+    <t xml:space="preserve">30.2695026397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8949356079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1859836578369</t>
   </si>
   <si>
     <t xml:space="preserve">29.3096771240234</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4969615936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6943664550781</t>
+    <t xml:space="preserve">29.4969577789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6943702697754</t>
   </si>
   <si>
     <t xml:space="preserve">25.7747230529785</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8047771453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3198051452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9218273162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5070858001709</t>
+    <t xml:space="preserve">26.8047752380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.319803237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9218292236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5070838928223</t>
   </si>
   <si>
     <t xml:space="preserve">26.9452381134033</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8215465545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.219518661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1091079711914</t>
+    <t xml:space="preserve">25.8215427398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2195205688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.10910987854</t>
   </si>
   <si>
     <t xml:space="preserve">27.624137878418</t>
@@ -350,40 +350,40 @@
     <t xml:space="preserve">27.3666248321533</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3030338287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8882923126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7478313446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4434967041016</t>
+    <t xml:space="preserve">28.303035736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8882884979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7478294372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4435005187988</t>
   </si>
   <si>
     <t xml:space="preserve">28.98193359375</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9117031097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3799057006836</t>
+    <t xml:space="preserve">28.9117012023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3799076080322</t>
   </si>
   <si>
     <t xml:space="preserve">29.4501399993896</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8481140136719</t>
+    <t xml:space="preserve">29.8481121063232</t>
   </si>
   <si>
     <t xml:space="preserve">30.1524486541748</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9651641845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.724422454834</t>
+    <t xml:space="preserve">29.9651660919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7244186401367</t>
   </si>
   <si>
     <t xml:space="preserve">29.1458053588867</t>
@@ -392,100 +392,100 @@
     <t xml:space="preserve">29.0989875793457</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9351100921631</t>
+    <t xml:space="preserve">28.9351139068604</t>
   </si>
   <si>
     <t xml:space="preserve">28.4903163909912</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9752960205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3732643127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0923461914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.272985458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0622901916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0388774871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8984203338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1492881774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7981357574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8917770385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7579574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.95188331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8816528320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8114204406738</t>
+    <t xml:space="preserve">27.9752902984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3732662200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0923404693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2729835510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0622863769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0388793945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.898416519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.149284362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.798131942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8917751312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7579555511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9518814086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8816471099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8114166259766</t>
   </si>
   <si>
     <t xml:space="preserve">27.9050617218018</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2963943481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8582401275635</t>
+    <t xml:space="preserve">27.2963924407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8582420349121</t>
   </si>
   <si>
     <t xml:space="preserve">27.5773181915283</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7177810668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7411861419678</t>
+    <t xml:space="preserve">27.7177772521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7411880493164</t>
   </si>
   <si>
     <t xml:space="preserve">28.0455207824707</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7880077362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3900356292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1223945617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6541900634766</t>
+    <t xml:space="preserve">27.7880058288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3900318145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1223926544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6541919708252</t>
   </si>
   <si>
     <t xml:space="preserve">28.2093944549561</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4134407043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0856971740723</t>
+    <t xml:space="preserve">27.413444519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0856990814209</t>
   </si>
   <si>
     <t xml:space="preserve">26.8515949249268</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4368534088135</t>
+    <t xml:space="preserve">27.4368495941162</t>
   </si>
   <si>
     <t xml:space="preserve">26.6877250671387</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">27.2261619567871</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8281879425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6409072875977</t>
+    <t xml:space="preserve">26.8281860351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.640905380249</t>
   </si>
   <si>
     <t xml:space="preserve">26.4536228179932</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">26.523853302002</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3365726470947</t>
+    <t xml:space="preserve">26.3365707397461</t>
   </si>
   <si>
     <t xml:space="preserve">25.7513160705566</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">24.7446689605713</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7680816650391</t>
+    <t xml:space="preserve">24.7680835723877</t>
   </si>
   <si>
     <t xml:space="preserve">24.8851356506348</t>
@@ -530,43 +530,43 @@
     <t xml:space="preserve">24.2530555725098</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0490055084229</t>
+    <t xml:space="preserve">25.0490074157715</t>
   </si>
   <si>
     <t xml:space="preserve">25.4703903198242</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5172100067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2831077575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1660556793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4469833374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0958271026611</t>
+    <t xml:space="preserve">25.5172119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.283109664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1660575866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4469776153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0958232879639</t>
   </si>
   <si>
     <t xml:space="preserve">24.9319534301758</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0724182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6342620849609</t>
+    <t xml:space="preserve">25.0724143981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6342639923096</t>
   </si>
   <si>
     <t xml:space="preserve">26.1961078643799</t>
   </si>
   <si>
-    <t xml:space="preserve">26.172700881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8348293304443</t>
+    <t xml:space="preserve">26.1726989746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.834831237793</t>
   </si>
   <si>
     <t xml:space="preserve">27.9284706115723</t>
@@ -581,70 +581,70 @@
     <t xml:space="preserve">28.6307773590088</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2160377502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3330898284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8648853302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3498573303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6073703765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4735507965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2394485473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7076511383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4267292022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8313426971436</t>
+    <t xml:space="preserve">29.2160358428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3330879211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8648815155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.349853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6073684692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4735469818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2394466400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7076530456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4267253875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8313407897949</t>
   </si>
   <si>
     <t xml:space="preserve">30.9952182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4868335723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2527351379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3697834014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1356792449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1891441345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3061904907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2660179138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0619659423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6472244262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4599380493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7408599853516</t>
+    <t xml:space="preserve">31.4868297576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2527332305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3697853088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1356773376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1891403198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3061943054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2660217285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0619621276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6472282409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4599456787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7408638000488</t>
   </si>
   <si>
     <t xml:space="preserve">34.6706352233887</t>
@@ -653,22 +653,22 @@
     <t xml:space="preserve">34.9983825683594</t>
   </si>
   <si>
-    <t xml:space="preserve">34.85791015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1790161132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.764274597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8813247680664</t>
+    <t xml:space="preserve">34.8579177856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1790199279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7642784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8813323974609</t>
   </si>
   <si>
     <t xml:space="preserve">34.389705657959</t>
   </si>
   <si>
-    <t xml:space="preserve">34.4131278991699</t>
+    <t xml:space="preserve">34.4131202697754</t>
   </si>
   <si>
     <t xml:space="preserve">35.6070442199707</t>
@@ -677,91 +677,91 @@
     <t xml:space="preserve">35.4665832519531</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7943305969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.8243751525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6671485900879</t>
+    <t xml:space="preserve">35.7943229675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.8243827819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6671524047852</t>
   </si>
   <si>
     <t xml:space="preserve">37.8778419494629</t>
   </si>
   <si>
-    <t xml:space="preserve">36.9882469177246</t>
+    <t xml:space="preserve">36.9882507324219</t>
   </si>
   <si>
     <t xml:space="preserve">37.5735054016113</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6203308105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6085357666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7264366149902</t>
+    <t xml:space="preserve">37.6203269958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6085395812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.726432800293</t>
   </si>
   <si>
     <t xml:space="preserve">37.9150695800781</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1980094909668</t>
+    <t xml:space="preserve">38.1980171203613</t>
   </si>
   <si>
     <t xml:space="preserve">37.9386444091797</t>
   </si>
   <si>
-    <t xml:space="preserve">38.1508560180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4906425476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0232772827148</t>
+    <t xml:space="preserve">38.1508598327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.490650177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0232810974121</t>
   </si>
   <si>
     <t xml:space="preserve">40.0843353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0607528686523</t>
+    <t xml:space="preserve">40.0607566833496</t>
   </si>
   <si>
     <t xml:space="preserve">39.8013916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">41.2397079467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0274963378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4519271850586</t>
+    <t xml:space="preserve">41.2397041320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0274925231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4519233703613</t>
   </si>
   <si>
     <t xml:space="preserve">41.7112846374512</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4990768432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8056030273438</t>
+    <t xml:space="preserve">41.4990730285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.805606842041</t>
   </si>
   <si>
     <t xml:space="preserve">42.3243446350098</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1828727722168</t>
+    <t xml:space="preserve">42.1828689575195</t>
   </si>
   <si>
     <t xml:space="preserve">42.0885543823242</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2771949768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8291816711426</t>
+    <t xml:space="preserve">42.2771911621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8291854858398</t>
   </si>
   <si>
     <t xml:space="preserve">39.9664421081543</t>
@@ -770,43 +770,43 @@
     <t xml:space="preserve">39.5891799926758</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4338073730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.999698638916</t>
+    <t xml:space="preserve">38.4338035583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9997024536133</t>
   </si>
   <si>
     <t xml:space="preserve">39.6363334655762</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9428634643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4380264282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.551700592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0565376281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1411743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3298110961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.070442199707</t>
+    <t xml:space="preserve">39.9428596496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4380226135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.5516967773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0565414428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1411819458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3298072814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0704383850098</t>
   </si>
   <si>
     <t xml:space="preserve">39.1647567749023</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6695938110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8346519470215</t>
+    <t xml:space="preserve">38.6695976257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.834644317627</t>
   </si>
   <si>
     <t xml:space="preserve">38.905387878418</t>
@@ -824,7 +824,7 @@
     <t xml:space="preserve">38.7403297424316</t>
   </si>
   <si>
-    <t xml:space="preserve">38.6931762695312</t>
+    <t xml:space="preserve">38.6931800842285</t>
   </si>
   <si>
     <t xml:space="preserve">39.2354927062988</t>
@@ -833,61 +833,61 @@
     <t xml:space="preserve">39.2590675354004</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1357154846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5129737854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7765579223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8001365661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5075149536133</t>
+    <t xml:space="preserve">42.1357078552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5129776000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7765617370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8001441955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.507511138916</t>
   </si>
   <si>
     <t xml:space="preserve">45.3188781738281</t>
   </si>
   <si>
-    <t xml:space="preserve">45.814037322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6822509765625</t>
+    <t xml:space="preserve">45.8140411376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.682243347168</t>
   </si>
   <si>
     <t xml:space="preserve">43.7862434387207</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7529792785645</t>
+    <t xml:space="preserve">44.7529830932617</t>
   </si>
   <si>
     <t xml:space="preserve">45.1302452087402</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4464530944824</t>
+    <t xml:space="preserve">44.4464569091797</t>
   </si>
   <si>
     <t xml:space="preserve">44.5879287719727</t>
   </si>
   <si>
-    <t xml:space="preserve">44.3285636901855</t>
+    <t xml:space="preserve">44.3285598754883</t>
   </si>
   <si>
     <t xml:space="preserve">44.3049812316895</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6211891174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1731910705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0788764953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5837173461914</t>
+    <t xml:space="preserve">43.6211929321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1731872558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0788688659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5837097167969</t>
   </si>
   <si>
     <t xml:space="preserve">43.267505645752</t>
@@ -896,10 +896,10 @@
     <t xml:space="preserve">45.3660354614258</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9887733459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4936141967773</t>
+    <t xml:space="preserve">44.9887771606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4936180114746</t>
   </si>
   <si>
     <t xml:space="preserve">44.5171966552734</t>
@@ -908,67 +908,67 @@
     <t xml:space="preserve">45.6254081726074</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8611946105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4035110473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5824699401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0637283325195</t>
+    <t xml:space="preserve">45.861198425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4035186767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5824661254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0637245178223</t>
   </si>
   <si>
     <t xml:space="preserve">47.134464263916</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1580429077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9125709533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3508911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7378387451172</t>
+    <t xml:space="preserve">47.1580390930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9125747680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3508949279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7378349304199</t>
   </si>
   <si>
     <t xml:space="preserve">48.101203918457</t>
   </si>
   <si>
-    <t xml:space="preserve">48.8321533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6296272277832</t>
+    <t xml:space="preserve">48.8321571350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6296195983887</t>
   </si>
   <si>
     <t xml:space="preserve">48.0540466308594</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8654098510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9597282409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1858367919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2717208862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0359344482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.5643539428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.9748764038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.560131072998</t>
+    <t xml:space="preserve">47.8654136657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9597320556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1858406066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2717247009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0359306335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.5643501281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.9748725891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5601387023926</t>
   </si>
   <si>
     <t xml:space="preserve">42.913818359375</t>
@@ -977,43 +977,43 @@
     <t xml:space="preserve">42.7251892089844</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2064476013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4328079223633</t>
+    <t xml:space="preserve">42.2064514160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.432804107666</t>
   </si>
   <si>
     <t xml:space="preserve">42.1781539916992</t>
   </si>
   <si>
-    <t xml:space="preserve">43.3476753234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9800872802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3010177612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0838394165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7534828186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5931396484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4799728393555</t>
+    <t xml:space="preserve">43.3476715087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9800796508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3010139465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0838356018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7534790039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.593147277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4799652099609</t>
   </si>
   <si>
     <t xml:space="preserve">43.0081367492676</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0458641052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3288078308105</t>
+    <t xml:space="preserve">43.0458602905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3288040161133</t>
   </si>
   <si>
     <t xml:space="preserve">41.3953323364258</t>
@@ -1022,31 +1022,31 @@
     <t xml:space="preserve">43.4891471862793</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2342491149902</t>
+    <t xml:space="preserve">44.2342414855957</t>
   </si>
   <si>
     <t xml:space="preserve">44.1210632324219</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2439231872559</t>
+    <t xml:space="preserve">43.2439270019531</t>
   </si>
   <si>
     <t xml:space="preserve">42.1027030944824</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1689720153809</t>
+    <t xml:space="preserve">41.1689758300781</t>
   </si>
   <si>
     <t xml:space="preserve">40.2729721069336</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4045066833496</t>
+    <t xml:space="preserve">42.4045104980469</t>
   </si>
   <si>
     <t xml:space="preserve">43.7626647949219</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2531089782715</t>
+    <t xml:space="preserve">44.253101348877</t>
   </si>
   <si>
     <t xml:space="preserve">45.0547943115234</t>
@@ -1058,13 +1058,13 @@
     <t xml:space="preserve">46.2809028625488</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1488647460938</t>
+    <t xml:space="preserve">46.1488609313965</t>
   </si>
   <si>
     <t xml:space="preserve">45.3094482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9982070922852</t>
+    <t xml:space="preserve">44.9982032775879</t>
   </si>
   <si>
     <t xml:space="preserve">45.5358047485352</t>
@@ -1079,28 +1079,28 @@
     <t xml:space="preserve">44.6586647033691</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2533531188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6683464050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2248153686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0830841064453</t>
+    <t xml:space="preserve">43.2533569335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6683502197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2248115539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0830917358398</t>
   </si>
   <si>
     <t xml:space="preserve">45.2056999206543</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3280601501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0356864929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6584167480469</t>
+    <t xml:space="preserve">46.328067779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0356826782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6584205627441</t>
   </si>
   <si>
     <t xml:space="preserve">45.5169410705566</t>
@@ -1121,43 +1121,43 @@
     <t xml:space="preserve">44.4606018066406</t>
   </si>
   <si>
-    <t xml:space="preserve">45.611255645752</t>
+    <t xml:space="preserve">45.6112594604492</t>
   </si>
   <si>
     <t xml:space="preserve">45.6301231384277</t>
   </si>
   <si>
-    <t xml:space="preserve">45.724437713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.290340423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0262565612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2148818969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.648738861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.705322265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5921516418457</t>
+    <t xml:space="preserve">45.7244338989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2903327941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0262489318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2148857116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6487312316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7053260803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5921478271484</t>
   </si>
   <si>
     <t xml:space="preserve">46.8939552307129</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7710952758789</t>
+    <t xml:space="preserve">47.7710990905762</t>
   </si>
   <si>
     <t xml:space="preserve">47.8182563781738</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1955146789551</t>
+    <t xml:space="preserve">48.1955223083496</t>
   </si>
   <si>
     <t xml:space="preserve">48.9972114562988</t>
@@ -1166,16 +1166,16 @@
     <t xml:space="preserve">48.5727844238281</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3273086547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3176307678223</t>
+    <t xml:space="preserve">49.3273124694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.317626953125</t>
   </si>
   <si>
     <t xml:space="preserve">50.4119491577148</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8460464477539</t>
+    <t xml:space="preserve">49.8460540771484</t>
   </si>
   <si>
     <t xml:space="preserve">49.3744697570801</t>
@@ -1184,40 +1184,40 @@
     <t xml:space="preserve">50.2233123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">50.081844329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5353126525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1960258483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2052001953125</t>
+    <t xml:space="preserve">50.0818405151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5353050231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1960144042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2052040100098</t>
   </si>
   <si>
     <t xml:space="preserve">48.0068855285645</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2523612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4223747253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8376197814941</t>
+    <t xml:space="preserve">47.2523574829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4223785400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8376121520996</t>
   </si>
   <si>
     <t xml:space="preserve">45.6489868164062</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8753471374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5732841491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.4687881469727</t>
+    <t xml:space="preserve">45.8753509521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5732879638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.4687919616699</t>
   </si>
   <si>
     <t xml:space="preserve">48.8085746765137</t>
@@ -1232,100 +1232,100 @@
     <t xml:space="preserve">46.5166931152344</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1774101257324</t>
+    <t xml:space="preserve">45.1774063110352</t>
   </si>
   <si>
     <t xml:space="preserve">44.7812805175781</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8378677368164</t>
+    <t xml:space="preserve">44.8378639221191</t>
   </si>
   <si>
     <t xml:space="preserve">44.4983291625977</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1776504516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8952026367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.291332244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4988250732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0652198791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9517936706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3283157348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4414863586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4603462219238</t>
+    <t xml:space="preserve">44.1776580810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.895206451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2913360595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.498836517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0652236938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.951789855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.328311920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4414939880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4603538513184</t>
   </si>
   <si>
     <t xml:space="preserve">45.4037666320801</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1017074584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.988525390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3846473693848</t>
+    <t xml:space="preserve">46.1017036437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9885215759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.384651184082</t>
   </si>
   <si>
     <t xml:space="preserve">49.0443649291992</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9028930664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.2898330688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1193237304688</t>
+    <t xml:space="preserve">48.902889251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.2898368835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1193199157715</t>
   </si>
   <si>
     <t xml:space="preserve">50.6948928833008</t>
   </si>
   <si>
-    <t xml:space="preserve">50.6005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.932861328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4107093811035</t>
+    <t xml:space="preserve">50.6005821228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9328536987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4107131958008</t>
   </si>
   <si>
     <t xml:space="preserve">51.0277900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">52.2144813537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1195487976074</t>
+    <t xml:space="preserve">52.2144889831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1195526123047</t>
   </si>
   <si>
     <t xml:space="preserve">51.7398071289062</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8410949707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5024681091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2714881896973</t>
+    <t xml:space="preserve">49.8410987854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5024719238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.271484375</t>
   </si>
   <si>
     <t xml:space="preserve">49.3664207458496</t>
@@ -1337,16 +1337,16 @@
     <t xml:space="preserve">49.7936325073242</t>
   </si>
   <si>
-    <t xml:space="preserve">48.2746620178223</t>
+    <t xml:space="preserve">48.2746658325195</t>
   </si>
   <si>
     <t xml:space="preserve">46.822151184082</t>
   </si>
   <si>
-    <t xml:space="preserve">48.0847930908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6544075012207</t>
+    <t xml:space="preserve">48.0847969055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6544036865234</t>
   </si>
   <si>
     <t xml:space="preserve">49.3189544677734</t>
@@ -1358,40 +1358,40 @@
     <t xml:space="preserve">49.9835014343262</t>
   </si>
   <si>
-    <t xml:space="preserve">50.3632431030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.217658996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1733665466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.455005645752</t>
+    <t xml:space="preserve">50.3632392883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2176666259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1733703613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4549980163574</t>
   </si>
   <si>
     <t xml:space="preserve">52.0246124267578</t>
   </si>
   <si>
-    <t xml:space="preserve">53.068904876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.7840919494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4422912597656</t>
+    <t xml:space="preserve">53.0689086914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.7840995788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4422874450684</t>
   </si>
   <si>
     <t xml:space="preserve">54.682804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1100120544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5846862792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3916435241699</t>
+    <t xml:space="preserve">55.1100158691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5846939086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3916473388672</t>
   </si>
   <si>
     <t xml:space="preserve">54.7302742004395</t>
@@ -1400,10 +1400,10 @@
     <t xml:space="preserve">55.0625495910645</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4897537231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2524147033691</t>
+    <t xml:space="preserve">55.4897575378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.2524185180664</t>
   </si>
   <si>
     <t xml:space="preserve">53.1638374328613</t>
@@ -1412,10 +1412,10 @@
     <t xml:space="preserve">53.6385154724121</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0182571411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3030662536621</t>
+    <t xml:space="preserve">54.0182609558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3030624389648</t>
   </si>
   <si>
     <t xml:space="preserve">54.1131896972656</t>
@@ -1424,10 +1424,10 @@
     <t xml:space="preserve">53.8283882141113</t>
   </si>
   <si>
-    <t xml:space="preserve">54.7777404785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4391136169434</t>
+    <t xml:space="preserve">54.7777442932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4391098022461</t>
   </si>
   <si>
     <t xml:space="preserve">56.9137878417969</t>
@@ -1436,67 +1436,67 @@
     <t xml:space="preserve">56.2967071533203</t>
   </si>
   <si>
-    <t xml:space="preserve">56.0119018554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2017784118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5340461730957</t>
+    <t xml:space="preserve">56.011905670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2017707824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5340423583984</t>
   </si>
   <si>
     <t xml:space="preserve">56.6764526367188</t>
   </si>
   <si>
-    <t xml:space="preserve">54.9676094055176</t>
+    <t xml:space="preserve">54.9676132202148</t>
   </si>
   <si>
     <t xml:space="preserve">52.5942306518555</t>
   </si>
   <si>
-    <t xml:space="preserve">53.0214347839355</t>
+    <t xml:space="preserve">53.0214309692383</t>
   </si>
   <si>
     <t xml:space="preserve">55.1574783325195</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3505325317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9264984130859</t>
+    <t xml:space="preserve">54.350528717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9264945983887</t>
   </si>
   <si>
     <t xml:space="preserve">52.8790321350098</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0657234191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5878639221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4486389160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.6859817504883</t>
+    <t xml:space="preserve">54.0657272338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5878715515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4486465454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.6859893798828</t>
   </si>
   <si>
     <t xml:space="preserve">53.3062438964844</t>
   </si>
   <si>
-    <t xml:space="preserve">52.404354095459</t>
+    <t xml:space="preserve">52.4043579101562</t>
   </si>
   <si>
     <t xml:space="preserve">51.0752563476562</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4581832885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.2619514465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8822059631348</t>
+    <t xml:space="preserve">50.458179473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.2619476318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8822174072266</t>
   </si>
   <si>
     <t xml:space="preserve">54.1606597900391</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">53.5435791015625</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5404052734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2049522399902</t>
+    <t xml:space="preserve">54.5404014587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.204948425293</t>
   </si>
   <si>
     <t xml:space="preserve">56.2492370605469</t>
@@ -1526,16 +1526,16 @@
     <t xml:space="preserve">57.9106101989746</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9612579345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.790454864502</t>
+    <t xml:space="preserve">56.961254119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7904586791992</t>
   </si>
   <si>
     <t xml:space="preserve">49.4138870239258</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0120162963867</t>
+    <t xml:space="preserve">47.0120239257812</t>
   </si>
   <si>
     <t xml:space="preserve">47.0499992370605</t>
@@ -1547,13 +1547,13 @@
     <t xml:space="preserve">47.4677085876465</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0309677124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3157730102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3474769592285</t>
+    <t xml:space="preserve">50.0309715270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3157768249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3474731445312</t>
   </si>
   <si>
     <t xml:space="preserve">44.7525596618652</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">44.6766128540039</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6956062316895</t>
+    <t xml:space="preserve">44.6956024169922</t>
   </si>
   <si>
     <t xml:space="preserve">46.1955757141113</t>
@@ -1571,16 +1571,16 @@
     <t xml:space="preserve">46.5563354492188</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4803848266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9487457275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4107513427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5373458862305</t>
+    <t xml:space="preserve">46.4803810119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9487495422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4107475280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5373497009277</t>
   </si>
   <si>
     <t xml:space="preserve">46.5183601379395</t>
@@ -1589,10 +1589,10 @@
     <t xml:space="preserve">46.7462005615234</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4424057006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4930572509766</t>
+    <t xml:space="preserve">46.4424095153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4930534362793</t>
   </si>
   <si>
     <t xml:space="preserve">45.1323013305664</t>
@@ -1601,55 +1601,55 @@
     <t xml:space="preserve">45.5690040588379</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7019119262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3601875305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4677925109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9234848022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8728370666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7462425231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2968673706055</t>
+    <t xml:space="preserve">45.7019195556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3601913452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4678001403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9234886169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8728332519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7462501525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2968635559082</t>
   </si>
   <si>
     <t xml:space="preserve">43.8601684570312</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7208938598633</t>
+    <t xml:space="preserve">45.7209014892578</t>
   </si>
   <si>
     <t xml:space="preserve">46.7841758728027</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7050476074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2398643493652</t>
+    <t xml:space="preserve">47.7050514221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.239860534668</t>
   </si>
   <si>
     <t xml:space="preserve">46.2905120849609</t>
   </si>
   <si>
-    <t xml:space="preserve">45.189266204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2082443237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2841987609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3158149719238</t>
+    <t xml:space="preserve">45.1892623901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2082481384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2842025756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3158187866211</t>
   </si>
   <si>
     <t xml:space="preserve">47.3727798461914</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">41.5627288818359</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2146453857422</t>
+    <t xml:space="preserve">40.2146492004395</t>
   </si>
   <si>
     <t xml:space="preserve">41.847541809082</t>
@@ -1688,10 +1688,10 @@
     <t xml:space="preserve">41.8095588684082</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1956176757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0310554504395</t>
+    <t xml:space="preserve">43.1956214904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0310478210449</t>
   </si>
   <si>
     <t xml:space="preserve">44.3158531188965</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">43.8791580200195</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7398872375488</t>
+    <t xml:space="preserve">45.7398910522461</t>
   </si>
   <si>
     <t xml:space="preserve">45.8348236083984</t>
@@ -1715,13 +1715,13 @@
     <t xml:space="preserve">46.3854484558105</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4234237670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1829032897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1765480041504</t>
+    <t xml:space="preserve">46.4234275817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1829071044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1765518188477</t>
   </si>
   <si>
     <t xml:space="preserve">48.3695945739746</t>
@@ -1736,40 +1736,40 @@
     <t xml:space="preserve">45.6449546813965</t>
   </si>
   <si>
-    <t xml:space="preserve">47.2588577270508</t>
+    <t xml:space="preserve">47.2588539123535</t>
   </si>
   <si>
     <t xml:space="preserve">48.4645385742188</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8885650634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.125904083252</t>
+    <t xml:space="preserve">49.8885688781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1259002685547</t>
   </si>
   <si>
     <t xml:space="preserve">50.6955146789551</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2208404541016</t>
+    <t xml:space="preserve">50.2208366394043</t>
   </si>
   <si>
     <t xml:space="preserve">49.93603515625</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0784378051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1670188903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6891632080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9739685058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.2555961608887</t>
+    <t xml:space="preserve">50.078441619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1670150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6891593933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9739646911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.2555923461914</t>
   </si>
   <si>
     <t xml:space="preserve">53.2587738037109</t>
@@ -1778,115 +1778,115 @@
     <t xml:space="preserve">53.9707870483398</t>
   </si>
   <si>
-    <t xml:space="preserve">53.7334518432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2998847961426</t>
+    <t xml:space="preserve">53.7334480285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.2998886108398</t>
   </si>
   <si>
     <t xml:space="preserve">54.3980026245117</t>
   </si>
   <si>
-    <t xml:space="preserve">53.401180267334</t>
+    <t xml:space="preserve">53.4011726379395</t>
   </si>
   <si>
     <t xml:space="preserve">53.9233207702637</t>
   </si>
   <si>
-    <t xml:space="preserve">54.4929389953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4454612731934</t>
+    <t xml:space="preserve">54.4929351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4454650878906</t>
   </si>
   <si>
     <t xml:space="preserve">53.4961128234863</t>
   </si>
   <si>
-    <t xml:space="preserve">54.6353378295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.964427947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.7270965576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1068344116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5328483581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5239105224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5717430114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6151008605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5194435119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4671401977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5283851623535</t>
+    <t xml:space="preserve">54.6353340148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.9644393920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.7270927429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1068305969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5328521728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5239143371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5717391967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6151084899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5194473266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4671363830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5283813476562</t>
   </si>
   <si>
     <t xml:space="preserve">55.9633407592773</t>
   </si>
   <si>
-    <t xml:space="preserve">56.0589981079102</t>
+    <t xml:space="preserve">56.0590019226074</t>
   </si>
   <si>
     <t xml:space="preserve">55.1980285644531</t>
   </si>
   <si>
-    <t xml:space="preserve">56.7764778137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0111656188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.6285171508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2024993896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.9155082702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4416580200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5806846618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3459968566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1501998901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5762100219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4327125549316</t>
+    <t xml:space="preserve">56.776481628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.011173248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.6285133361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2025032043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.9155120849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4416618347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.580680847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3459930419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1501960754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5762176513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4327201843262</t>
   </si>
   <si>
     <t xml:space="preserve">54.8632011413574</t>
   </si>
   <si>
-    <t xml:space="preserve">56.919979095459</t>
+    <t xml:space="preserve">56.9199829101562</t>
   </si>
   <si>
     <t xml:space="preserve">56.8243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">57.2547988891602</t>
+    <t xml:space="preserve">57.2547950744629</t>
   </si>
   <si>
     <t xml:space="preserve">56.6808166503906</t>
@@ -1895,31 +1895,31 @@
     <t xml:space="preserve">56.7286491394043</t>
   </si>
   <si>
-    <t xml:space="preserve">58.2114334106445</t>
+    <t xml:space="preserve">58.2114410400391</t>
   </si>
   <si>
     <t xml:space="preserve">57.6374588012695</t>
   </si>
   <si>
-    <t xml:space="preserve">58.5462684631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9244499206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.3549308776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.7331199645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3504638671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.3071098327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.2682151794434</t>
+    <t xml:space="preserve">58.5462646484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.924446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.3549346923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.7331161499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3504676818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.3071060180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.2682075500488</t>
   </si>
   <si>
     <t xml:space="preserve">60.172550201416</t>
@@ -1928,19 +1928,19 @@
     <t xml:space="preserve">59.7420616149902</t>
   </si>
   <si>
-    <t xml:space="preserve">59.2159080505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.1202430725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3026351928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.828784942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.1157722473145</t>
+    <t xml:space="preserve">59.2159156799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.120246887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3026428222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.8287887573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.1157760620117</t>
   </si>
   <si>
     <t xml:space="preserve">57.7809562683105</t>
@@ -1949,55 +1949,55 @@
     <t xml:space="preserve">59.0245819091797</t>
   </si>
   <si>
-    <t xml:space="preserve">59.4550743103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.3160400390625</t>
+    <t xml:space="preserve">59.4550704956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.3160438537598</t>
   </si>
   <si>
     <t xml:space="preserve">60.0290489196777</t>
   </si>
   <si>
-    <t xml:space="preserve">59.0724143981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.2592735290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0201148986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9888229370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4148368835449</t>
+    <t xml:space="preserve">59.0724105834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.25927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0201187133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9888191223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4148406982422</t>
   </si>
   <si>
     <t xml:space="preserve">51.2279777526855</t>
   </si>
   <si>
-    <t xml:space="preserve">51.3236465454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8931617736816</t>
+    <t xml:space="preserve">51.3236427307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8931579589844</t>
   </si>
   <si>
     <t xml:space="preserve">49.7930221557617</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8408546447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6928939819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2668724060059</t>
+    <t xml:space="preserve">49.8408508300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6928863525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2668762207031</t>
   </si>
   <si>
     <t xml:space="preserve">49.9843521118164</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9365158081055</t>
+    <t xml:space="preserve">49.9365196228027</t>
   </si>
   <si>
     <t xml:space="preserve">50.0800132751465</t>
@@ -2006,7 +2006,7 @@
     <t xml:space="preserve">50.6539993286133</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2235069274902</t>
+    <t xml:space="preserve">50.2235107421875</t>
   </si>
   <si>
     <t xml:space="preserve">50.8453254699707</t>
@@ -2018,37 +2018,37 @@
     <t xml:space="preserve">50.9409866333008</t>
   </si>
   <si>
-    <t xml:space="preserve">51.5149688720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7974891662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1323204040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6973571777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3147087097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.4581985473633</t>
+    <t xml:space="preserve">51.5149726867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.797492980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1323165893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6973609924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3147048950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.4582023620605</t>
   </si>
   <si>
     <t xml:space="preserve">49.7451934814453</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0321807861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8363838195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5972213745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3625297546387</t>
+    <t xml:space="preserve">50.0321769714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8363876342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.597225189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3625373840332</t>
   </si>
   <si>
     <t xml:space="preserve">54.0022315979004</t>
@@ -2057,43 +2057,43 @@
     <t xml:space="preserve">53.4282455444336</t>
   </si>
   <si>
-    <t xml:space="preserve">54.2892265319824</t>
+    <t xml:space="preserve">54.2892227172852</t>
   </si>
   <si>
     <t xml:space="preserve">54.1935577392578</t>
   </si>
   <si>
-    <t xml:space="preserve">53.0934257507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.4716110229492</t>
+    <t xml:space="preserve">53.0934219360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.471607208252</t>
   </si>
   <si>
     <t xml:space="preserve">53.2847518920898</t>
   </si>
   <si>
-    <t xml:space="preserve">54.0978965759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9110412597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3370513916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8587341308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4805526733398</t>
+    <t xml:space="preserve">54.097900390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9110374450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3370552062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8587379455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4805488586426</t>
   </si>
   <si>
     <t xml:space="preserve">55.0545310974121</t>
   </si>
   <si>
-    <t xml:space="preserve">55.3415184020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.8676719665527</t>
+    <t xml:space="preserve">55.3415260314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.86767578125</t>
   </si>
   <si>
     <t xml:space="preserve">56.5373191833496</t>
@@ -2102,10 +2102,10 @@
     <t xml:space="preserve">56.6329879760742</t>
   </si>
   <si>
-    <t xml:space="preserve">58.4027671813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0679473876953</t>
+    <t xml:space="preserve">58.4027633666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.067943572998</t>
   </si>
   <si>
     <t xml:space="preserve">59.6942291259766</t>
@@ -2114,76 +2114,76 @@
     <t xml:space="preserve">59.3115730285645</t>
   </si>
   <si>
-    <t xml:space="preserve">62.8511276245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6164398193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.3384017944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.3428573608398</t>
+    <t xml:space="preserve">62.8511390686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6164512634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.3383941650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.3428649902344</t>
   </si>
   <si>
     <t xml:space="preserve">66.9646835327148</t>
   </si>
   <si>
-    <t xml:space="preserve">67.9213180541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.260612487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.0692825317383</t>
+    <t xml:space="preserve">67.9213256835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.2606201171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.0692749023438</t>
   </si>
   <si>
     <t xml:space="preserve">67.3951568603516</t>
   </si>
   <si>
-    <t xml:space="preserve">68.0169830322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.869010925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.2994995117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.5386505126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.9257965087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.2127685546875</t>
+    <t xml:space="preserve">68.016975402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.8690185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.2995071411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.5386657714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.9257888793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.212776184082</t>
   </si>
   <si>
     <t xml:space="preserve">68.4474716186523</t>
   </si>
   <si>
-    <t xml:space="preserve">67.8734817504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.7778244018555</t>
+    <t xml:space="preserve">67.8734893798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.7778167724609</t>
   </si>
   <si>
     <t xml:space="preserve">67.0603408813477</t>
   </si>
   <si>
-    <t xml:space="preserve">66.0080413818359</t>
+    <t xml:space="preserve">66.0080490112305</t>
   </si>
   <si>
     <t xml:space="preserve">66.4385299682617</t>
   </si>
   <si>
-    <t xml:space="preserve">65.5775451660156</t>
+    <t xml:space="preserve">65.5775527954102</t>
   </si>
   <si>
     <t xml:space="preserve">65.9123840332031</t>
   </si>
   <si>
-    <t xml:space="preserve">67.2516708374023</t>
+    <t xml:space="preserve">67.2516632080078</t>
   </si>
   <si>
     <t xml:space="preserve">67.8256607055664</t>
@@ -2192,49 +2192,49 @@
     <t xml:space="preserve">67.6343231201172</t>
   </si>
   <si>
-    <t xml:space="preserve">65.7688903808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.1036987304688</t>
+    <t xml:space="preserve">65.7688827514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.1037063598633</t>
   </si>
   <si>
     <t xml:space="preserve">69.4519348144531</t>
   </si>
   <si>
-    <t xml:space="preserve">68.2083206176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.3129119873047</t>
+    <t xml:space="preserve">68.2083129882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.3129196166992</t>
   </si>
   <si>
     <t xml:space="preserve">73.3263244628906</t>
   </si>
   <si>
-    <t xml:space="preserve">73.2306671142578</t>
+    <t xml:space="preserve">73.2306594848633</t>
   </si>
   <si>
     <t xml:space="preserve">74.0916366577148</t>
   </si>
   <si>
-    <t xml:space="preserve">73.6611557006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.374153137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6955642700195</t>
+    <t xml:space="preserve">73.6611404418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.3741607666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6955718994141</t>
   </si>
   <si>
     <t xml:space="preserve">70.7912368774414</t>
   </si>
   <si>
-    <t xml:space="preserve">72.4653472900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.2650680541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.638801574707</t>
+    <t xml:space="preserve">72.4653549194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.2650756835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.6387939453125</t>
   </si>
   <si>
     <t xml:space="preserve">71.3173828125</t>
@@ -2243,28 +2243,28 @@
     <t xml:space="preserve">71.9391937255859</t>
   </si>
   <si>
-    <t xml:space="preserve">72.7045059204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.7523498535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.6088409423828</t>
+    <t xml:space="preserve">72.7044982910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.7523422241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.6088485717773</t>
   </si>
   <si>
     <t xml:space="preserve">74.4264602661133</t>
   </si>
   <si>
-    <t xml:space="preserve">74.1394653320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7478637695312</t>
+    <t xml:space="preserve">74.1394577026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7478790283203</t>
   </si>
   <si>
     <t xml:space="preserve">71.9870300292969</t>
   </si>
   <si>
-    <t xml:space="preserve">73.2784881591797</t>
+    <t xml:space="preserve">73.2784957885742</t>
   </si>
   <si>
     <t xml:space="preserve">71.4130477905273</t>
@@ -2273,28 +2273,28 @@
     <t xml:space="preserve">66.8211822509766</t>
   </si>
   <si>
-    <t xml:space="preserve">65.7210464477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.1336555480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.8077735900879</t>
+    <t xml:space="preserve">65.7210540771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.1336479187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.8077697753906</t>
   </si>
   <si>
     <t xml:space="preserve">61.8944931030273</t>
   </si>
   <si>
-    <t xml:space="preserve">60.9378547668457</t>
+    <t xml:space="preserve">60.937858581543</t>
   </si>
   <si>
     <t xml:space="preserve">57.8766174316406</t>
   </si>
   <si>
-    <t xml:space="preserve">52.5672760009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.0889549255371</t>
+    <t xml:space="preserve">52.5672721862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.0889587402344</t>
   </si>
   <si>
     <t xml:space="preserve">46.3778190612793</t>
@@ -2303,16 +2303,16 @@
     <t xml:space="preserve">48.7407188415527</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4594535827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7094268798828</t>
+    <t xml:space="preserve">45.4594497680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7094306945801</t>
   </si>
   <si>
     <t xml:space="preserve">43.8714332580566</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2107276916504</t>
+    <t xml:space="preserve">45.2107238769531</t>
   </si>
   <si>
     <t xml:space="preserve">45.344654083252</t>
@@ -2321,10 +2321,10 @@
     <t xml:space="preserve">47.1048698425293</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0844802856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2190361022949</t>
+    <t xml:space="preserve">51.0844841003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2190437316895</t>
   </si>
   <si>
     <t xml:space="preserve">59.1680793762207</t>
@@ -2336,7 +2336,7 @@
     <t xml:space="preserve">59.263744354248</t>
   </si>
   <si>
-    <t xml:space="preserve">61.0813522338867</t>
+    <t xml:space="preserve">61.081356048584</t>
   </si>
   <si>
     <t xml:space="preserve">60.3638763427734</t>
@@ -2345,25 +2345,25 @@
     <t xml:space="preserve">61.1291885375977</t>
   </si>
   <si>
-    <t xml:space="preserve">61.4161758422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.6598052978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.5207901000977</t>
+    <t xml:space="preserve">61.4161720275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.6598091125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.5207786560059</t>
   </si>
   <si>
     <t xml:space="preserve">62.5641403198242</t>
   </si>
   <si>
-    <t xml:space="preserve">63.138126373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0424728393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.990161895752</t>
+    <t xml:space="preserve">63.1381225585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0424652099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9901657104492</t>
   </si>
   <si>
     <t xml:space="preserve">61.0335235595703</t>
@@ -2372,58 +2372,58 @@
     <t xml:space="preserve">59.2684898376465</t>
   </si>
   <si>
-    <t xml:space="preserve">60.9081420898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.7279586791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.7051963806152</t>
+    <t xml:space="preserve">60.9081344604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.7279663085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.7052001953125</t>
   </si>
   <si>
     <t xml:space="preserve">64.7179107666016</t>
   </si>
   <si>
-    <t xml:space="preserve">63.3676071166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6569595336914</t>
+    <t xml:space="preserve">63.3676109313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6569557189941</t>
   </si>
   <si>
     <t xml:space="preserve">64.0909805297852</t>
   </si>
   <si>
-    <t xml:space="preserve">64.4285583496094</t>
+    <t xml:space="preserve">64.4285659790039</t>
   </si>
   <si>
     <t xml:space="preserve">64.9108047485352</t>
   </si>
   <si>
-    <t xml:space="preserve">68.4312286376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.0936508178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.3830184936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.6241302490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.9744415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.3984146118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.1217727661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.9288864135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.3628921508789</t>
+    <t xml:space="preserve">68.4312362670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.0936584472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.3830108642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.624137878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.9744262695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.3984069824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.1217803955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.9288787841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.362907409668</t>
   </si>
   <si>
     <t xml:space="preserve">75.8578720092773</t>
@@ -2435,22 +2435,22 @@
     <t xml:space="preserve">71.8552093505859</t>
   </si>
   <si>
-    <t xml:space="preserve">70.6013565063477</t>
+    <t xml:space="preserve">70.6013412475586</t>
   </si>
   <si>
     <t xml:space="preserve">71.1318283081055</t>
   </si>
   <si>
-    <t xml:space="preserve">70.2155532836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.9235382080078</t>
+    <t xml:space="preserve">70.2155609130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.9235305786133</t>
   </si>
   <si>
     <t xml:space="preserve">67.0327072143555</t>
   </si>
   <si>
-    <t xml:space="preserve">67.2256088256836</t>
+    <t xml:space="preserve">67.2256011962891</t>
   </si>
   <si>
     <t xml:space="preserve">64.8625869750977</t>
@@ -2462,16 +2462,16 @@
     <t xml:space="preserve">67.3220596313477</t>
   </si>
   <si>
-    <t xml:space="preserve">69.9262008666992</t>
+    <t xml:space="preserve">69.9262161254883</t>
   </si>
   <si>
     <t xml:space="preserve">71.180061340332</t>
   </si>
   <si>
-    <t xml:space="preserve">70.4084625244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3729629516602</t>
+    <t xml:space="preserve">70.4084548950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3729553222656</t>
   </si>
   <si>
     <t xml:space="preserve">69.4921798706055</t>
@@ -2480,10 +2480,10 @@
     <t xml:space="preserve">70.31201171875</t>
   </si>
   <si>
-    <t xml:space="preserve">68.5276794433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.2865676879883</t>
+    <t xml:space="preserve">68.5276870727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.2865600585938</t>
   </si>
   <si>
     <t xml:space="preserve">68.6723556518555</t>
@@ -2495,13 +2495,13 @@
     <t xml:space="preserve">69.2992782592773</t>
   </si>
   <si>
-    <t xml:space="preserve">72.1445541381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.276496887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.8069839477539</t>
+    <t xml:space="preserve">72.1445617675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.2765045166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.8069763183594</t>
   </si>
   <si>
     <t xml:space="preserve">70.1673278808594</t>
@@ -2510,28 +2510,28 @@
     <t xml:space="preserve">70.5531311035156</t>
   </si>
   <si>
-    <t xml:space="preserve">70.360221862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.6623153686523</t>
+    <t xml:space="preserve">70.3602294921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.6623077392578</t>
   </si>
   <si>
     <t xml:space="preserve">72.3374557495117</t>
   </si>
   <si>
-    <t xml:space="preserve">72.8679351806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.4466171264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.5430755615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.999885559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.0608367919922</t>
+    <t xml:space="preserve">72.8679275512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.4466400146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.543083190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9998779296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.0608291625977</t>
   </si>
   <si>
     <t xml:space="preserve">73.6877593994141</t>
@@ -2543,13 +2543,13 @@
     <t xml:space="preserve">72.9643859863281</t>
   </si>
   <si>
-    <t xml:space="preserve">74.7487030029297</t>
+    <t xml:space="preserve">74.7486953735352</t>
   </si>
   <si>
     <t xml:space="preserve">81.9342193603516</t>
   </si>
   <si>
-    <t xml:space="preserve">82.9469528198242</t>
+    <t xml:space="preserve">82.9469451904297</t>
   </si>
   <si>
     <t xml:space="preserve">85.117073059082</t>
@@ -2558,49 +2558,49 @@
     <t xml:space="preserve">86.0815734863281</t>
   </si>
   <si>
-    <t xml:space="preserve">85.3582000732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1398468017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.017951965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0661849975586</t>
+    <t xml:space="preserve">85.3581924438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1398544311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0179443359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0661773681641</t>
   </si>
   <si>
     <t xml:space="preserve">82.609375</t>
   </si>
   <si>
-    <t xml:space="preserve">80.8732604980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.0916290283203</t>
+    <t xml:space="preserve">80.8732833862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.0916213989258</t>
   </si>
   <si>
     <t xml:space="preserve">85.3099670410156</t>
   </si>
   <si>
-    <t xml:space="preserve">84.5865859985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.6348190307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.6703186035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.7795104980469</t>
+    <t xml:space="preserve">84.5865936279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.6348266601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.6703262329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.7794952392578</t>
   </si>
   <si>
     <t xml:space="preserve">84.6830520629883</t>
   </si>
   <si>
-    <t xml:space="preserve">87.3836441040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.2262420654297</t>
+    <t xml:space="preserve">87.3836517333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2262496948242</t>
   </si>
   <si>
     <t xml:space="preserve">87.7212142944336</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">88.1070175170898</t>
   </si>
   <si>
-    <t xml:space="preserve">87.8658905029297</t>
+    <t xml:space="preserve">87.8658981323242</t>
   </si>
   <si>
     <t xml:space="preserve">91.2416381835938</t>
@@ -2633,28 +2633,28 @@
     <t xml:space="preserve">90.8076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">92.9777374267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.0031967163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.90673828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7265701293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.218864440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5082244873047</t>
+    <t xml:space="preserve">92.9777450561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.0031890869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9067459106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.2188720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5082092285156</t>
   </si>
   <si>
     <t xml:space="preserve">91.4827728271484</t>
   </si>
   <si>
-    <t xml:space="preserve">89.939567565918</t>
+    <t xml:space="preserve">89.9395599365234</t>
   </si>
   <si>
     <t xml:space="preserve">91.62744140625</t>
@@ -2663,13 +2663,13 @@
     <t xml:space="preserve">92.1096954345703</t>
   </si>
   <si>
-    <t xml:space="preserve">93.3635406494141</t>
+    <t xml:space="preserve">93.3635482788086</t>
   </si>
   <si>
     <t xml:space="preserve">95.5336608886719</t>
   </si>
   <si>
-    <t xml:space="preserve">94.9549560546875</t>
+    <t xml:space="preserve">94.954963684082</t>
   </si>
   <si>
     <t xml:space="preserve">94.8102951049805</t>
@@ -2678,10 +2678,10 @@
     <t xml:space="preserve">93.6046676635742</t>
   </si>
   <si>
-    <t xml:space="preserve">94.5209350585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6883850097656</t>
+    <t xml:space="preserve">94.5209503173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6883926391602</t>
   </si>
   <si>
     <t xml:space="preserve">91.4345397949219</t>
@@ -2696,7 +2696,7 @@
     <t xml:space="preserve">97.2215423583984</t>
   </si>
   <si>
-    <t xml:space="preserve">100.115036010742</t>
+    <t xml:space="preserve">100.115028381348</t>
   </si>
   <si>
     <t xml:space="preserve">99.7292404174805</t>
@@ -2714,10 +2714,10 @@
     <t xml:space="preserve">96.3052597045898</t>
   </si>
   <si>
-    <t xml:space="preserve">93.7493438720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.8330764770508</t>
+    <t xml:space="preserve">93.7493362426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.8330612182617</t>
   </si>
   <si>
     <t xml:space="preserve">92.8813018798828</t>
@@ -2726,13 +2726,13 @@
     <t xml:space="preserve">88.4445953369141</t>
   </si>
   <si>
-    <t xml:space="preserve">88.2034606933594</t>
+    <t xml:space="preserve">88.2034530639648</t>
   </si>
   <si>
     <t xml:space="preserve">89.0233001708984</t>
   </si>
   <si>
-    <t xml:space="preserve">90.1324691772461</t>
+    <t xml:space="preserve">90.1324615478516</t>
   </si>
   <si>
     <t xml:space="preserve">92.2061386108398</t>
@@ -2741,16 +2741,16 @@
     <t xml:space="preserve">96.4499359130859</t>
   </si>
   <si>
-    <t xml:space="preserve">95.4372253417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.774787902832</t>
+    <t xml:space="preserve">95.4372177124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7747955322266</t>
   </si>
   <si>
     <t xml:space="preserve">92.4472732543945</t>
   </si>
   <si>
-    <t xml:space="preserve">92.0614547729492</t>
+    <t xml:space="preserve">92.0614624023438</t>
   </si>
   <si>
     <t xml:space="preserve">91.8685607910156</t>
@@ -2759,13 +2759,13 @@
     <t xml:space="preserve">91.8203430175781</t>
   </si>
   <si>
-    <t xml:space="preserve">90.7111740112305</t>
+    <t xml:space="preserve">90.711181640625</t>
   </si>
   <si>
     <t xml:space="preserve">90.855842590332</t>
   </si>
   <si>
-    <t xml:space="preserve">91.3863220214844</t>
+    <t xml:space="preserve">91.3863143920898</t>
   </si>
   <si>
     <t xml:space="preserve">90.759391784668</t>
@@ -2774,34 +2774,34 @@
     <t xml:space="preserve">87.7694473266602</t>
   </si>
   <si>
-    <t xml:space="preserve">88.2516937255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3608779907227</t>
+    <t xml:space="preserve">88.2517013549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3608703613281</t>
   </si>
   <si>
     <t xml:space="preserve">90.3735885620117</t>
   </si>
   <si>
-    <t xml:space="preserve">94.2798080444336</t>
+    <t xml:space="preserve">94.2798156738281</t>
   </si>
   <si>
     <t xml:space="preserve">90.0842514038086</t>
   </si>
   <si>
-    <t xml:space="preserve">91.1451873779297</t>
+    <t xml:space="preserve">91.1451950073242</t>
   </si>
   <si>
     <t xml:space="preserve">92.495491027832</t>
   </si>
   <si>
-    <t xml:space="preserve">89.4573211669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6756744384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.9168014526367</t>
+    <t xml:space="preserve">89.4573135375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.675666809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.9167938232422</t>
   </si>
   <si>
     <t xml:space="preserve">91.7238922119141</t>
@@ -2816,7 +2816,7 @@
     <t xml:space="preserve">92.3508148193359</t>
   </si>
   <si>
-    <t xml:space="preserve">93.4599990844727</t>
+    <t xml:space="preserve">93.4599914550781</t>
   </si>
   <si>
     <t xml:space="preserve">92.5437164306641</t>
@@ -2825,31 +2825,31 @@
     <t xml:space="preserve">95.9194641113281</t>
   </si>
   <si>
-    <t xml:space="preserve">93.26708984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5564346313477</t>
+    <t xml:space="preserve">93.2670822143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5564498901367</t>
   </si>
   <si>
     <t xml:space="preserve">94.5691680908203</t>
   </si>
   <si>
-    <t xml:space="preserve">96.0641479492188</t>
+    <t xml:space="preserve">96.0641403198242</t>
   </si>
   <si>
     <t xml:space="preserve">98.4753952026367</t>
   </si>
   <si>
-    <t xml:space="preserve">100.018592834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.1860504150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.4144439697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.790184020996</t>
+    <t xml:space="preserve">100.018585205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.18603515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.414436340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.790191650391</t>
   </si>
   <si>
     <t xml:space="preserve">102.912078857422</t>
@@ -2861,52 +2861,52 @@
     <t xml:space="preserve">102.719184875488</t>
   </si>
   <si>
-    <t xml:space="preserve">102.526290893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.140495300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.937530517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.104995727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.58723449707</t>
+    <t xml:space="preserve">102.52628326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.140487670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.937538146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.104988098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.587242126465</t>
   </si>
   <si>
     <t xml:space="preserve">102.815635681152</t>
   </si>
   <si>
-    <t xml:space="preserve">103.201438903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.500839233398</t>
+    <t xml:space="preserve">103.201446533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.500831604004</t>
   </si>
   <si>
     <t xml:space="preserve">100.404388427734</t>
   </si>
   <si>
-    <t xml:space="preserve">98.5718307495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.0514221191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.1351470947266</t>
+    <t xml:space="preserve">98.5718383789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.0514144897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.135139465332</t>
   </si>
   <si>
     <t xml:space="preserve">92.5919418334961</t>
   </si>
   <si>
-    <t xml:space="preserve">89.216194152832</t>
+    <t xml:space="preserve">89.2162017822266</t>
   </si>
   <si>
     <t xml:space="preserve">103.297882080078</t>
   </si>
   <si>
-    <t xml:space="preserve">99.3434371948242</t>
+    <t xml:space="preserve">99.3434448242188</t>
   </si>
   <si>
     <t xml:space="preserve">101.561790466309</t>
@@ -2918,13 +2918,13 @@
     <t xml:space="preserve">103.780136108398</t>
   </si>
   <si>
-    <t xml:space="preserve">105.323333740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.490791320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.069480895996</t>
+    <t xml:space="preserve">105.32332611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.490783691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.069488525391</t>
   </si>
   <si>
     <t xml:space="preserve">108.02392578125</t>
@@ -2945,16 +2945,16 @@
     <t xml:space="preserve">106.384284973145</t>
   </si>
   <si>
-    <t xml:space="preserve">108.891983032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.831039428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.795539855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.084884643555</t>
+    <t xml:space="preserve">108.891990661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.831047058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.795532226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.084892272949</t>
   </si>
   <si>
     <t xml:space="preserve">107.059432983398</t>
@@ -2972,19 +2972,19 @@
     <t xml:space="preserve">109.530754089355</t>
   </si>
   <si>
-    <t xml:space="preserve">107.786010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.755310058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.046104431152</t>
+    <t xml:space="preserve">107.786018371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.755325317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.046112060547</t>
   </si>
   <si>
     <t xml:space="preserve">109.918479919434</t>
   </si>
   <si>
-    <t xml:space="preserve">110.500061035156</t>
+    <t xml:space="preserve">110.500045776367</t>
   </si>
   <si>
     <t xml:space="preserve">109.821548461914</t>
@@ -2993,13 +2993,13 @@
     <t xml:space="preserve">110.88777923584</t>
   </si>
   <si>
-    <t xml:space="preserve">111.663208007812</t>
+    <t xml:space="preserve">111.663215637207</t>
   </si>
   <si>
     <t xml:space="preserve">113.117164611816</t>
   </si>
   <si>
-    <t xml:space="preserve">115.831207275391</t>
+    <t xml:space="preserve">115.831199645996</t>
   </si>
   <si>
     <t xml:space="preserve">113.795677185059</t>
@@ -3017,7 +3017,7 @@
     <t xml:space="preserve">114.474182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">116.509704589844</t>
+    <t xml:space="preserve">116.509712219238</t>
   </si>
   <si>
     <t xml:space="preserve">121.453140258789</t>
@@ -3029,10 +3029,10 @@
     <t xml:space="preserve">128.819793701172</t>
   </si>
   <si>
-    <t xml:space="preserve">127.365844726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.268936157227</t>
+    <t xml:space="preserve">127.365852355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.268928527832</t>
   </si>
   <si>
     <t xml:space="preserve">128.432083129883</t>
@@ -3041,7 +3041,7 @@
     <t xml:space="preserve">133.181640625</t>
   </si>
   <si>
-    <t xml:space="preserve">130.46760559082</t>
+    <t xml:space="preserve">130.467620849609</t>
   </si>
   <si>
     <t xml:space="preserve">130.273742675781</t>
@@ -3053,31 +3053,31 @@
     <t xml:space="preserve">134.635589599609</t>
   </si>
   <si>
-    <t xml:space="preserve">135.70182800293</t>
+    <t xml:space="preserve">135.701812744141</t>
   </si>
   <si>
     <t xml:space="preserve">134.44172668457</t>
   </si>
   <si>
-    <t xml:space="preserve">133.375518798828</t>
+    <t xml:space="preserve">133.375503540039</t>
   </si>
   <si>
     <t xml:space="preserve">135.798751831055</t>
   </si>
   <si>
-    <t xml:space="preserve">135.314102172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.574172973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.212326049805</t>
+    <t xml:space="preserve">135.314117431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.574203491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.212341308594</t>
   </si>
   <si>
     <t xml:space="preserve">135.023315429688</t>
   </si>
   <si>
-    <t xml:space="preserve">133.763229370117</t>
+    <t xml:space="preserve">133.763214111328</t>
   </si>
   <si>
     <t xml:space="preserve">137.446578979492</t>
@@ -3089,10 +3089,10 @@
     <t xml:space="preserve">134.344818115234</t>
   </si>
   <si>
-    <t xml:space="preserve">138.22200012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142.293045043945</t>
+    <t xml:space="preserve">138.221984863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142.293060302734</t>
   </si>
   <si>
     <t xml:space="preserve">141.032958984375</t>
@@ -3104,13 +3104,13 @@
     <t xml:space="preserve">140.063674926758</t>
   </si>
   <si>
-    <t xml:space="preserve">138.803588867188</t>
+    <t xml:space="preserve">138.803573608398</t>
   </si>
   <si>
     <t xml:space="preserve">140.548309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">140.160598754883</t>
+    <t xml:space="preserve">140.160614013672</t>
   </si>
   <si>
     <t xml:space="preserve">139.579010009766</t>
@@ -3119,13 +3119,13 @@
     <t xml:space="preserve">136.671127319336</t>
   </si>
   <si>
-    <t xml:space="preserve">138.609725952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.992630004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.640411376953</t>
+    <t xml:space="preserve">138.609710693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.992614746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.640426635742</t>
   </si>
   <si>
     <t xml:space="preserve">139.094375610352</t>
@@ -3146,28 +3146,28 @@
     <t xml:space="preserve">142.486923217773</t>
   </si>
   <si>
-    <t xml:space="preserve">146.073318481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.884292602539</t>
+    <t xml:space="preserve">146.073333740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.884307861328</t>
   </si>
   <si>
     <t xml:space="preserve">148.011917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">149.175079345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.756652832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.36408996582</t>
+    <t xml:space="preserve">149.175064086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.756637573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.364105224609</t>
   </si>
   <si>
     <t xml:space="preserve">147.236465454102</t>
   </si>
   <si>
-    <t xml:space="preserve">148.205764770508</t>
+    <t xml:space="preserve">148.205780029297</t>
   </si>
   <si>
     <t xml:space="preserve">147.818054199219</t>
@@ -3176,10 +3176,10 @@
     <t xml:space="preserve">150.532104492188</t>
   </si>
   <si>
-    <t xml:space="preserve">150.629028320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.087783813477</t>
+    <t xml:space="preserve">150.629013061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.087799072266</t>
   </si>
   <si>
     <t xml:space="preserve">154.893951416016</t>
@@ -3203,22 +3203,22 @@
     <t xml:space="preserve">165.847015380859</t>
   </si>
   <si>
-    <t xml:space="preserve">165.45930480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.653137207031</t>
+    <t xml:space="preserve">165.459289550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.65315246582</t>
   </si>
   <si>
     <t xml:space="preserve">167.397888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">168.851837158203</t>
+    <t xml:space="preserve">168.851852416992</t>
   </si>
   <si>
     <t xml:space="preserve">169.142623901367</t>
   </si>
   <si>
-    <t xml:space="preserve">169.62727355957</t>
+    <t xml:space="preserve">169.627288818359</t>
   </si>
   <si>
     <t xml:space="preserve">170.305786132812</t>
@@ -3239,19 +3239,19 @@
     <t xml:space="preserve">167.204025268555</t>
   </si>
   <si>
-    <t xml:space="preserve">165.071578979492</t>
+    <t xml:space="preserve">165.071594238281</t>
   </si>
   <si>
     <t xml:space="preserve">167.979476928711</t>
   </si>
   <si>
-    <t xml:space="preserve">173.989105224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.606216430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.372009277344</t>
+    <t xml:space="preserve">173.989120483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.606231689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.372024536133</t>
   </si>
   <si>
     <t xml:space="preserve">152.470687866211</t>
@@ -3266,13 +3266,13 @@
     <t xml:space="preserve">153.827697753906</t>
   </si>
   <si>
-    <t xml:space="preserve">149.465850830078</t>
+    <t xml:space="preserve">149.465866088867</t>
   </si>
   <si>
     <t xml:space="preserve">153.633865356445</t>
   </si>
   <si>
-    <t xml:space="preserve">147.430358886719</t>
+    <t xml:space="preserve">147.43034362793</t>
   </si>
   <si>
     <t xml:space="preserve">147.721115112305</t>
@@ -3293,28 +3293,28 @@
     <t xml:space="preserve">163.229888916016</t>
   </si>
   <si>
-    <t xml:space="preserve">160.418930053711</t>
+    <t xml:space="preserve">160.4189453125</t>
   </si>
   <si>
     <t xml:space="preserve">161.097442626953</t>
   </si>
   <si>
-    <t xml:space="preserve">160.806640625</t>
+    <t xml:space="preserve">160.806655883789</t>
   </si>
   <si>
     <t xml:space="preserve">160.612808227539</t>
   </si>
   <si>
-    <t xml:space="preserve">161.582107543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.551376342773</t>
+    <t xml:space="preserve">161.582092285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.551391601562</t>
   </si>
   <si>
     <t xml:space="preserve">161.872894287109</t>
   </si>
   <si>
-    <t xml:space="preserve">164.393081665039</t>
+    <t xml:space="preserve">164.393096923828</t>
   </si>
   <si>
     <t xml:space="preserve">171.275085449219</t>
@@ -3329,10 +3329,10 @@
     <t xml:space="preserve">174.182983398438</t>
   </si>
   <si>
-    <t xml:space="preserve">171.662826538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172.341323852539</t>
+    <t xml:space="preserve">171.662811279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.34130859375</t>
   </si>
   <si>
     <t xml:space="preserve">176.703155517578</t>
@@ -3347,25 +3347,25 @@
     <t xml:space="preserve">168.754913330078</t>
   </si>
   <si>
-    <t xml:space="preserve">168.561050415039</t>
+    <t xml:space="preserve">168.561019897461</t>
   </si>
   <si>
     <t xml:space="preserve">167.010177612305</t>
   </si>
   <si>
-    <t xml:space="preserve">159.934295654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.454483032227</t>
+    <t xml:space="preserve">159.934280395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.454467773438</t>
   </si>
   <si>
     <t xml:space="preserve">159.837356567383</t>
   </si>
   <si>
-    <t xml:space="preserve">166.040878295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.882537841797</t>
+    <t xml:space="preserve">166.040863037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.882522583008</t>
   </si>
   <si>
     <t xml:space="preserve">160.709732055664</t>
@@ -3377,49 +3377,49 @@
     <t xml:space="preserve">159.158843994141</t>
   </si>
   <si>
-    <t xml:space="preserve">172.535171508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.958435058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.698333740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.570693969727</t>
+    <t xml:space="preserve">172.53515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.958419799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.698348999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.570709228516</t>
   </si>
   <si>
     <t xml:space="preserve">169.43342590332</t>
   </si>
   <si>
-    <t xml:space="preserve">168.076400756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.617645263672</t>
+    <t xml:space="preserve">168.076385498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.617630004883</t>
   </si>
   <si>
     <t xml:space="preserve">164.877731323242</t>
   </si>
   <si>
-    <t xml:space="preserve">163.714569091797</t>
+    <t xml:space="preserve">163.714553833008</t>
   </si>
   <si>
     <t xml:space="preserve">170.596572875977</t>
   </si>
   <si>
-    <t xml:space="preserve">169.821136474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.473770141602</t>
+    <t xml:space="preserve">169.82112121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.473785400391</t>
   </si>
   <si>
     <t xml:space="preserve">164.005340576172</t>
   </si>
   <si>
-    <t xml:space="preserve">157.317184448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.572448730469</t>
+    <t xml:space="preserve">157.317199707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.572463989258</t>
   </si>
   <si>
     <t xml:space="preserve">155.863235473633</t>
@@ -3431,13 +3431,13 @@
     <t xml:space="preserve">153.149200439453</t>
   </si>
   <si>
-    <t xml:space="preserve">151.016754150391</t>
+    <t xml:space="preserve">151.016738891602</t>
   </si>
   <si>
     <t xml:space="preserve">157.220260620117</t>
   </si>
   <si>
-    <t xml:space="preserve">151.113662719727</t>
+    <t xml:space="preserve">151.113677978516</t>
   </si>
   <si>
     <t xml:space="preserve">152.858413696289</t>
@@ -3455,31 +3455,31 @@
     <t xml:space="preserve">143.553161621094</t>
   </si>
   <si>
-    <t xml:space="preserve">144.522430419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.910186767578</t>
+    <t xml:space="preserve">144.522445678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.910171508789</t>
   </si>
   <si>
     <t xml:space="preserve">139.385177612305</t>
   </si>
   <si>
-    <t xml:space="preserve">136.089553833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.600067138672</t>
+    <t xml:space="preserve">136.089538574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.600082397461</t>
   </si>
   <si>
     <t xml:space="preserve">132.309280395508</t>
   </si>
   <si>
-    <t xml:space="preserve">138.997421264648</t>
+    <t xml:space="preserve">138.997436523438</t>
   </si>
   <si>
     <t xml:space="preserve">137.834289550781</t>
   </si>
   <si>
-    <t xml:space="preserve">137.543487548828</t>
+    <t xml:space="preserve">137.543472290039</t>
   </si>
   <si>
     <t xml:space="preserve">138.125076293945</t>
@@ -3488,13 +3488,13 @@
     <t xml:space="preserve">138.512786865234</t>
   </si>
   <si>
-    <t xml:space="preserve">142.680770874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.692169189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.039535522461</t>
+    <t xml:space="preserve">142.680786132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.692184448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.039543151855</t>
   </si>
   <si>
     <t xml:space="preserve">136.9619140625</t>
@@ -3503,22 +3503,22 @@
     <t xml:space="preserve">135.507965087891</t>
   </si>
   <si>
-    <t xml:space="preserve">142.874633789062</t>
+    <t xml:space="preserve">142.874618530273</t>
   </si>
   <si>
     <t xml:space="preserve">149.562805175781</t>
   </si>
   <si>
-    <t xml:space="preserve">151.986038208008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.919815063477</t>
+    <t xml:space="preserve">151.986053466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.919830322266</t>
   </si>
   <si>
     <t xml:space="preserve">149.368942260742</t>
   </si>
   <si>
-    <t xml:space="preserve">146.267166137695</t>
+    <t xml:space="preserve">146.267181396484</t>
   </si>
   <si>
     <t xml:space="preserve">145.10400390625</t>
@@ -3545,16 +3545,16 @@
     <t xml:space="preserve">141.323760986328</t>
   </si>
   <si>
-    <t xml:space="preserve">137.058822631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.538665771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.477264404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.824630737305</t>
+    <t xml:space="preserve">137.058837890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.538681030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.477249145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.824615478516</t>
   </si>
   <si>
     <t xml:space="preserve">136.186462402344</t>
@@ -3563,13 +3563,13 @@
     <t xml:space="preserve">135.217178344727</t>
   </si>
   <si>
-    <t xml:space="preserve">130.952255249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.75358581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.16234588623</t>
+    <t xml:space="preserve">130.952270507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.753578186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.162353515625</t>
   </si>
   <si>
     <t xml:space="preserve">113.601806640625</t>
@@ -3578,7 +3578,7 @@
     <t xml:space="preserve">117.285148620605</t>
   </si>
   <si>
-    <t xml:space="preserve">114.958824157715</t>
+    <t xml:space="preserve">114.958831787109</t>
   </si>
   <si>
     <t xml:space="preserve">117.57593536377</t>
@@ -3587,7 +3587,7 @@
     <t xml:space="preserve">116.121994018555</t>
   </si>
   <si>
-    <t xml:space="preserve">119.708396911621</t>
+    <t xml:space="preserve">119.708389282227</t>
   </si>
   <si>
     <t xml:space="preserve">115.152694702148</t>
@@ -5478,6 +5478,9 @@
   </si>
   <si>
     <t xml:space="preserve">121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.800003051758</t>
   </si>
 </sst>
 </file>
@@ -70842,7 +70845,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6910648148</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>31849</v>
@@ -70863,6 +70866,32 @@
         <v>1784</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6910416667</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>55654</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>122.099998474121</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>118.400001525879</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>121.599998474121</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>118.800003051758</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>1822</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/REY.MI.xlsx
+++ b/data/REY.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1823" uniqueCount="1823">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1824" uniqueCount="1824">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,85 +38,85 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2559700012207</t>
+    <t xml:space="preserve">29.2559719085693</t>
   </si>
   <si>
     <t xml:space="preserve">REY.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8380298614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3272113800049</t>
+    <t xml:space="preserve">28.8380279541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3272132873535</t>
   </si>
   <si>
     <t xml:space="preserve">27.6306400299072</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8396110534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2111167907715</t>
+    <t xml:space="preserve">27.8396129608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2111148834229</t>
   </si>
   <si>
     <t xml:space="preserve">29.0005626678467</t>
   </si>
   <si>
-    <t xml:space="preserve">28.559398651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1414585113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1198196411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9789257049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8644104003906</t>
+    <t xml:space="preserve">28.5594005584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1414566040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1198234558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9789218902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8644123077393</t>
   </si>
   <si>
     <t xml:space="preserve">27.4448852539062</t>
   </si>
   <si>
-    <t xml:space="preserve">27.932487487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8163909912109</t>
+    <t xml:space="preserve">27.9324893951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8163948059082</t>
   </si>
   <si>
     <t xml:space="preserve">28.2807712554932</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6770782470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0950222015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8628273010254</t>
+    <t xml:space="preserve">27.677074432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0950202941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8628311157227</t>
   </si>
   <si>
     <t xml:space="preserve">27.2591361999512</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7018814086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1678428649902</t>
+    <t xml:space="preserve">26.7018775939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.167839050293</t>
   </si>
   <si>
     <t xml:space="preserve">25.2855167388916</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3799743652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6121654510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0053081512451</t>
+    <t xml:space="preserve">24.3799781799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6121673583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0053100585938</t>
   </si>
   <si>
     <t xml:space="preserve">25.517707824707</t>
@@ -125,28 +125,28 @@
     <t xml:space="preserve">25.6570224761963</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6074237823486</t>
+    <t xml:space="preserve">27.607421875</t>
   </si>
   <si>
     <t xml:space="preserve">26.3071556091309</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0733833312988</t>
+    <t xml:space="preserve">27.0733852386475</t>
   </si>
   <si>
     <t xml:space="preserve">26.2142791748047</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4696865081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0517444610596</t>
+    <t xml:space="preserve">26.469690322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0517425537109</t>
   </si>
   <si>
     <t xml:space="preserve">25.7034587860107</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7266788482666</t>
+    <t xml:space="preserve">25.7266807556152</t>
   </si>
   <si>
     <t xml:space="preserve">26.7483177185059</t>
@@ -161,169 +161,169 @@
     <t xml:space="preserve">27.1894779205322</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2359161376953</t>
+    <t xml:space="preserve">27.2359142303467</t>
   </si>
   <si>
     <t xml:space="preserve">27.1662578582764</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9092655181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0237808227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5546531677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3008289337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4169254302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9989795684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9757633209229</t>
+    <t xml:space="preserve">27.9092674255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0237827301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5546588897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3008251190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4169216156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9989776611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9757614135742</t>
   </si>
   <si>
     <t xml:space="preserve">29.7900104522705</t>
   </si>
   <si>
-    <t xml:space="preserve">29.952543258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2311687469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7203521728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.068639755249</t>
+    <t xml:space="preserve">29.9525413513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2311706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7203502655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0686359405518</t>
   </si>
   <si>
     <t xml:space="preserve">29.8596668243408</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5578193664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3256301879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4881629943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5113792419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2095317840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1615104675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3720664978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5345973968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4433040618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6754951477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8612518310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8148097991943</t>
+    <t xml:space="preserve">29.5578212738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3256282806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4881591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5113773345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2095336914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1615123748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3720645904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5346012115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4433059692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6754970550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8612499237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8148078918457</t>
   </si>
   <si>
     <t xml:space="preserve">28.9076881408691</t>
   </si>
   <si>
-    <t xml:space="preserve">28.629056930542</t>
+    <t xml:space="preserve">28.6290588378906</t>
   </si>
   <si>
     <t xml:space="preserve">28.4200897216797</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6775989532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.560546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0287551879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3264465332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5137252807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7946529388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0053443908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2628536224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1992702484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5036010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.550422668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9015808105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6674766540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7142925262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4567852020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4333724975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2695026397705</t>
+    <t xml:space="preserve">28.6776008605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5605487823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0287532806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3264484405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.513729095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7946510314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0053424835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2628574371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1992683410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.503604888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5504245758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.901575088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6674728393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7142963409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4567832946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.43337059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2694988250732</t>
   </si>
   <si>
     <t xml:space="preserve">29.8949356079102</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1859836578369</t>
+    <t xml:space="preserve">28.1859893798828</t>
   </si>
   <si>
     <t xml:space="preserve">29.3096771240234</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4969577789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6943702697754</t>
+    <t xml:space="preserve">29.4969596862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6943683624268</t>
   </si>
   <si>
     <t xml:space="preserve">25.7747230529785</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8047752380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.319803237915</t>
+    <t xml:space="preserve">26.804780960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3197994232178</t>
   </si>
   <si>
     <t xml:space="preserve">26.9218292236328</t>
@@ -332,52 +332,52 @@
     <t xml:space="preserve">27.5070838928223</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9452381134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8215427398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2195205688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.10910987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.624137878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3666248321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.303035736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8882884979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7478294372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4435005187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.98193359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9117012023926</t>
+    <t xml:space="preserve">26.945240020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8215446472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.219518661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1091117858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6241359710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3666229248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3030376434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8882923126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7478313446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4434986114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9819316864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9117050170898</t>
   </si>
   <si>
     <t xml:space="preserve">29.3799076080322</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4501399993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8481121063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1524486541748</t>
+    <t xml:space="preserve">29.4501419067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8481159210205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1524467468262</t>
   </si>
   <si>
     <t xml:space="preserve">29.9651660919189</t>
@@ -389,61 +389,61 @@
     <t xml:space="preserve">29.1458053588867</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0989875793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9351139068604</t>
+    <t xml:space="preserve">29.0989856719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9351119995117</t>
   </si>
   <si>
     <t xml:space="preserve">28.4903163909912</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9752902984619</t>
+    <t xml:space="preserve">27.9752922058105</t>
   </si>
   <si>
     <t xml:space="preserve">28.3732662200928</t>
   </si>
   <si>
-    <t xml:space="preserve">28.0923404693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2729835510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0622863769531</t>
+    <t xml:space="preserve">28.092342376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.272985458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0622901916504</t>
   </si>
   <si>
     <t xml:space="preserve">27.0388793945312</t>
   </si>
   <si>
-    <t xml:space="preserve">26.898416519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.149284362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.798131942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8917751312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7579555511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9518814086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8816471099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8114166259766</t>
+    <t xml:space="preserve">26.8984184265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1492881774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7981338500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.891773223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7579593658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.95188331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.881649017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8114204406738</t>
   </si>
   <si>
     <t xml:space="preserve">27.9050617218018</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2963924407959</t>
+    <t xml:space="preserve">27.2963943481445</t>
   </si>
   <si>
     <t xml:space="preserve">27.8582420349121</t>
@@ -452,43 +452,43 @@
     <t xml:space="preserve">27.5773181915283</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7177772521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7411880493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0455207824707</t>
+    <t xml:space="preserve">27.7177791595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7411918640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0455226898193</t>
   </si>
   <si>
     <t xml:space="preserve">27.7880058288574</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3900318145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1223926544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6541919708252</t>
+    <t xml:space="preserve">27.3900356292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1223945617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6541900634766</t>
   </si>
   <si>
     <t xml:space="preserve">28.2093944549561</t>
   </si>
   <si>
-    <t xml:space="preserve">27.413444519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0856990814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8515949249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4368495941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6877250671387</t>
+    <t xml:space="preserve">27.4134464263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0857009887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8515968322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4368572235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.68772315979</t>
   </si>
   <si>
     <t xml:space="preserve">27.2261619567871</t>
@@ -497,88 +497,88 @@
     <t xml:space="preserve">26.8281860351562</t>
   </si>
   <si>
-    <t xml:space="preserve">26.640905380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4536228179932</t>
+    <t xml:space="preserve">26.6409072875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4536209106445</t>
   </si>
   <si>
     <t xml:space="preserve">26.5706748962402</t>
   </si>
   <si>
-    <t xml:space="preserve">26.523853302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3365707397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7513160705566</t>
+    <t xml:space="preserve">26.5238552093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3365726470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7513179779053</t>
   </si>
   <si>
     <t xml:space="preserve">25.329927444458</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7446689605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7680835723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8851356506348</t>
+    <t xml:space="preserve">24.7446708679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7680854797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8851318359375</t>
   </si>
   <si>
     <t xml:space="preserve">24.2530555725098</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0490074157715</t>
+    <t xml:space="preserve">25.0490055084229</t>
   </si>
   <si>
     <t xml:space="preserve">25.4703903198242</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5172119140625</t>
+    <t xml:space="preserve">25.5172138214111</t>
   </si>
   <si>
     <t xml:space="preserve">25.283109664917</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1660575866699</t>
+    <t xml:space="preserve">25.1660556793213</t>
   </si>
   <si>
     <t xml:space="preserve">25.4469776153564</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0958232879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9319534301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0724143981934</t>
+    <t xml:space="preserve">25.0958290100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9319553375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.072416305542</t>
   </si>
   <si>
     <t xml:space="preserve">25.6342639923096</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1961078643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1726989746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.834831237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9284706115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4602642059326</t>
+    <t xml:space="preserve">26.1961097717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.172700881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8348293304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9284687042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4602603912354</t>
   </si>
   <si>
     <t xml:space="preserve">27.9987010955811</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6307773590088</t>
+    <t xml:space="preserve">28.6307811737061</t>
   </si>
   <si>
     <t xml:space="preserve">29.2160358428955</t>
@@ -593,10 +593,10 @@
     <t xml:space="preserve">28.349853515625</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6073684692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4735469818115</t>
+    <t xml:space="preserve">28.6073703765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4735507965088</t>
   </si>
   <si>
     <t xml:space="preserve">29.2394466400146</t>
@@ -605,13 +605,13 @@
     <t xml:space="preserve">29.7076530456543</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4267253875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8313407897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9952182769775</t>
+    <t xml:space="preserve">29.4267292022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8313503265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9952144622803</t>
   </si>
   <si>
     <t xml:space="preserve">31.4868297576904</t>
@@ -620,37 +620,37 @@
     <t xml:space="preserve">31.2527332305908</t>
   </si>
   <si>
-    <t xml:space="preserve">31.3697853088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1356773376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1891403198242</t>
+    <t xml:space="preserve">31.3697814941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1356830596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1891479492188</t>
   </si>
   <si>
     <t xml:space="preserve">32.3061943054199</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2660217285156</t>
+    <t xml:space="preserve">33.2660179138184</t>
   </si>
   <si>
     <t xml:space="preserve">34.0619621276855</t>
   </si>
   <si>
-    <t xml:space="preserve">34.6472282409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4599456787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7408638000488</t>
+    <t xml:space="preserve">34.6472206115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4599418640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7408676147461</t>
   </si>
   <si>
     <t xml:space="preserve">34.6706352233887</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9983825683594</t>
+    <t xml:space="preserve">34.9983749389648</t>
   </si>
   <si>
     <t xml:space="preserve">34.8579177856445</t>
@@ -659,31 +659,31 @@
     <t xml:space="preserve">34.1790199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7642784118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8813323974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.389705657959</t>
+    <t xml:space="preserve">34.7642707824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8813247680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3897094726562</t>
   </si>
   <si>
     <t xml:space="preserve">34.4131202697754</t>
   </si>
   <si>
-    <t xml:space="preserve">35.6070442199707</t>
+    <t xml:space="preserve">35.607048034668</t>
   </si>
   <si>
     <t xml:space="preserve">35.4665832519531</t>
   </si>
   <si>
-    <t xml:space="preserve">35.7943229675293</t>
+    <t xml:space="preserve">35.7943305969238</t>
   </si>
   <si>
     <t xml:space="preserve">36.8243827819824</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6671524047852</t>
+    <t xml:space="preserve">37.6671485900879</t>
   </si>
   <si>
     <t xml:space="preserve">37.8778419494629</t>
@@ -692,19 +692,19 @@
     <t xml:space="preserve">36.9882507324219</t>
   </si>
   <si>
-    <t xml:space="preserve">37.5735054016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6203269958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6085395812988</t>
+    <t xml:space="preserve">37.5735015869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6203231811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6085433959961</t>
   </si>
   <si>
     <t xml:space="preserve">37.726432800293</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9150695800781</t>
+    <t xml:space="preserve">37.9150657653809</t>
   </si>
   <si>
     <t xml:space="preserve">38.1980171203613</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">38.1508598327637</t>
   </si>
   <si>
-    <t xml:space="preserve">37.490650177002</t>
+    <t xml:space="preserve">37.4906387329102</t>
   </si>
   <si>
     <t xml:space="preserve">39.0232810974121</t>
@@ -728,31 +728,31 @@
     <t xml:space="preserve">40.0607566833496</t>
   </si>
   <si>
-    <t xml:space="preserve">39.8013916015625</t>
+    <t xml:space="preserve">39.8013954162598</t>
   </si>
   <si>
     <t xml:space="preserve">41.2397041320801</t>
   </si>
   <si>
-    <t xml:space="preserve">41.0274925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4519233703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7112846374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4990730285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.805606842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3243446350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1828689575195</t>
+    <t xml:space="preserve">41.0275001525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4519157409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7112884521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4990768432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8056106567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3243408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1828727722168</t>
   </si>
   <si>
     <t xml:space="preserve">42.0885543823242</t>
@@ -773,31 +773,31 @@
     <t xml:space="preserve">38.4338035583496</t>
   </si>
   <si>
-    <t xml:space="preserve">38.9997024536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6363334655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9428596496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4380226135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5516967773438</t>
+    <t xml:space="preserve">38.999698638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6363372802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9428634643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4380187988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.551700592041</t>
   </si>
   <si>
     <t xml:space="preserve">38.0565414428711</t>
   </si>
   <si>
-    <t xml:space="preserve">39.1411819458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3298072814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0704383850098</t>
+    <t xml:space="preserve">39.1411743164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3298110961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0704307556152</t>
   </si>
   <si>
     <t xml:space="preserve">39.1647567749023</t>
@@ -806,10 +806,10 @@
     <t xml:space="preserve">38.6695976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">38.834644317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.905387878418</t>
+    <t xml:space="preserve">38.8346481323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9053840637207</t>
   </si>
   <si>
     <t xml:space="preserve">39.0940208435059</t>
@@ -821,40 +821,40 @@
     <t xml:space="preserve">38.2687530517578</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7403297424316</t>
+    <t xml:space="preserve">38.7403335571289</t>
   </si>
   <si>
     <t xml:space="preserve">38.6931800842285</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2354927062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.2590675354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1357078552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5129776000977</t>
+    <t xml:space="preserve">39.2354888916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.2590713500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1357116699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5129814147949</t>
   </si>
   <si>
     <t xml:space="preserve">44.7765617370605</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8001441955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.507511138916</t>
+    <t xml:space="preserve">44.8001403808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5075149536133</t>
   </si>
   <si>
     <t xml:space="preserve">45.3188781738281</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8140411376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.682243347168</t>
+    <t xml:space="preserve">45.814037322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6822509765625</t>
   </si>
   <si>
     <t xml:space="preserve">43.7862434387207</t>
@@ -863,16 +863,16 @@
     <t xml:space="preserve">44.7529830932617</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1302452087402</t>
+    <t xml:space="preserve">45.1302490234375</t>
   </si>
   <si>
     <t xml:space="preserve">44.4464569091797</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5879287719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3285598754883</t>
+    <t xml:space="preserve">44.5879325866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.328556060791</t>
   </si>
   <si>
     <t xml:space="preserve">44.3049812316895</t>
@@ -881,25 +881,25 @@
     <t xml:space="preserve">43.6211929321289</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1731872558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0788688659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5837097167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.267505645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3660354614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9887771606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4936180114746</t>
+    <t xml:space="preserve">43.1731910705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0788726806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5837135314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2675018310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.366039276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9887733459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4936103820801</t>
   </si>
   <si>
     <t xml:space="preserve">44.5171966552734</t>
@@ -911,52 +911,52 @@
     <t xml:space="preserve">45.861198425293</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4035186767578</t>
+    <t xml:space="preserve">46.4035224914551</t>
   </si>
   <si>
     <t xml:space="preserve">47.5824661254883</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0637245178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.134464263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1580390930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9125747680664</t>
+    <t xml:space="preserve">47.0637321472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1344604492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1580429077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9125671386719</t>
   </si>
   <si>
     <t xml:space="preserve">49.3508949279785</t>
   </si>
   <si>
-    <t xml:space="preserve">48.7378349304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.101203918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8321571350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6296195983887</t>
+    <t xml:space="preserve">48.7378425598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1012077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8321533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6296272277832</t>
   </si>
   <si>
     <t xml:space="preserve">48.0540466308594</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8654136657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9597320556641</t>
+    <t xml:space="preserve">47.8654174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9597282409668</t>
   </si>
   <si>
     <t xml:space="preserve">49.1858406066895</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2717247009277</t>
+    <t xml:space="preserve">45.2717208862305</t>
   </si>
   <si>
     <t xml:space="preserve">45.0359306335449</t>
@@ -968,13 +968,13 @@
     <t xml:space="preserve">43.9748725891113</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5601387023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.913818359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7251892089844</t>
+    <t xml:space="preserve">42.5601272583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9138221740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7251853942871</t>
   </si>
   <si>
     <t xml:space="preserve">42.2064514160156</t>
@@ -986,103 +986,103 @@
     <t xml:space="preserve">42.1781539916992</t>
   </si>
   <si>
-    <t xml:space="preserve">43.3476715087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9800796508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3010139465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0838356018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7534790039062</t>
+    <t xml:space="preserve">43.3476753234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9800872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3010215759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0838317871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7534828186035</t>
   </si>
   <si>
     <t xml:space="preserve">42.593147277832</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4799652099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0081367492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0458602905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3288040161133</t>
+    <t xml:space="preserve">42.4799690246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0081253051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0458641052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3288078308105</t>
   </si>
   <si>
     <t xml:space="preserve">41.3953323364258</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4891471862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2342414855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1210632324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2439270019531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1027030944824</t>
+    <t xml:space="preserve">43.4891510009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2342529296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1210708618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2439231872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1026954650879</t>
   </si>
   <si>
     <t xml:space="preserve">41.1689758300781</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2729721069336</t>
+    <t xml:space="preserve">40.2729759216309</t>
   </si>
   <si>
     <t xml:space="preserve">42.4045104980469</t>
   </si>
   <si>
-    <t xml:space="preserve">43.7626647949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.253101348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0547943115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9510498046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2809028625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1488609313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3094482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9982032775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5358047485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1679725646973</t>
+    <t xml:space="preserve">43.7626724243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2531089782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0547904968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9510459899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2808990478516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.148853302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3094520568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9981994628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5358085632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.16796875</t>
   </si>
   <si>
     <t xml:space="preserve">45.5923957824707</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6586647033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2533569335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6683502197266</t>
+    <t xml:space="preserve">44.6586608886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.253360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6683464050293</t>
   </si>
   <si>
     <t xml:space="preserve">44.2248115539551</t>
@@ -1091,28 +1091,28 @@
     <t xml:space="preserve">45.0830917358398</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2056999206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.328067779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0356826782227</t>
+    <t xml:space="preserve">45.2057037353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3280601501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0356864929199</t>
   </si>
   <si>
     <t xml:space="preserve">45.6584205627441</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5169410705566</t>
+    <t xml:space="preserve">45.5169486999512</t>
   </si>
   <si>
     <t xml:space="preserve">44.1682243347168</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8664093017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5457344055176</t>
+    <t xml:space="preserve">43.8664131164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5457382202148</t>
   </si>
   <si>
     <t xml:space="preserve">43.8852767944336</t>
@@ -1121,46 +1121,46 @@
     <t xml:space="preserve">44.4606018066406</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6112594604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6301231384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7244338989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2903327941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0262489318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2148857116699</t>
+    <t xml:space="preserve">45.611255645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.630126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.724437713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.290340423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.026252746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2148818969727</t>
   </si>
   <si>
     <t xml:space="preserve">46.6487312316895</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7053260803223</t>
+    <t xml:space="preserve">46.7053298950195</t>
   </si>
   <si>
     <t xml:space="preserve">46.5921478271484</t>
   </si>
   <si>
-    <t xml:space="preserve">46.8939552307129</t>
+    <t xml:space="preserve">46.8939628601074</t>
   </si>
   <si>
     <t xml:space="preserve">47.7710990905762</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8182563781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1955223083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9972114562988</t>
+    <t xml:space="preserve">47.8182525634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1955184936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9972076416016</t>
   </si>
   <si>
     <t xml:space="preserve">48.5727844238281</t>
@@ -1175,28 +1175,28 @@
     <t xml:space="preserve">50.4119491577148</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8460540771484</t>
+    <t xml:space="preserve">49.8460464477539</t>
   </si>
   <si>
     <t xml:space="preserve">49.3744697570801</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2233123779297</t>
+    <t xml:space="preserve">50.223316192627</t>
   </si>
   <si>
     <t xml:space="preserve">50.0818405151367</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5353050231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1960144042969</t>
+    <t xml:space="preserve">47.5353088378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1960182189941</t>
   </si>
   <si>
     <t xml:space="preserve">47.2052040100098</t>
   </si>
   <si>
-    <t xml:space="preserve">48.0068855285645</t>
+    <t xml:space="preserve">48.006893157959</t>
   </si>
   <si>
     <t xml:space="preserve">47.2523574829102</t>
@@ -1205,88 +1205,88 @@
     <t xml:space="preserve">46.4223785400391</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8376121520996</t>
+    <t xml:space="preserve">45.8376159667969</t>
   </si>
   <si>
     <t xml:space="preserve">45.6489868164062</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8753509521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5732879638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.4687919616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8085746765137</t>
+    <t xml:space="preserve">45.8753433227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5732841491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.4687843322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8085784912109</t>
   </si>
   <si>
     <t xml:space="preserve">46.4789657592773</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3938331604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5166931152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1774063110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7812805175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8378639221191</t>
+    <t xml:space="preserve">47.3938369750977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5166893005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1774101257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7812767028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8378677368164</t>
   </si>
   <si>
     <t xml:space="preserve">44.4983291625977</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1776580810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.895206451416</t>
+    <t xml:space="preserve">44.177661895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8952026367188</t>
   </si>
   <si>
     <t xml:space="preserve">42.2913360595703</t>
   </si>
   <si>
-    <t xml:space="preserve">42.498836517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0652236938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.951789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.328311920166</t>
+    <t xml:space="preserve">42.4988327026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0652275085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9517936706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3283081054688</t>
   </si>
   <si>
     <t xml:space="preserve">45.4414939880371</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4603538513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4037666320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1017036437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9885215759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.384651184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.0443649291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.902889251709</t>
+    <t xml:space="preserve">45.4603614807129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4037590026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1016998291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.988525390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3846473693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.044361114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9028930664062</t>
   </si>
   <si>
     <t xml:space="preserve">48.2898368835449</t>
@@ -1298,37 +1298,37 @@
     <t xml:space="preserve">50.6948928833008</t>
   </si>
   <si>
-    <t xml:space="preserve">50.6005821228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9328536987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4107131958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0277900695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.2144889831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1195526123047</t>
+    <t xml:space="preserve">50.6005783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.932861328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.410717010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0277862548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.2144813537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.119556427002</t>
   </si>
   <si>
     <t xml:space="preserve">51.7398071289062</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8410987854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5024719238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.271484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3664207458496</t>
+    <t xml:space="preserve">49.8410949707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5024642944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2714881896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3664169311523</t>
   </si>
   <si>
     <t xml:space="preserve">49.081615447998</t>
@@ -1346,10 +1346,10 @@
     <t xml:space="preserve">48.0847969055176</t>
   </si>
   <si>
-    <t xml:space="preserve">48.6544036865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3189544677734</t>
+    <t xml:space="preserve">48.6543998718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3189506530762</t>
   </si>
   <si>
     <t xml:space="preserve">49.6512260437012</t>
@@ -1358,19 +1358,19 @@
     <t xml:space="preserve">49.9835014343262</t>
   </si>
   <si>
-    <t xml:space="preserve">50.3632392883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2176666259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1733703613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4549980163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.0246124267578</t>
+    <t xml:space="preserve">50.3632431030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.217658996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1733741760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4550018310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.0246086120605</t>
   </si>
   <si>
     <t xml:space="preserve">53.0689086914062</t>
@@ -1379,22 +1379,22 @@
     <t xml:space="preserve">52.7840995788574</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4422874450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.682804107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1100158691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5846939086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3916473388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.7302742004395</t>
+    <t xml:space="preserve">55.4422950744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6828079223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1100120544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5846900939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3916435241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.7302780151367</t>
   </si>
   <si>
     <t xml:space="preserve">55.0625495910645</t>
@@ -1409,13 +1409,13 @@
     <t xml:space="preserve">53.1638374328613</t>
   </si>
   <si>
-    <t xml:space="preserve">53.6385154724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0182609558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3030624389648</t>
+    <t xml:space="preserve">53.6385192871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0182647705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3030662536621</t>
   </si>
   <si>
     <t xml:space="preserve">54.1131896972656</t>
@@ -1424,79 +1424,79 @@
     <t xml:space="preserve">53.8283882141113</t>
   </si>
   <si>
-    <t xml:space="preserve">54.7777442932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4391098022461</t>
+    <t xml:space="preserve">54.7777404785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4391136169434</t>
   </si>
   <si>
     <t xml:space="preserve">56.9137878417969</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2967071533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.011905670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2017707824707</t>
+    <t xml:space="preserve">56.296703338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0119018554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.201774597168</t>
   </si>
   <si>
     <t xml:space="preserve">56.5340423583984</t>
   </si>
   <si>
-    <t xml:space="preserve">56.6764526367188</t>
+    <t xml:space="preserve">56.6764488220215</t>
   </si>
   <si>
     <t xml:space="preserve">54.9676132202148</t>
   </si>
   <si>
-    <t xml:space="preserve">52.5942306518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0214309692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1574783325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.350528717041</t>
+    <t xml:space="preserve">52.5942268371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0214424133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1574745178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3505325317383</t>
   </si>
   <si>
     <t xml:space="preserve">52.9264945983887</t>
   </si>
   <si>
-    <t xml:space="preserve">52.8790321350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0657272338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5878715515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4486465454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.6859893798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3062438964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.4043579101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0752563476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.458179473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.2619476318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8822174072266</t>
+    <t xml:space="preserve">52.879035949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0657234191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5878639221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4486427307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.685977935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3062477111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.404354095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.075252532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4581832885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.2619438171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.882209777832</t>
   </si>
   <si>
     <t xml:space="preserve">54.1606597900391</t>
@@ -1505,13 +1505,13 @@
     <t xml:space="preserve">54.2081260681152</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5435791015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5404014587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.204948425293</t>
+    <t xml:space="preserve">53.5435829162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5404052734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.2049522399902</t>
   </si>
   <si>
     <t xml:space="preserve">56.2492370605469</t>
@@ -1526,37 +1526,37 @@
     <t xml:space="preserve">57.9106101989746</t>
   </si>
   <si>
-    <t xml:space="preserve">56.961254119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7904586791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.4138870239258</t>
+    <t xml:space="preserve">56.9612579345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.790454864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.413890838623</t>
   </si>
   <si>
     <t xml:space="preserve">47.0120239257812</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0499992370605</t>
+    <t xml:space="preserve">47.0499954223633</t>
   </si>
   <si>
     <t xml:space="preserve">48.2271957397461</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4677085876465</t>
+    <t xml:space="preserve">47.4677124023438</t>
   </si>
   <si>
     <t xml:space="preserve">50.0309715270996</t>
   </si>
   <si>
-    <t xml:space="preserve">50.3157768249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3474731445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7525596618652</t>
+    <t xml:space="preserve">50.3157730102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3474769592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.752555847168</t>
   </si>
   <si>
     <t xml:space="preserve">44.6766128540039</t>
@@ -1565,28 +1565,28 @@
     <t xml:space="preserve">44.6956024169922</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1955757141113</t>
+    <t xml:space="preserve">46.1955795288086</t>
   </si>
   <si>
     <t xml:space="preserve">46.5563354492188</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4803810119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9487495422363</t>
+    <t xml:space="preserve">46.4803848266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9487419128418</t>
   </si>
   <si>
     <t xml:space="preserve">47.4107475280762</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5373497009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5183601379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7462005615234</t>
+    <t xml:space="preserve">46.5373420715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5183563232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7462043762207</t>
   </si>
   <si>
     <t xml:space="preserve">46.4424095153809</t>
@@ -1601,34 +1601,34 @@
     <t xml:space="preserve">45.5690040588379</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7019195556641</t>
+    <t xml:space="preserve">45.7019119262695</t>
   </si>
   <si>
     <t xml:space="preserve">42.3601913452148</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4678001403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9234886169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.8728332519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7462501525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2968635559082</t>
+    <t xml:space="preserve">41.4677925109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9234809875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.8728370666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7462463378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2968673706055</t>
   </si>
   <si>
     <t xml:space="preserve">43.8601684570312</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7209014892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7841758728027</t>
+    <t xml:space="preserve">45.7208976745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7841720581055</t>
   </si>
   <si>
     <t xml:space="preserve">47.7050514221191</t>
@@ -1643,16 +1643,16 @@
     <t xml:space="preserve">45.1892623901367</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2082481384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2842025756836</t>
+    <t xml:space="preserve">45.208251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2841987609863</t>
   </si>
   <si>
     <t xml:space="preserve">47.3158187866211</t>
   </si>
   <si>
-    <t xml:space="preserve">47.3727798461914</t>
+    <t xml:space="preserve">47.3727836608887</t>
   </si>
   <si>
     <t xml:space="preserve">46.6132926940918</t>
@@ -1661,13 +1661,13 @@
     <t xml:space="preserve">44.4867401123047</t>
   </si>
   <si>
-    <t xml:space="preserve">43.5373878479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5183982849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0753784179688</t>
+    <t xml:space="preserve">43.5373840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5184020996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.075382232666</t>
   </si>
   <si>
     <t xml:space="preserve">41.5627288818359</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">40.2146492004395</t>
   </si>
   <si>
-    <t xml:space="preserve">41.847541809082</t>
+    <t xml:space="preserve">41.8475379943848</t>
   </si>
   <si>
     <t xml:space="preserve">42.4551200866699</t>
@@ -1685,91 +1685,91 @@
     <t xml:space="preserve">40.2526245117188</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8095588684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1956214904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0310478210449</t>
+    <t xml:space="preserve">41.8095626831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.195613861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0310516357422</t>
   </si>
   <si>
     <t xml:space="preserve">44.3158531188965</t>
   </si>
   <si>
-    <t xml:space="preserve">44.334846496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8791580200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7398910522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8348236083984</t>
+    <t xml:space="preserve">44.3348426818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8791542053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7398872375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8348197937012</t>
   </si>
   <si>
     <t xml:space="preserve">46.8031616210938</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3854484558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4234275817871</t>
+    <t xml:space="preserve">46.3854522705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4234237670898</t>
   </si>
   <si>
     <t xml:space="preserve">47.1829071044922</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1765518188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.3695945739746</t>
+    <t xml:space="preserve">49.1765480041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.3696022033691</t>
   </si>
   <si>
     <t xml:space="preserve">45.4360961914062</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0753402709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6449546813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2588539123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4645385742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8885688781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1259002685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6955146789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2208366394043</t>
+    <t xml:space="preserve">45.0753364562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6449584960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2588500976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4645309448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8885650634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.125904083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6955223083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2208404541016</t>
   </si>
   <si>
     <t xml:space="preserve">49.93603515625</t>
   </si>
   <si>
-    <t xml:space="preserve">50.078441619873</t>
+    <t xml:space="preserve">50.0784378051758</t>
   </si>
   <si>
     <t xml:space="preserve">52.1670150756836</t>
   </si>
   <si>
-    <t xml:space="preserve">52.6891593933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9739646911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.2555923461914</t>
+    <t xml:space="preserve">52.6891632080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9739685058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.2555961608887</t>
   </si>
   <si>
     <t xml:space="preserve">53.2587738037109</t>
@@ -1784,19 +1784,19 @@
     <t xml:space="preserve">55.2998886108398</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3980026245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4011726379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.9233207702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4929351806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4454650878906</t>
+    <t xml:space="preserve">54.3979949951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.401180267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9233131408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4929389953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4454612731934</t>
   </si>
   <si>
     <t xml:space="preserve">53.4961128234863</t>
@@ -1808,7 +1808,7 @@
     <t xml:space="preserve">55.9644393920898</t>
   </si>
   <si>
-    <t xml:space="preserve">55.7270927429199</t>
+    <t xml:space="preserve">55.7270965576172</t>
   </si>
   <si>
     <t xml:space="preserve">56.1068305969238</t>
@@ -1820,25 +1820,25 @@
     <t xml:space="preserve">53.5239143371582</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5717391967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6151084899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5194473266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4671363830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5283813476562</t>
+    <t xml:space="preserve">53.5717430114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6151008605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5194435119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4671401977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5283851623535</t>
   </si>
   <si>
     <t xml:space="preserve">55.9633407592773</t>
   </si>
   <si>
-    <t xml:space="preserve">56.0590019226074</t>
+    <t xml:space="preserve">56.0589981079102</t>
   </si>
   <si>
     <t xml:space="preserve">55.1980285644531</t>
@@ -1850,25 +1850,25 @@
     <t xml:space="preserve">56.011173248291</t>
   </si>
   <si>
-    <t xml:space="preserve">55.6285133361816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2025032043457</t>
+    <t xml:space="preserve">55.6285171508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2024993896484</t>
   </si>
   <si>
     <t xml:space="preserve">55.9155120849609</t>
   </si>
   <si>
-    <t xml:space="preserve">56.4416618347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.580680847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3459930419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1501960754395</t>
+    <t xml:space="preserve">56.4416580200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5806846618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3459968566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1501998901367</t>
   </si>
   <si>
     <t xml:space="preserve">54.5762176513672</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">54.4327201843262</t>
   </si>
   <si>
-    <t xml:space="preserve">54.8632011413574</t>
+    <t xml:space="preserve">54.8632049560547</t>
   </si>
   <si>
     <t xml:space="preserve">56.9199829101562</t>
@@ -1886,10 +1886,10 @@
     <t xml:space="preserve">56.8243179321289</t>
   </si>
   <si>
-    <t xml:space="preserve">57.2547950744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6808166503906</t>
+    <t xml:space="preserve">57.2547988891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6808242797852</t>
   </si>
   <si>
     <t xml:space="preserve">56.7286491394043</t>
@@ -1898,7 +1898,7 @@
     <t xml:space="preserve">58.2114410400391</t>
   </si>
   <si>
-    <t xml:space="preserve">57.6374588012695</t>
+    <t xml:space="preserve">57.637451171875</t>
   </si>
   <si>
     <t xml:space="preserve">58.5462646484375</t>
@@ -1913,13 +1913,13 @@
     <t xml:space="preserve">57.7331161499023</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3504676818848</t>
+    <t xml:space="preserve">57.3504638671875</t>
   </si>
   <si>
     <t xml:space="preserve">58.3071060180664</t>
   </si>
   <si>
-    <t xml:space="preserve">60.2682075500488</t>
+    <t xml:space="preserve">60.2682151794434</t>
   </si>
   <si>
     <t xml:space="preserve">60.172550201416</t>
@@ -1928,70 +1928,70 @@
     <t xml:space="preserve">59.7420616149902</t>
   </si>
   <si>
-    <t xml:space="preserve">59.2159156799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.120246887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3026428222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.8287887573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.1157760620117</t>
+    <t xml:space="preserve">59.2159118652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.1202430725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3026313781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.828784942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.1157722473145</t>
   </si>
   <si>
     <t xml:space="preserve">57.7809562683105</t>
   </si>
   <si>
-    <t xml:space="preserve">59.0245819091797</t>
+    <t xml:space="preserve">59.024585723877</t>
   </si>
   <si>
     <t xml:space="preserve">59.4550704956055</t>
   </si>
   <si>
-    <t xml:space="preserve">60.3160438537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.0290489196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.0724105834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.25927734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0201187133789</t>
+    <t xml:space="preserve">60.3160400390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.029052734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.0724143981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.2592735290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0201110839844</t>
   </si>
   <si>
     <t xml:space="preserve">50.9888191223145</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4148406982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2279777526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.3236427307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.8931579589844</t>
+    <t xml:space="preserve">50.4148330688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2279815673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.3236465454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.8931541442871</t>
   </si>
   <si>
     <t xml:space="preserve">49.7930221557617</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8408508300781</t>
+    <t xml:space="preserve">49.8408546447754</t>
   </si>
   <si>
     <t xml:space="preserve">48.6928863525391</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2668762207031</t>
+    <t xml:space="preserve">49.2668724060059</t>
   </si>
   <si>
     <t xml:space="preserve">49.9843521118164</t>
@@ -2012,43 +2012,43 @@
     <t xml:space="preserve">50.8453254699707</t>
   </si>
   <si>
-    <t xml:space="preserve">51.4193077087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9409866333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5149726867676</t>
+    <t xml:space="preserve">51.419303894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.940990447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5149688720703</t>
   </si>
   <si>
     <t xml:space="preserve">50.797492980957</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1323165893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6973609924316</t>
+    <t xml:space="preserve">51.1323204040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6973571777344</t>
   </si>
   <si>
     <t xml:space="preserve">49.3147048950195</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4582023620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7451934814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0321769714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8363876342773</t>
+    <t xml:space="preserve">49.4581985473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.745189666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0321807861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8363838195801</t>
   </si>
   <si>
     <t xml:space="preserve">48.597225189209</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3625373840332</t>
+    <t xml:space="preserve">49.3625335693359</t>
   </si>
   <si>
     <t xml:space="preserve">54.0022315979004</t>
@@ -2060,94 +2060,94 @@
     <t xml:space="preserve">54.2892227172852</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1935577392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0934219360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.471607208252</t>
+    <t xml:space="preserve">54.1935653686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0934257507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.4716110229492</t>
   </si>
   <si>
     <t xml:space="preserve">53.2847518920898</t>
   </si>
   <si>
-    <t xml:space="preserve">54.097900390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9110374450684</t>
+    <t xml:space="preserve">54.0978965759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9110336303711</t>
   </si>
   <si>
     <t xml:space="preserve">54.3370552062988</t>
   </si>
   <si>
-    <t xml:space="preserve">53.8587379455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4805488586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.0545310974121</t>
+    <t xml:space="preserve">53.8587341308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4805564880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.0545349121094</t>
   </si>
   <si>
     <t xml:space="preserve">55.3415260314941</t>
   </si>
   <si>
-    <t xml:space="preserve">55.86767578125</t>
+    <t xml:space="preserve">55.8676795959473</t>
   </si>
   <si>
     <t xml:space="preserve">56.5373191833496</t>
   </si>
   <si>
-    <t xml:space="preserve">56.6329879760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.4027633666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.067943572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6942291259766</t>
+    <t xml:space="preserve">56.632984161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.4027671813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0679473876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6942329406738</t>
   </si>
   <si>
     <t xml:space="preserve">59.3115730285645</t>
   </si>
   <si>
-    <t xml:space="preserve">62.8511390686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6164512634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.3383941650391</t>
+    <t xml:space="preserve">62.8511276245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6164436340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.3384017944336</t>
   </si>
   <si>
     <t xml:space="preserve">66.3428649902344</t>
   </si>
   <si>
-    <t xml:space="preserve">66.9646835327148</t>
+    <t xml:space="preserve">66.9646759033203</t>
   </si>
   <si>
     <t xml:space="preserve">67.9213256835938</t>
   </si>
   <si>
-    <t xml:space="preserve">69.2606201171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.0692749023438</t>
+    <t xml:space="preserve">69.260612487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.0692825317383</t>
   </si>
   <si>
     <t xml:space="preserve">67.3951568603516</t>
   </si>
   <si>
-    <t xml:space="preserve">68.016975402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.8690185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.2995071411133</t>
+    <t xml:space="preserve">68.0169906616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.869010925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.2994995117188</t>
   </si>
   <si>
     <t xml:space="preserve">67.5386657714844</t>
@@ -2156,58 +2156,58 @@
     <t xml:space="preserve">68.9257888793945</t>
   </si>
   <si>
-    <t xml:space="preserve">69.212776184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.4474716186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.8734893798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.7778167724609</t>
+    <t xml:space="preserve">69.2127838134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.4474792480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.8734817504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.7778244018555</t>
   </si>
   <si>
     <t xml:space="preserve">67.0603408813477</t>
   </si>
   <si>
-    <t xml:space="preserve">66.0080490112305</t>
+    <t xml:space="preserve">66.0080413818359</t>
   </si>
   <si>
     <t xml:space="preserve">66.4385299682617</t>
   </si>
   <si>
-    <t xml:space="preserve">65.5775527954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.9123840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.2516632080078</t>
+    <t xml:space="preserve">65.5775604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.9123687744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.2516708374023</t>
   </si>
   <si>
     <t xml:space="preserve">67.8256607055664</t>
   </si>
   <si>
-    <t xml:space="preserve">67.6343231201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.7688827514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.1037063598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.4519348144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.2083129882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.3129196166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.3263244628906</t>
+    <t xml:space="preserve">67.6343154907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.7688903808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.1036911010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.4519424438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.2083053588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.3129119873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.3263168334961</t>
   </si>
   <si>
     <t xml:space="preserve">73.2306594848633</t>
@@ -2216,19 +2216,19 @@
     <t xml:space="preserve">74.0916366577148</t>
   </si>
   <si>
-    <t xml:space="preserve">73.6611404418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.3741607666016</t>
+    <t xml:space="preserve">73.6611480712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.374153137207</t>
   </si>
   <si>
     <t xml:space="preserve">70.6955718994141</t>
   </si>
   <si>
-    <t xml:space="preserve">70.7912368774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.4653549194336</t>
+    <t xml:space="preserve">70.7912292480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.4653472900391</t>
   </si>
   <si>
     <t xml:space="preserve">70.2650756835938</t>
@@ -2240,49 +2240,49 @@
     <t xml:space="preserve">71.3173828125</t>
   </si>
   <si>
-    <t xml:space="preserve">71.9391937255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.7044982910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.7523422241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.6088485717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.4264602661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.1394577026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7478790283203</t>
+    <t xml:space="preserve">71.9392013549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.7045211791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.7523498535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.6088409423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.4264678955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.1394653320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7478713989258</t>
   </si>
   <si>
     <t xml:space="preserve">71.9870300292969</t>
   </si>
   <si>
-    <t xml:space="preserve">73.2784957885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.4130477905273</t>
+    <t xml:space="preserve">73.2784881591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.4130554199219</t>
   </si>
   <si>
     <t xml:space="preserve">66.8211822509766</t>
   </si>
   <si>
-    <t xml:space="preserve">65.7210540771484</t>
+    <t xml:space="preserve">65.7210464477539</t>
   </si>
   <si>
     <t xml:space="preserve">62.1336479187012</t>
   </si>
   <si>
-    <t xml:space="preserve">63.8077697753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8944931030273</t>
+    <t xml:space="preserve">63.8077621459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8944969177246</t>
   </si>
   <si>
     <t xml:space="preserve">60.937858581543</t>
@@ -2291,115 +2291,115 @@
     <t xml:space="preserve">57.8766174316406</t>
   </si>
   <si>
-    <t xml:space="preserve">52.5672721862793</t>
+    <t xml:space="preserve">52.5672760009766</t>
   </si>
   <si>
     <t xml:space="preserve">52.0889587402344</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3778190612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.7407188415527</t>
+    <t xml:space="preserve">46.3778228759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.74072265625</t>
   </si>
   <si>
     <t xml:space="preserve">45.4594497680664</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7094306945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8714332580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2107238769531</t>
+    <t xml:space="preserve">41.7094345092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8714256286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2107200622559</t>
   </si>
   <si>
     <t xml:space="preserve">45.344654083252</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1048698425293</t>
+    <t xml:space="preserve">47.1048736572266</t>
   </si>
   <si>
     <t xml:space="preserve">51.0844841003418</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2190437316895</t>
+    <t xml:space="preserve">49.2190399169922</t>
   </si>
   <si>
     <t xml:space="preserve">59.1680793762207</t>
   </si>
   <si>
-    <t xml:space="preserve">57.6852836608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.263744354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.081356048584</t>
+    <t xml:space="preserve">57.6852874755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.2637405395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0813522338867</t>
   </si>
   <si>
     <t xml:space="preserve">60.3638763427734</t>
   </si>
   <si>
-    <t xml:space="preserve">61.1291885375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4161720275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.6598091125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.5207786560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.5641403198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.1381225585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0424652099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9901657104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.0335235595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.2684898376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9081344604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.7279663085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.7052001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.7179107666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.3676109313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6569557189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.0909805297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.4285659790039</t>
+    <t xml:space="preserve">61.1291847229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4161758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.6598014831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.5207862854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5641441345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.138126373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0424690246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.990161895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0335273742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.2684860229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9081382751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.7279624938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.705192565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.717903137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.367603302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6569595336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.0909729003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.4285583496094</t>
   </si>
   <si>
     <t xml:space="preserve">64.9108047485352</t>
   </si>
   <si>
-    <t xml:space="preserve">68.4312362670898</t>
+    <t xml:space="preserve">68.4312286376953</t>
   </si>
   <si>
     <t xml:space="preserve">68.0936584472656</t>
@@ -2411,19 +2411,19 @@
     <t xml:space="preserve">68.624137878418</t>
   </si>
   <si>
-    <t xml:space="preserve">69.9744262695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.3984069824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.1217803955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.9288787841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.362907409668</t>
+    <t xml:space="preserve">69.9744415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.3983993530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.1217727661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.9288711547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.3628997802734</t>
   </si>
   <si>
     <t xml:space="preserve">75.8578720092773</t>
@@ -2432,10 +2432,10 @@
     <t xml:space="preserve">74.6522598266602</t>
   </si>
   <si>
-    <t xml:space="preserve">71.8552093505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.6013412475586</t>
+    <t xml:space="preserve">71.8552017211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.6013565063477</t>
   </si>
   <si>
     <t xml:space="preserve">71.1318283081055</t>
@@ -2444,13 +2444,13 @@
     <t xml:space="preserve">70.2155609130859</t>
   </si>
   <si>
-    <t xml:space="preserve">65.9235305786133</t>
+    <t xml:space="preserve">65.9235382080078</t>
   </si>
   <si>
     <t xml:space="preserve">67.0327072143555</t>
   </si>
   <si>
-    <t xml:space="preserve">67.2256011962891</t>
+    <t xml:space="preserve">67.2256088256836</t>
   </si>
   <si>
     <t xml:space="preserve">64.8625869750977</t>
@@ -2462,10 +2462,10 @@
     <t xml:space="preserve">67.3220596313477</t>
   </si>
   <si>
-    <t xml:space="preserve">69.9262161254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.180061340332</t>
+    <t xml:space="preserve">69.9262008666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.1800537109375</t>
   </si>
   <si>
     <t xml:space="preserve">70.4084548950195</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">68.5276870727539</t>
   </si>
   <si>
-    <t xml:space="preserve">68.2865600585938</t>
+    <t xml:space="preserve">68.2865676879883</t>
   </si>
   <si>
     <t xml:space="preserve">68.6723556518555</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">69.2992782592773</t>
   </si>
   <si>
-    <t xml:space="preserve">72.1445617675781</t>
+    <t xml:space="preserve">72.1445541381836</t>
   </si>
   <si>
     <t xml:space="preserve">71.2765045166016</t>
@@ -2507,7 +2507,7 @@
     <t xml:space="preserve">70.1673278808594</t>
   </si>
   <si>
-    <t xml:space="preserve">70.5531311035156</t>
+    <t xml:space="preserve">70.5531387329102</t>
   </si>
   <si>
     <t xml:space="preserve">70.3602294921875</t>
@@ -2522,28 +2522,28 @@
     <t xml:space="preserve">72.8679275512695</t>
   </si>
   <si>
-    <t xml:space="preserve">73.4466400146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.543083190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9998779296875</t>
+    <t xml:space="preserve">73.4466171264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.5430755615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.999885559082</t>
   </si>
   <si>
     <t xml:space="preserve">73.0608291625977</t>
   </si>
   <si>
-    <t xml:space="preserve">73.6877593994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.59130859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.9643859863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.7486953735352</t>
+    <t xml:space="preserve">73.6877517700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.5913009643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.9643936157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.7487030029297</t>
   </si>
   <si>
     <t xml:space="preserve">81.9342193603516</t>
@@ -2561,19 +2561,19 @@
     <t xml:space="preserve">85.3581924438477</t>
   </si>
   <si>
-    <t xml:space="preserve">83.1398544311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0179443359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.0661773681641</t>
+    <t xml:space="preserve">83.1398468017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.017951965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.0661849975586</t>
   </si>
   <si>
     <t xml:space="preserve">82.609375</t>
   </si>
   <si>
-    <t xml:space="preserve">80.8732833862305</t>
+    <t xml:space="preserve">80.8732681274414</t>
   </si>
   <si>
     <t xml:space="preserve">83.0916213989258</t>
@@ -2585,88 +2585,88 @@
     <t xml:space="preserve">84.5865936279297</t>
   </si>
   <si>
-    <t xml:space="preserve">84.6348266601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.6703262329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.7794952392578</t>
+    <t xml:space="preserve">84.6348190307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.6703186035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.7795028686523</t>
   </si>
   <si>
     <t xml:space="preserve">84.6830520629883</t>
   </si>
   <si>
-    <t xml:space="preserve">87.3836517333984</t>
+    <t xml:space="preserve">87.3836364746094</t>
   </si>
   <si>
     <t xml:space="preserve">86.2262496948242</t>
   </si>
   <si>
-    <t xml:space="preserve">87.7212142944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.6984405517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3126373291016</t>
+    <t xml:space="preserve">87.7212066650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.6984329223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3126449584961</t>
   </si>
   <si>
     <t xml:space="preserve">90.6629409790039</t>
   </si>
   <si>
-    <t xml:space="preserve">88.1070175170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.8658981323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.2416381835938</t>
+    <t xml:space="preserve">88.1070098876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.8658905029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.2416458129883</t>
   </si>
   <si>
     <t xml:space="preserve">90.2771377563477</t>
   </si>
   <si>
-    <t xml:space="preserve">90.5664901733398</t>
+    <t xml:space="preserve">90.5664978027344</t>
   </si>
   <si>
     <t xml:space="preserve">90.8076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">92.9777450561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.0031890869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9067459106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.2188720703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5082092285156</t>
+    <t xml:space="preserve">92.9777374267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.0031967163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9067306518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7265701293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.218864440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5082168579102</t>
   </si>
   <si>
     <t xml:space="preserve">91.4827728271484</t>
   </si>
   <si>
-    <t xml:space="preserve">89.9395599365234</t>
+    <t xml:space="preserve">89.939567565918</t>
   </si>
   <si>
     <t xml:space="preserve">91.62744140625</t>
   </si>
   <si>
-    <t xml:space="preserve">92.1096954345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3635482788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.5336608886719</t>
+    <t xml:space="preserve">92.1096878051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3635406494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.5336685180664</t>
   </si>
   <si>
     <t xml:space="preserve">94.954963684082</t>
@@ -2675,34 +2675,34 @@
     <t xml:space="preserve">94.8102951049805</t>
   </si>
   <si>
-    <t xml:space="preserve">93.6046676635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.5209503173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6883926391602</t>
+    <t xml:space="preserve">93.6046752929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.5209350585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6883850097656</t>
   </si>
   <si>
     <t xml:space="preserve">91.4345397949219</t>
   </si>
   <si>
-    <t xml:space="preserve">93.0259628295898</t>
+    <t xml:space="preserve">93.0259704589844</t>
   </si>
   <si>
     <t xml:space="preserve">95.2925491333008</t>
   </si>
   <si>
-    <t xml:space="preserve">97.2215423583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.115028381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.7292404174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.6073379516602</t>
+    <t xml:space="preserve">97.2215347290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.115036010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.7292327880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.6073303222656</t>
   </si>
   <si>
     <t xml:space="preserve">97.8966903686523</t>
@@ -2711,22 +2711,22 @@
     <t xml:space="preserve">98.3789367675781</t>
   </si>
   <si>
-    <t xml:space="preserve">96.3052597045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.7493362426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.8330612182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.8813018798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.4445953369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.2034530639648</t>
+    <t xml:space="preserve">96.3052749633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7493438720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.8330688476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.8812942504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.4445877075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.2034683227539</t>
   </si>
   <si>
     <t xml:space="preserve">89.0233001708984</t>
@@ -2735,34 +2735,34 @@
     <t xml:space="preserve">90.1324615478516</t>
   </si>
   <si>
-    <t xml:space="preserve">92.2061386108398</t>
+    <t xml:space="preserve">92.2061309814453</t>
   </si>
   <si>
     <t xml:space="preserve">96.4499359130859</t>
   </si>
   <si>
-    <t xml:space="preserve">95.4372177124023</t>
+    <t xml:space="preserve">95.4372100830078</t>
   </si>
   <si>
     <t xml:space="preserve">95.7747955322266</t>
   </si>
   <si>
-    <t xml:space="preserve">92.4472732543945</t>
+    <t xml:space="preserve">92.447265625</t>
   </si>
   <si>
     <t xml:space="preserve">92.0614624023438</t>
   </si>
   <si>
-    <t xml:space="preserve">91.8685607910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.8203430175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.711181640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.855842590332</t>
+    <t xml:space="preserve">91.8685684204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.8203353881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7111663818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8558349609375</t>
   </si>
   <si>
     <t xml:space="preserve">91.3863143920898</t>
@@ -2771,25 +2771,25 @@
     <t xml:space="preserve">90.759391784668</t>
   </si>
   <si>
-    <t xml:space="preserve">87.7694473266602</t>
+    <t xml:space="preserve">87.7694396972656</t>
   </si>
   <si>
     <t xml:space="preserve">88.2517013549805</t>
   </si>
   <si>
-    <t xml:space="preserve">89.3608703613281</t>
+    <t xml:space="preserve">89.3608779907227</t>
   </si>
   <si>
     <t xml:space="preserve">90.3735885620117</t>
   </si>
   <si>
-    <t xml:space="preserve">94.2798156738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.0842514038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.1451950073242</t>
+    <t xml:space="preserve">94.2798233032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.0842361450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.1451873779297</t>
   </si>
   <si>
     <t xml:space="preserve">92.495491027832</t>
@@ -2798,10 +2798,10 @@
     <t xml:space="preserve">89.4573135375977</t>
   </si>
   <si>
-    <t xml:space="preserve">91.675666809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.9167938232422</t>
+    <t xml:space="preserve">91.6756744384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.9168014526367</t>
   </si>
   <si>
     <t xml:space="preserve">91.7238922119141</t>
@@ -2810,7 +2810,7 @@
     <t xml:space="preserve">91.0969696044922</t>
   </si>
   <si>
-    <t xml:space="preserve">90.9040679931641</t>
+    <t xml:space="preserve">90.9040756225586</t>
   </si>
   <si>
     <t xml:space="preserve">92.3508148193359</t>
@@ -2819,16 +2819,16 @@
     <t xml:space="preserve">93.4599914550781</t>
   </si>
   <si>
-    <t xml:space="preserve">92.5437164306641</t>
+    <t xml:space="preserve">92.5437088012695</t>
   </si>
   <si>
     <t xml:space="preserve">95.9194641113281</t>
   </si>
   <si>
-    <t xml:space="preserve">93.2670822143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5564498901367</t>
+    <t xml:space="preserve">93.2670974731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5564346313477</t>
   </si>
   <si>
     <t xml:space="preserve">94.5691680908203</t>
@@ -2837,10 +2837,10 @@
     <t xml:space="preserve">96.0641403198242</t>
   </si>
   <si>
-    <t xml:space="preserve">98.4753952026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.018585205078</t>
+    <t xml:space="preserve">98.4753875732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.018592834473</t>
   </si>
   <si>
     <t xml:space="preserve">98.18603515625</t>
@@ -2852,25 +2852,25 @@
     <t xml:space="preserve">100.790191650391</t>
   </si>
   <si>
-    <t xml:space="preserve">102.912078857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.46533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.719184875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.52628326416</t>
+    <t xml:space="preserve">102.912086486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.465324401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.719192504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.526290893555</t>
   </si>
   <si>
     <t xml:space="preserve">102.140487670898</t>
   </si>
   <si>
-    <t xml:space="preserve">104.937538146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.104988098145</t>
+    <t xml:space="preserve">104.937530517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.104995727539</t>
   </si>
   <si>
     <t xml:space="preserve">103.587242126465</t>
@@ -2879,10 +2879,10 @@
     <t xml:space="preserve">102.815635681152</t>
   </si>
   <si>
-    <t xml:space="preserve">103.201446533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.500831604004</t>
+    <t xml:space="preserve">103.201431274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.500839233398</t>
   </si>
   <si>
     <t xml:space="preserve">100.404388427734</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">98.5718383789062</t>
   </si>
   <si>
-    <t xml:space="preserve">95.0514144897461</t>
+    <t xml:space="preserve">95.0514221191406</t>
   </si>
   <si>
     <t xml:space="preserve">94.135139465332</t>
@@ -2900,61 +2900,61 @@
     <t xml:space="preserve">92.5919418334961</t>
   </si>
   <si>
-    <t xml:space="preserve">89.2162017822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.297882080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.3434448242188</t>
+    <t xml:space="preserve">89.216194152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.297889709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.3434371948242</t>
   </si>
   <si>
     <t xml:space="preserve">101.561790466309</t>
   </si>
   <si>
-    <t xml:space="preserve">103.973037719727</t>
+    <t xml:space="preserve">103.973030090332</t>
   </si>
   <si>
     <t xml:space="preserve">103.780136108398</t>
   </si>
   <si>
-    <t xml:space="preserve">105.32332611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.490783691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.069488525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.02392578125</t>
+    <t xml:space="preserve">105.323333740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.490791320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.069480895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.023933410645</t>
   </si>
   <si>
     <t xml:space="preserve">110.14582824707</t>
   </si>
   <si>
-    <t xml:space="preserve">108.699081420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.28783416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.445236206055</t>
+    <t xml:space="preserve">108.699073791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.287826538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.44522857666</t>
   </si>
   <si>
     <t xml:space="preserve">106.384284973145</t>
   </si>
   <si>
-    <t xml:space="preserve">108.891990661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.831047058105</t>
+    <t xml:space="preserve">108.891983032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.831039428711</t>
   </si>
   <si>
     <t xml:space="preserve">108.795532226562</t>
   </si>
   <si>
-    <t xml:space="preserve">109.084892272949</t>
+    <t xml:space="preserve">109.084884643555</t>
   </si>
   <si>
     <t xml:space="preserve">107.059432983398</t>
@@ -2966,7 +2966,7 @@
     <t xml:space="preserve">109.56713104248</t>
   </si>
   <si>
-    <t xml:space="preserve">108.50617980957</t>
+    <t xml:space="preserve">108.506187438965</t>
   </si>
   <si>
     <t xml:space="preserve">109.530754089355</t>
@@ -2975,25 +2975,25 @@
     <t xml:space="preserve">107.786018371582</t>
   </si>
   <si>
-    <t xml:space="preserve">108.755325317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.046112060547</t>
+    <t xml:space="preserve">108.755310058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.046104431152</t>
   </si>
   <si>
     <t xml:space="preserve">109.918479919434</t>
   </si>
   <si>
-    <t xml:space="preserve">110.500045776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.821548461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.88777923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.663215637207</t>
+    <t xml:space="preserve">110.500061035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.821556091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.887786865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.663208007812</t>
   </si>
   <si>
     <t xml:space="preserve">113.117164611816</t>
@@ -3002,10 +3002,10 @@
     <t xml:space="preserve">115.831199645996</t>
   </si>
   <si>
-    <t xml:space="preserve">113.795677185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.764976501465</t>
+    <t xml:space="preserve">113.795669555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.76496887207</t>
   </si>
   <si>
     <t xml:space="preserve">114.668045043945</t>
@@ -3014,10 +3014,10 @@
     <t xml:space="preserve">114.280319213867</t>
   </si>
   <si>
-    <t xml:space="preserve">114.474182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.509712219238</t>
+    <t xml:space="preserve">114.474174499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.509704589844</t>
   </si>
   <si>
     <t xml:space="preserve">121.453140258789</t>
@@ -3029,19 +3029,19 @@
     <t xml:space="preserve">128.819793701172</t>
   </si>
   <si>
-    <t xml:space="preserve">127.365852355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.268928527832</t>
+    <t xml:space="preserve">127.365844726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.268936157227</t>
   </si>
   <si>
     <t xml:space="preserve">128.432083129883</t>
   </si>
   <si>
-    <t xml:space="preserve">133.181640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.467620849609</t>
+    <t xml:space="preserve">133.181655883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.46760559082</t>
   </si>
   <si>
     <t xml:space="preserve">130.273742675781</t>
@@ -3053,22 +3053,22 @@
     <t xml:space="preserve">134.635589599609</t>
   </si>
   <si>
-    <t xml:space="preserve">135.701812744141</t>
+    <t xml:space="preserve">135.70182800293</t>
   </si>
   <si>
     <t xml:space="preserve">134.44172668457</t>
   </si>
   <si>
-    <t xml:space="preserve">133.375503540039</t>
+    <t xml:space="preserve">133.375518798828</t>
   </si>
   <si>
     <t xml:space="preserve">135.798751831055</t>
   </si>
   <si>
-    <t xml:space="preserve">135.314117431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.574203491211</t>
+    <t xml:space="preserve">135.314102172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.574172973633</t>
   </si>
   <si>
     <t xml:space="preserve">132.212341308594</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">135.023315429688</t>
   </si>
   <si>
-    <t xml:space="preserve">133.763214111328</t>
+    <t xml:space="preserve">133.763229370117</t>
   </si>
   <si>
     <t xml:space="preserve">137.446578979492</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">134.344818115234</t>
   </si>
   <si>
-    <t xml:space="preserve">138.221984863281</t>
+    <t xml:space="preserve">138.22200012207</t>
   </si>
   <si>
     <t xml:space="preserve">142.293060302734</t>
@@ -3098,7 +3098,7 @@
     <t xml:space="preserve">141.032958984375</t>
   </si>
   <si>
-    <t xml:space="preserve">143.359283447266</t>
+    <t xml:space="preserve">143.359268188477</t>
   </si>
   <si>
     <t xml:space="preserve">140.063674926758</t>
@@ -3110,7 +3110,7 @@
     <t xml:space="preserve">140.548309326172</t>
   </si>
   <si>
-    <t xml:space="preserve">140.160614013672</t>
+    <t xml:space="preserve">140.160598754883</t>
   </si>
   <si>
     <t xml:space="preserve">139.579010009766</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">136.671127319336</t>
   </si>
   <si>
-    <t xml:space="preserve">138.609710693359</t>
+    <t xml:space="preserve">138.609725952148</t>
   </si>
   <si>
     <t xml:space="preserve">135.992614746094</t>
@@ -3128,7 +3128,7 @@
     <t xml:space="preserve">137.640426635742</t>
   </si>
   <si>
-    <t xml:space="preserve">139.094375610352</t>
+    <t xml:space="preserve">139.094360351562</t>
   </si>
   <si>
     <t xml:space="preserve">141.226837158203</t>
@@ -3146,28 +3146,28 @@
     <t xml:space="preserve">142.486923217773</t>
   </si>
   <si>
-    <t xml:space="preserve">146.073333740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.884307861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.011917114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.175064086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.756637573242</t>
+    <t xml:space="preserve">146.073318481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.884292602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.011901855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.175079345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.75666809082</t>
   </si>
   <si>
     <t xml:space="preserve">146.364105224609</t>
   </si>
   <si>
-    <t xml:space="preserve">147.236465454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.205780029297</t>
+    <t xml:space="preserve">147.236480712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.205764770508</t>
   </si>
   <si>
     <t xml:space="preserve">147.818054199219</t>
@@ -3176,70 +3176,70 @@
     <t xml:space="preserve">150.532104492188</t>
   </si>
   <si>
-    <t xml:space="preserve">150.629013061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.087799072266</t>
+    <t xml:space="preserve">150.629028320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.087783813477</t>
   </si>
   <si>
     <t xml:space="preserve">154.893951416016</t>
   </si>
   <si>
-    <t xml:space="preserve">152.955352783203</t>
+    <t xml:space="preserve">152.955337524414</t>
   </si>
   <si>
     <t xml:space="preserve">157.89875793457</t>
   </si>
   <si>
-    <t xml:space="preserve">161.67903137207</t>
+    <t xml:space="preserve">161.679016113281</t>
   </si>
   <si>
     <t xml:space="preserve">166.816329956055</t>
   </si>
   <si>
-    <t xml:space="preserve">166.428604125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.847015380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.459289550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.65315246582</t>
+    <t xml:space="preserve">166.428588867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.847030639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.45930480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.653137207031</t>
   </si>
   <si>
     <t xml:space="preserve">167.397888183594</t>
   </si>
   <si>
-    <t xml:space="preserve">168.851852416992</t>
+    <t xml:space="preserve">168.851837158203</t>
   </si>
   <si>
     <t xml:space="preserve">169.142623901367</t>
   </si>
   <si>
-    <t xml:space="preserve">169.627288818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.305786132812</t>
+    <t xml:space="preserve">169.62727355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.305801391602</t>
   </si>
   <si>
     <t xml:space="preserve">169.239562988281</t>
   </si>
   <si>
-    <t xml:space="preserve">169.724227905273</t>
+    <t xml:space="preserve">169.724212646484</t>
   </si>
   <si>
     <t xml:space="preserve">168.948776245117</t>
   </si>
   <si>
-    <t xml:space="preserve">163.811477661133</t>
+    <t xml:space="preserve">163.811492919922</t>
   </si>
   <si>
     <t xml:space="preserve">167.204025268555</t>
   </si>
   <si>
-    <t xml:space="preserve">165.071594238281</t>
+    <t xml:space="preserve">165.071578979492</t>
   </si>
   <si>
     <t xml:space="preserve">167.979476928711</t>
@@ -3248,16 +3248,16 @@
     <t xml:space="preserve">173.989120483398</t>
   </si>
   <si>
-    <t xml:space="preserve">176.606231689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.372024536133</t>
+    <t xml:space="preserve">176.606216430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.372009277344</t>
   </si>
   <si>
     <t xml:space="preserve">152.470687866211</t>
   </si>
   <si>
-    <t xml:space="preserve">152.567611694336</t>
+    <t xml:space="preserve">152.567596435547</t>
   </si>
   <si>
     <t xml:space="preserve">154.506210327148</t>
@@ -3266,13 +3266,13 @@
     <t xml:space="preserve">153.827697753906</t>
   </si>
   <si>
-    <t xml:space="preserve">149.465866088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">153.633865356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.43034362793</t>
+    <t xml:space="preserve">149.465850830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">153.633850097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.430358886719</t>
   </si>
   <si>
     <t xml:space="preserve">147.721115112305</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">157.026382446289</t>
   </si>
   <si>
-    <t xml:space="preserve">159.643508911133</t>
+    <t xml:space="preserve">159.643493652344</t>
   </si>
   <si>
     <t xml:space="preserve">162.842193603516</t>
@@ -3296,7 +3296,7 @@
     <t xml:space="preserve">160.4189453125</t>
   </si>
   <si>
-    <t xml:space="preserve">161.097442626953</t>
+    <t xml:space="preserve">161.097457885742</t>
   </si>
   <si>
     <t xml:space="preserve">160.806655883789</t>
@@ -3308,16 +3308,16 @@
     <t xml:space="preserve">161.582092285156</t>
   </si>
   <si>
-    <t xml:space="preserve">162.551391601562</t>
+    <t xml:space="preserve">162.551376342773</t>
   </si>
   <si>
     <t xml:space="preserve">161.872894287109</t>
   </si>
   <si>
-    <t xml:space="preserve">164.393096923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171.275085449219</t>
+    <t xml:space="preserve">164.393081665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">171.27507019043</t>
   </si>
   <si>
     <t xml:space="preserve">173.213668823242</t>
@@ -3332,7 +3332,7 @@
     <t xml:space="preserve">171.662811279297</t>
   </si>
   <si>
-    <t xml:space="preserve">172.34130859375</t>
+    <t xml:space="preserve">172.341323852539</t>
   </si>
   <si>
     <t xml:space="preserve">176.703155517578</t>
@@ -3341,31 +3341,31 @@
     <t xml:space="preserve">179.804916381836</t>
   </si>
   <si>
-    <t xml:space="preserve">173.892181396484</t>
+    <t xml:space="preserve">173.892196655273</t>
   </si>
   <si>
     <t xml:space="preserve">168.754913330078</t>
   </si>
   <si>
-    <t xml:space="preserve">168.561019897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.010177612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.934280395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.454467773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.837356567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">166.040863037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.882522583008</t>
+    <t xml:space="preserve">168.561050415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.010162353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.934295654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.454483032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.837371826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">166.040878295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.882537841797</t>
   </si>
   <si>
     <t xml:space="preserve">160.709732055664</t>
@@ -3377,13 +3377,13 @@
     <t xml:space="preserve">159.158843994141</t>
   </si>
   <si>
-    <t xml:space="preserve">172.53515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.958419799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.698348999023</t>
+    <t xml:space="preserve">172.535171508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.958435058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.698333740234</t>
   </si>
   <si>
     <t xml:space="preserve">174.570709228516</t>
@@ -3392,7 +3392,7 @@
     <t xml:space="preserve">169.43342590332</t>
   </si>
   <si>
-    <t xml:space="preserve">168.076385498047</t>
+    <t xml:space="preserve">168.076400756836</t>
   </si>
   <si>
     <t xml:space="preserve">163.617630004883</t>
@@ -3404,43 +3404,43 @@
     <t xml:space="preserve">163.714553833008</t>
   </si>
   <si>
-    <t xml:space="preserve">170.596572875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.82112121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.473785400391</t>
+    <t xml:space="preserve">170.596588134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.821151733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.473770141602</t>
   </si>
   <si>
     <t xml:space="preserve">164.005340576172</t>
   </si>
   <si>
-    <t xml:space="preserve">157.317199707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.572463989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.863235473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.669387817383</t>
+    <t xml:space="preserve">157.317184448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.572448730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.863250732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.669372558594</t>
   </si>
   <si>
     <t xml:space="preserve">153.149200439453</t>
   </si>
   <si>
-    <t xml:space="preserve">151.016738891602</t>
+    <t xml:space="preserve">151.016754150391</t>
   </si>
   <si>
     <t xml:space="preserve">157.220260620117</t>
   </si>
   <si>
-    <t xml:space="preserve">151.113677978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.858413696289</t>
+    <t xml:space="preserve">151.113662719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.8583984375</t>
   </si>
   <si>
     <t xml:space="preserve">154.990875244141</t>
@@ -3452,19 +3452,19 @@
     <t xml:space="preserve">143.747009277344</t>
   </si>
   <si>
-    <t xml:space="preserve">143.553161621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.522445678711</t>
+    <t xml:space="preserve">143.553146362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.522430419922</t>
   </si>
   <si>
     <t xml:space="preserve">144.910171508789</t>
   </si>
   <si>
-    <t xml:space="preserve">139.385177612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.089538574219</t>
+    <t xml:space="preserve">139.385162353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.089553833008</t>
   </si>
   <si>
     <t xml:space="preserve">132.600082397461</t>
@@ -3473,28 +3473,28 @@
     <t xml:space="preserve">132.309280395508</t>
   </si>
   <si>
-    <t xml:space="preserve">138.997436523438</t>
+    <t xml:space="preserve">138.997421264648</t>
   </si>
   <si>
     <t xml:space="preserve">137.834289550781</t>
   </si>
   <si>
-    <t xml:space="preserve">137.543472290039</t>
+    <t xml:space="preserve">137.543487548828</t>
   </si>
   <si>
     <t xml:space="preserve">138.125076293945</t>
   </si>
   <si>
-    <t xml:space="preserve">138.512786865234</t>
+    <t xml:space="preserve">138.512771606445</t>
   </si>
   <si>
     <t xml:space="preserve">142.680786132812</t>
   </si>
   <si>
-    <t xml:space="preserve">129.692184448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.039543151855</t>
+    <t xml:space="preserve">129.692169189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.039527893066</t>
   </si>
   <si>
     <t xml:space="preserve">136.9619140625</t>
@@ -3506,13 +3506,13 @@
     <t xml:space="preserve">142.874618530273</t>
   </si>
   <si>
-    <t xml:space="preserve">149.562805175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.986053466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.919830322266</t>
+    <t xml:space="preserve">149.562789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.986038208008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.919815063477</t>
   </si>
   <si>
     <t xml:space="preserve">149.368942260742</t>
@@ -3539,37 +3539,37 @@
     <t xml:space="preserve">145.200958251953</t>
   </si>
   <si>
-    <t xml:space="preserve">141.517623901367</t>
+    <t xml:space="preserve">141.517608642578</t>
   </si>
   <si>
     <t xml:space="preserve">141.323760986328</t>
   </si>
   <si>
-    <t xml:space="preserve">137.058837890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.538681030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.477249145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">131.824615478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.186462402344</t>
+    <t xml:space="preserve">137.058822631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.538650512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.477264404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">131.824630737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.186477661133</t>
   </si>
   <si>
     <t xml:space="preserve">135.217178344727</t>
   </si>
   <si>
-    <t xml:space="preserve">130.952270507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.753578186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.162353515625</t>
+    <t xml:space="preserve">130.952255249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.75358581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.16234588623</t>
   </si>
   <si>
     <t xml:space="preserve">113.601806640625</t>
@@ -3578,7 +3578,7 @@
     <t xml:space="preserve">117.285148620605</t>
   </si>
   <si>
-    <t xml:space="preserve">114.958831787109</t>
+    <t xml:space="preserve">114.958824157715</t>
   </si>
   <si>
     <t xml:space="preserve">117.57593536377</t>
@@ -3587,13 +3587,13 @@
     <t xml:space="preserve">116.121994018555</t>
   </si>
   <si>
-    <t xml:space="preserve">119.708389282227</t>
+    <t xml:space="preserve">119.708396911621</t>
   </si>
   <si>
     <t xml:space="preserve">115.152694702148</t>
   </si>
   <si>
-    <t xml:space="preserve">114.86190032959</t>
+    <t xml:space="preserve">114.861907958984</t>
   </si>
   <si>
     <t xml:space="preserve">115.443481445312</t>
@@ -5481,6 +5481,9 @@
   </si>
   <si>
     <t xml:space="preserve">118.800003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.199996948242</t>
   </si>
 </sst>
 </file>
@@ -70871,7 +70874,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6910416667</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>55654</v>
@@ -70892,6 +70895,32 @@
         <v>1822</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6918402778</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>43071</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>119.199996948242</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>116.699996948242</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>118</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>119.199996948242</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>1823</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/REY.MI.xlsx
+++ b/data/REY.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2559700012207</t>
+    <t xml:space="preserve">29.2559719085693</t>
   </si>
   <si>
     <t xml:space="preserve">REY.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8380298614502</t>
+    <t xml:space="preserve">28.8380260467529</t>
   </si>
   <si>
     <t xml:space="preserve">28.3272094726562</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6306419372559</t>
+    <t xml:space="preserve">27.6306400299072</t>
   </si>
   <si>
     <t xml:space="preserve">27.8396110534668</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2111148834229</t>
+    <t xml:space="preserve">28.2111167907715</t>
   </si>
   <si>
     <t xml:space="preserve">29.0005645751953</t>
@@ -65,16 +65,16 @@
     <t xml:space="preserve">28.5594024658203</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1414546966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1198196411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9789237976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8644123077393</t>
+    <t xml:space="preserve">28.1414585113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1198253631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9789257049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8644104003906</t>
   </si>
   <si>
     <t xml:space="preserve">27.4448871612549</t>
@@ -86,40 +86,40 @@
     <t xml:space="preserve">27.8163909912109</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2807712554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6770782470703</t>
+    <t xml:space="preserve">28.2807731628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6770763397217</t>
   </si>
   <si>
     <t xml:space="preserve">28.0950183868408</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8628311157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2591361999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7018795013428</t>
+    <t xml:space="preserve">27.862829208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2591342926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7018814086914</t>
   </si>
   <si>
     <t xml:space="preserve">26.1678409576416</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2855186462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3799781799316</t>
+    <t xml:space="preserve">25.2855167388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.379976272583</t>
   </si>
   <si>
     <t xml:space="preserve">24.6121654510498</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0053081512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5177097320557</t>
+    <t xml:space="preserve">26.0053119659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.517707824707</t>
   </si>
   <si>
     <t xml:space="preserve">25.6570224761963</t>
@@ -131,25 +131,25 @@
     <t xml:space="preserve">26.3071556091309</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0733814239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2142791748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4696884155273</t>
+    <t xml:space="preserve">27.0733852386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2142810821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4696865081787</t>
   </si>
   <si>
     <t xml:space="preserve">26.0517444610596</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7034587860107</t>
+    <t xml:space="preserve">25.7034606933594</t>
   </si>
   <si>
     <t xml:space="preserve">25.7266807556152</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7483158111572</t>
+    <t xml:space="preserve">26.7483177185059</t>
   </si>
   <si>
     <t xml:space="preserve">26.4929065704346</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">27.3520107269287</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1894760131836</t>
+    <t xml:space="preserve">27.1894779205322</t>
   </si>
   <si>
     <t xml:space="preserve">27.2359180450439</t>
@@ -167,151 +167,151 @@
     <t xml:space="preserve">27.1662578582764</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9092693328857</t>
+    <t xml:space="preserve">27.9092674255371</t>
   </si>
   <si>
     <t xml:space="preserve">29.0237808227539</t>
   </si>
   <si>
-    <t xml:space="preserve">31.5546493530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3008289337158</t>
+    <t xml:space="preserve">31.5546550750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3008251190186</t>
   </si>
   <si>
     <t xml:space="preserve">30.4169235229492</t>
   </si>
   <si>
-    <t xml:space="preserve">29.9989814758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9757595062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7900104522705</t>
+    <t xml:space="preserve">29.9989776611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9757652282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7900123596191</t>
   </si>
   <si>
     <t xml:space="preserve">29.952543258667</t>
   </si>
   <si>
-    <t xml:space="preserve">30.2311706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7203540802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.068639755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8596687316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5578193664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3256301879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4881629943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5113773345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2095317840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1615123748779</t>
+    <t xml:space="preserve">30.2311687469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7203502655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0686340332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8596649169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5578174591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3256282806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4881591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.511381149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2095336914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1615142822266</t>
   </si>
   <si>
     <t xml:space="preserve">29.3720664978027</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5346012115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4433040618896</t>
+    <t xml:space="preserve">29.5345993041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4433059692383</t>
   </si>
   <si>
     <t xml:space="preserve">28.6754951477051</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8612480163574</t>
+    <t xml:space="preserve">28.8612461090088</t>
   </si>
   <si>
     <t xml:space="preserve">28.8148059844971</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9076843261719</t>
+    <t xml:space="preserve">28.9076881408691</t>
   </si>
   <si>
     <t xml:space="preserve">28.629056930542</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4200859069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6776027679443</t>
+    <t xml:space="preserve">28.4200839996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6776008605957</t>
   </si>
   <si>
     <t xml:space="preserve">28.5605487823486</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0287551879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3264446258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5137271881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7946510314941</t>
+    <t xml:space="preserve">29.0287570953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3264465332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5137310028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7946529388428</t>
   </si>
   <si>
     <t xml:space="preserve">29.0053443908691</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2628555297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1992702484131</t>
+    <t xml:space="preserve">29.2628574371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1992683410645</t>
   </si>
   <si>
     <t xml:space="preserve">30.5036010742188</t>
   </si>
   <si>
-    <t xml:space="preserve">30.550422668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.901575088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6674747467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.714298248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4567813873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4333724975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2695026397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8949337005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1859836578369</t>
+    <t xml:space="preserve">30.5504207611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9015769958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6674766540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7142925262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4567852020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.43337059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2694988250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8949356079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1859798431396</t>
   </si>
   <si>
     <t xml:space="preserve">29.3096771240234</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4969596862793</t>
+    <t xml:space="preserve">29.4969615936279</t>
   </si>
   <si>
     <t xml:space="preserve">27.6943683624268</t>
@@ -323,28 +323,28 @@
     <t xml:space="preserve">26.8047771453857</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3198051452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9218273162842</t>
+    <t xml:space="preserve">27.3198013305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9218292236328</t>
   </si>
   <si>
     <t xml:space="preserve">27.5070858001709</t>
   </si>
   <si>
-    <t xml:space="preserve">26.945240020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8215446472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2195224761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.10910987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6241359710693</t>
+    <t xml:space="preserve">26.9452381134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8215427398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2195205688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1091136932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.624137878418</t>
   </si>
   <si>
     <t xml:space="preserve">27.3666248321533</t>
@@ -353,16 +353,16 @@
     <t xml:space="preserve">28.303035736084</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8882904052734</t>
+    <t xml:space="preserve">28.8882923126221</t>
   </si>
   <si>
     <t xml:space="preserve">28.7478313446045</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4434986114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.98193359375</t>
+    <t xml:space="preserve">28.4434967041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9819355010986</t>
   </si>
   <si>
     <t xml:space="preserve">28.9117031097412</t>
@@ -371,49 +371,49 @@
     <t xml:space="preserve">29.3799095153809</t>
   </si>
   <si>
-    <t xml:space="preserve">29.450138092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8481159210205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1524486541748</t>
+    <t xml:space="preserve">29.4501419067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8481140136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1524448394775</t>
   </si>
   <si>
     <t xml:space="preserve">29.9651660919189</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7244186401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1458072662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0989875793457</t>
+    <t xml:space="preserve">28.7244205474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1458053588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0989856719971</t>
   </si>
   <si>
     <t xml:space="preserve">28.9351139068604</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4903144836426</t>
+    <t xml:space="preserve">28.4903163909912</t>
   </si>
   <si>
     <t xml:space="preserve">27.9752922058105</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3732624053955</t>
+    <t xml:space="preserve">28.3732643127441</t>
   </si>
   <si>
     <t xml:space="preserve">28.092342376709</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2729816436768</t>
+    <t xml:space="preserve">27.2729835510254</t>
   </si>
   <si>
     <t xml:space="preserve">27.0622882843018</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0388813018799</t>
+    <t xml:space="preserve">27.0388793945312</t>
   </si>
   <si>
     <t xml:space="preserve">26.8984184265137</t>
@@ -422,16 +422,16 @@
     <t xml:space="preserve">26.1492881774902</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7981338500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.891773223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7579612731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9518814086914</t>
+    <t xml:space="preserve">25.798131942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8917751312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7579555511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9518795013428</t>
   </si>
   <si>
     <t xml:space="preserve">27.881649017334</t>
@@ -443,64 +443,64 @@
     <t xml:space="preserve">27.9050598144531</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2963943481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8582420349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.577320098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7177772521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.741189956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0455226898193</t>
+    <t xml:space="preserve">27.2963905334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8582401275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5773181915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7177734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7411918640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.045524597168</t>
   </si>
   <si>
     <t xml:space="preserve">27.7880077362061</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3900318145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1223945617676</t>
+    <t xml:space="preserve">27.3900337219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1223926544189</t>
   </si>
   <si>
     <t xml:space="preserve">28.6541881561279</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2093944549561</t>
+    <t xml:space="preserve">28.2093963623047</t>
   </si>
   <si>
     <t xml:space="preserve">27.413444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0857009887695</t>
+    <t xml:space="preserve">27.0856990814209</t>
   </si>
   <si>
     <t xml:space="preserve">26.8515949249268</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4368553161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6877250671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2261638641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8281898498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6409072875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4536190032959</t>
+    <t xml:space="preserve">27.4368534088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6877269744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2261619567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8281860351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6409091949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4536228179932</t>
   </si>
   <si>
     <t xml:space="preserve">26.5706748962402</t>
@@ -521,58 +521,58 @@
     <t xml:space="preserve">24.7446708679199</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7680816650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8851318359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2530536651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0490055084229</t>
+    <t xml:space="preserve">24.7680778503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8851337432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2530574798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0490036010742</t>
   </si>
   <si>
     <t xml:space="preserve">25.4703903198242</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5172119140625</t>
+    <t xml:space="preserve">25.5172100067139</t>
   </si>
   <si>
     <t xml:space="preserve">25.2831077575684</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1660556793213</t>
+    <t xml:space="preserve">25.1660575866699</t>
   </si>
   <si>
     <t xml:space="preserve">25.4469814300537</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0958271026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9319515228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0724143981934</t>
+    <t xml:space="preserve">25.0958251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9319534301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0724182128906</t>
   </si>
   <si>
     <t xml:space="preserve">25.6342601776123</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1961135864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.172700881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8348293304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9284744262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4602661132812</t>
+    <t xml:space="preserve">26.1961097717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1727027893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.834831237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9284706115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4602642059326</t>
   </si>
   <si>
     <t xml:space="preserve">27.9987010955811</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">28.6307792663574</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2160377502441</t>
+    <t xml:space="preserve">29.2160358428955</t>
   </si>
   <si>
     <t xml:space="preserve">29.3330860137939</t>
@@ -590,76 +590,76 @@
     <t xml:space="preserve">28.8648815155029</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3498573303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.607364654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4735469818115</t>
+    <t xml:space="preserve">28.349853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6073684692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4735488891602</t>
   </si>
   <si>
     <t xml:space="preserve">29.2394485473633</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7076511383057</t>
+    <t xml:space="preserve">29.7076530456543</t>
   </si>
   <si>
     <t xml:space="preserve">29.4267292022705</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8313503265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9952163696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4868392944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2527294158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3697814941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1356773376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1891441345215</t>
+    <t xml:space="preserve">30.8313484191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9952125549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4868297576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2527275085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3697853088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1356830596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.189136505127</t>
   </si>
   <si>
     <t xml:space="preserve">32.3061943054199</t>
   </si>
   <si>
-    <t xml:space="preserve">33.2660179138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0619621276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6472244262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4599380493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7408599853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6706390380859</t>
+    <t xml:space="preserve">33.2660217285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0619659423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.647216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4599418640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7408676147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.6706352233887</t>
   </si>
   <si>
     <t xml:space="preserve">34.9983787536621</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8579139709473</t>
+    <t xml:space="preserve">34.85791015625</t>
   </si>
   <si>
     <t xml:space="preserve">34.1790161132812</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7642784118652</t>
+    <t xml:space="preserve">34.764274597168</t>
   </si>
   <si>
     <t xml:space="preserve">34.8813285827637</t>
@@ -674,10 +674,10 @@
     <t xml:space="preserve">35.6070442199707</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4665832519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.7943344116211</t>
+    <t xml:space="preserve">35.4665794372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.7943229675293</t>
   </si>
   <si>
     <t xml:space="preserve">36.8243751525879</t>
@@ -686,82 +686,82 @@
     <t xml:space="preserve">37.6671485900879</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8778457641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9882507324219</t>
+    <t xml:space="preserve">37.8778419494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9882469177246</t>
   </si>
   <si>
     <t xml:space="preserve">37.5735092163086</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6203231811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6085357666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.7264289855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9150733947754</t>
+    <t xml:space="preserve">37.6203308105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6085395812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.7264366149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9150695800781</t>
   </si>
   <si>
     <t xml:space="preserve">38.1980171203613</t>
   </si>
   <si>
-    <t xml:space="preserve">37.9386444091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1508636474609</t>
+    <t xml:space="preserve">37.9386405944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1508598327637</t>
   </si>
   <si>
     <t xml:space="preserve">37.4906463623047</t>
   </si>
   <si>
-    <t xml:space="preserve">39.0232810974121</t>
+    <t xml:space="preserve">39.0232849121094</t>
   </si>
   <si>
     <t xml:space="preserve">40.0843353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0607528686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8013916015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2397079467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0274925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4519271850586</t>
+    <t xml:space="preserve">40.0607604980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8013877868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2397041320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0274963378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4519233703613</t>
   </si>
   <si>
     <t xml:space="preserve">41.7112808227539</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4990768432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8055992126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3243446350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1828689575195</t>
+    <t xml:space="preserve">41.4990730285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.805606842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.324348449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1828651428223</t>
   </si>
   <si>
     <t xml:space="preserve">42.0885581970215</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2771873474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8291778564453</t>
+    <t xml:space="preserve">42.2771911621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8291816711426</t>
   </si>
   <si>
     <t xml:space="preserve">39.9664459228516</t>
@@ -773,28 +773,28 @@
     <t xml:space="preserve">38.4338073730469</t>
   </si>
   <si>
-    <t xml:space="preserve">38.999698638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.6363410949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.9428558349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4380264282227</t>
+    <t xml:space="preserve">38.9996948242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.6363372802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.9428596496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4380226135254</t>
   </si>
   <si>
     <t xml:space="preserve">38.5517044067383</t>
   </si>
   <si>
-    <t xml:space="preserve">38.0565376281738</t>
+    <t xml:space="preserve">38.0565414428711</t>
   </si>
   <si>
     <t xml:space="preserve">39.1411743164062</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3298110961914</t>
+    <t xml:space="preserve">39.3298149108887</t>
   </si>
   <si>
     <t xml:space="preserve">39.0704383850098</t>
@@ -806,10 +806,10 @@
     <t xml:space="preserve">38.6695976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8346519470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.905387878418</t>
+    <t xml:space="preserve">38.834644317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9053840637207</t>
   </si>
   <si>
     <t xml:space="preserve">39.0940208435059</t>
@@ -818,10 +818,10 @@
     <t xml:space="preserve">38.8110733032227</t>
   </si>
   <si>
-    <t xml:space="preserve">38.2687492370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.7403335571289</t>
+    <t xml:space="preserve">38.2687530517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.7403373718262</t>
   </si>
   <si>
     <t xml:space="preserve">38.6931762695312</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">39.2354927062988</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2590637207031</t>
+    <t xml:space="preserve">39.2590675354004</t>
   </si>
   <si>
     <t xml:space="preserve">42.1357154846191</t>
@@ -845,25 +845,25 @@
     <t xml:space="preserve">44.8001403808594</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5075073242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3188858032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8140411376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6822471618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7862396240234</t>
+    <t xml:space="preserve">45.507511138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3188819885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8140449523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6822509765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7862434387207</t>
   </si>
   <si>
     <t xml:space="preserve">44.7529830932617</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1302452087402</t>
+    <t xml:space="preserve">45.1302490234375</t>
   </si>
   <si>
     <t xml:space="preserve">44.446460723877</t>
@@ -872,13 +872,13 @@
     <t xml:space="preserve">44.5879364013672</t>
   </si>
   <si>
-    <t xml:space="preserve">44.3285636901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.3049812316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6211891174316</t>
+    <t xml:space="preserve">44.3285598754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3049774169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6211853027344</t>
   </si>
   <si>
     <t xml:space="preserve">43.1731910705566</t>
@@ -887,16 +887,16 @@
     <t xml:space="preserve">43.0788688659668</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5837097167969</t>
+    <t xml:space="preserve">42.5837135314941</t>
   </si>
   <si>
     <t xml:space="preserve">43.267505645752</t>
   </si>
   <si>
-    <t xml:space="preserve">45.3660430908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9887733459473</t>
+    <t xml:space="preserve">45.3660354614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.98876953125</t>
   </si>
   <si>
     <t xml:space="preserve">44.4936141967773</t>
@@ -908,46 +908,46 @@
     <t xml:space="preserve">45.6254043579102</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8611946105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4035186767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.582462310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.0637283325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1344680786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1580429077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9125747680664</t>
+    <t xml:space="preserve">45.8611907958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4035148620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.5824699401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.0637245178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.134464263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1580390930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9125709533691</t>
   </si>
   <si>
     <t xml:space="preserve">49.3508911132812</t>
   </si>
   <si>
-    <t xml:space="preserve">48.7378425598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.101203918457</t>
+    <t xml:space="preserve">48.7378349304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1012001037598</t>
   </si>
   <si>
     <t xml:space="preserve">48.8321533203125</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6296272277832</t>
+    <t xml:space="preserve">47.6296234130859</t>
   </si>
   <si>
     <t xml:space="preserve">48.0540466308594</t>
   </si>
   <si>
-    <t xml:space="preserve">47.8654174804688</t>
+    <t xml:space="preserve">47.8654136657715</t>
   </si>
   <si>
     <t xml:space="preserve">47.9597282409668</t>
@@ -959,25 +959,25 @@
     <t xml:space="preserve">45.2717247009277</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0359306335449</t>
+    <t xml:space="preserve">45.0359344482422</t>
   </si>
   <si>
     <t xml:space="preserve">44.5643501281738</t>
   </si>
   <si>
-    <t xml:space="preserve">43.9748725891113</t>
+    <t xml:space="preserve">43.9748764038086</t>
   </si>
   <si>
     <t xml:space="preserve">42.5601348876953</t>
   </si>
   <si>
-    <t xml:space="preserve">42.9138221740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7251853942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2064476013184</t>
+    <t xml:space="preserve">42.913818359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7251892089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2064514160156</t>
   </si>
   <si>
     <t xml:space="preserve">42.4328079223633</t>
@@ -989,31 +989,31 @@
     <t xml:space="preserve">43.3476715087891</t>
   </si>
   <si>
-    <t xml:space="preserve">41.9800834655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3010139465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0838394165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7534828186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5931396484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4799652099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0081405639648</t>
+    <t xml:space="preserve">41.9800872802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.3010101318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0838432312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.753490447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5931434631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4799690246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0081329345703</t>
   </si>
   <si>
     <t xml:space="preserve">43.0458641052246</t>
   </si>
   <si>
-    <t xml:space="preserve">43.3288116455078</t>
+    <t xml:space="preserve">43.3288078308105</t>
   </si>
   <si>
     <t xml:space="preserve">41.3953285217285</t>
@@ -1022,31 +1022,31 @@
     <t xml:space="preserve">43.4891510009766</t>
   </si>
   <si>
-    <t xml:space="preserve">44.234245300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1210632324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2439231872559</t>
+    <t xml:space="preserve">44.2342414855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1210670471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.2439270019531</t>
   </si>
   <si>
     <t xml:space="preserve">42.1027030944824</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1689758300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2729682922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4045143127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7626686096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2531089782715</t>
+    <t xml:space="preserve">41.1689720153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2729721069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4045066833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7626609802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2531127929688</t>
   </si>
   <si>
     <t xml:space="preserve">45.0547943115234</t>
@@ -1058,37 +1058,37 @@
     <t xml:space="preserve">46.2809028625488</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1488609313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3094520568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.9982070922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5358047485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1679763793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.592399597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6586647033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.2533569335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6683502197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2248077392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0830955505371</t>
+    <t xml:space="preserve">46.1488647460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3094482421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.9982032775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5358085632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.16796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5923957824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6586608886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.253360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.668342590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2248039245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0830917358398</t>
   </si>
   <si>
     <t xml:space="preserve">45.2057037353516</t>
@@ -1097,28 +1097,28 @@
     <t xml:space="preserve">46.3280563354492</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0356864929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6584167480469</t>
+    <t xml:space="preserve">46.0356826782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6584129333496</t>
   </si>
   <si>
     <t xml:space="preserve">45.5169410705566</t>
   </si>
   <si>
-    <t xml:space="preserve">44.1682281494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8664131164551</t>
+    <t xml:space="preserve">44.1682243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8664054870605</t>
   </si>
   <si>
     <t xml:space="preserve">43.5457344055176</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8852729797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4606018066406</t>
+    <t xml:space="preserve">43.8852767944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4606056213379</t>
   </si>
   <si>
     <t xml:space="preserve">45.6112594604492</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">45.6301231384277</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7244338989258</t>
+    <t xml:space="preserve">45.7244300842285</t>
   </si>
   <si>
     <t xml:space="preserve">46.290340423584</t>
@@ -1139,19 +1139,19 @@
     <t xml:space="preserve">46.2148818969727</t>
   </si>
   <si>
-    <t xml:space="preserve">46.648738861084</t>
+    <t xml:space="preserve">46.6487350463867</t>
   </si>
   <si>
     <t xml:space="preserve">46.7053260803223</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5921478271484</t>
+    <t xml:space="preserve">46.5921440124512</t>
   </si>
   <si>
     <t xml:space="preserve">46.8939590454102</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7711029052734</t>
+    <t xml:space="preserve">47.7710990905762</t>
   </si>
   <si>
     <t xml:space="preserve">47.8182601928711</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">48.1955184936523</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9972038269043</t>
+    <t xml:space="preserve">48.9972114562988</t>
   </si>
   <si>
     <t xml:space="preserve">48.5727844238281</t>
@@ -1169,28 +1169,28 @@
     <t xml:space="preserve">49.3273124694824</t>
   </si>
   <si>
-    <t xml:space="preserve">50.3176307678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4119491577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8460502624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3744659423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2233085632324</t>
+    <t xml:space="preserve">50.317626953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4119529724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8460540771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3744697570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.223316192627</t>
   </si>
   <si>
     <t xml:space="preserve">50.0818405151367</t>
   </si>
   <si>
-    <t xml:space="preserve">47.5353164672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1960220336914</t>
+    <t xml:space="preserve">47.5353088378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1960144042969</t>
   </si>
   <si>
     <t xml:space="preserve">47.2052001953125</t>
@@ -1202,22 +1202,22 @@
     <t xml:space="preserve">47.2523612976074</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4223785400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8376197814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6489906311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8753433227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5732841491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.4687843322754</t>
+    <t xml:space="preserve">46.4223747253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8376159667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6489868164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8753471374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5732879638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.4687881469727</t>
   </si>
   <si>
     <t xml:space="preserve">48.8085784912109</t>
@@ -1232,31 +1232,31 @@
     <t xml:space="preserve">46.5166969299316</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1774101257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7812728881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8378639221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4983291625977</t>
+    <t xml:space="preserve">45.1774063110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7812690734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8378677368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4983253479004</t>
   </si>
   <si>
     <t xml:space="preserve">44.1776542663574</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8952102661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.291332244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4988250732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0652275085449</t>
+    <t xml:space="preserve">41.895206451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2913360595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4988288879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0652236938477</t>
   </si>
   <si>
     <t xml:space="preserve">41.9517936706543</t>
@@ -1268,22 +1268,22 @@
     <t xml:space="preserve">45.4414901733398</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4603538513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4037628173828</t>
+    <t xml:space="preserve">45.4603500366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4037666320801</t>
   </si>
   <si>
     <t xml:space="preserve">46.1017036437988</t>
   </si>
   <si>
-    <t xml:space="preserve">45.9885215759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3846473693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.0443687438965</t>
+    <t xml:space="preserve">45.9885177612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.384651184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.0443649291992</t>
   </si>
   <si>
     <t xml:space="preserve">48.902889251709</t>
@@ -1292,16 +1292,16 @@
     <t xml:space="preserve">48.2898368835449</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1193237304688</t>
+    <t xml:space="preserve">51.1193199157715</t>
   </si>
   <si>
     <t xml:space="preserve">50.694896697998</t>
   </si>
   <si>
-    <t xml:space="preserve">50.6005821228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9328575134277</t>
+    <t xml:space="preserve">50.6005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.932861328125</t>
   </si>
   <si>
     <t xml:space="preserve">50.4107093811035</t>
@@ -1310,16 +1310,16 @@
     <t xml:space="preserve">51.0277900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">52.2144813537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1195449829102</t>
+    <t xml:space="preserve">52.2144889831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1195526123047</t>
   </si>
   <si>
     <t xml:space="preserve">51.7398109436035</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8411026000977</t>
+    <t xml:space="preserve">49.8410987854004</t>
   </si>
   <si>
     <t xml:space="preserve">51.5024719238281</t>
@@ -1328,13 +1328,13 @@
     <t xml:space="preserve">49.2714881896973</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3664245605469</t>
+    <t xml:space="preserve">49.3664207458496</t>
   </si>
   <si>
     <t xml:space="preserve">49.081615447998</t>
   </si>
   <si>
-    <t xml:space="preserve">49.793628692627</t>
+    <t xml:space="preserve">49.7936325073242</t>
   </si>
   <si>
     <t xml:space="preserve">48.2746620178223</t>
@@ -1343,46 +1343,46 @@
     <t xml:space="preserve">46.8221549987793</t>
   </si>
   <si>
-    <t xml:space="preserve">48.0847969055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6544036865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3189506530762</t>
+    <t xml:space="preserve">48.0847930908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6544075012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3189582824707</t>
   </si>
   <si>
     <t xml:space="preserve">49.6512260437012</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9834976196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3632431030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.217658996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.1733703613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.455005645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.0246124267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0689010620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.7840919494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4422874450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.6827964782715</t>
+    <t xml:space="preserve">49.9835014343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3632469177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2176628112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1733741760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.4550018310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.0246086120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.068904876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.7840995788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4422912597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.682804107666</t>
   </si>
   <si>
     <t xml:space="preserve">55.1100158691406</t>
@@ -1391,10 +1391,10 @@
     <t xml:space="preserve">55.5846900939941</t>
   </si>
   <si>
-    <t xml:space="preserve">56.3916435241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.7302742004395</t>
+    <t xml:space="preserve">56.3916511535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.7302703857422</t>
   </si>
   <si>
     <t xml:space="preserve">55.0625495910645</t>
@@ -1409,10 +1409,10 @@
     <t xml:space="preserve">53.1638412475586</t>
   </si>
   <si>
-    <t xml:space="preserve">53.6385078430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0182647705078</t>
+    <t xml:space="preserve">53.6385154724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0182609558105</t>
   </si>
   <si>
     <t xml:space="preserve">54.3030624389648</t>
@@ -1424,13 +1424,13 @@
     <t xml:space="preserve">53.8283882141113</t>
   </si>
   <si>
-    <t xml:space="preserve">54.7777442932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4391136169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9137878417969</t>
+    <t xml:space="preserve">54.7777404785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4391098022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9137840270996</t>
   </si>
   <si>
     <t xml:space="preserve">56.2967071533203</t>
@@ -1445,16 +1445,16 @@
     <t xml:space="preserve">56.5340461730957</t>
   </si>
   <si>
-    <t xml:space="preserve">56.6764488220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9676094055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5942306518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0214309692383</t>
+    <t xml:space="preserve">56.6764526367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9676132202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5942268371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0214347839355</t>
   </si>
   <si>
     <t xml:space="preserve">55.1574821472168</t>
@@ -1463,10 +1463,10 @@
     <t xml:space="preserve">54.3505325317383</t>
   </si>
   <si>
-    <t xml:space="preserve">52.9265022277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.8790321350098</t>
+    <t xml:space="preserve">52.9264984130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.8790283203125</t>
   </si>
   <si>
     <t xml:space="preserve">54.065731048584</t>
@@ -1484,22 +1484,22 @@
     <t xml:space="preserve">53.3062438964844</t>
   </si>
   <si>
-    <t xml:space="preserve">52.4043579101562</t>
+    <t xml:space="preserve">52.4043502807617</t>
   </si>
   <si>
     <t xml:space="preserve">51.0752563476562</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4581756591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.2619552612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.882209777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1606597900391</t>
+    <t xml:space="preserve">50.4581832885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.2619476318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8822174072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1606636047363</t>
   </si>
   <si>
     <t xml:space="preserve">54.2081260681152</t>
@@ -1511,28 +1511,28 @@
     <t xml:space="preserve">54.5404014587402</t>
   </si>
   <si>
-    <t xml:space="preserve">55.2049522399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2492408752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.1036605834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.2460556030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.9106063842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.961254119873</t>
+    <t xml:space="preserve">55.2049446105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2492370605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1036567687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.2460594177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.9106140136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9612579345703</t>
   </si>
   <si>
     <t xml:space="preserve">50.790454864502</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4138832092285</t>
+    <t xml:space="preserve">49.413890838623</t>
   </si>
   <si>
     <t xml:space="preserve">47.0120239257812</t>
@@ -1541,70 +1541,70 @@
     <t xml:space="preserve">47.0499992370605</t>
   </si>
   <si>
-    <t xml:space="preserve">48.2271995544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4677124023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0309715270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3157768249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3474731445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7525596618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6766090393066</t>
+    <t xml:space="preserve">48.2271957397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4677085876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0309677124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3157730102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3474769592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7525634765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6766166687012</t>
   </si>
   <si>
     <t xml:space="preserve">44.6956024169922</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1955757141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5563316345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4803810119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9487495422363</t>
+    <t xml:space="preserve">46.1955795288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.556339263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4803848266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9487457275391</t>
   </si>
   <si>
     <t xml:space="preserve">47.4107513427734</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5373420715332</t>
+    <t xml:space="preserve">46.5373458862305</t>
   </si>
   <si>
     <t xml:space="preserve">46.5183563232422</t>
   </si>
   <si>
-    <t xml:space="preserve">46.7462005615234</t>
+    <t xml:space="preserve">46.7462043762207</t>
   </si>
   <si>
     <t xml:space="preserve">46.4424057006836</t>
   </si>
   <si>
-    <t xml:space="preserve">45.493049621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1322975158691</t>
+    <t xml:space="preserve">45.4930534362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1323013305664</t>
   </si>
   <si>
     <t xml:space="preserve">45.5690078735352</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7019119262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3601875305176</t>
+    <t xml:space="preserve">45.7019157409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3601913452148</t>
   </si>
   <si>
     <t xml:space="preserve">41.4677963256836</t>
@@ -1613,16 +1613,16 @@
     <t xml:space="preserve">41.9234848022461</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8728332519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7462463378906</t>
+    <t xml:space="preserve">42.8728370666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7462425231934</t>
   </si>
   <si>
     <t xml:space="preserve">44.2968673706055</t>
   </si>
   <si>
-    <t xml:space="preserve">43.860164642334</t>
+    <t xml:space="preserve">43.8601684570312</t>
   </si>
   <si>
     <t xml:space="preserve">45.7209014892578</t>
@@ -1637,22 +1637,22 @@
     <t xml:space="preserve">47.2398643493652</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2905120849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1892585754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2082481384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2841987609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3158149719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3727798461914</t>
+    <t xml:space="preserve">46.2905082702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1892547607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.208251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2841949462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3158187866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3727760314941</t>
   </si>
   <si>
     <t xml:space="preserve">46.6132965087891</t>
@@ -1661,13 +1661,13 @@
     <t xml:space="preserve">44.4867401123047</t>
   </si>
   <si>
-    <t xml:space="preserve">43.5373840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5184020996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0753784179688</t>
+    <t xml:space="preserve">43.5373878479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5183982849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.075382232666</t>
   </si>
   <si>
     <t xml:space="preserve">41.5627288818359</t>
@@ -1676,22 +1676,22 @@
     <t xml:space="preserve">40.2146453857422</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8475379943848</t>
+    <t xml:space="preserve">41.8475341796875</t>
   </si>
   <si>
     <t xml:space="preserve">42.4551239013672</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2526206970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8095588684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1956214904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0310554504395</t>
+    <t xml:space="preserve">40.2526245117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8095626831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1956176757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0310516357422</t>
   </si>
   <si>
     <t xml:space="preserve">44.3158569335938</t>
@@ -1706,22 +1706,22 @@
     <t xml:space="preserve">45.7398872375488</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8348197937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8031692504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3854484558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4234275817871</t>
+    <t xml:space="preserve">45.8348236083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.8031616210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3854522705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4234237670898</t>
   </si>
   <si>
     <t xml:space="preserve">47.1829071044922</t>
   </si>
   <si>
-    <t xml:space="preserve">49.1765518188477</t>
+    <t xml:space="preserve">49.1765480041504</t>
   </si>
   <si>
     <t xml:space="preserve">48.3695983886719</t>
@@ -1730,28 +1730,28 @@
     <t xml:space="preserve">45.4360961914062</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0753364562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6449546813965</t>
+    <t xml:space="preserve">45.0753326416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6449584960938</t>
   </si>
   <si>
     <t xml:space="preserve">47.2588539123535</t>
   </si>
   <si>
-    <t xml:space="preserve">48.4645347595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8885650634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.125904083252</t>
+    <t xml:space="preserve">48.4645385742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8885688781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.1259002685547</t>
   </si>
   <si>
     <t xml:space="preserve">50.6955184936523</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2208404541016</t>
+    <t xml:space="preserve">50.2208442687988</t>
   </si>
   <si>
     <t xml:space="preserve">49.9360313415527</t>
@@ -1763,19 +1763,19 @@
     <t xml:space="preserve">52.1670188903809</t>
   </si>
   <si>
-    <t xml:space="preserve">52.6891632080078</t>
+    <t xml:space="preserve">52.6891670227051</t>
   </si>
   <si>
     <t xml:space="preserve">52.9739646911621</t>
   </si>
   <si>
-    <t xml:space="preserve">54.2556037902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2587699890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.9707908630371</t>
+    <t xml:space="preserve">54.2555999755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2587738037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9707870483398</t>
   </si>
   <si>
     <t xml:space="preserve">53.7334480285645</t>
@@ -1784,40 +1784,40 @@
     <t xml:space="preserve">55.2998847961426</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3979988098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.401180267334</t>
+    <t xml:space="preserve">54.3980026245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4011764526367</t>
   </si>
   <si>
     <t xml:space="preserve">53.9233207702637</t>
   </si>
   <si>
-    <t xml:space="preserve">54.4929389953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4454612731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4961128234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.6353340148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.9644355773926</t>
+    <t xml:space="preserve">54.4929351806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4454650878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4961090087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.6353378295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.9644317626953</t>
   </si>
   <si>
     <t xml:space="preserve">55.7270965576172</t>
   </si>
   <si>
-    <t xml:space="preserve">56.1068305969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5328521728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5239181518555</t>
+    <t xml:space="preserve">56.1068344116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5328559875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5239105224609</t>
   </si>
   <si>
     <t xml:space="preserve">53.5717430114746</t>
@@ -1826,7 +1826,7 @@
     <t xml:space="preserve">52.6151084899902</t>
   </si>
   <si>
-    <t xml:space="preserve">52.5194435119629</t>
+    <t xml:space="preserve">52.5194473266602</t>
   </si>
   <si>
     <t xml:space="preserve">51.4671363830566</t>
@@ -1835,34 +1835,34 @@
     <t xml:space="preserve">54.5283851623535</t>
   </si>
   <si>
-    <t xml:space="preserve">55.9633369445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0590057373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1980323791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.7764778137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0111694335938</t>
+    <t xml:space="preserve">55.9633407592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0590019226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1980285644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.7764854431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.011173248291</t>
   </si>
   <si>
     <t xml:space="preserve">55.6285171508789</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2025032043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.9155082702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4416580200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5806846618652</t>
+    <t xml:space="preserve">56.2024993896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.9155120849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4416618347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.580680847168</t>
   </si>
   <si>
     <t xml:space="preserve">56.3459968566895</t>
@@ -1871,31 +1871,31 @@
     <t xml:space="preserve">55.1501960754395</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5762100219727</t>
+    <t xml:space="preserve">54.5762176513672</t>
   </si>
   <si>
     <t xml:space="preserve">54.4327239990234</t>
   </si>
   <si>
-    <t xml:space="preserve">54.8632011413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.919979095459</t>
+    <t xml:space="preserve">54.8632049560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.9199829101562</t>
   </si>
   <si>
     <t xml:space="preserve">56.8243141174316</t>
   </si>
   <si>
-    <t xml:space="preserve">57.2548027038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6808166503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.7286529541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.2114372253418</t>
+    <t xml:space="preserve">57.2547988891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6808128356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.7286491394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.2114448547363</t>
   </si>
   <si>
     <t xml:space="preserve">57.6374549865723</t>
@@ -1904,7 +1904,7 @@
     <t xml:space="preserve">58.5462608337402</t>
   </si>
   <si>
-    <t xml:space="preserve">57.9244499206543</t>
+    <t xml:space="preserve">57.924446105957</t>
   </si>
   <si>
     <t xml:space="preserve">58.3549385070801</t>
@@ -1913,46 +1913,46 @@
     <t xml:space="preserve">57.7331199645996</t>
   </si>
   <si>
-    <t xml:space="preserve">57.3504638671875</t>
+    <t xml:space="preserve">57.3504676818848</t>
   </si>
   <si>
     <t xml:space="preserve">58.3071060180664</t>
   </si>
   <si>
-    <t xml:space="preserve">60.2682151794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.1725463867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.7420654296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.2159118652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.1202430725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3026313781738</t>
+    <t xml:space="preserve">60.2682113647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.172550201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.7420616149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.2159156799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.120246887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3026390075684</t>
   </si>
   <si>
     <t xml:space="preserve">57.828784942627</t>
   </si>
   <si>
-    <t xml:space="preserve">58.1157760620117</t>
+    <t xml:space="preserve">58.1157722473145</t>
   </si>
   <si>
     <t xml:space="preserve">57.7809562683105</t>
   </si>
   <si>
-    <t xml:space="preserve">59.0245819091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.4550743103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.3160400390625</t>
+    <t xml:space="preserve">59.0245780944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.4550704956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.3160438537598</t>
   </si>
   <si>
     <t xml:space="preserve">60.0290489196777</t>
@@ -1961,52 +1961,52 @@
     <t xml:space="preserve">59.0724143981934</t>
   </si>
   <si>
-    <t xml:space="preserve">58.2592697143555</t>
+    <t xml:space="preserve">58.2592735290527</t>
   </si>
   <si>
     <t xml:space="preserve">58.0201148986816</t>
   </si>
   <si>
-    <t xml:space="preserve">50.9888229370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.4148445129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2279739379883</t>
+    <t xml:space="preserve">50.9888191223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.4148406982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2279777526855</t>
   </si>
   <si>
     <t xml:space="preserve">51.3236465454102</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8931541442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7930221557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8408508300781</t>
+    <t xml:space="preserve">50.8931579589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7930183410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8408546447754</t>
   </si>
   <si>
     <t xml:space="preserve">48.6928901672363</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2668647766113</t>
+    <t xml:space="preserve">49.2668724060059</t>
   </si>
   <si>
     <t xml:space="preserve">49.9843521118164</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9365196228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0800094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.653995513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2235107421875</t>
+    <t xml:space="preserve">49.9365158081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.080005645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6539993286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2235069274902</t>
   </si>
   <si>
     <t xml:space="preserve">50.845329284668</t>
@@ -2018,16 +2018,16 @@
     <t xml:space="preserve">50.9409866333008</t>
   </si>
   <si>
-    <t xml:space="preserve">51.514965057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.797492980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.1323204040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6973571777344</t>
+    <t xml:space="preserve">51.5149688720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7974891662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.13232421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6973648071289</t>
   </si>
   <si>
     <t xml:space="preserve">49.3147048950195</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">49.4582023620605</t>
   </si>
   <si>
-    <t xml:space="preserve">49.745189666748</t>
+    <t xml:space="preserve">49.7451934814453</t>
   </si>
   <si>
     <t xml:space="preserve">50.0321807861328</t>
@@ -2048,7 +2048,7 @@
     <t xml:space="preserve">48.597225189209</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3625373840332</t>
+    <t xml:space="preserve">49.3625335693359</t>
   </si>
   <si>
     <t xml:space="preserve">54.0022315979004</t>
@@ -2057,13 +2057,13 @@
     <t xml:space="preserve">53.4282455444336</t>
   </si>
   <si>
-    <t xml:space="preserve">54.2892265319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1935539245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0934257507324</t>
+    <t xml:space="preserve">54.2892227172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1935577392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0934219360352</t>
   </si>
   <si>
     <t xml:space="preserve">52.4716110229492</t>
@@ -2078,67 +2078,67 @@
     <t xml:space="preserve">54.9110412597656</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3370475769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8587379455566</t>
+    <t xml:space="preserve">54.3370513916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8587341308594</t>
   </si>
   <si>
     <t xml:space="preserve">54.4805488586426</t>
   </si>
   <si>
-    <t xml:space="preserve">55.0545310974121</t>
+    <t xml:space="preserve">55.0545349121094</t>
   </si>
   <si>
     <t xml:space="preserve">55.3415260314941</t>
   </si>
   <si>
-    <t xml:space="preserve">55.8676795959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5373191833496</t>
+    <t xml:space="preserve">55.86767578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5373153686523</t>
   </si>
   <si>
     <t xml:space="preserve">56.6329917907715</t>
   </si>
   <si>
-    <t xml:space="preserve">58.4027671813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.067943572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6942329406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.3115768432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.8511238098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.6164474487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.3384017944336</t>
+    <t xml:space="preserve">58.4027633666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.0679473876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6942291259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.3115730285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.8511352539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.6164436340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.3383941650391</t>
   </si>
   <si>
     <t xml:space="preserve">66.3428649902344</t>
   </si>
   <si>
-    <t xml:space="preserve">66.9646682739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.9213256835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.2606048583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.0692825317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.3951644897461</t>
+    <t xml:space="preserve">66.9646835327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.9213104248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.2606201171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.0692749023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.3951721191406</t>
   </si>
   <si>
     <t xml:space="preserve">68.016975402832</t>
@@ -2150,34 +2150,34 @@
     <t xml:space="preserve">67.2994995117188</t>
   </si>
   <si>
-    <t xml:space="preserve">67.5386505126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.9257965087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.2127838134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.4474716186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.8734741210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.7778244018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.0603485107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.0080413818359</t>
+    <t xml:space="preserve">67.5386657714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.9257888793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.212776184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.4474639892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.8734817504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.7778091430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.0603408813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.0080490112305</t>
   </si>
   <si>
     <t xml:space="preserve">66.4385223388672</t>
   </si>
   <si>
-    <t xml:space="preserve">65.5775527954102</t>
+    <t xml:space="preserve">65.5775451660156</t>
   </si>
   <si>
     <t xml:space="preserve">65.9123764038086</t>
@@ -2186,97 +2186,97 @@
     <t xml:space="preserve">67.2516708374023</t>
   </si>
   <si>
-    <t xml:space="preserve">67.8256530761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.6343231201172</t>
+    <t xml:space="preserve">67.8256607055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.6343154907227</t>
   </si>
   <si>
     <t xml:space="preserve">65.7688827514648</t>
   </si>
   <si>
-    <t xml:space="preserve">66.1037063598633</t>
+    <t xml:space="preserve">66.1036987304688</t>
   </si>
   <si>
     <t xml:space="preserve">69.4519424438477</t>
   </si>
   <si>
-    <t xml:space="preserve">68.2083129882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.3129119873047</t>
+    <t xml:space="preserve">68.2083053588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.3129196166992</t>
   </si>
   <si>
     <t xml:space="preserve">73.3263244628906</t>
   </si>
   <si>
-    <t xml:space="preserve">73.2306671142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.0916366577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.6611480712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.3741607666016</t>
+    <t xml:space="preserve">73.2306594848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.0916290283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.6611404418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.374153137207</t>
   </si>
   <si>
     <t xml:space="preserve">70.6955795288086</t>
   </si>
   <si>
-    <t xml:space="preserve">70.7912292480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.4653549194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.2650833129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.6388092041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3173904418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9391937255859</t>
+    <t xml:space="preserve">70.7912216186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.4653472900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.2650756835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.6387939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3173828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9391860961914</t>
   </si>
   <si>
     <t xml:space="preserve">72.7045059204102</t>
   </si>
   <si>
-    <t xml:space="preserve">72.7523422241211</t>
+    <t xml:space="preserve">72.7523498535156</t>
   </si>
   <si>
     <t xml:space="preserve">72.6088485717773</t>
   </si>
   <si>
-    <t xml:space="preserve">74.4264602661133</t>
+    <t xml:space="preserve">74.4264678955078</t>
   </si>
   <si>
     <t xml:space="preserve">74.1394729614258</t>
   </si>
   <si>
-    <t xml:space="preserve">71.7478790283203</t>
+    <t xml:space="preserve">71.7478713989258</t>
   </si>
   <si>
     <t xml:space="preserve">71.9870300292969</t>
   </si>
   <si>
-    <t xml:space="preserve">73.2784957885742</t>
+    <t xml:space="preserve">73.2784881591797</t>
   </si>
   <si>
     <t xml:space="preserve">71.4130477905273</t>
   </si>
   <si>
-    <t xml:space="preserve">66.821174621582</t>
+    <t xml:space="preserve">66.8211822509766</t>
   </si>
   <si>
     <t xml:space="preserve">65.7210464477539</t>
   </si>
   <si>
-    <t xml:space="preserve">62.1336555480957</t>
+    <t xml:space="preserve">62.1336517333984</t>
   </si>
   <si>
     <t xml:space="preserve">63.8077774047852</t>
@@ -2285,10 +2285,10 @@
     <t xml:space="preserve">61.8944931030273</t>
   </si>
   <si>
-    <t xml:space="preserve">60.937858581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.8766136169434</t>
+    <t xml:space="preserve">60.9378547668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.8766174316406</t>
   </si>
   <si>
     <t xml:space="preserve">52.5672721862793</t>
@@ -2300,19 +2300,19 @@
     <t xml:space="preserve">46.3778228759766</t>
   </si>
   <si>
-    <t xml:space="preserve">48.7407188415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4594497680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7094306945801</t>
+    <t xml:space="preserve">48.74072265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4594535827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7094268798828</t>
   </si>
   <si>
     <t xml:space="preserve">43.8714332580566</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2107238769531</t>
+    <t xml:space="preserve">45.2107200622559</t>
   </si>
   <si>
     <t xml:space="preserve">45.344654083252</t>
@@ -2321,52 +2321,52 @@
     <t xml:space="preserve">47.1048698425293</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0844802856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.2190399169922</t>
+    <t xml:space="preserve">51.0844841003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.2190437316895</t>
   </si>
   <si>
     <t xml:space="preserve">59.1680793762207</t>
   </si>
   <si>
-    <t xml:space="preserve">57.6852874755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.2637405395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.0813484191895</t>
+    <t xml:space="preserve">57.6852836608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.263744354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0813522338867</t>
   </si>
   <si>
     <t xml:space="preserve">60.3638763427734</t>
   </si>
   <si>
-    <t xml:space="preserve">61.1291923522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.4161796569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.6598091125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.5207824707031</t>
+    <t xml:space="preserve">61.1291885375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.4161720275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.6598129272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.5207748413086</t>
   </si>
   <si>
     <t xml:space="preserve">62.564136505127</t>
   </si>
   <si>
-    <t xml:space="preserve">63.1381187438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.0424728393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9901657104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.033519744873</t>
+    <t xml:space="preserve">63.138126373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.0424690246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.9901695251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.0335273742676</t>
   </si>
   <si>
     <t xml:space="preserve">59.2684936523438</t>
@@ -2378,7 +2378,7 @@
     <t xml:space="preserve">61.7279624938965</t>
   </si>
   <si>
-    <t xml:space="preserve">63.7051887512207</t>
+    <t xml:space="preserve">63.705192565918</t>
   </si>
   <si>
     <t xml:space="preserve">64.717903137207</t>
@@ -2399,13 +2399,13 @@
     <t xml:space="preserve">64.9108123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">68.4312286376953</t>
+    <t xml:space="preserve">68.4312362670898</t>
   </si>
   <si>
     <t xml:space="preserve">68.0936584472656</t>
   </si>
   <si>
-    <t xml:space="preserve">68.3830032348633</t>
+    <t xml:space="preserve">68.3830108642578</t>
   </si>
   <si>
     <t xml:space="preserve">68.6241302490234</t>
@@ -2414,22 +2414,22 @@
     <t xml:space="preserve">69.9744338989258</t>
   </si>
   <si>
-    <t xml:space="preserve">73.3983917236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.1217727661133</t>
+    <t xml:space="preserve">73.3983993530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.1217803955078</t>
   </si>
   <si>
     <t xml:space="preserve">73.9288787841797</t>
   </si>
   <si>
-    <t xml:space="preserve">74.362907409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75.8578796386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.6522521972656</t>
+    <t xml:space="preserve">74.3628997802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75.8578720092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.6522598266602</t>
   </si>
   <si>
     <t xml:space="preserve">71.8552093505859</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">67.03271484375</t>
   </si>
   <si>
-    <t xml:space="preserve">67.2256088256836</t>
+    <t xml:space="preserve">67.2256011962891</t>
   </si>
   <si>
     <t xml:space="preserve">64.8625946044922</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">67.3220596313477</t>
   </si>
   <si>
-    <t xml:space="preserve">69.9262084960938</t>
+    <t xml:space="preserve">69.9262161254883</t>
   </si>
   <si>
     <t xml:space="preserve">71.180061340332</t>
@@ -2486,13 +2486,13 @@
     <t xml:space="preserve">68.2865600585938</t>
   </si>
   <si>
-    <t xml:space="preserve">68.6723556518555</t>
+    <t xml:space="preserve">68.6723480224609</t>
   </si>
   <si>
     <t xml:space="preserve">69.0099334716797</t>
   </si>
   <si>
-    <t xml:space="preserve">69.2992782592773</t>
+    <t xml:space="preserve">69.2992706298828</t>
   </si>
   <si>
     <t xml:space="preserve">72.1445617675781</t>
@@ -2516,7 +2516,7 @@
     <t xml:space="preserve">71.6623001098633</t>
   </si>
   <si>
-    <t xml:space="preserve">72.3374557495117</t>
+    <t xml:space="preserve">72.3374481201172</t>
   </si>
   <si>
     <t xml:space="preserve">72.8679351806641</t>
@@ -2525,13 +2525,13 @@
     <t xml:space="preserve">73.4466323852539</t>
   </si>
   <si>
-    <t xml:space="preserve">73.5430755615234</t>
+    <t xml:space="preserve">73.543083190918</t>
   </si>
   <si>
     <t xml:space="preserve">71.999885559082</t>
   </si>
   <si>
-    <t xml:space="preserve">73.0608291625977</t>
+    <t xml:space="preserve">73.0608215332031</t>
   </si>
   <si>
     <t xml:space="preserve">73.6877593994141</t>
@@ -2549,22 +2549,22 @@
     <t xml:space="preserve">81.9342193603516</t>
   </si>
   <si>
-    <t xml:space="preserve">82.9469528198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1170654296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.0815734863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3582000732422</t>
+    <t xml:space="preserve">82.9469451904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.117073059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.0815658569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3581924438477</t>
   </si>
   <si>
     <t xml:space="preserve">83.1398468017578</t>
   </si>
   <si>
-    <t xml:space="preserve">81.0179443359375</t>
+    <t xml:space="preserve">81.017936706543</t>
   </si>
   <si>
     <t xml:space="preserve">81.0661773681641</t>
@@ -2573,7 +2573,7 @@
     <t xml:space="preserve">82.609375</t>
   </si>
   <si>
-    <t xml:space="preserve">80.8732757568359</t>
+    <t xml:space="preserve">80.8732833862305</t>
   </si>
   <si>
     <t xml:space="preserve">83.0916213989258</t>
@@ -2585,13 +2585,13 @@
     <t xml:space="preserve">84.5865936279297</t>
   </si>
   <si>
-    <t xml:space="preserve">84.6348266601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.6703186035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.7795028686523</t>
+    <t xml:space="preserve">84.6348190307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.6703262329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.7794952392578</t>
   </si>
   <si>
     <t xml:space="preserve">84.6830444335938</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">89.3126449584961</t>
   </si>
   <si>
-    <t xml:space="preserve">90.6629486083984</t>
+    <t xml:space="preserve">90.6629409790039</t>
   </si>
   <si>
     <t xml:space="preserve">88.1070251464844</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">87.8658981323242</t>
   </si>
   <si>
-    <t xml:space="preserve">91.2416458129883</t>
+    <t xml:space="preserve">91.2416381835938</t>
   </si>
   <si>
     <t xml:space="preserve">90.2771453857422</t>
@@ -2630,10 +2630,10 @@
     <t xml:space="preserve">90.5664901733398</t>
   </si>
   <si>
-    <t xml:space="preserve">90.8076095581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9777374267578</t>
+    <t xml:space="preserve">90.8076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9777450561523</t>
   </si>
   <si>
     <t xml:space="preserve">95.0031890869141</t>
@@ -2645,16 +2645,16 @@
     <t xml:space="preserve">95.7265625</t>
   </si>
   <si>
-    <t xml:space="preserve">93.2188720703125</t>
+    <t xml:space="preserve">93.218864440918</t>
   </si>
   <si>
     <t xml:space="preserve">93.5082092285156</t>
   </si>
   <si>
-    <t xml:space="preserve">91.4827651977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.939567565918</t>
+    <t xml:space="preserve">91.4827728271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9395599365234</t>
   </si>
   <si>
     <t xml:space="preserve">91.6274337768555</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">92.1096878051758</t>
   </si>
   <si>
-    <t xml:space="preserve">93.3635330200195</t>
+    <t xml:space="preserve">93.3635406494141</t>
   </si>
   <si>
     <t xml:space="preserve">95.5336608886719</t>
@@ -2681,7 +2681,7 @@
     <t xml:space="preserve">94.5209503173828</t>
   </si>
   <si>
-    <t xml:space="preserve">92.6884002685547</t>
+    <t xml:space="preserve">92.6883926391602</t>
   </si>
   <si>
     <t xml:space="preserve">91.4345397949219</t>
@@ -2702,22 +2702,22 @@
     <t xml:space="preserve">99.7292404174805</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6073455810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.8966903686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3789443969727</t>
+    <t xml:space="preserve">97.6073379516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.8966979980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3789367675781</t>
   </si>
   <si>
     <t xml:space="preserve">96.3052597045898</t>
   </si>
   <si>
-    <t xml:space="preserve">93.7493438720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.8330612182617</t>
+    <t xml:space="preserve">93.7493515014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.8330688476562</t>
   </si>
   <si>
     <t xml:space="preserve">92.8813018798828</t>
@@ -2744,10 +2744,10 @@
     <t xml:space="preserve">95.4372100830078</t>
   </si>
   <si>
-    <t xml:space="preserve">95.7747955322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.447265625</t>
+    <t xml:space="preserve">95.774787902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4472732543945</t>
   </si>
   <si>
     <t xml:space="preserve">92.0614624023438</t>
@@ -2756,7 +2756,7 @@
     <t xml:space="preserve">91.8685607910156</t>
   </si>
   <si>
-    <t xml:space="preserve">91.8203430175781</t>
+    <t xml:space="preserve">91.8203353881836</t>
   </si>
   <si>
     <t xml:space="preserve">90.7111740112305</t>
@@ -2765,7 +2765,7 @@
     <t xml:space="preserve">90.855842590332</t>
   </si>
   <si>
-    <t xml:space="preserve">91.3863296508789</t>
+    <t xml:space="preserve">91.3863220214844</t>
   </si>
   <si>
     <t xml:space="preserve">90.759391784668</t>
@@ -2774,10 +2774,10 @@
     <t xml:space="preserve">87.7694396972656</t>
   </si>
   <si>
-    <t xml:space="preserve">88.2516860961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.3608779907227</t>
+    <t xml:space="preserve">88.2516937255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.3608703613281</t>
   </si>
   <si>
     <t xml:space="preserve">90.3735885620117</t>
@@ -2792,25 +2792,25 @@
     <t xml:space="preserve">91.1451950073242</t>
   </si>
   <si>
-    <t xml:space="preserve">92.495491027832</t>
+    <t xml:space="preserve">92.4954833984375</t>
   </si>
   <si>
     <t xml:space="preserve">89.4573211669922</t>
   </si>
   <si>
-    <t xml:space="preserve">91.675666809082</t>
+    <t xml:space="preserve">91.6756744384766</t>
   </si>
   <si>
     <t xml:space="preserve">91.9167938232422</t>
   </si>
   <si>
-    <t xml:space="preserve">91.7238922119141</t>
+    <t xml:space="preserve">91.7238998413086</t>
   </si>
   <si>
     <t xml:space="preserve">91.0969619750977</t>
   </si>
   <si>
-    <t xml:space="preserve">90.9040679931641</t>
+    <t xml:space="preserve">90.9040756225586</t>
   </si>
   <si>
     <t xml:space="preserve">92.3508224487305</t>
@@ -2819,22 +2819,22 @@
     <t xml:space="preserve">93.4599914550781</t>
   </si>
   <si>
-    <t xml:space="preserve">92.5437164306641</t>
+    <t xml:space="preserve">92.5437088012695</t>
   </si>
   <si>
     <t xml:space="preserve">95.9194717407227</t>
   </si>
   <si>
-    <t xml:space="preserve">93.26708984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5564422607422</t>
+    <t xml:space="preserve">93.2670822143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5564498901367</t>
   </si>
   <si>
     <t xml:space="preserve">94.5691757202148</t>
   </si>
   <si>
-    <t xml:space="preserve">96.0641326904297</t>
+    <t xml:space="preserve">96.0641403198242</t>
   </si>
   <si>
     <t xml:space="preserve">98.4753875732422</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">98.1860427856445</t>
   </si>
   <si>
-    <t xml:space="preserve">97.414436340332</t>
+    <t xml:space="preserve">97.4144439697266</t>
   </si>
   <si>
     <t xml:space="preserve">100.790184020996</t>
@@ -2855,19 +2855,19 @@
     <t xml:space="preserve">102.912078857422</t>
   </si>
   <si>
-    <t xml:space="preserve">101.465339660645</t>
+    <t xml:space="preserve">101.46533203125</t>
   </si>
   <si>
     <t xml:space="preserve">102.719177246094</t>
   </si>
   <si>
-    <t xml:space="preserve">102.52628326416</t>
+    <t xml:space="preserve">102.526290893555</t>
   </si>
   <si>
     <t xml:space="preserve">102.140487670898</t>
   </si>
   <si>
-    <t xml:space="preserve">104.937538146973</t>
+    <t xml:space="preserve">104.937530517578</t>
   </si>
   <si>
     <t xml:space="preserve">103.104995727539</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">102.815635681152</t>
   </si>
   <si>
-    <t xml:space="preserve">103.201431274414</t>
+    <t xml:space="preserve">103.201438903809</t>
   </si>
   <si>
     <t xml:space="preserve">100.500831604004</t>
@@ -2891,13 +2891,13 @@
     <t xml:space="preserve">98.5718307495117</t>
   </si>
   <si>
-    <t xml:space="preserve">95.0514297485352</t>
+    <t xml:space="preserve">95.0514221191406</t>
   </si>
   <si>
     <t xml:space="preserve">94.135139465332</t>
   </si>
   <si>
-    <t xml:space="preserve">92.5919494628906</t>
+    <t xml:space="preserve">92.5919418334961</t>
   </si>
   <si>
     <t xml:space="preserve">89.2162017822266</t>
@@ -2912,16 +2912,16 @@
     <t xml:space="preserve">101.561790466309</t>
   </si>
   <si>
-    <t xml:space="preserve">103.973037719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.780128479004</t>
+    <t xml:space="preserve">103.973045349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.780136108398</t>
   </si>
   <si>
     <t xml:space="preserve">105.323333740234</t>
   </si>
   <si>
-    <t xml:space="preserve">103.490791320801</t>
+    <t xml:space="preserve">103.490783691406</t>
   </si>
   <si>
     <t xml:space="preserve">104.069488525391</t>
@@ -2930,7 +2930,7 @@
     <t xml:space="preserve">108.023933410645</t>
   </si>
   <si>
-    <t xml:space="preserve">110.14582824707</t>
+    <t xml:space="preserve">110.145820617676</t>
   </si>
   <si>
     <t xml:space="preserve">108.699081420898</t>
@@ -2945,22 +2945,22 @@
     <t xml:space="preserve">106.384284973145</t>
   </si>
   <si>
-    <t xml:space="preserve">108.891983032227</t>
+    <t xml:space="preserve">108.891990661621</t>
   </si>
   <si>
     <t xml:space="preserve">107.831039428711</t>
   </si>
   <si>
-    <t xml:space="preserve">108.795539855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.08487701416</t>
+    <t xml:space="preserve">108.795532226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.084884643555</t>
   </si>
   <si>
     <t xml:space="preserve">107.059425354004</t>
   </si>
   <si>
-    <t xml:space="preserve">107.348785400391</t>
+    <t xml:space="preserve">107.348777770996</t>
   </si>
   <si>
     <t xml:space="preserve">109.567123413086</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">108.50617980957</t>
   </si>
   <si>
-    <t xml:space="preserve">109.530769348145</t>
+    <t xml:space="preserve">109.53076171875</t>
   </si>
   <si>
     <t xml:space="preserve">107.786018371582</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">109.046104431152</t>
   </si>
   <si>
-    <t xml:space="preserve">109.918487548828</t>
+    <t xml:space="preserve">109.918479919434</t>
   </si>
   <si>
     <t xml:space="preserve">110.500053405762</t>
@@ -2999,13 +2999,13 @@
     <t xml:space="preserve">113.117164611816</t>
   </si>
   <si>
-    <t xml:space="preserve">115.831192016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.79566192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.764976501465</t>
+    <t xml:space="preserve">115.831199645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.795669555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.76496887207</t>
   </si>
   <si>
     <t xml:space="preserve">114.668045043945</t>
@@ -3017,7 +3017,7 @@
     <t xml:space="preserve">114.474182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">116.509704589844</t>
+    <t xml:space="preserve">116.509712219238</t>
   </si>
   <si>
     <t xml:space="preserve">121.453140258789</t>
@@ -3029,10 +3029,10 @@
     <t xml:space="preserve">128.819793701172</t>
   </si>
   <si>
-    <t xml:space="preserve">127.365844726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.268936157227</t>
+    <t xml:space="preserve">127.365852355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.268928527832</t>
   </si>
   <si>
     <t xml:space="preserve">128.432083129883</t>
@@ -3059,13 +3059,13 @@
     <t xml:space="preserve">134.44172668457</t>
   </si>
   <si>
-    <t xml:space="preserve">133.375503540039</t>
+    <t xml:space="preserve">133.375518798828</t>
   </si>
   <si>
     <t xml:space="preserve">135.798767089844</t>
   </si>
   <si>
-    <t xml:space="preserve">135.314117431641</t>
+    <t xml:space="preserve">135.314102172852</t>
   </si>
   <si>
     <t xml:space="preserve">136.574188232422</t>
@@ -3080,10 +3080,10 @@
     <t xml:space="preserve">133.763229370117</t>
   </si>
   <si>
-    <t xml:space="preserve">137.446548461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.895690917969</t>
+    <t xml:space="preserve">137.446563720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.89567565918</t>
   </si>
   <si>
     <t xml:space="preserve">134.344818115234</t>
@@ -3095,7 +3095,7 @@
     <t xml:space="preserve">142.293060302734</t>
   </si>
   <si>
-    <t xml:space="preserve">141.032974243164</t>
+    <t xml:space="preserve">141.032958984375</t>
   </si>
   <si>
     <t xml:space="preserve">143.359268188477</t>
@@ -3122,7 +3122,7 @@
     <t xml:space="preserve">138.609725952148</t>
   </si>
   <si>
-    <t xml:space="preserve">135.992630004883</t>
+    <t xml:space="preserve">135.992614746094</t>
   </si>
   <si>
     <t xml:space="preserve">137.640426635742</t>
@@ -3152,13 +3152,13 @@
     <t xml:space="preserve">148.884292602539</t>
   </si>
   <si>
-    <t xml:space="preserve">148.011901855469</t>
+    <t xml:space="preserve">148.011917114258</t>
   </si>
   <si>
     <t xml:space="preserve">149.175079345703</t>
   </si>
   <si>
-    <t xml:space="preserve">149.75666809082</t>
+    <t xml:space="preserve">149.756652832031</t>
   </si>
   <si>
     <t xml:space="preserve">146.364105224609</t>
@@ -3167,13 +3167,13 @@
     <t xml:space="preserve">147.236465454102</t>
   </si>
   <si>
-    <t xml:space="preserve">148.205749511719</t>
+    <t xml:space="preserve">148.205764770508</t>
   </si>
   <si>
     <t xml:space="preserve">147.81803894043</t>
   </si>
   <si>
-    <t xml:space="preserve">150.532104492188</t>
+    <t xml:space="preserve">150.532119750977</t>
   </si>
   <si>
     <t xml:space="preserve">150.629013061523</t>
@@ -3185,7 +3185,7 @@
     <t xml:space="preserve">154.893936157227</t>
   </si>
   <si>
-    <t xml:space="preserve">152.955337524414</t>
+    <t xml:space="preserve">152.955352783203</t>
   </si>
   <si>
     <t xml:space="preserve">157.898773193359</t>
@@ -3197,7 +3197,7 @@
     <t xml:space="preserve">166.816314697266</t>
   </si>
   <si>
-    <t xml:space="preserve">166.428588867188</t>
+    <t xml:space="preserve">166.428604125977</t>
   </si>
   <si>
     <t xml:space="preserve">165.847015380859</t>
@@ -3224,19 +3224,19 @@
     <t xml:space="preserve">170.305770874023</t>
   </si>
   <si>
-    <t xml:space="preserve">169.239562988281</t>
+    <t xml:space="preserve">169.23957824707</t>
   </si>
   <si>
     <t xml:space="preserve">169.724212646484</t>
   </si>
   <si>
-    <t xml:space="preserve">168.948776245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.811492919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.204055786133</t>
+    <t xml:space="preserve">168.948791503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.811477661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.204040527344</t>
   </si>
   <si>
     <t xml:space="preserve">165.071578979492</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">176.606231689453</t>
   </si>
   <si>
-    <t xml:space="preserve">171.372009277344</t>
+    <t xml:space="preserve">171.372024536133</t>
   </si>
   <si>
     <t xml:space="preserve">152.470672607422</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">153.633865356445</t>
   </si>
   <si>
-    <t xml:space="preserve">147.430328369141</t>
+    <t xml:space="preserve">147.43034362793</t>
   </si>
   <si>
     <t xml:space="preserve">147.721130371094</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">159.643508911133</t>
   </si>
   <si>
-    <t xml:space="preserve">162.842193603516</t>
+    <t xml:space="preserve">162.842178344727</t>
   </si>
   <si>
     <t xml:space="preserve">163.229904174805</t>
@@ -3311,25 +3311,25 @@
     <t xml:space="preserve">162.551406860352</t>
   </si>
   <si>
-    <t xml:space="preserve">161.87287902832</t>
+    <t xml:space="preserve">161.872894287109</t>
   </si>
   <si>
     <t xml:space="preserve">164.39306640625</t>
   </si>
   <si>
-    <t xml:space="preserve">171.27507019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.21369934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172.825973510742</t>
+    <t xml:space="preserve">171.275085449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.213684082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.825958251953</t>
   </si>
   <si>
     <t xml:space="preserve">174.182983398438</t>
   </si>
   <si>
-    <t xml:space="preserve">171.662811279297</t>
+    <t xml:space="preserve">171.662826538086</t>
   </si>
   <si>
     <t xml:space="preserve">172.341323852539</t>
@@ -3350,16 +3350,16 @@
     <t xml:space="preserve">168.561050415039</t>
   </si>
   <si>
-    <t xml:space="preserve">167.010177612305</t>
+    <t xml:space="preserve">167.010192871094</t>
   </si>
   <si>
     <t xml:space="preserve">159.934280395508</t>
   </si>
   <si>
-    <t xml:space="preserve">162.454483032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.837356567383</t>
+    <t xml:space="preserve">162.454467773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.837371826172</t>
   </si>
   <si>
     <t xml:space="preserve">166.040863037109</t>
@@ -3371,13 +3371,13 @@
     <t xml:space="preserve">160.709747314453</t>
   </si>
   <si>
-    <t xml:space="preserve">162.745269775391</t>
+    <t xml:space="preserve">162.745254516602</t>
   </si>
   <si>
     <t xml:space="preserve">159.158843994141</t>
   </si>
   <si>
-    <t xml:space="preserve">172.535186767578</t>
+    <t xml:space="preserve">172.535171508789</t>
   </si>
   <si>
     <t xml:space="preserve">174.958404541016</t>
@@ -3392,16 +3392,16 @@
     <t xml:space="preserve">169.43342590332</t>
   </si>
   <si>
-    <t xml:space="preserve">168.076400756836</t>
+    <t xml:space="preserve">168.076385498047</t>
   </si>
   <si>
     <t xml:space="preserve">163.617630004883</t>
   </si>
   <si>
-    <t xml:space="preserve">164.877716064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.714553833008</t>
+    <t xml:space="preserve">164.877731323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.714538574219</t>
   </si>
   <si>
     <t xml:space="preserve">170.596572875977</t>
@@ -3413,10 +3413,10 @@
     <t xml:space="preserve">174.473785400391</t>
   </si>
   <si>
-    <t xml:space="preserve">164.005340576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.317184448242</t>
+    <t xml:space="preserve">164.005325317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.317199707031</t>
   </si>
   <si>
     <t xml:space="preserve">155.572448730469</t>
@@ -3434,13 +3434,13 @@
     <t xml:space="preserve">151.016738891602</t>
   </si>
   <si>
-    <t xml:space="preserve">157.220245361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.113662719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.8583984375</t>
+    <t xml:space="preserve">157.220260620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.113677978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.858413696289</t>
   </si>
   <si>
     <t xml:space="preserve">154.990875244141</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">143.746994018555</t>
   </si>
   <si>
-    <t xml:space="preserve">143.553131103516</t>
+    <t xml:space="preserve">143.553146362305</t>
   </si>
   <si>
     <t xml:space="preserve">144.5224609375</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">129.692184448242</t>
   </si>
   <si>
-    <t xml:space="preserve">125.039527893066</t>
+    <t xml:space="preserve">125.039535522461</t>
   </si>
   <si>
     <t xml:space="preserve">136.9619140625</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">150.919815063477</t>
   </si>
   <si>
-    <t xml:space="preserve">149.368957519531</t>
+    <t xml:space="preserve">149.368942260742</t>
   </si>
   <si>
     <t xml:space="preserve">146.267181396484</t>
@@ -3524,16 +3524,16 @@
     <t xml:space="preserve">145.104019165039</t>
   </si>
   <si>
-    <t xml:space="preserve">148.6904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.394821166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.751815795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.659729003906</t>
+    <t xml:space="preserve">148.690414428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.394805908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.751831054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.659713745117</t>
   </si>
   <si>
     <t xml:space="preserve">145.200958251953</t>
@@ -3545,7 +3545,7 @@
     <t xml:space="preserve">141.323760986328</t>
   </si>
   <si>
-    <t xml:space="preserve">137.058822631836</t>
+    <t xml:space="preserve">137.058837890625</t>
   </si>
   <si>
     <t xml:space="preserve">134.538681030273</t>
@@ -3563,10 +3563,10 @@
     <t xml:space="preserve">135.217178344727</t>
   </si>
   <si>
-    <t xml:space="preserve">130.952285766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.753570556641</t>
+    <t xml:space="preserve">130.952270507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.753578186035</t>
   </si>
   <si>
     <t xml:space="preserve">121.16234588623</t>
@@ -3575,13 +3575,13 @@
     <t xml:space="preserve">113.601806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">117.285148620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.958831787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.575942993164</t>
+    <t xml:space="preserve">117.285140991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.958824157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.57593536377</t>
   </si>
   <si>
     <t xml:space="preserve">116.12198638916</t>
@@ -5480,7 +5480,7 @@
     <t xml:space="preserve">119.199996948242</t>
   </si>
   <si>
-    <t xml:space="preserve">119.300003051758</t>
+    <t xml:space="preserve">115.900001525879</t>
   </si>
 </sst>
 </file>
@@ -70923,22 +70923,22 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45966.6911574074</v>
+        <v>45967.6912384259</v>
       </c>
       <c r="B2505" t="n">
-        <v>31419</v>
+        <v>37910</v>
       </c>
       <c r="C2505" t="n">
-        <v>119.5</v>
+        <v>119.300003051758</v>
       </c>
       <c r="D2505" t="n">
-        <v>116.699996948242</v>
+        <v>115.900001525879</v>
       </c>
       <c r="E2505" t="n">
-        <v>117.800003051758</v>
+        <v>119</v>
       </c>
       <c r="F2505" t="n">
-        <v>119.300003051758</v>
+        <v>115.900001525879</v>
       </c>
       <c r="G2505" t="s">
         <v>1822</v>

--- a/data/REY.MI.xlsx
+++ b/data/REY.MI.xlsx
@@ -38,52 +38,52 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2559719085693</t>
+    <t xml:space="preserve">29.2559700012207</t>
   </si>
   <si>
     <t xml:space="preserve">REY.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8380260467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3272094726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6306400299072</t>
+    <t xml:space="preserve">28.8380241394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3272132873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6306381225586</t>
   </si>
   <si>
     <t xml:space="preserve">27.8396110534668</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2111167907715</t>
+    <t xml:space="preserve">28.2111148834229</t>
   </si>
   <si>
     <t xml:space="preserve">29.0005645751953</t>
   </si>
   <si>
-    <t xml:space="preserve">28.5594024658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.1414585113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1198253631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9789257049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8644104003906</t>
+    <t xml:space="preserve">28.5594005584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.1414546966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1198215484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9789237976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8644123077393</t>
   </si>
   <si>
     <t xml:space="preserve">27.4448871612549</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9324893951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8163909912109</t>
+    <t xml:space="preserve">27.932487487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8163928985596</t>
   </si>
   <si>
     <t xml:space="preserve">28.2807731628418</t>
@@ -98,49 +98,49 @@
     <t xml:space="preserve">27.862829208374</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2591342926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7018814086914</t>
+    <t xml:space="preserve">27.2591381072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7018775939941</t>
   </si>
   <si>
     <t xml:space="preserve">26.1678409576416</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2855167388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.379976272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6121654510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0053119659424</t>
+    <t xml:space="preserve">25.2855186462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3799781799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6121673583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0053062438965</t>
   </si>
   <si>
     <t xml:space="preserve">25.517707824707</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6570224761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6074199676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3071556091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0733852386475</t>
+    <t xml:space="preserve">25.6570243835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6074237823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3071537017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0733833312988</t>
   </si>
   <si>
     <t xml:space="preserve">26.2142810821533</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4696865081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0517444610596</t>
+    <t xml:space="preserve">26.4696884155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0517463684082</t>
   </si>
   <si>
     <t xml:space="preserve">25.7034606933594</t>
@@ -161,109 +161,109 @@
     <t xml:space="preserve">27.1894779205322</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2359180450439</t>
+    <t xml:space="preserve">27.2359142303467</t>
   </si>
   <si>
     <t xml:space="preserve">27.1662578582764</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9092674255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0237808227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5546550750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3008251190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4169235229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9989776611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9757652282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7900123596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.952543258667</t>
+    <t xml:space="preserve">27.9092693328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0237789154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5546588897705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3008270263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4169254302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9989833831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9757633209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7900085449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9525451660156</t>
   </si>
   <si>
     <t xml:space="preserve">30.2311687469482</t>
   </si>
   <si>
-    <t xml:space="preserve">29.7203502655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0686340332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8596649169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5578174591064</t>
+    <t xml:space="preserve">29.7203521728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0686359405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8596687316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5578212738037</t>
   </si>
   <si>
     <t xml:space="preserve">29.3256282806396</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4881591796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.511381149292</t>
+    <t xml:space="preserve">29.4881610870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5113830566406</t>
   </si>
   <si>
     <t xml:space="preserve">29.2095336914062</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1615142822266</t>
+    <t xml:space="preserve">30.161506652832</t>
   </si>
   <si>
     <t xml:space="preserve">29.3720664978027</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5345993041992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4433059692383</t>
+    <t xml:space="preserve">29.534595489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4433040618896</t>
   </si>
   <si>
     <t xml:space="preserve">28.6754951477051</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8612461090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8148059844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9076881408691</t>
+    <t xml:space="preserve">28.8612480163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8148097991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9076862335205</t>
   </si>
   <si>
     <t xml:space="preserve">28.629056930542</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4200839996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6776008605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5605487823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0287570953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3264465332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5137310028076</t>
+    <t xml:space="preserve">28.4200859069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6775989532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5605506896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0287532806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3264446258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.513729095459</t>
   </si>
   <si>
     <t xml:space="preserve">28.7946529388428</t>
@@ -272,28 +272,28 @@
     <t xml:space="preserve">29.0053443908691</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2628574371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1992683410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5036010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5504207611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9015769958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.6674766540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.7142925262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4567852020264</t>
+    <t xml:space="preserve">29.2628536224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1992721557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5036029815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5504245758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.901575088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.6674785614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.7142944335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.456787109375</t>
   </si>
   <si>
     <t xml:space="preserve">30.43337059021</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">29.8949356079102</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1859798431396</t>
+    <t xml:space="preserve">28.1859836578369</t>
   </si>
   <si>
     <t xml:space="preserve">29.3096771240234</t>
@@ -314,91 +314,91 @@
     <t xml:space="preserve">29.4969615936279</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6943683624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7747249603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8047771453857</t>
+    <t xml:space="preserve">27.6943702697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7747230529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8047752380371</t>
   </si>
   <si>
     <t xml:space="preserve">27.3198013305664</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9218292236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5070858001709</t>
+    <t xml:space="preserve">26.9218311309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5070838928223</t>
   </si>
   <si>
     <t xml:space="preserve">26.9452381134033</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8215427398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2195205688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1091136932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.624137878418</t>
+    <t xml:space="preserve">25.8215465545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.219518661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1091117858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6241359710693</t>
   </si>
   <si>
     <t xml:space="preserve">27.3666248321533</t>
   </si>
   <si>
-    <t xml:space="preserve">28.303035736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8882923126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7478313446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4434967041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9819355010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9117031097412</t>
+    <t xml:space="preserve">28.3030338287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8882942199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7478332519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4434947967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.98193359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9117012023926</t>
   </si>
   <si>
     <t xml:space="preserve">29.3799095153809</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4501419067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.8481140136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1524448394775</t>
+    <t xml:space="preserve">29.4501399993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.8481121063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1524505615234</t>
   </si>
   <si>
     <t xml:space="preserve">29.9651660919189</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7244205474854</t>
+    <t xml:space="preserve">28.7244186401367</t>
   </si>
   <si>
     <t xml:space="preserve">29.1458053588867</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0989856719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.9351139068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4903163909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9752922058105</t>
+    <t xml:space="preserve">29.0989875793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9351119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4903182983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9752902984619</t>
   </si>
   <si>
     <t xml:space="preserve">28.3732643127441</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">28.092342376709</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2729835510254</t>
+    <t xml:space="preserve">27.2729816436768</t>
   </si>
   <si>
     <t xml:space="preserve">27.0622882843018</t>
@@ -416,76 +416,76 @@
     <t xml:space="preserve">27.0388793945312</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8984184265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1492881774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.798131942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8917751312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7579555511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9518795013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.881649017334</t>
+    <t xml:space="preserve">26.8984203338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1492862701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7981357574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.891773223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7579574584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9518814086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8816509246826</t>
   </si>
   <si>
     <t xml:space="preserve">27.8114204406738</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9050598144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2963905334473</t>
+    <t xml:space="preserve">27.9050579071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2963943481445</t>
   </si>
   <si>
     <t xml:space="preserve">27.8582401275635</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5773181915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7411918640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.045524597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7880077362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3900337219238</t>
+    <t xml:space="preserve">27.5773162841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7177772521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.741189956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0455226898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7880096435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3900318145752</t>
   </si>
   <si>
     <t xml:space="preserve">29.1223926544189</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6541881561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2093963623047</t>
+    <t xml:space="preserve">28.6541900634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2093944549561</t>
   </si>
   <si>
     <t xml:space="preserve">27.413444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0856990814209</t>
+    <t xml:space="preserve">27.0857009887695</t>
   </si>
   <si>
     <t xml:space="preserve">26.8515949249268</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4368534088135</t>
+    <t xml:space="preserve">27.4368553161621</t>
   </si>
   <si>
     <t xml:space="preserve">26.6877269744873</t>
@@ -503,31 +503,31 @@
     <t xml:space="preserve">26.4536228179932</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5706748962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.523853302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3365726470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7513122558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3299255371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7446708679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7680778503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8851337432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2530574798584</t>
+    <t xml:space="preserve">26.570671081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5238552093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3365745544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.751314163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3299293518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7446727752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7680797576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8851356506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2530555725098</t>
   </si>
   <si>
     <t xml:space="preserve">25.0490036010742</t>
@@ -539,31 +539,31 @@
     <t xml:space="preserve">25.5172100067139</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2831077575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1660575866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4469814300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0958251953125</t>
+    <t xml:space="preserve">25.2831115722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1660556793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4469757080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0958271026611</t>
   </si>
   <si>
     <t xml:space="preserve">24.9319534301758</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0724182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6342601776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1961097717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1727027893066</t>
+    <t xml:space="preserve">25.0724143981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6342620849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1961135864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1726989746094</t>
   </si>
   <si>
     <t xml:space="preserve">27.834831237793</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">28.6307792663574</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2160358428955</t>
+    <t xml:space="preserve">29.2160377502441</t>
   </si>
   <si>
     <t xml:space="preserve">29.3330860137939</t>
@@ -590,70 +590,70 @@
     <t xml:space="preserve">28.8648815155029</t>
   </si>
   <si>
-    <t xml:space="preserve">28.349853515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6073684692383</t>
+    <t xml:space="preserve">28.3498554229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6073703765869</t>
   </si>
   <si>
     <t xml:space="preserve">29.4735488891602</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2394485473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7076530456543</t>
+    <t xml:space="preserve">29.2394504547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7076549530029</t>
   </si>
   <si>
     <t xml:space="preserve">29.4267292022705</t>
   </si>
   <si>
-    <t xml:space="preserve">30.8313484191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9952125549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4868297576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2527275085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3697853088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1356830596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.189136505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3061943054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2660217285156</t>
+    <t xml:space="preserve">30.8313426971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9952163696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4868316650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2527332305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.3697814941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1356811523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1891403198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3061981201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2660179138184</t>
   </si>
   <si>
     <t xml:space="preserve">34.0619659423828</t>
   </si>
   <si>
-    <t xml:space="preserve">34.647216796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4599418640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7408676147461</t>
+    <t xml:space="preserve">34.6472244262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4599456787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7408638000488</t>
   </si>
   <si>
     <t xml:space="preserve">34.6706352233887</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9983787536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.85791015625</t>
+    <t xml:space="preserve">34.9983749389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8579139709473</t>
   </si>
   <si>
     <t xml:space="preserve">34.1790161132812</t>
@@ -662,73 +662,73 @@
     <t xml:space="preserve">34.764274597168</t>
   </si>
   <si>
-    <t xml:space="preserve">34.8813285827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.3897094726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4131202697754</t>
+    <t xml:space="preserve">34.8813247680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.389705657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4131164550781</t>
   </si>
   <si>
     <t xml:space="preserve">35.6070442199707</t>
   </si>
   <si>
-    <t xml:space="preserve">35.4665794372559</t>
+    <t xml:space="preserve">35.4665832519531</t>
   </si>
   <si>
     <t xml:space="preserve">35.7943229675293</t>
   </si>
   <si>
-    <t xml:space="preserve">36.8243751525879</t>
+    <t xml:space="preserve">36.8243789672852</t>
   </si>
   <si>
     <t xml:space="preserve">37.6671485900879</t>
   </si>
   <si>
-    <t xml:space="preserve">37.8778419494629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9882469177246</t>
+    <t xml:space="preserve">37.8778381347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9882507324219</t>
   </si>
   <si>
     <t xml:space="preserve">37.5735092163086</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6203308105469</t>
+    <t xml:space="preserve">37.6203269958496</t>
   </si>
   <si>
     <t xml:space="preserve">37.6085395812988</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7264366149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9150695800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1980171203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9386405944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1508598327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4906463623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0232849121094</t>
+    <t xml:space="preserve">37.7264404296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9150657653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1980133056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9386444091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1508560180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4906387329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0232810974121</t>
   </si>
   <si>
     <t xml:space="preserve">40.0843353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">40.0607604980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8013877868652</t>
+    <t xml:space="preserve">40.0607566833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8013916015625</t>
   </si>
   <si>
     <t xml:space="preserve">41.2397041320801</t>
@@ -737,91 +737,91 @@
     <t xml:space="preserve">41.0274963378906</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4519233703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7112808227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4990730285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.805606842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.324348449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1828651428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0885581970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2771911621094</t>
+    <t xml:space="preserve">41.4519195556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7112846374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4990768432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8056106567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3243446350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1828689575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0885543823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2771873474121</t>
   </si>
   <si>
     <t xml:space="preserve">41.8291816711426</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9664459228516</t>
+    <t xml:space="preserve">39.9664421081543</t>
   </si>
   <si>
     <t xml:space="preserve">39.5891761779785</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4338073730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9996948242188</t>
+    <t xml:space="preserve">38.4337997436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.9997024536133</t>
   </si>
   <si>
     <t xml:space="preserve">39.6363372802734</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9428596496582</t>
+    <t xml:space="preserve">39.9428672790527</t>
   </si>
   <si>
     <t xml:space="preserve">40.4380226135254</t>
   </si>
   <si>
-    <t xml:space="preserve">38.5517044067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0565414428711</t>
+    <t xml:space="preserve">38.5516967773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0565452575684</t>
   </si>
   <si>
     <t xml:space="preserve">39.1411743164062</t>
   </si>
   <si>
-    <t xml:space="preserve">39.3298149108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0704383850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1647529602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6695976257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.834644317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9053840637207</t>
+    <t xml:space="preserve">39.3298034667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0704345703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1647605895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6696014404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8346481323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.905387878418</t>
   </si>
   <si>
     <t xml:space="preserve">39.0940208435059</t>
   </si>
   <si>
-    <t xml:space="preserve">38.8110733032227</t>
+    <t xml:space="preserve">38.8110694885254</t>
   </si>
   <si>
     <t xml:space="preserve">38.2687530517578</t>
   </si>
   <si>
-    <t xml:space="preserve">38.7403373718262</t>
+    <t xml:space="preserve">38.7403335571289</t>
   </si>
   <si>
     <t xml:space="preserve">38.6931762695312</t>
@@ -830,16 +830,16 @@
     <t xml:space="preserve">39.2354927062988</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2590675354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1357154846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5129776000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7765655517578</t>
+    <t xml:space="preserve">39.2590751647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1357116699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5129699707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7765617370605</t>
   </si>
   <si>
     <t xml:space="preserve">44.8001403808594</t>
@@ -854,19 +854,19 @@
     <t xml:space="preserve">45.8140449523926</t>
   </si>
   <si>
-    <t xml:space="preserve">44.6822509765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7862434387207</t>
+    <t xml:space="preserve">44.682243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7862396240234</t>
   </si>
   <si>
     <t xml:space="preserve">44.7529830932617</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1302490234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.446460723877</t>
+    <t xml:space="preserve">45.130241394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4464530944824</t>
   </si>
   <si>
     <t xml:space="preserve">44.5879364013672</t>
@@ -875,19 +875,19 @@
     <t xml:space="preserve">44.3285598754883</t>
   </si>
   <si>
-    <t xml:space="preserve">44.3049774169922</t>
+    <t xml:space="preserve">44.3049812316895</t>
   </si>
   <si>
     <t xml:space="preserve">43.6211853027344</t>
   </si>
   <si>
-    <t xml:space="preserve">43.1731910705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0788688659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5837135314941</t>
+    <t xml:space="preserve">43.1731834411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0788764953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5837173461914</t>
   </si>
   <si>
     <t xml:space="preserve">43.267505645752</t>
@@ -896,25 +896,25 @@
     <t xml:space="preserve">45.3660354614258</t>
   </si>
   <si>
-    <t xml:space="preserve">44.98876953125</t>
+    <t xml:space="preserve">44.9887771606445</t>
   </si>
   <si>
     <t xml:space="preserve">44.4936141967773</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5171966552734</t>
+    <t xml:space="preserve">44.5171928405762</t>
   </si>
   <si>
     <t xml:space="preserve">45.6254043579102</t>
   </si>
   <si>
-    <t xml:space="preserve">45.8611907958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4035148620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.5824699401855</t>
+    <t xml:space="preserve">45.861198425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4035110473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.582462310791</t>
   </si>
   <si>
     <t xml:space="preserve">47.0637245178223</t>
@@ -923,52 +923,52 @@
     <t xml:space="preserve">47.134464263916</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1580390930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9125709533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3508911132812</t>
+    <t xml:space="preserve">47.1580467224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9125671386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3508987426758</t>
   </si>
   <si>
     <t xml:space="preserve">48.7378349304199</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1012001037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8321533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.6296234130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0540466308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8654136657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9597282409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1858406066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2717247009277</t>
+    <t xml:space="preserve">48.1012077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8321571350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.6296272277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0540428161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8654098510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9597244262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1858367919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2717208862305</t>
   </si>
   <si>
     <t xml:space="preserve">45.0359344482422</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5643501281738</t>
+    <t xml:space="preserve">44.5643463134766</t>
   </si>
   <si>
     <t xml:space="preserve">43.9748764038086</t>
   </si>
   <si>
-    <t xml:space="preserve">42.5601348876953</t>
+    <t xml:space="preserve">42.560131072998</t>
   </si>
   <si>
     <t xml:space="preserve">42.913818359375</t>
@@ -977,37 +977,37 @@
     <t xml:space="preserve">42.7251892089844</t>
   </si>
   <si>
-    <t xml:space="preserve">42.2064514160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4328079223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1781539916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3476715087891</t>
+    <t xml:space="preserve">42.2064476013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4328117370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1781578063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3476753234863</t>
   </si>
   <si>
     <t xml:space="preserve">41.9800872802734</t>
   </si>
   <si>
-    <t xml:space="preserve">41.3010101318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0838432312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.753490447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5931434631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4799690246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0081329345703</t>
+    <t xml:space="preserve">41.3010177612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0838394165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7534790039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.593147277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4799652099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0081367492676</t>
   </si>
   <si>
     <t xml:space="preserve">43.0458641052246</t>
@@ -1019,7 +1019,7 @@
     <t xml:space="preserve">41.3953285217285</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4891510009766</t>
+    <t xml:space="preserve">43.4891471862793</t>
   </si>
   <si>
     <t xml:space="preserve">44.2342414855957</t>
@@ -1028,37 +1028,37 @@
     <t xml:space="preserve">44.1210670471191</t>
   </si>
   <si>
-    <t xml:space="preserve">43.2439270019531</t>
+    <t xml:space="preserve">43.2439231872559</t>
   </si>
   <si>
     <t xml:space="preserve">42.1027030944824</t>
   </si>
   <si>
-    <t xml:space="preserve">41.1689720153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2729721069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4045066833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7626609802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2531127929688</t>
+    <t xml:space="preserve">41.1689796447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2729682922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4045143127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7626647949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2531089782715</t>
   </si>
   <si>
     <t xml:space="preserve">45.0547943115234</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9510459899902</t>
+    <t xml:space="preserve">44.9510498046875</t>
   </si>
   <si>
     <t xml:space="preserve">46.2809028625488</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1488647460938</t>
+    <t xml:space="preserve">46.1488571166992</t>
   </si>
   <si>
     <t xml:space="preserve">45.3094482421875</t>
@@ -1067,58 +1067,58 @@
     <t xml:space="preserve">44.9982032775879</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5358085632324</t>
+    <t xml:space="preserve">45.5358009338379</t>
   </si>
   <si>
     <t xml:space="preserve">45.16796875</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5923957824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6586608886719</t>
+    <t xml:space="preserve">45.5923919677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6586685180664</t>
   </si>
   <si>
     <t xml:space="preserve">43.253360748291</t>
   </si>
   <si>
-    <t xml:space="preserve">43.668342590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2248039245605</t>
+    <t xml:space="preserve">43.6683502197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2248115539551</t>
   </si>
   <si>
     <t xml:space="preserve">45.0830917358398</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2057037353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3280563354492</t>
+    <t xml:space="preserve">45.205696105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3280639648438</t>
   </si>
   <si>
     <t xml:space="preserve">46.0356826782227</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6584129333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5169410705566</t>
+    <t xml:space="preserve">45.6584167480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5169448852539</t>
   </si>
   <si>
     <t xml:space="preserve">44.1682243347168</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8664054870605</t>
+    <t xml:space="preserve">43.8664131164551</t>
   </si>
   <si>
     <t xml:space="preserve">43.5457344055176</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8852767944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4606056213379</t>
+    <t xml:space="preserve">43.8852729797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4605979919434</t>
   </si>
   <si>
     <t xml:space="preserve">45.6112594604492</t>
@@ -1127,103 +1127,103 @@
     <t xml:space="preserve">45.6301231384277</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7244300842285</t>
+    <t xml:space="preserve">45.724437713623</t>
   </si>
   <si>
     <t xml:space="preserve">46.290340423584</t>
   </si>
   <si>
-    <t xml:space="preserve">46.0262451171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2148818969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6487350463867</t>
+    <t xml:space="preserve">46.0262489318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2148857116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.648738861084</t>
   </si>
   <si>
     <t xml:space="preserve">46.7053260803223</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5921440124512</t>
+    <t xml:space="preserve">46.5921516418457</t>
   </si>
   <si>
     <t xml:space="preserve">46.8939590454102</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7710990905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8182601928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1955184936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9972114562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5727844238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3273124694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.317626953125</t>
+    <t xml:space="preserve">47.7711067199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8182640075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1955146789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9972076416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5727882385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3273086547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3176307678223</t>
   </si>
   <si>
     <t xml:space="preserve">50.4119529724121</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8460540771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3744697570801</t>
+    <t xml:space="preserve">49.8460502624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3744735717773</t>
   </si>
   <si>
     <t xml:space="preserve">50.223316192627</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0818405151367</t>
+    <t xml:space="preserve">50.0818367004395</t>
   </si>
   <si>
     <t xml:space="preserve">47.5353088378906</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1960144042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2052001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0068893432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2523612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4223747253418</t>
+    <t xml:space="preserve">46.1960220336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.205207824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0068855285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2523536682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4223823547363</t>
   </si>
   <si>
     <t xml:space="preserve">45.8376159667969</t>
   </si>
   <si>
-    <t xml:space="preserve">45.6489868164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8753471374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5732879638672</t>
+    <t xml:space="preserve">45.6489906311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8753509521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5732841491699</t>
   </si>
   <si>
     <t xml:space="preserve">49.4687881469727</t>
   </si>
   <si>
-    <t xml:space="preserve">48.8085784912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4789657592773</t>
+    <t xml:space="preserve">48.8085708618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4789619445801</t>
   </si>
   <si>
     <t xml:space="preserve">47.3938331604004</t>
@@ -1232,25 +1232,25 @@
     <t xml:space="preserve">46.5166969299316</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1774063110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7812690734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8378677368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4983253479004</t>
+    <t xml:space="preserve">45.1774024963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7812767028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8378715515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4983329772949</t>
   </si>
   <si>
     <t xml:space="preserve">44.1776542663574</t>
   </si>
   <si>
-    <t xml:space="preserve">41.895206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2913360595703</t>
+    <t xml:space="preserve">41.8952026367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.291332244873</t>
   </si>
   <si>
     <t xml:space="preserve">42.4988288879395</t>
@@ -1262,19 +1262,19 @@
     <t xml:space="preserve">41.9517936706543</t>
   </si>
   <si>
-    <t xml:space="preserve">45.328311920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4414901733398</t>
+    <t xml:space="preserve">45.3283157348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4414939880371</t>
   </si>
   <si>
     <t xml:space="preserve">45.4603500366211</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4037666320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1017036437988</t>
+    <t xml:space="preserve">45.4037590026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1016998291016</t>
   </si>
   <si>
     <t xml:space="preserve">45.9885177612305</t>
@@ -1283,10 +1283,10 @@
     <t xml:space="preserve">46.384651184082</t>
   </si>
   <si>
-    <t xml:space="preserve">49.0443649291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.902889251709</t>
+    <t xml:space="preserve">49.0443687438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9028854370117</t>
   </si>
   <si>
     <t xml:space="preserve">48.2898368835449</t>
@@ -1295,28 +1295,28 @@
     <t xml:space="preserve">51.1193199157715</t>
   </si>
   <si>
-    <t xml:space="preserve">50.694896697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.932861328125</t>
+    <t xml:space="preserve">50.6949005126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6005821228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.9328575134277</t>
   </si>
   <si>
     <t xml:space="preserve">50.4107093811035</t>
   </si>
   <si>
-    <t xml:space="preserve">51.0277900695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.2144889831543</t>
+    <t xml:space="preserve">51.0277938842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.214485168457</t>
   </si>
   <si>
     <t xml:space="preserve">52.1195526123047</t>
   </si>
   <si>
-    <t xml:space="preserve">51.7398109436035</t>
+    <t xml:space="preserve">51.7398071289062</t>
   </si>
   <si>
     <t xml:space="preserve">49.8410987854004</t>
@@ -1331,43 +1331,43 @@
     <t xml:space="preserve">49.3664207458496</t>
   </si>
   <si>
-    <t xml:space="preserve">49.081615447998</t>
+    <t xml:space="preserve">49.0816192626953</t>
   </si>
   <si>
     <t xml:space="preserve">49.7936325073242</t>
   </si>
   <si>
-    <t xml:space="preserve">48.2746620178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.8221549987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0847930908203</t>
+    <t xml:space="preserve">48.274658203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.822151184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0848007202148</t>
   </si>
   <si>
     <t xml:space="preserve">48.6544075012207</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3189582824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6512260437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9835014343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3632469177246</t>
+    <t xml:space="preserve">49.3189544677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6512222290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9835052490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3632431030273</t>
   </si>
   <si>
     <t xml:space="preserve">51.2176628112793</t>
   </si>
   <si>
-    <t xml:space="preserve">50.1733741760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.4550018310547</t>
+    <t xml:space="preserve">50.1733703613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.455005645752</t>
   </si>
   <si>
     <t xml:space="preserve">52.0246086120605</t>
@@ -1376,25 +1376,25 @@
     <t xml:space="preserve">53.068904876709</t>
   </si>
   <si>
-    <t xml:space="preserve">52.7840995788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4422912597656</t>
+    <t xml:space="preserve">52.7840957641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4422950744629</t>
   </si>
   <si>
     <t xml:space="preserve">54.682804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1100158691406</t>
+    <t xml:space="preserve">55.1100120544434</t>
   </si>
   <si>
     <t xml:space="preserve">55.5846900939941</t>
   </si>
   <si>
-    <t xml:space="preserve">56.3916511535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.7302703857422</t>
+    <t xml:space="preserve">56.3916473388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.7302742004395</t>
   </si>
   <si>
     <t xml:space="preserve">55.0625495910645</t>
@@ -1403,22 +1403,22 @@
     <t xml:space="preserve">55.4897575378418</t>
   </si>
   <si>
-    <t xml:space="preserve">55.2524185180664</t>
+    <t xml:space="preserve">55.2524147033691</t>
   </si>
   <si>
     <t xml:space="preserve">53.1638412475586</t>
   </si>
   <si>
-    <t xml:space="preserve">53.6385154724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0182609558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3030624389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1131935119629</t>
+    <t xml:space="preserve">53.6385116577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0182571411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3030662536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1131973266602</t>
   </si>
   <si>
     <t xml:space="preserve">53.8283882141113</t>
@@ -1430,61 +1430,61 @@
     <t xml:space="preserve">56.4391098022461</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9137840270996</t>
+    <t xml:space="preserve">56.9137916564941</t>
   </si>
   <si>
     <t xml:space="preserve">56.2967071533203</t>
   </si>
   <si>
-    <t xml:space="preserve">56.0118980407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2017707824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5340461730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6764526367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.9676132202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5942268371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0214347839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1574821472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3505325317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9264984130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.8790283203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.065731048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5878677368164</t>
+    <t xml:space="preserve">56.0119018554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.201774597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5340423583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6764488220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.9676094055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5942306518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.021427154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1574859619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.350528717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9265022277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.8790321350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0657272338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5878715515137</t>
   </si>
   <si>
     <t xml:space="preserve">53.4486427307129</t>
   </si>
   <si>
-    <t xml:space="preserve">53.6859817504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3062438964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.4043502807617</t>
+    <t xml:space="preserve">53.6859855651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3062400817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.4043579101562</t>
   </si>
   <si>
     <t xml:space="preserve">51.0752563476562</t>
@@ -1493,43 +1493,43 @@
     <t xml:space="preserve">50.4581832885742</t>
   </si>
   <si>
-    <t xml:space="preserve">52.2619476318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.8822174072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.1606636047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.2081260681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5435791015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5404014587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2049446105957</t>
+    <t xml:space="preserve">52.2619514465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.882209777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.1606597900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.2081298828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.543586730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.540397644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.2049522399902</t>
   </si>
   <si>
     <t xml:space="preserve">56.2492370605469</t>
   </si>
   <si>
-    <t xml:space="preserve">57.1036567687988</t>
+    <t xml:space="preserve">57.1036605834961</t>
   </si>
   <si>
     <t xml:space="preserve">57.2460594177246</t>
   </si>
   <si>
-    <t xml:space="preserve">57.9106140136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9612579345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.790454864502</t>
+    <t xml:space="preserve">57.9106101989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.961254119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.7904510498047</t>
   </si>
   <si>
     <t xml:space="preserve">49.413890838623</t>
@@ -1541,22 +1541,22 @@
     <t xml:space="preserve">47.0499992370605</t>
   </si>
   <si>
-    <t xml:space="preserve">48.2271957397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.4677085876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0309677124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3157730102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3474769592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7525634765625</t>
+    <t xml:space="preserve">48.2271919250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.467716217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0309715270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.3157768249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3474731445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.7525596618652</t>
   </si>
   <si>
     <t xml:space="preserve">44.6766166687012</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">46.1955795288086</t>
   </si>
   <si>
-    <t xml:space="preserve">46.556339263916</t>
+    <t xml:space="preserve">46.5563354492188</t>
   </si>
   <si>
     <t xml:space="preserve">46.4803848266602</t>
@@ -1577,136 +1577,136 @@
     <t xml:space="preserve">45.9487457275391</t>
   </si>
   <si>
-    <t xml:space="preserve">47.4107513427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5373458862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5183563232422</t>
+    <t xml:space="preserve">47.4107475280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5373497009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5183601379395</t>
   </si>
   <si>
     <t xml:space="preserve">46.7462043762207</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4424057006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4930534362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1323013305664</t>
+    <t xml:space="preserve">46.4424095153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4930572509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1323051452637</t>
   </si>
   <si>
     <t xml:space="preserve">45.5690078735352</t>
   </si>
   <si>
-    <t xml:space="preserve">45.7019157409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3601913452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.4677963256836</t>
+    <t xml:space="preserve">45.7019081115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3601875305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4678001403809</t>
   </si>
   <si>
     <t xml:space="preserve">41.9234848022461</t>
   </si>
   <si>
-    <t xml:space="preserve">42.8728370666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7462425231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2968673706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8601684570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7209014892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7841758728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7050514221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2398643493652</t>
+    <t xml:space="preserve">42.8728408813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7462463378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2968635559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8601722717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7208976745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7841796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7050476074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2398681640625</t>
   </si>
   <si>
     <t xml:space="preserve">46.2905082702637</t>
   </si>
   <si>
-    <t xml:space="preserve">45.1892547607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.208251953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2841949462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3158187866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3727760314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6132965087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4867401123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5373878479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5183982849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.075382232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5627288818359</t>
+    <t xml:space="preserve">45.1892585754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2082481384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2842025756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3158149719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3727798461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6132888793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4867362976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5373916625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5183944702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.0753784179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5627326965332</t>
   </si>
   <si>
     <t xml:space="preserve">40.2146453857422</t>
   </si>
   <si>
-    <t xml:space="preserve">41.8475341796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4551239013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2526245117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8095626831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1956176757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0310516357422</t>
+    <t xml:space="preserve">41.8475379943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4551277160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2526206970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8095588684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.195613861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0310478210449</t>
   </si>
   <si>
     <t xml:space="preserve">44.3158569335938</t>
   </si>
   <si>
-    <t xml:space="preserve">44.334846496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8791542053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7398872375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8348236083984</t>
+    <t xml:space="preserve">44.3348426818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8791580200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7398910522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8348197937012</t>
   </si>
   <si>
     <t xml:space="preserve">46.8031616210938</t>
@@ -1718,22 +1718,22 @@
     <t xml:space="preserve">46.4234237670898</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1829071044922</t>
+    <t xml:space="preserve">47.1829109191895</t>
   </si>
   <si>
     <t xml:space="preserve">49.1765480041504</t>
   </si>
   <si>
-    <t xml:space="preserve">48.3695983886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4360961914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0753326416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6449584960938</t>
+    <t xml:space="preserve">48.3696022033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.436092376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0753364562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6449546813965</t>
   </si>
   <si>
     <t xml:space="preserve">47.2588539123535</t>
@@ -1745,34 +1745,34 @@
     <t xml:space="preserve">49.8885688781738</t>
   </si>
   <si>
-    <t xml:space="preserve">50.1259002685547</t>
+    <t xml:space="preserve">50.125904083252</t>
   </si>
   <si>
     <t xml:space="preserve">50.6955184936523</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2208442687988</t>
+    <t xml:space="preserve">50.2208366394043</t>
   </si>
   <si>
     <t xml:space="preserve">49.9360313415527</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0784339904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1670188903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.6891670227051</t>
+    <t xml:space="preserve">50.0784378051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1670150756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.6891632080078</t>
   </si>
   <si>
     <t xml:space="preserve">52.9739646911621</t>
   </si>
   <si>
-    <t xml:space="preserve">54.2555999755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.2587738037109</t>
+    <t xml:space="preserve">54.2555961608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.2587776184082</t>
   </si>
   <si>
     <t xml:space="preserve">53.9707870483398</t>
@@ -1784,19 +1784,19 @@
     <t xml:space="preserve">55.2998847961426</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3980026245117</t>
+    <t xml:space="preserve">54.3979988098145</t>
   </si>
   <si>
     <t xml:space="preserve">53.4011764526367</t>
   </si>
   <si>
-    <t xml:space="preserve">53.9233207702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4929351806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4454650878906</t>
+    <t xml:space="preserve">53.9233131408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4929389953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4454612731934</t>
   </si>
   <si>
     <t xml:space="preserve">53.4961090087891</t>
@@ -1805,22 +1805,22 @@
     <t xml:space="preserve">54.6353378295898</t>
   </si>
   <si>
-    <t xml:space="preserve">55.9644317626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.7270965576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.1068344116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5328559875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5239105224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5717430114746</t>
+    <t xml:space="preserve">55.9644355773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.7270927429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.1068382263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5328483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5239143371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5717468261719</t>
   </si>
   <si>
     <t xml:space="preserve">52.6151084899902</t>
@@ -1832,10 +1832,10 @@
     <t xml:space="preserve">51.4671363830566</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5283851623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.9633407592773</t>
+    <t xml:space="preserve">54.5283889770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.9633369445801</t>
   </si>
   <si>
     <t xml:space="preserve">56.0590019226074</t>
@@ -1847,67 +1847,67 @@
     <t xml:space="preserve">56.7764854431152</t>
   </si>
   <si>
-    <t xml:space="preserve">56.011173248291</t>
+    <t xml:space="preserve">56.0111694335938</t>
   </si>
   <si>
     <t xml:space="preserve">55.6285171508789</t>
   </si>
   <si>
-    <t xml:space="preserve">56.2024993896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.9155120849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4416618347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.580680847168</t>
+    <t xml:space="preserve">56.2025032043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.9155082702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4416580200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5806884765625</t>
   </si>
   <si>
     <t xml:space="preserve">56.3459968566895</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1501960754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.5762176513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4327239990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.8632049560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.9199829101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.8243141174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.2547988891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6808128356934</t>
+    <t xml:space="preserve">55.1501998901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5762138366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4327201843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8632011413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.919979095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.8243179321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.2548027038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6808166503906</t>
   </si>
   <si>
     <t xml:space="preserve">56.7286491394043</t>
   </si>
   <si>
-    <t xml:space="preserve">58.2114448547363</t>
+    <t xml:space="preserve">58.2114410400391</t>
   </si>
   <si>
     <t xml:space="preserve">57.6374549865723</t>
   </si>
   <si>
-    <t xml:space="preserve">58.5462608337402</t>
+    <t xml:space="preserve">58.546257019043</t>
   </si>
   <si>
     <t xml:space="preserve">57.924446105957</t>
   </si>
   <si>
-    <t xml:space="preserve">58.3549385070801</t>
+    <t xml:space="preserve">58.3549346923828</t>
   </si>
   <si>
     <t xml:space="preserve">57.7331199645996</t>
@@ -1928,25 +1928,25 @@
     <t xml:space="preserve">59.7420616149902</t>
   </si>
   <si>
-    <t xml:space="preserve">59.2159156799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.120246887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3026390075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.828784942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.1157722473145</t>
+    <t xml:space="preserve">59.2159080505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.1202430725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3026351928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.8287887573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.115779876709</t>
   </si>
   <si>
     <t xml:space="preserve">57.7809562683105</t>
   </si>
   <si>
-    <t xml:space="preserve">59.0245780944824</t>
+    <t xml:space="preserve">59.024585723877</t>
   </si>
   <si>
     <t xml:space="preserve">59.4550704956055</t>
@@ -1958,13 +1958,13 @@
     <t xml:space="preserve">60.0290489196777</t>
   </si>
   <si>
-    <t xml:space="preserve">59.0724143981934</t>
+    <t xml:space="preserve">59.0724105834961</t>
   </si>
   <si>
     <t xml:space="preserve">58.2592735290527</t>
   </si>
   <si>
-    <t xml:space="preserve">58.0201148986816</t>
+    <t xml:space="preserve">58.0201110839844</t>
   </si>
   <si>
     <t xml:space="preserve">50.9888191223145</t>
@@ -1979,16 +1979,16 @@
     <t xml:space="preserve">51.3236465454102</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8931579589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7930183410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8408546447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6928901672363</t>
+    <t xml:space="preserve">50.8931541442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.793025970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8408508300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6928863525391</t>
   </si>
   <si>
     <t xml:space="preserve">49.2668724060059</t>
@@ -1997,37 +1997,37 @@
     <t xml:space="preserve">49.9843521118164</t>
   </si>
   <si>
-    <t xml:space="preserve">49.9365158081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.080005645752</t>
+    <t xml:space="preserve">49.9365196228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0800132751465</t>
   </si>
   <si>
     <t xml:space="preserve">50.6539993286133</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2235069274902</t>
+    <t xml:space="preserve">50.2235107421875</t>
   </si>
   <si>
     <t xml:space="preserve">50.845329284668</t>
   </si>
   <si>
-    <t xml:space="preserve">51.4193077087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.9409866333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5149688720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.7974891662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.13232421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6973648071289</t>
+    <t xml:space="preserve">51.4193115234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.940990447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.514965057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.797492980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.1323204040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6973609924316</t>
   </si>
   <si>
     <t xml:space="preserve">49.3147048950195</t>
@@ -2036,37 +2036,37 @@
     <t xml:space="preserve">49.4582023620605</t>
   </si>
   <si>
-    <t xml:space="preserve">49.7451934814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0321807861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8363838195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.597225189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3625335693359</t>
+    <t xml:space="preserve">49.745189666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0321769714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8363876342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5972213745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3625373840332</t>
   </si>
   <si>
     <t xml:space="preserve">54.0022315979004</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4282455444336</t>
+    <t xml:space="preserve">53.4282417297363</t>
   </si>
   <si>
     <t xml:space="preserve">54.2892227172852</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1935577392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.0934219360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.4716110229492</t>
+    <t xml:space="preserve">54.1935615539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0934257507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.471607208252</t>
   </si>
   <si>
     <t xml:space="preserve">53.2847518920898</t>
@@ -2078,13 +2078,13 @@
     <t xml:space="preserve">54.9110412597656</t>
   </si>
   <si>
-    <t xml:space="preserve">54.3370513916016</t>
+    <t xml:space="preserve">54.3370475769043</t>
   </si>
   <si>
     <t xml:space="preserve">53.8587341308594</t>
   </si>
   <si>
-    <t xml:space="preserve">54.4805488586426</t>
+    <t xml:space="preserve">54.4805526733398</t>
   </si>
   <si>
     <t xml:space="preserve">55.0545349121094</t>
@@ -2093,31 +2093,31 @@
     <t xml:space="preserve">55.3415260314941</t>
   </si>
   <si>
-    <t xml:space="preserve">55.86767578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.5373153686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6329917907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.4027633666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.0679473876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6942291259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.3115730285645</t>
+    <t xml:space="preserve">55.8676834106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.5373229980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6329879760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.4027709960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.067943572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6942329406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.3115768432617</t>
   </si>
   <si>
     <t xml:space="preserve">62.8511352539062</t>
   </si>
   <si>
-    <t xml:space="preserve">63.6164436340332</t>
+    <t xml:space="preserve">63.6164474487305</t>
   </si>
   <si>
     <t xml:space="preserve">65.3383941650391</t>
@@ -2126,25 +2126,25 @@
     <t xml:space="preserve">66.3428649902344</t>
   </si>
   <si>
-    <t xml:space="preserve">66.9646835327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.9213104248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.2606201171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.0692749023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.3951721191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.016975402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.8690185546875</t>
+    <t xml:space="preserve">66.9646759033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.9213256835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.260612487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.0692825317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.3951644897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.0169830322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.869026184082</t>
   </si>
   <si>
     <t xml:space="preserve">67.2994995117188</t>
@@ -2159,40 +2159,40 @@
     <t xml:space="preserve">69.212776184082</t>
   </si>
   <si>
-    <t xml:space="preserve">68.4474639892578</t>
+    <t xml:space="preserve">68.4474716186523</t>
   </si>
   <si>
     <t xml:space="preserve">67.8734817504883</t>
   </si>
   <si>
-    <t xml:space="preserve">67.7778091430664</t>
+    <t xml:space="preserve">67.7778167724609</t>
   </si>
   <si>
     <t xml:space="preserve">67.0603408813477</t>
   </si>
   <si>
-    <t xml:space="preserve">66.0080490112305</t>
+    <t xml:space="preserve">66.0080413818359</t>
   </si>
   <si>
     <t xml:space="preserve">66.4385223388672</t>
   </si>
   <si>
-    <t xml:space="preserve">65.5775451660156</t>
+    <t xml:space="preserve">65.5775527954102</t>
   </si>
   <si>
     <t xml:space="preserve">65.9123764038086</t>
   </si>
   <si>
-    <t xml:space="preserve">67.2516708374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.8256607055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.6343154907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.7688827514648</t>
+    <t xml:space="preserve">67.2516632080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.8256454467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.6343231201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.7688751220703</t>
   </si>
   <si>
     <t xml:space="preserve">66.1036987304688</t>
@@ -2201,31 +2201,31 @@
     <t xml:space="preserve">69.4519424438477</t>
   </si>
   <si>
-    <t xml:space="preserve">68.2083053588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.3129196166992</t>
+    <t xml:space="preserve">68.2083129882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.3129119873047</t>
   </si>
   <si>
     <t xml:space="preserve">73.3263244628906</t>
   </si>
   <si>
-    <t xml:space="preserve">73.2306594848633</t>
+    <t xml:space="preserve">73.2306671142578</t>
   </si>
   <si>
     <t xml:space="preserve">74.0916290283203</t>
   </si>
   <si>
-    <t xml:space="preserve">73.6611404418945</t>
+    <t xml:space="preserve">73.6611557006836</t>
   </si>
   <si>
     <t xml:space="preserve">73.374153137207</t>
   </si>
   <si>
-    <t xml:space="preserve">70.6955795288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.7912216186523</t>
+    <t xml:space="preserve">70.6955718994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.7912368774414</t>
   </si>
   <si>
     <t xml:space="preserve">72.4653472900391</t>
@@ -2234,43 +2234,43 @@
     <t xml:space="preserve">70.2650756835938</t>
   </si>
   <si>
-    <t xml:space="preserve">68.6387939453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.3173828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9391860961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.7045059204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.7523498535156</t>
+    <t xml:space="preserve">68.638801574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.3173904418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9392013549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.7045135498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.7523345947266</t>
   </si>
   <si>
     <t xml:space="preserve">72.6088485717773</t>
   </si>
   <si>
-    <t xml:space="preserve">74.4264678955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.1394729614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.7478713989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.9870300292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.2784881591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.4130477905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.8211822509766</t>
+    <t xml:space="preserve">74.4264602661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.1394653320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.7478637695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.9870376586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.2784957885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.4130554199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.821174621582</t>
   </si>
   <si>
     <t xml:space="preserve">65.7210464477539</t>
@@ -2279,13 +2279,13 @@
     <t xml:space="preserve">62.1336517333984</t>
   </si>
   <si>
-    <t xml:space="preserve">63.8077774047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8944931030273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9378547668457</t>
+    <t xml:space="preserve">63.8077621459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8945007324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.9378623962402</t>
   </si>
   <si>
     <t xml:space="preserve">57.8766174316406</t>
@@ -2306,13 +2306,13 @@
     <t xml:space="preserve">45.4594535827637</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7094268798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8714332580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2107200622559</t>
+    <t xml:space="preserve">41.7094306945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8714370727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2107238769531</t>
   </si>
   <si>
     <t xml:space="preserve">45.344654083252</t>
@@ -2324,22 +2324,22 @@
     <t xml:space="preserve">51.0844841003418</t>
   </si>
   <si>
-    <t xml:space="preserve">49.2190437316895</t>
+    <t xml:space="preserve">49.2190399169922</t>
   </si>
   <si>
     <t xml:space="preserve">59.1680793762207</t>
   </si>
   <si>
-    <t xml:space="preserve">57.6852836608887</t>
+    <t xml:space="preserve">57.6852874755859</t>
   </si>
   <si>
     <t xml:space="preserve">59.263744354248</t>
   </si>
   <si>
-    <t xml:space="preserve">61.0813522338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.3638763427734</t>
+    <t xml:space="preserve">61.0813484191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.3638725280762</t>
   </si>
   <si>
     <t xml:space="preserve">61.1291885375977</t>
@@ -2348,16 +2348,16 @@
     <t xml:space="preserve">61.4161720275879</t>
   </si>
   <si>
-    <t xml:space="preserve">62.6598129272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.5207748413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.564136505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.138126373291</t>
+    <t xml:space="preserve">62.6598167419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.5207901000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.5641403198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.1381187438965</t>
   </si>
   <si>
     <t xml:space="preserve">63.0424690246582</t>
@@ -2369,7 +2369,7 @@
     <t xml:space="preserve">61.0335273742676</t>
   </si>
   <si>
-    <t xml:space="preserve">59.2684936523438</t>
+    <t xml:space="preserve">59.2684898376465</t>
   </si>
   <si>
     <t xml:space="preserve">60.9081382751465</t>
@@ -2378,13 +2378,13 @@
     <t xml:space="preserve">61.7279624938965</t>
   </si>
   <si>
-    <t xml:space="preserve">63.705192565918</t>
+    <t xml:space="preserve">63.7051887512207</t>
   </si>
   <si>
     <t xml:space="preserve">64.717903137207</t>
   </si>
   <si>
-    <t xml:space="preserve">63.367603302002</t>
+    <t xml:space="preserve">63.3676109313965</t>
   </si>
   <si>
     <t xml:space="preserve">63.6569557189941</t>
@@ -2399,16 +2399,16 @@
     <t xml:space="preserve">64.9108123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">68.4312362670898</t>
+    <t xml:space="preserve">68.4312286376953</t>
   </si>
   <si>
     <t xml:space="preserve">68.0936584472656</t>
   </si>
   <si>
-    <t xml:space="preserve">68.3830108642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.6241302490234</t>
+    <t xml:space="preserve">68.3830032348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.624137878418</t>
   </si>
   <si>
     <t xml:space="preserve">69.9744338989258</t>
@@ -2426,34 +2426,34 @@
     <t xml:space="preserve">74.3628997802734</t>
   </si>
   <si>
-    <t xml:space="preserve">75.8578720092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.6522598266602</t>
+    <t xml:space="preserve">75.8578872680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.6522521972656</t>
   </si>
   <si>
     <t xml:space="preserve">71.8552093505859</t>
   </si>
   <si>
-    <t xml:space="preserve">70.6013488769531</t>
+    <t xml:space="preserve">70.6013565063477</t>
   </si>
   <si>
     <t xml:space="preserve">71.1318283081055</t>
   </si>
   <si>
-    <t xml:space="preserve">70.2155532836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.9235382080078</t>
+    <t xml:space="preserve">70.2155609130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.9235305786133</t>
   </si>
   <si>
     <t xml:space="preserve">67.03271484375</t>
   </si>
   <si>
-    <t xml:space="preserve">67.2256011962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.8625946044922</t>
+    <t xml:space="preserve">67.2256088256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.8625869750977</t>
   </si>
   <si>
     <t xml:space="preserve">66.5504608154297</t>
@@ -2462,10 +2462,10 @@
     <t xml:space="preserve">67.3220596313477</t>
   </si>
   <si>
-    <t xml:space="preserve">69.9262161254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.180061340332</t>
+    <t xml:space="preserve">69.9262084960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.1800537109375</t>
   </si>
   <si>
     <t xml:space="preserve">70.4084548950195</t>
@@ -2480,19 +2480,19 @@
     <t xml:space="preserve">70.31201171875</t>
   </si>
   <si>
-    <t xml:space="preserve">68.5276947021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.2865600585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.6723480224609</t>
+    <t xml:space="preserve">68.5276870727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.2865676879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.6723556518555</t>
   </si>
   <si>
     <t xml:space="preserve">69.0099334716797</t>
   </si>
   <si>
-    <t xml:space="preserve">69.2992706298828</t>
+    <t xml:space="preserve">69.2992782592773</t>
   </si>
   <si>
     <t xml:space="preserve">72.1445617675781</t>
@@ -2513,10 +2513,10 @@
     <t xml:space="preserve">70.3602294921875</t>
   </si>
   <si>
-    <t xml:space="preserve">71.6623001098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.3374481201172</t>
+    <t xml:space="preserve">71.6623077392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.3374557495117</t>
   </si>
   <si>
     <t xml:space="preserve">72.8679351806641</t>
@@ -2525,13 +2525,13 @@
     <t xml:space="preserve">73.4466323852539</t>
   </si>
   <si>
-    <t xml:space="preserve">73.543083190918</t>
+    <t xml:space="preserve">73.5430755615234</t>
   </si>
   <si>
     <t xml:space="preserve">71.999885559082</t>
   </si>
   <si>
-    <t xml:space="preserve">73.0608215332031</t>
+    <t xml:space="preserve">73.0608291625977</t>
   </si>
   <si>
     <t xml:space="preserve">73.6877593994141</t>
@@ -2549,22 +2549,22 @@
     <t xml:space="preserve">81.9342193603516</t>
   </si>
   <si>
-    <t xml:space="preserve">82.9469451904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.117073059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86.0815658569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3581924438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1398468017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.017936706543</t>
+    <t xml:space="preserve">82.9469528198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1170654296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.0815734863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3582000732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1398544311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.017951965332</t>
   </si>
   <si>
     <t xml:space="preserve">81.0661773681641</t>
@@ -2573,25 +2573,25 @@
     <t xml:space="preserve">82.609375</t>
   </si>
   <si>
-    <t xml:space="preserve">80.8732833862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.0916213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.3099670410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.5865936279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.6348190307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.6703262329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.7794952392578</t>
+    <t xml:space="preserve">80.8732757568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.0916137695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.3099594116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.5865859985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.6348266601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.6703186035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.7795028686523</t>
   </si>
   <si>
     <t xml:space="preserve">84.6830444335938</t>
@@ -2603,10 +2603,10 @@
     <t xml:space="preserve">86.2262496948242</t>
   </si>
   <si>
-    <t xml:space="preserve">87.7212142944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.6984329223633</t>
+    <t xml:space="preserve">87.7212219238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.6984405517578</t>
   </si>
   <si>
     <t xml:space="preserve">89.3126449584961</t>
@@ -2621,19 +2621,19 @@
     <t xml:space="preserve">87.8658981323242</t>
   </si>
   <si>
-    <t xml:space="preserve">91.2416381835938</t>
+    <t xml:space="preserve">91.2416458129883</t>
   </si>
   <si>
     <t xml:space="preserve">90.2771453857422</t>
   </si>
   <si>
-    <t xml:space="preserve">90.5664901733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9777450561523</t>
+    <t xml:space="preserve">90.5664978027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8076095581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9777374267578</t>
   </si>
   <si>
     <t xml:space="preserve">95.0031890869141</t>
@@ -2645,31 +2645,31 @@
     <t xml:space="preserve">95.7265625</t>
   </si>
   <si>
-    <t xml:space="preserve">93.218864440918</t>
+    <t xml:space="preserve">93.218879699707</t>
   </si>
   <si>
     <t xml:space="preserve">93.5082092285156</t>
   </si>
   <si>
-    <t xml:space="preserve">91.4827728271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.9395599365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6274337768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.1096878051758</t>
+    <t xml:space="preserve">91.4827651977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.939567565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.62744140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.1096954345703</t>
   </si>
   <si>
     <t xml:space="preserve">93.3635406494141</t>
   </si>
   <si>
-    <t xml:space="preserve">95.5336608886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.9549560546875</t>
+    <t xml:space="preserve">95.5336685180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.954963684082</t>
   </si>
   <si>
     <t xml:space="preserve">94.8102951049805</t>
@@ -2681,7 +2681,7 @@
     <t xml:space="preserve">94.5209503173828</t>
   </si>
   <si>
-    <t xml:space="preserve">92.6883926391602</t>
+    <t xml:space="preserve">92.6884002685547</t>
   </si>
   <si>
     <t xml:space="preserve">91.4345397949219</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">95.2925491333008</t>
   </si>
   <si>
-    <t xml:space="preserve">97.2215423583984</t>
+    <t xml:space="preserve">97.2215347290039</t>
   </si>
   <si>
     <t xml:space="preserve">100.115036010742</t>
@@ -2702,31 +2702,31 @@
     <t xml:space="preserve">99.7292404174805</t>
   </si>
   <si>
-    <t xml:space="preserve">97.6073379516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.8966979980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3789367675781</t>
+    <t xml:space="preserve">97.6073455810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.8966827392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3789443969727</t>
   </si>
   <si>
     <t xml:space="preserve">96.3052597045898</t>
   </si>
   <si>
-    <t xml:space="preserve">93.7493515014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.8330688476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.8813018798828</t>
+    <t xml:space="preserve">93.7493362426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.8330612182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.8812942504883</t>
   </si>
   <si>
     <t xml:space="preserve">88.4445953369141</t>
   </si>
   <si>
-    <t xml:space="preserve">88.2034606933594</t>
+    <t xml:space="preserve">88.2034530639648</t>
   </si>
   <si>
     <t xml:space="preserve">89.0233001708984</t>
@@ -2744,10 +2744,10 @@
     <t xml:space="preserve">95.4372100830078</t>
   </si>
   <si>
-    <t xml:space="preserve">95.774787902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4472732543945</t>
+    <t xml:space="preserve">95.7747955322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4472579956055</t>
   </si>
   <si>
     <t xml:space="preserve">92.0614624023438</t>
@@ -2756,10 +2756,10 @@
     <t xml:space="preserve">91.8685607910156</t>
   </si>
   <si>
-    <t xml:space="preserve">91.8203353881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.7111740112305</t>
+    <t xml:space="preserve">91.8203430175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.711181640625</t>
   </si>
   <si>
     <t xml:space="preserve">90.855842590332</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">91.3863220214844</t>
   </si>
   <si>
-    <t xml:space="preserve">90.759391784668</t>
+    <t xml:space="preserve">90.7593994140625</t>
   </si>
   <si>
     <t xml:space="preserve">87.7694396972656</t>
@@ -2777,7 +2777,7 @@
     <t xml:space="preserve">88.2516937255859</t>
   </si>
   <si>
-    <t xml:space="preserve">89.3608703613281</t>
+    <t xml:space="preserve">89.3608779907227</t>
   </si>
   <si>
     <t xml:space="preserve">90.3735885620117</t>
@@ -2786,61 +2786,61 @@
     <t xml:space="preserve">94.2798156738281</t>
   </si>
   <si>
-    <t xml:space="preserve">90.0842514038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.1451950073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.4954833984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.4573211669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.6756744384766</t>
+    <t xml:space="preserve">90.0842437744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.1451873779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.4954986572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.4573287963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.675666809082</t>
   </si>
   <si>
     <t xml:space="preserve">91.9167938232422</t>
   </si>
   <si>
-    <t xml:space="preserve">91.7238998413086</t>
+    <t xml:space="preserve">91.7238845825195</t>
   </si>
   <si>
     <t xml:space="preserve">91.0969619750977</t>
   </si>
   <si>
-    <t xml:space="preserve">90.9040756225586</t>
+    <t xml:space="preserve">90.9040679931641</t>
   </si>
   <si>
     <t xml:space="preserve">92.3508224487305</t>
   </si>
   <si>
-    <t xml:space="preserve">93.4599914550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.5437088012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.9194717407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.2670822143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5564498901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.5691757202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.0641403198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.4753875732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.018585205078</t>
+    <t xml:space="preserve">93.4599838256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.5437164306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9194641113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.26708984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5564422607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.5691680908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.0641326904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.4753952026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.018577575684</t>
   </si>
   <si>
     <t xml:space="preserve">98.1860427856445</t>
@@ -2849,16 +2849,16 @@
     <t xml:space="preserve">97.4144439697266</t>
   </si>
   <si>
-    <t xml:space="preserve">100.790184020996</t>
+    <t xml:space="preserve">100.790191650391</t>
   </si>
   <si>
     <t xml:space="preserve">102.912078857422</t>
   </si>
   <si>
-    <t xml:space="preserve">101.46533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.719177246094</t>
+    <t xml:space="preserve">101.465339660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.719184875488</t>
   </si>
   <si>
     <t xml:space="preserve">102.526290893555</t>
@@ -2867,25 +2867,25 @@
     <t xml:space="preserve">102.140487670898</t>
   </si>
   <si>
-    <t xml:space="preserve">104.937530517578</t>
+    <t xml:space="preserve">104.937538146973</t>
   </si>
   <si>
     <t xml:space="preserve">103.104995727539</t>
   </si>
   <si>
-    <t xml:space="preserve">103.58723449707</t>
+    <t xml:space="preserve">103.587242126465</t>
   </si>
   <si>
     <t xml:space="preserve">102.815635681152</t>
   </si>
   <si>
-    <t xml:space="preserve">103.201438903809</t>
+    <t xml:space="preserve">103.201431274414</t>
   </si>
   <si>
     <t xml:space="preserve">100.500831604004</t>
   </si>
   <si>
-    <t xml:space="preserve">100.404388427734</t>
+    <t xml:space="preserve">100.404396057129</t>
   </si>
   <si>
     <t xml:space="preserve">98.5718307495117</t>
@@ -2900,28 +2900,28 @@
     <t xml:space="preserve">92.5919418334961</t>
   </si>
   <si>
-    <t xml:space="preserve">89.2162017822266</t>
+    <t xml:space="preserve">89.216194152832</t>
   </si>
   <si>
     <t xml:space="preserve">103.297889709473</t>
   </si>
   <si>
-    <t xml:space="preserve">99.3434371948242</t>
+    <t xml:space="preserve">99.3434448242188</t>
   </si>
   <si>
     <t xml:space="preserve">101.561790466309</t>
   </si>
   <si>
-    <t xml:space="preserve">103.973045349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.780136108398</t>
+    <t xml:space="preserve">103.973037719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.780128479004</t>
   </si>
   <si>
     <t xml:space="preserve">105.323333740234</t>
   </si>
   <si>
-    <t xml:space="preserve">103.490783691406</t>
+    <t xml:space="preserve">103.490791320801</t>
   </si>
   <si>
     <t xml:space="preserve">104.069488525391</t>
@@ -2930,37 +2930,37 @@
     <t xml:space="preserve">108.023933410645</t>
   </si>
   <si>
-    <t xml:space="preserve">110.145820617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.699081420898</t>
+    <t xml:space="preserve">110.145835876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.699073791504</t>
   </si>
   <si>
     <t xml:space="preserve">106.287826538086</t>
   </si>
   <si>
-    <t xml:space="preserve">107.445236206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.384284973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.891990661621</t>
+    <t xml:space="preserve">107.44522857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.38427734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.891983032227</t>
   </si>
   <si>
     <t xml:space="preserve">107.831039428711</t>
   </si>
   <si>
-    <t xml:space="preserve">108.795532226562</t>
+    <t xml:space="preserve">108.795547485352</t>
   </si>
   <si>
     <t xml:space="preserve">109.084884643555</t>
   </si>
   <si>
-    <t xml:space="preserve">107.059425354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.348777770996</t>
+    <t xml:space="preserve">107.059432983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.348793029785</t>
   </si>
   <si>
     <t xml:space="preserve">109.567123413086</t>
@@ -2981,16 +2981,16 @@
     <t xml:space="preserve">109.046104431152</t>
   </si>
   <si>
-    <t xml:space="preserve">109.918479919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.500053405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.821556091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.88777923584</t>
+    <t xml:space="preserve">109.918487548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.500061035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.821548461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.887771606445</t>
   </si>
   <si>
     <t xml:space="preserve">111.663208007812</t>
@@ -2999,25 +2999,25 @@
     <t xml:space="preserve">113.117164611816</t>
   </si>
   <si>
-    <t xml:space="preserve">115.831199645996</t>
+    <t xml:space="preserve">115.831192016602</t>
   </si>
   <si>
     <t xml:space="preserve">113.795669555664</t>
   </si>
   <si>
-    <t xml:space="preserve">114.76496887207</t>
+    <t xml:space="preserve">114.764976501465</t>
   </si>
   <si>
     <t xml:space="preserve">114.668045043945</t>
   </si>
   <si>
-    <t xml:space="preserve">114.280334472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.474182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.509712219238</t>
+    <t xml:space="preserve">114.280326843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.474174499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.509696960449</t>
   </si>
   <si>
     <t xml:space="preserve">121.453140258789</t>
@@ -3029,13 +3029,13 @@
     <t xml:space="preserve">128.819793701172</t>
   </si>
   <si>
-    <t xml:space="preserve">127.365852355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.268928527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.432083129883</t>
+    <t xml:space="preserve">127.365844726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.268936157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.432067871094</t>
   </si>
   <si>
     <t xml:space="preserve">133.181640625</t>
@@ -3050,22 +3050,22 @@
     <t xml:space="preserve">128.916732788086</t>
   </si>
   <si>
-    <t xml:space="preserve">134.635589599609</t>
+    <t xml:space="preserve">134.635604858398</t>
   </si>
   <si>
     <t xml:space="preserve">135.701812744141</t>
   </si>
   <si>
-    <t xml:space="preserve">134.44172668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.375518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.798767089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.314102172852</t>
+    <t xml:space="preserve">134.441741943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.375503540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.798751831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.314117431641</t>
   </si>
   <si>
     <t xml:space="preserve">136.574188232422</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">135.023315429688</t>
   </si>
   <si>
-    <t xml:space="preserve">133.763229370117</t>
+    <t xml:space="preserve">133.763214111328</t>
   </si>
   <si>
     <t xml:space="preserve">137.446563720703</t>
@@ -3089,28 +3089,28 @@
     <t xml:space="preserve">134.344818115234</t>
   </si>
   <si>
-    <t xml:space="preserve">138.222015380859</t>
+    <t xml:space="preserve">138.22200012207</t>
   </si>
   <si>
     <t xml:space="preserve">142.293060302734</t>
   </si>
   <si>
-    <t xml:space="preserve">141.032958984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.359268188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.063674926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.803573608398</t>
+    <t xml:space="preserve">141.032974243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.359283447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.063659667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.803558349609</t>
   </si>
   <si>
     <t xml:space="preserve">140.548324584961</t>
   </si>
   <si>
-    <t xml:space="preserve">140.160598754883</t>
+    <t xml:space="preserve">140.160614013672</t>
   </si>
   <si>
     <t xml:space="preserve">139.579025268555</t>
@@ -3119,19 +3119,19 @@
     <t xml:space="preserve">136.671127319336</t>
   </si>
   <si>
-    <t xml:space="preserve">138.609725952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.992614746094</t>
+    <t xml:space="preserve">138.609710693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.992630004883</t>
   </si>
   <si>
     <t xml:space="preserve">137.640426635742</t>
   </si>
   <si>
-    <t xml:space="preserve">139.094360351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.226821899414</t>
+    <t xml:space="preserve">139.094375610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.226837158203</t>
   </si>
   <si>
     <t xml:space="preserve">142.583847045898</t>
@@ -3146,7 +3146,7 @@
     <t xml:space="preserve">142.486907958984</t>
   </si>
   <si>
-    <t xml:space="preserve">146.073333740234</t>
+    <t xml:space="preserve">146.073318481445</t>
   </si>
   <si>
     <t xml:space="preserve">148.884292602539</t>
@@ -3155,28 +3155,28 @@
     <t xml:space="preserve">148.011917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">149.175079345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.756652832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.364105224609</t>
+    <t xml:space="preserve">149.175064086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.75666809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.364120483398</t>
   </si>
   <si>
     <t xml:space="preserve">147.236465454102</t>
   </si>
   <si>
-    <t xml:space="preserve">148.205764770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.81803894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.532119750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">150.629013061523</t>
+    <t xml:space="preserve">148.205749511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.818054199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.532104492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150.629028320312</t>
   </si>
   <si>
     <t xml:space="preserve">155.087799072266</t>
@@ -3185,19 +3185,19 @@
     <t xml:space="preserve">154.893936157227</t>
   </si>
   <si>
-    <t xml:space="preserve">152.955352783203</t>
+    <t xml:space="preserve">152.955337524414</t>
   </si>
   <si>
     <t xml:space="preserve">157.898773193359</t>
   </si>
   <si>
-    <t xml:space="preserve">161.67903137207</t>
+    <t xml:space="preserve">161.679016113281</t>
   </si>
   <si>
     <t xml:space="preserve">166.816314697266</t>
   </si>
   <si>
-    <t xml:space="preserve">166.428604125977</t>
+    <t xml:space="preserve">166.428588867188</t>
   </si>
   <si>
     <t xml:space="preserve">165.847015380859</t>
@@ -3218,25 +3218,25 @@
     <t xml:space="preserve">169.142639160156</t>
   </si>
   <si>
-    <t xml:space="preserve">169.627288818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">170.305770874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.23957824707</t>
+    <t xml:space="preserve">169.62727355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">170.305786132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.239562988281</t>
   </si>
   <si>
     <t xml:space="preserve">169.724212646484</t>
   </si>
   <si>
-    <t xml:space="preserve">168.948791503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.811477661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.204040527344</t>
+    <t xml:space="preserve">168.948760986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.811492919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.204055786133</t>
   </si>
   <si>
     <t xml:space="preserve">165.071578979492</t>
@@ -3284,10 +3284,10 @@
     <t xml:space="preserve">157.026397705078</t>
   </si>
   <si>
-    <t xml:space="preserve">159.643508911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.842178344727</t>
+    <t xml:space="preserve">159.643493652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.842208862305</t>
   </si>
   <si>
     <t xml:space="preserve">163.229904174805</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">161.097457885742</t>
   </si>
   <si>
-    <t xml:space="preserve">160.806655883789</t>
+    <t xml:space="preserve">160.806671142578</t>
   </si>
   <si>
     <t xml:space="preserve">160.61279296875</t>
@@ -3308,28 +3308,28 @@
     <t xml:space="preserve">161.582077026367</t>
   </si>
   <si>
-    <t xml:space="preserve">162.551406860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.872894287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164.39306640625</t>
+    <t xml:space="preserve">162.551391601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.87287902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164.393081665039</t>
   </si>
   <si>
     <t xml:space="preserve">171.275085449219</t>
   </si>
   <si>
-    <t xml:space="preserve">173.213684082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172.825958251953</t>
+    <t xml:space="preserve">173.21369934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.825973510742</t>
   </si>
   <si>
     <t xml:space="preserve">174.182983398438</t>
   </si>
   <si>
-    <t xml:space="preserve">171.662826538086</t>
+    <t xml:space="preserve">171.662796020508</t>
   </si>
   <si>
     <t xml:space="preserve">172.341323852539</t>
@@ -3344,31 +3344,31 @@
     <t xml:space="preserve">173.892196655273</t>
   </si>
   <si>
-    <t xml:space="preserve">168.754928588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.561050415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.010192871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.934280395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.454467773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">159.837371826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">166.040863037109</t>
+    <t xml:space="preserve">168.754913330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.56103515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.010177612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.934295654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.454483032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">159.837356567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">166.040878295898</t>
   </si>
   <si>
     <t xml:space="preserve">167.882537841797</t>
   </si>
   <si>
-    <t xml:space="preserve">160.709747314453</t>
+    <t xml:space="preserve">160.709732055664</t>
   </si>
   <si>
     <t xml:space="preserve">162.745254516602</t>
@@ -3377,7 +3377,7 @@
     <t xml:space="preserve">159.158843994141</t>
   </si>
   <si>
-    <t xml:space="preserve">172.535171508789</t>
+    <t xml:space="preserve">172.535186767578</t>
   </si>
   <si>
     <t xml:space="preserve">174.958404541016</t>
@@ -3386,40 +3386,40 @@
     <t xml:space="preserve">173.698333740234</t>
   </si>
   <si>
-    <t xml:space="preserve">174.570709228516</t>
+    <t xml:space="preserve">174.570724487305</t>
   </si>
   <si>
     <t xml:space="preserve">169.43342590332</t>
   </si>
   <si>
-    <t xml:space="preserve">168.076385498047</t>
+    <t xml:space="preserve">168.076416015625</t>
   </si>
   <si>
     <t xml:space="preserve">163.617630004883</t>
   </si>
   <si>
-    <t xml:space="preserve">164.877731323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.714538574219</t>
+    <t xml:space="preserve">164.877700805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.714553833008</t>
   </si>
   <si>
     <t xml:space="preserve">170.596572875977</t>
   </si>
   <si>
-    <t xml:space="preserve">169.821151733398</t>
+    <t xml:space="preserve">169.821136474609</t>
   </si>
   <si>
     <t xml:space="preserve">174.473785400391</t>
   </si>
   <si>
-    <t xml:space="preserve">164.005325317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.317199707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.572448730469</t>
+    <t xml:space="preserve">164.005355834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.317184448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.57243347168</t>
   </si>
   <si>
     <t xml:space="preserve">155.863235473633</t>
@@ -3431,25 +3431,25 @@
     <t xml:space="preserve">153.149200439453</t>
   </si>
   <si>
-    <t xml:space="preserve">151.016738891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">157.220260620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.113677978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.858413696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">154.990875244141</t>
+    <t xml:space="preserve">151.016754150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">157.220245361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.113662719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.8583984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">154.990859985352</t>
   </si>
   <si>
     <t xml:space="preserve">137.931213378906</t>
   </si>
   <si>
-    <t xml:space="preserve">143.746994018555</t>
+    <t xml:space="preserve">143.747009277344</t>
   </si>
   <si>
     <t xml:space="preserve">143.553146362305</t>
@@ -3458,7 +3458,7 @@
     <t xml:space="preserve">144.5224609375</t>
   </si>
   <si>
-    <t xml:space="preserve">144.910171508789</t>
+    <t xml:space="preserve">144.91015625</t>
   </si>
   <si>
     <t xml:space="preserve">139.385162353516</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">132.309280395508</t>
   </si>
   <si>
-    <t xml:space="preserve">138.997451782227</t>
+    <t xml:space="preserve">138.997436523438</t>
   </si>
   <si>
     <t xml:space="preserve">137.834274291992</t>
@@ -3482,16 +3482,16 @@
     <t xml:space="preserve">137.543487548828</t>
   </si>
   <si>
-    <t xml:space="preserve">138.125061035156</t>
+    <t xml:space="preserve">138.125076293945</t>
   </si>
   <si>
     <t xml:space="preserve">138.512771606445</t>
   </si>
   <si>
-    <t xml:space="preserve">142.680786132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.692184448242</t>
+    <t xml:space="preserve">142.680770874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.692169189453</t>
   </si>
   <si>
     <t xml:space="preserve">125.039535522461</t>
@@ -3503,13 +3503,13 @@
     <t xml:space="preserve">135.507965087891</t>
   </si>
   <si>
-    <t xml:space="preserve">142.874633789062</t>
+    <t xml:space="preserve">142.874618530273</t>
   </si>
   <si>
     <t xml:space="preserve">149.562805175781</t>
   </si>
   <si>
-    <t xml:space="preserve">151.986053466797</t>
+    <t xml:space="preserve">151.986038208008</t>
   </si>
   <si>
     <t xml:space="preserve">150.919815063477</t>
@@ -3518,31 +3518,31 @@
     <t xml:space="preserve">149.368942260742</t>
   </si>
   <si>
-    <t xml:space="preserve">146.267181396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.104019165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.690414428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.394805908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.751831054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">149.659713745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.200958251953</t>
+    <t xml:space="preserve">146.267166137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.10400390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.6904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.394821166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.751815795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">149.659729003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.200942993164</t>
   </si>
   <si>
     <t xml:space="preserve">141.517608642578</t>
   </si>
   <si>
-    <t xml:space="preserve">141.323760986328</t>
+    <t xml:space="preserve">141.323776245117</t>
   </si>
   <si>
     <t xml:space="preserve">137.058837890625</t>
@@ -3563,28 +3563,28 @@
     <t xml:space="preserve">135.217178344727</t>
   </si>
   <si>
-    <t xml:space="preserve">130.952270507812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.753578186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.16234588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.601806640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.285140991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.958824157715</t>
+    <t xml:space="preserve">130.952285766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.75358581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.162338256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.60181427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.28515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.958831787109</t>
   </si>
   <si>
     <t xml:space="preserve">117.57593536377</t>
   </si>
   <si>
-    <t xml:space="preserve">116.12198638916</t>
+    <t xml:space="preserve">116.121994018555</t>
   </si>
   <si>
     <t xml:space="preserve">119.708396911621</t>
@@ -3605,7 +3605,7 @@
     <t xml:space="preserve">113.003852844238</t>
   </si>
   <si>
-    <t xml:space="preserve">117.102432250977</t>
+    <t xml:space="preserve">117.102424621582</t>
   </si>
   <si>
     <t xml:space="preserve">116.71208190918</t>
@@ -3617,25 +3617,25 @@
     <t xml:space="preserve">124.909255981445</t>
   </si>
   <si>
-    <t xml:space="preserve">123.640640258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.834823608398</t>
+    <t xml:space="preserve">123.640647888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.834815979004</t>
   </si>
   <si>
     <t xml:space="preserve">120.225158691406</t>
   </si>
   <si>
-    <t xml:space="preserve">119.346900939941</t>
+    <t xml:space="preserve">119.346893310547</t>
   </si>
   <si>
     <t xml:space="preserve">121.005844116211</t>
   </si>
   <si>
-    <t xml:space="preserve">114.857971191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.539054870605</t>
+    <t xml:space="preserve">114.857963562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.5390625</t>
   </si>
   <si>
     <t xml:space="preserve">102.367042541504</t>
@@ -3644,7 +3644,7 @@
     <t xml:space="preserve">100.512916564941</t>
   </si>
   <si>
-    <t xml:space="preserve">101.586357116699</t>
+    <t xml:space="preserve">101.586349487305</t>
   </si>
   <si>
     <t xml:space="preserve">99.146728515625</t>
@@ -3653,16 +3653,16 @@
     <t xml:space="preserve">103.14771270752</t>
   </si>
   <si>
-    <t xml:space="preserve">103.830825805664</t>
+    <t xml:space="preserve">103.83081817627</t>
   </si>
   <si>
     <t xml:space="preserve">106.075286865234</t>
   </si>
   <si>
-    <t xml:space="preserve">108.417335510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.319747924805</t>
+    <t xml:space="preserve">108.417327880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.31974029541</t>
   </si>
   <si>
     <t xml:space="preserve">112.418327331543</t>
@@ -3683,13 +3683,13 @@
     <t xml:space="preserve">113.882110595703</t>
   </si>
   <si>
-    <t xml:space="preserve">111.24730682373</t>
+    <t xml:space="preserve">111.247314453125</t>
   </si>
   <si>
     <t xml:space="preserve">110.661796569824</t>
   </si>
   <si>
-    <t xml:space="preserve">116.321739196777</t>
+    <t xml:space="preserve">116.321746826172</t>
   </si>
   <si>
     <t xml:space="preserve">118.566207885742</t>
@@ -3698,16 +3698,16 @@
     <t xml:space="preserve">120.615501403809</t>
   </si>
   <si>
-    <t xml:space="preserve">119.054130554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.956550598145</t>
+    <t xml:space="preserve">119.054138183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.956558227539</t>
   </si>
   <si>
     <t xml:space="preserve">113.101432800293</t>
   </si>
   <si>
-    <t xml:space="preserve">116.907257080078</t>
+    <t xml:space="preserve">116.907264709473</t>
   </si>
   <si>
     <t xml:space="preserve">122.469619750977</t>
@@ -3716,13 +3716,13 @@
     <t xml:space="preserve">124.323753356934</t>
   </si>
   <si>
-    <t xml:space="preserve">125.885108947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.006851196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.66478729248</t>
+    <t xml:space="preserve">125.885116577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.006843566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.664794921875</t>
   </si>
   <si>
     <t xml:space="preserve">125.68994140625</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">123.055137634277</t>
   </si>
   <si>
-    <t xml:space="preserve">126.470634460449</t>
+    <t xml:space="preserve">126.470626831055</t>
   </si>
   <si>
     <t xml:space="preserve">122.957550048828</t>
@@ -3749,7 +3749,7 @@
     <t xml:space="preserve">134.082275390625</t>
   </si>
   <si>
-    <t xml:space="preserve">134.960540771484</t>
+    <t xml:space="preserve">134.960556030273</t>
   </si>
   <si>
     <t xml:space="preserve">134.179870605469</t>
@@ -3761,13 +3761,13 @@
     <t xml:space="preserve">126.177871704102</t>
   </si>
   <si>
-    <t xml:space="preserve">121.20100402832</t>
+    <t xml:space="preserve">121.201011657715</t>
   </si>
   <si>
     <t xml:space="preserve">120.42032623291</t>
   </si>
   <si>
-    <t xml:space="preserve">119.151710510254</t>
+    <t xml:space="preserve">119.151718139648</t>
   </si>
   <si>
     <t xml:space="preserve">122.176864624023</t>
@@ -3779,22 +3779,22 @@
     <t xml:space="preserve">115.736228942871</t>
   </si>
   <si>
-    <t xml:space="preserve">114.955558776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.271461486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.053146362305</t>
+    <t xml:space="preserve">114.955551147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.271453857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.05313873291</t>
   </si>
   <si>
     <t xml:space="preserve">112.711090087891</t>
   </si>
   <si>
-    <t xml:space="preserve">113.686943054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.46662902832</t>
+    <t xml:space="preserve">113.686935424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.466621398926</t>
   </si>
   <si>
     <t xml:space="preserve">117.590354919434</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">111.832817077637</t>
   </si>
   <si>
-    <t xml:space="preserve">110.369041442871</t>
+    <t xml:space="preserve">110.369033813477</t>
   </si>
   <si>
     <t xml:space="preserve">105.977699279785</t>
@@ -3821,7 +3821,7 @@
     <t xml:space="preserve">103.928405761719</t>
   </si>
   <si>
-    <t xml:space="preserve">100.708084106445</t>
+    <t xml:space="preserve">100.70809173584</t>
   </si>
   <si>
     <t xml:space="preserve">101.391189575195</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">104.904258728027</t>
   </si>
   <si>
-    <t xml:space="preserve">104.513916015625</t>
+    <t xml:space="preserve">104.51392364502</t>
   </si>
   <si>
     <t xml:space="preserve">101.196014404297</t>
@@ -3839,13 +3839,13 @@
     <t xml:space="preserve">105.001846313477</t>
   </si>
   <si>
-    <t xml:space="preserve">107.734230041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.83381652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.150726318359</t>
+    <t xml:space="preserve">107.734237670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.833824157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.150718688965</t>
   </si>
   <si>
     <t xml:space="preserve">112.12557220459</t>
@@ -3863,13 +3863,13 @@
     <t xml:space="preserve">108.026992797852</t>
   </si>
   <si>
-    <t xml:space="preserve">109.100425720215</t>
+    <t xml:space="preserve">109.100433349609</t>
   </si>
   <si>
     <t xml:space="preserve">108.514915466309</t>
   </si>
   <si>
-    <t xml:space="preserve">107.636650085449</t>
+    <t xml:space="preserve">107.636657714844</t>
   </si>
   <si>
     <t xml:space="preserve">109.978691101074</t>
@@ -3887,16 +3887,16 @@
     <t xml:space="preserve">108.905258178711</t>
   </si>
   <si>
-    <t xml:space="preserve">109.685943603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.320739746094</t>
+    <t xml:space="preserve">109.68595123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.320747375488</t>
   </si>
   <si>
     <t xml:space="preserve">122.274459838867</t>
   </si>
   <si>
-    <t xml:space="preserve">123.738227844238</t>
+    <t xml:space="preserve">123.738235473633</t>
   </si>
   <si>
     <t xml:space="preserve">116.028991699219</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">107.929405212402</t>
   </si>
   <si>
-    <t xml:space="preserve">112.223159790039</t>
+    <t xml:space="preserve">112.223167419434</t>
   </si>
   <si>
     <t xml:space="preserve">109.78352355957</t>
@@ -3917,7 +3917,7 @@
     <t xml:space="preserve">110.856964111328</t>
   </si>
   <si>
-    <t xml:space="preserve">109.588356018066</t>
+    <t xml:space="preserve">109.588363647461</t>
   </si>
   <si>
     <t xml:space="preserve">109.198020935059</t>
@@ -3926,13 +3926,13 @@
     <t xml:space="preserve">110.759384155273</t>
   </si>
   <si>
-    <t xml:space="preserve">117.200019836426</t>
+    <t xml:space="preserve">117.200012207031</t>
   </si>
   <si>
     <t xml:space="preserve">113.784530639648</t>
   </si>
   <si>
-    <t xml:space="preserve">105.587348937988</t>
+    <t xml:space="preserve">105.587356567383</t>
   </si>
   <si>
     <t xml:space="preserve">107.831817626953</t>
@@ -3950,10 +3950,10 @@
     <t xml:space="preserve">106.465621948242</t>
   </si>
   <si>
-    <t xml:space="preserve">104.416328430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.88011932373</t>
+    <t xml:space="preserve">104.41633605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.880111694336</t>
   </si>
   <si>
     <t xml:space="preserve">107.343894958496</t>
@@ -3962,10 +3962,10 @@
     <t xml:space="preserve">111.052139282227</t>
   </si>
   <si>
-    <t xml:space="preserve">114.467620849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.419334411621</t>
+    <t xml:space="preserve">114.467628479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.419342041016</t>
   </si>
   <si>
     <t xml:space="preserve">117.883117675781</t>
@@ -3980,25 +3980,25 @@
     <t xml:space="preserve">117.395195007324</t>
   </si>
   <si>
-    <t xml:space="preserve">118.273452758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.760375976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.980697631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.933410644531</t>
+    <t xml:space="preserve">118.273445129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.760383605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.98070526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.933403015137</t>
   </si>
   <si>
     <t xml:space="preserve">124.226165771484</t>
   </si>
   <si>
-    <t xml:space="preserve">123.152717590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.493766784668</t>
+    <t xml:space="preserve">123.152725219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.493774414062</t>
   </si>
   <si>
     <t xml:space="preserve">118.663795471191</t>
@@ -4010,25 +4010,25 @@
     <t xml:space="preserve">118.858963012695</t>
   </si>
   <si>
-    <t xml:space="preserve">114.37003326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.515930175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.149719238281</t>
+    <t xml:space="preserve">114.370040893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.515922546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.149726867676</t>
   </si>
   <si>
     <t xml:space="preserve">113.199012756348</t>
   </si>
   <si>
-    <t xml:space="preserve">111.540069580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.613510131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.124588012695</t>
+    <t xml:space="preserve">111.540061950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.613502502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.124580383301</t>
   </si>
   <si>
     <t xml:space="preserve">110.954551696777</t>
@@ -4061,10 +4061,10 @@
     <t xml:space="preserve">102.464630126953</t>
   </si>
   <si>
-    <t xml:space="preserve">101.683944702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.95255279541</t>
+    <t xml:space="preserve">101.683937072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.952560424805</t>
   </si>
   <si>
     <t xml:space="preserve">101.781532287598</t>
@@ -4076,7 +4076,7 @@
     <t xml:space="preserve">103.342895507812</t>
   </si>
   <si>
-    <t xml:space="preserve">101.000839233398</t>
+    <t xml:space="preserve">101.000846862793</t>
   </si>
   <si>
     <t xml:space="preserve">100.415336608887</t>
@@ -5480,7 +5480,7 @@
     <t xml:space="preserve">119.199996948242</t>
   </si>
   <si>
-    <t xml:space="preserve">115.900001525879</t>
+    <t xml:space="preserve">114.599998474121</t>
   </si>
 </sst>
 </file>
@@ -70923,22 +70923,22 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45967.6912384259</v>
+        <v>45968.6912268518</v>
       </c>
       <c r="B2505" t="n">
-        <v>37910</v>
+        <v>68091</v>
       </c>
       <c r="C2505" t="n">
-        <v>119.300003051758</v>
+        <v>116.900001525879</v>
       </c>
       <c r="D2505" t="n">
-        <v>115.900001525879</v>
+        <v>114.599998474121</v>
       </c>
       <c r="E2505" t="n">
-        <v>119</v>
+        <v>116.099998474121</v>
       </c>
       <c r="F2505" t="n">
-        <v>115.900001525879</v>
+        <v>114.599998474121</v>
       </c>
       <c r="G2505" t="s">
         <v>1822</v>

--- a/data/REY.MI.xlsx
+++ b/data/REY.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1823" uniqueCount="1823">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1827" uniqueCount="1827">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,61 +44,61 @@
     <t xml:space="preserve">REY.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8380241394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3272132873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6306381225586</t>
+    <t xml:space="preserve">28.8380260467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3272094726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6306400299072</t>
   </si>
   <si>
     <t xml:space="preserve">27.8396110534668</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2111148834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0005645751953</t>
+    <t xml:space="preserve">28.2111167907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0005626678467</t>
   </si>
   <si>
     <t xml:space="preserve">28.5594005584717</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1414546966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1198215484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9789237976074</t>
+    <t xml:space="preserve">28.1414566040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1198234558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9789257049561</t>
   </si>
   <si>
     <t xml:space="preserve">26.8644123077393</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4448871612549</t>
+    <t xml:space="preserve">27.4448852539062</t>
   </si>
   <si>
     <t xml:space="preserve">27.932487487793</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8163928985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2807731628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6770763397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0950183868408</t>
+    <t xml:space="preserve">27.8163909912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2807750701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6770782470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0950202941895</t>
   </si>
   <si>
     <t xml:space="preserve">27.862829208374</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2591381072998</t>
+    <t xml:space="preserve">27.2591342926025</t>
   </si>
   <si>
     <t xml:space="preserve">26.7018775939941</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">24.3799781799316</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6121673583984</t>
+    <t xml:space="preserve">24.6121654510498</t>
   </si>
   <si>
     <t xml:space="preserve">26.0053062438965</t>
@@ -122,25 +122,25 @@
     <t xml:space="preserve">25.517707824707</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6570243835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6074237823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3071537017822</t>
+    <t xml:space="preserve">25.6570224761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6074199676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3071556091309</t>
   </si>
   <si>
     <t xml:space="preserve">27.0733833312988</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2142810821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4696884155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0517463684082</t>
+    <t xml:space="preserve">26.2142791748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.469690322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0517482757568</t>
   </si>
   <si>
     <t xml:space="preserve">25.7034606933594</t>
@@ -149,10 +149,10 @@
     <t xml:space="preserve">25.7266807556152</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7483177185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4929065704346</t>
+    <t xml:space="preserve">26.7483158111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4929084777832</t>
   </si>
   <si>
     <t xml:space="preserve">27.3520107269287</t>
@@ -164,67 +164,67 @@
     <t xml:space="preserve">27.2359142303467</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1662578582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9092693328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0237789154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.5546588897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.3008270263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.4169254302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9989833831787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9757633209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7900085449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9525451660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2311687469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7203521728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.0686359405518</t>
+    <t xml:space="preserve">27.166259765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9092674255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.0237808227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.5546569824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.3008251190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4169235229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9989795684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9757595062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7900104522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9525413513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2311706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7203540802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.0686378479004</t>
   </si>
   <si>
     <t xml:space="preserve">29.8596687316895</t>
   </si>
   <si>
-    <t xml:space="preserve">29.5578212738037</t>
+    <t xml:space="preserve">29.5578174591064</t>
   </si>
   <si>
     <t xml:space="preserve">29.3256282806396</t>
   </si>
   <si>
-    <t xml:space="preserve">29.4881610870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.5113830566406</t>
+    <t xml:space="preserve">29.4881572723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.5113792419434</t>
   </si>
   <si>
     <t xml:space="preserve">29.2095336914062</t>
   </si>
   <si>
-    <t xml:space="preserve">30.161506652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3720664978027</t>
+    <t xml:space="preserve">30.1615104675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3720645904541</t>
   </si>
   <si>
     <t xml:space="preserve">29.534595489502</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">28.8148097991943</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9076862335205</t>
+    <t xml:space="preserve">28.9076881408691</t>
   </si>
   <si>
     <t xml:space="preserve">28.629056930542</t>
@@ -257,46 +257,46 @@
     <t xml:space="preserve">28.5605506896973</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0287532806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3264446258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.513729095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7946529388428</t>
+    <t xml:space="preserve">29.0287551879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3264465332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.5137310028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7946510314941</t>
   </si>
   <si>
     <t xml:space="preserve">29.0053443908691</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2628536224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1992721557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5036029815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5504245758057</t>
+    <t xml:space="preserve">29.2628555297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1992664337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.503604888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5504207611084</t>
   </si>
   <si>
     <t xml:space="preserve">30.901575088501</t>
   </si>
   <si>
-    <t xml:space="preserve">30.6674785614014</t>
+    <t xml:space="preserve">30.6674747467041</t>
   </si>
   <si>
     <t xml:space="preserve">30.7142944335938</t>
   </si>
   <si>
-    <t xml:space="preserve">30.456787109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.43337059021</t>
+    <t xml:space="preserve">30.4567852020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.4333724975586</t>
   </si>
   <si>
     <t xml:space="preserve">30.2694988250732</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">28.1859836578369</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3096771240234</t>
+    <t xml:space="preserve">29.3096752166748</t>
   </si>
   <si>
     <t xml:space="preserve">29.4969615936279</t>
@@ -317,31 +317,31 @@
     <t xml:space="preserve">27.6943702697754</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7747230529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8047752380371</t>
+    <t xml:space="preserve">25.7747287750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8047771453857</t>
   </si>
   <si>
     <t xml:space="preserve">27.3198013305664</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9218311309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5070838928223</t>
+    <t xml:space="preserve">26.9218254089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5070858001709</t>
   </si>
   <si>
     <t xml:space="preserve">26.9452381134033</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8215465545654</t>
+    <t xml:space="preserve">25.8215446472168</t>
   </si>
   <si>
     <t xml:space="preserve">26.219518661499</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1091117858887</t>
+    <t xml:space="preserve">27.1091136932373</t>
   </si>
   <si>
     <t xml:space="preserve">27.6241359710693</t>
@@ -353,55 +353,55 @@
     <t xml:space="preserve">28.3030338287354</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8882942199707</t>
+    <t xml:space="preserve">28.8882904052734</t>
   </si>
   <si>
     <t xml:space="preserve">28.7478332519531</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4434947967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.98193359375</t>
+    <t xml:space="preserve">28.4434986114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.9819374084473</t>
   </si>
   <si>
     <t xml:space="preserve">28.9117012023926</t>
   </si>
   <si>
-    <t xml:space="preserve">29.3799095153809</t>
+    <t xml:space="preserve">29.3799114227295</t>
   </si>
   <si>
     <t xml:space="preserve">29.4501399993896</t>
   </si>
   <si>
-    <t xml:space="preserve">29.8481121063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1524505615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.9651660919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.7244186401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1458053588867</t>
+    <t xml:space="preserve">29.8481140136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1524486541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.9651641845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.7244205474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1458072662354</t>
   </si>
   <si>
     <t xml:space="preserve">29.0989875793457</t>
   </si>
   <si>
-    <t xml:space="preserve">28.9351119995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4903182983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9752902984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3732643127441</t>
+    <t xml:space="preserve">28.9351139068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4903163909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9752922058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3732662200928</t>
   </si>
   <si>
     <t xml:space="preserve">28.092342376709</t>
@@ -416,19 +416,19 @@
     <t xml:space="preserve">27.0388793945312</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8984203338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1492862701416</t>
+    <t xml:space="preserve">26.898416519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1492900848389</t>
   </si>
   <si>
     <t xml:space="preserve">25.7981357574463</t>
   </si>
   <si>
-    <t xml:space="preserve">25.891773223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7579574584961</t>
+    <t xml:space="preserve">25.8917770385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7579593658447</t>
   </si>
   <si>
     <t xml:space="preserve">27.9518814086914</t>
@@ -437,40 +437,40 @@
     <t xml:space="preserve">27.8816509246826</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8114204406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9050579071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2963943481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8582401275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5773162841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7177772521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.741189956665</t>
+    <t xml:space="preserve">27.8114223480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9050617218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2963924407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8582420349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5773181915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7177810668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7411918640137</t>
   </si>
   <si>
     <t xml:space="preserve">28.0455226898193</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7880096435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3900318145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1223926544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6541900634766</t>
+    <t xml:space="preserve">27.7880077362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3900337219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1223964691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6541881561279</t>
   </si>
   <si>
     <t xml:space="preserve">28.2093944549561</t>
@@ -482,10 +482,10 @@
     <t xml:space="preserve">27.0857009887695</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8515949249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4368553161621</t>
+    <t xml:space="preserve">26.851598739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4368515014648</t>
   </si>
   <si>
     <t xml:space="preserve">26.6877269744873</t>
@@ -494,31 +494,31 @@
     <t xml:space="preserve">27.2261619567871</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8281860351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6409091949463</t>
+    <t xml:space="preserve">26.8281898498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.640905380249</t>
   </si>
   <si>
     <t xml:space="preserve">26.4536228179932</t>
   </si>
   <si>
-    <t xml:space="preserve">26.570671081543</t>
+    <t xml:space="preserve">26.5706748962402</t>
   </si>
   <si>
     <t xml:space="preserve">26.5238552093506</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3365745544434</t>
+    <t xml:space="preserve">26.3365688323975</t>
   </si>
   <si>
     <t xml:space="preserve">25.751314163208</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3299293518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7446727752686</t>
+    <t xml:space="preserve">25.329927444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7446708679199</t>
   </si>
   <si>
     <t xml:space="preserve">24.7680797576904</t>
@@ -527,64 +527,64 @@
     <t xml:space="preserve">24.8851356506348</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2530555725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0490036010742</t>
+    <t xml:space="preserve">24.2530536651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0490055084229</t>
   </si>
   <si>
     <t xml:space="preserve">25.4703903198242</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5172100067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2831115722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1660556793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4469757080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0958271026611</t>
+    <t xml:space="preserve">25.5172119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2831077575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1660575866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4469795227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0958251953125</t>
   </si>
   <si>
     <t xml:space="preserve">24.9319534301758</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0724143981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6342620849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1961135864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1726989746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.834831237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.9284706115723</t>
+    <t xml:space="preserve">25.072416305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6342601776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1961097717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1727027893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8348293304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.9284744262695</t>
   </si>
   <si>
     <t xml:space="preserve">27.4602642059326</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9987010955811</t>
+    <t xml:space="preserve">27.9986991882324</t>
   </si>
   <si>
     <t xml:space="preserve">28.6307792663574</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2160377502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.3330860137939</t>
+    <t xml:space="preserve">29.2160339355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.3330879211426</t>
   </si>
   <si>
     <t xml:space="preserve">28.8648815155029</t>
@@ -593,88 +593,88 @@
     <t xml:space="preserve">28.3498554229736</t>
   </si>
   <si>
-    <t xml:space="preserve">28.6073703765869</t>
+    <t xml:space="preserve">28.6073665618896</t>
   </si>
   <si>
     <t xml:space="preserve">29.4735488891602</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2394504547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.7076549530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.4267292022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.8313426971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.9952163696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4868316650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.2527332305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.3697814941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.1356811523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.1891403198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.3061981201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.2660179138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.0619659423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.6472244262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4599456787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7408638000488</t>
+    <t xml:space="preserve">29.239444732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.7076530456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.4267272949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.8313484191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9952220916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.4868354797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.2527275085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.369779586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.1356773376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.1891441345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3061904907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.2660217285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.0619735717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.647216796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4599418640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7408599853516</t>
   </si>
   <si>
     <t xml:space="preserve">34.6706352233887</t>
   </si>
   <si>
-    <t xml:space="preserve">34.9983749389648</t>
+    <t xml:space="preserve">34.9983787536621</t>
   </si>
   <si>
     <t xml:space="preserve">34.8579139709473</t>
   </si>
   <si>
-    <t xml:space="preserve">34.1790161132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.764274597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8813247680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.389705657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.4131164550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.6070442199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4665832519531</t>
+    <t xml:space="preserve">34.1790199279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7642784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8813209533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.3897132873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4131202697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.607048034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4665870666504</t>
   </si>
   <si>
     <t xml:space="preserve">35.7943229675293</t>
@@ -683,55 +683,55 @@
     <t xml:space="preserve">36.8243789672852</t>
   </si>
   <si>
-    <t xml:space="preserve">37.6671485900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.8778381347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.9882507324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.5735092163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.6203269958496</t>
+    <t xml:space="preserve">37.6671524047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.8778457641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.9882431030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.5735130310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.6203308105469</t>
   </si>
   <si>
     <t xml:space="preserve">37.6085395812988</t>
   </si>
   <si>
-    <t xml:space="preserve">37.7264404296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9150657653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.1980133056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.9386444091797</t>
+    <t xml:space="preserve">37.7264366149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.9150695800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.1980171203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.938648223877</t>
   </si>
   <si>
     <t xml:space="preserve">38.1508560180664</t>
   </si>
   <si>
-    <t xml:space="preserve">37.4906387329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0232810974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0843353271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.0607566833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8013916015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2397041320801</t>
+    <t xml:space="preserve">37.4906463623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0232772827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0843391418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.0607528686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.8013877868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.2397079467773</t>
   </si>
   <si>
     <t xml:space="preserve">41.0274963378906</t>
@@ -743,16 +743,16 @@
     <t xml:space="preserve">41.7112846374512</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4990768432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8056106567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3243446350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1828689575195</t>
+    <t xml:space="preserve">41.499080657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.8056030273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3243408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1828651428223</t>
   </si>
   <si>
     <t xml:space="preserve">42.0885543823242</t>
@@ -764,13 +764,13 @@
     <t xml:space="preserve">41.8291816711426</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9664421081543</t>
+    <t xml:space="preserve">39.9664459228516</t>
   </si>
   <si>
     <t xml:space="preserve">39.5891761779785</t>
   </si>
   <si>
-    <t xml:space="preserve">38.4337997436523</t>
+    <t xml:space="preserve">38.4338035583496</t>
   </si>
   <si>
     <t xml:space="preserve">38.9997024536133</t>
@@ -779,43 +779,43 @@
     <t xml:space="preserve">39.6363372802734</t>
   </si>
   <si>
-    <t xml:space="preserve">39.9428672790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4380226135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.5516967773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.0565452575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1411743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3298034667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0704345703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1647605895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6696014404297</t>
+    <t xml:space="preserve">39.9428596496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.4380149841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.551700592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0565414428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.141170501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3298149108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0704383850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1647567749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6695938110352</t>
   </si>
   <si>
     <t xml:space="preserve">38.8346481323242</t>
   </si>
   <si>
-    <t xml:space="preserve">38.905387878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0940208435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.8110694885254</t>
+    <t xml:space="preserve">38.9053840637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0940170288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8110733032227</t>
   </si>
   <si>
     <t xml:space="preserve">38.2687530517578</t>
@@ -830,46 +830,46 @@
     <t xml:space="preserve">39.2354927062988</t>
   </si>
   <si>
-    <t xml:space="preserve">39.2590751647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.1357116699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5129699707031</t>
+    <t xml:space="preserve">39.2590713500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1357154846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5129814147949</t>
   </si>
   <si>
     <t xml:space="preserve">44.7765617370605</t>
   </si>
   <si>
-    <t xml:space="preserve">44.8001403808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.507511138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.3188819885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8140449523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.682243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7862396240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.7529830932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.130241394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4464530944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.5879364013672</t>
+    <t xml:space="preserve">44.8001441955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5075073242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3188781738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8140487670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6822509765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7862434387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.752986907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1302452087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4464569091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.5879287719727</t>
   </si>
   <si>
     <t xml:space="preserve">44.3285598754883</t>
@@ -878,13 +878,13 @@
     <t xml:space="preserve">44.3049812316895</t>
   </si>
   <si>
-    <t xml:space="preserve">43.6211853027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.1731834411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.0788764953613</t>
+    <t xml:space="preserve">43.6211891174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.1731910705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.0788688659668</t>
   </si>
   <si>
     <t xml:space="preserve">42.5837173461914</t>
@@ -896,10 +896,10 @@
     <t xml:space="preserve">45.3660354614258</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9887771606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4936141967773</t>
+    <t xml:space="preserve">44.98876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4936103820801</t>
   </si>
   <si>
     <t xml:space="preserve">44.5171928405762</t>
@@ -908,88 +908,88 @@
     <t xml:space="preserve">45.6254043579102</t>
   </si>
   <si>
-    <t xml:space="preserve">45.861198425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4035110473633</t>
+    <t xml:space="preserve">45.8611946105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4035148620605</t>
   </si>
   <si>
     <t xml:space="preserve">47.582462310791</t>
   </si>
   <si>
-    <t xml:space="preserve">47.0637245178223</t>
+    <t xml:space="preserve">47.0637283325195</t>
   </si>
   <si>
     <t xml:space="preserve">47.134464263916</t>
   </si>
   <si>
-    <t xml:space="preserve">47.1580467224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9125671386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3508987426758</t>
+    <t xml:space="preserve">47.1580429077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9125709533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3508911132812</t>
   </si>
   <si>
     <t xml:space="preserve">48.7378349304199</t>
   </si>
   <si>
-    <t xml:space="preserve">48.1012077331543</t>
+    <t xml:space="preserve">48.101203918457</t>
   </si>
   <si>
     <t xml:space="preserve">48.8321571350098</t>
   </si>
   <si>
-    <t xml:space="preserve">47.6296272277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0540428161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8654098510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.9597244262695</t>
+    <t xml:space="preserve">47.6296234130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0540466308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8654136657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9597282409668</t>
   </si>
   <si>
     <t xml:space="preserve">49.1858367919922</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2717208862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0359344482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.5643463134766</t>
+    <t xml:space="preserve">45.2717170715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0359382629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.5643501281738</t>
   </si>
   <si>
     <t xml:space="preserve">43.9748764038086</t>
   </si>
   <si>
-    <t xml:space="preserve">42.560131072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.913818359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.7251892089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2064476013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.4328117370605</t>
+    <t xml:space="preserve">42.5601348876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.9138221740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.7251815795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2064514160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.432804107666</t>
   </si>
   <si>
     <t xml:space="preserve">42.1781578063965</t>
   </si>
   <si>
-    <t xml:space="preserve">43.3476753234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.9800872802734</t>
+    <t xml:space="preserve">43.3476715087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.9800910949707</t>
   </si>
   <si>
     <t xml:space="preserve">41.3010177612305</t>
@@ -998,112 +998,112 @@
     <t xml:space="preserve">42.0838394165039</t>
   </si>
   <si>
-    <t xml:space="preserve">42.7534790039062</t>
+    <t xml:space="preserve">42.7534866333008</t>
   </si>
   <si>
     <t xml:space="preserve">42.593147277832</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4799652099609</t>
+    <t xml:space="preserve">42.4799613952637</t>
   </si>
   <si>
     <t xml:space="preserve">43.0081367492676</t>
   </si>
   <si>
-    <t xml:space="preserve">43.0458641052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.3288078308105</t>
+    <t xml:space="preserve">43.0458602905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.3288192749023</t>
   </si>
   <si>
     <t xml:space="preserve">41.3953285217285</t>
   </si>
   <si>
-    <t xml:space="preserve">43.4891471862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2342414855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1210670471191</t>
+    <t xml:space="preserve">43.4891510009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.234245300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1210632324219</t>
   </si>
   <si>
     <t xml:space="preserve">43.2439231872559</t>
   </si>
   <si>
-    <t xml:space="preserve">42.1027030944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.1689796447754</t>
+    <t xml:space="preserve">42.1026992797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1689720153809</t>
   </si>
   <si>
     <t xml:space="preserve">40.2729682922363</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4045143127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.7626647949219</t>
+    <t xml:space="preserve">42.4045104980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7626686096191</t>
   </si>
   <si>
     <t xml:space="preserve">44.2531089782715</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0547943115234</t>
+    <t xml:space="preserve">45.0547981262207</t>
   </si>
   <si>
     <t xml:space="preserve">44.9510498046875</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2809028625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1488571166992</t>
+    <t xml:space="preserve">46.2809066772461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1488647460938</t>
   </si>
   <si>
     <t xml:space="preserve">45.3094482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">44.9982032775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5358009338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.16796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5923919677734</t>
+    <t xml:space="preserve">44.9982070922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5358047485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1679725646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.592399597168</t>
   </si>
   <si>
     <t xml:space="preserve">44.6586685180664</t>
   </si>
   <si>
-    <t xml:space="preserve">43.253360748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.6683502197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.2248115539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.0830917358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.205696105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.3280639648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.0356826782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6584167480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5169448852539</t>
+    <t xml:space="preserve">43.2533531188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.6683540344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.2248153686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.0830879211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2057037353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3280601501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.0356864929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6584205627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5169372558594</t>
   </si>
   <si>
     <t xml:space="preserve">44.1682243347168</t>
@@ -1115,10 +1115,10 @@
     <t xml:space="preserve">43.5457344055176</t>
   </si>
   <si>
-    <t xml:space="preserve">43.8852729797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4605979919434</t>
+    <t xml:space="preserve">43.8852767944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4606056213379</t>
   </si>
   <si>
     <t xml:space="preserve">45.6112594604492</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">45.6301231384277</t>
   </si>
   <si>
-    <t xml:space="preserve">45.724437713623</t>
+    <t xml:space="preserve">45.7244415283203</t>
   </si>
   <si>
     <t xml:space="preserve">46.290340423584</t>
@@ -1145,31 +1145,31 @@
     <t xml:space="preserve">46.7053260803223</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5921516418457</t>
+    <t xml:space="preserve">46.5921478271484</t>
   </si>
   <si>
     <t xml:space="preserve">46.8939590454102</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7711067199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.8182640075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.1955146789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.9972076416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5727882385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3273086547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.3176307678223</t>
+    <t xml:space="preserve">47.7711029052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.8182601928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.1955223083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.9972114562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.5727844238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3273162841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.317626953125</t>
   </si>
   <si>
     <t xml:space="preserve">50.4119529724121</t>
@@ -1184,34 +1184,34 @@
     <t xml:space="preserve">50.223316192627</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0818367004395</t>
+    <t xml:space="preserve">50.081844329834</t>
   </si>
   <si>
     <t xml:space="preserve">47.5353088378906</t>
   </si>
   <si>
-    <t xml:space="preserve">46.1960220336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.205207824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.0068855285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2523536682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4223823547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8376159667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6489906311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.8753509521484</t>
+    <t xml:space="preserve">46.1960182189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2052001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.0068893432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2523612976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4223785400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8376197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6489868164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.8753395080566</t>
   </si>
   <si>
     <t xml:space="preserve">46.5732841491699</t>
@@ -1223,16 +1223,16 @@
     <t xml:space="preserve">48.8085708618164</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4789619445801</t>
+    <t xml:space="preserve">46.4789695739746</t>
   </si>
   <si>
     <t xml:space="preserve">47.3938331604004</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5166969299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1774024963379</t>
+    <t xml:space="preserve">46.5166931152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1774101257324</t>
   </si>
   <si>
     <t xml:space="preserve">44.7812767028809</t>
@@ -1241,22 +1241,22 @@
     <t xml:space="preserve">44.8378715515137</t>
   </si>
   <si>
-    <t xml:space="preserve">44.4983329772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.1776542663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.8952026367188</t>
+    <t xml:space="preserve">44.4983253479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.1776580810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.895206451416</t>
   </si>
   <si>
     <t xml:space="preserve">42.291332244873</t>
   </si>
   <si>
-    <t xml:space="preserve">42.4988288879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0652236938477</t>
+    <t xml:space="preserve">42.4988250732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0652275085449</t>
   </si>
   <si>
     <t xml:space="preserve">41.9517936706543</t>
@@ -1265,37 +1265,37 @@
     <t xml:space="preserve">45.3283157348633</t>
   </si>
   <si>
-    <t xml:space="preserve">45.4414939880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4603500366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.4037590026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1016998291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.9885177612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.384651184082</t>
+    <t xml:space="preserve">45.4414901733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4603576660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.4037666320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1017074584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.9885215759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.3846473693848</t>
   </si>
   <si>
     <t xml:space="preserve">49.0443687438965</t>
   </si>
   <si>
-    <t xml:space="preserve">48.9028854370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.2898368835449</t>
+    <t xml:space="preserve">48.902889251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.2898406982422</t>
   </si>
   <si>
     <t xml:space="preserve">51.1193199157715</t>
   </si>
   <si>
-    <t xml:space="preserve">50.6949005126953</t>
+    <t xml:space="preserve">50.694896697998</t>
   </si>
   <si>
     <t xml:space="preserve">50.6005821228027</t>
@@ -1304,106 +1304,106 @@
     <t xml:space="preserve">50.9328575134277</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4107093811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0277938842773</t>
+    <t xml:space="preserve">50.4107131958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0277900695801</t>
   </si>
   <si>
     <t xml:space="preserve">52.214485168457</t>
   </si>
   <si>
-    <t xml:space="preserve">52.1195526123047</t>
+    <t xml:space="preserve">52.1195487976074</t>
   </si>
   <si>
     <t xml:space="preserve">51.7398071289062</t>
   </si>
   <si>
-    <t xml:space="preserve">49.8410987854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.5024719238281</t>
+    <t xml:space="preserve">49.8410949707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.5024681091309</t>
   </si>
   <si>
     <t xml:space="preserve">49.2714881896973</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3664207458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.0816192626953</t>
+    <t xml:space="preserve">49.3664245605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.0816116333008</t>
   </si>
   <si>
     <t xml:space="preserve">49.7936325073242</t>
   </si>
   <si>
-    <t xml:space="preserve">48.274658203125</t>
+    <t xml:space="preserve">48.2746620178223</t>
   </si>
   <si>
     <t xml:space="preserve">46.822151184082</t>
   </si>
   <si>
-    <t xml:space="preserve">48.0848007202148</t>
+    <t xml:space="preserve">48.0847969055176</t>
   </si>
   <si>
     <t xml:space="preserve">48.6544075012207</t>
   </si>
   <si>
-    <t xml:space="preserve">49.3189544677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.6512222290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9835052490234</t>
+    <t xml:space="preserve">49.3189582824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.6512298583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9835014343262</t>
   </si>
   <si>
     <t xml:space="preserve">50.3632431030273</t>
   </si>
   <si>
-    <t xml:space="preserve">51.2176628112793</t>
+    <t xml:space="preserve">51.217658996582</t>
   </si>
   <si>
     <t xml:space="preserve">50.1733703613281</t>
   </si>
   <si>
-    <t xml:space="preserve">51.455005645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.0246086120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.068904876709</t>
+    <t xml:space="preserve">51.4550018310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.0246124267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0689086914062</t>
   </si>
   <si>
     <t xml:space="preserve">52.7840957641602</t>
   </si>
   <si>
-    <t xml:space="preserve">55.4422950744629</t>
+    <t xml:space="preserve">55.4422912597656</t>
   </si>
   <si>
     <t xml:space="preserve">54.682804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">55.1100120544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5846900939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3916473388672</t>
+    <t xml:space="preserve">55.1100196838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.5846862792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3916435241699</t>
   </si>
   <si>
     <t xml:space="preserve">54.7302742004395</t>
   </si>
   <si>
-    <t xml:space="preserve">55.0625495910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.4897575378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2524147033691</t>
+    <t xml:space="preserve">55.0625457763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.4897613525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.2524185180664</t>
   </si>
   <si>
     <t xml:space="preserve">53.1638412475586</t>
@@ -1418,55 +1418,55 @@
     <t xml:space="preserve">54.3030662536621</t>
   </si>
   <si>
-    <t xml:space="preserve">54.1131973266602</t>
+    <t xml:space="preserve">54.1131896972656</t>
   </si>
   <si>
     <t xml:space="preserve">53.8283882141113</t>
   </si>
   <si>
-    <t xml:space="preserve">54.7777404785156</t>
+    <t xml:space="preserve">54.7777366638184</t>
   </si>
   <si>
     <t xml:space="preserve">56.4391098022461</t>
   </si>
   <si>
-    <t xml:space="preserve">56.9137916564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2967071533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0119018554688</t>
+    <t xml:space="preserve">56.9137878417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.296703338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0118980407715</t>
   </si>
   <si>
     <t xml:space="preserve">56.201774597168</t>
   </si>
   <si>
-    <t xml:space="preserve">56.5340423583984</t>
+    <t xml:space="preserve">56.5340461730957</t>
   </si>
   <si>
     <t xml:space="preserve">56.6764488220215</t>
   </si>
   <si>
-    <t xml:space="preserve">54.9676094055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.5942306518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.021427154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1574859619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.350528717041</t>
+    <t xml:space="preserve">54.9676170349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.5942268371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.0214385986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1574783325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3505325317383</t>
   </si>
   <si>
     <t xml:space="preserve">52.9265022277832</t>
   </si>
   <si>
-    <t xml:space="preserve">52.8790321350098</t>
+    <t xml:space="preserve">52.8790283203125</t>
   </si>
   <si>
     <t xml:space="preserve">54.0657272338867</t>
@@ -1475,28 +1475,28 @@
     <t xml:space="preserve">54.5878715515137</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4486427307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.6859855651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.3062400817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.4043579101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0752563476562</t>
+    <t xml:space="preserve">53.4486465454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.6859817504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.3062438964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.404354095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.075252532959</t>
   </si>
   <si>
     <t xml:space="preserve">50.4581832885742</t>
   </si>
   <si>
-    <t xml:space="preserve">52.2619514465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.882209777832</t>
+    <t xml:space="preserve">52.2619552612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.8822135925293</t>
   </si>
   <si>
     <t xml:space="preserve">54.1606597900391</t>
@@ -1505,19 +1505,19 @@
     <t xml:space="preserve">54.2081298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">53.543586730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.540397644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.2049522399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2492370605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.1036605834961</t>
+    <t xml:space="preserve">53.5435791015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.5404014587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.204948425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2492446899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.1036567687988</t>
   </si>
   <si>
     <t xml:space="preserve">57.2460594177246</t>
@@ -1529,10 +1529,10 @@
     <t xml:space="preserve">56.961254119873</t>
   </si>
   <si>
-    <t xml:space="preserve">50.7904510498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.413890838623</t>
+    <t xml:space="preserve">50.790454864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.4138870239258</t>
   </si>
   <si>
     <t xml:space="preserve">47.0120239257812</t>
@@ -1541,34 +1541,34 @@
     <t xml:space="preserve">47.0499992370605</t>
   </si>
   <si>
-    <t xml:space="preserve">48.2271919250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.467716217041</t>
+    <t xml:space="preserve">48.2271957397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.4677124023438</t>
   </si>
   <si>
     <t xml:space="preserve">50.0309715270996</t>
   </si>
   <si>
-    <t xml:space="preserve">50.3157768249512</t>
+    <t xml:space="preserve">50.3157730102539</t>
   </si>
   <si>
     <t xml:space="preserve">46.3474731445312</t>
   </si>
   <si>
-    <t xml:space="preserve">44.7525596618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6766166687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6956024169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.1955795288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5563354492188</t>
+    <t xml:space="preserve">44.7525634765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6766052246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6955986022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.1955718994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.5563316345215</t>
   </si>
   <si>
     <t xml:space="preserve">46.4803848266602</t>
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">47.4107475280762</t>
   </si>
   <si>
-    <t xml:space="preserve">46.5373497009277</t>
+    <t xml:space="preserve">46.5373458862305</t>
   </si>
   <si>
     <t xml:space="preserve">46.5183601379395</t>
@@ -1589,7 +1589,7 @@
     <t xml:space="preserve">46.7462043762207</t>
   </si>
   <si>
-    <t xml:space="preserve">46.4424095153809</t>
+    <t xml:space="preserve">46.4424057006836</t>
   </si>
   <si>
     <t xml:space="preserve">45.4930572509766</t>
@@ -1598,16 +1598,16 @@
     <t xml:space="preserve">45.1323051452637</t>
   </si>
   <si>
-    <t xml:space="preserve">45.5690078735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7019081115723</t>
+    <t xml:space="preserve">45.5690002441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7019157409668</t>
   </si>
   <si>
     <t xml:space="preserve">42.3601875305176</t>
   </si>
   <si>
-    <t xml:space="preserve">41.4678001403809</t>
+    <t xml:space="preserve">41.4677925109863</t>
   </si>
   <si>
     <t xml:space="preserve">41.9234848022461</t>
@@ -1619,61 +1619,61 @@
     <t xml:space="preserve">43.7462463378906</t>
   </si>
   <si>
-    <t xml:space="preserve">44.2968635559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8601722717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7208976745605</t>
+    <t xml:space="preserve">44.2968673706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8601684570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7209014892578</t>
   </si>
   <si>
     <t xml:space="preserve">46.7841796875</t>
   </si>
   <si>
-    <t xml:space="preserve">47.7050476074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2398681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.2905082702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.1892585754395</t>
+    <t xml:space="preserve">47.7050514221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2398643493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.2905120849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.1892623901367</t>
   </si>
   <si>
     <t xml:space="preserve">45.2082481384277</t>
   </si>
   <si>
-    <t xml:space="preserve">45.2842025756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3158149719238</t>
+    <t xml:space="preserve">45.2841949462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3158111572266</t>
   </si>
   <si>
     <t xml:space="preserve">47.3727798461914</t>
   </si>
   <si>
-    <t xml:space="preserve">46.6132888793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.4867362976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5373916625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.5183944702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.0753784179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5627326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.2146453857422</t>
+    <t xml:space="preserve">46.6132926940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.4867477416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5373802185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.5183982849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.075382232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5627288818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2146492004395</t>
   </si>
   <si>
     <t xml:space="preserve">41.8475379943848</t>
@@ -1682,28 +1682,28 @@
     <t xml:space="preserve">42.4551277160645</t>
   </si>
   <si>
-    <t xml:space="preserve">40.2526206970215</t>
+    <t xml:space="preserve">40.2526245117188</t>
   </si>
   <si>
     <t xml:space="preserve">41.8095588684082</t>
   </si>
   <si>
-    <t xml:space="preserve">43.195613861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.0310478210449</t>
+    <t xml:space="preserve">43.1956214904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.0310516357422</t>
   </si>
   <si>
     <t xml:space="preserve">44.3158569335938</t>
   </si>
   <si>
-    <t xml:space="preserve">44.3348426818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8791580200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7398910522461</t>
+    <t xml:space="preserve">44.334846496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8791542053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7398872375488</t>
   </si>
   <si>
     <t xml:space="preserve">45.8348197937012</t>
@@ -1712,37 +1712,37 @@
     <t xml:space="preserve">46.8031616210938</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3854522705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.4234237670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1829109191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.1765480041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.3696022033691</t>
+    <t xml:space="preserve">46.3854484558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.4234275817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1829071044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.1765518188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.3695983886719</t>
   </si>
   <si>
     <t xml:space="preserve">45.436092376709</t>
   </si>
   <si>
-    <t xml:space="preserve">45.0753364562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.6449546813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.2588539123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.4645385742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8885688781738</t>
+    <t xml:space="preserve">45.0753402709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.6449584960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.2588500976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.4645347595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8885612487793</t>
   </si>
   <si>
     <t xml:space="preserve">50.125904083252</t>
@@ -1751,10 +1751,10 @@
     <t xml:space="preserve">50.6955184936523</t>
   </si>
   <si>
-    <t xml:space="preserve">50.2208366394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.9360313415527</t>
+    <t xml:space="preserve">50.2208404541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.9360275268555</t>
   </si>
   <si>
     <t xml:space="preserve">50.0784378051758</t>
@@ -1763,22 +1763,22 @@
     <t xml:space="preserve">52.1670150756836</t>
   </si>
   <si>
-    <t xml:space="preserve">52.6891632080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9739646911621</t>
+    <t xml:space="preserve">52.6891593933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9739685058594</t>
   </si>
   <si>
     <t xml:space="preserve">54.2555961608887</t>
   </si>
   <si>
-    <t xml:space="preserve">53.2587776184082</t>
+    <t xml:space="preserve">53.2587699890137</t>
   </si>
   <si>
     <t xml:space="preserve">53.9707870483398</t>
   </si>
   <si>
-    <t xml:space="preserve">53.7334480285645</t>
+    <t xml:space="preserve">53.7334518432617</t>
   </si>
   <si>
     <t xml:space="preserve">55.2998847961426</t>
@@ -1787,40 +1787,40 @@
     <t xml:space="preserve">54.3979988098145</t>
   </si>
   <si>
-    <t xml:space="preserve">53.4011764526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.9233131408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4929389953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.4454612731934</t>
+    <t xml:space="preserve">53.4011726379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.9233207702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4929275512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.4454689025879</t>
   </si>
   <si>
     <t xml:space="preserve">53.4961090087891</t>
   </si>
   <si>
-    <t xml:space="preserve">54.6353378295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.9644355773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.7270927429199</t>
+    <t xml:space="preserve">54.6353340148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.964427947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.7270965576172</t>
   </si>
   <si>
     <t xml:space="preserve">56.1068382263184</t>
   </si>
   <si>
-    <t xml:space="preserve">55.5328483581543</t>
+    <t xml:space="preserve">55.5328559875488</t>
   </si>
   <si>
     <t xml:space="preserve">53.5239143371582</t>
   </si>
   <si>
-    <t xml:space="preserve">53.5717468261719</t>
+    <t xml:space="preserve">53.5717430114746</t>
   </si>
   <si>
     <t xml:space="preserve">52.6151084899902</t>
@@ -1832,43 +1832,43 @@
     <t xml:space="preserve">51.4671363830566</t>
   </si>
   <si>
-    <t xml:space="preserve">54.5283889770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.9633369445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0590019226074</t>
+    <t xml:space="preserve">54.5283851623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.9633407592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0589981079102</t>
   </si>
   <si>
     <t xml:space="preserve">55.1980285644531</t>
   </si>
   <si>
-    <t xml:space="preserve">56.7764854431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0111694335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.6285171508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.2025032043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.9155082702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4416580200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.5806884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.3459968566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.1501998901367</t>
+    <t xml:space="preserve">56.7764778137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0111656188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.6285133361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.2024993896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.9155120849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4416542053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.580680847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.3460006713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.1501960754395</t>
   </si>
   <si>
     <t xml:space="preserve">54.5762138366699</t>
@@ -1877,31 +1877,31 @@
     <t xml:space="preserve">54.4327201843262</t>
   </si>
   <si>
-    <t xml:space="preserve">54.8632011413574</t>
+    <t xml:space="preserve">54.8632049560547</t>
   </si>
   <si>
     <t xml:space="preserve">56.919979095459</t>
   </si>
   <si>
-    <t xml:space="preserve">56.8243179321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.2548027038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.6808166503906</t>
+    <t xml:space="preserve">56.8243141174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.2547988891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.6808242797852</t>
   </si>
   <si>
     <t xml:space="preserve">56.7286491394043</t>
   </si>
   <si>
-    <t xml:space="preserve">58.2114410400391</t>
+    <t xml:space="preserve">58.2114372253418</t>
   </si>
   <si>
     <t xml:space="preserve">57.6374549865723</t>
   </si>
   <si>
-    <t xml:space="preserve">58.546257019043</t>
+    <t xml:space="preserve">58.5462646484375</t>
   </si>
   <si>
     <t xml:space="preserve">57.924446105957</t>
@@ -1919,25 +1919,25 @@
     <t xml:space="preserve">58.3071060180664</t>
   </si>
   <si>
-    <t xml:space="preserve">60.2682113647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.172550201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.7420616149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.2159080505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.1202430725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.3026351928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.8287887573242</t>
+    <t xml:space="preserve">60.2682151794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.1725463867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.742057800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.2159156799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.120246887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.3026313781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.828784942627</t>
   </si>
   <si>
     <t xml:space="preserve">58.115779876709</t>
@@ -1946,49 +1946,49 @@
     <t xml:space="preserve">57.7809562683105</t>
   </si>
   <si>
-    <t xml:space="preserve">59.024585723877</t>
+    <t xml:space="preserve">59.0245819091797</t>
   </si>
   <si>
     <t xml:space="preserve">59.4550704956055</t>
   </si>
   <si>
-    <t xml:space="preserve">60.3160438537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.0290489196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.0724105834961</t>
+    <t xml:space="preserve">60.316047668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.029052734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.0724143981934</t>
   </si>
   <si>
     <t xml:space="preserve">58.2592735290527</t>
   </si>
   <si>
-    <t xml:space="preserve">58.0201110839844</t>
+    <t xml:space="preserve">58.0201148986816</t>
   </si>
   <si>
     <t xml:space="preserve">50.9888191223145</t>
   </si>
   <si>
-    <t xml:space="preserve">50.4148406982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2279777526855</t>
+    <t xml:space="preserve">50.4148368835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2279853820801</t>
   </si>
   <si>
     <t xml:space="preserve">51.3236465454102</t>
   </si>
   <si>
-    <t xml:space="preserve">50.8931541442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.793025970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.8408508300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.6928863525391</t>
+    <t xml:space="preserve">50.8931579589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7930221557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.8408470153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.6928901672363</t>
   </si>
   <si>
     <t xml:space="preserve">49.2668724060059</t>
@@ -2000,10 +2000,10 @@
     <t xml:space="preserve">49.9365196228027</t>
   </si>
   <si>
-    <t xml:space="preserve">50.0800132751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6539993286133</t>
+    <t xml:space="preserve">50.0800170898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.653995513916</t>
   </si>
   <si>
     <t xml:space="preserve">50.2235107421875</t>
@@ -2012,19 +2012,19 @@
     <t xml:space="preserve">50.845329284668</t>
   </si>
   <si>
-    <t xml:space="preserve">51.4193115234375</t>
+    <t xml:space="preserve">51.419303894043</t>
   </si>
   <si>
     <t xml:space="preserve">50.940990447998</t>
   </si>
   <si>
-    <t xml:space="preserve">51.514965057373</t>
+    <t xml:space="preserve">51.5149726867676</t>
   </si>
   <si>
     <t xml:space="preserve">50.797492980957</t>
   </si>
   <si>
-    <t xml:space="preserve">51.1323204040527</t>
+    <t xml:space="preserve">51.1323165893555</t>
   </si>
   <si>
     <t xml:space="preserve">49.6973609924316</t>
@@ -2033,28 +2033,28 @@
     <t xml:space="preserve">49.3147048950195</t>
   </si>
   <si>
-    <t xml:space="preserve">49.4582023620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.745189666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.0321769714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.8363876342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.5972213745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.3625373840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0022315979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.4282417297363</t>
+    <t xml:space="preserve">49.458194732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7451934814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.0321846008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.8363838195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.597225189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.3625335693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0022277832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.4282531738281</t>
   </si>
   <si>
     <t xml:space="preserve">54.2892227172852</t>
@@ -2063,10 +2063,10 @@
     <t xml:space="preserve">54.1935615539551</t>
   </si>
   <si>
-    <t xml:space="preserve">53.0934257507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.471607208252</t>
+    <t xml:space="preserve">53.0934219360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.4716110229492</t>
   </si>
   <si>
     <t xml:space="preserve">53.2847518920898</t>
@@ -2075,10 +2075,10 @@
     <t xml:space="preserve">54.0978965759277</t>
   </si>
   <si>
-    <t xml:space="preserve">54.9110412597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.3370475769043</t>
+    <t xml:space="preserve">54.9110336303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3370513916016</t>
   </si>
   <si>
     <t xml:space="preserve">53.8587341308594</t>
@@ -2090,10 +2090,10 @@
     <t xml:space="preserve">55.0545349121094</t>
   </si>
   <si>
-    <t xml:space="preserve">55.3415260314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55.8676834106445</t>
+    <t xml:space="preserve">55.3415222167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55.8676795959473</t>
   </si>
   <si>
     <t xml:space="preserve">56.5373229980469</t>
@@ -2105,22 +2105,22 @@
     <t xml:space="preserve">58.4027709960938</t>
   </si>
   <si>
-    <t xml:space="preserve">58.067943572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.6942329406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.3115768432617</t>
+    <t xml:space="preserve">58.0679473876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.6942291259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.3115730285645</t>
   </si>
   <si>
     <t xml:space="preserve">62.8511352539062</t>
   </si>
   <si>
-    <t xml:space="preserve">63.6164474487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.3383941650391</t>
+    <t xml:space="preserve">63.6164436340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.3384017944336</t>
   </si>
   <si>
     <t xml:space="preserve">66.3428649902344</t>
@@ -2132,7 +2132,7 @@
     <t xml:space="preserve">67.9213256835938</t>
   </si>
   <si>
-    <t xml:space="preserve">69.260612487793</t>
+    <t xml:space="preserve">69.2606201171875</t>
   </si>
   <si>
     <t xml:space="preserve">69.0692825317383</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">68.0169830322266</t>
   </si>
   <si>
-    <t xml:space="preserve">66.869026184082</t>
+    <t xml:space="preserve">66.869010925293</t>
   </si>
   <si>
     <t xml:space="preserve">67.2994995117188</t>
@@ -2162,10 +2162,10 @@
     <t xml:space="preserve">68.4474716186523</t>
   </si>
   <si>
-    <t xml:space="preserve">67.8734817504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.7778167724609</t>
+    <t xml:space="preserve">67.8734893798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.7778244018555</t>
   </si>
   <si>
     <t xml:space="preserve">67.0603408813477</t>
@@ -2177,28 +2177,28 @@
     <t xml:space="preserve">66.4385223388672</t>
   </si>
   <si>
-    <t xml:space="preserve">65.5775527954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.9123764038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.2516632080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.8256454467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.6343231201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">65.7688751220703</t>
+    <t xml:space="preserve">65.5775604248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.9123840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.2516784667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.8256530761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.6343307495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.7688827514648</t>
   </si>
   <si>
     <t xml:space="preserve">66.1036987304688</t>
   </si>
   <si>
-    <t xml:space="preserve">69.4519424438477</t>
+    <t xml:space="preserve">69.4519348144531</t>
   </si>
   <si>
     <t xml:space="preserve">68.2083129882812</t>
@@ -2207,16 +2207,16 @@
     <t xml:space="preserve">70.3129119873047</t>
   </si>
   <si>
-    <t xml:space="preserve">73.3263244628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.2306671142578</t>
+    <t xml:space="preserve">73.3263168334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.2306594848633</t>
   </si>
   <si>
     <t xml:space="preserve">74.0916290283203</t>
   </si>
   <si>
-    <t xml:space="preserve">73.6611557006836</t>
+    <t xml:space="preserve">73.6611480712891</t>
   </si>
   <si>
     <t xml:space="preserve">73.374153137207</t>
@@ -2228,31 +2228,31 @@
     <t xml:space="preserve">70.7912368774414</t>
   </si>
   <si>
-    <t xml:space="preserve">72.4653472900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.2650756835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.638801574707</t>
+    <t xml:space="preserve">72.4653549194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.2650909423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.6387939453125</t>
   </si>
   <si>
     <t xml:space="preserve">71.3173904418945</t>
   </si>
   <si>
-    <t xml:space="preserve">71.9392013549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.7045135498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.7523345947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72.6088485717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.4264602661133</t>
+    <t xml:space="preserve">71.9391937255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.7045059204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.7523498535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72.6088409423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.4264678955078</t>
   </si>
   <si>
     <t xml:space="preserve">74.1394653320312</t>
@@ -2261,16 +2261,16 @@
     <t xml:space="preserve">71.7478637695312</t>
   </si>
   <si>
-    <t xml:space="preserve">71.9870376586914</t>
+    <t xml:space="preserve">71.9870300292969</t>
   </si>
   <si>
     <t xml:space="preserve">73.2784957885742</t>
   </si>
   <si>
-    <t xml:space="preserve">71.4130554199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.821174621582</t>
+    <t xml:space="preserve">71.4130477905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.8211822509766</t>
   </si>
   <si>
     <t xml:space="preserve">65.7210464477539</t>
@@ -2279,16 +2279,16 @@
     <t xml:space="preserve">62.1336517333984</t>
   </si>
   <si>
-    <t xml:space="preserve">63.8077621459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8945007324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.9378623962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57.8766174316406</t>
+    <t xml:space="preserve">63.8077697753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.8944931030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.937858581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57.8766136169434</t>
   </si>
   <si>
     <t xml:space="preserve">52.5672721862793</t>
@@ -2297,31 +2297,31 @@
     <t xml:space="preserve">52.0889549255371</t>
   </si>
   <si>
-    <t xml:space="preserve">46.3778228759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">48.74072265625</t>
+    <t xml:space="preserve">46.3778266906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48.7407188415527</t>
   </si>
   <si>
     <t xml:space="preserve">45.4594535827637</t>
   </si>
   <si>
-    <t xml:space="preserve">41.7094306945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43.8714370727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.2107238769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.344654083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1048698425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.0844841003418</t>
+    <t xml:space="preserve">41.7094268798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.8714256286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.2107276916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.3446578979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1048736572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.0844879150391</t>
   </si>
   <si>
     <t xml:space="preserve">49.2190399169922</t>
@@ -2330,58 +2330,58 @@
     <t xml:space="preserve">59.1680793762207</t>
   </si>
   <si>
-    <t xml:space="preserve">57.6852874755859</t>
+    <t xml:space="preserve">57.6852912902832</t>
   </si>
   <si>
     <t xml:space="preserve">59.263744354248</t>
   </si>
   <si>
-    <t xml:space="preserve">61.0813484191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.3638725280762</t>
+    <t xml:space="preserve">61.081356048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.3638801574707</t>
   </si>
   <si>
     <t xml:space="preserve">61.1291885375977</t>
   </si>
   <si>
-    <t xml:space="preserve">61.4161720275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.6598167419434</t>
+    <t xml:space="preserve">61.4161758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.6598091125488</t>
   </si>
   <si>
     <t xml:space="preserve">63.5207901000977</t>
   </si>
   <si>
-    <t xml:space="preserve">62.5641403198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.1381187438965</t>
+    <t xml:space="preserve">62.5641441345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.138126373291</t>
   </si>
   <si>
     <t xml:space="preserve">63.0424690246582</t>
   </si>
   <si>
-    <t xml:space="preserve">61.9901695251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.0335273742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.2684898376465</t>
+    <t xml:space="preserve">61.9901657104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.033519744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.2684860229492</t>
   </si>
   <si>
     <t xml:space="preserve">60.9081382751465</t>
   </si>
   <si>
-    <t xml:space="preserve">61.7279624938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">63.7051887512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.717903137207</t>
+    <t xml:space="preserve">61.7279586791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.705192565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.7179107666016</t>
   </si>
   <si>
     <t xml:space="preserve">63.3676109313965</t>
@@ -2390,34 +2390,34 @@
     <t xml:space="preserve">63.6569557189941</t>
   </si>
   <si>
-    <t xml:space="preserve">64.0909881591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.4285659790039</t>
+    <t xml:space="preserve">64.0909805297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">64.4285583496094</t>
   </si>
   <si>
     <t xml:space="preserve">64.9108123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">68.4312286376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.0936584472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.3830032348633</t>
+    <t xml:space="preserve">68.4312362670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.0936508178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.3830108642578</t>
   </si>
   <si>
     <t xml:space="preserve">68.624137878418</t>
   </si>
   <si>
-    <t xml:space="preserve">69.9744338989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.3983993530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.1217803955078</t>
+    <t xml:space="preserve">69.9744415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.3983917236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.1217727661133</t>
   </si>
   <si>
     <t xml:space="preserve">73.9288787841797</t>
@@ -2426,19 +2426,19 @@
     <t xml:space="preserve">74.3628997802734</t>
   </si>
   <si>
-    <t xml:space="preserve">75.8578872680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">74.6522521972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.8552093505859</t>
+    <t xml:space="preserve">75.8578720092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">74.6522598266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.8552017211914</t>
   </si>
   <si>
     <t xml:space="preserve">70.6013565063477</t>
   </si>
   <si>
-    <t xml:space="preserve">71.1318283081055</t>
+    <t xml:space="preserve">71.1318206787109</t>
   </si>
   <si>
     <t xml:space="preserve">70.2155609130859</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">65.9235305786133</t>
   </si>
   <si>
-    <t xml:space="preserve">67.03271484375</t>
+    <t xml:space="preserve">67.0326995849609</t>
   </si>
   <si>
     <t xml:space="preserve">67.2256088256836</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">66.5504608154297</t>
   </si>
   <si>
-    <t xml:space="preserve">67.3220596313477</t>
+    <t xml:space="preserve">67.3220520019531</t>
   </si>
   <si>
     <t xml:space="preserve">69.9262084960938</t>
@@ -2468,43 +2468,43 @@
     <t xml:space="preserve">71.1800537109375</t>
   </si>
   <si>
-    <t xml:space="preserve">70.4084548950195</t>
+    <t xml:space="preserve">70.408447265625</t>
   </si>
   <si>
     <t xml:space="preserve">71.3729553222656</t>
   </si>
   <si>
-    <t xml:space="preserve">69.4921798706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.31201171875</t>
+    <t xml:space="preserve">69.4921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.3120040893555</t>
   </si>
   <si>
     <t xml:space="preserve">68.5276870727539</t>
   </si>
   <si>
-    <t xml:space="preserve">68.2865676879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68.6723556518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">69.0099334716797</t>
+    <t xml:space="preserve">68.2865600585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68.67236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.0099258422852</t>
   </si>
   <si>
     <t xml:space="preserve">69.2992782592773</t>
   </si>
   <si>
-    <t xml:space="preserve">72.1445617675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.2765121459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.8069839477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70.1673278808594</t>
+    <t xml:space="preserve">72.1445541381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.276496887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.8069763183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.1673355102539</t>
   </si>
   <si>
     <t xml:space="preserve">70.5531311035156</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">70.3602294921875</t>
   </si>
   <si>
-    <t xml:space="preserve">71.6623077392578</t>
+    <t xml:space="preserve">71.6623153686523</t>
   </si>
   <si>
     <t xml:space="preserve">72.3374557495117</t>
@@ -2522,19 +2522,19 @@
     <t xml:space="preserve">72.8679351806641</t>
   </si>
   <si>
-    <t xml:space="preserve">73.4466323852539</t>
+    <t xml:space="preserve">73.4466247558594</t>
   </si>
   <si>
     <t xml:space="preserve">73.5430755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">71.999885559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.0608291625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.6877593994141</t>
+    <t xml:space="preserve">71.9998779296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.0608367919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.6877517700195</t>
   </si>
   <si>
     <t xml:space="preserve">73.5913009643555</t>
@@ -2546,22 +2546,22 @@
     <t xml:space="preserve">74.7487030029297</t>
   </si>
   <si>
-    <t xml:space="preserve">81.9342193603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.9469528198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.1170654296875</t>
+    <t xml:space="preserve">81.9342269897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.9469375610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.117073059082</t>
   </si>
   <si>
     <t xml:space="preserve">86.0815734863281</t>
   </si>
   <si>
-    <t xml:space="preserve">85.3582000732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.1398544311523</t>
+    <t xml:space="preserve">85.3581924438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.1398468017578</t>
   </si>
   <si>
     <t xml:space="preserve">81.017951965332</t>
@@ -2576,13 +2576,13 @@
     <t xml:space="preserve">80.8732757568359</t>
   </si>
   <si>
-    <t xml:space="preserve">83.0916137695312</t>
+    <t xml:space="preserve">83.0916213989258</t>
   </si>
   <si>
     <t xml:space="preserve">85.3099594116211</t>
   </si>
   <si>
-    <t xml:space="preserve">84.5865859985352</t>
+    <t xml:space="preserve">84.5865936279297</t>
   </si>
   <si>
     <t xml:space="preserve">84.6348266601562</t>
@@ -2591,19 +2591,19 @@
     <t xml:space="preserve">83.6703186035156</t>
   </si>
   <si>
-    <t xml:space="preserve">84.7795028686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.6830444335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.3836517333984</t>
+    <t xml:space="preserve">84.7794952392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.6830596923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.3836441040039</t>
   </si>
   <si>
     <t xml:space="preserve">86.2262496948242</t>
   </si>
   <si>
-    <t xml:space="preserve">87.7212219238281</t>
+    <t xml:space="preserve">87.7212142944336</t>
   </si>
   <si>
     <t xml:space="preserve">89.6984405517578</t>
@@ -2612,10 +2612,10 @@
     <t xml:space="preserve">89.3126449584961</t>
   </si>
   <si>
-    <t xml:space="preserve">90.6629409790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.1070251464844</t>
+    <t xml:space="preserve">90.6629486083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.1070175170898</t>
   </si>
   <si>
     <t xml:space="preserve">87.8658981323242</t>
@@ -2624,34 +2624,34 @@
     <t xml:space="preserve">91.2416458129883</t>
   </si>
   <si>
-    <t xml:space="preserve">90.2771453857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.5664978027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.8076095581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.9777374267578</t>
+    <t xml:space="preserve">90.2771301269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.5664901733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8076248168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.9777450561523</t>
   </si>
   <si>
     <t xml:space="preserve">95.0031890869141</t>
   </si>
   <si>
-    <t xml:space="preserve">94.90673828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.7265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.218879699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.5082092285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4827651977539</t>
+    <t xml:space="preserve">94.9067459106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.7265701293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.2188720703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.5082244873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4827728271484</t>
   </si>
   <si>
     <t xml:space="preserve">89.939567565918</t>
@@ -2660,61 +2660,61 @@
     <t xml:space="preserve">91.62744140625</t>
   </si>
   <si>
-    <t xml:space="preserve">92.1096954345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.3635406494141</t>
+    <t xml:space="preserve">92.1096878051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.3635482788086</t>
   </si>
   <si>
     <t xml:space="preserve">95.5336685180664</t>
   </si>
   <si>
-    <t xml:space="preserve">94.954963684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.8102951049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.6046676635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.5209503173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.6884002685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.4345397949219</t>
+    <t xml:space="preserve">94.9549560546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.8102874755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.6046752929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.5209350585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.6883850097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4345474243164</t>
   </si>
   <si>
     <t xml:space="preserve">93.0259628295898</t>
   </si>
   <si>
-    <t xml:space="preserve">95.2925491333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.2215347290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.115036010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.7292404174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.6073455810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.8966827392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.3789443969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.3052597045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.7493362426758</t>
+    <t xml:space="preserve">95.2925415039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.2215423583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.115043640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.7292327880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.6073303222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.8966903686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3789367675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.3052673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7493438720703</t>
   </si>
   <si>
     <t xml:space="preserve">92.8330612182617</t>
@@ -2723,16 +2723,16 @@
     <t xml:space="preserve">92.8812942504883</t>
   </si>
   <si>
-    <t xml:space="preserve">88.4445953369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88.2034530639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.0233001708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.1324615478516</t>
+    <t xml:space="preserve">88.4445877075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.2034683227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.0232925415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.132453918457</t>
   </si>
   <si>
     <t xml:space="preserve">92.2061386108398</t>
@@ -2747,31 +2747,31 @@
     <t xml:space="preserve">95.7747955322266</t>
   </si>
   <si>
-    <t xml:space="preserve">92.4472579956055</t>
+    <t xml:space="preserve">92.447265625</t>
   </si>
   <si>
     <t xml:space="preserve">92.0614624023438</t>
   </si>
   <si>
-    <t xml:space="preserve">91.8685607910156</t>
+    <t xml:space="preserve">91.8685684204102</t>
   </si>
   <si>
     <t xml:space="preserve">91.8203430175781</t>
   </si>
   <si>
-    <t xml:space="preserve">90.711181640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90.855842590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.3863220214844</t>
+    <t xml:space="preserve">90.7111663818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.8558349609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.3863296508789</t>
   </si>
   <si>
     <t xml:space="preserve">90.7593994140625</t>
   </si>
   <si>
-    <t xml:space="preserve">87.7694396972656</t>
+    <t xml:space="preserve">87.7694473266602</t>
   </si>
   <si>
     <t xml:space="preserve">88.2516937255859</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">90.3735885620117</t>
   </si>
   <si>
-    <t xml:space="preserve">94.2798156738281</t>
+    <t xml:space="preserve">94.2798233032227</t>
   </si>
   <si>
     <t xml:space="preserve">90.0842437744141</t>
@@ -2792,40 +2792,40 @@
     <t xml:space="preserve">91.1451873779297</t>
   </si>
   <si>
-    <t xml:space="preserve">92.4954986572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">89.4573287963867</t>
+    <t xml:space="preserve">92.495491027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.4573211669922</t>
   </si>
   <si>
     <t xml:space="preserve">91.675666809082</t>
   </si>
   <si>
-    <t xml:space="preserve">91.9167938232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.7238845825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.0969619750977</t>
+    <t xml:space="preserve">91.9168014526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7238922119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.0969696044922</t>
   </si>
   <si>
     <t xml:space="preserve">90.9040679931641</t>
   </si>
   <si>
-    <t xml:space="preserve">92.3508224487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.4599838256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92.5437164306641</t>
+    <t xml:space="preserve">92.3508148193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.4599914550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.5437088012695</t>
   </si>
   <si>
     <t xml:space="preserve">95.9194641113281</t>
   </si>
   <si>
-    <t xml:space="preserve">93.26708984375</t>
+    <t xml:space="preserve">93.2670822143555</t>
   </si>
   <si>
     <t xml:space="preserve">93.5564422607422</t>
@@ -2834,67 +2834,67 @@
     <t xml:space="preserve">94.5691680908203</t>
   </si>
   <si>
-    <t xml:space="preserve">96.0641326904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.4753952026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.018577575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.1860427856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">97.4144439697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.790191650391</t>
+    <t xml:space="preserve">96.0641403198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.4753875732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.018585205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.1860504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.414436340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.790184020996</t>
   </si>
   <si>
     <t xml:space="preserve">102.912078857422</t>
   </si>
   <si>
-    <t xml:space="preserve">101.465339660645</t>
+    <t xml:space="preserve">101.46533203125</t>
   </si>
   <si>
     <t xml:space="preserve">102.719184875488</t>
   </si>
   <si>
-    <t xml:space="preserve">102.526290893555</t>
+    <t xml:space="preserve">102.526298522949</t>
   </si>
   <si>
     <t xml:space="preserve">102.140487670898</t>
   </si>
   <si>
-    <t xml:space="preserve">104.937538146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.104995727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.587242126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.815635681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.201431274414</t>
+    <t xml:space="preserve">104.937530517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.104988098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.58723449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.815628051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.201438903809</t>
   </si>
   <si>
     <t xml:space="preserve">100.500831604004</t>
   </si>
   <si>
-    <t xml:space="preserve">100.404396057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.5718307495117</t>
+    <t xml:space="preserve">100.404388427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.5718383789062</t>
   </si>
   <si>
     <t xml:space="preserve">95.0514221191406</t>
   </si>
   <si>
-    <t xml:space="preserve">94.135139465332</t>
+    <t xml:space="preserve">94.1351470947266</t>
   </si>
   <si>
     <t xml:space="preserve">92.5919418334961</t>
@@ -2903,10 +2903,10 @@
     <t xml:space="preserve">89.216194152832</t>
   </si>
   <si>
-    <t xml:space="preserve">103.297889709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.3434448242188</t>
+    <t xml:space="preserve">103.297897338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.3434371948242</t>
   </si>
   <si>
     <t xml:space="preserve">101.561790466309</t>
@@ -2927,10 +2927,10 @@
     <t xml:space="preserve">104.069488525391</t>
   </si>
   <si>
-    <t xml:space="preserve">108.023933410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.145835876465</t>
+    <t xml:space="preserve">108.02392578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.145820617676</t>
   </si>
   <si>
     <t xml:space="preserve">108.699073791504</t>
@@ -2939,10 +2939,10 @@
     <t xml:space="preserve">106.287826538086</t>
   </si>
   <si>
-    <t xml:space="preserve">107.44522857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.38427734375</t>
+    <t xml:space="preserve">107.445236206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.384284973145</t>
   </si>
   <si>
     <t xml:space="preserve">108.891983032227</t>
@@ -2951,25 +2951,25 @@
     <t xml:space="preserve">107.831039428711</t>
   </si>
   <si>
-    <t xml:space="preserve">108.795547485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.084884643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.059432983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.348793029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.567123413086</t>
+    <t xml:space="preserve">108.795539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.08487701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.059425354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.348785400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.56713104248</t>
   </si>
   <si>
     <t xml:space="preserve">108.50617980957</t>
   </si>
   <si>
-    <t xml:space="preserve">109.53076171875</t>
+    <t xml:space="preserve">109.530754089355</t>
   </si>
   <si>
     <t xml:space="preserve">107.786018371582</t>
@@ -2981,16 +2981,16 @@
     <t xml:space="preserve">109.046104431152</t>
   </si>
   <si>
-    <t xml:space="preserve">109.918487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.500061035156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.821548461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.887771606445</t>
+    <t xml:space="preserve">109.918479919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.500068664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.82154083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.88777923584</t>
   </si>
   <si>
     <t xml:space="preserve">111.663208007812</t>
@@ -2999,7 +2999,7 @@
     <t xml:space="preserve">113.117164611816</t>
   </si>
   <si>
-    <t xml:space="preserve">115.831192016602</t>
+    <t xml:space="preserve">115.831199645996</t>
   </si>
   <si>
     <t xml:space="preserve">113.795669555664</t>
@@ -3011,10 +3011,10 @@
     <t xml:space="preserve">114.668045043945</t>
   </si>
   <si>
-    <t xml:space="preserve">114.280326843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.474174499512</t>
+    <t xml:space="preserve">114.280319213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.474182128906</t>
   </si>
   <si>
     <t xml:space="preserve">116.509696960449</t>
@@ -3029,58 +3029,58 @@
     <t xml:space="preserve">128.819793701172</t>
   </si>
   <si>
-    <t xml:space="preserve">127.365844726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.268936157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">128.432067871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.181640625</t>
+    <t xml:space="preserve">127.365852355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.268928527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.432083129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.181655883789</t>
   </si>
   <si>
     <t xml:space="preserve">130.467620849609</t>
   </si>
   <si>
-    <t xml:space="preserve">130.27375793457</t>
+    <t xml:space="preserve">130.273742675781</t>
   </si>
   <si>
     <t xml:space="preserve">128.916732788086</t>
   </si>
   <si>
-    <t xml:space="preserve">134.635604858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.701812744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.441741943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.375503540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.798751831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.314117431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.574188232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.212341308594</t>
+    <t xml:space="preserve">134.635589599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.70182800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.44172668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.375518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.798767089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.314102172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.574203491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.212356567383</t>
   </si>
   <si>
     <t xml:space="preserve">135.023315429688</t>
   </si>
   <si>
-    <t xml:space="preserve">133.763214111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.446563720703</t>
+    <t xml:space="preserve">133.763229370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.446578979492</t>
   </si>
   <si>
     <t xml:space="preserve">135.89567565918</t>
@@ -3092,25 +3092,25 @@
     <t xml:space="preserve">138.22200012207</t>
   </si>
   <si>
-    <t xml:space="preserve">142.293060302734</t>
+    <t xml:space="preserve">142.293075561523</t>
   </si>
   <si>
     <t xml:space="preserve">141.032974243164</t>
   </si>
   <si>
-    <t xml:space="preserve">143.359283447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.063659667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.803558349609</t>
+    <t xml:space="preserve">143.359268188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.063674926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.803573608398</t>
   </si>
   <si>
     <t xml:space="preserve">140.548324584961</t>
   </si>
   <si>
-    <t xml:space="preserve">140.160614013672</t>
+    <t xml:space="preserve">140.160598754883</t>
   </si>
   <si>
     <t xml:space="preserve">139.579025268555</t>
@@ -3122,31 +3122,31 @@
     <t xml:space="preserve">138.609710693359</t>
   </si>
   <si>
-    <t xml:space="preserve">135.992630004883</t>
+    <t xml:space="preserve">135.992614746094</t>
   </si>
   <si>
     <t xml:space="preserve">137.640426635742</t>
   </si>
   <si>
-    <t xml:space="preserve">139.094375610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.226837158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142.583847045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.905319213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">143.262359619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142.486907958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.073318481445</t>
+    <t xml:space="preserve">139.094360351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.226821899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142.583862304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.905334472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">143.262344360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142.486923217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.073303222656</t>
   </si>
   <si>
     <t xml:space="preserve">148.884292602539</t>
@@ -3155,22 +3155,22 @@
     <t xml:space="preserve">148.011917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">149.175064086914</t>
+    <t xml:space="preserve">149.175079345703</t>
   </si>
   <si>
     <t xml:space="preserve">149.75666809082</t>
   </si>
   <si>
-    <t xml:space="preserve">146.364120483398</t>
+    <t xml:space="preserve">146.364105224609</t>
   </si>
   <si>
     <t xml:space="preserve">147.236465454102</t>
   </si>
   <si>
-    <t xml:space="preserve">148.205749511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.818054199219</t>
+    <t xml:space="preserve">148.205764770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.81803894043</t>
   </si>
   <si>
     <t xml:space="preserve">150.532104492188</t>
@@ -3182,61 +3182,61 @@
     <t xml:space="preserve">155.087799072266</t>
   </si>
   <si>
-    <t xml:space="preserve">154.893936157227</t>
+    <t xml:space="preserve">154.893951416016</t>
   </si>
   <si>
     <t xml:space="preserve">152.955337524414</t>
   </si>
   <si>
-    <t xml:space="preserve">157.898773193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">161.679016113281</t>
+    <t xml:space="preserve">157.89875793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">161.67903137207</t>
   </si>
   <si>
     <t xml:space="preserve">166.816314697266</t>
   </si>
   <si>
-    <t xml:space="preserve">166.428588867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">165.847015380859</t>
+    <t xml:space="preserve">166.428573608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">165.847030639648</t>
   </si>
   <si>
     <t xml:space="preserve">165.459289550781</t>
   </si>
   <si>
-    <t xml:space="preserve">165.653137207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.397903442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.851837158203</t>
+    <t xml:space="preserve">165.65315246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.397888183594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.851852416992</t>
   </si>
   <si>
     <t xml:space="preserve">169.142639160156</t>
   </si>
   <si>
-    <t xml:space="preserve">169.62727355957</t>
+    <t xml:space="preserve">169.627288818359</t>
   </si>
   <si>
     <t xml:space="preserve">170.305786132812</t>
   </si>
   <si>
-    <t xml:space="preserve">169.239562988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169.724212646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.948760986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">163.811492919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">167.204055786133</t>
+    <t xml:space="preserve">169.23957824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169.724227905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.948776245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">163.811477661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.204025268555</t>
   </si>
   <si>
     <t xml:space="preserve">165.071578979492</t>
@@ -3245,7 +3245,7 @@
     <t xml:space="preserve">167.979476928711</t>
   </si>
   <si>
-    <t xml:space="preserve">173.989120483398</t>
+    <t xml:space="preserve">173.989135742188</t>
   </si>
   <si>
     <t xml:space="preserve">176.606231689453</t>
@@ -3254,7 +3254,7 @@
     <t xml:space="preserve">171.372024536133</t>
   </si>
   <si>
-    <t xml:space="preserve">152.470672607422</t>
+    <t xml:space="preserve">152.470687866211</t>
   </si>
   <si>
     <t xml:space="preserve">152.567611694336</t>
@@ -3263,19 +3263,19 @@
     <t xml:space="preserve">154.506210327148</t>
   </si>
   <si>
-    <t xml:space="preserve">153.827713012695</t>
+    <t xml:space="preserve">153.827697753906</t>
   </si>
   <si>
     <t xml:space="preserve">149.465866088867</t>
   </si>
   <si>
-    <t xml:space="preserve">153.633865356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.43034362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">147.721130371094</t>
+    <t xml:space="preserve">153.633850097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.430358886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">147.721115112305</t>
   </si>
   <si>
     <t xml:space="preserve">145.97639465332</t>
@@ -3284,43 +3284,43 @@
     <t xml:space="preserve">157.026397705078</t>
   </si>
   <si>
-    <t xml:space="preserve">159.643493652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">162.842208862305</t>
+    <t xml:space="preserve">159.643508911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">162.842193603516</t>
   </si>
   <si>
     <t xml:space="preserve">163.229904174805</t>
   </si>
   <si>
-    <t xml:space="preserve">160.4189453125</t>
+    <t xml:space="preserve">160.418930053711</t>
   </si>
   <si>
     <t xml:space="preserve">161.097457885742</t>
   </si>
   <si>
-    <t xml:space="preserve">160.806671142578</t>
+    <t xml:space="preserve">160.806655883789</t>
   </si>
   <si>
     <t xml:space="preserve">160.61279296875</t>
   </si>
   <si>
-    <t xml:space="preserve">161.582077026367</t>
+    <t xml:space="preserve">161.582092285156</t>
   </si>
   <si>
     <t xml:space="preserve">162.551391601562</t>
   </si>
   <si>
-    <t xml:space="preserve">161.87287902832</t>
+    <t xml:space="preserve">161.872894287109</t>
   </si>
   <si>
     <t xml:space="preserve">164.393081665039</t>
   </si>
   <si>
-    <t xml:space="preserve">171.275085449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.21369934082</t>
+    <t xml:space="preserve">171.27507019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.213684082031</t>
   </si>
   <si>
     <t xml:space="preserve">172.825973510742</t>
@@ -3329,25 +3329,25 @@
     <t xml:space="preserve">174.182983398438</t>
   </si>
   <si>
-    <t xml:space="preserve">171.662796020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">172.341323852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">176.703170776367</t>
+    <t xml:space="preserve">171.662811279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.34130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">176.703155517578</t>
   </si>
   <si>
     <t xml:space="preserve">179.804916381836</t>
   </si>
   <si>
-    <t xml:space="preserve">173.892196655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.754913330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">168.56103515625</t>
+    <t xml:space="preserve">173.892181396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.754928588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.561050415039</t>
   </si>
   <si>
     <t xml:space="preserve">167.010177612305</t>
@@ -3356,7 +3356,7 @@
     <t xml:space="preserve">159.934295654297</t>
   </si>
   <si>
-    <t xml:space="preserve">162.454483032227</t>
+    <t xml:space="preserve">162.454467773438</t>
   </si>
   <si>
     <t xml:space="preserve">159.837356567383</t>
@@ -3377,13 +3377,13 @@
     <t xml:space="preserve">159.158843994141</t>
   </si>
   <si>
-    <t xml:space="preserve">172.535186767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">174.958404541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">173.698333740234</t>
+    <t xml:space="preserve">172.535171508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">174.958435058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">173.698348999023</t>
   </si>
   <si>
     <t xml:space="preserve">174.570724487305</t>
@@ -3392,19 +3392,19 @@
     <t xml:space="preserve">169.43342590332</t>
   </si>
   <si>
-    <t xml:space="preserve">168.076416015625</t>
+    <t xml:space="preserve">168.076385498047</t>
   </si>
   <si>
     <t xml:space="preserve">163.617630004883</t>
   </si>
   <si>
-    <t xml:space="preserve">164.877700805664</t>
+    <t xml:space="preserve">164.877731323242</t>
   </si>
   <si>
     <t xml:space="preserve">163.714553833008</t>
   </si>
   <si>
-    <t xml:space="preserve">170.596572875977</t>
+    <t xml:space="preserve">170.596588134766</t>
   </si>
   <si>
     <t xml:space="preserve">169.821136474609</t>
@@ -3419,10 +3419,10 @@
     <t xml:space="preserve">157.317184448242</t>
   </si>
   <si>
-    <t xml:space="preserve">155.57243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">155.863235473633</t>
+    <t xml:space="preserve">155.572448730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155.863250732422</t>
   </si>
   <si>
     <t xml:space="preserve">155.669387817383</t>
@@ -3437,16 +3437,16 @@
     <t xml:space="preserve">157.220245361328</t>
   </si>
   <si>
-    <t xml:space="preserve">151.113662719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">152.8583984375</t>
+    <t xml:space="preserve">151.113677978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">152.858413696289</t>
   </si>
   <si>
     <t xml:space="preserve">154.990859985352</t>
   </si>
   <si>
-    <t xml:space="preserve">137.931213378906</t>
+    <t xml:space="preserve">137.931228637695</t>
   </si>
   <si>
     <t xml:space="preserve">143.747009277344</t>
@@ -3455,34 +3455,34 @@
     <t xml:space="preserve">143.553146362305</t>
   </si>
   <si>
-    <t xml:space="preserve">144.5224609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">144.91015625</t>
+    <t xml:space="preserve">144.522445678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">144.910171508789</t>
   </si>
   <si>
     <t xml:space="preserve">139.385162353516</t>
   </si>
   <si>
-    <t xml:space="preserve">136.089538574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.600067138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.309280395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.997436523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.834274291992</t>
+    <t xml:space="preserve">136.089553833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.600082397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.309295654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.997421264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.834289550781</t>
   </si>
   <si>
     <t xml:space="preserve">137.543487548828</t>
   </si>
   <si>
-    <t xml:space="preserve">138.125076293945</t>
+    <t xml:space="preserve">138.125061035156</t>
   </si>
   <si>
     <t xml:space="preserve">138.512771606445</t>
@@ -3506,10 +3506,10 @@
     <t xml:space="preserve">142.874618530273</t>
   </si>
   <si>
-    <t xml:space="preserve">149.562805175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">151.986038208008</t>
+    <t xml:space="preserve">149.562789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">151.986053466797</t>
   </si>
   <si>
     <t xml:space="preserve">150.919815063477</t>
@@ -3518,37 +3518,37 @@
     <t xml:space="preserve">149.368942260742</t>
   </si>
   <si>
-    <t xml:space="preserve">146.267166137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">145.10400390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">148.6904296875</t>
+    <t xml:space="preserve">146.267181396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">145.104019165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">148.690399169922</t>
   </si>
   <si>
     <t xml:space="preserve">145.394821166992</t>
   </si>
   <si>
-    <t xml:space="preserve">146.751815795898</t>
+    <t xml:space="preserve">146.751831054688</t>
   </si>
   <si>
     <t xml:space="preserve">149.659729003906</t>
   </si>
   <si>
-    <t xml:space="preserve">145.200942993164</t>
+    <t xml:space="preserve">145.200958251953</t>
   </si>
   <si>
     <t xml:space="preserve">141.517608642578</t>
   </si>
   <si>
-    <t xml:space="preserve">141.323776245117</t>
+    <t xml:space="preserve">141.323760986328</t>
   </si>
   <si>
     <t xml:space="preserve">137.058837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">134.538681030273</t>
+    <t xml:space="preserve">134.538665771484</t>
   </si>
   <si>
     <t xml:space="preserve">136.477264404297</t>
@@ -3560,31 +3560,31 @@
     <t xml:space="preserve">136.186477661133</t>
   </si>
   <si>
-    <t xml:space="preserve">135.217178344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.952285766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.75358581543</t>
+    <t xml:space="preserve">135.217193603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.952270507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.753593444824</t>
   </si>
   <si>
     <t xml:space="preserve">121.162338256836</t>
   </si>
   <si>
-    <t xml:space="preserve">113.60181427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.28515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.958831787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.57593536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.121994018555</t>
+    <t xml:space="preserve">113.601806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.285148620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.958824157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.575942993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.12198638916</t>
   </si>
   <si>
     <t xml:space="preserve">119.708396911621</t>
@@ -3593,7 +3593,7 @@
     <t xml:space="preserve">115.152694702148</t>
   </si>
   <si>
-    <t xml:space="preserve">114.86190032959</t>
+    <t xml:space="preserve">114.861907958984</t>
   </si>
   <si>
     <t xml:space="preserve">115.443481445312</t>
@@ -3605,7 +3605,7 @@
     <t xml:space="preserve">113.003852844238</t>
   </si>
   <si>
-    <t xml:space="preserve">117.102424621582</t>
+    <t xml:space="preserve">117.102432250977</t>
   </si>
   <si>
     <t xml:space="preserve">116.71208190918</t>
@@ -3617,16 +3617,16 @@
     <t xml:space="preserve">124.909255981445</t>
   </si>
   <si>
-    <t xml:space="preserve">123.640647888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.834815979004</t>
+    <t xml:space="preserve">123.640640258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.834823608398</t>
   </si>
   <si>
     <t xml:space="preserve">120.225158691406</t>
   </si>
   <si>
-    <t xml:space="preserve">119.346893310547</t>
+    <t xml:space="preserve">119.346900939941</t>
   </si>
   <si>
     <t xml:space="preserve">121.005844116211</t>
@@ -3635,55 +3635,55 @@
     <t xml:space="preserve">114.857963562012</t>
   </si>
   <si>
-    <t xml:space="preserve">107.5390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.367042541504</t>
+    <t xml:space="preserve">107.539054870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.367034912109</t>
   </si>
   <si>
     <t xml:space="preserve">100.512916564941</t>
   </si>
   <si>
-    <t xml:space="preserve">101.586349487305</t>
+    <t xml:space="preserve">101.586357116699</t>
   </si>
   <si>
     <t xml:space="preserve">99.146728515625</t>
   </si>
   <si>
-    <t xml:space="preserve">103.14771270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.83081817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.075286865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.417327880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.31974029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.418327331543</t>
+    <t xml:space="preserve">103.147720336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.830825805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.07527923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.417335510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.319747924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.418334960938</t>
   </si>
   <si>
     <t xml:space="preserve">113.296600341797</t>
   </si>
   <si>
-    <t xml:space="preserve">115.541061401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.272453308105</t>
+    <t xml:space="preserve">115.541069030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.272445678711</t>
   </si>
   <si>
     <t xml:space="preserve">112.906257629395</t>
   </si>
   <si>
-    <t xml:space="preserve">113.882110595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.247314453125</t>
+    <t xml:space="preserve">113.882102966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.24730682373</t>
   </si>
   <si>
     <t xml:space="preserve">110.661796569824</t>
@@ -3698,31 +3698,31 @@
     <t xml:space="preserve">120.615501403809</t>
   </si>
   <si>
-    <t xml:space="preserve">119.054138183594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.956558227539</t>
+    <t xml:space="preserve">119.054130554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.95654296875</t>
   </si>
   <si>
     <t xml:space="preserve">113.101432800293</t>
   </si>
   <si>
-    <t xml:space="preserve">116.907264709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.469619750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.323753356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.885116577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.006843566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.664794921875</t>
+    <t xml:space="preserve">116.907257080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.469627380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.323745727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.885108947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.006851196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.66478729248</t>
   </si>
   <si>
     <t xml:space="preserve">125.68994140625</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">123.055137634277</t>
   </si>
   <si>
-    <t xml:space="preserve">126.470626831055</t>
+    <t xml:space="preserve">126.470634460449</t>
   </si>
   <si>
     <t xml:space="preserve">122.957550048828</t>
@@ -3749,22 +3749,22 @@
     <t xml:space="preserve">134.082275390625</t>
   </si>
   <si>
-    <t xml:space="preserve">134.960556030273</t>
+    <t xml:space="preserve">134.960540771484</t>
   </si>
   <si>
     <t xml:space="preserve">134.179870605469</t>
   </si>
   <si>
-    <t xml:space="preserve">127.544067382812</t>
+    <t xml:space="preserve">127.544059753418</t>
   </si>
   <si>
     <t xml:space="preserve">126.177871704102</t>
   </si>
   <si>
-    <t xml:space="preserve">121.201011657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120.42032623291</t>
+    <t xml:space="preserve">121.20100402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120.420333862305</t>
   </si>
   <si>
     <t xml:space="preserve">119.151718139648</t>
@@ -3776,10 +3776,10 @@
     <t xml:space="preserve">120.029991149902</t>
   </si>
   <si>
-    <t xml:space="preserve">115.736228942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.955551147461</t>
+    <t xml:space="preserve">115.736236572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.955558776855</t>
   </si>
   <si>
     <t xml:space="preserve">110.271453857422</t>
@@ -3791,10 +3791,10 @@
     <t xml:space="preserve">112.711090087891</t>
   </si>
   <si>
-    <t xml:space="preserve">113.686935424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110.466621398926</t>
+    <t xml:space="preserve">113.686943054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.46662902832</t>
   </si>
   <si>
     <t xml:space="preserve">117.590354919434</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">111.832817077637</t>
   </si>
   <si>
-    <t xml:space="preserve">110.369033813477</t>
+    <t xml:space="preserve">110.369041442871</t>
   </si>
   <si>
     <t xml:space="preserve">105.977699279785</t>
@@ -3821,61 +3821,61 @@
     <t xml:space="preserve">103.928405761719</t>
   </si>
   <si>
-    <t xml:space="preserve">100.70809173584</t>
+    <t xml:space="preserve">100.708084106445</t>
   </si>
   <si>
     <t xml:space="preserve">101.391189575195</t>
   </si>
   <si>
-    <t xml:space="preserve">104.904258728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.51392364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.196014404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.001846313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.734237670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.833824157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">115.150718688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.12557220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.758377075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.440475463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">106.270454406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">108.026992797852</t>
+    <t xml:space="preserve">104.904251098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.513916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.196022033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.001838684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.734230041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.83381652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.150726318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.125579833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.75838470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.440483093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.270462036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.026985168457</t>
   </si>
   <si>
     <t xml:space="preserve">109.100433349609</t>
   </si>
   <si>
-    <t xml:space="preserve">108.514915466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.636657714844</t>
+    <t xml:space="preserve">108.514923095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.636650085449</t>
   </si>
   <si>
     <t xml:space="preserve">109.978691101074</t>
   </si>
   <si>
-    <t xml:space="preserve">108.612510681152</t>
+    <t xml:space="preserve">108.612503051758</t>
   </si>
   <si>
     <t xml:space="preserve">107.441474914551</t>
@@ -3887,28 +3887,28 @@
     <t xml:space="preserve">108.905258178711</t>
   </si>
   <si>
-    <t xml:space="preserve">109.68595123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.320747375488</t>
+    <t xml:space="preserve">109.685935974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.320739746094</t>
   </si>
   <si>
     <t xml:space="preserve">122.274459838867</t>
   </si>
   <si>
-    <t xml:space="preserve">123.738235473633</t>
+    <t xml:space="preserve">123.738227844238</t>
   </si>
   <si>
     <t xml:space="preserve">116.028991699219</t>
   </si>
   <si>
-    <t xml:space="preserve">110.076278686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107.929405212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.223167419434</t>
+    <t xml:space="preserve">110.076286315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.929412841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.223152160645</t>
   </si>
   <si>
     <t xml:space="preserve">109.78352355957</t>
@@ -3917,22 +3917,22 @@
     <t xml:space="preserve">110.856964111328</t>
   </si>
   <si>
-    <t xml:space="preserve">109.588363647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.198020935059</t>
+    <t xml:space="preserve">109.588356018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.198013305664</t>
   </si>
   <si>
     <t xml:space="preserve">110.759384155273</t>
   </si>
   <si>
-    <t xml:space="preserve">117.200012207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.784530639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.587356567383</t>
+    <t xml:space="preserve">117.200019836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.784523010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.587348937988</t>
   </si>
   <si>
     <t xml:space="preserve">107.831817626953</t>
@@ -3944,28 +3944,28 @@
     <t xml:space="preserve">105.099426269531</t>
   </si>
   <si>
-    <t xml:space="preserve">104.221160888672</t>
+    <t xml:space="preserve">104.221168518066</t>
   </si>
   <si>
     <t xml:space="preserve">106.465621948242</t>
   </si>
   <si>
-    <t xml:space="preserve">104.41633605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105.880111694336</t>
+    <t xml:space="preserve">104.416328430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.88011932373</t>
   </si>
   <si>
     <t xml:space="preserve">107.343894958496</t>
   </si>
   <si>
-    <t xml:space="preserve">111.052139282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.467628479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.419342041016</t>
+    <t xml:space="preserve">111.052146911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.467620849609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.419326782227</t>
   </si>
   <si>
     <t xml:space="preserve">117.883117675781</t>
@@ -3974,58 +3974,58 @@
     <t xml:space="preserve">118.761375427246</t>
   </si>
   <si>
-    <t xml:space="preserve">115.931411743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.395195007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.273445129395</t>
+    <t xml:space="preserve">115.93140411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.39518737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.273452758789</t>
   </si>
   <si>
     <t xml:space="preserve">114.760383605957</t>
   </si>
   <si>
-    <t xml:space="preserve">117.98070526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123.933403015137</t>
+    <t xml:space="preserve">117.980697631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123.933410644531</t>
   </si>
   <si>
     <t xml:space="preserve">124.226165771484</t>
   </si>
   <si>
-    <t xml:space="preserve">123.152725219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.493774414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.663795471191</t>
+    <t xml:space="preserve">123.152709960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.493766784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.663787841797</t>
   </si>
   <si>
     <t xml:space="preserve">119.6396484375</t>
   </si>
   <si>
-    <t xml:space="preserve">118.858963012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114.370040893555</t>
+    <t xml:space="preserve">118.85897064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.37003326416</t>
   </si>
   <si>
     <t xml:space="preserve">112.515922546387</t>
   </si>
   <si>
-    <t xml:space="preserve">111.149726867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.199012756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.540061950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112.613502502441</t>
+    <t xml:space="preserve">111.149719238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.199020385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.540069580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.613510131836</t>
   </si>
   <si>
     <t xml:space="preserve">108.124580383301</t>
@@ -4040,13 +4040,13 @@
     <t xml:space="preserve">109.490768432617</t>
   </si>
   <si>
-    <t xml:space="preserve">107.148727416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.58935546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">109.881103515625</t>
+    <t xml:space="preserve">107.148719787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.589363098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.88111114502</t>
   </si>
   <si>
     <t xml:space="preserve">107.051132202148</t>
@@ -4058,37 +4058,37 @@
     <t xml:space="preserve">102.562210083008</t>
   </si>
   <si>
-    <t xml:space="preserve">102.464630126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.683937072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.952560424805</t>
+    <t xml:space="preserve">102.464622497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.683944702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.952545166016</t>
   </si>
   <si>
     <t xml:space="preserve">101.781532287598</t>
   </si>
   <si>
-    <t xml:space="preserve">100.610496520996</t>
+    <t xml:space="preserve">100.610504150391</t>
   </si>
   <si>
     <t xml:space="preserve">103.342895507812</t>
   </si>
   <si>
-    <t xml:space="preserve">101.000846862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.415336608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.074279785156</t>
+    <t xml:space="preserve">101.000839233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.415328979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.074287414551</t>
   </si>
   <si>
     <t xml:space="preserve">103.040893554688</t>
   </si>
   <si>
-    <t xml:space="preserve">103.237915039062</t>
+    <t xml:space="preserve">103.237922668457</t>
   </si>
   <si>
     <t xml:space="preserve">99.3960494995117</t>
@@ -4115,7 +4115,7 @@
     <t xml:space="preserve">103.139404296875</t>
   </si>
   <si>
-    <t xml:space="preserve">102.449844360352</t>
+    <t xml:space="preserve">102.449836730957</t>
   </si>
   <si>
     <t xml:space="preserve">102.351333618164</t>
@@ -4142,7 +4142,7 @@
     <t xml:space="preserve">109.641036987305</t>
   </si>
   <si>
-    <t xml:space="preserve">106.390213012695</t>
+    <t xml:space="preserve">106.39022064209</t>
   </si>
   <si>
     <t xml:space="preserve">101.267730712891</t>
@@ -4154,7 +4154,7 @@
     <t xml:space="preserve">99.1005172729492</t>
   </si>
   <si>
-    <t xml:space="preserve">98.0661773681641</t>
+    <t xml:space="preserve">98.0661697387695</t>
   </si>
   <si>
     <t xml:space="preserve">100.479652404785</t>
@@ -4172,10 +4172,10 @@
     <t xml:space="preserve">106.685752868652</t>
   </si>
   <si>
-    <t xml:space="preserve">104.420036315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">101.957290649414</t>
+    <t xml:space="preserve">104.420028686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.957298278809</t>
   </si>
   <si>
     <t xml:space="preserve">101.858787536621</t>
@@ -4190,16 +4190,16 @@
     <t xml:space="preserve">103.631950378418</t>
   </si>
   <si>
-    <t xml:space="preserve">99.4945526123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">98.7064819335938</t>
+    <t xml:space="preserve">99.4945602416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.7064743041992</t>
   </si>
   <si>
     <t xml:space="preserve">97.2288360595703</t>
   </si>
   <si>
-    <t xml:space="preserve">98.2631912231445</t>
+    <t xml:space="preserve">98.26318359375</t>
   </si>
   <si>
     <t xml:space="preserve">98.164680480957</t>
@@ -4214,22 +4214,22 @@
     <t xml:space="preserve">97.1303329467773</t>
   </si>
   <si>
-    <t xml:space="preserve">94.5198287963867</t>
+    <t xml:space="preserve">94.5198211669922</t>
   </si>
   <si>
     <t xml:space="preserve">95.9974670410156</t>
   </si>
   <si>
-    <t xml:space="preserve">94.7660980224609</t>
+    <t xml:space="preserve">94.7661056518555</t>
   </si>
   <si>
     <t xml:space="preserve">94.4213180541992</t>
   </si>
   <si>
-    <t xml:space="preserve">93.7317504882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.0421829223633</t>
+    <t xml:space="preserve">93.7317581176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.0421905517578</t>
   </si>
   <si>
     <t xml:space="preserve">92.2048568725586</t>
@@ -4238,7 +4238,7 @@
     <t xml:space="preserve">92.8451690673828</t>
   </si>
   <si>
-    <t xml:space="preserve">91.1212463378906</t>
+    <t xml:space="preserve">91.1212539672852</t>
   </si>
   <si>
     <t xml:space="preserve">91.9093322753906</t>
@@ -4247,7 +4247,7 @@
     <t xml:space="preserve">91.0719909667969</t>
   </si>
   <si>
-    <t xml:space="preserve">86.8853378295898</t>
+    <t xml:space="preserve">86.8853454589844</t>
   </si>
   <si>
     <t xml:space="preserve">86.7868347167969</t>
@@ -4256,7 +4256,7 @@
     <t xml:space="preserve">86.0972747802734</t>
   </si>
   <si>
-    <t xml:space="preserve">86.4913177490234</t>
+    <t xml:space="preserve">86.4913101196289</t>
   </si>
   <si>
     <t xml:space="preserve">87.8211898803711</t>
@@ -4271,22 +4271,22 @@
     <t xml:space="preserve">91.7123107910156</t>
   </si>
   <si>
-    <t xml:space="preserve">91.6630554199219</t>
+    <t xml:space="preserve">91.6630630493164</t>
   </si>
   <si>
     <t xml:space="preserve">92.1556015014648</t>
   </si>
   <si>
-    <t xml:space="preserve">91.1705169677734</t>
+    <t xml:space="preserve">91.1705093383789</t>
   </si>
   <si>
     <t xml:space="preserve">90.3331756591797</t>
   </si>
   <si>
-    <t xml:space="preserve">88.6585159301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.0331115722656</t>
+    <t xml:space="preserve">88.6585235595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.0331039428711</t>
   </si>
   <si>
     <t xml:space="preserve">86.6883239746094</t>
@@ -4304,7 +4304,7 @@
     <t xml:space="preserve">87.4271469116211</t>
   </si>
   <si>
-    <t xml:space="preserve">86.9838638305664</t>
+    <t xml:space="preserve">86.9838562011719</t>
   </si>
   <si>
     <t xml:space="preserve">86.1465225219727</t>
@@ -4322,10 +4322,10 @@
     <t xml:space="preserve">81.1717987060547</t>
   </si>
   <si>
-    <t xml:space="preserve">84.915153503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.2255859375</t>
+    <t xml:space="preserve">84.9151611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.2255935668945</t>
   </si>
   <si>
     <t xml:space="preserve">87.7226791381836</t>
@@ -4334,19 +4334,19 @@
     <t xml:space="preserve">88.3137359619141</t>
   </si>
   <si>
-    <t xml:space="preserve">86.2942886352539</t>
+    <t xml:space="preserve">86.2942810058594</t>
   </si>
   <si>
     <t xml:space="preserve">88.2644805908203</t>
   </si>
   <si>
-    <t xml:space="preserve">87.6734237670898</t>
+    <t xml:space="preserve">87.6734161376953</t>
   </si>
   <si>
     <t xml:space="preserve">88.806282043457</t>
   </si>
   <si>
-    <t xml:space="preserve">89.0032958984375</t>
+    <t xml:space="preserve">89.003303527832</t>
   </si>
   <si>
     <t xml:space="preserve">92.1063461303711</t>
@@ -4355,7 +4355,7 @@
     <t xml:space="preserve">86.4420547485352</t>
   </si>
   <si>
-    <t xml:space="preserve">85.3584442138672</t>
+    <t xml:space="preserve">85.3584518432617</t>
   </si>
   <si>
     <t xml:space="preserve">83.3390045166016</t>
@@ -4370,13 +4370,13 @@
     <t xml:space="preserve">84.6688766479492</t>
   </si>
   <si>
-    <t xml:space="preserve">85.013671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.1763305664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">83.7822952270508</t>
+    <t xml:space="preserve">85.0136642456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.1763381958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">83.7823028564453</t>
   </si>
   <si>
     <t xml:space="preserve">84.521125793457</t>
@@ -4388,10 +4388,10 @@
     <t xml:space="preserve">89.8898849487305</t>
   </si>
   <si>
-    <t xml:space="preserve">92.6481475830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.3228149414062</t>
+    <t xml:space="preserve">92.6481552124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.3228073120117</t>
   </si>
   <si>
     <t xml:space="preserve">92.3033676147461</t>
@@ -4409,13 +4409,13 @@
     <t xml:space="preserve">103.336433410645</t>
   </si>
   <si>
-    <t xml:space="preserve">101.661766052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">102.154304504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104.715560913086</t>
+    <t xml:space="preserve">101.661758422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.154312133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.71556854248</t>
   </si>
   <si>
     <t xml:space="preserve">104.223014831543</t>
@@ -4430,7 +4430,7 @@
     <t xml:space="preserve">102.942390441895</t>
   </si>
   <si>
-    <t xml:space="preserve">104.814064025879</t>
+    <t xml:space="preserve">104.814071655273</t>
   </si>
   <si>
     <t xml:space="preserve">105.602142333984</t>
@@ -4439,7 +4439,7 @@
     <t xml:space="preserve">105.306617736816</t>
   </si>
   <si>
-    <t xml:space="preserve">106.784255981445</t>
+    <t xml:space="preserve">106.78426361084</t>
   </si>
   <si>
     <t xml:space="preserve">108.557426452637</t>
@@ -4448,28 +4448,28 @@
     <t xml:space="preserve">108.951461791992</t>
   </si>
   <si>
-    <t xml:space="preserve">107.473823547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.778434753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113.285888671875</t>
+    <t xml:space="preserve">107.473815917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.778427124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.28588104248</t>
   </si>
   <si>
     <t xml:space="preserve">111.808242797852</t>
   </si>
   <si>
-    <t xml:space="preserve">115.354583740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.029243469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">116.438186645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">117.521797180176</t>
+    <t xml:space="preserve">115.35457611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.029251098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.438179016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.521789550781</t>
   </si>
   <si>
     <t xml:space="preserve">119.491981506348</t>
@@ -4484,7 +4484,7 @@
     <t xml:space="preserve">114.763519287109</t>
   </si>
   <si>
-    <t xml:space="preserve">112.300788879395</t>
+    <t xml:space="preserve">112.30078125</t>
   </si>
   <si>
     <t xml:space="preserve">112.596313476562</t>
@@ -4496,7 +4496,7 @@
     <t xml:space="preserve">115.847129821777</t>
   </si>
   <si>
-    <t xml:space="preserve">116.339668273926</t>
+    <t xml:space="preserve">116.33967590332</t>
   </si>
   <si>
     <t xml:space="preserve">118.112846374512</t>
@@ -4505,13 +4505,13 @@
     <t xml:space="preserve">119.886009216309</t>
   </si>
   <si>
-    <t xml:space="preserve">120.181549072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.787506103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">119.393463134766</t>
+    <t xml:space="preserve">120.181541442871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.787498474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">119.39347076416</t>
   </si>
   <si>
     <t xml:space="preserve">121.757698059082</t>
@@ -4532,13 +4532,13 @@
     <t xml:space="preserve">125.10701751709</t>
   </si>
   <si>
-    <t xml:space="preserve">125.304039001465</t>
+    <t xml:space="preserve">125.30403137207</t>
   </si>
   <si>
     <t xml:space="preserve">125.599563598633</t>
   </si>
   <si>
-    <t xml:space="preserve">124.811492919922</t>
+    <t xml:space="preserve">124.811485290527</t>
   </si>
   <si>
     <t xml:space="preserve">125.008506774902</t>
@@ -4550,16 +4550,16 @@
     <t xml:space="preserve">126.584663391113</t>
   </si>
   <si>
-    <t xml:space="preserve">123.727890014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.796577453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.121917724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.46216583252</t>
+    <t xml:space="preserve">123.727882385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.796585083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.121925354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.462173461914</t>
   </si>
   <si>
     <t xml:space="preserve">120.280052185059</t>
@@ -4568,7 +4568,7 @@
     <t xml:space="preserve">121.659187316895</t>
   </si>
   <si>
-    <t xml:space="preserve">120.575576782227</t>
+    <t xml:space="preserve">120.575584411621</t>
   </si>
   <si>
     <t xml:space="preserve">122.64427947998</t>
@@ -4577,7 +4577,7 @@
     <t xml:space="preserve">122.742790222168</t>
   </si>
   <si>
-    <t xml:space="preserve">125.205520629883</t>
+    <t xml:space="preserve">125.205528259277</t>
   </si>
   <si>
     <t xml:space="preserve">126.190628051758</t>
@@ -4592,10 +4592,10 @@
     <t xml:space="preserve">123.235336303711</t>
   </si>
   <si>
-    <t xml:space="preserve">124.515960693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.151733398438</t>
+    <t xml:space="preserve">124.515968322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.151741027832</t>
   </si>
   <si>
     <t xml:space="preserve">122.841300964355</t>
@@ -4610,10 +4610,10 @@
     <t xml:space="preserve">130.032501220703</t>
   </si>
   <si>
-    <t xml:space="preserve">130.820556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130.722045898438</t>
+    <t xml:space="preserve">130.820571899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130.722061157227</t>
   </si>
   <si>
     <t xml:space="preserve">129.835479736328</t>
@@ -4628,7 +4628,7 @@
     <t xml:space="preserve">127.569747924805</t>
   </si>
   <si>
-    <t xml:space="preserve">127.668258666992</t>
+    <t xml:space="preserve">127.668266296387</t>
   </si>
   <si>
     <t xml:space="preserve">129.244415283203</t>
@@ -4640,7 +4640,7 @@
     <t xml:space="preserve">130.131011962891</t>
   </si>
   <si>
-    <t xml:space="preserve">129.441421508789</t>
+    <t xml:space="preserve">129.441436767578</t>
   </si>
   <si>
     <t xml:space="preserve">126.486145019531</t>
@@ -4649,22 +4649,22 @@
     <t xml:space="preserve">128.16081237793</t>
   </si>
   <si>
-    <t xml:space="preserve">126.387649536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">124.910003662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.05322265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.265151977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122.250244140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">121.166641235352</t>
+    <t xml:space="preserve">126.387641906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124.909996032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.053230285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.265144348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.25023651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">121.166633605957</t>
   </si>
   <si>
     <t xml:space="preserve">133.677337646484</t>
@@ -4673,111 +4673,114 @@
     <t xml:space="preserve">131.116104125977</t>
   </si>
   <si>
+    <t xml:space="preserve">134.760955810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.058654785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.455581665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.959411621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.356338500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.547180175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.447937011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.577774047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.280075073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.43286895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.417556762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">127.516799926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">129.799194335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.073959350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.554824829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.379302978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">133.371643066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">132.776245117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.16552734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.936462402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.043350219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">141.111968994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.325744628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">137.142578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.745635986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135.257125854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.531875610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">139.12727355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.318084716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.134918212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.928802490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140.516571044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138.730331420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">136.249465942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134.860168457031</t>
+  </si>
+  <si>
     <t xml:space="preserve">134.760940551758</t>
   </si>
   <si>
-    <t xml:space="preserve">135.058654785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.455581665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.959411621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.356338500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.547180175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.447937011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.577774047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.280075073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">125.43286895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.417556762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">127.516799926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">129.799194335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.073959350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.554824829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.379302978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">133.371643066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">132.776245117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.16552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.936462402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.043350219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">141.111968994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.325744628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">137.142578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.745635986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135.257125854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.531875610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">139.12727355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.318084716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.134918212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.928802490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">140.516571044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">138.730331420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">136.249465942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.860168457031</t>
-  </si>
-  <si>
     <t xml:space="preserve">136.944107055664</t>
   </si>
   <si>
@@ -5480,7 +5483,16 @@
     <t xml:space="preserve">119.199996948242</t>
   </si>
   <si>
+    <t xml:space="preserve">119.300003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.900001525879</t>
+  </si>
+  <si>
     <t xml:space="preserve">114.599998474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.199996948242</t>
   </si>
 </sst>
 </file>
@@ -62413,7 +62425,7 @@
         <v>135.800003051758</v>
       </c>
       <c r="G2177" t="s">
-        <v>1553</v>
+        <v>1588</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -62439,7 +62451,7 @@
         <v>138</v>
       </c>
       <c r="G2178" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -62491,7 +62503,7 @@
         <v>135.800003051758</v>
       </c>
       <c r="G2180" t="s">
-        <v>1553</v>
+        <v>1588</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -62517,7 +62529,7 @@
         <v>132.699996948242</v>
       </c>
       <c r="G2181" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -62543,7 +62555,7 @@
         <v>133.100006103516</v>
       </c>
       <c r="G2182" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -62569,7 +62581,7 @@
         <v>131.800003051758</v>
       </c>
       <c r="G2183" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -62595,7 +62607,7 @@
         <v>131.800003051758</v>
       </c>
       <c r="G2184" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -62621,7 +62633,7 @@
         <v>131.199996948242</v>
       </c>
       <c r="G2185" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -62647,7 +62659,7 @@
         <v>129</v>
       </c>
       <c r="G2186" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -62673,7 +62685,7 @@
         <v>126.599998474121</v>
       </c>
       <c r="G2187" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -62699,7 +62711,7 @@
         <v>124.300003051758</v>
       </c>
       <c r="G2188" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -62725,7 +62737,7 @@
         <v>125.099998474121</v>
       </c>
       <c r="G2189" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -62751,7 +62763,7 @@
         <v>125.599998474121</v>
       </c>
       <c r="G2190" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -62777,7 +62789,7 @@
         <v>124.900001525879</v>
       </c>
       <c r="G2191" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -62803,7 +62815,7 @@
         <v>127.199996948242</v>
       </c>
       <c r="G2192" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -62855,7 +62867,7 @@
         <v>129.899993896484</v>
       </c>
       <c r="G2194" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -62881,7 +62893,7 @@
         <v>131.5</v>
       </c>
       <c r="G2195" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -62933,7 +62945,7 @@
         <v>135.300003051758</v>
       </c>
       <c r="G2197" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -62985,7 +62997,7 @@
         <v>138.699996948242</v>
       </c>
       <c r="G2199" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -63063,7 +63075,7 @@
         <v>140.899993896484</v>
       </c>
       <c r="G2202" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -63141,7 +63153,7 @@
         <v>141.800003051758</v>
       </c>
       <c r="G2205" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -63167,7 +63179,7 @@
         <v>142.699996948242</v>
       </c>
       <c r="G2206" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -63193,7 +63205,7 @@
         <v>141</v>
       </c>
       <c r="G2207" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -63219,7 +63231,7 @@
         <v>140.699996948242</v>
       </c>
       <c r="G2208" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -63297,7 +63309,7 @@
         <v>134</v>
       </c>
       <c r="G2211" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -63323,7 +63335,7 @@
         <v>134.899993896484</v>
       </c>
       <c r="G2212" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -63349,7 +63361,7 @@
         <v>135</v>
       </c>
       <c r="G2213" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -63375,7 +63387,7 @@
         <v>135.100006103516</v>
       </c>
       <c r="G2214" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -63453,7 +63465,7 @@
         <v>135.699996948242</v>
       </c>
       <c r="G2217" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -63479,7 +63491,7 @@
         <v>137.100006103516</v>
       </c>
       <c r="G2218" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -63505,7 +63517,7 @@
         <v>134.899993896484</v>
       </c>
       <c r="G2219" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -63531,7 +63543,7 @@
         <v>136.899993896484</v>
       </c>
       <c r="G2220" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -63557,7 +63569,7 @@
         <v>135.5</v>
       </c>
       <c r="G2221" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -63583,7 +63595,7 @@
         <v>135.800003051758</v>
       </c>
       <c r="G2222" t="s">
-        <v>1553</v>
+        <v>1588</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -63635,7 +63647,7 @@
         <v>134.800003051758</v>
       </c>
       <c r="G2224" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -63661,7 +63673,7 @@
         <v>136.699996948242</v>
       </c>
       <c r="G2225" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -63687,7 +63699,7 @@
         <v>136.800003051758</v>
       </c>
       <c r="G2226" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -63739,7 +63751,7 @@
         <v>132.899993896484</v>
       </c>
       <c r="G2228" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -63765,7 +63777,7 @@
         <v>134</v>
       </c>
       <c r="G2229" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -63791,7 +63803,7 @@
         <v>132</v>
       </c>
       <c r="G2230" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -63817,7 +63829,7 @@
         <v>132</v>
       </c>
       <c r="G2231" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -63843,7 +63855,7 @@
         <v>131.800003051758</v>
       </c>
       <c r="G2232" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -63869,7 +63881,7 @@
         <v>131.600006103516</v>
       </c>
       <c r="G2233" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -63895,7 +63907,7 @@
         <v>135.699996948242</v>
       </c>
       <c r="G2234" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -63973,7 +63985,7 @@
         <v>138.300003051758</v>
       </c>
       <c r="G2237" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -64025,7 +64037,7 @@
         <v>139.399993896484</v>
       </c>
       <c r="G2239" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -64051,7 +64063,7 @@
         <v>141</v>
       </c>
       <c r="G2240" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -64077,7 +64089,7 @@
         <v>143.100006103516</v>
       </c>
       <c r="G2241" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -64103,7 +64115,7 @@
         <v>142.100006103516</v>
       </c>
       <c r="G2242" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -64129,7 +64141,7 @@
         <v>143.399993896484</v>
       </c>
       <c r="G2243" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -64155,7 +64167,7 @@
         <v>143.199996948242</v>
       </c>
       <c r="G2244" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -64181,7 +64193,7 @@
         <v>147.300003051758</v>
       </c>
       <c r="G2245" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -64207,7 +64219,7 @@
         <v>143.300003051758</v>
       </c>
       <c r="G2246" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -64233,7 +64245,7 @@
         <v>144.600006103516</v>
       </c>
       <c r="G2247" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -64259,7 +64271,7 @@
         <v>142.899993896484</v>
       </c>
       <c r="G2248" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -64285,7 +64297,7 @@
         <v>143</v>
       </c>
       <c r="G2249" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -64311,7 +64323,7 @@
         <v>140.300003051758</v>
       </c>
       <c r="G2250" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -64337,7 +64349,7 @@
         <v>142</v>
       </c>
       <c r="G2251" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -64363,7 +64375,7 @@
         <v>139.100006103516</v>
       </c>
       <c r="G2252" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -64389,7 +64401,7 @@
         <v>139.300003051758</v>
       </c>
       <c r="G2253" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -64415,7 +64427,7 @@
         <v>136.899993896484</v>
       </c>
       <c r="G2254" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -64441,7 +64453,7 @@
         <v>140.5</v>
       </c>
       <c r="G2255" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -64467,7 +64479,7 @@
         <v>140.300003051758</v>
       </c>
       <c r="G2256" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -64493,7 +64505,7 @@
         <v>143.300003051758</v>
       </c>
       <c r="G2257" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -64519,7 +64531,7 @@
         <v>141.800003051758</v>
       </c>
       <c r="G2258" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -64571,7 +64583,7 @@
         <v>150.800003051758</v>
       </c>
       <c r="G2260" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -64597,7 +64609,7 @@
         <v>152.800003051758</v>
       </c>
       <c r="G2261" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -64623,7 +64635,7 @@
         <v>152.300003051758</v>
       </c>
       <c r="G2262" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -64649,7 +64661,7 @@
         <v>153.899993896484</v>
       </c>
       <c r="G2263" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -64675,7 +64687,7 @@
         <v>152.899993896484</v>
       </c>
       <c r="G2264" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -64701,7 +64713,7 @@
         <v>154.600006103516</v>
       </c>
       <c r="G2265" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -64727,7 +64739,7 @@
         <v>149.899993896484</v>
       </c>
       <c r="G2266" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -64753,7 +64765,7 @@
         <v>153.399993896484</v>
       </c>
       <c r="G2267" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -64779,7 +64791,7 @@
         <v>152.300003051758</v>
       </c>
       <c r="G2268" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -64805,7 +64817,7 @@
         <v>150.399993896484</v>
       </c>
       <c r="G2269" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -64831,7 +64843,7 @@
         <v>150.899993896484</v>
       </c>
       <c r="G2270" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -64857,7 +64869,7 @@
         <v>151.5</v>
       </c>
       <c r="G2271" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -64883,7 +64895,7 @@
         <v>151.5</v>
       </c>
       <c r="G2272" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -64909,7 +64921,7 @@
         <v>152.699996948242</v>
       </c>
       <c r="G2273" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -64935,7 +64947,7 @@
         <v>157.100006103516</v>
       </c>
       <c r="G2274" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -64961,7 +64973,7 @@
         <v>155.5</v>
       </c>
       <c r="G2275" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -64987,7 +64999,7 @@
         <v>156.899993896484</v>
       </c>
       <c r="G2276" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -65013,7 +65025,7 @@
         <v>154.199996948242</v>
       </c>
       <c r="G2277" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -65039,7 +65051,7 @@
         <v>154.899993896484</v>
       </c>
       <c r="G2278" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -65065,7 +65077,7 @@
         <v>157.800003051758</v>
       </c>
       <c r="G2279" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -65091,7 +65103,7 @@
         <v>155</v>
       </c>
       <c r="G2280" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -65117,7 +65129,7 @@
         <v>156</v>
       </c>
       <c r="G2281" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -65143,7 +65155,7 @@
         <v>155.600006103516</v>
       </c>
       <c r="G2282" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -65169,7 +65181,7 @@
         <v>156.800003051758</v>
       </c>
       <c r="G2283" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -65195,7 +65207,7 @@
         <v>156.399993896484</v>
       </c>
       <c r="G2284" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -65221,7 +65233,7 @@
         <v>152.300003051758</v>
       </c>
       <c r="G2285" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -65247,7 +65259,7 @@
         <v>155</v>
       </c>
       <c r="G2286" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -65273,7 +65285,7 @@
         <v>153.600006103516</v>
       </c>
       <c r="G2287" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -65299,7 +65311,7 @@
         <v>155.5</v>
       </c>
       <c r="G2288" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -65325,7 +65337,7 @@
         <v>153.399993896484</v>
       </c>
       <c r="G2289" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -65351,7 +65363,7 @@
         <v>155.800003051758</v>
       </c>
       <c r="G2290" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -65377,7 +65389,7 @@
         <v>154.800003051758</v>
       </c>
       <c r="G2291" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -65403,7 +65415,7 @@
         <v>157.600006103516</v>
       </c>
       <c r="G2292" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -65429,7 +65441,7 @@
         <v>157.800003051758</v>
       </c>
       <c r="G2293" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -65455,7 +65467,7 @@
         <v>152.199996948242</v>
       </c>
       <c r="G2294" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -65481,7 +65493,7 @@
         <v>149.5</v>
       </c>
       <c r="G2295" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -65507,7 +65519,7 @@
         <v>148.100006103516</v>
       </c>
       <c r="G2296" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -65533,7 +65545,7 @@
         <v>146.199996948242</v>
       </c>
       <c r="G2297" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -65559,7 +65571,7 @@
         <v>144.800003051758</v>
       </c>
       <c r="G2298" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -65585,7 +65597,7 @@
         <v>149.699996948242</v>
       </c>
       <c r="G2299" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -65611,7 +65623,7 @@
         <v>151</v>
       </c>
       <c r="G2300" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -65637,7 +65649,7 @@
         <v>150.5</v>
       </c>
       <c r="G2301" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -65663,7 +65675,7 @@
         <v>151.600006103516</v>
       </c>
       <c r="G2302" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -65689,7 +65701,7 @@
         <v>152.600006103516</v>
       </c>
       <c r="G2303" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -65715,7 +65727,7 @@
         <v>155.600006103516</v>
       </c>
       <c r="G2304" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -65741,7 +65753,7 @@
         <v>153.699996948242</v>
       </c>
       <c r="G2305" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -65767,7 +65779,7 @@
         <v>155.899993896484</v>
       </c>
       <c r="G2306" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -65793,7 +65805,7 @@
         <v>153.699996948242</v>
       </c>
       <c r="G2307" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -65819,7 +65831,7 @@
         <v>156.300003051758</v>
       </c>
       <c r="G2308" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -65845,7 +65857,7 @@
         <v>157.699996948242</v>
       </c>
       <c r="G2309" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -65871,7 +65883,7 @@
         <v>157.199996948242</v>
       </c>
       <c r="G2310" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -65897,7 +65909,7 @@
         <v>159.600006103516</v>
       </c>
       <c r="G2311" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -65923,7 +65935,7 @@
         <v>158.100006103516</v>
       </c>
       <c r="G2312" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -65949,7 +65961,7 @@
         <v>158</v>
       </c>
       <c r="G2313" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -65975,7 +65987,7 @@
         <v>158.199996948242</v>
       </c>
       <c r="G2314" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -66001,7 +66013,7 @@
         <v>161.399993896484</v>
       </c>
       <c r="G2315" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -66027,7 +66039,7 @@
         <v>159.800003051758</v>
       </c>
       <c r="G2316" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -66053,7 +66065,7 @@
         <v>160.100006103516</v>
       </c>
       <c r="G2317" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -66079,7 +66091,7 @@
         <v>159.800003051758</v>
       </c>
       <c r="G2318" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -66105,7 +66117,7 @@
         <v>161.300003051758</v>
       </c>
       <c r="G2319" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -66131,7 +66143,7 @@
         <v>164.100006103516</v>
       </c>
       <c r="G2320" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -66157,7 +66169,7 @@
         <v>163.699996948242</v>
       </c>
       <c r="G2321" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -66183,7 +66195,7 @@
         <v>165.300003051758</v>
       </c>
       <c r="G2322" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -66209,7 +66221,7 @@
         <v>164.399993896484</v>
       </c>
       <c r="G2323" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -66235,7 +66247,7 @@
         <v>159.600006103516</v>
       </c>
       <c r="G2324" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -66261,7 +66273,7 @@
         <v>158.399993896484</v>
       </c>
       <c r="G2325" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -66287,7 +66299,7 @@
         <v>159.699996948242</v>
       </c>
       <c r="G2326" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -66313,7 +66325,7 @@
         <v>158</v>
       </c>
       <c r="G2327" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -66339,7 +66351,7 @@
         <v>157.899993896484</v>
       </c>
       <c r="G2328" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -66365,7 +66377,7 @@
         <v>157.5</v>
       </c>
       <c r="G2329" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -66391,7 +66403,7 @@
         <v>156.699996948242</v>
       </c>
       <c r="G2330" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -66417,7 +66429,7 @@
         <v>154.199996948242</v>
       </c>
       <c r="G2331" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -66443,7 +66455,7 @@
         <v>154.800003051758</v>
       </c>
       <c r="G2332" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -66469,7 +66481,7 @@
         <v>150</v>
       </c>
       <c r="G2333" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -66495,7 +66507,7 @@
         <v>153.5</v>
       </c>
       <c r="G2334" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -66521,7 +66533,7 @@
         <v>153.899993896484</v>
       </c>
       <c r="G2335" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -66547,7 +66559,7 @@
         <v>153.800003051758</v>
       </c>
       <c r="G2336" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -66573,7 +66585,7 @@
         <v>153.300003051758</v>
       </c>
       <c r="G2337" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -66599,7 +66611,7 @@
         <v>146.199996948242</v>
       </c>
       <c r="G2338" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -66625,7 +66637,7 @@
         <v>149.100006103516</v>
       </c>
       <c r="G2339" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -66651,7 +66663,7 @@
         <v>157.199996948242</v>
       </c>
       <c r="G2340" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -66677,7 +66689,7 @@
         <v>164</v>
       </c>
       <c r="G2341" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -66703,7 +66715,7 @@
         <v>164.100006103516</v>
       </c>
       <c r="G2342" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -66729,7 +66741,7 @@
         <v>165.399993896484</v>
       </c>
       <c r="G2343" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -66755,7 +66767,7 @@
         <v>167.5</v>
       </c>
       <c r="G2344" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -66781,7 +66793,7 @@
         <v>164.699996948242</v>
       </c>
       <c r="G2345" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -66807,7 +66819,7 @@
         <v>163.100006103516</v>
       </c>
       <c r="G2346" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -66833,7 +66845,7 @@
         <v>162.699996948242</v>
       </c>
       <c r="G2347" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -66859,7 +66871,7 @@
         <v>163.699996948242</v>
       </c>
       <c r="G2348" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -66885,7 +66897,7 @@
         <v>160.600006103516</v>
       </c>
       <c r="G2349" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -66911,7 +66923,7 @@
         <v>159.5</v>
       </c>
       <c r="G2350" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -66937,7 +66949,7 @@
         <v>156.600006103516</v>
       </c>
       <c r="G2351" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -66963,7 +66975,7 @@
         <v>150.800003051758</v>
       </c>
       <c r="G2352" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -66989,7 +67001,7 @@
         <v>153</v>
       </c>
       <c r="G2353" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -67015,7 +67027,7 @@
         <v>152.899993896484</v>
       </c>
       <c r="G2354" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -67041,7 +67053,7 @@
         <v>147.600006103516</v>
       </c>
       <c r="G2355" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -67067,7 +67079,7 @@
         <v>143.800003051758</v>
       </c>
       <c r="G2356" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -67119,7 +67131,7 @@
         <v>141.800003051758</v>
       </c>
       <c r="G2358" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -67145,7 +67157,7 @@
         <v>135.5</v>
       </c>
       <c r="G2359" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -67171,7 +67183,7 @@
         <v>142.899993896484</v>
       </c>
       <c r="G2360" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -67197,7 +67209,7 @@
         <v>143.800003051758</v>
       </c>
       <c r="G2361" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -67223,7 +67235,7 @@
         <v>146.899993896484</v>
       </c>
       <c r="G2362" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -67249,7 +67261,7 @@
         <v>149</v>
       </c>
       <c r="G2363" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -67275,7 +67287,7 @@
         <v>149.699996948242</v>
       </c>
       <c r="G2364" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -67301,7 +67313,7 @@
         <v>148.899993896484</v>
       </c>
       <c r="G2365" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -67327,7 +67339,7 @@
         <v>147.399993896484</v>
       </c>
       <c r="G2366" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -67353,7 +67365,7 @@
         <v>150.800003051758</v>
       </c>
       <c r="G2367" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -67379,7 +67391,7 @@
         <v>149.399993896484</v>
       </c>
       <c r="G2368" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -67405,7 +67417,7 @@
         <v>149.399993896484</v>
       </c>
       <c r="G2369" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -67431,7 +67443,7 @@
         <v>151.899993896484</v>
       </c>
       <c r="G2370" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -67457,7 +67469,7 @@
         <v>153.600006103516</v>
       </c>
       <c r="G2371" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -67483,7 +67495,7 @@
         <v>156.800003051758</v>
       </c>
       <c r="G2372" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -67509,7 +67521,7 @@
         <v>158.699996948242</v>
       </c>
       <c r="G2373" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -67535,7 +67547,7 @@
         <v>157.699996948242</v>
       </c>
       <c r="G2374" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -67561,7 +67573,7 @@
         <v>158.899993896484</v>
       </c>
       <c r="G2375" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -67587,7 +67599,7 @@
         <v>156.399993896484</v>
       </c>
       <c r="G2376" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -67613,7 +67625,7 @@
         <v>159.600006103516</v>
       </c>
       <c r="G2377" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -67639,7 +67651,7 @@
         <v>161.600006103516</v>
       </c>
       <c r="G2378" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -67665,7 +67677,7 @@
         <v>157.600006103516</v>
       </c>
       <c r="G2379" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -67691,7 +67703,7 @@
         <v>154.100006103516</v>
       </c>
       <c r="G2380" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -67717,7 +67729,7 @@
         <v>150.699996948242</v>
       </c>
       <c r="G2381" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -67743,7 +67755,7 @@
         <v>150.600006103516</v>
       </c>
       <c r="G2382" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -67769,7 +67781,7 @@
         <v>150.300003051758</v>
       </c>
       <c r="G2383" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -67795,7 +67807,7 @@
         <v>147.5</v>
       </c>
       <c r="G2384" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -67821,7 +67833,7 @@
         <v>147.100006103516</v>
       </c>
       <c r="G2385" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -67847,7 +67859,7 @@
         <v>147</v>
       </c>
       <c r="G2386" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -67873,7 +67885,7 @@
         <v>144.5</v>
       </c>
       <c r="G2387" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -67899,7 +67911,7 @@
         <v>142.899993896484</v>
       </c>
       <c r="G2388" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -67925,7 +67937,7 @@
         <v>146.5</v>
       </c>
       <c r="G2389" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -67951,7 +67963,7 @@
         <v>145.300003051758</v>
       </c>
       <c r="G2390" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -67977,7 +67989,7 @@
         <v>148.199996948242</v>
       </c>
       <c r="G2391" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -68003,7 +68015,7 @@
         <v>147</v>
       </c>
       <c r="G2392" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -68029,7 +68041,7 @@
         <v>148.5</v>
       </c>
       <c r="G2393" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -68055,7 +68067,7 @@
         <v>146.100006103516</v>
       </c>
       <c r="G2394" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -68081,7 +68093,7 @@
         <v>146.5</v>
       </c>
       <c r="G2395" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -68107,7 +68119,7 @@
         <v>148.399993896484</v>
       </c>
       <c r="G2396" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -68133,7 +68145,7 @@
         <v>150.399993896484</v>
       </c>
       <c r="G2397" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -68159,7 +68171,7 @@
         <v>149.100006103516</v>
       </c>
       <c r="G2398" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -68185,7 +68197,7 @@
         <v>149.300003051758</v>
       </c>
       <c r="G2399" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -68211,7 +68223,7 @@
         <v>151.600006103516</v>
       </c>
       <c r="G2400" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -68237,7 +68249,7 @@
         <v>151.899993896484</v>
       </c>
       <c r="G2401" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -68263,7 +68275,7 @@
         <v>148.800003051758</v>
       </c>
       <c r="G2402" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -68289,7 +68301,7 @@
         <v>145.100006103516</v>
       </c>
       <c r="G2403" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -68315,7 +68327,7 @@
         <v>145.600006103516</v>
       </c>
       <c r="G2404" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -68341,7 +68353,7 @@
         <v>144.800003051758</v>
       </c>
       <c r="G2405" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -68367,7 +68379,7 @@
         <v>145.800003051758</v>
       </c>
       <c r="G2406" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -68393,7 +68405,7 @@
         <v>142.899993896484</v>
       </c>
       <c r="G2407" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -68419,7 +68431,7 @@
         <v>142.5</v>
       </c>
       <c r="G2408" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -68445,7 +68457,7 @@
         <v>142.100006103516</v>
       </c>
       <c r="G2409" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -68471,7 +68483,7 @@
         <v>142.600006103516</v>
       </c>
       <c r="G2410" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -68497,7 +68509,7 @@
         <v>141.899993896484</v>
       </c>
       <c r="G2411" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -68523,7 +68535,7 @@
         <v>143.100006103516</v>
       </c>
       <c r="G2412" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -68549,7 +68561,7 @@
         <v>143.699996948242</v>
       </c>
       <c r="G2413" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -68575,7 +68587,7 @@
         <v>146.600006103516</v>
       </c>
       <c r="G2414" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -68601,7 +68613,7 @@
         <v>145.5</v>
       </c>
       <c r="G2415" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -68627,7 +68639,7 @@
         <v>142.100006103516</v>
       </c>
       <c r="G2416" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -68653,7 +68665,7 @@
         <v>143.5</v>
       </c>
       <c r="G2417" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -68679,7 +68691,7 @@
         <v>141.5</v>
       </c>
       <c r="G2418" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -68705,7 +68717,7 @@
         <v>141.5</v>
       </c>
       <c r="G2419" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -68731,7 +68743,7 @@
         <v>145.300003051758</v>
       </c>
       <c r="G2420" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -68757,7 +68769,7 @@
         <v>144.399993896484</v>
       </c>
       <c r="G2421" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -68783,7 +68795,7 @@
         <v>144.600006103516</v>
       </c>
       <c r="G2422" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -68809,7 +68821,7 @@
         <v>142.600006103516</v>
       </c>
       <c r="G2423" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -68835,7 +68847,7 @@
         <v>140.800003051758</v>
       </c>
       <c r="G2424" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -68861,7 +68873,7 @@
         <v>142.5</v>
       </c>
       <c r="G2425" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -68887,7 +68899,7 @@
         <v>140.800003051758</v>
       </c>
       <c r="G2426" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -68913,7 +68925,7 @@
         <v>143.399993896484</v>
       </c>
       <c r="G2427" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -68939,7 +68951,7 @@
         <v>142</v>
       </c>
       <c r="G2428" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -68965,7 +68977,7 @@
         <v>140.899993896484</v>
       </c>
       <c r="G2429" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -68991,7 +69003,7 @@
         <v>139.100006103516</v>
       </c>
       <c r="G2430" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -69017,7 +69029,7 @@
         <v>139</v>
       </c>
       <c r="G2431" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -69043,7 +69055,7 @@
         <v>136.899993896484</v>
       </c>
       <c r="G2432" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -69069,7 +69081,7 @@
         <v>136.800003051758</v>
       </c>
       <c r="G2433" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -69095,7 +69107,7 @@
         <v>139.899993896484</v>
       </c>
       <c r="G2434" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -69121,7 +69133,7 @@
         <v>138.300003051758</v>
       </c>
       <c r="G2435" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -69147,7 +69159,7 @@
         <v>137.399993896484</v>
       </c>
       <c r="G2436" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -69173,7 +69185,7 @@
         <v>137.600006103516</v>
       </c>
       <c r="G2437" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -69199,7 +69211,7 @@
         <v>131.699996948242</v>
       </c>
       <c r="G2438" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -69225,7 +69237,7 @@
         <v>131.600006103516</v>
       </c>
       <c r="G2439" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -69251,7 +69263,7 @@
         <v>133.199996948242</v>
       </c>
       <c r="G2440" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -69277,7 +69289,7 @@
         <v>128.199996948242</v>
       </c>
       <c r="G2441" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -69303,7 +69315,7 @@
         <v>128</v>
       </c>
       <c r="G2442" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -69329,7 +69341,7 @@
         <v>128.600006103516</v>
       </c>
       <c r="G2443" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -69355,7 +69367,7 @@
         <v>127</v>
       </c>
       <c r="G2444" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -69381,7 +69393,7 @@
         <v>122.5</v>
       </c>
       <c r="G2445" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -69407,7 +69419,7 @@
         <v>122.300003051758</v>
       </c>
       <c r="G2446" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -69433,7 +69445,7 @@
         <v>121.599998474121</v>
       </c>
       <c r="G2447" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -69459,7 +69471,7 @@
         <v>123</v>
       </c>
       <c r="G2448" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -69485,7 +69497,7 @@
         <v>125.599998474121</v>
       </c>
       <c r="G2449" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -69511,7 +69523,7 @@
         <v>123.300003051758</v>
       </c>
       <c r="G2450" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -69537,7 +69549,7 @@
         <v>121.800003051758</v>
       </c>
       <c r="G2451" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -69563,7 +69575,7 @@
         <v>122.699996948242</v>
       </c>
       <c r="G2452" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -69589,7 +69601,7 @@
         <v>124</v>
       </c>
       <c r="G2453" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -69615,7 +69627,7 @@
         <v>122.900001525879</v>
       </c>
       <c r="G2454" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -69641,7 +69653,7 @@
         <v>123.800003051758</v>
       </c>
       <c r="G2455" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -69667,7 +69679,7 @@
         <v>124.300003051758</v>
       </c>
       <c r="G2456" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -69693,7 +69705,7 @@
         <v>123.099998474121</v>
       </c>
       <c r="G2457" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -69719,7 +69731,7 @@
         <v>123</v>
       </c>
       <c r="G2458" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -69745,7 +69757,7 @@
         <v>119</v>
       </c>
       <c r="G2459" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -69771,7 +69783,7 @@
         <v>119</v>
       </c>
       <c r="G2460" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -69797,7 +69809,7 @@
         <v>119.099998474121</v>
       </c>
       <c r="G2461" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -69823,7 +69835,7 @@
         <v>119.699996948242</v>
       </c>
       <c r="G2462" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -69849,7 +69861,7 @@
         <v>120</v>
       </c>
       <c r="G2463" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -69875,7 +69887,7 @@
         <v>119.900001525879</v>
       </c>
       <c r="G2464" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -69901,7 +69913,7 @@
         <v>115.300003051758</v>
       </c>
       <c r="G2465" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -69927,7 +69939,7 @@
         <v>115.099998474121</v>
       </c>
       <c r="G2466" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -69953,7 +69965,7 @@
         <v>116.5</v>
       </c>
       <c r="G2467" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -69979,7 +69991,7 @@
         <v>117.199996948242</v>
       </c>
       <c r="G2468" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -70005,7 +70017,7 @@
         <v>117.5</v>
       </c>
       <c r="G2469" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -70031,7 +70043,7 @@
         <v>120.400001525879</v>
       </c>
       <c r="G2470" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -70057,7 +70069,7 @@
         <v>123.199996948242</v>
       </c>
       <c r="G2471" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -70083,7 +70095,7 @@
         <v>121.900001525879</v>
       </c>
       <c r="G2472" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -70109,7 +70121,7 @@
         <v>121.800003051758</v>
       </c>
       <c r="G2473" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -70135,7 +70147,7 @@
         <v>122.699996948242</v>
       </c>
       <c r="G2474" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -70161,7 +70173,7 @@
         <v>122.599998474121</v>
       </c>
       <c r="G2475" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -70187,7 +70199,7 @@
         <v>120.300003051758</v>
       </c>
       <c r="G2476" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -70213,7 +70225,7 @@
         <v>118.300003051758</v>
       </c>
       <c r="G2477" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -70239,7 +70251,7 @@
         <v>120.699996948242</v>
       </c>
       <c r="G2478" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -70265,7 +70277,7 @@
         <v>121.199996948242</v>
       </c>
       <c r="G2479" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -70291,7 +70303,7 @@
         <v>121.199996948242</v>
       </c>
       <c r="G2480" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -70317,7 +70329,7 @@
         <v>124</v>
       </c>
       <c r="G2481" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -70343,7 +70355,7 @@
         <v>123</v>
       </c>
       <c r="G2482" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -70369,7 +70381,7 @@
         <v>123</v>
       </c>
       <c r="G2483" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -70395,7 +70407,7 @@
         <v>123.699996948242</v>
       </c>
       <c r="G2484" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -70421,7 +70433,7 @@
         <v>123.5</v>
       </c>
       <c r="G2485" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -70447,7 +70459,7 @@
         <v>123.300003051758</v>
       </c>
       <c r="G2486" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -70473,7 +70485,7 @@
         <v>121.800003051758</v>
       </c>
       <c r="G2487" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -70499,7 +70511,7 @@
         <v>120.400001525879</v>
       </c>
       <c r="G2488" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -70525,7 +70537,7 @@
         <v>118.300003051758</v>
       </c>
       <c r="G2489" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -70551,7 +70563,7 @@
         <v>118.900001525879</v>
       </c>
       <c r="G2490" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -70577,7 +70589,7 @@
         <v>118.300003051758</v>
       </c>
       <c r="G2491" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -70603,7 +70615,7 @@
         <v>118.099998474121</v>
       </c>
       <c r="G2492" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -70629,7 +70641,7 @@
         <v>118.5</v>
       </c>
       <c r="G2493" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -70655,7 +70667,7 @@
         <v>121.099998474121</v>
       </c>
       <c r="G2494" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -70681,7 +70693,7 @@
         <v>120.199996948242</v>
       </c>
       <c r="G2495" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -70707,7 +70719,7 @@
         <v>120.400001525879</v>
       </c>
       <c r="G2496" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -70733,7 +70745,7 @@
         <v>121.300003051758</v>
       </c>
       <c r="G2497" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -70759,7 +70771,7 @@
         <v>120.300003051758</v>
       </c>
       <c r="G2498" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -70785,7 +70797,7 @@
         <v>123.099998474121</v>
       </c>
       <c r="G2499" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -70811,7 +70823,7 @@
         <v>121</v>
       </c>
       <c r="G2500" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -70837,7 +70849,7 @@
         <v>121.300003051758</v>
       </c>
       <c r="G2501" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -70863,7 +70875,7 @@
         <v>121.599998474121</v>
       </c>
       <c r="G2502" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -70889,7 +70901,7 @@
         <v>118.800003051758</v>
       </c>
       <c r="G2503" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -70915,7 +70927,7 @@
         <v>119.199996948242</v>
       </c>
       <c r="G2504" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -70923,27 +70935,105 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45968.6912268518</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2505" t="n">
+        <v>31419</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>116.699996948242</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>117.800003051758</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>119.300003051758</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1823</v>
+      </c>
+      <c r="H2505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>37910</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>119.300003051758</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>115.900001525879</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>119</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>115.900001525879</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>1824</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2507" t="n">
         <v>68091</v>
       </c>
-      <c r="C2505" t="n">
+      <c r="C2507" t="n">
         <v>116.900001525879</v>
       </c>
-      <c r="D2505" t="n">
+      <c r="D2507" t="n">
         <v>114.599998474121</v>
       </c>
-      <c r="E2505" t="n">
+      <c r="E2507" t="n">
         <v>116.099998474121</v>
       </c>
-      <c r="F2505" t="n">
+      <c r="F2507" t="n">
         <v>114.599998474121</v>
       </c>
-      <c r="G2505" t="s">
-        <v>1822</v>
-      </c>
-      <c r="H2505" t="s">
+      <c r="G2507" t="s">
+        <v>1825</v>
+      </c>
+      <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.6911342593</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>44528</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>118.199996948242</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>115.900001525879</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>116</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>116.199996948242</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>1826</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/REY.MI.xlsx
+++ b/data/REY.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2559700012207</t>
+    <t xml:space="preserve">29.2559719085693</t>
   </si>
   <si>
     <t xml:space="preserve">REY.MI</t>
@@ -47,31 +47,31 @@
     <t xml:space="preserve">28.8380260467529</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3272094726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6306400299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8396110534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2111167907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.0005626678467</t>
+    <t xml:space="preserve">28.3272113800049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6306419372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8396129608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2111148834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.000560760498</t>
   </si>
   <si>
     <t xml:space="preserve">28.5594005584717</t>
   </si>
   <si>
-    <t xml:space="preserve">28.1414566040039</t>
+    <t xml:space="preserve">28.1414585113525</t>
   </si>
   <si>
     <t xml:space="preserve">27.1198234558105</t>
   </si>
   <si>
-    <t xml:space="preserve">27.9789257049561</t>
+    <t xml:space="preserve">27.9789237976074</t>
   </si>
   <si>
     <t xml:space="preserve">26.8644123077393</t>
@@ -80,103 +80,103 @@
     <t xml:space="preserve">27.4448852539062</t>
   </si>
   <si>
-    <t xml:space="preserve">27.932487487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8163909912109</t>
+    <t xml:space="preserve">27.9324913024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8163928985596</t>
   </si>
   <si>
     <t xml:space="preserve">28.2807750701904</t>
   </si>
   <si>
-    <t xml:s